--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,22 +512,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 09:11:15</t>
+          <t>2026-06-01 05:22:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Ahmet Çakar'ın MASAK raporu ortaya çıktı: Hesaplarda milyonluk trafik, yurt dışı bahis ve 13 milyonluk zarar</t>
+          <t>Güney Kore: Çip fabrikasında çıkan yangın sonucu zehirli gaz sızıntısı meydana geldi.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ahmet Çakar'ın MASAK raporu ortaya çıktı: Hesaplarda milyonluk trafik, yurt dışı bahis ve 13 milyonluk zarar dokuz8HABER</t>
+          <t>Güney Kore: Çip fabrikasında çıkan yangın sonucu zehirli gaz sızıntısı meydana geldi. Vietnam.vn</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 11:03:05</t>
+          <t>2026-05-31 23:36:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -558,12 +558,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Elektrikli araç depolama tesisinde yangın çıktı, birçok varlık yok oldu.</t>
+          <t>Esenler'de Depo Yangını: 3 Bina Zarar Gördü</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Elektrikli araç depolama tesisinde yangın çıktı, birçok varlık yok oldu. Vietnam.vn</t>
+          <t>Esenler'de Depo Yangını: 3 Bina Zarar Gördü Son Dakika</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -571,8 +571,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Esenler</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
@@ -584,22 +592,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 20:01:15</t>
+          <t>2026-05-31 23:21:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Altın parıltılı dolaplar MASAK'ın merceğinde: 'Şirinler yöntemi' ile kredi kartı limitleri nakde dönüyor</t>
+          <t>İstanbul Esenler'de Bir Depoda Çıkan Yangın, Yanındaki İki Bina ile Üçüncü Bina Çatısını Zarar Verdi</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Altın parıltılı dolaplar MASAK'ın merceğinde: 'Şirinler yöntemi' ile kredi kartı limitleri nakde dönüyor Haberhergün</t>
+          <t>İstanbul Esenler'de Bir Depoda Çıkan Yangın, Yanındaki İki Bina ile Üçüncü Bina Çatısını Zarar Verdi Mersin Haber</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -607,8 +615,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Esenler</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
@@ -620,22 +636,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 16:11:00</t>
+          <t>2026-05-31 14:29:02</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek’ten Rasim Ozan Kütahyalı açıklaması: Süreç MASAK raporları doğrultusunda ilerliyor</t>
+          <t>Bankalar yarışa girdi, mevduat faiz oranları güncellendi! 250 bin TL’nin aylık getirisi belli oldu</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek’ten Rasim Ozan Kütahyalı açıklaması: Süreç MASAK raporları doğrultusunda ilerliyor Ortadoğu Gazetesi</t>
+          <t>Bankalar yarışa girdi, mevduat faiz oranları güncellendi! 250 bin TL’nin aylık getirisi belli oldu Halk TV</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -643,11 +659,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Adana</t>
-        </is>
-      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
@@ -660,7 +672,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 12:57:38</t>
+          <t>2026-06-01 08:10:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -670,12 +682,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de ikinci el eşyaların bulunduğu depoda çıkan yangın söndürüldü</t>
+          <t>Bursa Demirtaş Organize Sanayi Bölgesi'nde fabrika yangını</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de ikinci el eşyaların bulunduğu depoda çıkan yangın söndürüldü Habertürk</t>
+          <t>Bursa Demirtaş Organize Sanayi Bölgesi'nde fabrika yangını turkhaber.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -685,41 +697,45 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mersin | İstanbul | Tekirdağ | Van</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Beşiktaş | Erdemli | Saray</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Bursa Demirtaş Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Dumlupınar OSB</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 22:23:29</t>
+          <t>2026-06-01 07:36:33</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Trafikte ailenin yolunu kesip sürücüyü darbetti: 180 bin TL ceza, ehliyetine 60 gün el konuldu</t>
+          <t>Bursa'da fabrika yangını! Organize Sanayi Bölgesinde korku dolu anlar...</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Trafikte ailenin yolunu kesip sürücüyü darbetti: 180 bin TL ceza, ehliyetine 60 gün el konuldu SON TV</t>
+          <t>Bursa'da fabrika yangını! Organize Sanayi Bölgesinde korku dolu anlar... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -727,35 +743,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Bursa Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 13:18:30</t>
+          <t>2026-06-01 07:34:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi</t>
+          <t>Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Taşınmaz Haber</t>
+          <t>Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Mersin Haber</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -763,43 +791,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi</t>
-        </is>
-      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Adıyaman | Bursa | Düzce | İstanbul | Kars</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Merkez | Solhan | İnegöl | Osmangazi | Yıldırım</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Nakliyat Ve Toprak Sanayi Limited Şirketi</t>
+          <t>Şantiye</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 08:48:00</t>
+          <t>2026-06-01 08:23:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi!</t>
+          <t>Bursa'daki fabrika yangını korkuttu</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi! T24</t>
+          <t>Bursa'daki fabrika yangını korkuttu Türk İnform</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -820,22 +852,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 23:03:33</t>
+          <t>2026-06-01 09:43:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Brezilya'da Kripto Para Birimleri İçin Yeni Kurallar: Merkez Bankası, VASP'lerden Sıkı ve Bağımsız Denetimler Yapılmasını Talep Ediyor</t>
+          <t>Konkordato da kurtarmadı! Ünlü inşaat şirketi iflas etti</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Brezilya'da Kripto Para Birimleri İçin Yeni Kurallar: Merkez Bankası, VASP'lerden Sıkı ve Bağımsız Denetimler Yapılmasını Talep Ediyor Bitcoin News</t>
+          <t>Konkordato da kurtarmadı! Ünlü inşaat şirketi iflas etti Bursada Bugün</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -843,35 +875,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Ankara | Bursa</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Çakıroğulları İnşaat</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31 07:54:45</t>
+          <t>2026-06-01 08:12:34</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor</t>
+          <t>Türk inşaat devi bayramda iflas etti: Bölgede büyük ses getirdi</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Bitcoin News</t>
+          <t>Türk inşaat devi bayramda iflas etti: Bölgede büyük ses getirdi Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -879,11 +923,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Antalya</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
@@ -896,22 +936,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:04:42</t>
+          <t>2026-05-31 14:17:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Enerji krizi bir havacılık devini daha iflasa sürükledi</t>
+          <t>Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Enerji krizi bir havacılık devini daha iflasa sürükledi İlke Haber Ajansı</t>
+          <t>Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor T24</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -932,22 +972,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 08:54:45</t>
+          <t>2026-05-31 10:49:57</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Banka, dolandırıcılık şüphesiyle 4,4 trilyon VND'yi bloke etti.</t>
+          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Banka, dolandırıcılık şüphesiyle 4,4 trilyon VND'yi bloke etti. Vietnam.vn</t>
+          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Bitcoin News</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -968,22 +1008,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 11:04:00</t>
+          <t>2026-06-01 06:03:00</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Avusturya Kodlu Aramalara Dikkat: Yeni Nesil Dolandırıcılık Yöntemi Deşifre Edildi</t>
+          <t>134 yıllık şirketten iflas başvurusu</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Avusturya Kodlu Aramalara Dikkat: Yeni Nesil Dolandırıcılık Yöntemi Deşifre Edildi Personel Sağlık Personeli Haber NET</t>
+          <t>134 yıllık şirketten iflas başvurusu Gazete Oksijen</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1004,22 +1044,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 08:22:52</t>
+          <t>2026-06-01 05:36:00</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Mersin'deki Tekstil İşletmesinde Yangın</t>
+          <t>Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Mersin'deki Tekstil İşletmesinde Yangın Son Dakika</t>
+          <t>Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti Yeni Akit Gazetesi</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1027,16 +1067,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Mersin</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Toroslar</t>
-        </is>
-      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
@@ -1048,22 +1080,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:31:32</t>
+          <t>2026-06-01 10:12:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Ha Lam mahallesindeki bir depoda çıkan yangın derhal söndürüldü.</t>
+          <t>Buca'daki yolsuzluğun detayları ortaya çıktı: Belediyede "rüşvet fabrikası" kurmuşlar</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ha Lam mahallesindeki bir depoda çıkan yangın derhal söndürüldü. Vietnam.vn</t>
+          <t>Buca'daki yolsuzluğun detayları ortaya çıktı: Belediyede "rüşvet fabrikası" kurmuşlar Yirmidört Tv</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1084,22 +1116,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:11:10</t>
+          <t>2026-06-01 05:15:08</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Sarıgöl'de TARİŞ deposu önünde yangın: Ekipler sevk edildi</t>
+          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp…</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sarıgöl'de TARİŞ deposu önünde yangın: Ekipler sevk edildi Manisa Aktif Haber</t>
+          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1109,45 +1141,41 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Manisa</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Sarıgöl</t>
+          <t>Buca</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Tariş</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 08:15:17</t>
+          <t>2026-05-31 17:11:07</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de tekstil ürünleri satan işletmede çıkan yangın söndürüldü</t>
+          <t>Araştırmacı gazetecilik ağı, vize şirketi VFS Global'i mercek altına aldı: Rüşvet, bot yazılımlar, zorunlu ödemeler...</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de tekstil ürünleri satan işletmede çıkan yangın söndürüldü ensondakika.com.tr</t>
+          <t>Araştırmacı gazetecilik ağı, vize şirketi VFS Global'i mercek altına aldı: Rüşvet, bot yazılımlar, zorunlu ödemeler... Gazete Oksijen</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1155,47 +1183,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Mersin</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Toroslar</t>
-        </is>
-      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>MERSİN DEPO YAPI İNŞAAT MALZEMELERİ</t>
-        </is>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 19:34:42</t>
+          <t>2026-06-01 08:18:59</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Dev gıda şirketi iflas etti: 5 milyon dolarlık yatırım yapılmıştı</t>
+          <t>Buca Belediyesi’ne yolsuzluk operasyonu: Bankamatik memur sistemi ortaya çıktı</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Dev gıda şirketi iflas etti: 5 milyon dolarlık yatırım yapılmıştı Yeniçağ Gazetesi</t>
+          <t>Buca Belediyesi’ne yolsuzluk operasyonu: Bankamatik memur sistemi ortaya çıktı TRHaber</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1216,22 +1232,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 09:57:58</t>
+          <t>2026-05-31 14:56:22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Seattle merkezli pizzacı robot şirketi iflas etti</t>
+          <t>Muğla Ortaca’da Korku Dolu Anlar: Savrulan Araç Bankaya Daldı</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Seattle merkezli pizzacı robot şirketi iflas etti Ege Alternatif</t>
+          <t>Muğla Ortaca’da Korku Dolu Anlar: Savrulan Araç Bankaya Daldı Muğla Gazetesi</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1239,8 +1255,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Muğla</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Ortaca</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
@@ -1252,22 +1276,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:45:17</t>
+          <t>2026-06-01 07:41:24</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Peter Schiff: Soruşturmada herhangi bir suç tespit edilmemesine rağmen banka iflas idaresine alındı</t>
+          <t>Bursa'da Ermetal Fabrikası'nda Kaynak Kaynaklı Yangın Paniği: Maddi Hasar Var, Can Kaybı Yok</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Peter Schiff: Soruşturmada herhangi bir suç tespit edilmemesine rağmen banka iflas idaresine alındı Traders Union</t>
+          <t>Bursa'da Ermetal Fabrikası'nda Kaynak Kaynaklı Yangın Paniği: Maddi Hasar Var, Can Kaybı Yok Ege Alternatif</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1275,7 +1299,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1288,22 +1316,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31 06:34:22</t>
+          <t>2026-06-01 07:59:37</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Hollanda’da Uyuşturucu Davası: Quincy Promes’in 8 Milyon Euroluk Mal Varlığına El Konulması İsteniyor</t>
+          <t>Fabrikada korkutan yangın: Kaynak çalışması faciaya yol açıyordu</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Hollanda’da Uyuşturucu Davası: Quincy Promes’in 8 Milyon Euroluk Mal Varlığına El Konulması İsteniyor Turkinfo</t>
+          <t>Fabrikada korkutan yangın: Kaynak çalışması faciaya yol açıyordu Yeni Şafak</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1311,8 +1339,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Osmangazi</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
@@ -1324,22 +1360,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31 02:00:42</t>
+          <t>2026-06-01 06:51:07</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ülke genelinde birçok insan, kendilerini banka çalışanı olarak tanıtan dolandırıcıların düzenlediği sahtekarlıkların kurbanı oldu.</t>
+          <t>Ayvalık'ta Saman Deposunda Yangın</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Ülke genelinde birçok insan, kendilerini banka çalışanı olarak tanıtan dolandırıcıların düzenlediği sahtekarlıkların kurbanı oldu. Vietnam.vn</t>
+          <t>Ayvalık'ta Saman Deposunda Yangın Son Dakika</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1347,8 +1383,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Balıkesir</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Ayvalık</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
@@ -1360,22 +1404,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 17:00:00</t>
+          <t>2026-06-01 05:41:00</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki o bankaya dudak uçuklatan ceza!</t>
+          <t>Roket yakıtı fabrikasında yangın: Ölü ve yaralılar var</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki o bankaya dudak uçuklatan ceza! Düzce Damla Gazetesi</t>
+          <t>Roket yakıtı fabrikasında yangın: Ölü ve yaralılar var Nefes Gazetesi</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1396,22 +1440,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 21:29:21</t>
+          <t>2026-06-01 05:30:00</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Paranızı bankalardan tahsil edin! Akbank ve Garanti BBVA duyuru yaptı</t>
+          <t>Bir anda büyüdü! Depoda başlayan yangın çevredeki binaları sardı</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Paranızı bankalardan tahsil edin! Akbank ve Garanti BBVA duyuru yaptı Artı Gerçek</t>
+          <t>Bir anda büyüdü! Depoda başlayan yangın çevredeki binaları sardı Bursada Bugün</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1419,8 +1463,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Esenler</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
@@ -1432,7 +1484,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:12:00</t>
+          <t>2026-06-01 08:11:00</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1442,12 +1494,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Bankacılık Düzenleme ve Denetleme Kurumu Mesaj Yağmuruna Tutuldu!</t>
+          <t>Gaziantep'te bankalardan uyarı</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Bankacılık Düzenleme ve Denetleme Kurumu Mesaj Yağmuruna Tutuldu! Eskişehir Durum</t>
+          <t>Gaziantep'te bankalardan uyarı Gaziantep Oluşum Gazetesi</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1455,7 +1507,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1465,84 +1521,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30 09:05:01</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Fiziksel Risk / Yangın</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş'ta şantiye yangınında ağır yaralanan işçi hayatını kaybetti</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş'ta şantiye yangınında ağır yaralanan işçi hayatını kaybetti Saray Medya</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30 09:10:23</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Fiziksel Risk / Yangın</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Turizm sezonunun en yoğun olduğu dönemde yangın güvenliğinin sağlanması.</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Turizm sezonunun en yoğun olduğu dönemde yangın güvenliğinin sağlanması. Vietnam.vn</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J26"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -1569,8 +1549,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1582,7 +1560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1760,27 +1738,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 09:11:15</t>
+          <t>2026-06-01 05:22:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MASAK raporu</t>
+          <t>üretim tesisi yangını</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ahmet Çakar'ın MASAK raporu ortaya çıktı: Hesaplarda milyonluk trafik, yurt dışı bahis ve 13 milyonluk zarar</t>
+          <t>Güney Kore: Çip fabrikasında çıkan yangın sonucu zehirli gaz sızıntısı meydana geldi.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ahmet Çakar'ın MASAK raporu ortaya çıktı: Hesaplarda milyonluk trafik, yurt dışı bahis ve 13 milyonluk zarar dokuz8HABER</t>
+          <t>Güney Kore: Çip fabrikasında çıkan yangın sonucu zehirli gaz sızıntısı meydana geldi. Vietnam.vn</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1790,18 +1768,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Ahmet Çakar'ın MASAK raporu ortaya çıktı: Hesaplarda milyonluk trafik, yurt dışı bahis ve 13 milyonluk zarar dokuz8HABER</t>
+          <t>Güney Kore: Çip fabrikasında çıkan yangın sonucu zehirli gaz sızıntısı meydana geldi. Vietnam.vn</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Ahmet Çakar'ın MASAK raporu ortaya çıktı: Hesaplarda milyonluk trafik, yurt dışı bahis ve 13 milyonluk zarar Ahmet Çakar'ın MASAK raporu ortaya çıktı: Hesaplarda milyonluk trafik, yurt dışı bahis ve 13 milyonluk zarar dokuz8HABER Ahmet Çakar'ın MASAK raporu ortaya çıktı: Hesaplarda milyonluk trafik, yurt dışı bahis ve 13 milyonluk zarar dokuz8HABER</t>
+          <t>Güney Kore: Çip fabrikasında çıkan yangın sonucu zehirli gaz sızıntısı meydana geldi. Güney Kore: Çip fabrikasında çıkan yangın sonucu zehirli gaz sızıntısı meydana geldi. Vietnam.vn Güney Kore: Çip fabrikasında çıkan yangın sonucu zehirli gaz sızıntısı meydana geldi.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -1811,7 +1793,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOZDFIcUQ5bUNlYnYweDR5a1h1eWROQzZTZ3RkWW9tVkdRSUVEUXJVa2QxQjZBX0t3aTVxVFVZYmVlcDVSeGhlVE9Td3JOckFsXzJDLVZOUXNmRG5JRVZQVjNMNHhndnFNLWJSTEdXbzNhX1VqTUN5VnlWcTZ6VlkxdWd4eHBQNC13SFQzRVNrV1lUTF9XTGRpQnFfV3ZuMGdsRTZrY0VwQS1lT1ZrTzlVNTZBWVVranBkdXBCOVpKdDQ2VnVoOHlVZA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1QM2dzdXNWeGxUdTgxamtyMjE0b1Y2NzZ6R254VVVsay1ibHhrTl9rMHRPQUlmY3lJUjRESXV0OVVPYTBaUHpkWmliVlduN0U3UTdoa0JBWGtSRlVIMElnSWxKeTZVUS05RE05cUVWaS12Qi1iUlVuOWVuR2JZVEk?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
@@ -1837,7 +1819,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="n">
-        <v>101.2</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -1846,12 +1828,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 11:03:05</t>
+          <t>2026-05-31 23:36:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1861,12 +1843,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Elektrikli araç depolama tesisinde yangın çıktı, birçok varlık yok oldu.</t>
+          <t>Esenler'de Depo Yangını: 3 Bina Zarar Gördü</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Elektrikli araç depolama tesisinde yangın çıktı, birçok varlık yok oldu. Vietnam.vn</t>
+          <t>Esenler'de Depo Yangını: 3 Bina Zarar Gördü Son Dakika</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1876,7 +1858,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>depo, tesis</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1886,12 +1868,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>30 Mayıs öğleden sonra, Gia Lai İl Polis Müdürlüğü İtfaiye ve Kurtarma Birimi ekipleri, önemli miktarda mal kaybına neden olan elektrikli araç deposundaki yangın yerini hala kordon altına almış ve soruşturma yürütüyordu. 30 Mayıs öğleden sonra, Gia Lai İl Polis Müdürlüğü İtfaiye ve Kurtarma Birimi ekipleri, önemli miktarda mal kaybına neden olan elektrikli araç deposundaki yangın yerini hala kordon altına almış ve soruşturma yürütüyordu. 30 Mayıs öğleden sonra, Gia Lai İl Polis Müdürlüğü İtfaiye ve Kurtarma Birimi ekipleri, önemli miktarda mal kaybına neden olan elektrikli araç deposundaki yangın yerini hala kordon altına almış ve soruşturma yürütüyordu. Vietnam.vn'i takip et G o o g l e News 0 Aynı gün öğleden sonra saat 3 civarında, Gia Lai Eyaleti, Quy Nhon Mahallesi, Le Duc Tho Caddesi 2 numaradaki fabrika bölgesinde büyük bir yangın çıktı ve duman onlarca metre yüksekliğe yükseldi. Yangını fark eden yakındaki sakinler alevleri söndürmek için yardım çağrısında bulundu ve olayı yetkililere bildirdi. İtfaiyeciler olay yerine hızla ulaşarak yangını kontrol altına aldı ve yayılmasını önledi. Olayla ilgili bilgi alınmasının ardından, Yangın Önleme ve Kurtarma Polis Departmanı (Gia Lai İl Polisi), yangını söndürmek için olay yerine çok sayıda özel itfaiye aracı ve onlarca polis memuru ve asker sevk etti. Burada itfaiyeciler birkaç ekibe ayrılarak depoyu çevreleyen duvarları yıktılar ve hortumlarla doğrudan yangına su püskürttüler. Yaklaşık 15:30'da yangın büyük ölçüde kontrol altına alındı ​​ve bitişikteki spor salonuna ve pickleball sahasına yayılma ihtimali kalmadı. Deponun içinde küle dönmüş çok sayıda elektrikli araç vardı. Yangının yeniden alevlenmesini önlemek için yetkililer, yaklaşık 300 metrekarelik depoyu tamamen söndürmek amacıyla yüksek basınçlı su jetleri kullanmaya devam ediyor. Edinilen bilgilere göre, yangın bir elektrikli araç depolama tesisinde meydana geldi. Yangın sırasında depoda birkaç yüksek patlama sesi duyuldu ve siyah bir duman yükseldi. Yangın kontrol altına alındıktan sonra, depoda çok sayıda elektrikli aracın tamamen yanmış halde bulunduğu tespit edildi. Olayın sebebi ve hasarın boyutu yetkililer tarafından araştırılıyor. Chi Hao Kaynak: https://cand.vn/kho-chua-xe-dien-boc-chay-nhieu-tai-san-bi-thieu-rui-post812473.html Vietnam.vn'i takip et G o o g l e News 0 Yorum ( 0 ) En popüler En yeni Duygularınızı paylaşma</t>
+          <t>Esenler'deki depoda çıkan yangın, 3 binanın dış cephesine sıçrayarak itfaiye tarafından söndürüldü. Esenler'deki depoda çıkan yangın, 3 binanın dış cephesine sıçrayarak itfaiye tarafından söndürüldü. Esenler'deki depoda çıkan yangın, 3 binanın dış cephesine sıçrayarak itfaiye tarafından söndürüldü. Esenler'de Depo Yangını: 3 Bina Zarar Gördü Son Güncelleme: 01.06.2026 02:36 Esenler'deki depoda çıkan yangın, 3 binanın dış cephesine sıçrayarak itfaiye tarafından söndürüldü. Esenler 'de bir depoda çıkan ve 3 binanın dış cephesi ile bir çatıya sıçrayan yangın itfaiye ekiplerince söndürüldü. Atışalanı Mahallesi Gaye Sokak'ta içinde iplik rulosu ve hurda eşyaların bulunduğu depoda henüz bilinmeyen bir nedenle yangın çıktı. Kısa sürede büyüyen alevler deponun yanındaki 3 binanın dış cephesine ve bir çatıya sıçradı. Vatandaşların ihbarı üzerine bölgeye itfaiye, polis ve sağlık ekipleri sevk edildi. Polis ekipleri şerit çekerek çevrede güvenlik önlemi aldı. Yangın, itfaiyenin müdahalesiyle söndürüldü. Yangın nedeniyle depo kullanılamaz hale gelirken, binaların dış cephesi ve çatı da zarar gördü. Ekipler, yangının çıkış sebebini belirlemek üzere çalışma başlattı. Kaynak: AA Esenler 'de bir depoda çıkan ve 3 binanın dış cephesi ile bir çatıya sıçrayan yangın itfaiye ekiplerince söndürüldü. Atışalanı Mahallesi Gaye Sokak'ta içinde iplik rulosu ve hurda eşyaların bulunduğu depoda henüz bilinmeyen bir nedenle yangın çıktı. Kısa sürede büyüyen alevler deponun yanındaki 3 binanın dış cephesine ve bir çatıya sıçradı. Vatandaşların ihbarı üzerine bölgeye itfaiye, polis ve sağlık ekipleri sevk edildi. Polis ekipleri şerit çekerek çevrede güvenlik önlemi aldı. Yangın, itfaiyenin müdahalesiyle söndürüldü. Yangın nedeniyle depo kullanılamaz hale gelirken, binaların dış cephesi ve çatı da zarar gördü. Ekipler, yangının çıkış sebebini belirlemek üzere çalışma başlattı. Esenler'de Depo Yangını: 3 Bina Zarar Gördü Esenler'deki depoda çıkan yangın, 3 binanın dış cephesine sıçrayarak itfaiye tarafından söndürüldü. Esenler 'de bir depoda çıkan ve 3 binanın dış cephesi ile bir çatıya sıçrayan yangın itfaiye ekiplerince söndürüldü. Atışalanı Mahallesi Gaye Sokak'ta içinde iplik rulosu ve hurda eşyaların bulunduğu depoda henüz bilinmeyen bir nedenle yangın çıktı. Kısa sürede büyüyen alevler deponun yanındaki 3 binanın dış cephesine ve bir çatıya sıçradı. Vatandaşların ihbarı üzerine bölgeye itfaiye, polis ve sağlık ekipleri sevk edildi. Polis ekipleri şerit çekerek çevrede güvenlik önlemi aldı. Yangın, itfaiyenin müdahalesiyle söndürüldü. Yangın nedeniyle depo kullanılamaz hale gelirken, binaların dış cephesi ve çatı da zarar gördü. Ekipler, yangının çıkış sebebini belirlemek üzere çalışma başlattı.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Elektrikli araç depolama tesisinde yangın çıktı, birçok varlık yok oldu. Elektrikli araç depolama tesisinde yangın çıktı, birçok varlık yok oldu. Vietnam.vn 30 Mayıs öğleden sonra, Gia Lai İl Polis Müdürlüğü İtfaiye ve Kurtarma Birimi ekipleri, önemli miktarda mal kaybına neden olan elektrikli araç deposundaki yangın yerini hala kordon altına almış ve soruşturma yürütüyordu. Vietnam.vn'i takip et G o o g l e News 0 Aynı gün öğleden sonra saat 3 civarında, Gia Lai Eyaleti, Quy Nhon Mahallesi, Le Duc Tho Caddesi 2 numaradaki fabrika bölgesinde büyük bir yangın çıktı ve duman onlarca metre yüksekliğe yükseldi. Yangını fark eden yakındaki sakinler alevleri söndürmek için yardım çağrısında bulundu ve olayı yetkililere bildirdi. İtfaiyeciler olay yerine hızla ulaşarak yangını kontrol altına aldı ve yayılmasını önledi. Olayla ilgili bilgi alınmasının ardından, Yangın Önleme ve Kurtarma Polis Departmanı (Gia Lai İl Polisi), yangını söndürmek için olay yerine çok sayıda özel itfaiye aracı ve onlarca polis memuru ve asker sevk etti. Burada itfaiyeciler birkaç ekibe ayrılarak depoyu çevreleyen duvarları yıktılar ve hortumlarla doğrudan yangına su püskürttüler. Yaklaşık 15:30'da yangın büyük ölçüde kontrol altına alındı ​​ve bitişikteki spor salonuna ve pickleball sahasına yayılma ihtimali kalmadı. Deponun içinde küle dönmüş çok sayıda elektrikli araç vardı. Yangının yeniden alevlenmesini önlemek için yetkililer, yaklaşık 300 metrekarelik depoyu tamamen söndürmek amacıyla yüksek basınçlı su jetleri kullanmaya devam ediyor. Edinilen bilgilere göre, yangın bir elektrikli araç depolama tesisinde meydana geldi. Yangın sırasında depoda birkaç yüksek patlama sesi duyuldu ve siyah bir duman yükseldi. Yangın kontrol altına alındıktan sonra, depoda çok sayıda elektrikli aracın tamamen yanmış halde bulunduğu tespit edildi. Olayın sebebi ve hasarın boyutu yetkililer tarafından araştırılıyor.</t>
+          <t>Esenler'de Depo Yangını: 3 Bina Zarar Gördü Esenler'de Depo Yangını: 3 Bina Zarar Gördü Son Dakika Esenler'deki depoda çıkan yangın, 3 binanın dış cephesine sıçrayarak itfaiye tarafından söndürüldü. Esenler'de Depo Yangını: 3 Bina Zarar Gördü Son Güncelleme: 01.06.2026 02:36 Esenler'deki depoda çıkan yangın, 3 binanın dış cephesine sıçrayarak itfaiye tarafından söndürüldü. Esenler 'de bir depoda çıkan ve 3 binanın dış cephesi ile bir çatıya sıçrayan yangın itfaiye ekiplerince söndürüldü. Atışalanı Mahallesi Gaye Sokak'ta içinde iplik rulosu ve hurda eşyaların bulunduğu depoda henüz bilinmeyen bir nedenle yangın çıktı. Kısa sürede büyüyen alevler deponun yanındaki 3 binanın dış cephesine ve bir çatıya sıçradı. Vatandaşların ihbarı üzerine bölgeye itfaiye, polis ve sağlık ekipleri sevk edildi. Polis ekipleri şerit çekerek çevrede güvenlik önlemi aldı. Yangın, itfaiyenin müdahalesiyle söndürüldü. Yangın nedeniyle depo kullanılamaz hale gelirken, binaların dış cephesi ve çatı da zarar gördü. Ekipler, yangının çıkış sebebini belirlemek üzere çalışma başlattı. Kaynak: AA Esenler 'de bir depoda çıkan ve 3 binanın dış cephesi ile bir çatıya sıçrayan yangın itfaiye ekiplerince söndürüldü. Esenler'de Depo Yangını: 3 Bina Zarar Gördü Esenler'deki depoda çıkan yangın, 3 binanın dış cephesine sıçrayarak itfaiye tarafından söndürüldü.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -1901,27 +1883,31 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.vietnam.vn/tr/kho-chua-xe-dien-boc-chay-nhieu-tai-san-bi-thieu-rui</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>https://www.sondakika.com/amp/haber-esenler-de-depo-yangini-3-bina-zarar-gordu-19897635/</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Esenler</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Quy Nhon Mahallesi</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Le Duc Tho Caddesi</t>
-        </is>
-      </c>
+          <t>Atışalanı Mahallesi</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
@@ -1935,7 +1921,7 @@
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="n">
-        <v>121.75</v>
+        <v>108</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>2</v>
@@ -1944,27 +1930,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 20:01:15</t>
+          <t>2026-05-31 23:21:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>para aklama</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Altın parıltılı dolaplar MASAK'ın merceğinde: 'Şirinler yöntemi' ile kredi kartı limitleri nakde dönüyor</t>
+          <t>İstanbul Esenler'de Bir Depoda Çıkan Yangın, Yanındaki İki Bina ile Üçüncü Bina Çatısını Zarar Verdi</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Altın parıltılı dolaplar MASAK'ın merceğinde: 'Şirinler yöntemi' ile kredi kartı limitleri nakde dönüyor Haberhergün</t>
+          <t>İstanbul Esenler'de Bir Depoda Çıkan Yangın, Yanındaki İki Bina ile Üçüncü Bina Çatısını Zarar Verdi Mersin Haber</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1974,18 +1960,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Altın parıltılı dolaplar MASAK'ın merceğinde: 'Şirinler yöntemi' ile kredi kartı limitleri nakde dönüyor Haberhergün</t>
+          <t>İstanbul Esenler'de Bir Depoda Çıkan Yangın, Yanındaki İki Bina ile Üçüncü Bina Çatısını Zarar Verdi Mersin Haber</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Altın parıltılı dolaplar MASAK'ın merceğinde: 'Şirinler yöntemi' ile kredi kartı limitleri nakde dönüyor Altın parıltılı dolaplar MASAK'ın merceğinde: 'Şirinler yöntemi' ile kredi kartı limitleri nakde dönüyor Haberhergün Altın parıltılı dolaplar MASAK'ın merceğinde: 'Şirinler yöntemi' ile kredi kartı limitleri nakde dönüyor Haberhergün</t>
+          <t>İstanbul Esenler'de Bir Depoda Çıkan Yangın, Yanındaki İki Bina ile Üçüncü Bina Çatısını Zarar Verdi İstanbul Esenler'de Bir Depoda Çıkan Yangın, Yanındaki İki Bina ile Üçüncü Bina Çatısını Zarar Verdi Mersin Haber İstanbul Esenler'de Bir Depoda Çıkan Yangın, Yanındaki İki Bina ile Üçüncü Bina Çatısını Zarar Verdi Mersin Haber</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1995,11 +1985,19 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOUkd2OTdKTlFOQlNhUkdDZ1dGcnhMVzFFa204a255bzZ3d1dlY2EyUXNBcTNuSUhLMUIzdUpTcU1nQWY1OE5QbUQ3bHlPMGM4NDRHZXZFUm5aYWpTRG5HNGFrWThPWV9UdlRaaHFEb1RPZ29DQkJlVlhsU0FnWkxkS1Q1aE8tLUFZckdFRG9wM01UUmloUjNJcWxYWXJ5eTJWNnhOQ1dEQ0p3d1lxcWhnYmNuaTdJZlhmcURHQmpQNkJyclpqM1dKc0lIRnpZWjQzODdoUjJBUXJtQQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNMHpvdF90TFViMXI5U0NLQXRyLTljNXJuX05MVEZtS2UyU01Yd1ZSNHI4TldEREczZFpyNUNUamlPRWF5Y2F2MjJmcWJscHd1OGpfemI1YUM0VWRidXZQdVZ6OXZIWFI4SVZFQ2pOcVJyc2ZWQ1RtdXdSRkFTOFFRVXJHcUV6WEZKZkRubllSM0VtZklXRDJ5dkV0RE5XaVFRRGpVbGdOZ0twaVVvbE52ZDRnYzAxMzFlUGdtOVBrMmp3ZmRVREF1VjJIYUFzTnJ2dm1jTENB0gFXQVVfeXFMT21mSVE3WDYxS2tHV0NLelUyUWYzMEU4Mk9EaFlRZnJlSUMyQTVkT1U3akJ1N1pyejNnM1ZJODFncnQ0emNGTEU0d2h5T0ZlRk9yZGp5dmlB?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Esenler</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -2007,7 +2005,7 @@
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr"/>
@@ -2021,7 +2019,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="n">
-        <v>98.16</v>
+        <v>123.38</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>3</v>
@@ -2030,27 +2028,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 16:11:00</t>
+          <t>2026-05-31 14:29:02</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>borç krizi</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek’ten Rasim Ozan Kütahyalı açıklaması: Süreç MASAK raporları doğrultusunda ilerliyor</t>
+          <t>Bankalar yarışa girdi, mevduat faiz oranları güncellendi! 250 bin TL’nin aylık getirisi belli oldu</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek’ten Rasim Ozan Kütahyalı açıklaması: Süreç MASAK raporları doğrultusunda ilerliyor Ortadoğu Gazetesi</t>
+          <t>Bankalar yarışa girdi, mevduat faiz oranları güncellendi! 250 bin TL’nin aylık getirisi belli oldu Halk TV</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2060,35 +2058,35 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0Adalet Bakanı Akın Gürlek, yasa dışı bahis soruşturması kapsamında tutuklanan gazeteci ve televizyon yorumcusu Rasim Ozan Kütahyalı hakkında açıklamalarda bulundu. Kabine Toplantısı sonrasında gazetecilerin sorularını yanıtlayan Gürlek, yürütülen soruşturmanın kapsamlı bir mali incelemeye dayandığını belirtti. Gürlek, soruşturmanın Adana Cumhuriyet Başsavcılığı tarafından yürütüldüğünü ve sürecin tamamen Mali Suçları Araştırma Kurulu'nun hazırladığı raporlar doğrultusunda ilerlediğini ifade etti. “MASAK takibine takılmış durumda” Bakan Gürlek, soruşturma kapsamında para hareketlerinin incelendiğini belirterek, Kütahyalı'nın mali işlemler sırasında MASAK incelemesine takıldığını söyledi. Açıklamada, yasa dışı bahis sitelerine para gönderme ve aracılık etme iddialarının bulunduğu ifade edildi. Gürlek, başsavcılığın mali hareketleri değerlendirerek kendi takdiri doğrultusunda işlem yaptığını belirtti. Soruşturmanın yargı makamları tarafından yürütüldüğünü vurguladı. Yasa dışı bahisle mücadele vurgusu Adalet Bakanı, mevcut mevzuata göre yasa dışı bahis oynatan, buna aracılık eden, yer ve imkân sağlayan ya da bu sitelere para transferi gerçekleştiren kişilerin suç işlediğini hatırlattı. Yasa dışı bahis organizasyonlarına yönelik mücadelenin kararlılıkla sürdürüldüğünü ifade etti. Gürlek, dijital platformlar üzerinden faaliyet gösteren yasa dışı bahis ağlarına karşı erişim engelleme kararlarının hızlı şekilde uygulandığını da belirtti. Yurt dışındaki şüpheliler için adli süreç sürüyor Soruşturma kapsamında yurt dışında bulunan şüphelilere yönelik işlemlerin de devam ettiğini açıklayan Gürlek, bazı isimler hakkında kırmızı bülten çıkarıldığını söyledi. Açıklamada, yasa dışı bahis organizasyonlarında adı geçen kişilere yönelik hukuki süreçlerin kesintisiz sürdüğü vurgulandı. Yetkililer, soruşturmanın çok yönlü şekilde devam ettiğini ve mali hareketlerin ayrıntılı olarak incelendiğini belirtiyor. Gözler soruşturmanın ilerleyen aşamalarında Kamuoyunda geniş yankı uyandıran soruşturmaya ilişkin süreç devam ederken, dosyaya ilişkin yeni gelişmelerin yargı makamlarının yapacağı değerlendirmeler sonucunda netleşmesi bekleniyor. Yetkililer, yasa dışı bahisle mücadelede hem mali hem de dijital takip mekanizmalarının etkin şekilde kullanılmaya devam edeceğini ifade ediyor. İstanbul Açık 19° Adana Adıyaman Afyonkarahisar Ağrı Amasya Ankara Antalya Artvin Aydın Balıkesir Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Isparta Mersin İstanbul İzmir Kars Kastamonu Kayseri Kırklareli Kırşehir Kocaeli Konya Kütahya Malatya Manisa Kahramanmaraş Mardin Muğla Muş Nevşehir Niğde Ordu Rize Sakarya Samsun Siirt Sinop Sivas Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yozgat Zonguldak Aksaray Bayburt Karaman Kırıkkale Batman Şırnak Bartın Ardahan Iğdır Yalova Karabük Kilis Osmaniye Düzce Emine Koç Genel Yayın Yönetmeni Ortadoğu Gazetesi artık WhatsApp’ta! Gündemin en önemli gelişmeleri anında cebinize gelsin istiyorsanız tıklayın ve katılın. Pay</t>
+          <t>Bankalar, müşteri kazanmak amacıyla mevduat faiz oranlarını güncellemeyi sürdürüyor. Değişen oranlarla birlikte 250 bin TL’lik birikimin 32 günlük getirisi de bankalara göre farklı seviyelere ulaştı. Bankalar, müşteri kazanmak amacıyla mevduat faiz oranlarını güncellemeyi sürdürüyor. Değişen oranlarla birlikte 250 bin TL’lik birikimin 32 günlük getirisi de bankalara göre farklı seviyelere ulaştı. Bankalar, müşteri kazanmak amacıyla mevduat faiz oranlarını güncellemeyi sürdürüyor. Değişen oranlarla birlikte 250 bin TL’lik birikimin 32 günlük getirisi de bankalara göre farklı seviyelere ulaştı.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek’ten Rasim Ozan Kütahyalı açıklaması: Süreç MASAK raporları doğrultusunda ilerliyor Bakan Gürlek’ten Rasim Ozan Kütahyalı açıklaması: Süreç MASAK raporları doğrultusunda ilerliyor Ortadoğu Gazetesi 0Adalet Bakanı Akın Gürlek, yasa dışı bahis soruşturması kapsamında tutuklanan gazeteci ve televizyon yorumcusu Rasim Ozan Kütahyalı hakkında açıklamalarda bulundu. Kabine Toplantısı sonrasında gazetecilerin sorularını yanıtlayan Gürlek, yürütülen soruşturmanın kapsamlı bir mali incelemeye dayandığını belirtti. Gürlek, soruşturmanın Adana Cumhuriyet Başsavcılığı tarafından yürütüldüğünü ve sürecin tamamen Mali Suçları Araştırma Kurulu'nun hazırladığı raporlar doğrultusunda ilerlediğini ifade etti. “MASAK takibine takılmış durumda” Bakan Gürlek, soruşturma kapsamında para hareketlerinin incelendiğini belirterek, Kütahyalı'nın mali işlemler sırasında MASAK incelemesine takıldığını söyledi. Açıklamada, yasa dışı bahis sitelerine para gönderme ve aracılık etme iddialarının bulunduğu ifade edildi. Gürlek, başsavcılığın mali hareketleri değerlendirerek kendi takdiri doğrultusunda işlem yaptığını belirtti. Soruşturmanın yargı makamları tarafından yürütüldüğünü vurguladı. Yasa dışı bahisle mücadele vurgusu Adalet Bakanı, mevcut mevzuata göre yasa dışı bahis oynatan, buna aracılık eden, yer ve imkân sağlayan ya da bu sitelere para transferi gerçekleştiren kişilerin suç işlediğini hatırlattı. Yasa dışı bahis organizasyonlarına yönelik mücadelenin kararlılıkla sürdürüldüğünü ifade etti. Gürlek, dijital platformlar üzerinden faaliyet gösteren yasa dışı bahis ağlarına karşı erişim engelleme kararlarının hızlı şekilde uygulandığını da belirtti. Yurt dışındaki şüpheliler için adli süreç sürüyor Soruşturma kapsamında yurt dışında bulunan şüphelilere yönelik işlemlerin de devam ettiğini açıklayan Gürlek, bazı isimler hakkında kırmızı bülten çıkarıldığını söyledi. Açıklamada, yasa dışı bahis organizasyonlarında adı geçen kişilere yönelik hukuki süreçlerin kesintisiz sürdüğü vurgulandı. Yetkililer, soruşturmanın çok yönlü şekilde devam ettiğini ve mali hareketlerin ayrıntılı olarak incelendiğini belirtiyor. Gözler soruşturmanın ilerleyen aşamalarında Kamuoyunda geniş yankı uyandıran soruşturmaya ilişkin süreç devam ederken, dosyaya ilişkin yeni gelişmelerin yargı makamlarının yapacağı değerlendirmeler sonucunda netleşmesi bekleniyor. Yetkililer, yasa dışı bahisle mücadelede hem mali hem de dijital takip mekanizmalarının etkin şekilde kullanılmaya devam edeceğini ifade ediyor. İstanbul Açık 19° Adana Adıyaman Afyonkarahisar Ağrı Amasya Ankara Antalya Artvin Aydın Balıkesir Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Isparta Mersin İstanbul İzmir Kars Kastamonu Kayseri Kırklareli Kırşehir Kocaeli Konya Kütahya Malatya Manisa Kahramanmaraş Mardin Muğla Muş Nevşehir Niğde Ordu Rize Sakarya Samsun Siirt Sinop Sivas Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yozgat Zonguldak Aksaray Bayburt Karaman Kırıkkale Batman Şırnak Bartın Ardahan Iğdır Yalova Karabük Kilis Osmaniye Düzce Emine Koç Genel Yayın Yönetmeni Ortadoğu Gazetesi artık WhatsApp’ta!</t>
+          <t>Bankalar yarışa girdi, mevduat faiz oranları güncellendi! 250 bin TL’nin aylık getirisi belli oldu Bankalar yarışa girdi, mevduat faiz oranları güncellendi! 250 bin TL’nin aylık getirisi belli oldu Halk TV Bankalar, müşteri kazanmak amacıyla mevduat faiz oranlarını güncellemeyi sürdürüyor. Değişen oranlarla birlikte 250 bin TL’lik birikimin 32 günlük getirisi de bankalara göre farklı seviyelere ulaştı.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOZUxYdHJCOVc4WHBjdFlUQXJDUnAzWFJpTmtBY04zb2hmVllTVkZwQTdSMkd6VVJUcE9wN1BuR0tNVmlUNm8yTF9WRVZHc1NwVmpENURoYmFSbDF3SWRDaTZWLS1TVlV3cWdPSEhVTHMwWHJ1VndZSm5GOERlLVlEQUgwaWpBX1c5RV9MbVVaX1VMZXMwdWg4MUYzeVNWTzdWR3RFdGJJSWNoVnRrWmlrZUk4Q3JLeEFPWEExdFhQQlRidHpSY1ZwT2Rwblk1TnNjUDZ6cmlZSXROYlc0U2t2alRLNA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Adana</t>
-        </is>
-      </c>
+          <t>https://halktv.com.tr/ekonomi/bankalar-yarisa-girdi-mevduat-faiz-oranlari-guncellendi-250-bin-tlnin-aylik-getirisi-belli-oldu-1033049h</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
@@ -2097,7 +2095,7 @@
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr"/>
@@ -2111,7 +2109,7 @@
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="n">
-        <v>116.75</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>4</v>
@@ -2120,12 +2118,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 12:57:38</t>
+          <t>2026-06-01 08:10:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2135,12 +2133,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de ikinci el eşyaların bulunduğu depoda çıkan yangın söndürüldü</t>
+          <t>Bursa Demirtaş Organize Sanayi Bölgesi'nde fabrika yangını</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de ikinci el eşyaların bulunduğu depoda çıkan yangın söndürüldü Habertürk</t>
+          <t>Bursa Demirtaş Organize Sanayi Bölgesi'nde fabrika yangını turkhaber.com</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -2150,70 +2148,94 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>fabrika, organize sanayi, sanayi</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Mersin'in Erdemli ilçesinde ikinci el eşyaların satıldığı iş yerinin deposunda çıkan yangın itfaiye ekiplerince söndürüldü. Kılıçdaroğlu CHP Genel Merkezi'nde "Kurultaydan korkmuyorum ön seçim de istiyorum" Alkollü magandanın kurşunu, genç kızı hayattan kopardı Trabzonspor'da transferde mutlu son! Kadın yazarı yeğeni miras için öldürdü! Avrupa'daki en iyi 10 plajından biri Türkiye'de Şampiyonlar Ligi'nde dev final! Yüzlerce kişi bir anda fenalaştı, nedeni 46 yıldır bulunamadı! G.Saray'dan Curtis Jones hamlesi! Ozan Güven'e tepki: Failler dışarı Tarihin unutulan nükleer felaketi "Yorum yapmam, benim de ilişkim var" Hükümeti protesto etmek için bağımsızlık ilan eden kasaba Beşiktaş'ta tek gündem yeni hoca! Anne ve 2 çocuğu öldü, 4 kişi yaralandı Norveç'te bulunan kadının kimliği hâlâ çözülemedi TEM Otoyolu ve D-100'de uzun araç kuyrukları! Erkek şiddeti her yerde... Kadın dayanışması! İşyerinin arkasındaki eşyalar yandı, çevreyi kara dumanlar kapladı Mersin'de kuşaklar aynı sahnede buluştu Mersin'de kurban kesim alanlarında bayram temizliği Mersin'de iş yeri yangını, ekiplerin zamanında müdahalesiyle söndürüldü Dolu, kayısı ve zeytinlere zarar verdi Kardeşlerin çifte mutluluğu: Aynı gün evlenip, birbirlerine şahit oldular Mersin'de ikinci el eşyaların bulunduğu depoda çıkan yangın söndürüldü Mersin'in Erdemli ilçesinde ikinci el eşyaların satıldığı iş yerinin deposunda çıkan yangın itfaiye ekiplerince söndürüldü. Mersin'in Erdemli ilçesinde ikinci el eşyaların satıldığı iş yerinin deposunda çıkan yangın itfaiye ekiplerince söndürüldü. Serinler Caddesi'ndeki işletmenin depo bölümünde henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine bölgeye 112 Acil Sağlık, polis ve itfaiye ekipleri sevk edildi. İtfaiye ekiplerin müdahalesiyle söndürülen yangın nedeniyle depoda hasar oluştu. Anadolu Ajansı, DHA ve İHA tarafından geçilen tüm Mersin haberleri, bu bölümde Haberturk.com editörlerinin hiçbir editoryal müdahalesi olmadan otomatik olarak ajans kanallarından geldiği şekliyle yer almaktadır. Mersin Haberleri alanında yer alan haberlerin hepsinin hukuki muhatabı haberi geçen ajanslardır.</t>
+          <t>Bursa Demirtaş Organize Sanayi Bölgesi'nde fabrika yangını turkhaber.com</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de ikinci el eşyaların bulunduğu depoda çıkan yangın söndürüldü Mersin'de ikinci el eşyaların bulunduğu depoda çıkan yangın söndürüldü Habertürk Mersin'in Erdemli ilçesinde ikinci el eşyaların satıldığı iş yerinin deposunda çıkan yangın itfaiye ekiplerince söndürüldü. Kılıçdaroğlu CHP Genel Merkezi'nde "Kurultaydan korkmuyorum ön seçim de istiyorum" Alkollü magandanın kurşunu, genç kızı hayattan kopardı Trabzonspor'da transferde mutlu son! Kadın yazarı yeğeni miras için öldürdü! Avrupa'daki en iyi 10 plajından biri Türkiye'de Şampiyonlar Ligi'nde dev final! Yüzlerce kişi bir anda fenalaştı, nedeni 46 yıldır bulunamadı! G.Saray'dan Curtis Jones hamlesi! Ozan Güven'e tepki: Failler dışarı Tarihin unutulan nükleer felaketi "Yorum yapmam, benim de ilişkim var" Hükümeti protesto etmek için bağımsızlık ilan eden kasaba Beşiktaş'ta tek gündem yeni hoca! Anne ve 2 çocuğu öldü, 4 kişi yaralandı Norveç'te bulunan kadının kimliği hâlâ çözülemedi TEM Otoyolu ve D-100'de uzun araç kuyrukları! Erkek şiddeti her yerde... İşyerinin arkasındaki eşyalar yandı, çevreyi kara dumanlar kapladı Mersin'de kuşaklar aynı sahnede buluştu Mersin'de kurban kesim alanlarında bayram temizliği Mersin'de iş yeri yangını, ekiplerin zamanında müdahalesiyle söndürüldü Dolu, kayısı ve zeytinlere zarar verdi Kardeşlerin çifte mutluluğu: Aynı gün evlenip, birbirlerine şahit oldular Mersin'de ikinci el eşyaların bulunduğu depoda çıkan yangın söndürüldü Mersin'in Erdemli ilçesinde ikinci el eşyaların satıldığı iş yerinin deposunda çıkan yangın itfaiye ekiplerince söndürüldü. Serinler Caddesi'ndeki işletmenin depo bölümünde henüz belirlenemeyen nedenle yangın çıktı. İtfaiye ekiplerin müdahalesiyle söndürülen yangın nedeniyle depoda hasar oluştu. Anadolu Ajansı, DHA ve İHA tarafından geçilen tüm Mersin haberleri, bu bölümde Haberturk.com editörlerinin hiçbir editoryal müdahalesi olmadan otomatik olarak ajans kanallarından geldiği şekliyle yer almaktadır. Mersin Haberleri alanında yer alan haberlerin hepsinin hukuki muhatabı haberi geçen ajanslardır.</t>
+          <t>Bursa Demirtaş Organize Sanayi Bölgesi'nde fabrika yangını Bursa Demirtaş Organize Sanayi Bölgesi'nde fabrika yangını turkhaber.com Bursa Demirtaş Organize Sanayi Bölgesi'nde fabrika yangını turkhaber.com</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.haberturk.com/yerel-haberler/mersin-haberleri/mersinde-ikinci-el-esyalarin-bulundugu-depoda-cikan-yangin-sonduruldu-41532920</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPc1kxSHMzZnF5LWdKWVh5am05cEM3LTVrRlNBckJ0UEFIVzhQcDdnVllRa1hMbUpiWjF1dllPb1o2bUpFeF9tUEtKcVVPMHpwR3RQVGV6enhsajVyN296dVBkcWltZktLTzBjem9hMS1nZFJpRUU1NjFFSW12cVpuekRjbnkxOWNkUzdIRUlia3FCdFNSeHRJeHRKVEhxbkk0SEE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Mersin | İstanbul | Tekirdağ | Van</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Beşiktaş | Erdemli | Saray</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Serinler Caddesi</t>
-        </is>
-      </c>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş | Bursa Demirtaş Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Bursa Demirtaş Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Bursa Demirtaş Organize Sanayi:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Bursa Demirtaş Organize Sanayi Demirtaş Bursa Türkiye</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Dumlupınar OSB | Demirtaş | Demirtaş Organize Sanayi Cami</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Dumlupınar OSB</t>
+        </is>
+      </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>52.83018867924528 | 100.0 | 90.56603773584905</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>DOSAB Bölge Müdürlüğü | DOSAB OSGB</t>
+        </is>
+      </c>
       <c r="AA6" s="2" t="n">
-        <v>118</v>
+        <v>193.72</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>5</v>
@@ -2222,27 +2244,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 22:23:29</t>
+          <t>2026-06-01 07:36:33</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>bahis operasyonu</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Trafikte ailenin yolunu kesip sürücüyü darbetti: 180 bin TL ceza, ehliyetine 60 gün el konuldu</t>
+          <t>Bursa'da fabrika yangını! Organize Sanayi Bölgesinde korku dolu anlar...</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Trafikte ailenin yolunu kesip sürücüyü darbetti: 180 bin TL ceza, ehliyetine 60 gün el konuldu SON TV</t>
+          <t>Bursa'da fabrika yangını! Organize Sanayi Bölgesinde korku dolu anlar... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -2252,18 +2274,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>fabrika, organize sanayi, sanayi</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Trafikte ailenin yolunu kesip sürücüyü darbetti: 180 bin TL ceza, ehliyetine 60 gün el konuldu SON TV</t>
+          <t>Bursa'da fabrika yangını! Organize Sanayi Bölgesinde korku dolu anlar... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Trafikte ailenin yolunu kesip sürücüyü darbetti: 180 bin TL ceza, ehliyetine 60 gün el konuldu Trafikte ailenin yolunu kesip sürücüyü darbetti: 180 bin TL ceza, ehliyetine 60 gün el konuldu SON TV Trafikte ailenin yolunu kesip sürücüyü darbetti: 180 bin TL ceza, ehliyetine 60 gün el konuldu SON TV</t>
+          <t>Bursa'da fabrika yangını! Organize Sanayi Bölgesinde korku dolu anlar... Bursa'da fabrika yangını! Organize Sanayi Bölgesinde korku dolu anlar... Bursa Hakimiyet Bursa'da fabrika yangını! Organize Sanayi Bölgesinde korku dolu anlar...</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2273,33 +2299,61 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.son.tv/trafikte-ailenin-yolunu-kesip-surucuyu-darbetti-180-bin-tl-ceza-ehliyetine-60-gun-el-konuldu/amp/</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>https://www.bursahakimiyet.com.tr/bursa/bursa-da-fabrika-yangini-organize-sanayi-bolgesinde-korku-dolu-anlar-1640063</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Organize Sanayi:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Organize Sanayi Bursa Türkiye</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bursa Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Bursa Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="n">
-        <v>89.26000000000001</v>
+        <v>190.88</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>6</v>
@@ -2308,27 +2362,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 13:18:30</t>
+          <t>2026-06-01 07:34:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi</t>
+          <t>Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Taşınmaz Haber</t>
+          <t>Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Mersin Haber</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -2338,82 +2392,90 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Ana Sayfa › Şirket Haberleri › Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Kartal Hafriyat konkordato sürecine ilişkin yeni mahkeme kararı kamuoyuyla paylaşılmıştır. Ankara 2. Asliye Ticaret Mahkemesi tarafından görülen dava kapsamında şirket ve şirket ortakları hakkında kesin mühlet kararı verilmiştir. Mahkemenin 2025/972 Esas sayılı dosyada aldığı karara göre, Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi ile şirket ortakları Nuri Kartal ve Mustafa Kartal için konkordato sürecinin devamına hükmedilmiştir. Karar, 22 Mayıs 2026 tarihinde açıklanmıştır. Mahkeme 1 Yıllık Kesin Mühlet Kararı Vermiştir Mahkeme tarafından yapılan değerlendirme sonucunda davacıların kesin mühlet talebi kabul edilmiştir. Karara göre, daha önce tanınan geçici mühlet süresinin sona erdiği tarihten itibaren geçerli olmak üzere borçlular hakkında 1 yıllık kesin mühlet uygulanacaktır. Kesin mühlet süresi 25 Mayıs 2026 tarihi itibarıyla başlamaktadır. Üstelik bu karar kapsamında şirket ve ortakları, konkordato hükümleri çerçevesinde faaliyetlerini sürdürmeye devam edecektir. Konkordatonun Hukuki Sonuçları Yürürlüğe Girmiştir Mahkeme kararında, kesin mühlet verilmesiyle birlikte İcra ve İflas Kanunu’nun ilgili hükümlerinin uygulanmaya başladığı belirtilmiştir. Karar doğrultusunda; İİK 294. madde İİK 295. madde İİK 296. madde İİK 297. madde kapsamında düzenlenen konkordato hükümleri yürürlüğe girmiştir. Bu düzenlemeler, borçlunun malvarlığı üzerindeki işlemler ile alacaklıların haklarına ilişkin çeşitli koruma mekanizmalarını içermektedir. Ayrıca konkordato sürecinin sağlıklı şekilde yürütülmesi amaçlanmaktadır. Komiserler Kurulu Görevine Devam Edecek Mahkeme tarafından alınan karar kapsamında daha önce görevlendirilen komiserler kurulunun görev süresine ilişkin de değerlendirme yapılmıştır. Buna göre geçici mühlet döneminde görev yapan komiserler kurulu, kesin mühlet süresi boyunca da görevini sürdürecektir. Komiserler kurulu, konkordato sürecinin mevzuata uygun şekilde yürütülmesini takip etmektedir. Aynı zamanda şirketin mali yapısına ilişkin gelişmeleri mahkemeye raporlamaktadır. Karar Resmi Olarak İlan Edilmiştir Ankara 2. Asliye Ticaret Mahkemesi tarafından verilen karar, İcra ve İflas Kanunu’nun 288. maddesi kapsamında ilan edilmiştir. İlan edilen kararda, kesin mühlet kararının yürürlüğe girdiği ve konkordato sürecinin yasal çerçevede devam ettiği belirtilmiştir. Üstelik bu süreçte mahkeme gözetiminde yürütülen konkordato işlemleri, belirlenen süre boyunca takip edilecektir. Kartal Hafriyat konkordato dosyasında mahkeme tarafından önemli bir karar verilmiştir. Ankara 2. Asliye Ticaret Mahkemesi, şirket ve ortakları hakkında 25 Mayıs 2026 tarihinden itibaren geçerli olmak üzere 1 yıllık kesin mühlet tanımıştır. Ayrıca kararla birlikte konkordatonun hukuki sonuçları yürürlüğe girerken, komiserler kurulunun görevinin de devam etmesine hükmedilmiştir. Fulya GÜRBÜZ TÜM YAZILARI Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Kartal Hafriyat konkordato sürecinde önemli bir gelişme yaşanmıştır. Ankara 2. Asliye Ticaret Mahkemesi, Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi ile şirket ortakları hakkında 1 yıllık kesin mühlet kararı vermiştir. Kararla birlikte konkordatonun hukuki sonuçları da yürürlüğe girmiştir. Mahkeme 1 Yıllık Kesin Mühlet Kararı Vermiştir Konkordatonun Hukuki Sonuçları Yürürlüğe Girmiştir Komiserler Kurulu Görevine Devam Edecek Karar Resmi Olarak İlan Edilmiştir Kartal Hafriyat konkordato sürecine ilişkin yeni mahkeme kararı kamuoyuyla paylaşılmıştır. Ankara 2. Asliye Ticaret Mahkemesi tarafından görülen dava kapsamında şirket ve şirket ortakları hakkında kesin mühlet kararı verilmiştir. Mahkemenin 2025/972 Esas sayılı dosyada aldığı karara göre, Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi ile şirket ortakları Nuri Kartal ve Mustafa Kartal için konkordato sürecinin devamına hükmedilmiştir. Karar, 22 Mayıs 2026 tarihinde açıklanmıştır. Mahkeme tarafından yapılan değerlendirme sonucunda davacıların kesin mühlet talebi kabul edilmiştir. Karara göre, daha önce tanınan geçici mühlet süresinin sona erdiği tarihten itibaren geçerli olmak üzere borçlular hakkında 1 yıllık kesin mühlet uygulanacaktır. Kesin mühlet süresi 25 Mayıs 2026 tarihi itibarıyla başlamaktadır. Üstelik bu karar kapsamında şirket ve ortakları, konkordato hükümleri çerçevesinde faaliyetlerini sürdürmeye devam edecektir. Mahkeme kararında, kesin mühlet verilmesiyle birlikte İcra ve İflas Kanunu’nun ilgili hükümlerinin uygulanmaya başladığı belirtilmiştir. kapsamında düzenlenen konkordato hükümleri yürürlüğe girmiştir. Bu düzenlemeler, borçlunun malvarlığı üzerindeki işlemler ile alacaklıların haklarına ilişkin çeşitli koruma mekanizmalarını içermektedir. Ayrıca konkordato sürecinin sağlıklı şekilde yürütülmesi amaçlanmaktadır. Mahkeme tarafından alınan karar kapsamında daha önce görevlendirilen komiserler kurulunun görev süresine ilişkin de değerlendirme yapılmıştır. Buna göre geçici mühlet döneminde görev yapan komiserler kurulu, kesin mühlet süresi boyunca da görevini sürdürecektir. Komiserler kurulu, konkordato sürecinin mevzuata uygun şekilde yürütülmesini takip etmektedir. Aynı zamanda şirketin mali yapısına ilişkin gelişmeleri mahkemeye raporlamaktadır. Ankara 2. Asliye Ticaret Mahkemesi tarafından verilen karar, İcra ve İflas Kanunu’nun 288. maddesi kapsamında ilan edilmiştir. İlan edilen kararda, kesin mühlet kararının yürürlüğe girdiği ve konkordato sürecinin yasal çerçevede devam ettiği belirtilmiştir. Üstelik bu süreçte mahkeme gözetiminde yürütülen konkordato işlemleri, belirlenen süre boyunca takip edilecektir. Kartal Hafriyat konkordato dosyasında mahkeme tarafından önemli bir karar verilmiştir. Ankara 2. Asliye Ticaret Mahkemesi, şirket ve ortakları hakkında 25 Mayıs 2026 tarihinden itibaren geçerli olmak üzere 1 yıllık kesin mühlet tanımıştır. Ayrıca kararla birlikte konkordatonun hukuki sonuçları yürürlüğe girerken, komiserler kurulunun görevinin de devam etmesine hükmedilmiştir.</t>
+          <t>Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Yangın, itfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alındı. Facebook X WhatsApp 01 Haziran 2026 10:34 Yangın, sabah saat 08.30 civarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi'nde bulunan Ermetal fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikada gerçekleştirilen kaynak çalışması, yangının çıkmasına neden oldu. Alevlerin hızla büyüdüğünü fark eden çalışanlar, durumu hemen 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin hızlı ve etkili müdahalesi sayesinde yangın kısa sürede kontrol altına alındı. Alevlerin çevredeki bölümlere sıçramadan söndürülmesi, büyük bir faciayı önledi. Yangında can kaybı veya yaralanma yaşanmazken, fabrikanın bazı kısımlarında maddi hasar meydana geldi. Olayla ilgili detaylı bir inceleme başlatıldığı bildirildi. Bingöl Solhan'da Bayramda Yüzen Adalar'a Gelen Ziyaretçi Sayısı Artış Gösterdi Bursa Yıldırım'daki Faik Çelik Kız Lisesi, Sıfır Atık Projeleriyle Ekonomiye Katkı Sağlıyor. Bursa Kaynak: Mersin Haber + IHA İlgili Haberler Facebook X WhatsApp Son Eklenen Haberler 13:13 Ustasından yazlık ayakkabı önerisi 13:14 Yazın görülen kulak ağrılarına dikkat: "Yüzücü kulağı tatili kabusa çevirebilir" 13:12 İstanbul Ataşehir'de TOKİ Projesi Tamamlandı 13:12 Muğla'da Ormanlık Alanlardaki Kirlilik Sorunu 13:12 Hakan Fidan Singapur'a Resmi Ziyaret Gerçekleştiriyor 13:12 Kırşehir'de Ruhsatsız Silah Ele Geçirildi 13:09 Kars'ta Vali Polat Misafirlere Rehberlik Etti 13:10 Bursa'da Yasa Dışı Papağan Ticareti 13:10 Bursa'da Sağlıklı Kampüs Belgesi Alındı 13:10 Bursa'da Alkollü Sürücüye Eğitim Verildi 13:11 Ordu’da ırmak yatağında mahsur kalan köpekleri itfaiye kurtardı 13:11 Başkan Palancıoğlu, mesaiye personel ile bayramlaşarak başladı 13:09 İnegöl'de İnşaatta Ölüm Olayı 13:09 Kürşat Açıkgöz Erciyes TV’yi Devraldı 13:07 Düzce'de AK Parti Toplantısı 13:04 Ordu'da Mahsur Kalan Köpekler Kurtarıldı 13:07 Naz Arıcı'dan İstanbul'da Yeni Madalya 13:02 Osmangazi'de Çocuklar Toprağa Şekil Verdi 13:02 Yıldırım'da Gönül Belediyeciliği Uygulamaları 13:03 Osman Abanoz Görevine Dönüyor Çok Okunanlar Eski Mersin Milletvekili Fevzi Arıcı Hayatını Kaybetti Eski Muhtar İş Kazasında Hayatını Kaybetti Mersin'de Yabancı Uyruklu Cinayet Erdemli'de Trafik Kazası Yaşandı Mersin'de Hızlı Tren Hattı Projesi Kardeşlerin Aynı Gün Evliliği Mersin'de Gerçekleşti Adıyaman'da Trafik Kazası: 3 Ölü, 4 Yaralı Mersin’de Üniversite Hastanesi Yakınında Bıçaklı Yaralama: Onkoloji Bölümü Civarında Kesici Aletle Yaralanan Genç Tedaviye Alındı Mersin'de Hırsızlık Olayı Yaşandı Mersin'de Dolu Yağışı Etkili Oldu Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Haber Merkezi • 01 Haziran 2026 10:34 • Güncellendi: 01 Haziran 2026 10:37 Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Yangın, itfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alındı. Anasayfa Haberler Kategoriler Asayiş Bursa'da Fabrika Yangını Paniğe Neden Oldu Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Yangın, itfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alındı. Facebook X WhatsApp 01 Haziran 2026 10:34 Yangın, sabah saat 08.30 civarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi'nde bulunan Ermetal fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikada gerçekleştirilen kaynak çalışması, yangının çıkmasına neden oldu. Alevlerin hızla büyüdüğünü fark eden çalışanlar, durumu hemen 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin hızlı ve etkili müdahalesi sayesinde yangın kısa sürede kontrol altına alındı. Alevlerin çevredeki bölümlere sıçramadan söndürülmesi, büyük bir faciayı önledi. Yangında can kaybı veya yaralanma yaşanmazken, fabrikanın bazı kısımlarında maddi hasar meydana geldi. Olayla ilgili detaylı bir inceleme başlatıldığı bildirildi. Bingöl Solhan'da Bayramda Yüzen Adalar'a Gelen Ziyaretçi Sayısı Artış Gösterdi Bursa Yıldırım'daki Faik Çelik Kız Lisesi, Sıfır Atık Projeleriyle Ekonomiye Katkı Sağlıyor. Bursa Kaynak: Mersin Haber + IHA İlgili Haberler Facebook X WhatsApp Son Eklenen Haberler 13:13 Ustasından yazlık ayakkabı önerisi 13:14 Yazın görülen kulak ağrılarına dikkat: "Yüzücü kulağı tatili kabusa çevirebilir" 13:12 İstanbul Ataşehir'de TOKİ Projesi Tamamlandı 13:12 Muğla'da Ormanlık Alanlardaki Kirlilik Sorunu 13:12 Hakan Fidan Singapur'a Resmi Ziyaret Gerçekleştiriyor 13:12 Kırşehir'de Ruhsatsız Silah Ele Geçirildi 13:09 Kars'ta Vali Polat Misafirlere Rehberlik Etti 13:10 Bursa'da Yasa Dışı Papağan Ticareti 13:10 Bursa'da Sağlıklı Kampüs Belgesi Alındı 13:10 Bursa'da Alkollü Sürücüye Eğitim Verildi 13:11 Ordu’da ırmak yatağında mahsur kalan köpekleri itfaiye kurtardı 13:11 Başkan Palancıoğlu, mesaiye personel ile bayramlaşarak başladı 13:09 İnegöl'de İnşaatta Ölüm Olayı 13:09 Kürşat Açıkgöz Erciyes TV’yi Devraldı 13:07 Düzce'de AK Parti Toplantısı 13:04 Ordu'da Mahsur Kalan Köpekler Kurtarıldı 13:07 Naz Arıcı'dan İstanbul'da Yeni Madalya 13:02 Osmangazi'de Çocuklar Toprağa Şekil Verdi 13:02 Yıldırım'da Gönül Belediyeciliği Uygulamaları 13:03 Osman Abanoz Görevine Dönüyor Çok Okunanlar Eski Mersin Milletvekili Fevzi Arıcı Hayatını Kaybetti Eski Muhtar İş Kazasında Hayatını Kaybetti Mersin'de Yabancı Uyruklu Cinayet Erdemli'de Trafik Kazası Yaşandı Mersin'de Hızlı Tren Hattı Projesi Kardeşlerin Aynı Gün Evliliği Mersin'de Gerçekleşti Adıyaman'da Trafik Kazası: 3 Ölü, 4 Yaralı Mersin’de Üniversite Hastanesi Yakınında Bıçaklı Yaralama: Onkoloji Bölümü Civarında Kesici Aletle Yaralanan Genç Tedaviye Alındı Mersin'de Hırsızlık Olayı Yaşandı Mersin'de Dolu Yağışı Etkili Oldu Yangın, sabah saat 08.30 civarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi'nde bulunan Ermetal fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikada gerçekleştirilen kaynak çalışması, yangının çıkmasına neden oldu. Alevlerin hızla büyüdüğünü fark eden çalışanlar, durumu hemen 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin hızlı ve etkili müdahalesi sayesinde yangın kısa sürede kontrol altına alındı. Alevlerin çevredeki bölümlere sıçramadan söndürülmesi, büyük bir faciayı önledi. Yangında can kaybı veya yaralanma yaşanmazken, fabrikanın bazı kısımlarında maddi hasar meydana geldi. Olayla ilgili detaylı bir inceleme başlatıldığı bildirildi. Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Haber Merkezi • 01 Haziran 2026 10:34 • Güncellendi: 01 Haziran 2026 10:37 Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Yangın, itfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alındı. Haber Merkezi • 01 Haziran 2026 10:34 • Güncellendi: 01 Haziran 2026 10:37 Anasayfa Haberler Kategoriler Asayiş Bursa'da Fabrika Yangını Paniğe Neden Oldu Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Yangın, itfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alındı. Facebook X WhatsApp 01 Haziran 2026 10:34 Yangın, sabah saat 08.30 civarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi'nde bulunan Ermetal fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikada gerçekleştirilen kaynak çalışması, yangının çıkmasına neden oldu. Alevlerin hızla büyüdüğünü fark eden çalışanlar, durumu hemen 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin hızlı ve etkili müdahalesi sayesinde yangın kısa sürede kontrol altına alındı. Alevlerin çevredeki bölümlere sıçramadan söndürülmesi, büyük bir faciayı önledi. Yangında can kaybı veya yaralanma yaşanmazken, fabrikanın bazı kısımlarında maddi hasar meydana geldi. Olayla ilgili detaylı bir inceleme başlatıldığı bildirildi. Bingöl Solhan'da Bayramda Yüzen Adalar'a Gelen Ziyaretçi Sayısı Artış Gösterdi Bursa Yıldırım'daki Faik Çelik Kız Lisesi, Sıfır Atık Projeleriyle Ekonomiye Katkı Sağlıyor. Bursa Kaynak: Mersin Haber + IHA İlgili Haberler Facebook X WhatsApp Son Eklenen Haberler 13:13 Ustasından yazlık ayakkabı önerisi 13:14 Yazın görülen kulak ağrılarına dikkat: "Yüzücü kulağı tatili kabusa çevirebilir" 13:12 İstanbul Ataşehir'de TOKİ Projesi Tamamlandı 13:12 Muğla'da Ormanlık Alanlardaki Kirlilik Sorunu 13:12 Hakan Fidan Singapur'a Resmi Ziyaret Gerçekleştiriyor 13:12 Kırşehir'de Ruhsatsız Silah Ele Geçirildi 13:09 Kars'ta Vali Polat Misafirlere Rehberlik Etti 13:10 Bursa'da Yasa Dışı Papağan Ticareti 13:10 Bursa'da Sağlıklı Kampüs Belgesi Alındı 13:10 Bursa'da Alkollü Sürücüye Eğitim Verildi 13:11 Ordu’da ırmak yatağında mahsur kalan köpekleri itfaiye kurtardı 13:11 Başkan Palancıoğlu, mesaiye personel ile bayramlaşarak başladı 13:09 İnegöl'de İnşaatta Ölüm Olayı 13:09 Kürşat Açıkgöz Erciyes TV’yi Devraldı 13:07 Düzce'de AK Parti Toplantısı 13:04 Ordu'da Mahsur Kalan Köpekler Kurtarıldı 13:07 Naz Arıcı'dan İstanbul'da Yeni Madalya 13:02 Osmangazi'de Çocuklar Toprağa Şekil Verdi 13:02 Yıldırım'da Gönül Belediyeciliği Uygulamaları 13:03 Osman Abanoz Görevine Dönüyor Çok Okunanlar Eski Mersin Milletvekili Fevzi Arıcı Hayatını Kaybetti Eski Muhtar İş Kazasında Hayatını Kaybetti Mersin'de Yabancı Uyruklu Cinayet Erdemli'de Trafik Kazası Yaşandı Mersin'de Hızlı Tren Hattı Projesi Kardeşlerin Aynı Gün Evliliği Mersin'de Gerçekleşti Adıyaman'da Trafik Kazası: 3 Ölü, 4 Yaralı Mersin’de Üniversite Hastanesi Yakınında Bıçaklı Yaralama: Onkoloji Bölümü Civarında Kesici Aletle Yaralanan Genç Tedaviye Alındı Mersin'de Hırsızlık Olayı Yaşandı Mersin'de Dolu Yağışı Etkili Oldu Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Yangın, itfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alındı. Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Yangın, sabah saat 08.30 civarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi'nde bulunan Ermetal fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikada gerçekleştirilen kaynak çalışması, yangının çıkmasına neden oldu. Alevlerin hızla büyüdüğünü fark eden çalışanlar, durumu hemen 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin hızlı ve etkili müdahalesi sayesinde yangın kısa sürede kontrol altına alındı. Alevlerin çevredeki bölümlere sıçramadan söndürülmesi, büyük bir faciayı önledi. Yangında can kaybı veya yaralanma yaşanmazken, fabrikanın bazı kısımlarında maddi hasar meydana geldi. Olayla ilgili detaylı bir inceleme başlatıldığı bildirildi. Kayseri’de ayakkabı tamirciliği yapan usta, havaların ısınmasıyla birlikte yazlık ayakkabı alacak vatandaşlara önerilerde bulundu. Yaz aylarında deniz ve havuz kullanımının artmasıyla kulakta su kalması ve nemli ortamların etkisiyle ’yüzücü kulağı’ olarak bilinen dış kulak yolu enfeksiyonlarında artış yaşandığını belirten Prof. Dr. Cenk Evren, bu dönemde kulak sağlığına dikkat edilmesi gerektiğini söyledi. İstanbul Ataşehir'de gerçekleştirilen kentsel dönüşüm projesi ile 1.442 konut güvenli hale getirildi. Çevre, Şehircilik ve İklim Değişikliği Bakanı Murat Kurum, vatandaşların devletine güvenerek sağlam konutlara kavuştuğunu vurguladı. Proje kapsamında inşa edilen konutlar, hak sahiplerine etap etap teslim ediliyor. Muğla Menteşe ilçesinde, ormanlık alanlara kaçak dökülen moloz ve inşaat atıkları nedeniyle çevre kirliliği ve yangın riski artıyor. Mahalle sakinleri, bu duruma karşı yetkililere seslenerek sorunun çözülmesini talep ediyor. Dışişleri Bakanı Hakan Fidan, 2 Haziran tarihinde Singapur’a yapacağı ziyaretle, Türkiye-Singapur ilişkilerini güçlendirmek amacıyla önemli temaslarda bulunacak. Ziyaret kapsamında ticaret, savunma sanayii, yapay zeka ve enerji güvenliği gibi konular ele alınacak. Ayrıca, bölgesel gelişmeler hakkında da görüş alışverişinde bulunulacak. Kırşehir Merkez'de gerçekleştirilen operasyon sonucunda bir adet ruhsatsız tabanca ve 12 adet fişek ele geçirildi. Olayla ilgili adli işlemler başlatıldı. Kars Valisi Ziya Polat, kente gelen ziyaretçilere rehberlik ederek kentin tarihi ve kültürel zenginliklerini tanıttı. Peynir Müzesi'ni de gezen Polat, misafirlerine Kars'ın gastronomik değerleri hakkında bilgi verdi. Bursa'da yasa dışı ticarete konu olan 3 İskender papağanı yavrusu koruma altına alındı. Doğa Koruma ve Milli Parklar ekipleri, gelen ihbar sonrasında harekete geçerek bu yavruları kurtardı. Bursa Teknik Üniversitesi, sağlıklı yaşam kültürünü yaygınlaştırma çabalarıyla önemli bir belge aldı. Bursa İnegöl'de meydana gelen olayda, alkollü sürücü, kazadan sonra uyurken yakalandı. Ekipler, alkolmetreyi kullanması için sürücüye uygulamalı eğitim verdi. Yapılan testte 2.76 promil alkollü olduğu belirlenen sürücüye 25 bin lira ceza kesildi ve 6 ay süreyle ehliyetine el konuldu. Ordu’da ırmak yatağında mahsur kalan köpekler, itfaiye ekiplerinin çalışması sonucu kurtarıldı. Melikgazi Belediye Başkanı Doç. Dr. Mustafa Palancıoğlu; Kurban Bayramı dönüşü ilk mesai gününde İnecik Şantiyesi, Park ve Bahçeler Müdürlüğü Yeniköy Bakım ve Onarım Merkezi, Melikgazi Belediyesi Ek Hizmet Binası ve Ana Hizmet Binası’nda çalışan personel tek tek bayramlaştı. Bursa'nın İnegöl ilçesinde inşaat halindeki bir apartmandan düşen duvar ustası, oğlu Tolga'nın gözleri önünde hayatını kaybetti. Kürşat Açıkgöz, Kayseri’nin önde gelen televizyon kanallarından biri olan Erciyes TV’yi devraldığını duyurdu. Açıkgöz, kanalın yeni dönemde daha etkili bir yayın anlayışıyla devam edeceğini ifade etti. Düzce'de AK Parti, haziran ayı Belediye Meclis toplantısını gerçekleştirdi. Ordu Altınordu ilçesinde bir irmak yatağında mahsur kalan iki köpek, itfaiye ekiplerinin hızlı müdahalesiyle kurtarıldı. İstanbul'da gerçekleştirilen uluslararası masterlar artistik buz pateni yarışmasında Türkiye'yi temsil eden Naz Arıcı, gümüş madalya ile ülkemize döndü. Yarışma, Almanya'nın Münih kentinde yapıldı ve 30'dan fazla ülke ile 500'den fazla sporcu katıldı. Arıcı, altın bayanlar kategorisinde gösterdiği performansla dikkat çekti. Bursa Osmangazi Belediyesi'nin kreşlerinde düzenlenen çömlek atölyeleri, çocukların geleneksel sanatla buluşarak hem eğlenmesini sağladı hem de el becerilerini geliştirdi. Bursa Yıldırım'da, Belediye Başkanı Oktay Yılmaz, vatandaşlarla gönül köprüleri kurarak iletişimi güçlendirmeye devam ediyor. Mahalle ziyaretleri ile büyüklerin taleplerini dinleyen Yılmaz, toplumun değerlerine vurgu yapıyor. Samsun Kavak ilçesinde, geçirdiği kaza sonrasında tedavi edilen Osman Abanoz, yeniden görevine başladı. Sağlık sorunları nedeniyle uzun bir süre uzak kaldığı görevine geri dönmenin mutluluğunu yaşıyor.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Taşınmaz Haber Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Ana Sayfa › Şirket Haberleri › Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Kartal Hafriyat konkordato sürecine ilişkin yeni mahkeme kararı kamuoyuyla paylaşılmıştır. Asliye Ticaret Mahkemesi tarafından görülen dava kapsamında şirket ve şirket ortakları hakkında kesin mühlet kararı verilmiştir. Mahkemenin 2025/972 Esas sayılı dosyada aldığı karara göre, Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi ile şirket ortakları Nuri Kartal ve Mustafa Kartal için konkordato sürecinin devamına hükmedilmiştir. Karar, 22 Mayıs 2026 tarihinde açıklanmıştır. Mahkeme 1 Yıllık Kesin Mühlet Kararı Vermiştir Mahkeme tarafından yapılan değerlendirme sonucunda davacıların kesin mühlet talebi kabul edilmiştir. Karara göre, daha önce tanınan geçici mühlet süresinin sona erdiği tarihten itibaren geçerli olmak üzere borçlular hakkında 1 yıllık kesin mühlet uygulanacaktır. Kesin mühlet süresi 25 Mayıs 2026 tarihi itibarıyla başlamaktadır. Üstelik bu karar kapsamında şirket ve ortakları, konkordato hükümleri çerçevesinde faaliyetlerini sürdürmeye devam edecektir. Konkordatonun Hukuki Sonuçları Yürürlüğe Girmiştir Mahkeme kararında, kesin mühlet verilmesiyle birlikte İcra ve İflas Kanunu’nun ilgili hükümlerinin uygulanmaya başladığı belirtilmiştir. madde kapsamında düzenlenen konkordato hükümleri yürürlüğe girmiştir. Ayrıca konkordato sürecinin sağlıklı şekilde yürütülmesi amaçlanmaktadır. Buna göre geçici mühlet döneminde görev yapan komiserler kurulu, kesin mühlet süresi boyunca da görevini sürdürecektir. Komiserler kurulu, konkordato sürecinin mevzuata uygun şekilde yürütülmesini takip etmektedir. Aynı zamanda şirketin mali yapısına ilişkin gelişmeleri mahkemeye raporlamaktadır. Karar Resmi Olarak İlan Edilmiştir Ankara 2. Asliye Ticaret Mahkemesi tarafından verilen karar, İcra ve İflas Kanunu’nun 288. İlan edilen kararda, kesin mühlet kararının yürürlüğe girdiği ve konkordato sürecinin yasal çerçevede devam ettiği belirtilmiştir. Üstelik bu süreçte mahkeme gözetiminde yürütülen konkordato işlemleri, belirlenen süre boyunca takip edilecektir. Kartal Hafriyat konkordato dosyasında mahkeme tarafından önemli bir karar verilmiştir. Asliye Ticaret Mahkemesi, şirket ve ortakları hakkında 25 Mayıs 2026 tarihinden itibaren geçerli olmak üzere 1 yıllık kesin mühlet tanımıştır. Fulya GÜRBÜZ TÜM YAZILARI Kartal Hafriyat Konkordato Sürecinde Yeni Karar Alındı! Şirkete 1 Yıllık Kesin Mühlet Verildi Kartal Hafriyat konkordato sürecinde önemli bir gelişme yaşanmıştır. Asliye Ticaret Mahkemesi, Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi ile şirket ortakları hakkında 1 yıllık kesin mühlet kararı vermiştir. Mahkeme 1 Yıllık Kesin Mühlet Kararı Vermiştir Konkordatonun Hukuki Sonuçları Yürürlüğe Girmiştir Komiserler Kurulu Görevine Devam Edecek Karar Resmi Olarak İlan Edilmiştir Kartal Hafriyat konkordato sürecine ilişkin yeni mahkeme kararı kamuoyuyla paylaşılmıştır. Mahkeme tarafından yapılan değerlendirme sonucunda davacıların kesin mühlet talebi kabul edilmiştir. Mahkeme kararında, kesin mühlet verilmesiyle birlikte İcra ve İflas Kanunu’nun ilgili hükümlerinin uygulanmaya başladığı belirtilmiştir. kapsamında düzenlenen konkordato hükümleri yürürlüğe girmiştir.</t>
+          <t>Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Mersin Haber Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Yangın, itfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alındı. Facebook X WhatsApp 01 Haziran 2026 10:34 Yangın, sabah saat 08.30 civarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi'nde bulunan Ermetal fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikada gerçekleştirilen kaynak çalışması, yangının çıkmasına neden oldu. Alevlerin hızla büyüdüğünü fark eden çalışanlar, durumu hemen 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin hızlı ve etkili müdahalesi sayesinde yangın kısa sürede kontrol altına alındı. Alevlerin çevredeki bölümlere sıçramadan söndürülmesi, büyük bir faciayı önledi. Yangında can kaybı veya yaralanma yaşanmazken, fabrikanın bazı kısımlarında maddi hasar meydana geldi. Olayla ilgili detaylı bir inceleme başlatıldığı bildirildi. Bingöl Solhan'da Bayramda Yüzen Adalar'a Gelen Ziyaretçi Sayısı Artış Gösterdi Bursa Yıldırım'daki Faik Çelik Kız Lisesi, Sıfır Atık Projeleriyle Ekonomiye Katkı Sağlıyor. Bursa Kaynak: Mersin Haber + IHA İlgili Haberler Facebook X WhatsApp Son Eklenen Haberler 13:13 Ustasından yazlık ayakkabı önerisi 13:14 Yazın görülen kulak ağrılarına dikkat: "Yüzücü kulağı tatili kabusa çevirebilir" 13:12 İstanbul Ataşehir'de TOKİ Projesi Tamamlandı 13:12 Muğla'da Ormanlık Alanlardaki Kirlilik Sorunu 13:12 Hakan Fidan Singapur'a Resmi Ziyaret Gerçekleştiriyor 13:12 Kırşehir'de Ruhsatsız Silah Ele Geçirildi 13:09 Kars'ta Vali Polat Misafirlere Rehberlik Etti 13:10 Bursa'da Yasa Dışı Papağan Ticareti 13:10 Bursa'da Sağlıklı Kampüs Belgesi Alındı 13:10 Bursa'da Alkollü Sürücüye Eğitim Verildi 13:11 Ordu’da ırmak yatağında mahsur kalan köpekleri itfaiye kurtardı 13:11 Başkan Palancıoğlu, mesaiye personel ile bayramlaşarak başladı 13:09 İnegöl'de İnşaatta Ölüm Olayı 13:09 Kürşat Açıkgöz Erciyes TV’yi Devraldı 13:07 Düzce'de AK Parti Toplantısı 13:04 Ordu'da Mahsur Kalan Köpekler Kurtarıldı 13:07 Naz Arıcı'dan İstanbul'da Yeni Madalya 13:02 Osmangazi'de Çocuklar Toprağa Şekil Verdi 13:02 Yıldırım'da Gönül Belediyeciliği Uygulamaları 13:03 Osman Abanoz Görevine Dönüyor Çok Okunanlar Eski Mersin Milletvekili Fevzi Arıcı Hayatını Kaybetti Eski Muhtar İş Kazasında Hayatını Kaybetti Mersin'de Yabancı Uyruklu Cinayet Erdemli'de Trafik Kazası Yaşandı Mersin'de Hızlı Tren Hattı Projesi Kardeşlerin Aynı Gün Evliliği Mersin'de Gerçekleşti Adıyaman'da Trafik Kazası: 3 Ölü, 4 Yaralı Mersin’de Üniversite Hastanesi Yakınında Bıçaklı Yaralama: Onkoloji Bölümü Civarında Kesici Aletle Yaralanan Genç Tedaviye Alındı Mersin'de Hırsızlık Olayı Yaşandı Mersin'de Dolu Yağışı Etkili Oldu Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Haber Merkezi • 01 Haziran 2026 10:34 • Güncellendi: 01 Haziran 2026 10:37 Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Anasayfa Haberler Kategoriler Asayiş Bursa'da Fabrika Yangını Paniğe Neden Oldu Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Bursa Kaynak: Mersin Haber + IHA İlgili Haberler Facebook X WhatsApp Son Eklenen Haberler 13:13 Ustasından yazlık ayakkabı önerisi 13:14 Yazın görülen kulak ağrılarına dikkat: "Yüzücü kulağı tatili kabusa çevirebilir" 13:12 İstanbul Ataşehir'de TOKİ Projesi Tamamlandı 13:12 Muğla'da Ormanlık Alanlardaki Kirlilik Sorunu 13:12 Hakan Fidan Singapur'a Resmi Ziyaret Gerçekleştiriyor 13:12 Kırşehir'de Ruhsatsız Silah Ele Geçirildi 13:09 Kars'ta Vali Polat Misafirlere Rehberlik Etti 13:10 Bursa'da Yasa Dışı Papağan Ticareti 13:10 Bursa'da Sağlıklı Kampüs Belgesi Alındı 13:10 Bursa'da Alkollü Sürücüye Eğitim Verildi 13:11 Ordu’da ırmak yatağında mahsur kalan köpekleri itfaiye kurtardı 13:11 Başkan Palancıoğlu, mesaiye personel ile bayramlaşarak başladı 13:09 İnegöl'de İnşaatta Ölüm Olayı 13:09 Kürşat Açıkgöz Erciyes TV’yi Devraldı 13:07 Düzce'de AK Parti Toplantısı 13:04 Ordu'da Mahsur Kalan Köpekler Kurtarıldı 13:07 Naz Arıcı'dan İstanbul'da Yeni Madalya 13:02 Osmangazi'de Çocuklar Toprağa Şekil Verdi 13:02 Yıldırım'da Gönül Belediyeciliği Uygulamaları 13:03 Osman Abanoz Görevine Dönüyor Çok Okunanlar Eski Mersin Milletvekili Fevzi Arıcı Hayatını Kaybetti Eski Muhtar İş Kazasında Hayatını Kaybetti Mersin'de Yabancı Uyruklu Cinayet Erdemli'de Trafik Kazası Yaşandı Mersin'de Hızlı Tren Hattı Projesi Kardeşlerin Aynı Gün Evliliği Mersin'de Gerçekleşti Adıyaman'da Trafik Kazası: 3 Ölü, 4 Yaralı Mersin’de Üniversite Hastanesi Yakınında Bıçaklı Yaralama: Onkoloji Bölümü Civarında Kesici Aletle Yaralanan Genç Tedaviye Alındı Mersin'de Hırsızlık Olayı Yaşandı Mersin'de Dolu Yağışı Etkili Oldu Yangın, sabah saat 08.30 civarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi'nde bulunan Ermetal fabrikasında meydana geldi. Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Haber Merkezi • 01 Haziran 2026 10:34 • Güncellendi: 01 Haziran 2026 10:37 Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Haber Merkezi • 01 Haziran 2026 10:34 • Güncellendi: 01 Haziran 2026 10:37 Anasayfa Haberler Kategoriler Asayiş Bursa'da Fabrika Yangını Paniğe Neden Oldu Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Bursa Kaynak: Mersin Haber + IHA İlgili Haberler Facebook X WhatsApp Son Eklenen Haberler 13:13 Ustasından yazlık ayakkabı önerisi 13:14 Yazın görülen kulak ağrılarına dikkat: "Yüzücü kulağı tatili kabusa çevirebilir" 13:12 İstanbul Ataşehir'de TOKİ Projesi Tamamlandı 13:12 Muğla'da Ormanlık Alanlardaki Kirlilik Sorunu 13:12 Hakan Fidan Singapur'a Resmi Ziyaret Gerçekleştiriyor 13:12 Kırşehir'de Ruhsatsız Silah Ele Geçirildi 13:09 Kars'ta Vali Polat Misafirlere Rehberlik Etti 13:10 Bursa'da Yasa Dışı Papağan Ticareti 13:10 Bursa'da Sağlıklı Kampüs Belgesi Alındı 13:10 Bursa'da Alkollü Sürücüye Eğitim Verildi 13:11 Ordu’da ırmak yatağında mahsur kalan köpekleri itfaiye kurtardı 13:11 Başkan Palancıoğlu, mesaiye personel ile bayramlaşarak başladı 13:09 İnegöl'de İnşaatta Ölüm Olayı 13:09 Kürşat Açıkgöz Erciyes TV’yi Devraldı 13:07 Düzce'de AK Parti Toplantısı 13:04 Ordu'da Mahsur Kalan Köpekler Kurtarıldı 13:07 Naz Arıcı'dan İstanbul'da Yeni Madalya 13:02 Osmangazi'de Çocuklar Toprağa Şekil Verdi 13:02 Yıldırım'da Gönül Belediyeciliği Uygulamaları 13:03 Osman Abanoz Görevine Dönüyor Çok Okunanlar Eski Mersin Milletvekili Fevzi Arıcı Hayatını Kaybetti Eski Muhtar İş Kazasında Hayatını Kaybetti Mersin'de Yabancı Uyruklu Cinayet Erdemli'de Trafik Kazası Yaşandı Mersin'de Hızlı Tren Hattı Projesi Kardeşlerin Aynı Gün Evliliği Mersin'de Gerçekleşti Adıyaman'da Trafik Kazası: 3 Ölü, 4 Yaralı Mersin’de Üniversite Hastanesi Yakınında Bıçaklı Yaralama: Onkoloji Bölümü Civarında Kesici Aletle Yaralanan Genç Tedaviye Alındı Mersin'de Hırsızlık Olayı Yaşandı Mersin'de Dolu Yağışı Etkili Oldu Bursa Osmangazi'deki bir fabrikada çıkan yangın, çalışanlar arasında paniğe yol açtı. Bursa Osmangazi ilçesinde meydana gelen fabrika yangınında can kaybı yoktu Yangın, sabah saat 08.30 civarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi'nde bulunan Ermetal fabrikasında meydana geldi. Kayseri’de ayakkabı tamirciliği yapan usta, havaların ısınmasıyla birlikte yazlık ayakkabı alacak vatandaşlara önerilerde bulundu. Yaz aylarında deniz ve havuz kullanımının artmasıyla kulakta su kalması ve nemli ortamların etkisiyle ’yüzücü kulağı’ olarak bilinen dış kulak yolu enfeksiyonlarında artış yaşandığını belirten Prof. İstanbul Ataşehir'de gerçekleştirilen kentsel dönüşüm projesi ile 1.442 konut güvenli hale getirildi. Çevre, Şehircilik ve İklim Değişikliği Bakanı Murat Kurum, vatandaşların devletine güvenerek sağlam konutlara kavuştuğunu vurguladı. Muğla Menteşe ilçesinde, ormanlık alanlara kaçak dökülen moloz ve inşaat atıkları nedeniyle çevre kirliliği ve yangın riski artıyor. Dışişleri Bakanı Hakan Fidan, 2 Haziran tarihinde Singapur’a yapacağı ziyaretle, Türkiye-Singapur ilişkilerini güçlendirmek amacıyla önemli temaslarda bulunacak. Ziyaret kapsamında ticaret, savunma sanayii, yapay zeka ve enerji güvenliği gibi konular ele alınacak. Kırşehir Merkez'de gerçekleştirilen operasyon sonucunda bir adet ruhsatsız tabanca ve 12 adet fişek ele geçirildi. Olayla ilgili adli işlemler başlatıldı. Kars Valisi Ziya Polat, kente gelen ziyaretçilere rehberlik ederek kentin tarihi ve kültürel zenginliklerini tanıttı. Peynir Müzesi'ni de gezen Polat, misafirlerine Kars'ın gastronomik değerleri hakkında bilgi verdi. Bursa'da yasa dışı ticarete konu olan 3 İskender papağanı yavrusu koruma altına alındı. Doğa Koruma ve Milli Parklar ekipleri, gelen ihbar sonrasında harekete geçerek bu yavruları kurtardı. Bursa Teknik Üniversitesi, sağlıklı yaşam kültürünü yaygınlaştırma çabalarıyla önemli bir belge aldı. Bursa İnegöl'de meydana gelen olayda, alkollü sürücü, kazadan sonra uyurken yakalandı. Ekipler, alkolmetreyi kullanması için sürücüye uygulamalı eğitim verdi. Ordu’da ırmak yatağında mahsur kalan köpekler, itfaiye ekiplerinin çalışması sonucu kurtarıldı. Melikgazi Belediye Başkanı Doç. Mustafa Palancıoğlu; Kurban Bayramı dönüşü ilk mesai gününde İnecik Şantiyesi, Park ve Bahçeler Müdürlüğü Yeniköy Bakım ve Onarım Merkezi, Melikgazi Belediyesi Ek Hizmet Binası ve Ana Hizmet Binası’nda çalışan personel tek tek bayramlaştı. Bursa'nın İnegöl ilçesinde inşaat halindeki bir apartmandan düşen duvar ustası, oğlu Tolga'nın gözleri önünde hayatını kaybetti. Kürşat Açıkgöz, Kayseri’nin önde gelen televizyon kanallarından biri olan Erciyes TV’yi devraldığını duyurdu. Düzce'de AK Parti, haziran ayı Belediye Meclis toplantısını gerçekleştirdi. Ordu Altınordu ilçesinde bir irmak yatağında mahsur kalan iki köpek, itfaiye ekiplerinin hızlı müdahalesiyle kurtarıldı. İstanbul'da gerçekleştirilen uluslararası masterlar artistik buz pateni yarışmasında Türkiye'yi temsil eden Naz Arıcı, gümüş madalya ile ülkemize döndü. Yarışma, Almanya'nın Münih kentinde yapıldı ve 30'dan fazla ülke ile 500'den fazla sporcu katıldı. Bursa Osmangazi Belediyesi'nin kreşlerinde düzenlenen çömlek atölyeleri, çocukların geleneksel sanatla buluşarak hem eğlenmesini sağladı hem de el becerilerini geliştirdi. Bursa Yıldırım'da, Belediye Başkanı Oktay Yılmaz, vatandaşlarla gönül köprüleri kurarak iletişimi güçlendirmeye devam ediyor. Samsun Kavak ilçesinde, geçirdiği kaza sonrasında tedavi edilen Osman Abanoz, yeniden görevine başladı. Sağlık sorunları nedeniyle uzun bir süre uzak kaldığı görevine geri dönmenin mutluluğunu yaşıyor.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://tasinmazhaber.com/kartal-hafriyat-konkordato-surecinde-yeni-karar-alindi-sirkete-1-yillik-kesin-muhlet-verildi/</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVVpPeC1YMkFualZSNXA5OC1LZGpYV0htVGktTHdScW9HY0ZlNmw4TzU0UHJhbl9Ca1pxWEEtVHdudGl4U3pySDF4OUlMRlQtUjEwZGFtOGFUTFpYYk5mR2JfbmhxTTBtenFidW4zY0dVRmFNZjV6UmNMZllQQjZ5U2dPcVlpZjVKenJGY1gxVmx0SWhvdkdkRXZiLTFrSXVYeGttUWRiWFVMRmNqTnYwZTUwMDVYZ9IBV0FVX3lxTE0yVjlDZlRDOF93am8tUHZvMDdLdTZYYUc0aU9RR0s0aHhKSFRFb0Vqc0ZJVHRtdE5tQWxHMGNaNUVrdjNEU09IT09XUk50eFVqZnM3TW9Jdw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Adıyaman | Bursa | Düzce | İstanbul | Kars</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Merkez | Solhan | İnegöl | Osmangazi | Yıldırım</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi:57:body | Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi:raw_legal</t>
-        </is>
-      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>gününde İnecik Şantiyesi</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+          <t>firma yok</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Nakliyat ve Toprak Sanayi Limited Şirketi Türkiye</t>
+          <t>gününde İnecik Şantiyesi Demirtaş Merkez Adıyaman Türkiye</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Nakliyat Ve Toprak Sanayi Limited Şirketi</t>
+          <t>Şantiye</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Kartal Hafriyat Nakliyat Ve Toprak Sanayi Limited Şirketi</t>
+          <t>Şantiye</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="n">
-        <v>181.9</v>
+        <v>205.75</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>7</v>
@@ -2422,27 +2484,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 08:48:00</t>
+          <t>2026-06-01 08:23:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>kara para</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi!</t>
+          <t>Bursa'daki fabrika yangını korkuttu</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi! T24</t>
+          <t>Bursa'daki fabrika yangını korkuttu Türk İnform</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2452,32 +2514,32 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi! Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi! Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi!</t>
+          <t>Bursa'daki fabrika yangını korkuttu Türk İnform</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi! Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi! T24 Dolandırıcıların yeni yöntemi: Banka hesabı kiralayana günlük 100 bin lira ve tatil vaadi!</t>
+          <t>Bursa'daki fabrika yangını korkuttu Bursa'daki fabrika yangını korkuttu Türk İnform Bursa'daki fabrika yangını korkuttu Türk İnform</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://t24.com.tr/ekonomi/dolandiricilarin-yeni-yontemi-banka-hesabi-kiralayana-gunluk-100-bin-lira-ve-tatil-vaadi,1325188</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5laXp0MHZHeWFUbUo1MWYzSHJGZWpIM3R5RUp6MXhlTHVJZmU1a3RGbVhuamV2VXFPZHFBR21WWlBnaWVxcnJpd04wSTlEM2pDZl9RNnpBOXZDV1JVTlNKeXBJMFU3U1V2Zjc1Yw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
@@ -2503,7 +2565,7 @@
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="n">
-        <v>77.22</v>
+        <v>37.72</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>8</v>
@@ -2512,27 +2574,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 23:03:33</t>
+          <t>2026-06-01 09:43:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>kara para</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Brezilya'da Kripto Para Birimleri İçin Yeni Kurallar: Merkez Bankası, VASP'lerden Sıkı ve Bağımsız Denetimler Yapılmasını Talep Ediyor</t>
+          <t>Konkordato da kurtarmadı! Ünlü inşaat şirketi iflas etti</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Brezilya'da Kripto Para Birimleri İçin Yeni Kurallar: Merkez Bankası, VASP'lerden Sıkı ve Bağımsız Denetimler Yapılmasını Talep Ediyor Bitcoin News</t>
+          <t>Konkordato da kurtarmadı! Ünlü inşaat şirketi iflas etti Bursada Bugün</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -2542,58 +2604,86 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>inşaat, şirket</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Brezilya'da Kripto Para Birimleri İçin Yeni Kurallar: Merkez Bankası, VASP'lerden Sıkı ve Bağımsız Denetimler Yapılmasını Talep Ediyor Bitcoin News</t>
+          <t>Ankara'da uzun yıllardır konut ve lüks yaşam projeleriyle adından söz ettiren Çakıroğulları İnşaat, yürüttüğü mali yeniden yapılandırma sürecinden olumlu sonuç alamadı. Bir süredir finansal darboğaz nedeniyle konkordato koruması altında faaliyetlerini sürdüren şirket hakkında mahkeme kritik kararını verdi ve iflasına hükmetti. Karar, başkentte gayrimenkul sektöründe dikkatle takip edilen davalardan biri olarak kayıtlara geçti. Ankara'da uzun yıllardır konut ve lüks yaşam projeleriyle adından söz ettiren Çakıroğulları İnşaat, yürüttüğü mali yeniden yapılandırma sürecinden olumlu sonuç alamadı. Bir süredir finansal darboğaz nedeniyle konkordato koruması altında faaliyetlerini sürdüren şirket hakkında mahkeme kritik kararını verdi ve iflasına hükmetti. Karar, başkentte gayrimenkul sektöründe dikkatle takip edilen davalardan biri olarak kayıtlara geçti. Ankara'da uzun yıllardır konut ve lüks yaşam projeleriyle adından söz ettiren Çakıroğulları İnşaat, yürüttüğü mali yeniden yapılandırma sürecinden olumlu sonuç alamadı. Bir süredir finansal darboğaz nedeniyle konkordato koruması altında faaliyetlerini sürdüren şirket hakkında mahkeme kritik kararını verdi ve iflasına hükmetti. Karar, başkentte gayrimenkul sektöründe dikkatle takip edilen davalardan biri olarak kayıtlara geçti. Konkordato da kurtarmadı! Ünlü inşaat şirketi iflas etti Mahkeme Tüm Koruma Tedbirlerini Kaldırdı İflas Kararı Resmen Açıklandı Sektörde Yankı Uyandıran Gelişme Ankara'da uzun yıllardır konut ve lüks yaşam projeleriyle adından söz ettiren Çakıroğulları İnşaat, yürüttüğü mali yeniden yapılandırma sürecinden olumlu sonuç alamadı. Bir süredir finansal darboğaz nedeniyle konkordato koruması altında faaliyetlerini sürdüren şirket hakkında mahkeme kritik kararını verdi ve iflasına hükmetti. Karar, başkentte gayrimenkul sektöründe dikkatle takip edilen davalardan biri olarak kayıtlara geçti. Ankara Ticaret Sicil Müdürlüğü'ne kayıtlı olan ve 2016 yılından bu yana özellikle konut projeleri, çok katlı yapılar ve lüks yaşam alanları inşa eden Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi, son dönemde artan mali baskılar nedeniyle konkordato talebinde bulunmuştu. Şirket, borçlarını yeniden yapılandırarak faaliyetlerini sürdürmeyi hedeflerken, süreç boyunca mahkeme tarafından sağlanan koruma tedbirleriyle çalışmalarına devam ediyordu. Ancak Ankara'da görülen davada mahkeme heyeti, yapılan değerlendirmeler sonucunda konkordato sürecinin sürdürülebilir olmadığına kanaat getirdi. Şirketin mali yapısındaki bozulmanın giderilemediği, borçların yeniden yapılandırılması için gerekli koşulların oluşmadığı yönündeki tespitler kararın seyrini belirledi. 2025/1029 esas numarasıyla yürütülen dava kapsamında 21 Mayıs 2026 tarihinde yapılan duruşmada kritik bir dönemeç yaşandı. Mahkeme, daha önce şirketi ekonomik baskılardan korumak amacıyla verilen geçici ve kesin mühlet kararlarını geçersiz kıldı. Böylece Çakıroğulları İnşaat'ın konkordato süreci boyunca yararlandığı tüm hukuki koruma zırhı ortadan kaldırılmış oldu. Kararla birlikte yalnızca mühlet uygulamaları değil, şirketin faaliyetlerini denetlemek üzere görevlendirilen konkordato komiserleri kurulunun da görevine son verildi. Bu gelişme, şirketin yönetim ve mali denetim sürecinde tamamen yeni bir dönemin başladığını ortaya koydu. Mahkeme, İcra ve İflas Kanunu'nun ilgili maddeleri kapsamında değerlendirme yaparak Çakıroğulları İnşaat'ın iflasına hükmetti. Kararda, şirketin mali yükümlülüklerini karşılayamayacak durumda olduğu ve konkordato sürecinin başarı şansını yitirdiği ifade edildi. Alınan karar doğrultusunda şirketin iflası 21 Mayıs 2026 tarihi saat 12.12 itibarıyla resmi olarak açılmış sayıldı. Bu gelişmeyle birlikte şirketin tüm ticari faaliyetleri ve mali süreçleri yasal iflas prosedürüne devredildi. Çakıroğulları İnşaat'ın iflas kararı, Ankara'daki inşaat ve gayrimenkul piyasasında da dikkatle karşılandı. Uzun yıllar boyunca özellikle konut üretimiyle bilinen şirketin konkordato sürecinden çıkamaması, sektörde yaşanan finansal sıkıntıların boyutunu bir kez daha gündeme taşıdı. Uzmanlar, son dönemde inşaat sektöründe artan maliyetler, finansmana erişimde yaşanan zorluklar ve daralan piyasa koşullarının birçok firmayı benzer süreçlere sürükleyebileceğine dikkat çekiyor. Çakıroğulları İnşaat hakkında verilen iflas kararı ise bu tabloyu somutlaştıran en çarpıcı örneklerden biri olarak değerlendiriliyor. Mahkeme kararıyla birlikte şirketin geleceğine ilişkin tüm süreç artık iflas idaresi tarafından yürütülecek. Bu kapsamda şirketin varlıklarının değerlendirilmesi, alacaklıların haklarının korunması ve yasal tasfiye sürecinin işletilmesi bekleniyor. Diğer Ekonomi Haberleri için tıklayın Bursa'da nefes kesen operasyon! Kaçak satışa hazırlıyorlardı 12 Haziran'da Okullar Tatil Mi? 12 Haziran Neden Tatil? MEB Duyurdu Bayram tatilinin acı bilançosu: Bakan Çiftçi açıkladı Bursa'da servis minibüsü kontrolden çıktı! Çok sayıda yaralı var Bursa'da inşaatta ölüm! 30 yıl önceki detay şoke etti... Yargıtay'dan emsal karar! İş yerinde çekilen fotoğraf başını yaktı</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Brezilya'da Kripto Para Birimleri İçin Yeni Kurallar: Merkez Bankası, VASP'lerden Sıkı ve Bağımsız Denetimler Yapılmasını Talep Ediyor Brezilya'da Kripto Para Birimleri İçin Yeni Kurallar: Merkez Bankası, VASP'lerden Sıkı ve Bağımsız Denetimler Yapılmasını Talep Ediyor Bitcoin News Brezilya'da Kripto Para Birimleri İçin Yeni Kurallar: Merkez Bankası, VASP'lerden Sıkı ve Bağımsız Denetimler Yapılmasını Talep Ediyor Bitcoin News</t>
+          <t>Konkordato da kurtarmadı! Ünlü inşaat şirketi iflas etti Konkordato da kurtarmadı! Ünlü inşaat şirketi iflas etti Bursada Bugün Ankara'da uzun yıllardır konut ve lüks yaşam projeleriyle adından söz ettiren Çakıroğulları İnşaat, yürüttüğü mali yeniden yapılandırma sürecinden olumlu sonuç alamadı. Bir süredir finansal darboğaz nedeniyle konkordato koruması altında faaliyetlerini sürdüren şirket hakkında mahkeme kritik kararını verdi ve iflasına hükmetti. Karar, başkentte gayrimenkul sektöründe dikkatle takip edilen davalardan biri olarak kayıtlara geçti. Konkordato da kurtarmadı! Ünlü inşaat şirketi iflas etti Mahkeme Tüm Koruma Tedbirlerini Kaldırdı İflas Kararı Resmen Açıklandı Sektörde Yankı Uyandıran Gelişme Ankara'da uzun yıllardır konut ve lüks yaşam projeleriyle adından söz ettiren Çakıroğulları İnşaat, yürüttüğü mali yeniden yapılandırma sürecinden olumlu sonuç alamadı. Ankara Ticaret Sicil Müdürlüğü'ne kayıtlı olan ve 2016 yılından bu yana özellikle konut projeleri, çok katlı yapılar ve lüks yaşam alanları inşa eden Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi, son dönemde artan mali baskılar nedeniyle konkordato talebinde bulunmuştu. Şirket, borçlarını yeniden yapılandırarak faaliyetlerini sürdürmeyi hedeflerken, süreç boyunca mahkeme tarafından sağlanan koruma tedbirleriyle çalışmalarına devam ediyordu. Ancak Ankara'da görülen davada mahkeme heyeti, yapılan değerlendirmeler sonucunda konkordato sürecinin sürdürülebilir olmadığına kanaat getirdi. Şirketin mali yapısındaki bozulmanın giderilemediği, borçların yeniden yapılandırılması için gerekli koşulların oluşmadığı yönündeki tespitler kararın seyrini belirledi. 2025/1029 esas numarasıyla yürütülen dava kapsamında 21 Mayıs 2026 tarihinde yapılan duruşmada kritik bir dönemeç yaşandı. Mahkeme, daha önce şirketi ekonomik baskılardan korumak amacıyla verilen geçici ve kesin mühlet kararlarını geçersiz kıldı. Böylece Çakıroğulları İnşaat'ın konkordato süreci boyunca yararlandığı tüm hukuki koruma zırhı ortadan kaldırılmış oldu. Kararla birlikte yalnızca mühlet uygulamaları değil, şirketin faaliyetlerini denetlemek üzere görevlendirilen konkordato komiserleri kurulunun da görevine son verildi. Bu gelişme, şirketin yönetim ve mali denetim sürecinde tamamen yeni bir dönemin başladığını ortaya koydu. Mahkeme, İcra ve İflas Kanunu'nun ilgili maddeleri kapsamında değerlendirme yaparak Çakıroğulları İnşaat'ın iflasına hükmetti. Kararda, şirketin mali yükümlülüklerini karşılayamayacak durumda olduğu ve konkordato sürecinin başarı şansını yitirdiği ifade edildi. Alınan karar doğrultusunda şirketin iflası 21 Mayıs 2026 tarihi saat 12.12 itibarıyla resmi olarak açılmış sayıldı. Bu gelişmeyle birlikte şirketin tüm ticari faaliyetleri ve mali süreçleri yasal iflas prosedürüne devredildi. Çakıroğulları İnşaat'ın iflas kararı, Ankara'daki inşaat ve gayrimenkul piyasasında da dikkatle karşılandı. Uzun yıllar boyunca özellikle konut üretimiyle bilinen şirketin konkordato sürecinden çıkamaması, sektörde yaşanan finansal sıkıntıların boyutunu bir kez daha gündeme taşıdı. Uzmanlar, son dönemde inşaat sektöründe artan maliyetler, finansmana erişimde yaşanan zorluklar ve daralan piyasa koşullarının birçok firmayı benzer süreçlere sürükleyebileceğine dikkat çekiyor. Çakıroğulları İnşaat hakkında verilen iflas kararı ise bu tabloyu somutlaştıran en çarpıcı örneklerden biri olarak değerlendiriliyor. Mahkeme kararıyla birlikte şirketin geleceğine ilişkin tüm süreç artık iflas idaresi tarafından yürütülecek. Bu kapsamda şirketin varlıklarının değerlendirilmesi, alacaklıların haklarının korunması ve yasal tasfiye sürecinin işletilmesi bekleniyor. Diğer Ekonomi Haberleri için tıklayın Bursa'da nefes kesen operasyon! MEB Duyurdu Bayram tatilinin acı bilançosu: Bakan Çiftçi açıkladı Bursa'da servis minibüsü kontrolden çıktı! Çok sayıda yaralı var Bursa'da inşaatta ölüm! 30 yıl önceki detay şoke etti... İş yerinde çekilen fotoğraf başını yaktı</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQS0VkNExDZ19wT3UxdDhBMUxtdVc4Q1h6MjNCOXRSek1GWW5mZWFwV3JmSGVYaWw2WFloV3Z6dl83VzBDMXV2R1pJVkc5SFNuWWgxS0dIVDMtN3FoMDlwVDNaem01ZDBQaERHQmh0aXJyZEktMUJSQ3kwU285SWJKM0hOa1REdTNiZXlSWE1OT1pRZ2pJTEVOcW45MmhOeTc2aXI2c0tGNElzV3g0d2pPb1JJeVdxVm4zWm1hSmY5UlYwT1d4QW8wcEJuQWVrSjVBSDNxcmx2aTI4Z1ZlTGRna1E3cDZ6YnBLWG5heVNSa0c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>https://www.bursadabugun.com/haber/konkordato-da-kurtarmadi-unlu-insaat-sirketi-iflas-etti-1925745.html</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Ankara | Bursa</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi:114:body | Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi:raw_legal</t>
+        </is>
+      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi Ankara Türkiye</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Çakıroğulları İnşaat</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Çakıroğulları İnşaat</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="n">
-        <v>111.22</v>
+        <v>177.3</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>9</v>
@@ -2602,27 +2692,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31 07:54:45</t>
+          <t>2026-06-01 08:12:34</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>kara para</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor</t>
+          <t>Türk inşaat devi bayramda iflas etti: Bölgede büyük ses getirdi</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Bitcoin News</t>
+          <t>Türk inşaat devi bayramda iflas etti: Bölgede büyük ses getirdi Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2632,52 +2722,40 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>inşaat</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Roman Storm, Adalet Bakanlığı ile yaşadığı gerçek deneyimlere atıfta bulunarak ve Tornado Cash davasıyla ilgili görüşlerini paylaşarak, “bankadan dışlanma” iddialarına karşı çıkıyor. Roman Storm, Adalet Bakanlığı ile yaşadığı gerçek deneyimlere atıfta bulunarak ve Tornado Cash davasıyla ilgili görüşlerini paylaşarak, “bankadan dışlanma” iddialarına karşı çıkıyor. Crypto News Yayınlandı: 31 May 2026 3:45 Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Tornado Cash davasında yeniden yargılanma ihtimali bulunan Storm, "banka hizmetlerinden mahrum bırakma"yı "saçmalık" olarak nitelendiren Lead Bank CEO'su Jackie Reses'in açıklamalarını sert bir dille eleştirdi. Storm, bu durumun gerçek olduğunu ve Adalet Bakanlığı'nın hesaplarına el koymasının ardından bunu defalarca yaşadığını vurguladı. YAZAN Sergio Goschenko PAYLAŞ Yayınlandı: 31 May 2026 3:45 Önemli Noktalar Roman Storm, yargılanması sırasında Adalet Bakanlığı'nı "bankadan çıkarılma" uygulamasını kullanmakla suçlayarak kripto paranın piyasadaki faydasını vurguladı. GoFundMe tarafından engellendikten sonra Storm, banka hesaplarına el konulmasının ardından savunmasını sürdürmek için kripto parayı kullandı. Kara para aklama suçlamasıyla ikinci bir duruşmaya çıkacak olan Roman Storm, hayatta kalmak için kripto para bağışlarına güvenecek. Tornado Cash Roman Storm: "Hesabım kapatıldı. Hem de birçok kez." Ethereum karıştırma protokolü Tornado Cash'in geliştiricisi Roman Storm, lisanssız para transferi işi yürütmek için komplo kurmaktan suçlu bulunmuş ve Adalet Bakanlığı'nı (DOJ) kovuşturma süreçlerinde banka hesaplarının dondurulmasını bir silah olarak kullandığını suçladı. Sosyal medyada Storm, banka hesaplarının kapatılmasını "tamamen saçmalık" olarak nitelendiren Lead Bank'ın kurucu ortağı ve CEO'su Jackie Reses'in açıklamalarını eleştirdi . "Amerika Birleşik Devletleri'nde 5.000 banka var. Çok sayıda Cumhuriyetçi eyaletimiz var. Bana, şirketimin genel merkezinin bulunduğu Missouri eyaletinin Kansas City şehri de dahil olmak üzere birçok Cumhuriyetçi eyalette, bu bankaların örneğin muhafazakar şirketlere hizmet vermek istemediğini mi söylüyorsunuz?" diye vurguladı . Storm, Reses'in iddialarını eleştirmek için sosyal medyaya başvurdu ve DOJ'dan celp alan bankaların hizmet sunmayı durdurması nedeniyle yargılanırken birçok kez bankacılık hizmetlerinden mahrum kaldığını belirtti. "Adalet Bakanlığı'nın kovuşturmasına maruz kalan herkes bu kalıbı çabucak öğrenir: Adalet Bakanlığı tüm hesaplarınıza celp gönderir göndermez, bankanız hesabınızı kapatır. Bu, kendinizi savunma yeteneğinizi kısıtlamak için kullandıkları araçlardan biridir; avukatlara ödeme yapmanızı, davanızı yönetmenizi ve ödeme gücünüzü korumanızı zorlaştırır," diye açıkladı Storm. Ayrıca Storm, GoFundMe'nin herhangi bir açıklama yapmadan bağışları iade etmesinin ardından, savunmasını finanse etmek için kripto paranın önemini vurguladı. "Kripto, hukuki savunmam için kitlesel fonlamaya olanak sağladı. Kripto olmasaydı, bu davayla hiç mücadele edemezdim. Kripto olmasaydı nasıl mücadeleye devam edebilirdim bilmiyorum," dedi. Son olarak, kara para aklama ve ABD yaptırımlarını ihlal etme suçlamalarıyla ikinci bir davayla karşı karşıya kalabileceği konusunda uyarıda bulunan Storm, yaklaşan sürecin finansmanı için yine kripto para bağışlarına güveneceğini belirtti. "İkinci bir davayla karşı karşıya kalabiliriz. Temyiz sürecinden geçmemiz gerekebilir. Önümüzde pek çok bilinmeyen var ve bunların her biri maliyet gerektiriyor," diye konuştu. Tornado Cash Kurucusu Ruhsatsız İşletme Faaliyetinden Suçlu Bulundu Tornado Cash geliştiricisi Roman Storm, Çarşamba günü lisanssız bir para transferi işletmesi yürütme komplosundan suçlu bulundu. read more. Şimdi oku Tornado Cash Kurucusu Ruhsatsız İşletme Faaliyetinden Suçlu Bulundu Tornado Cash geliştiricisi Roman Storm, Çarşamba günü lisanssız bir para transferi işletmesi yürütme komplosundan suçlu bulundu. read more. Şimdi oku Tornado Cash Kurucusu Ruhsatsız İşletme Faaliyetinden Suçlu Bulundu Şimdi oku Tornado Cash geliştiricisi Roman Storm, Çarşamba günü lisanssız bir para transferi işletmesi yürütme komplosundan suçlu bulundu. read more. İlgili makaleler 2 gün önce Sumitomo Mitsui Trust, Kart Puanlarını JPYC Stabilcoinlerine Dönüştürmek İçin Hashport ile İşbirliği Yaptı Crypto News 4 gün önce Sharplink ve Forward, 2,3 milyar dolarlık kripto varlıklarıyla Russell endekslerine girdi Crypto News 5 gün önce Meltem Demirors, Bitcoin ETF’lerinin Kripto Paraları Wall Street’in Etki Alanına Çekmesiyle Bankaların Kazandığını Söyledi Crypto News 6 gün önce Latin Amerika'dan Haberler: ABD, Sinaloa Karteli'nin kripto para aklamasına yaptırım uyguladı; Venezuela bir madencilik tesisini kapattı Crypto News 6 gün önce Meksika ve AB, Küresel Kripto Para Aklamayı Engellemek İçin Güçlerini Birleştiriyor Crypto News 24 May 2026 Libra Trust, Tartışmalı Kripto Paradan Elde Edilen Milyonları Arjantinli Şirketlere Dağıtmaya Hazırlanıyor Crypto News Bu haberdeki etiketle</t>
+          <t>Türk inşaat devi bayramda iflas etti: Bölgede büyük ses getirdi Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Bitcoin News Roman Storm, Adalet Bakanlığı ile yaşadığı gerçek deneyimlere atıfta bulunarak ve Tornado Cash davasıyla ilgili görüşlerini paylaşarak, “bankadan dışlanma” iddialarına karşı çıkıyor. Crypto News Yayınlandı: 31 May 2026 3:45 Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Tornado Cash davasında yeniden yargılanma ihtimali bulunan Storm, "banka hizmetlerinden mahrum bırakma"yı "saçmalık" olarak nitelendiren Lead Bank CEO'su Jackie Reses'in açıklamalarını sert bir dille eleştirdi. Storm, bu durumun gerçek olduğunu ve Adalet Bakanlığı'nın hesaplarına el koymasının ardından bunu defalarca yaşadığını vurguladı. YAZAN Sergio Goschenko PAYLAŞ Yayınlandı: 31 May 2026 3:45 Önemli Noktalar Roman Storm, yargılanması sırasında Adalet Bakanlığı'nı "bankadan çıkarılma" uygulamasını kullanmakla suçlayarak kripto paranın piyasadaki faydasını vurguladı. GoFundMe tarafından engellendikten sonra Storm, banka hesaplarına el konulmasının ardından savunmasını sürdürmek için kripto parayı kullandı. Kara para aklama suçlamasıyla ikinci bir duruşmaya çıkacak olan Roman Storm, hayatta kalmak için kripto para bağışlarına güvenecek. Tornado Cash Roman Storm: "Hesabım kapatıldı. Hem de birçok kez." Ethereum karıştırma protokolü Tornado Cash'in geliştiricisi Roman Storm, lisanssız para transferi işi yürütmek için komplo kurmaktan suçlu bulunmuş ve Adalet Bakanlığı'nı (DOJ) kovuşturma süreçlerinde banka hesaplarının dondurulmasını bir silah olarak kullandığını suçladı. Sosyal medyada Storm, banka hesaplarının kapatılmasını "tamamen saçmalık" olarak nitelendiren Lead Bank'ın kurucu ortağı ve CEO'su Jackie Reses'in açıklamalarını eleştirdi . "Amerika Birleşik Devletleri'nde 5.000 banka var. Bana, şirketimin genel merkezinin bulunduğu Missouri eyaletinin Kansas City şehri de dahil olmak üzere birçok Cumhuriyetçi eyalette, bu bankaların örneğin muhafazakar şirketlere hizmet vermek istemediğini mi söylüyorsunuz?" diye vurguladı . Storm, Reses'in iddialarını eleştirmek için sosyal medyaya başvurdu ve DOJ'dan celp alan bankaların hizmet sunmayı durdurması nedeniyle yargılanırken birçok kez bankacılık hizmetlerinden mahrum kaldığını belirtti. "Adalet Bakanlığı'nın kovuşturmasına maruz kalan herkes bu kalıbı çabucak öğrenir: Adalet Bakanlığı tüm hesaplarınıza celp gönderir göndermez, bankanız hesabınızı kapatır. Bu, kendinizi savunma yeteneğinizi kısıtlamak için kullandıkları araçlardan biridir; avukatlara ödeme yapmanızı, davanızı yönetmenizi ve ödeme gücünüzü korumanızı zorlaştırır," diye açıkladı Storm. Ayrıca Storm, GoFundMe'nin herhangi bir açıklama yapmadan bağışları iade etmesinin ardından, savunmasını finanse etmek için kripto paranın önemini vurguladı. Kripto olmasaydı, bu davayla hiç mücadele edemezdim. Kripto olmasaydı nasıl mücadeleye devam edebilirdim bilmiyorum," dedi. Son olarak, kara para aklama ve ABD yaptırımlarını ihlal etme suçlamalarıyla ikinci bir davayla karşı karşıya kalabileceği konusunda uyarıda bulunan Storm, yaklaşan sürecin finansmanı için yine kripto para bağışlarına güveneceğini belirtti. Tornado Cash Kurucusu Ruhsatsız İşletme Faaliyetinden Suçlu Bulundu Tornado Cash geliştiricisi Roman Storm, Çarşamba günü lisanssız bir para transferi işletmesi yürütme komplosundan suçlu bulundu. Şimdi oku Tornado Cash Kurucusu Ruhsatsız İşletme Faaliyetinden Suçlu Bulundu Tornado Cash geliştiricisi Roman Storm, Çarşamba günü lisanssız bir para transferi işletmesi yürütme komplosundan suçlu bulundu. Şimdi oku Tornado Cash Kurucusu Ruhsatsız İşletme Faaliyetinden Suçlu Bulundu Şimdi oku Tornado Cash geliştiricisi Roman Storm, Çarşamba günü lisanssız bir para transferi işletmesi yürütme komplosundan suçlu bulundu. İlgili makaleler 2 gün önce Sumitomo Mitsui Trust, Kart Puanlarını JPYC Stabilcoinlerine Dönüştürmek İçin Hashport ile İşbirliği Yaptı Crypto News 4 gün önce Sharplink ve Forward, 2,3 milyar dolarlık kripto varlıklarıyla Russell endekslerine girdi Crypto News 5 gün önce Meltem Demirors, Bitcoin ETF’lerinin Kripto Paraları Wall Street’in Etki Alanına Çekmesiyle Bankaların Kazandığını Söyledi Crypto News 6 gün önce Latin Amerika'dan Haberler: ABD, Sinaloa Karteli'nin kripto para aklamasına yaptırım uyguladı; Venezuela bir madencilik tesisini kapattı Crypto News 6 gün önce Meksika ve AB, Küresel Kripto Para Aklamayı Engellemek İçin Güçlerini Birleştiriyor Crypto News 24 May 2026 Libra Trust, Tartışmalı Kripto Paradan Elde Edilen Milyonları Arjantinli Şirketlere Dağıtmaya Hazırlanıyor Crypto News Bu haberdeki etiketle</t>
+          <t>Türk inşaat devi bayramda iflas etti: Bölgede büyük ses getirdi Türk inşaat devi bayramda iflas etti: Bölgede büyük ses getirdi Yeniçağ Gazetesi Türk inşaat devi bayramda iflas etti: Bölgede büyük ses getirdi Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://news.bitcoin.com/tr/roman-storm-adalet-bakanligini-yasal-savunmasini-baltalamak-icin-banka-hesaplarinin-dondurulmasini-bir-silah-olarak-kullandigini-iddia-ediyor/</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Antalya</t>
-        </is>
-      </c>
+          <t>https://www.yenicaggazetesi.com/turk-insaat-devi-cakirogullari-bayramda-iflas-etti-bolgede-buyuk-ses-getirdi-1035820h.htm</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Meltem</t>
-        </is>
-      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr"/>
@@ -2691,7 +2769,7 @@
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="n">
-        <v>163.5</v>
+        <v>60.3</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>10</v>
@@ -2700,27 +2778,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:04:42</t>
+          <t>2026-05-31 14:17:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>mali kriz</t>
+          <t>kara para</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Enerji krizi bir havacılık devini daha iflasa sürükledi</t>
+          <t>Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Enerji krizi bir havacılık devini daha iflasa sürükledi İlke Haber Ajansı</t>
+          <t>Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor T24</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -2730,18 +2808,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>enerji</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>ilkha.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. ilkha.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. ilkha.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Enerji krizi bir havacılık devini daha iflasa sürükledi Enerji krizi bir havacılık devini daha iflasa sürükledi İlke Haber Ajansı ilkha.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. ilkha.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. ilkha.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor T24 Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor Deutsche Bank'tan çarpıcı altın tahmini: Ons fiyatı 8 bin doları görebilir, merkez bankaları dolardan kaçıyor</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2751,7 +2833,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://ilkha.com/dunya/enerji-krizi-bir-havacilik-devini-daha-iflasa-surukledi-536261</t>
+          <t>https://t24.com.tr/ekonomi/deutsche-banktan-carpici-altin-tahmini-ons-fiyati-8-bin-dolari-gorebilir-merkez-bankalari-dolardan-kaciyor,1325409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
@@ -2777,7 +2859,7 @@
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="n">
-        <v>43.88</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>11</v>
@@ -2786,27 +2868,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 08:54:45</t>
+          <t>2026-05-31 10:49:57</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>kara para</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Banka, dolandırıcılık şüphesiyle 4,4 trilyon VND'yi bloke etti.</t>
+          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Banka, dolandırıcılık şüphesiyle 4,4 trilyon VND'yi bloke etti. Vietnam.vn</t>
+          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Bitcoin News</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2826,12 +2908,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Banka, dolandırıcılık şüphesiyle 4,4 trilyon VND'yi bloke etti. Vietnam.vn</t>
+          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Bitcoin News</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Banka, dolandırıcılık şüphesiyle 4,4 trilyon VND'yi bloke etti. Banka, dolandırıcılık şüphesiyle 4,4 trilyon VND'yi bloke etti. Vietnam.vn Banka, dolandırıcılık şüphesiyle 4,4 trilyon VND'yi bloke etti.</t>
+          <t>Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Bitcoin News Roman Storm, Adalet Bakanlığı’nı yasal savunmasını baltalamak için banka hesaplarının dondurulmasını bir silah olarak kullandığını iddia ediyor Bitcoin News</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2841,7 +2923,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNT3Z6aFRFaGJlWlFqdEZhNHdxSEdrb3hXZ0h5RWVpV2EzTnppbWZYN3RqMF85S0NmQ25yZ29Za2ZIZjJPcFVNNWc1a1lLZ21rYVFaUzRhSVhBc182c2xaRkNxUE5IWVpBaVB4N2ZTNHQyX25qcDJHdndRd2RwbVdXcjR3U1Rsdlpz?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxNcmFMY2JUdjlQVDVjN1p3OXJ1MnhWOXBfUWlvdVFKQkpfZlY1OTZjWTRRWlVTYklrYjc4SV9ZOC11ejBXQmdMOU56VktTbWp0LUs3UDVtbWR2ek1uZUV2dEd0QVRQMFNST0k0encwNkZfeTZtNUI3cTh3NkR4am9WNE94SDJMTnpvZ1diZS1ubkExUTFhaTg3M0ZibTA3XzdXWGJ1UE1hWFBrdGJwWXZSSEM5dHZ3NTAwc3VpaFltYXN6a2VDZURZXzh4bkg5T0x4eTdOd1JkMWJwWFYzODJQZ0FyRm1xQUczU3NGVEJQQkZ4eGhqaXZneWFXeUtZZm8?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
@@ -2867,7 +2949,7 @@
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="n">
-        <v>48.74</v>
+        <v>118.06</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>12</v>
@@ -2876,27 +2958,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 11:04:00</t>
+          <t>2026-06-01 06:03:00</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Avusturya Kodlu Aramalara Dikkat: Yeni Nesil Dolandırıcılık Yöntemi Deşifre Edildi</t>
+          <t>134 yıllık şirketten iflas başvurusu</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Avusturya Kodlu Aramalara Dikkat: Yeni Nesil Dolandırıcılık Yöntemi Deşifre Edildi Personel Sağlık Personeli Haber NET</t>
+          <t>134 yıllık şirketten iflas başvurusu Gazete Oksijen</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -2906,18 +2988,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>sağlık</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Avusturya Kodlu Aramalara Dikkat: Yeni Nesil Dolandırıcılık Yöntemi Deşifre Edildi Personel Sağlık Personeli Haber NET</t>
+          <t>134 yıllık şirketten iflas başvurusu Gazete Oksijen</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Avusturya Kodlu Aramalara Dikkat: Yeni Nesil Dolandırıcılık Yöntemi Deşifre Edildi Avusturya Kodlu Aramalara Dikkat: Yeni Nesil Dolandırıcılık Yöntemi Deşifre Edildi Personel Sağlık Personeli Haber NET Avusturya Kodlu Aramalara Dikkat: Yeni Nesil Dolandırıcılık Yöntemi Deşifre Edildi Personel Sağlık Personeli Haber NET</t>
+          <t>134 yıllık şirketten iflas başvurusu 134 yıllık şirketten iflas başvurusu Gazete Oksijen 134 yıllık şirketten iflas başvurusu Gazete Oksijen</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2927,7 +3013,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxONmhVRDNxZldtMXhNdlZxMjluY05VVXd5T05wanpqMVdDWnU3ZElySHZxeUt3QndDYlFGYTVmRi0tNTVsNk5YdTN3RTZmQjMtRGtVaUVXYkNLRkg2bUc4dlhsdDg3Qm9JbE5QQThHZWlpRFQzTV83T0lSWEpkZGJXWEFMdDE3MWs5YjNlU3haWXdmeElqMXcxWmtBOVU0WjBDZGNjMXd6VFJ5SEdjOWdwRlAxNVVVY0nSAbwBQVVfeXFMT2pDVEsxQk1qZkVUc2NoQ3dtV21naFFFWHdfam5XbWtOejlENUs0SmZCYUZ4bDJoYllvajRZQ0FLRGMyeWVTMUhKT2ZJdDRxQmp4NlR1Q0dhVDdTNG1GQldRUFNKaUZuTVpUbFZzTFlpZ25XVlctcy1yMTNxRjMyT2dSVEV5OFNqbjNwMndBTGFScVBkdWlmdDU1aDJWRUdkSmtFV1pkd0FsTUpaYVRkNkVGVjVTVWVMTzRoWTQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://gazeteoksijen.com/ekonomi/134-yillik-sirketten-iflas-basvurusu-277335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
@@ -2953,7 +3039,7 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="n">
-        <v>87.68000000000001</v>
+        <v>39.26</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>13</v>
@@ -2962,27 +3048,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 08:22:52</t>
+          <t>2026-06-01 05:36:00</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Mersin'deki Tekstil İşletmesinde Yangın</t>
+          <t>Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Mersin'deki Tekstil İşletmesinde Yangın Son Dakika</t>
+          <t>Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti Yeni Akit Gazetesi</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -2992,18 +3078,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>tekstil</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>gıda, şirket</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Toroslar'da bir tekstil deposunda çıkan yangın itfaiye ekipleri tarafından kontrol altına alındı. Toroslar'da bir tekstil deposunda çıkan yangın itfaiye ekipleri tarafından kontrol altına alındı. Toroslar'da bir tekstil deposunda çıkan yangın itfaiye ekipleri tarafından kontrol altına alındı.</t>
+          <t>Ekonomi Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti 2026-06-01 08:36 Güncelleme Tarihi: 2026-06-01 11:52 5 milyon dolarlık yatırımla pizza üretim robotları icat eden şirket, 10. yılında iflas ettiğini duyurdu. 3 ABD'de Seattle merkezli robotik şirketi Picnic Works, faaliyetlerini sona erdirerek varlıklarının tasfiye sürecini başlattı. 4 Picnic Works, tek bir işçinin saatte 130 pizza yapmasına imkan tanıyan robotik pizza yapma makinesi geliştirmişti. Fakat geliştirilen makinelerin pizzaları pişirmediği ortaya çıktı. Pizza malzemelerinin boyutları ve miktarları da yine çalışanlar tarafından seçilmek zorundaydı, makine sadece peyniri, sosları ve diğer malzemeleri ekliyordu. 5 Picnic Works'ün ilk robot pizza makinesi olan Leonardo, yaklaşık 2,1 metre genişliğinde, 1,5 metre yüksekliğinde ve 0,9 metre derinliğindeydi. 6 Ardından şirket, 1,5 metreden daha az genişliğe sahip Michelangelo adlı daha küçük bir model icat etti. 2016 senesinde kurulan şirket, 2024 yılında yüksek hacimli müşteri segmentine yönelmek için 5 milyon dolarlık yatırım almıştı. Fakat bu strateji şirketi ayakta tutmaya yetmedi. 7 Son senelerde yönetim kademesinde de değişiklikler yaşayan şirket iflastan sonra tasfiye sürecine girerken, şirketin varlıklarının tek bir alıcıya satıldığı belirtildi. 8 Şirket robot pizza makinelerini kontrol eden 20 çalışanıyla faaliyet gösteriyordu. Ekonomi Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti 2026-06-01 08:36 Güncelleme Tarihi: 2026-06-01 11:52 5 milyon dolarlık yatırımla pizza üretim robotları icat eden şirket, 10. yılında iflas ettiğini duyurdu. 3 ABD'de Seattle merkezli robotik şirketi Picnic Works, faaliyetlerini sona erdirerek varlıklarının tasfiye sürecini başlattı. 4 Picnic Works, tek bir işçinin saatte 130 pizza yapmasına imkan tanıyan robotik pizza yapma makinesi geliştirmişti. Fakat geliştirilen makinelerin pizzaları pişirmediği ortaya çıktı. Pizza malzemelerinin boyutları ve miktarları da yine çalışanlar tarafından seçilmek zorundaydı, makine sadece peyniri, sosları ve diğer malzemeleri ekliyordu. 5 Picnic Works'ün ilk robot pizza makinesi olan Leonardo, yaklaşık 2,1 metre genişliğinde, 1,5 metre yüksekliğinde ve 0,9 metre derinliğindeydi. 6 Ardından şirket, 1,5 metreden daha az genişliğe sahip Michelangelo adlı daha küçük bir model icat etti. 2016 senesinde kurulan şirket, 2024 yılında yüksek hacimli müşteri segmentine yönelmek için 5 milyon dolarlık yatırım almıştı. Fakat bu strateji şirketi ayakta tutmaya yetmedi. 7 Son senelerde yönetim kademesinde de değişiklikler yaşayan şirket iflastan sonra tasfiye sürecine girerken, şirketin varlıklarının tek bir alıcıya satıldığı belirtildi. 8 Şirket robot pizza makinelerini kontrol eden 20 çalışanıyla faaliyet gösteriyordu. Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti 5 milyon dolarlık yatırımla pizza üretim robotları icat eden şirket, 10. yılında iflas ettiğini duyurdu. ABD'de Seattle merkezli robotik şirketi Picnic Works, faaliyetlerini sona erdirerek varlıklarının tasfiye sürecini başlattı. Picnic Works, tek bir işçinin saatte 130 pizza yapmasına imkan tanıyan robotik pizza yapma makinesi geliştirmişti. Fakat geliştirilen makinelerin pizzaları pişirmediği ortaya çıktı. Pizza malzemelerinin boyutları ve miktarları da yine çalışanlar tarafından seçilmek zorundaydı, makine sadece peyniri, sosları ve diğer malzemeleri ekliyordu. Picnic Works'ün ilk robot pizza makinesi olan Leonardo, yaklaşık 2,1 metre genişliğinde, 1,5 metre yüksekliğinde ve 0,9 metre derinliğindeydi. Ardından şirket, 1,5 metreden daha az genişliğe sahip Michelangelo adlı daha küçük bir model icat etti. 2016 senesinde kurulan şirket, 2024 yılında yüksek hacimli müşteri segmentine yönelmek için 5 milyon dolarlık yatırım almıştı. Fakat bu strateji şirketi ayakta tutmaya yetmedi. Son senelerde yönetim kademesinde de değişiklikler yaşayan şirket iflastan sonra tasfiye sürecine girerken, şirketin varlıklarının tek bir alıcıya satıldığı belirtildi. Şirket robot pizza makinelerini kontrol eden 20 çalışanıyla faaliyet gösteriyordu.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Mersin'deki Tekstil İşletmesinde Yangın Mersin'deki Tekstil İşletmesinde Yangın Son Dakika Toroslar'da bir tekstil deposunda çıkan yangın itfaiye ekipleri tarafından kontrol altına alındı.</t>
+          <t>Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti Yeni Akit Gazetesi Ekonomi Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti 2026-06-01 08:36 Güncelleme Tarihi: 2026-06-01 11:52 5 milyon dolarlık yatırımla pizza üretim robotları icat eden şirket, 10. yılında iflas ettiğini duyurdu. 3 ABD'de Seattle merkezli robotik şirketi Picnic Works, faaliyetlerini sona erdirerek varlıklarının tasfiye sürecini başlattı. 4 Picnic Works, tek bir işçinin saatte 130 pizza yapmasına imkan tanıyan robotik pizza yapma makinesi geliştirmişti. Fakat geliştirilen makinelerin pizzaları pişirmediği ortaya çıktı. Pizza malzemelerinin boyutları ve miktarları da yine çalışanlar tarafından seçilmek zorundaydı, makine sadece peyniri, sosları ve diğer malzemeleri ekliyordu. 5 Picnic Works'ün ilk robot pizza makinesi olan Leonardo, yaklaşık 2,1 metre genişliğinde, 1,5 metre yüksekliğinde ve 0,9 metre derinliğindeydi. 6 Ardından şirket, 1,5 metreden daha az genişliğe sahip Michelangelo adlı daha küçük bir model icat etti. 2016 senesinde kurulan şirket, 2024 yılında yüksek hacimli müşteri segmentine yönelmek için 5 milyon dolarlık yatırım almıştı. Fakat bu strateji şirketi ayakta tutmaya yetmedi. 7 Son senelerde yönetim kademesinde de değişiklikler yaşayan şirket iflastan sonra tasfiye sürecine girerken, şirketin varlıklarının tek bir alıcıya satıldığı belirtildi. 8 Şirket robot pizza makinelerini kontrol eden 20 çalışanıyla faaliyet gösteriyordu. Çuvalla para harcayarak büyük yatırım yapmışlardı! Dev gıda şirketi sessiz sedasız iflas etti 5 milyon dolarlık yatırımla pizza üretim robotları icat eden şirket, 10. ABD'de Seattle merkezli robotik şirketi Picnic Works, faaliyetlerini sona erdirerek varlıklarının tasfiye sürecini başlattı. Picnic Works, tek bir işçinin saatte 130 pizza yapmasına imkan tanıyan robotik pizza yapma makinesi geliştirmişti. Picnic Works'ün ilk robot pizza makinesi olan Leonardo, yaklaşık 2,1 metre genişliğinde, 1,5 metre yüksekliğinde ve 0,9 metre derinliğindeydi. Ardından şirket, 1,5 metreden daha az genişliğe sahip Michelangelo adlı daha küçük bir model icat etti. Son senelerde yönetim kademesinde de değişiklikler yaşayan şirket iflastan sonra tasfiye sürecine girerken, şirketin varlıklarının tek bir alıcıya satıldığı belirtildi. Şirket robot pizza makinelerini kontrol eden 20 çalışanıyla faaliyet gösteriyordu.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -3013,19 +3103,11 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.sondakika.com/amp/haber-mersin-deki-tekstil-isletmesinde-yangin-19894040/</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Mersin</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Toroslar</t>
-        </is>
-      </c>
+          <t>https://m.yeniakit.com.tr/amp/foto-galeri/158871/cuvalla-para-harcayarak-buyuk-yatirim-yapmislardi-dev-gida-sirketi-sessiz-sedasiz-iflas-etti</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -3033,7 +3115,7 @@
       <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr"/>
@@ -3047,7 +3129,7 @@
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="n">
-        <v>70.93000000000001</v>
+        <v>105.5</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>14</v>
@@ -3056,27 +3138,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:31:32</t>
+          <t>2026-06-01 10:12:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>mali suç</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ha Lam mahallesindeki bir depoda çıkan yangın derhal söndürüldü.</t>
+          <t>Buca'daki yolsuzluğun detayları ortaya çıktı: Belediyede "rüşvet fabrikası" kurmuşlar</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Ha Lam mahallesindeki bir depoda çıkan yangın derhal söndürüldü. Vietnam.vn</t>
+          <t>Buca'daki yolsuzluğun detayları ortaya çıktı: Belediyede "rüşvet fabrikası" kurmuşlar Yirmidört Tv</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -3086,22 +3168,22 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Ha Lam mahallesindeki bir depoda çıkan yangın derhal söndürüldü. Vietnam.vn</t>
+          <t>Buca'daki yolsuzluğun detayları ortaya çıktı: Belediyede "rüşvet fabrikası" kurmuşlar Yirmidört Tv</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Ha Lam mahallesindeki bir depoda çıkan yangın derhal söndürüldü. Ha Lam mahallesindeki bir depoda çıkan yangın derhal söndürüldü. Vietnam.vn Ha Lam mahallesindeki bir depoda çıkan yangın derhal söndürüldü.</t>
+          <t>Buca'daki yolsuzluğun detayları ortaya çıktı: Belediyede "rüşvet fabrikası" kurmuşlar Buca'daki yolsuzluğun detayları ortaya çıktı: Belediyede "rüşvet fabrikası" kurmuşlar Yirmidört Tv Buca'daki yolsuzluğun detayları ortaya çıktı: Belediyede "rüşvet fabrikası" kurmuşlar Yirmidört Tv</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -3111,19 +3193,23 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQdEJrZXVUcHhOMGpaUTlTRVZSbFFyNHQ2NzB3WUxCZUVfekI5UGFxWUZac05kT1hXWkxwUUdobjVhbkZMTXo5NFFFZXd3RUJHWXphMEFuUGFIY01VZDRiSWR6bTNzVlJoeWtoenZMMGRrY0FlUENVM0NaaE4wZzMwbkJBcw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPVndjdmxIaTc3cENuQ1lxeFlrbk5iVVF0d3dKYU9tQTdKTml2aEU4MnpEZFVaRVhnb3BHWFdEVnRfLUd4QnhRWXpJOF9KX1pSYzRnblpiaHR1WjZtT2VVWDhaaHQ1TVh3cDkyemcxZXJoV2hJZGsyR1BVQk1OdDN4MTR5b240UGQ3dXJUc2xLNzNaSDBYY3FIWWszSlFGRy1kWEtOT1NaS1RXVjFQb1RPbW1qc3JjU2pYcEJxdQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>rüşvet fabrikası</t>
+        </is>
+      </c>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr"/>
@@ -3137,7 +3223,7 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="n">
-        <v>59.5</v>
+        <v>107.98</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>15</v>
@@ -3146,27 +3232,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:11:10</t>
+          <t>2026-06-01 05:15:08</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>örgütlü suç</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sarıgöl'de TARİŞ deposu önünde yangın: Ekipler sevk edildi</t>
+          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Sarıgöl'de TARİŞ deposu önünde yangın: Ekipler sevk edildi Manisa Aktif Haber</t>
+          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -3176,86 +3262,66 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Manisa'nın Sarıgöl ilçesinde bulunan ''TARİŞ'' deposu önündeki otluk alanda çıkan yangın paniğe neden oldu. Manisa'nın Sarıgöl ilçesinde bulunan ''TARİŞ'' deposu önündeki otluk alanda çıkan yangın paniğe neden oldu. Manisa'nın Sarıgöl ilçesinde bulunan ''TARİŞ'' deposu önündeki otluk alanda çıkan yangın paniğe neden oldu.</t>
+          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Sarıgöl'de TARİŞ deposu önünde yangın: Ekipler sevk edildi Sarıgöl'de TARİŞ deposu önünde yangın: Ekipler sevk edildi Manisa Aktif Haber Manisa'nın Sarıgöl ilçesinde bulunan ''TARİŞ'' deposu önündeki otluk alanda çıkan yangın paniğe neden oldu.</t>
+          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.manisaaktifhaber.com.tr/foto-galeri/sarigolde-taris-deposu-yangini-ekipler-sevk-edildi</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPbXM5VzU2ZnFuUGhEcXdzemhyVUdVaFVNNXMzRkZicklFZjAtT0tCRkVBTlp6TmJyYmp4eEI2eS1PQU04NVNHVHpvazVXYWstdi1HTWVCV3hzbm5ONmZMZXZUanhwY2EtVGUxNkhOS3QzQmhkWS00cG9pU3RncUJMSC15LWVJTTVyTl9jQzluWnI2Y2RxSS1iNDdBbWFENkRlaGNmNGpxaFNCTTh6OUV1Tk9aRlgtdmtBb2l3WjREODkzbkt5akNpV01iRmktWEdNVXc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Manisa</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Sarıgöl</t>
+          <t>Buca</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>de TARİŞ deposu</t>
-        </is>
-      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>de TARİŞ deposu Sarıgöl Manisa Türkiye</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tariş</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>Tariş</t>
-        </is>
-      </c>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>38.095238095238095</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="n">
-        <v>153.48</v>
+        <v>119.46</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>16</v>
@@ -3264,27 +3330,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 08:15:17</t>
+          <t>2026-05-31 17:11:07</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>usulsüzlük</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de tekstil ürünleri satan işletmede çıkan yangın söndürüldü</t>
+          <t>Araştırmacı gazetecilik ağı, vize şirketi VFS Global'i mercek altına aldı: Rüşvet, bot yazılımlar, zorunlu ödemeler...</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de tekstil ürünleri satan işletmede çıkan yangın söndürüldü ensondakika.com.tr</t>
+          <t>Araştırmacı gazetecilik ağı, vize şirketi VFS Global'i mercek altına aldı: Rüşvet, bot yazılımlar, zorunlu ödemeler... Gazete Oksijen</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -3294,86 +3360,58 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>işletme, tekstil</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Yerel Haberler Yayınlanma: 30 Mayıs 2026 - 11:15 Mersin'de tekstil ürünleri satan işletmede çıkan yangın söndürüldü Mersin - Mersin'in Toroslar ilçesinde tekstil ürünlerinin satıldığı iş yerinde çıkan yangın itfaiye ekiplerince söndürüldü. Yerel Haberler 30 Mayıs 2026 - 11:15 TAKİP ET A Büyüt A Küçült Mersin Haberleri - Mersin'in Toroslar ilçesinde tekstil ürünlerinin satıldığı iş yerinde çıkan yangın itfaiye ekiplerince söndürüldü. Tozkoparan Mahallesi'ndeki işletmenin malzeme deposu bölümünde henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine bölgeye 112 Acil Sağlık, polis ve itfaiye ekipleri sevk edildi. İtfaiye ekiplerinin müdahalesiyle yangın söndürüldü. İş yerinde hasara neden olan yangına müdahale anları, itfaiye ekiplerinin yaka kamerasınca görüntülendi. # Mersin# tekstil# Toroslar# yangın EDİTÖR Anadolu Ajansı Anadolu Ajansı haberleri. Anadolu Ajansı Son d</t>
+          <t>Araştırmacı gazetecilik ağı, vize şirketi VFS Global'i mercek altına aldı: Rüşvet, bot yazılımlar, zorunlu ödemeler... Gazete Oksijen</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de tekstil ürünleri satan işletmede çıkan yangın söndürüldü Mersin'de tekstil ürünleri satan işletmede çıkan yangın söndürüldü ensondakika.com.tr Yerel Haberler Yayınlanma: 30 Mayıs 2026 - 11:15 Mersin'de tekstil ürünleri satan işletmede çıkan yangın söndürüldü Mersin - Mersin'in Toroslar ilçesinde tekstil ürünlerinin satıldığı iş yerinde çıkan yangın itfaiye ekiplerince söndürüldü. Yerel Haberler 30 Mayıs 2026 - 11:15 TAKİP ET A Büyüt A Küçült Mersin Haberleri - Mersin'in Toroslar ilçesinde tekstil ürünlerinin satıldığı iş yerinde çıkan yangın itfaiye ekiplerince söndürüldü. Tozkoparan Mahallesi'ndeki işletmenin malzeme deposu bölümünde henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine bölgeye 112 Acil Sağlık, polis ve itfaiye ekipleri sevk edildi. İtfaiye ekiplerinin müdahalesiyle yangın söndürüldü. İş yerinde hasara neden olan yangına müdahale anları, itfaiye ekiplerinin yaka kamerasınca görüntülendi. # Mersin# tekstil# Toroslar# yangın EDİTÖR Anadolu Ajansı Anadolu Ajansı haberleri.</t>
+          <t>Araştırmacı gazetecilik ağı, vize şirketi VFS Global'i mercek altına aldı: Rüşvet, bot yazılımlar, zorunlu ödemeler... Araştırmacı gazetecilik ağı, vize şirketi VFS Global'i mercek altına aldı: Rüşvet, bot yazılımlar, zorunlu ödemeler... Gazete Oksijen Araştırmacı gazetecilik ağı, vize şirketi VFS Global'i mercek altına aldı: Rüşvet, bot yazılımlar, zorunlu ödemeler...</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxORFAyaUJ2SUpyd1BwU2pRZXlnekdZeVFxRnVaektDZEFPNmZ5WXhHckV4VXl5ZGktakxTNTlNSlYybW0xU3Y0ejd1cjFPYnRqMkxLTXFqZ1dMWTBOR0V5cWVUMllhSkdMWE5xOW9YNjdyQ2wwdzRsTk81cVVBM2ZuaWhWQjRucGp5NmxKTk11anZ0cEdzR3E2bF9DUG9oYThjeldPQzZXMjXSAbYBQVVfeXFMTnNsZDhjVE5vVHgzNWJFZjhpMWw3Wk1EYUV6M0Y1a29MbnZ5WFJmT3BxMjBqaGYtOEZJZlVaUF9aUEhwc1V0X25JSUUzRnhvVnUwclpHaGRzZE9UcVZyQmNfN2VQT0txRzY5c1BwVXFxZ1paV0kwQmFReDJONGNxa1dlUHdOSEprZWJIaGc4eWJuMWJCM01jaUtHSS0xelM3N2h6TmZQb25qNkNRdkhTcERUSjF5V0E?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Mersin</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Toroslar</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Tozkoparan Mahallesi</t>
-        </is>
-      </c>
+          <t>https://gazeteoksijen.com/dunya/uluslararasi-arastirmaci-gazetecilik-agindan-vfs-global-dosyasi-vize-almak-isteyenler-nasil-ek-ucret-odemeye-zorlandi-277221</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>ndeki işletmenin malzeme deposu</t>
-        </is>
-      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr"/>
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>ndeki işletmenin malzeme deposu Tozkoparan Mahallesi Toroslar Mersin Türkiye</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>MERSİN DEPO YAPI İNŞAAT MALZEMELERİ</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>MERSİN DEPO YAPI İNŞAAT MALZEMELERİ</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="n">
-        <v>195.08</v>
+        <v>99.58</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>17</v>
@@ -3382,27 +3420,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 19:34:42</t>
+          <t>2026-06-01 08:18:59</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>ihale yolsuzluğu</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Dev gıda şirketi iflas etti: 5 milyon dolarlık yatırım yapılmıştı</t>
+          <t>Buca Belediyesi’ne yolsuzluk operasyonu: Bankamatik memur sistemi ortaya çıktı</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Dev gıda şirketi iflas etti: 5 milyon dolarlık yatırım yapılmıştı Yeniçağ Gazetesi</t>
+          <t>Buca Belediyesi’ne yolsuzluk operasyonu: Bankamatik memur sistemi ortaya çıktı TRHaber</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3412,22 +3450,22 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>gıda, şirket</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Dev gıda şirketi iflas etti: 5 milyon dolarlık yatırım yapılmıştı Yeniçağ Gazetesi</t>
+          <t>Buca Belediyesi’ne yolsuzluk operasyonu: Bankamatik memur sistemi ortaya çıktı TRHaber</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Dev gıda şirketi iflas etti: 5 milyon dolarlık yatırım yapılmıştı Dev gıda şirketi iflas etti: 5 milyon dolarlık yatırım yapılmıştı Yeniçağ Gazetesi Dev gıda şirketi iflas etti: 5 milyon dolarlık yatırım yapılmıştı Yeniçağ Gazetesi</t>
+          <t>Buca Belediyesi’ne yolsuzluk operasyonu: Bankamatik memur sistemi ortaya çıktı Buca Belediyesi’ne yolsuzluk operasyonu: Bankamatik memur sistemi ortaya çıktı TRHaber Buca Belediyesi’ne yolsuzluk operasyonu: Bankamatik memur sistemi ortaya çıktı TRHaber</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3437,7 +3475,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.yenicaggazetesi.com/dev-gida-sirketi-iflas-etti-5-milyon-dolarlik-yatirim-yapilmisti-1035397h.htm</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNNWtsaTNFMlB6SzY4OHBtVDVWejhSOGkzZVRLLWVwUm5qWGc3SldLUXFleVowajZHakVXUzdnekhRTkJseWZqcXdOTk5sRUN0LW9XMVN6bXlzNHJLTmdCMVZGT1NNeUpGUlpsLUxmdklVcGkyNVI5ckNUT0llNVJpRGtBaVdyNE9laVN2eTVzN0VKNWdPd3FOeWpKc0Nla0Vjbi1PT0h3ZDNKM3A3dTd1TS1IUFgtdWxQVXJYRGhTeG9MZw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
@@ -3463,7 +3501,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="n">
-        <v>69.81999999999999</v>
+        <v>67.36</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>18</v>
@@ -3472,27 +3510,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 09:57:58</t>
+          <t>2026-05-31 14:56:22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>bankaya soruşturma</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Seattle merkezli pizzacı robot şirketi iflas etti</t>
+          <t>Muğla Ortaca’da Korku Dolu Anlar: Savrulan Araç Bankaya Daldı</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Seattle merkezli pizzacı robot şirketi iflas etti Ege Alternatif</t>
+          <t>Muğla Ortaca’da Korku Dolu Anlar: Savrulan Araç Bankaya Daldı Muğla Gazetesi</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3502,22 +3540,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Seattle merkezli pizzacı robot şirketi iflas etti Ege Alternatif</t>
+          <t>Muğla Ortaca’da Korku Dolu Anlar: Savrulan Araç Bankaya Daldı Muğla Gazetesi</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Seattle merkezli pizzacı robot şirketi iflas etti Seattle merkezli pizzacı robot şirketi iflas etti Ege Alternatif Seattle merkezli pizzacı robot şirketi iflas etti Ege Alternatif</t>
+          <t>Muğla Ortaca’da Korku Dolu Anlar: Savrulan Araç Bankaya Daldı Muğla Ortaca’da Korku Dolu Anlar: Savrulan Araç Bankaya Daldı Muğla Gazetesi Muğla Ortaca’da Korku Dolu Anlar: Savrulan Araç Bankaya Daldı Muğla Gazetesi</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3527,11 +3565,19 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOeTZURGJPUXFWbW1laTZJa2pCVVJyLVI1OVlzdE9IT25rbWlZSU1UcmRoV0pZcVFtZkJtNEtiRVp1UXVxNm1jTUdRdlpLS1l4eUhqSXJUNUE0MmNNQW42c09sN1RJRnhabTNOcmhIVDBvQWtidVR4SWlyS1dXZlZQVnJOSjVpUENPNk5KM00xS05RMGYzcjk0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPSWUzY0lyUHNOaWRUbDZ0NzlHVlF3VGt2N2w5MERBV3JBbUR1eWJTSmpBV2tNVE5wQ3FOLTBSeFF0b0Z3NHhnVVZqSnJvT042X1RKWWp4VE5Kc1FMVUpyY3FydGROa3lVT1lyZk91TTVUUkxRNlhFc1gwS3hhYWxZbERNZmoyRnVQLXozd3I5UjhZZi1lb2Z1R29FQWZmVVdWQVZQdDNhdGxlYW1hVUVjS1FqU041Q0cy?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Muğla</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Ortaca</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -3539,7 +3585,7 @@
       <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr"/>
@@ -3553,7 +3599,7 @@
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="n">
-        <v>49.14</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>19</v>
@@ -3562,27 +3608,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:45:17</t>
+          <t>2026-06-01 07:41:24</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Peter Schiff: Soruşturmada herhangi bir suç tespit edilmemesine rağmen banka iflas idaresine alındı</t>
+          <t>Bursa'da Ermetal Fabrikası'nda Kaynak Kaynaklı Yangın Paniği: Maddi Hasar Var, Can Kaybı Yok</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Peter Schiff: Soruşturmada herhangi bir suç tespit edilmemesine rağmen banka iflas idaresine alındı Traders Union</t>
+          <t>Bursa'da Ermetal Fabrikası'nda Kaynak Kaynaklı Yangın Paniği: Maddi Hasar Var, Can Kaybı Yok Ege Alternatif</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3592,22 +3638,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Peter Schiff: Soruşturmada herhangi bir suç tespit edilmemesine rağmen banka iflas idaresine alındı Traders Union</t>
+          <t>Bursa'da Ermetal Fabrikası'nda Kaynak Kaynaklı Yangın Paniği: Maddi Hasar Var, Can Kaybı Yok Ege Alternatif</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Peter Schiff: Soruşturmada herhangi bir suç tespit edilmemesine rağmen banka iflas idaresine alındı Peter Schiff: Soruşturmada herhangi bir suç tespit edilmemesine rağmen banka iflas idaresine alındı Traders Union Peter Schiff: Soruşturmada herhangi bir suç tespit edilmemesine rağmen banka iflas idaresine alındı Traders Union</t>
+          <t>Bursa'da Ermetal Fabrikası'nda Kaynak Kaynaklı Yangın Paniği: Maddi Hasar Var, Can Kaybı Yok Bursa'da Ermetal Fabrikası'nda Kaynak Kaynaklı Yangın Paniği: Maddi Hasar Var, Can Kaybı Yok Ege Alternatif Bursa'da Ermetal Fabrikası'nda Kaynak Kaynaklı Yangın Paniği: Maddi Hasar Var, Can Kaybı Yok Ege Alternatif</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3617,19 +3663,27 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPMVBmeTlFNl9qVVVONGpTTTRVRUxkd1FaV1VYTFZRTHRQWkJ0STRwM1B4RUFPdWhPZXlVeTIxcE1TX096dlk2djNXcEUtUHNnRTdHd2ZDQjVBNjNiaFZfTVJsdDU5bjBodFpBc1BtZWw4bkRRYkxPcW9mWTRZYUg3alVxeVlrbXRkOVVxMll2Z3JuNW40aW45WjdicEJzdTc3?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPdUJoeldKeldiSlR1YzI1YmpFRmFwbFY4OVNuS0hQdFI0c1BwS1hKcnUxLXdxaU9DT19aTUd5MjdpRVljTk9hMmpYS2ROMVF0UVVRWHFyTzh4YnVfXzZ0NGk5dTBCUUV4SE1ySjhwVlZVTDB2V01DM1EySkh0TVU1OHNMZXlSWlVCX0lUUFFneTdXMnIxQk9Jc2xuY2ZiTHNhZ1NaNEdLVlpRTzRfemdScWFWZW9meDM5alVjNm1TbjBYNjI3T2t6V2JLa1FaQQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>da Ermetal Fabrikası</t>
+        </is>
+      </c>
       <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr"/>
@@ -3643,7 +3697,7 @@
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="n">
-        <v>84.88</v>
+        <v>123.82</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>20</v>
@@ -3652,27 +3706,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31 06:34:22</t>
+          <t>2026-06-01 07:59:37</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>mali suç</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Hollanda’da Uyuşturucu Davası: Quincy Promes’in 8 Milyon Euroluk Mal Varlığına El Konulması İsteniyor</t>
+          <t>Fabrikada korkutan yangın: Kaynak çalışması faciaya yol açıyordu</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Hollanda’da Uyuşturucu Davası: Quincy Promes’in 8 Milyon Euroluk Mal Varlığına El Konulması İsteniyor Turkinfo</t>
+          <t>Fabrikada korkutan yangın: Kaynak çalışması faciaya yol açıyordu Yeni Şafak</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3682,40 +3736,56 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>mal varlığı</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Hollanda’da Uyuşturucu Davası: Quincy Promes’in 8 Milyon Euroluk Mal Varlığına El Konulması İsteniyor Turkinfo</t>
+          <t>GÜNDEM Ömerli Barajı’nda doluluk oranı yüzde 96’ya ulaştı GÜNDEM TEM Otoyolu'nu kullanacaklar dikkat: İstanbul yönü trafiğe kapatılıyor GÜNDEM Bayramda acı bilanço: Bakan Çiftçi trafik kazalarında yaşanan can kaybını açıkladı GÜNDEM Şüpheli tırda 5,5 milyon adet bandrolsüz sigara ele geçirildi GÜNDEM 29 bin 353 personelin yeri değişti: Jandarma’da dev atama listesi açıklandı Fabrikada korkutan yangın: Kaynak çalışması faciaya yol açıyordu Bursa’da bir fabrikada çıkan yangın paniğe neden oldu. İtfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alınan yangın, korku dolu anlar yaşattı. Yangın, saat 08.30 sıralarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi’nde faaliyet gösteren Ermetal fabrikasında meydana geldi. Edinilen bilgiye göre, fabrikada yapılan kaynak çalışması yangına neden oldu. Kısa sürede büyüyen alevleri fark eden çalışanlar durumu 112 Acil Çağrı Merkezi’ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. Ekiplerin hızlı müdahalesi sayesinde yangın kısa sürede kontrol altına alınırken, alevler çevredeki bölümlere sıçramadan söndürüldü. Yangında can kaybı ya da yaralanma yaşanmazken, fabrikada maddi hasar meydana geldi. Olayla ilgili inceleme başlatıldı.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Hollanda’da Uyuşturucu Davası: Quincy Promes’in 8 Milyon Euroluk Mal Varlığına El Konulması İsteniyor Hollanda’da Uyuşturucu Davası: Quincy Promes’in 8 Milyon Euroluk Mal Varlığına El Konulması İsteniyor Turkinfo Hollanda’da Uyuşturucu Davası: Quincy Promes’in 8 Milyon Euroluk Mal Varlığına El Konulması İsteniyor Turkinfo</t>
+          <t>Fabrikada korkutan yangın: Kaynak çalışması faciaya yol açıyordu Fabrikada korkutan yangın: Kaynak çalışması faciaya yol açıyordu Yeni Şafak GÜNDEM Ömerli Barajı’nda doluluk oranı yüzde 96’ya ulaştı GÜNDEM TEM Otoyolu'nu kullanacaklar dikkat: İstanbul yönü trafiğe kapatılıyor GÜNDEM Bayramda acı bilanço: Bakan Çiftçi trafik kazalarında yaşanan can kaybını açıkladı GÜNDEM Şüpheli tırda 5,5 milyon adet bandrolsüz sigara ele geçirildi GÜNDEM 29 bin 353 personelin yeri değişti: Jandarma’da dev atama listesi açıklandı Fabrikada korkutan yangın: Kaynak çalışması faciaya yol açıyordu Bursa’da bir fabrikada çıkan yangın paniğe neden oldu. İtfaiye ekiplerinin hızlı müdahalesiyle kontrol altına alınan yangın, korku dolu anlar yaşattı. Yangın, saat 08.30 sıralarında Osmangazi ilçesi Demirtaş Organize Sanayi Bölgesi’nde faaliyet gösteren Ermetal fabrikasında meydana geldi. Edinilen bilgiye göre, fabrikada yapılan kaynak çalışması yangına neden oldu. Kısa sürede büyüyen alevleri fark eden çalışanlar durumu 112 Acil Çağrı Merkezi’ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. Ekiplerin hızlı müdahalesi sayesinde yangın kısa sürede kontrol altına alınırken, alevler çevredeki bölümlere sıçramadan söndürüldü. Yangında can kaybı ya da yaralanma yaşanmazken, fabrikada maddi hasar meydana geldi. Olayla ilgili inceleme başlatıldı.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxONnFCUjZtTkZ5c2ZaZ2ZiU3ZlcUx4Sk1SVHNKdzdOZ3RnYkgtYk9fcDNpZkNUZFQ5V2JUWkM4alZ1Q2NaNjVmZS1fSHhMVHg1Y3hjQXRvQ0x0T21QNERaWUVDMzJiWUc5RnFLa3QxVHdfbVRTb0xHbWpoMjVONlVYTGxIRTU0cXRFWWxTTzkzRHVZY3ROalJCRnJjQXl0Ri1PNWxLb0dUdlRSdDVZSUZKYlZjRm1OWW1rV3NMRVBOYVBpX2lzbTZZ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPcjBnMXdJWW9QVkRSTHdWd0FzSE1uSmw2M01FbEtxcTJXUWkxTDI2eDNqYjZ4STVJRktvSWVkeFB1SVhiT3ZlOXBscUhEenZmWUJuR1E2MFdxSTlEUjllUnlqRndtUXdyaDZOVmxmZEZ5X2g3U3Y4ZnlOQkJTV1RMRkx4WC1Bc2Q1XzUtMjVXTnNBRWhEWGN3REEtOGoyczg4RHpOaGgtQVkzYzBVWlBRZzBR0gGyAUFVX3lxTE9yMGcxd0lZb1BWRFJMd1Z3QXNITW5KbDYzTUVsS3FxMldRaTFMMjZ4M2piNnhJNUlGS29JZWR4UHVJWGJPdmU5cGxxSER6dmZZQm5HUTYwV3FJOURSOWVSeWpGd21Rd3JoNk5WbGZkRnlfaDdTdjhmeU5CQlNXVExGTHhYLUFzZDVfNS0yNVdOc0FFaERYY3dEQS04ajJzODhEek5oaC1BWTNjMFVaUFFnMFE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Osmangazi</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr"/>
@@ -3729,7 +3799,7 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>120.95</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>21</v>
@@ -3738,27 +3808,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31 02:00:42</t>
+          <t>2026-06-01 06:51:07</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Ülke genelinde birçok insan, kendilerini banka çalışanı olarak tanıtan dolandırıcıların düzenlediği sahtekarlıkların kurbanı oldu.</t>
+          <t>Ayvalık'ta Saman Deposunda Yangın</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Ülke genelinde birçok insan, kendilerini banka çalışanı olarak tanıtan dolandırıcıların düzenlediği sahtekarlıkların kurbanı oldu. Vietnam.vn</t>
+          <t>Ayvalık'ta Saman Deposunda Yangın Son Dakika</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3768,44 +3838,56 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Ülke genelinde birçok insan, kendilerini banka çalışanı olarak tanıtan dolandırıcıların düzenlediği sahtekarlıkların kurbanı oldu. Vietnam.vn</t>
+          <t>Ayvalık'ta bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alındı. Ayvalık'ta bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alındı. Ayvalık'ta bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alındı. Ayvalık'ta Saman Deposunda Yangın Son Güncelleme: 01.06.2026 09:51 Ayvalık'ta bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alındı. Balıkesir'in Ayvalık ilçesinde bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. 150 Evler Mahallesi Talimname mevkisindeki saman deposunda henüz belirlenemeyen bir nedenle yangın çıktı. İhbar üzerine bölgeye Balıkesir Büyükşehir Belediyesi İtfaiye Daire Başkanlığına bağlı ekipler sevk edildi. Yangına, Ayvalık, Burhaniye ve Gömeç'ten gelen toplam 7 araç ve 19 personelle müdahale edildi. Ekiplerin yoğun çalışması sonucu yangın söndürüldü. Kaynak: AA Balıkesir'in Ayvalık ilçesinde bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. 150 Evler Mahallesi Talimname mevkisindeki saman deposunda henüz belirlenemeyen bir nedenle yangın çıktı. İhbar üzerine bölgeye Balıkesir Büyükşehir Belediyesi İtfaiye Daire Başkanlığına bağlı ekipler sevk edildi. Yangına, Ayvalık, Burhaniye ve Gömeç'ten gelen toplam 7 araç ve 19 personelle müdahale edildi. Ekiplerin yoğun çalışması sonucu yangın söndürüldü. Ayvalık'ta Saman Deposunda Yangın Ayvalık'ta bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alındı. Balıkesir'in Ayvalık ilçesinde bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. 150 Evler Mahallesi Talimname mevkisindeki saman deposunda henüz belirlenemeyen bir nedenle yangın çıktı. İhbar üzerine bölgeye Balıkesir Büyükşehir Belediyesi İtfaiye Daire Başkanlığına bağlı ekipler sevk edildi. Yangına, Ayvalık, Burhaniye ve Gömeç'ten gelen toplam 7 araç ve 19 personelle müdahale edildi. Ekiplerin yoğun çalışması sonucu yangın söndürüldü.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Ülke genelinde birçok insan, kendilerini banka çalışanı olarak tanıtan dolandırıcıların düzenlediği sahtekarlıkların kurbanı oldu. Ülke genelinde birçok insan, kendilerini banka çalışanı olarak tanıtan dolandırıcıların düzenlediği sahtekarlıkların kurbanı oldu. Vietnam.vn Ülke genelinde birçok insan, kendilerini banka çalışanı olarak tanıtan dolandırıcıların düzenlediği sahtekarlıkların kurbanı oldu.</t>
+          <t>Ayvalık'ta Saman Deposunda Yangın Ayvalık'ta Saman Deposunda Yangın Son Dakika Ayvalık'ta bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alındı. Ayvalık'ta Saman Deposunda Yangın Son Güncelleme: 01.06.2026 09:51 Ayvalık'ta bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alındı. Balıkesir'in Ayvalık ilçesinde bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. 150 Evler Mahallesi Talimname mevkisindeki saman deposunda henüz belirlenemeyen bir nedenle yangın çıktı. İhbar üzerine bölgeye Balıkesir Büyükşehir Belediyesi İtfaiye Daire Başkanlığına bağlı ekipler sevk edildi. Yangına, Ayvalık, Burhaniye ve Gömeç'ten gelen toplam 7 araç ve 19 personelle müdahale edildi. Ekiplerin yoğun çalışması sonucu yangın söndürüldü. Kaynak: AA Balıkesir'in Ayvalık ilçesinde bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. Ayvalık'ta Saman Deposunda Yangın Ayvalık'ta bir saman deposunda çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQeDBCblJkTUMyd3h6UXgweG10cVVhcE0wckNBOXVOWU04Q3gtb2w0dmh1WTNWMnd0RkRNUC1qMTRJaVlmUXFkSGp3S1FGVjVOUmRta2daNktZRkc0VWdILVdUUnBmWVRFckRVX1lWVmZRZnI4OExUeVdkcmpPUzlmZW5iME9SNW5jdEljOHRHTUpObHNveW9CRTJsbjRycUJV?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
+          <t>https://www.sondakika.com/amp/haber-ayvalik-ta-saman-deposunda-yangin-19897909/</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Balıkesir</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Ayvalık</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>150 Evler Mahallesi</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr"/>
@@ -3819,7 +3901,7 @@
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="n">
-        <v>107.66</v>
+        <v>100.5</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>22</v>
@@ -3828,27 +3910,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 17:00:00</t>
+          <t>2026-06-01 05:41:00</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki o bankaya dudak uçuklatan ceza!</t>
+          <t>Roket yakıtı fabrikasında yangın: Ölü ve yaralılar var</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki o bankaya dudak uçuklatan ceza! Düzce Damla Gazetesi</t>
+          <t>Roket yakıtı fabrikasında yangın: Ölü ve yaralılar var Nefes Gazetesi</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -3858,32 +3940,32 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>www.duzcedamla.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.duzcedamla.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.duzcedamla.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Roket yakıtı fabrikasında yangın: Ölü ve yaralılar var Nefes Gazetesi</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki o bankaya dudak uçuklatan ceza! Düzce'deki o bankaya dudak uçuklatan ceza! Düzce Damla Gazetesi www.duzcedamla.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.duzcedamla.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.duzcedamla.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Roket yakıtı fabrikasında yangın: Ölü ve yaralılar var Roket yakıtı fabrikasında yangın: Ölü ve yaralılar var Nefes Gazetesi Roket yakıtı fabrikasında yangın: Ölü ve yaralılar var Nefes Gazetesi</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.duzcedamla.com/haber/28053413/duzcedeki-o-bankaya-dudak-ucuklatan-ceza</t>
+          <t>https://www.nefes.com.tr/roket-yakiti-fabrikasinda-yangin-olu-ve-yaralilar-var-128664</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
@@ -3909,7 +3991,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="n">
-        <v>40.15</v>
+        <v>52.94</v>
       </c>
       <c r="AB24" s="2" t="n">
         <v>23</v>
@@ -3918,27 +4000,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 21:29:21</t>
+          <t>2026-06-01 05:30:00</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>şüpheli işlem</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Paranızı bankalardan tahsil edin! Akbank ve Garanti BBVA duyuru yaptı</t>
+          <t>Bir anda büyüdü! Depoda başlayan yangın çevredeki binaları sardı</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Paranızı bankalardan tahsil edin! Akbank ve Garanti BBVA duyuru yaptı Artı Gerçek</t>
+          <t>Bir anda büyüdü! Depoda başlayan yangın çevredeki binaları sardı Bursada Bugün</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -3948,36 +4030,44 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Paranızı bankalardan tahsil edin! Akbank ve Garanti BBVA duyuru yaptı Artı Gerçek</t>
+          <t>İstanbul'un Esenler ilçesinde gece saatlerinde çıkan yangın mahallede paniğe neden oldu. İçerisinde yanıcı malzemelerin bulunduğu bir depoda başlayan alevler kısa sürede büyüyerek çevredeki binaları tehdit etti. Gökyüzünü kaplayan yoğun duman ve yükselen alevler nedeniyle bölgeye çok sayıda ekip sevk edilirken, yangının çevredeki yapılara sıçraması endişeyi daha da artırdı. İstanbul'un Esenler ilçesinde gece saatlerinde çıkan yangın mahallede paniğe neden oldu. İçerisinde yanıcı malzemelerin bulunduğu bir depoda başlayan alevler kısa sürede büyüyerek çevredeki binaları tehdit etti. Gökyüzünü kaplayan yoğun duman ve yükselen alevler nedeniyle bölgeye çok sayıda ekip sevk edilirken, yangının çevredeki yapılara sıçraması endişeyi daha da artırdı. İstanbul'un Esenler ilçesinde gece saatlerinde çıkan yangın mahallede paniğe neden oldu. İçerisinde yanıcı malzemelerin bulunduğu bir depoda başlayan alevler kısa sürede büyüyerek çevredeki binaları tehdit etti. Gökyüzünü kaplayan yoğun duman ve yükselen alevler nedeniyle bölgeye çok sayıda ekip sevk edilirken, yangının çevredeki yapılara sıçraması endişeyi daha da artırdı.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Paranızı bankalardan tahsil edin! Akbank ve Garanti BBVA duyuru yaptı Paranızı bankalardan tahsil edin! Akbank ve Garanti BBVA duyuru yaptı Artı Gerçek Paranızı bankalardan tahsil edin! Akbank ve Garanti BBVA duyuru yaptı Artı Gerçek</t>
+          <t>Bir anda büyüdü! Depoda başlayan yangın çevredeki binaları sardı Bir anda büyüdü! Depoda başlayan yangın çevredeki binaları sardı Bursada Bugün İstanbul'un Esenler ilçesinde gece saatlerinde çıkan yangın mahallede paniğe neden oldu. İçerisinde yanıcı malzemelerin bulunduğu bir depoda başlayan alevler kısa sürede büyüyerek çevredeki binaları tehdit etti. Gökyüzünü kaplayan yoğun duman ve yükselen alevler nedeniyle bölgeye çok sayıda ekip sevk edilirken, yangının çevredeki yapılara sıçraması endişeyi daha da artırdı.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://artigercek.com/ekonomi/paranizi-bankalardan-tahsil-edin-akbank-ve-garanti-bbva-duyuru-yapti-346776h</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>https://www.bursadabugun.com/haber/bir-anda-buyudu-depoda-baslayan-yangin-cevredeki-binalari-sardi-1925645.html</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Esenler</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -3985,7 +4075,7 @@
       <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr"/>
@@ -3999,7 +4089,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="n">
-        <v>61.56</v>
+        <v>98.8</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>24</v>
@@ -4008,7 +4098,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:12:00</t>
+          <t>2026-06-01 08:11:00</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -4023,12 +4113,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Bankacılık Düzenleme ve Denetleme Kurumu Mesaj Yağmuruna Tutuldu!</t>
+          <t>Gaziantep'te bankalardan uyarı</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Bankacılık Düzenleme ve Denetleme Kurumu Mesaj Yağmuruna Tutuldu! Eskişehir Durum</t>
+          <t>Gaziantep'te bankalardan uyarı Gaziantep Oluşum Gazetesi</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4038,7 +4128,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>banka, bankacılık</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -4048,42 +4138,38 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Bankacılık Düzenleme ve Denetleme Kurumu mesaj yağmuruna tutuldu! Son birkaç ayda kart şikayetlerinde artış yaşanıyor. Kart kullanım sayısındaki artış, dolandırıcılık mağduriyeti yaşayan kişi sayısını da doğrudan etkiliyor. Hatalı kullanım veya şüpheli işlem bildirimlerinde yapılması gerekenler bu haberde. Bankacılık Düzenleme ve Denetleme Kurumu Şikayet Hattı Var mı? Kart başvurularında geçmiş yıllara göre artış yaşanıyor. Kredi kartı kullanan sayısı her geçen yıl daha da artıyor. Alışveriş, ödeme ve daha birçok alanda kullanıcı sayısı artarken yapılandırma başvuru sayısında da artış görülüyor. Son yıllarda özellikle de ihtiyaç kredilerinde yapılandırma ihtiyacı duyan kişi sayısında büyük bir artış var. Aynı zamanda toplam şikayet sayısındaki artışta dolandırıcılık mağdurlarından oluşuyor. BDDK şikayet etmek isteyenler tarafından vatandaş şikayet hattında büyük yoğunluk yaşanıyor. Bankacılık Düzenleme ve Denetleme Kurumu İletişim Bilgisi Her geçen gün artan dolandırıcılık suçu kart kullanıcılarını mağdur ediyor. Şüpheli kart kullanımlarında hiç vakit kaybetmeden doğrudan bankayla iletişime geçerek işlem iptalini talep etmek gerekiyor. Bankacılık Düzenleme ve Denetleme Kurumu itiraz hakkı kullanmayı kurallar ile tanımlıyor. 1- Bankacılık Düzenleme ve Denetleme Kurumu Telefon Numarası BDDK web sitesi üzerindeki iletişim sayfası üzerinden telefon ve adres bilgisine ulaşmak mümkün. BDDK vatandaş şikayet hattı 0850 222 22 35 olup, 08.30 – 02.00 saatleri arasında hizmet veren çağrı merkezi üzerinden iletişime geçilebilir. Ayrıca, kendini BDDK personeli olarak tanıtan başka telefon numaraları tarafından iletişime geçilen numaralara da itibar etmemek gerekiyor. 2- Bankacılık Düzenleme ve Denetleme Kurumu Adres Bilgisi BDDK Müşteri Hizmetleri 08.30 – 02.00 saatleri arasında hizmet vermektedir. Her türlü bankacılık şikayetlerinde çağrı merkezi yetkilileri ile iletişime geçilebilir. BDDK iletişim sayfasındaki adres bilgileri; Finanskent Mahallesi Finans Caddesi No 42/1 34760 Ümraniye/İSTANBUL Ticari Müşterilerde Artış Ticari müşteri sayısı geçmiş yıllara göre büyük oranda arttı. 2024 yılında 5 bin civarında başvuru bulunurken 2025 yılında 10 bin civarında seyretti. 2026 yılında ise bu rakamın 2 katı olarak tamamlanması öngörülüyor. · Ticari müşteri sayısı geçmiş yıllara göre arttı. · İcraya ilişkin sorunlar her geçen gün artıyor. · Kredi notu araştıran kişi sayısında da artış gözleniyor. · Kara listeye kayıtlı kişi sayısı da yükselişte. Bankacılık Düzenleme ve Denetleme Kurumu Mesaj Yağmuruna Tutuldu! BDDK şikayet hattı yoğunluk yaşıyor. Kart dolandırıcılığı, şüpheli işlemler ve bankacılık şikayetlerinde yapılması gerekenleri öğrenin. Bankacılık Düzenleme ve Denetleme Kurumu Şikayet Hattı Var mı? Bankacılık Düzenleme ve Denetleme Kurumu İletişim Bilgisi Ticari Müşterilerde Artış Bankacılık Düzenleme ve Denetleme Kurumu mesaj yağmuruna tutuldu! Son birkaç ayda kart şikayetlerinde artış yaşanıyor. Kart kullanım sayısındaki artış, dolandırıcılık mağduriyeti yaşayan kişi sayısını da doğrudan etkiliyor. Hatalı kullanım veya şüpheli işlem bildirimlerinde yapılması gerekenler bu haberde. Kart başvurularında geçmiş yıllara göre artış yaşanıyor. Kredi kartı kullanan sayısı her geçen yıl daha da artıyor. Alışveriş, ödeme ve daha birçok alanda kullanıcı sayısı artarken yapılandırma başvuru sayısında da artış görülüyor. Son yıllarda özellikle de ihtiyaç kredilerinde yapılandırma ihtiyacı duyan kişi sayısında büyük bir artış var. Aynı zamanda toplam şikayet sayısındaki artışta dolandırıcılık mağdurlarından oluşuyor. BDDK şikayet etmek isteyenler tarafından vatandaş şikayet hattında büyük yoğunluk yaşanıyor. Her geçen gün artan dolandırıcılık suçu kart kullanıcılarını mağdur ediyor. Şüpheli kart kullanımlarında hiç vakit kaybetmeden doğrudan bankayla iletişime geçerek işlem iptalini talep etmek gerekiyor. Bankacılık Düzenleme ve Denetleme Kurumu itiraz hakkı kullanmayı kurallar ile tanımlıyor. BDDK web sitesi üzerindeki iletişim sayfası üzerinden telefon ve adres bilgisine ulaşmak mümkün. BDDK vatandaş şikayet hattı 0850 222 22 35 olup, 08.30 – 02.00 saatleri arasında hizmet veren çağrı merkezi üzerinden iletişime geçilebilir. Ayrıca, kendini BDDK personeli olarak tanıtan başka telefon numaraları tarafından iletişime geçilen numaralara da itibar etmemek gerekiyor. BDDK Müşteri Hizmetleri 08.30 – 02.00 saatleri arasında hizmet vermektedir. Her türlü bankacılık şikayetlerinde çağrı merkezi yetkilileri ile iletişime geçilebilir. BDDK iletişim sayfasındaki adres bilgileri; Finanskent Mahallesi Finans Caddesi No 42/1 34760 Ümraniye/İSTANBUL Ticari müşteri sayısı geçmiş yıllara göre büyük oranda arttı. 2024 yılında 5 bin civarında başvuru bulunurken 2025 yılında 10 bin civarında seyretti. 2026 yılında ise bu rakamın 2 katı olarak tamamlanması öngörülüyor. · Ticari müşteri sayısı geçmiş yıllara göre arttı. · İcraya ilişkin sorunlar her geçen gün artıyor. · Kredi notu araştıran kişi sayısında da artış gözleniyor. · Kara listeye kayıtlı kişi sayısı da yükselişte.</t>
+          <t>Dijital bankacılık işlemlerinin yaygınlaşmasıyla birlikte kredi kartı kullanımı artarken, Gaziantep’te vatandaşların en çok dikkat ettiği ko... Dijital bankacılık işlemlerinin yaygınlaşmasıyla birlikte kredi kartı kullanımı artarken, Gaziantep’te vatandaşların en çok dikkat ettiği konuların başında güve... Dijital bankacılık işlemlerinin yaygınlaşmasıyla birlikte kredi kartı kullanımı artarken, Gaziantep’te vatandaşların en çok dikkat ettiği ko...</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Bankacılık Düzenleme ve Denetleme Kurumu Mesaj Yağmuruna Tutuldu! Bankacılık Düzenleme ve Denetleme Kurumu Mesaj Yağmuruna Tutuldu! Eskişehir Durum Bankacılık Düzenleme ve Denetleme Kurumu mesaj yağmuruna tutuldu! Son birkaç ayda kart şikayetlerinde artış yaşanıyor. Kart kullanım sayısındaki artış, dolandırıcılık mağduriyeti yaşayan kişi sayısını da doğrudan etkiliyor. Hatalı kullanım veya şüpheli işlem bildirimlerinde yapılması gerekenler bu haberde. Bankacılık Düzenleme ve Denetleme Kurumu Şikayet Hattı Var mı? Kart başvurularında geçmiş yıllara göre artış yaşanıyor. Kredi kartı kullanan sayısı her geçen yıl daha da artıyor. Alışveriş, ödeme ve daha birçok alanda kullanıcı sayısı artarken yapılandırma başvuru sayısında da artış görülüyor. Son yıllarda özellikle de ihtiyaç kredilerinde yapılandırma ihtiyacı duyan kişi sayısında büyük bir artış var. Aynı zamanda toplam şikayet sayısındaki artışta dolandırıcılık mağdurlarından oluşuyor. BDDK şikayet etmek isteyenler tarafından vatandaş şikayet hattında büyük yoğunluk yaşanıyor. Bankacılık Düzenleme ve Denetleme Kurumu İletişim Bilgisi Her geçen gün artan dolandırıcılık suçu kart kullanıcılarını mağdur ediyor. Bankacılık Düzenleme ve Denetleme Kurumu itiraz hakkı kullanmayı kurallar ile tanımlıyor. 1- Bankacılık Düzenleme ve Denetleme Kurumu Telefon Numarası BDDK web sitesi üzerindeki iletişim sayfası üzerinden telefon ve adres bilgisine ulaşmak mümkün. BDDK vatandaş şikayet hattı 0850 222 22 35 olup, 08.30 – 02.00 saatleri arasında hizmet veren çağrı merkezi üzerinden iletişime geçilebilir. Ayrıca, kendini BDDK personeli olarak tanıtan başka telefon numaraları tarafından iletişime geçilen numaralara da itibar etmemek gerekiyor. 2- Bankacılık Düzenleme ve Denetleme Kurumu Adres Bilgisi BDDK Müşteri Hizmetleri 08.30 – 02.00 saatleri arasında hizmet vermektedir. BDDK iletişim sayfasındaki adres bilgileri; Finanskent Mahallesi Finans Caddesi No 42/1 34760 Ümraniye/İSTANBUL Ticari Müşterilerde Artış Ticari müşteri sayısı geçmiş yıllara göre büyük oranda arttı. 2024 yılında 5 bin civarında başvuru bulunurken 2025 yılında 10 bin civarında seyretti. 2026 yılında ise bu rakamın 2 katı olarak tamamlanması öngörülüyor. · Kredi notu araştıran kişi sayısında da artış gözleniyor. BDDK şikayet hattı yoğunluk yaşıyor. Kart dolandırıcılığı, şüpheli işlemler ve bankacılık şikayetlerinde yapılması gerekenleri öğrenin. Bankacılık Düzenleme ve Denetleme Kurumu İletişim Bilgisi Ticari Müşterilerde Artış Bankacılık Düzenleme ve Denetleme Kurumu mesaj yağmuruna tutuldu! Her geçen gün artan dolandırıcılık suçu kart kullanıcılarını mağdur ediyor. BDDK web sitesi üzerindeki iletişim sayfası üzerinden telefon ve adres bilgisine ulaşmak mümkün. BDDK Müşteri Hizmetleri 08.30 – 02.00 saatleri arasında hizmet vermektedir. BDDK iletişim sayfasındaki adres bilgileri; Finanskent Mahallesi Finans Caddesi No 42/1 34760 Ümraniye/İSTANBUL Ticari müşteri sayısı geçmiş yıllara göre büyük oranda arttı.</t>
+          <t>Gaziantep'te bankalardan uyarı Gaziantep'te bankalardan uyarı Gaziantep Oluşum Gazetesi Dijital bankacılık işlemlerinin yaygınlaşmasıyla birlikte kredi kartı kullanımı artarken, Gaziantep’te vatandaşların en çok dikkat ettiği ko... Dijital bankacılık işlemlerinin yaygınlaşmasıyla birlikte kredi kartı kullanımı artarken, Gaziantep’te vatandaşların en çok dikkat ettiği konuların başında güve...</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNWTdHbGZtaEJ3NXh6R0NOczQ1TWtKZy1aMkkwSDJvNkNpZ1N5VUVQNTM3eXdrN09ZQjJSZzkyMUROc0dtN3BUeDRnVnZldUtnbl9BTXp0OElVZ09nOUlGQTBocGNxWkVSWjg3QzN3Yk9wZTZOOUZMUml1Z1VxekhwX1Q5TzJOdHE5SVlSaTRFTDdRMWQyVGJmNXo5MNIBmwFBVV95cUxNWTdHbGZtaEJ3NXh6R0NOczQ1TWtKZy1aMkkwSDJvNkNpZ1N5VUVQNTM3eXdrN09ZQjJSZzkyMUROc0dtN3BUeDRnVnZldUtnbl9BTXp0OElVZ09nOUlGQTBocGNxWkVSWjg3QzN3Yk9wZTZOOUZMUml1Z1VxekhwX1Q5TzJOdHE5SVlSaTRFTDdRMWQyVGJmNXo5MA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>https://www.gaziantepolusum.com/haber/28073220/gaziantepte-bankalardan-uyari</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Finanskent Mahallesi</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>Finanskent Mahallesi Finans Caddesi</t>
-        </is>
-      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr"/>
@@ -4097,194 +4183,14 @@
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="n">
-        <v>107.75</v>
+        <v>41.51</v>
       </c>
       <c r="AB26" s="2" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30 09:05:01</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>soruşturma</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Fiziksel Risk / Yangın</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş'ta şantiye yangınında ağır yaralanan işçi hayatını kaybetti</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş'ta şantiye yangınında ağır yaralanan işçi hayatını kaybetti Saray Medya</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>şantiye</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>şantiye</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş'ta şantiye yangınında ağır yaralanan işçi hayatını kaybetti Saray Medya</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş'ta şantiye yangınında ağır yaralanan işçi hayatını kaybetti Kahramanmaraş'ta şantiye yangınında ağır yaralanan işçi hayatını kaybetti Saray Medya Kahramanmaraş'ta şantiye yangınında ağır yaralanan işçi hayatını kaybetti Saray Medya</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>browser_failed</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.saraymedya.com/haber/kahramanmaras-ta-santiye-yangininda-agir-yaralanan-isci-hayatini-kaybetti_266923/</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr"/>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr"/>
-      <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="2" t="inlineStr"/>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr"/>
-      <c r="Z27" s="2" t="inlineStr"/>
-      <c r="AA27" s="2" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="AB27" s="2" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-30 09:10:23</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>yangın</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Fiziksel Risk / Yangın</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Turizm sezonunun en yoğun olduğu dönemde yangın güvenliğinin sağlanması.</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Turizm sezonunun en yoğun olduğu dönemde yangın güvenliğinin sağlanması. Vietnam.vn</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>turizm</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Turizm sezonunun en yoğun olduğu dönemde yangın güvenliğinin sağlanması. Vietnam.vn</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Turizm sezonunun en yoğun olduğu dönemde yangın güvenliğinin sağlanması. Turizm sezonunun en yoğun olduğu dönemde yangın güvenliğinin sağlanması. Vietnam.vn Turizm sezonunun en yoğun olduğu dönemde yangın güvenliğinin sağlanması.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>browser_failed</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPak9INlpFb21xVE5yTnNQRXBwaXE5U2hRRTMtcmxTQW01eVFYRlVLLWNIZnNUaHVrT2lmNTFRR0FYWVZURkczd1pNMnRKZGRXMF9FeHNjYUpqczc0R1ZPbzVDOFVNVlF6QlNuZWhMcE1SN1pra0NKb2dGQzNHZGROc2p3?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr"/>
-      <c r="V28" s="2" t="inlineStr"/>
-      <c r="W28" s="2" t="inlineStr"/>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr"/>
-      <c r="Z28" s="2" t="inlineStr"/>
-      <c r="AA28" s="2" t="n">
-        <v>73.58</v>
-      </c>
-      <c r="AB28" s="2" t="n">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AB28"/>
+  <autoFilter ref="A1:AB26"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -4311,8 +4217,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -512,22 +512,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:11:00</t>
+          <t>2026-06-04 06:27:08</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı</t>
+          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Çağdaş Kocaeli Gazetesi</t>
+          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Canlı Gaste</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -537,12 +537,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli | Kütahya</t>
+          <t>Diyarbakır | İzmir</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Derince | Gebze | Gediz</t>
+          <t>Çeşme</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -556,22 +556,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 12:34:00</t>
+          <t>2026-06-04 06:05:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul merkezli 27 ilde büyük operasyon! 4.6 milyarlık mal varlığına el konuldu</t>
+          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul merkezli 27 ilde büyük operasyon! 4.6 milyarlık mal varlığına el konuldu Gazete Vatan</t>
+          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu birgun.net</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -581,10 +581,14 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Diyarbakır | İzmir</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Çeşme</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
@@ -596,22 +600,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 02:01:12</t>
+          <t>2026-06-04 07:34:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CHP kurultayında MASAK raporu krizi: Delegeler geri çekilebilir mi?</t>
+          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>CHP kurultayında MASAK raporu krizi: Delegeler geri çekilebilir mi? Haberhergün</t>
+          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -632,22 +636,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:01:00</t>
+          <t>2026-06-04 02:50:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Antalya Büyükşehir'e yönelik soruşturmada dijital materyallere el konuldu</t>
+          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Antalya Büyükşehir'e yönelik soruşturmada dijital materyallere el konuldu Karadeniz Gazetesi</t>
+          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Evrensel.net</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -655,35 +659,51 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | İstanbul</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Osmangazi | Küçükçekmece</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Ağaç AŞ</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>İSTANBUL AĞAÇ A.Ş</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:31:44</t>
+          <t>2026-06-03 12:11:56</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Kamu görevlisi ve banka çalışanı gibi tanıttılar: 17 ilde operasyon</t>
+          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kamu görevlisi ve banka çalışanı gibi tanıttılar: 17 ilde operasyon Nefes Gazetesi</t>
+          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Haberler</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -704,22 +724,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 12:57:45</t>
+          <t>2026-06-04 05:38:26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 1 trilyon lira gördü: 32 yaşındaki genç hayatının şokunu yaşadı</t>
+          <t>Bursa Haberleri</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 1 trilyon lira gördü: 32 yaşındaki genç hayatının şokunu yaşadı İlke TV</t>
+          <t>Bursa Haberleri - Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü - Yerel Haberler Hürriyet</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -727,35 +747,43 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Torun Geri Dönüşüm - Küçükbalıklı Hurda Kağıt Alımı</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 09:56:00</t>
+          <t>2026-06-03 12:18:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bir anda banka hesabına 1 trilyon TL geldi! Hayatı altüst oldu: MASAK soruşturma başlattı</t>
+          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını!</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bir anda banka hesabına 1 trilyon TL geldi! Hayatı altüst oldu: MASAK soruşturma başlattı Doğru Haber</t>
+          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını! Ege'de Sonsöz</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -765,37 +793,41 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Denizli Kauçuk</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:56:26</t>
+          <t>2026-06-04 02:27:59</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Van'da 999 Milyar TL'lik bakiye ortaya çıktı, MASAK devrede</t>
+          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Van'da 999 Milyar TL'lik bakiye ortaya çıktı, MASAK devrede Vansesi Gazetesi</t>
+          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri bolgegundemi.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -805,7 +837,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Bursa</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -820,7 +852,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:57:00</t>
+          <t>2026-06-04 06:18:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -830,12 +862,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti"</t>
+          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti" tv100 Haber</t>
+          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Amed Haber</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -845,10 +877,14 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>Diyarbakır | İzmir</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Çeşme</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
@@ -860,7 +896,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 09:43:00</t>
+          <t>2026-06-04 06:00:00</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -870,12 +906,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Van'da bir kişinin hesabına '1 trilyon' lira yattı, MASAK harekete geçti!</t>
+          <t>15 milyar liralık kara para ağı! Hepsine el konuldu</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Van'da bir kişinin hesabına '1 trilyon' lira yattı, MASAK harekete geçti! Elips Haber</t>
+          <t>15 milyar liralık kara para ağı! Hepsine el konuldu babaocagi.com.tr</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -885,10 +921,14 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>Diyarbakır | İzmir</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Çeşme</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
@@ -900,22 +940,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 09:48:38</t>
+          <t>2026-06-04 07:25:29</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CHP’de MASAK Depremi: Yeni Parti mi Kuruluyor?</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CHP’de MASAK Depremi: Yeni Parti mi Kuruluyor? bolgegundemi.com</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -923,16 +963,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Aksaray | Karaman | Konya</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Selçuklu</t>
-        </is>
-      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
@@ -944,22 +976,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:20:40</t>
+          <t>2026-06-04 06:07:14</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: MASAK tüm hesaplarını dondurdu</t>
+          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: MASAK tüm hesaplarını dondurdu YatırımX</t>
+          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -967,7 +999,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
@@ -980,22 +1016,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 13:13:00</t>
+          <t>2026-06-04 06:17:45</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti</t>
+          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti Sözcü Gazetesi</t>
+          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1003,51 +1039,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Konya</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Karapınar</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Salih Karakaya Tarım Ürünleri Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Salih Karakaya Tarim Ürünleri</t>
-        </is>
-      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 04:06:14</t>
+          <t>2026-06-03 12:19:00</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devi iflas bayrağını çekti</t>
+          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devi iflas bayrağını çekti Bold Medya</t>
+          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu STAR - Haberler</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1057,45 +1077,41 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Ankara</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Çakıroğulları İnşaat</t>
-        </is>
-      </c>
+          <t>Denizli | Malatya</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Kale</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:11:43</t>
+          <t>2026-06-03 17:21:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Dev ilaç şirketi iflasın eşiğinde: Konkardota talebinde bulundu!</t>
+          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dev ilaç şirketi iflasın eşiğinde: Konkardota talebinde bulundu! GZT</t>
+          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü İnegöl Online</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1103,8 +1119,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>İnegöl</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
@@ -1116,7 +1140,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:44:50</t>
+          <t>2026-06-04 07:48:14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1126,12 +1150,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devinden kötü haber: Mahkeme biletini kesti, resmen iflas etti</t>
+          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devinden kötü haber: Mahkeme biletini kesti, resmen iflas etti Yeni Akit Gazetesi</t>
+          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1152,22 +1176,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:44:00</t>
+          <t>2026-06-04 03:41:40</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17 ilde nitelikli dolandırıcılık şebekelerine operasyon! 261 tutuklama... 1 milyar 50 milyon liralık taşınmaz varlığına el konuldu</t>
+          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17 ilde nitelikli dolandırıcılık şebekelerine operasyon! 261 tutuklama... 1 milyar 50 milyon liralık taşınmaz varlığına el konuldu Yirmidört Tv</t>
+          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Vietnam.vn</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1175,11 +1199,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Zonguldak</t>
-        </is>
-      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1192,7 +1212,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:55:56</t>
+          <t>2026-06-03 09:30:00</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1202,12 +1222,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tasfiye halindeki şirketin o ürününe satış yasağı getirildi: İşte dikkat çeken karar!</t>
+          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Tasfiye halindeki şirketin o ürününe satış yasağı getirildi: İşte dikkat çeken karar! Kayseri Anadolu Haber</t>
+          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1228,7 +1248,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:40:00</t>
+          <t>2026-06-03 14:41:37</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1238,12 +1258,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi</t>
+          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi T24</t>
+          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi Foreks.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1251,20 +1271,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Battal Holding A.Ş</t>
+          <t>Akın Tekstil A.Ş</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Battal Group</t>
+          <t>AKIN TEKSTİL</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1276,7 +1292,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:40:00</t>
+          <t>2026-06-04 06:30:00</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1286,12 +1302,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>KAP duyurdu: Türk İlaç ve Serum Sanayi A.Ş.'den konkordato başvurusu</t>
+          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>KAP duyurdu: Türk İlaç ve Serum Sanayi A.Ş.'den konkordato başvurusu 24 Saat Gazetesi Ankara</t>
+          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı Kanal 46</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1299,7 +1315,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Kahramanmaraş</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1312,7 +1332,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:48:11</t>
+          <t>2026-06-03 10:44:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1322,12 +1342,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Borsadaki Şirkete Konkordato Şoku! Halka açık şirket konkordato ilan etti!</t>
+          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Borsadaki Şirkete Konkordato Şoku! Halka açık şirket konkordato ilan etti! ParaMedya</t>
+          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor Mavi Marmara Gazetesi</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1335,7 +1355,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Kocaeli</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1348,22 +1372,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:37:23</t>
+          <t>2026-06-03 09:47:15</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Borsa İstanbul konkordato ilan eden şirket hakkında yeni kararını açıkladı</t>
+          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon!</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Borsa İstanbul konkordato ilan eden şirket hakkında yeni kararını açıkladı Rota Borsa</t>
+          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! GDH.Digital</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1384,7 +1408,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 20:12:00</t>
+          <t>2026-06-04 07:49:41</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1394,12 +1418,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Borsada İşlem Gören Şirketten Konkordato Başvurusu</t>
+          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor!</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Borsada İşlem Gören Şirketten Konkordato Başvurusu Paranın Yönü</t>
+          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! EmlakDream</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1420,22 +1444,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 05:01:51</t>
+          <t>2026-06-03 17:54:22</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp…</t>
+          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç</t>
+          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1443,16 +1467,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Buca</t>
-        </is>
-      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
@@ -1464,22 +1480,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 17:00:00</t>
+          <t>2026-06-04 04:11:41</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anlaştığım ücreti aldım; CHP’li vekille polemiğe girmem</t>
+          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anlaştığım ücreti aldım; CHP’li vekille polemiğe girmem T24</t>
+          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1487,16 +1503,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Kartal</t>
-        </is>
-      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
@@ -1508,22 +1516,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:12:00</t>
+          <t>2026-06-03 09:08:15</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi.</t>
+          <t>İzmirli üç medikal şirkete konkordato uzatması</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi. Mersin Haber</t>
+          <t>İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1531,47 +1539,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Kültür A.Ş | Medya A.Ş</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Kültür A.Ş Genel Müdürlüğü</t>
-        </is>
-      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 06:23:00</t>
+          <t>2026-06-03 12:12:35</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Rüşvetle tahliye: Mahkeme başkanı hakim görevden uzaklaştırıldı</t>
+          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Rüşvetle tahliye: Mahkeme başkanı hakim görevden uzaklaştırıldı Personel Sağlık Personeli Haber NET</t>
+          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1579,47 +1575,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Adana</t>
-        </is>
-      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Personel Sağlık</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Personel Sağlık</t>
-        </is>
-      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 01:00:00</t>
+          <t>2026-06-03 10:50:38</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Yasa dışı bahisçiler yoğun para transferine takıldı</t>
+          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Yasa dışı bahisçiler yoğun para transferine takıldı Yeni Şafak</t>
+          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün Merhaba Gazetesi</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1629,7 +1613,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Nevşehir</t>
+          <t>Konya</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1644,22 +1628,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 17:28:51</t>
+          <t>2026-06-03 14:41:47</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ordu'da mobilya atölyesinde yangın</t>
+          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ordu'da mobilya atölyesinde yangın Sözcü Gazetesi</t>
+          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1667,16 +1651,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Ordu</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Çatalpınar</t>
-        </is>
-      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
@@ -1688,22 +1664,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 04:00:08</t>
+          <t>2026-06-03 15:46:28</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Vietnamlı işletmeler yangın önleme ve yangın söndürme alanındaki teknolojik yeteneklerini sergiliyor.</t>
+          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Vietnamlı işletmeler yangın önleme ve yangın söndürme alanındaki teknolojik yeteneklerini sergiliyor. Vietnam.vn</t>
+          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1724,22 +1700,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:55:00</t>
+          <t>2026-06-03 09:45:31</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>İTÜ’de dolandırıcılık iddiası: Spor tesisleri çalışanlarına operasyon</t>
+          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>İTÜ’de dolandırıcılık iddiası: Spor tesisleri çalışanlarına operasyon birgun.net</t>
+          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu velev.press</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1747,35 +1723,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Battal Holding A.Ş</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Battal Group</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 07:53:00</t>
+          <t>2026-06-03 10:24:46</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var</t>
+          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var tele1.com.tr</t>
+          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı Samanyolu Haber</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1788,11 +1776,7 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Esenyurt</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
@@ -1804,22 +1788,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 12:14:00</t>
+          <t>2026-06-03 15:49:03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>60 milyarlık dolandırıcılık ağına operasyon: 4 şirkete kayyum atandı</t>
+          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>60 milyarlık dolandırıcılık ağına operasyon: 4 şirkete kayyum atandı Ortadoğu Gazetesi</t>
+          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1827,11 +1811,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
+      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1844,22 +1824,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 14:54:00</t>
+          <t>2026-06-04 06:39:17</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Yargıda rüşvet iddiası : HSK, Hakim Mustafa Ece'yi görevden uzaklaştırdı</t>
+          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Yargıda rüşvet iddiası : HSK, Hakim Mustafa Ece'yi görevden uzaklaştırdı İşçi Haber</t>
+          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1880,22 +1860,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 14:33:00</t>
+          <t>2026-06-03 09:28:00</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'de sahte çek şoku: Bankada gerçek ortaya çıktı</t>
+          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'de sahte çek şoku: Bankada gerçek ortaya çıktı Yıldırım Gazetesi</t>
+          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı Cumhuriyet</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1903,16 +1883,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl</t>
-        </is>
-      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
@@ -1924,22 +1896,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:29:46</t>
+          <t>2026-06-03 16:43:00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>27 ilde yatırım dolandırıcılığı operasyonu: 89 gözaltı, 4 şirket ve 15 akaryakıt istasyonuna kayyım</t>
+          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>27 ilde yatırım dolandırıcılığı operasyonu: 89 gözaltı, 4 şirket ve 15 akaryakıt istasyonuna kayyım Gaziantep Sabah Gazetesi</t>
+          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1947,20 +1919,32 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Bitlis</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Bitlis Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:45:00</t>
+          <t>2026-06-03 22:06:29</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1970,12 +1954,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: Bütün hesapları donduruldu</t>
+          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: Bütün hesapları donduruldu Ekonomim</t>
+          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Vietnam.vn</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1996,22 +1980,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:53:00</t>
+          <t>2026-06-03 11:32:00</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Jahangar Takalo Kimdir? Banka Hesabında 1 Trilyon TL Görünen Şaşırtan Olay Gündem Oldu</t>
+          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Jahangar Takalo Kimdir? Banka Hesabında 1 Trilyon TL Görünen Şaşırtan Olay Gündem Oldu Uyan 32</t>
+          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek sonhaber.eu</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2019,11 +2003,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Van</t>
-        </is>
-      </c>
+      <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2036,22 +2016,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:10:23</t>
+          <t>2026-06-03 11:38:00</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>CHP’li Özgür Özel ve milletvekilleri hakkında rüşvet fezlekesi: Muhittin Böcek’ten para istendiği iddiası yargıda</t>
+          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CHP’li Özgür Özel ve milletvekilleri hakkında rüşvet fezlekesi: Muhittin Böcek’ten para istendiği iddiası yargıda ehamedya.com.tr</t>
+          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2059,7 +2039,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2072,7 +2056,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 05:30:00</t>
+          <t>2026-06-03 15:26:35</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2082,12 +2066,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Emekliye Büyük Rekabet: Haziran Promosyonlarında Bankalar Rakamları Güncelledi!</t>
+          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü?</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Emekliye Büyük Rekabet: Haziran Promosyonlarında Bankalar Rakamları Güncelledi! konyayenigun.com</t>
+          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2108,7 +2092,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 00:10:08</t>
+          <t>2026-06-03 13:28:43</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2118,12 +2102,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Beş kişi, Kamboçya'daki suçlulara satış yapmak amacıyla "paravan şirketler" kurmak ve 100'den fazla banka hesabı açmakla suçlandı.</t>
+          <t>Sürekli banka kartı kullananlar yandı</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Beş kişi, Kamboçya'daki suçlulara satış yapmak amacıyla "paravan şirketler" kurmak ve 100'den fazla banka hesabı açmakla suçlandı. Vietnam.vn</t>
+          <t>Sürekli banka kartı kullananlar yandı Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2144,22 +2128,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 09:50:16</t>
+          <t>2026-06-03 13:33:47</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CHP delegelerinin banka kayıtları incelenecek: Denizli’den 15 isim var</t>
+          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu!</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CHP delegelerinin banka kayıtları incelenecek: Denizli’den 15 isim var Denizli Haber</t>
+          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! Erzincan Birlik Medya</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2167,11 +2151,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Denizli</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2184,22 +2164,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:43:02</t>
+          <t>2026-06-03 11:14:00</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Bankacı ve Uzman Kılığıyla Vurgun: 89 Şüpheli Yakalandı</t>
+          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Bankacı ve Uzman Kılığıyla Vurgun: 89 Şüpheli Yakalandı Ajans Balıklıgöl</t>
+          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2207,8 +2187,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Esenyurt</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
@@ -2220,7 +2208,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 07:02:23</t>
+          <t>2026-06-03 09:31:16</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2230,12 +2218,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Havai Fişek Fabrikasındaki Patlama Sonrası Gıda Alarmı: Yetkililer Soruşturma Başlattı</t>
+          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede!</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Havai Fişek Fabrikasındaki Patlama Sonrası Gıda Alarmı: Yetkililer Soruşturma Başlattı Malta Haber</t>
+          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2245,11 +2233,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Fişek Fabrikasındaki Patlama Sonrası Gıda</t>
-        </is>
-      </c>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -2260,7 +2244,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 21:25:46</t>
+          <t>2026-06-03 12:50:00</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2270,12 +2254,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Kosmos 5 Milyon Dolar Yatırım Aldı ve Şirketlerin Gizli IT Soruşturma Maliyetlerini Ortadan Kaldırmalarına Yardımcı Oluyor</t>
+          <t>Yedi vize şirketine soruşturma</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Kosmos 5 Milyon Dolar Yatırım Aldı ve Şirketlerin Gizli IT Soruşturma Maliyetlerini Ortadan Kaldırmalarına Yardımcı Oluyor Unite.AI</t>
+          <t>Yedi vize şirketine soruşturma Memurlar.Net</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2283,7 +2267,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2296,22 +2284,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 20:37:00</t>
+          <t>2026-06-04 06:47:24</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Yenidoğan Yoğun Bakım Ünitesinde Kötü Muamele İddiasına Soruşturma Açıldı</t>
+          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu!</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Yenidoğan Yoğun Bakım Ünitesinde Kötü Muamele İddiasına Soruşturma Açıldı Personel Sağlık Personeli Haber NET</t>
+          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Takvim</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2319,7 +2307,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul | Samsun</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2332,22 +2324,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 15:25:00</t>
+          <t>2026-06-03 11:30:50</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Sanayide gizli kapaklı dönem bitti: Bildirmeyene 75 bin TL ceza ve lisans iptali!</t>
+          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Sanayide gizli kapaklı dönem bitti: Bildirmeyene 75 bin TL ceza ve lisans iptali! Bu Sabah Malatya</t>
+          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Vietnam.vn</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2368,22 +2360,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 15:00:01</t>
+          <t>2026-06-03 09:38:09</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümle 1</t>
+          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümle 1 Donanım Günlüğü</t>
+          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Habertürk</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2391,8 +2383,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | İstanbul | Sivas | Tekirdağ | Van</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>İnegöl | Saray</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
@@ -2641,27 +2641,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:11:00</t>
+          <t>2026-06-04 06:27:08</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>banka soruşturma</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı</t>
+          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Çağdaş Kocaeli Gazetesi</t>
+          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Canlı Gaste</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2671,22 +2671,18 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>mal varlığı</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli Gebze Muallimköy'de bir alüminyum fabrikasının kimyasal atık alanında yangın çıktı. Yangın söndürülürken fabrikada hasar oluştu. Kocaeli Gebze Muallimköy'de bir alüminyum fabrikasının kimyasal atık alanında yangın çıktı. Yangın söndürülürken fabrikada hasar oluştu. Kocaeli Gebze Muallimköy'de bir alüminyum fabrikasının kimyasal atık alanında yangın çıktı. Yangın söndürülürken fabrikada hasar oluştu. 02 Haziran 2026 - Asayiş Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Gebze Muallimköy Mahallesi'nde bulunan bir alüminyum fabrikasının kimyasal atık alanında yangın çıktı. İtfaiye ekiplerinin müdahalesiyle söndürülen yangında fabrikada hasar oluştu. Gebze ilçesinde bulunan bir alüminyum fabrikasında yangın çıktı. Muallimköy Mahallesi Gediz Caddesi 'ndeki fabrikanın kimyasal atıkların bulunduğu bölümünde başlayan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. Yangın, Kocaeli 'nin sanayi bölgeleri arasında yer alan Gebze Muallimköy Mahallesi'nde meydana geldi. Alüminyum fabrikasındaki kimyasal atıkların bulunduğu alanda başlayan alevleri görenlerin ihbarı üzerine bölgeye itfaiye ekipleri sevk edildi. Yangının ana bilgisi: Gebze Muallimköy Mahallesi Gediz Caddesi'ndeki alüminyum fabrikasında kimyasal atıkların bulunduğu alanda yangın çıktı. Yangın itfaiye ekiplerince söndürülürken, fabrikanın bir bölümünde hasar oluştu. Kimyasal atık alanında başladı Fabrikadaki yangın, kimyasal atıkların bulunduğu alanda çıktı. Kısa sürede fark edilen yangın için 112 Acil Çağrı Merkezi'ne ihbarda bulunuldu. İhbarın ardından adrese itfaiye ekipleri yönlendirildi. Ekipler, yangının fabrikanın diğer bölümlerine yayılmaması için çalışma yürüttü. İtfaiye ekipleri yangını söndürdü Bölgeye gelen itfaiye ekiplerinin müdahalesiyle yangın kontrol altına alınarak söndürüldü. Yangında fabrikanın bir bölümünde hasar meydana geldi. Yangının çıkış nedeni ve hasarın boyutuna ilişkin inceleme sürecinin ardından ayrıntıların netleşmesi bekleniyor. Gebze'deki fabrika yangınında öne çıkan bilgiler İlçe Gebze Mahalle Muallimköy Mahallesi Adres bilgisi Gediz Caddesi Yangının çıktığı yer Alüminyum fabrikasındaki kimyasal atık alanı Müdahale eden ekip İtfaiye Son durum Yangın söndürüldü, fabrikanın bir bölümünde hasar oluştu YORUM YAP Gebze’de bayram acısı: Bisiklet kazasında ağır yaralanan 13 yaşındaki Atabey kurtarılamadı Karamürsel'i yasa boğan ölüm: Çocuk doktoru Esra Erdağ Özdemirci ölü bulundu TEM Otoyolu'nda Kocaelili aileye dehşeti yaşatmıştı: Trafik terörü estiren o magandaya öyle bir ceza kesildi ki... Derince’de yürek yakan kaza: 18 yaşındaki Çağrı hayatını kaybetti! Arkadaşlarından duygusal veda Gölcük'teki ATV faciasında yürek yakan veda: Anne ve oğlu toprağa verildi 02 Haziran 2026 - Asayiş Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Gebze Muallimköy Mahallesi'nde bulunan bir alüminyum fabrikasının kimyasal atık alanında yangın çıktı. İtfaiye ekiplerinin müdahalesiyle söndürülen yangında fabrikada hasar oluştu. Gebze ilçesinde bulunan bir alüminyum fabrikasında yangın çıktı. Muallimköy Mahallesi Gediz Caddesi 'ndeki fabrikanın kimyasal atıkların bulunduğu bölümünde başlayan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. Yangın, Kocaeli 'nin sanayi bölgeleri arasında yer alan Gebze Muallimköy Mahallesi'nde meydana geldi. Alüminyum fabrikasındaki kimyasal atıkların bulunduğu alanda başlayan alevleri görenlerin ihbarı üzerine bölgeye itfaiye ekipleri sevk edildi. Yangının ana bilgisi: Gebze Muallimköy Mahallesi Gediz Caddesi'ndeki alüminyum fabrikasında kimyasal atıkların bulunduğu alanda yangın çıktı. Yangın itfaiye ekiplerince söndürülürken, fabrikanın bir bölümünde hasar oluştu. Kimyasal atık alanında başladı Fabrikadaki yangın, kimyasal atıkların bulunduğu alanda çıktı. Kısa sürede fark edilen yangın için 112 Acil Çağrı Merkezi'ne ihbarda bulunuldu. İhbarın ardından adrese itfaiye ekipleri yönlendirildi. Ekipler, yangının fabrikanın diğer bölümlerine yayılmaması için çalışma yürüttü. İtfaiye ekipleri yangını söndürdü Bölgeye gelen itfaiye ekiplerinin müdahalesiyle yangın kontrol altına alınarak söndürüldü. Yangında fabrikanın bir bölümünde hasar meydana geldi. Yangının çıkış nedeni ve hasarın boyutuna ilişkin inceleme sürecinin ardından ayrıntıların netleşmesi bekleniyor. Gebze'deki fabrika yangınında öne çıkan bilgiler İlçe Gebze Mahalle Muallimköy Mahallesi Adres bilgisi Gediz Caddesi Yangının çıktığı yer Alüminyum fabrikasındaki kimyasal atık alanı Müdahale eden ekip İtfaiye Son durum Yangın söndürüldü, fabrikanın bir bölümünde hasar oluştu Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Kimyasal atık alanında başladı İtfaiye ekipleri yangını söndürdü Gebze ilçesinde bulunan bir alüminyum fabrikasında yangın çıktı. Muallimköy Mahallesi Gediz Caddesi 'ndeki fabrikanın kimyasal atıkların bulunduğu bölümünde başlayan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. Yangın, Kocaeli 'nin sanayi bölgeleri arasında yer alan Gebze Muallimköy Mahallesi'nde meydana geldi. Alüminyum fabrikasındaki kimyasal atıkların bulunduğu alanda başlayan alevleri görenlerin ihbarı üzerine bölgeye itfaiye ekipleri sevk edildi. Yangının ana bilgisi: Gebze Muallimköy Mahallesi Gediz Caddesi'ndeki alüminyum fabrikasında kimyasal atıkların bulunduğu alanda yangın çıktı. Yangın itfaiye ekiplerince söndürülürken, fabrikanın bir bölümünde hasar oluştu. Fabrikadaki yangın, kimyasal atıkların bulunduğu alanda çıktı. Kısa sürede fark edilen yangın için 112 Acil Çağrı Merkezi'ne ihbarda bulunuldu. İhbarın ardından adrese itfaiye ekipleri yönlendirildi. Ekipler, yangının fabrikanın diğer bölümlerine yayılmaması için çalışma yürüttü. Bölgeye gelen itfaiye ekiplerinin müdahalesiyle yangın kontrol altına alınarak söndürüldü. Yangında fabrikanın bir bölümünde hasar meydana geldi. Yangının çıkış nedeni ve hasarın boyutuna ilişkin inceleme sürecinin ardından ayrıntıların netleşmesi bekleniyor.</t>
+          <t>Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Yerel Haberler Yayınlanma: 04 Haziran 2026 - 09:27 Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Yerel Haberler 04 Haziran 2026 - 09:27 TAKİP ET Dinle A Büyüt A Küçült Diyarbakır Haberleri — Diyarbakır'da uyuşturucu suçundan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon düzenlendi. ​​​​​​​Valilikten yapılan açıklamada, Diyarbakır Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında, Terörizmin Finansmanı ve Aklama Suçları Soruşturma Bürosu koordinesinde, İl Jandarma Komutanlığı, Jandarma Genel Komutanlığı Kaçakçılık ve Organize Suçlarla Mücadele (KOM) ve Narkotik Suçlarla Mücadele daire başkanlıkları ekiplerince, uyuşturucu veya uyarıcı madde imal ve ticareti ile kullanımına yönelik operasyonların devam ettiği bildirildi. Bu kapsamda uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama, yasa dışı kenevir ekimi ve tohumu temin etme, yasa dışı ekimi kolaylaştırma ve kenevir ekiminden elde ettikleri uyuşturucu maddeyi ülke genelinde piyasaya sürerek haksız kazanç elde eden ve çeşitli yöntemlerle parayı mal varlığı edinmeye dönüştürerek suç gelirlerini aklama suçlarını işleyenlere yönelik çalışma yürütüldüğü ifade edilen açıklamada, elde ettikleri uyuşturucuları Diyarbakır ve diğer illere sevk ederek ülkede uyuşturucu madde kullanımının artmasına neden olan, uyuşturucu imal ve ticareti yaparak haksız kazanç elde eden, elde ettikleri haksız kazançları (kara parayı) çeşitli yöntemlerle aklayarak finansal sisteme aktaran ve böylece hem vatandaşları zehirleyen hem de ülkenin finansal sistemine zarar verenlerin yakalanabilmesi ve faaliyetlerine son verilmesi amacıyla 8 aylık kapsamlı ve titiz çalışmalar yürütüldüğü belirtildi. Açıklamada, şunlar kaydedildi: Diyarbakır'da 'uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama' ve '2313 sayılı Kanun'a muhalefet' öncül suçlarından haksız kazanç elde ederek kendi adına ve birlikte yaşadığı aile fertleri veya bağlantılı oldukları üçüncü şahıslar adına taşınır veya taşınmaz mal varlığı edindiği değerlendirilen şüpheliler hakkında yapılan araştırma neticesinde TCK-282 suçtan kaynaklanan mal varlığı değerlerini aklama suçu kapsamında 5 soruşturma dosyası açılarak 18 şüpheli hakkında soruşturma başlatılmıştır. Soruşturma kapsamında, İl Jandarma Komutanlığı ekiplerince uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama ve 2313 sayılı Kanun'a muhalefet öncül suçlarını işleyen ve suçtan kaynaklanan mal varlığı değerlerini aklama suçuna karıştıkları tespit edilen 18 şüpheliye yönelik operasyon düzenlendiği bildirilen açıklamada, şunlar aktarıldı: Operasyonda 18 şüpheli hakkında gerekli yasal işlemler yapılarak fazla miktarda uyuşturucu madde ele geçirilmiştir. Ayrıca bu şahıslara ait İzmir'in Çeşme ilçesinde faaliyet gösteren dört yıldızlı otel, 3 özel halk otobüsü ve hatları, 2 ticari taksi ve hatları, Diyarbakır'da bulunan toplam 970 dönümlük 109 arsa ve tarla, Çeşme ilçesinde bulunan 9 dönümlük arsa, 7 araç, 33 daire, 4 dükkan, 128 banka hesabı olmak üzere piyasa değeri yaklaşık 15 milyar lira değerinde olan mal varlığına yönelik el koyma işlemi yapılmıştır. # Diyarbakır # İzmir # kara para # operasyon # uyuşturucu EDİTÖR Anadolu Ajansı Anadolu Ajansı haberleri, son da</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Çağdaş Kocaeli Gazetesi Kocaeli Gebze Muallimköy'de bir alüminyum fabrikasının kimyasal atık alanında yangın çıktı. Yangın söndürülürken fabrikada hasar oluştu. 02 Haziran 2026 - Asayiş Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Gebze Muallimköy Mahallesi'nde bulunan bir alüminyum fabrikasının kimyasal atık alanında yangın çıktı. İtfaiye ekiplerinin müdahalesiyle söndürülen yangında fabrikada hasar oluştu. Gebze ilçesinde bulunan bir alüminyum fabrikasında yangın çıktı. Muallimköy Mahallesi Gediz Caddesi 'ndeki fabrikanın kimyasal atıkların bulunduğu bölümünde başlayan yangın, itfaiye ekiplerinin müdahalesiyle söndürüldü. Yangın, Kocaeli 'nin sanayi bölgeleri arasında yer alan Gebze Muallimköy Mahallesi'nde meydana geldi. Alüminyum fabrikasındaki kimyasal atıkların bulunduğu alanda başlayan alevleri görenlerin ihbarı üzerine bölgeye itfaiye ekipleri sevk edildi. Yangının ana bilgisi: Gebze Muallimköy Mahallesi Gediz Caddesi'ndeki alüminyum fabrikasında kimyasal atıkların bulunduğu alanda yangın çıktı. Yangın itfaiye ekiplerince söndürülürken, fabrikanın bir bölümünde hasar oluştu. Kimyasal atık alanında başladı Fabrikadaki yangın, kimyasal atıkların bulunduğu alanda çıktı. Kısa sürede fark edilen yangın için 112 Acil Çağrı Merkezi'ne ihbarda bulunuldu. Ekipler, yangının fabrikanın diğer bölümlerine yayılmaması için çalışma yürüttü. İtfaiye ekipleri yangını söndürdü Bölgeye gelen itfaiye ekiplerinin müdahalesiyle yangın kontrol altına alınarak söndürüldü. Yangında fabrikanın bir bölümünde hasar meydana geldi. Yangının çıkış nedeni ve hasarın boyutuna ilişkin inceleme sürecinin ardından ayrıntıların netleşmesi bekleniyor. Gebze'deki fabrika yangınında öne çıkan bilgiler İlçe Gebze Mahalle Muallimköy Mahallesi Adres bilgisi Gediz Caddesi Yangının çıktığı yer Alüminyum fabrikasındaki kimyasal atık alanı Müdahale eden ekip İtfaiye Son durum Yangın söndürüldü, fabrikanın bir bölümünde hasar oluştu YORUM YAP Gebze’de bayram acısı: Bisiklet kazasında ağır yaralanan 13 yaşındaki Atabey kurtarılamadı Karamürsel'i yasa boğan ölüm: Çocuk doktoru Esra Erdağ Özdemirci ölü bulundu TEM Otoyolu'nda Kocaelili aileye dehşeti yaşatmıştı: Trafik terörü estiren o magandaya öyle bir ceza kesildi ki... Derince’de yürek yakan kaza: 18 yaşındaki Çağrı hayatını kaybetti! Arkadaşlarından duygusal veda Gölcük'teki ATV faciasında yürek yakan veda: Anne ve oğlu toprağa verildi 02 Haziran 2026 - Asayiş Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Gebze Muallimköy Mahallesi'nde bulunan bir alüminyum fabrikasının kimyasal atık alanında yangın çıktı. Gebze'deki fabrika yangınında öne çıkan bilgiler İlçe Gebze Mahalle Muallimköy Mahallesi Adres bilgisi Gediz Caddesi Yangının çıktığı yer Alüminyum fabrikasındaki kimyasal atık alanı Müdahale eden ekip İtfaiye Son durum Yangın söndürüldü, fabrikanın bir bölümünde hasar oluştu Gebze'de alüminyum fabrikasında yangın çıktı: Kimyasal atık alanı alev aldı Kimyasal atık alanında başladı İtfaiye ekipleri yangını söndürdü Gebze ilçesinde bulunan bir alüminyum fabrikasında yangın çıktı. Fabrikadaki yangın, kimyasal atıkların bulunduğu alanda çıktı. Bölgeye gelen itfaiye ekiplerinin müdahalesiyle yangın kontrol altına alınarak söndürüldü.</t>
+          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Canlı Gaste Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Yerel Haberler Yayınlanma: 04 Haziran 2026 - 09:27 Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Yerel Haberler 04 Haziran 2026 - 09:27 TAKİP ET Dinle A Büyüt A Küçült Diyarbakır Haberleri — Diyarbakır'da uyuşturucu suçundan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon düzenlendi. ​​​​​​​Valilikten yapılan açıklamada, Diyarbakır Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında, Terörizmin Finansmanı ve Aklama Suçları Soruşturma Bürosu koordinesinde, İl Jandarma Komutanlığı, Jandarma Genel Komutanlığı Kaçakçılık ve Organize Suçlarla Mücadele (KOM) ve Narkotik Suçlarla Mücadele daire başkanlıkları ekiplerince, uyuşturucu veya uyarıcı madde imal ve ticareti ile kullanımına yönelik operasyonların devam ettiği bildirildi. Bu kapsamda uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama, yasa dışı kenevir ekimi ve tohumu temin etme, yasa dışı ekimi kolaylaştırma ve kenevir ekiminden elde ettikleri uyuşturucu maddeyi ülke genelinde piyasaya sürerek haksız kazanç elde eden ve çeşitli yöntemlerle parayı mal varlığı edinmeye dönüştürerek suç gelirlerini aklama suçlarını işleyenlere yönelik çalışma yürütüldüğü ifade edilen açıklamada, elde ettikleri uyuşturucuları Diyarbakır ve diğer illere sevk ederek ülkede uyuşturucu madde kullanımının artmasına neden olan, uyuşturucu imal ve ticareti yaparak haksız kazanç elde eden, elde ettikleri haksız kazançları (kara parayı) çeşitli yöntemlerle aklayarak finansal sisteme aktaran ve böylece hem vatandaşları zehirleyen hem de ülkenin finansal sistemine zarar verenlerin yakalanabilmesi ve faaliyetlerine son verilmesi amacıyla 8 aylık kapsamlı ve titiz çalışmalar yürütüldüğü belirtildi. Açıklamada, şunlar kaydedildi: Diyarbakır'da 'uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama' ve '2313 sayılı Kanun'a muhalefet' öncül suçlarından haksız kazanç elde ederek kendi adına ve birlikte yaşadığı aile fertleri veya bağlantılı oldukları üçüncü şahıslar adına taşınır veya taşınmaz mal varlığı edindiği değerlendirilen şüpheliler hakkında yapılan araştırma neticesinde TCK-282 suçtan kaynaklanan mal varlığı değerlerini aklama suçu kapsamında 5 soruşturma dosyası açılarak 18 şüpheli hakkında soruşturma başlatılmıştır. Soruşturma kapsamında, İl Jandarma Komutanlığı ekiplerince uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama ve 2313 sayılı Kanun'a muhalefet öncül suçlarını işleyen ve suçtan kaynaklanan mal varlığı değerlerini aklama suçuna karıştıkları tespit edilen 18 şüpheliye yönelik operasyon düzenlendiği bildirilen açıklamada, şunlar aktarıldı: Operasyonda 18 şüpheli hakkında gerekli yasal işlemler yapılarak fazla miktarda uyuşturucu madde ele geçirilmiştir. Ayrıca bu şahıslara ait İzmir'in Çeşme ilçesinde faaliyet gösteren dört yıldızlı otel, 3 özel halk otobüsü ve hatları, 2 ticari taksi ve hatları, Diyarbakır'da bulunan toplam 970 dönümlük 109 arsa ve tarla, Çeşme ilçesinde bulunan 9 dönümlük arsa, 7 araç, 33 daire, 4 dükkan, 128 banka hesabı olmak üzere piyasa değeri yaklaşık 15 milyar lira değerinde olan mal varlığına yönelik el koyma işlemi yapılmıştır. # Diyarbakır # İzmir # kara para # operasyon # uyuşturucu EDİTÖR Anadolu Ajansı Anadolu Ajansı haberleri, son da</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -2696,29 +2692,21 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cagdaskocaeli.com.tr/amp/haber/28102403/gebze-aluminyum-fabrikasi-yangin</t>
+          <t>https://www.canligaste.com/diyarbakir-da-suctan-kaynaklanan-mal-varligini-akladigi-tespit-edilen-18-supheliye-yonelik-operasyon/857018/</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli | Kütahya</t>
+          <t>Diyarbakır | İzmir</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Derince | Gebze | Gediz</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>alev aldı Gebze Muallimköy Mahallesi | Muallimköy Mahallesi | yer alan Gebze Muallimköy Mahallesi | Gebze Muallimköy Mahallesi | İlçe Gebze Mahalle Muallimköy Mahallesi</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Muallimköy Mahallesi Gediz Caddesi | Gebze Muallimköy Mahallesi Gediz Caddesi | Mahallesi Adres bilgisi Gediz Caddesi</t>
-        </is>
-      </c>
+          <t>Çeşme</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
@@ -2738,7 +2726,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="n">
-        <v>155.25</v>
+        <v>137</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -2747,27 +2735,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 12:34:00</t>
+          <t>2026-06-04 06:05:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>mal varlığına el konuldu</t>
+          <t>kara para</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul merkezli 27 ilde büyük operasyon! 4.6 milyarlık mal varlığına el konuldu</t>
+          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul merkezli 27 ilde büyük operasyon! 4.6 milyarlık mal varlığına el konuldu Gazete Vatan</t>
+          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu birgun.net</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2783,30 +2771,34 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul merkezli 27 ilde büyük operasyon! 4.6 milyarlık mal varlığına el konuldu Gazete Vatan</t>
+          <t>Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. İstanbul Ankara İzmir Adana Adıyaman Afyon Ağrı Aksaray Amasya Antalya Ardahan Artvin Aydın Balıkesir Bartın Batman Bayburt Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Düzce Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Iğdır Isparta Mersin K.Maraş Karabük Karaman Kars Kastamonu Kayseri Kırıkkale Kırklareli Kırşehir Kilis Kocaeli Konya Kütahya Malatya Manisa Mardin Muğla Muş Nevşehir Niğde Ordu Osmaniye Rize Sakarya Samsun Siirt Sinop Sivas Şırnak Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yalova Yozgat Zonguldak 23° Parçalı Az Bulutlu Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. Güncel 04.06.2026 09:05 Giriş: 04.06.2026 09:05 Güncelleme: 04.06.2026 09:32 Kaynak: ANKA A- A A+ Fotoğraf: AA (Arşiv) BirGün'ü Google'da favori kaynak olarak tanımlayın. Tıkla ve anında ekle Diyarbakır 'da uyuşturucu suçundan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon düzenlendi. ​​​​​​​Valilikten yapılan açıklamada, Diyarbakır Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında, Terörizmin Finansmanı ve Aklama Suçları Soruşturma Bürosu koordinesinde, İl Jandarma Komutanlığı, Jandarma Genel Komutanlığı Kaçakçılık ve Organize Suçlarla Mücadele (KOM) ve Narkotik Suçlarla Mücadele daire başkanlıkları ekiplerince, uyuşturucu veya uyarıcı madde imal ve ticareti ile kullanımına yönelik operasyonların devam ettiği bildirildi. Bu kapsamda "uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama", "yasa dışı kenevir ekimi ve tohumu temin etme", "yasa dışı ekimi kolaylaştırma ve kenevir ekiminden elde ettikleri uyuşturucu maddeyi ülke genelinde piyasaya sürerek haksız kazanç elde eden ve çeşitli yöntemlerle parayı mal varlığı edinmeye dönüştürerek suç gelirlerini aklama" suçlarını işleyenlere yönelik çalışma yürütüldüğü ifade edilen açıklamada, elde ettikleri uyuşturucuları Diyarbakır ve diğer illere sevk ederek ülkede uyuşturucu madde kullanımının artmasına neden olan, uyuşturucu imal ve ticareti yaparak haksız kazanç elde eden, elde ettikleri haksız kazançları (kara parayı) çeşitli yöntemlerle aklayarak finansal sisteme aktaran ve böylece hem vatandaşları zehirleyen hem de ülkenin finansal sistemine zarar verenlerin yakalanabilmesi ve faaliyetlerine son verilmesi amacıyla 8 aylık kapsamlı ve titiz çalışmalar yürütüldüğü belirtildi. VALİLİKTEN AÇIKLAMA Açıklamada, şunlar kaydedildi: "Diyarbakır'da 'uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama' ve '2313 sayılı Kanun'a muhalefet' öncül suçlarından haksız kazanç elde ederek kendi adına ve birlikte yaşadığı aile fertleri veya bağlantılı oldukları üçüncü şahıslar adına taşınır veya taşınmaz mal varlığı edindiği değerlendirilen şüpheliler hakkında yapılan araştırma neticesinde TCK-282 suçtan kaynaklanan mal varlığı değerlerini aklama suçu kapsamında 5 soruşturma dosyası açılarak 18 şüpheli hakkında soruşturma başlatılmıştır." Soruşturma kapsamında, İl Jandarma Komutanlığı ekiplerince "uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama" ve "2313 sayılı Kanun'a muhalefet" öncül suçlarını işleyen ve "suçtan kaynaklanan mal varlığı değerlerini aklama" suçuna karıştıkları tespit edilen 18 şüpheliye yönelik operasyon düzenlendiği bildirilen açıklamada, şunlar aktarıldı: "Operasyonda 18 şüpheli hakkında gerekli yasal işlemler yapılarak fazla miktarda uyuşturucu madde ele geçirilmiştir. Ayrıca bu şahıslara ait İzmir'in Çeşme ilçesinde faaliyet gösteren dört yıldızlı otel, 3 özel halk otobüsü ve hatları, 2 ticari taksi ve hatları, Diyarbakır'da bulunan toplam 970 dönümlük 109 arsa ve tarla, Çeşme ilçesinde bulunan 9 dönümlük arsa, 7 araç, 33 daire, 4 dükkan, 128 banka hesabı olmak üzere piyasa değeri yaklaşık 15 milyar lira değerinde olan mal varlığına yönelik el koyma işlemi yapılmıştır." #uyuşturucu #operasyon #diyarbakır #el koyma #mal varlığı #gözaltı Sıradak</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul merkezli 27 ilde büyük operasyon! 4.6 milyarlık mal varlığına el konuldu İstanbul merkezli 27 ilde büyük operasyon! 4.6 milyarlık mal varlığına el konuldu Gazete Vatan İstanbul merkezli 27 ilde büyük operasyon! 4.6 milyarlık mal varlığına el konuldu Gazete Vatan</t>
+          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu birgun.net Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. İstanbul Ankara İzmir Adana Adıyaman Afyon Ağrı Aksaray Amasya Antalya Ardahan Artvin Aydın Balıkesir Bartın Batman Bayburt Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Düzce Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Iğdır Isparta Mersin K.Maraş Karabük Karaman Kars Kastamonu Kayseri Kırıkkale Kırklareli Kırşehir Kilis Kocaeli Konya Kütahya Malatya Manisa Mardin Muğla Muş Nevşehir Niğde Ordu Osmaniye Rize Sakarya Samsun Siirt Sinop Sivas Şırnak Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yalova Yozgat Zonguldak 23° Parçalı Az Bulutlu Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. Güncel 04.06.2026 09:05 Giriş: 04.06.2026 09:05 Güncelleme: 04.06.2026 09:32 Kaynak: ANKA A- A A+ Fotoğraf: AA (Arşiv) BirGün'ü Google'da favori kaynak olarak tanımlayın. Tıkla ve anında ekle Diyarbakır 'da uyuşturucu suçundan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon düzenlendi. ​​​​​​​Valilikten yapılan açıklamada, Diyarbakır Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında, Terörizmin Finansmanı ve Aklama Suçları Soruşturma Bürosu koordinesinde, İl Jandarma Komutanlığı, Jandarma Genel Komutanlığı Kaçakçılık ve Organize Suçlarla Mücadele (KOM) ve Narkotik Suçlarla Mücadele daire başkanlıkları ekiplerince, uyuşturucu veya uyarıcı madde imal ve ticareti ile kullanımına yönelik operasyonların devam ettiği bildirildi. Bu kapsamda "uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama", "yasa dışı kenevir ekimi ve tohumu temin etme", "yasa dışı ekimi kolaylaştırma ve kenevir ekiminden elde ettikleri uyuşturucu maddeyi ülke genelinde piyasaya sürerek haksız kazanç elde eden ve çeşitli yöntemlerle parayı mal varlığı edinmeye dönüştürerek suç gelirlerini aklama" suçlarını işleyenlere yönelik çalışma yürütüldüğü ifade edilen açıklamada, elde ettikleri uyuşturucuları Diyarbakır ve diğer illere sevk ederek ülkede uyuşturucu madde kullanımının artmasına neden olan, uyuşturucu imal ve ticareti yaparak haksız kazanç elde eden, elde ettikleri haksız kazançları (kara parayı) çeşitli yöntemlerle aklayarak finansal sisteme aktaran ve böylece hem vatandaşları zehirleyen hem de ülkenin finansal sistemine zarar verenlerin yakalanabilmesi ve faaliyetlerine son verilmesi amacıyla 8 aylık kapsamlı ve titiz çalışmalar yürütüldüğü belirtildi. VALİLİKTEN AÇIKLAMA Açıklamada, şunlar kaydedildi: "Diyarbakır'da 'uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama' ve '2313 sayılı Kanun'a muhalefet' öncül suçlarından haksız kazanç elde ederek kendi adına ve birlikte yaşadığı aile fertleri veya bağlantılı oldukları üçüncü şahıslar adına taşınır veya taşınmaz mal varlığı edindiği değerlendirilen şüpheliler hakkında yapılan araştırma neticesinde TCK-282 suçtan kaynaklanan mal varlığı değerlerini aklama suçu kapsamında 5 soruşturma dosyası açılarak 18 şüpheli hakkında soruşturma başlatılmıştır." Soruşturma kapsamında, İl Jandarma Komutanlığı ekiplerince "uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama" ve "2313 sayılı Kanun'a muhalefet" öncül suçlarını işleyen ve "suçtan kaynaklanan mal varlığı değerlerini aklama" suçuna karıştıkları tespit edilen 18 şüpheliye yönelik operasyon düzenlendiği bildirilen açıklamada, şunlar aktarıldı: "Operasyonda 18 şüpheli hakkında gerekli yasal işlemler yapılarak fazla miktarda uyuşturucu madde ele geçirilmiştir. Ayrıca bu şahıslara ait İzmir'in Çeşme ilçesinde faaliyet gösteren dört yıldızlı otel, 3 özel halk otobüsü ve hatları, 2 ticari taksi ve hatları, Diyarbakır'da bulunan toplam 970 dönümlük 109 arsa ve tarla, Çeşme ilçesinde bulunan 9 dönümlük arsa, 7 araç, 33 daire, 4 dükkan, 128 banka hesabı olmak üzere piyasa değeri yaklaşık 15 milyar lira değerinde olan mal varlığına yönelik el koyma işlemi yapılmıştır." #uyuşturucu #operasyon #diyarbakır #el koyma #mal varlığı #gözaltı Sıradak</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOX0haS2Q5RWZSQUFSWlBNdHdzNDhBUmRtSk82b3kyek9mTzlMN3RUaFlpaDdCeGRjM3JiNDlkOWpMQWNiZGJQOTRUTDFIV09TVmZvM1U0RXJJQUdxWUtOaGo1NktiRS1vMlhQdnQ1TkN0MlVEbFEwT1hkU1pfbFpsd3dvQkEzVU5nQ0NGZHJwT1hyLWl5UmVzY1Y2ZE5VZ2xtdENPUEtLczc2SnJUblo0aTF1QTI1OEJmTVVFN3BodHU?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.birgun.net/haber/diyarbakir-da-uyusturucu-ve-kara-para-operasyonu-15-milyar-lira-degerinde-mal-varligina-el-konuldu-716349</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Diyarbakır | İzmir</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Çeşme</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -2814,7 +2806,7 @@
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
@@ -2828,7 +2820,7 @@
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="n">
-        <v>90.94</v>
+        <v>136</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>2</v>
@@ -2837,27 +2829,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 02:01:12</t>
+          <t>2026-06-04 07:34:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MASAK raporu</t>
+          <t>para aklama</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>CHP kurultayında MASAK raporu krizi: Delegeler geri çekilebilir mi?</t>
+          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>CHP kurultayında MASAK raporu krizi: Delegeler geri çekilebilir mi? Haberhergün</t>
+          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2867,18 +2859,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>CHP kurultayında MASAK raporu krizi: Delegeler geri çekilebilir mi? Haberhergün</t>
+          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CHP kurultayında MASAK raporu krizi: Delegeler geri çekilebilir mi? CHP kurultayında MASAK raporu krizi: Delegeler geri çekilebilir mi? Haberhergün CHP kurultayında MASAK raporu krizi: Delegeler geri çekilebilir mi?</t>
+          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2888,7 +2884,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNOHZvQUZwdmZEZjJaRzBTQzk5SzlaQmNBVGFYV2o3SG8tSGdWcWNaQXhRRmNEMXUyUzUwRnFScmM4Q3BaOVB1NXVhZmZLSWNHOEpwZjUtM0xoTXJBYWozR2xiQUpibTV0SFctbGZpVnhwR0JyWnJ3THVDakpGR3Y0V3I0NnlvemVtenJRUUlsT1RCdWh5U1JPSlQwdFNvclJRcHdWZ2FkdGdIUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNelBSVXlkY21jWlZtSVdxQzJ0cS1qM1BFay1TRTRUTTRlbjVWeXBWNzBZYl96elNBMWhuRWl5M2JSMnNrMTNPTzN1eXpiLXNETTVndFZHWEFxQXZPLTlEbkdEdk15VXFqby1BZDI0UGYxUkxGYUJVUXpSWHdFMTlDQll4YjdRRlNzXzItWENNdDBiTkRrUVk4dmJndDdZN0xCM1JROFRjbWItWko0clZLREtKR0N5bXIwY1VHdzNua0dCbFQtUmtrOXpsMDdfU2tWQ0czNTlqUzdtUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -2914,7 +2910,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="n">
-        <v>62.04</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>3</v>
@@ -2923,27 +2919,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:01:00</t>
+          <t>2026-06-04 02:50:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>rüşvet</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Antalya Büyükşehir'e yönelik soruşturmada dijital materyallere el konuldu</t>
+          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Antalya Büyükşehir'e yönelik soruşturmada dijital materyallere el konuldu Karadeniz Gazetesi</t>
+          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Evrensel.net</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2953,54 +2949,94 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
+          <t>tesis</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Antalya Büyükşehir'e yönelik soruşturmada dijital materyallere el konuldu Karadeniz Gazetesi</t>
+          <t>Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. 04.06.2026 05:50 Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Fotoğraf: DHA Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 05:50 Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Fotoğraf: DHA Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 22:03 Ağaç AŞ işçileri, işlerini geri istiyor Güvenlik soruşturması gerekçesiyle işten çıkarılan İBB’ye bağlı Ağaç AŞ işçileri işe iadelerini istedi. İçerik yükleniyor... (İşçi Sendika Servisi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 23:47 Emniyet ve vergi düzenlemeleri içeren kanun teklifi komisyondan geçti Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. Fotoğraf: ANKA İçerik yükleniyor... (ANKA) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 19:05 TBMM'de 'mutlak butlan' protestosu TBMM Genel Kurulunda 'mutlak butlan' kararının araştırılması amacıyla verilen önergenin görüşmeleri sırasında CHP grubu, AKP'li Adalet Komisyonu Başkanı Cüneyt Yüksel'i sıralara vurarak protesto etti. Fotoğraf: ANKA İçerik yükleniyor... (ANKA) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 03:04 / Güncelleme: 03:25 Meksika'da grevdeki öğretmenler Eğitim Bakanlığını bastı Meksika'da Dünya Kupası açılışına 10 gün kala çalışma koşullarının iyileştirilmesi talebiyle süresiz greve çıkan öğretmenler, dün başkentte Eğitim Bakanlığı binasını bastı. Fotoğraf: AA İçerik yükleniyor... (Dış Haberler) Devamını Oku Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 01:04 'Devlet, patronlar işçinin hakkını daha rahat yesin diye seferber oluyor' EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Fotoğraf: Evrensel İçerik yükleniyor... (Evrensel) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Fotoğraf: DHA Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin Güvenlik soruşturması gerekçesiyle işten çıkarılan İBB’ye bağlı Ağaç AŞ işçileri işe iadelerini istedi. Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. Fotoğraf: ANKA TBMM Genel Kurulunda 'mutlak butlan' kararının araştırılması amacıyla verilen önergenin görüşmeleri sırasında CHP grubu, AKP'li Adalet Komisyonu Başkanı Cüneyt Yüksel'i sıralara vurarak protesto etti. Fotoğraf: ANKA Meksika'da Dünya Kupası açılışına 10 gün kala çalışma koşullarının iyileştirilmesi talebiyle süresiz greve çıkan öğretmenler, dün başkentte Eğitim Bakanlığı binasını bastı. Fotoğraf: AA EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Fotoğraf: Evrensel Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) İçerik yükleniyor... (İşçi Sendika Servisi) İçerik yükleniyor... (ANKA) İçerik yükleniyor... (Dış Haberler) Devamını Oku İçerik yükleniyor... (Evrensel) Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Ağaç AŞ işçileri, işlerini geri istiyor Emniyet ve vergi düzenlemeleri içeren kanun teklifi komisyondan geçti Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. TBMM'de 'mutlak butlan' protestosu TBMM Genel Kurulunda 'mutlak butlan' kararının araştırılması amacıyla verilen önergenin görüşmeleri sırasında CHP grubu, AKP'li Adalet Komisyonu Başkanı Cüneyt Yüksel'i sıralara vurarak protesto etti. Meksika'da grevdeki öğretmenler Eğitim Bakanlığını bastı Meksika'da Dünya Kupası açılışına 10 gün kala çalışma koşullarının iyileştirilmesi talebiyle süresiz greve çıkan öğretmenler, dün başkentte Eğitim Bakanlığı binasını bastı. 'Devlet, patronlar işçinin hakkını daha rahat yesin diye seferber oluyor' EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Önemli haberlerden ve gelişmelerden haberdar olmak ister misiniz?</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Antalya Büyükşehir'e yönelik soruşturmada dijital materyallere el konuldu Antalya Büyükşehir'e yönelik soruşturmada dijital materyallere el konuldu Karadeniz Gazetesi Antalya Büyükşehir'e yönelik soruşturmada dijital materyallere el konuldu Karadeniz Gazetesi</t>
+          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Evrensel.net Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. 04.06.2026 05:50 Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Fotoğraf: DHA Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 05:50 Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 22:03 Ağaç AŞ işçileri, işlerini geri istiyor Güvenlik soruşturması gerekçesiyle işten çıkarılan İBB’ye bağlı Ağaç AŞ işçileri işe iadelerini istedi. (İşçi Sendika Servisi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 23:47 Emniyet ve vergi düzenlemeleri içeren kanun teklifi komisyondan geçti Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. (Dış Haberler) Devamını Oku Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 01:04 'Devlet, patronlar işçinin hakkını daha rahat yesin diye seferber oluyor' EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. (Evrensel) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin Güvenlik soruşturması gerekçesiyle işten çıkarılan İBB’ye bağlı Ağaç AŞ işçileri işe iadelerini istedi. Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. Fotoğraf: AA EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Fotoğraf: Evrensel Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) İçerik yükleniyor... (İşçi Sendika Servisi) İçerik yükleniyor... (Evrensel) Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Ağaç AŞ işçileri, işlerini geri istiyor Emniyet ve vergi düzenlemeleri içeren kanun teklifi komisyondan geçti Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. Meksika'da grevdeki öğretmenler Eğitim Bakanlığını bastı Meksika'da Dünya Kupası açılışına 10 gün kala çalışma koşullarının iyileştirilmesi talebiyle süresiz greve çıkan öğretmenler, dün başkentte Eğitim Bakanlığı binasını bastı. 'Devlet, patronlar işçinin hakkını daha rahat yesin diye seferber oluyor' EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQSFZQTllrdWtJenZWNW5NMkxjYmdhSFlWQjFiTkxCM3c4QTY0NWVsRW0tVWFBT2ZrNVdfay0tN1A0X19IVWQ3YWFQNWJxSVNRcUpCbWVMNVBuSE0yb3R3aUVScXpHclp6MjJjeU9LbVJMdW9sMVY3SVJVRjEyNmFMMXZMRFpTYXRHdFZnY0VhTVpQUTFaSVBreDBGdS1UbjMzVDRTSm11cS1ibWZXLV9RLVFsMmpCRHpX?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
+          <t>https://www.evrensel.net/haber/5986860/bursada-geri-donusum-tesisinde-yangin-zaman-zaman-patlamalar-yasandi</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | İstanbul</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Osmangazi | Küçükçekmece</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Küçükbalıklı Mahallesi</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Ağaç AŞ</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Ağaç AŞ:73:body | Ağaç AŞ:raw_legal</t>
+        </is>
+      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
+          <t>faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Ağaç AŞ Küçükbalıklı Mahallesi Osmangazi Bursa Türkiye</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>İSTANBUL AĞAÇ A.Ş</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>İSTANBUL AĞAÇ A.Ş</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>BURSA OSMANGAZİ KÜÇÜKBALIKLI</t>
+        </is>
+      </c>
       <c r="AA5" s="2" t="n">
-        <v>76.42</v>
+        <v>227.35</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>4</v>
@@ -3009,27 +3045,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:31:44</t>
+          <t>2026-06-03 12:11:56</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kamu görevlisi ve banka çalışanı gibi tanıttılar: 17 ilde operasyon</t>
+          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Kamu görevlisi ve banka çalışanı gibi tanıttılar: 17 ilde operasyon Nefes Gazetesi</t>
+          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Haberler</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -3039,22 +3075,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>İçişleri Bakanlığı tarafından 17 ilde düzenlenen nitelikli dolandırıcılık operasyonlarında 503 şüpheli yakalandı. Vatandaşları yaklaşık 985 milyon lira dolandırdıkları belirlenen şüphelilerden 261'i tutuklanırken, MASAK raporlarında 1 milyar 135 milyon liralık işlem hacmi tespit edildi.</t>
+          <t>Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi. Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi. Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi. Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Kamu görevlisi ve banka çalışanı gibi tanıttılar: 17 ilde operasyon Kamu görevlisi ve banka çalışanı gibi tanıttılar: 17 ilde operasyon Nefes Gazetesi İçişleri Bakanlığı tarafından 17 ilde düzenlenen nitelikli dolandırıcılık operasyonlarında 503 şüpheli yakalandı. Vatandaşları yaklaşık 985 milyon lira dolandırdıkları belirlenen şüphelilerden 261'i tutuklanırken, MASAK raporlarında 1 milyar 135 milyon liralık işlem hacmi tespit edildi.</t>
+          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Haberler Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi. Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -3064,7 +3100,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.nefes.com.tr/kamu-gorevlisi-ve-banka-calisani-gibi-tanittilar-17-ilde-operasyon-129231</t>
+          <t>https://www.haberler.com/amp/kutahya-da-orman-yangini-sezonu-oncesi-denetim-ve-hazirlik-19906604-haberi/</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
@@ -3090,7 +3126,7 @@
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="n">
-        <v>62.87</v>
+        <v>80.05</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>5</v>
@@ -3099,27 +3135,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 12:57:45</t>
+          <t>2026-06-04 05:38:26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 1 trilyon lira gördü: 32 yaşındaki genç hayatının şokunu yaşadı</t>
+          <t>Bursa Haberleri</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 1 trilyon lira gördü: 32 yaşındaki genç hayatının şokunu yaşadı İlke TV</t>
+          <t>Bursa Haberleri - Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü - Yerel Haberler Hürriyet</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3129,58 +3165,86 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>tesis</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 1 trilyon lira gördü: 32 yaşındaki genç hayatının şokunu yaşadı İlke TV</t>
+          <t>Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü AA / Cem Şan Oluşturulma Tarihi: Haziran 04, 2026 03:39 Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Haberin Devamı BURSA (AA) - Bursa’nın Osmangazi ilçesindeki geri dönüşüm tesisinde çıkan yangın itfaiye ekiplerince söndürüldü. Küçükbalıklı Mahallesi’nde bulunan bir geri dönüşüm tesisinde bilinmeyen bir nedenle yangın çıktı. Yangını fark eden vatandaşların ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin kısa sürede kontrol altına aldığı yangın nedeniyle geri dönüşüm tesisinde maddi hasar meydana geldi. Haberle ilgili daha fazlası: #Bursa #Geri Dönüşüm Tesisi #Yangın AA / Cem Şan Oluşturulma Tarihi: Haziran 04, 2026 03:39 Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Haberin Devamı BURSA (AA) - Bursa’nın Osmangazi ilçesindeki geri dönüşüm tesisinde çıkan yangın itfaiye ekiplerince söndürüldü. Küçükbalıklı Mahallesi’nde bulunan bir geri dönüşüm tesisinde bilinmeyen bir nedenle yangın çıktı. Yangını fark eden vatandaşların ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin kısa sürede kontrol altına aldığı yangın nedeniyle geri dönüşüm tesisinde maddi hasar meydana geldi. × GÜNDEM DÜNYA BİGPARA ANASAYFA BORSA DÖVİZ ALTIN VİOP&amp;VARANT ANALİZ KOBİ KRİPTO PARALAR SPOR ARENA ANASAYFA FUTBOL BASKETBOL VOLEYBOL CANLI SKOR KELEBEK ANASAYFA EKRANDA HAYAT SEYAHAT STİL FAKİR HAUSGERATE İLE LEZZETLİ TARİFLER SAĞLIK YAŞAM ANASAYFA CUMARTESİ PAZAR LEZZETLİ HAYAT ÇOCUKLA HAYAT SEYAHAT YAZARLAR RESMİ İLANLAR ASTROLOJİ TÜMÜ EKONOMİ TV REHBERİ MAHMURE HÜRRİYET AİLE VİDEO ASTROLOJİ HESAPLAMA ARAÇLARI BULMACA EN İYİ ON CUMA LEZİZZ TEKNOLOJİ FOTO GALERİ RAMAZAN KİTAP</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 1 trilyon lira gördü: 32 yaşındaki genç hayatının şokunu yaşadı Banka hesabında 1 trilyon lira gördü: 32 yaşındaki genç hayatının şokunu yaşadı İlke TV Banka hesabında 1 trilyon lira gördü: 32 yaşındaki genç hayatının şokunu yaşadı İlke TV</t>
+          <t>Bursa Haberleri Bursa Haberleri - Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü - Yerel Haberler Hürriyet Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü AA / Cem Şan Oluşturulma Tarihi: Haziran 04, 2026 03:39 Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Haberin Devamı BURSA (AA) - Bursa’nın Osmangazi ilçesindeki geri dönüşüm tesisinde çıkan yangın itfaiye ekiplerince söndürüldü. Küçükbalıklı Mahallesi’nde bulunan bir geri dönüşüm tesisinde bilinmeyen bir nedenle yangın çıktı. Yangını fark eden vatandaşların ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin kısa sürede kontrol altına aldığı yangın nedeniyle geri dönüşüm tesisinde maddi hasar meydana geldi. Haberle ilgili daha fazlası: #Bursa #Geri Dönüşüm Tesisi #Yangın AA / Cem Şan Oluşturulma Tarihi: Haziran 04, 2026 03:39 Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Haberin Devamı BURSA (AA) - Bursa’nın Osmangazi ilçesindeki geri dönüşüm tesisinde çıkan yangın itfaiye ekiplerince söndürüldü.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPSEx4dFVtSURLQ0o3RWNnb3NtU3ZsTkJxa2lXUTZwMHBlX3E1MlFpVnN4N1BZQ3JKMlFDMzFjNExNS0RJeTR3X0tYQklWMEQxQ18zZHlLeFlwWHNvMDRkU1g2NDlTbGFaMlYxemV3ZkwtX1VEUklwYWhReU1hbjJZbzFvdkU1Yml6VklSc1NQbWgwNmF0WGYxaW5RcUFLbC1sbnI0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>https://www.hurriyet.com.tr/yerel-haberler/bursa/bursada-geri-donusum-tesisinde-cikan-yangin-so-43192537</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Küçükbalıklı Mahallesi</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Geri Dönüşüm Tesisi</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
+          <t>ilçe yok | firma yok</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Geri Dönüşüm Tesisi Küçükbalıklı Mahallesi Bursa Türkiye</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Torun Geri Dönüşüm - Küçükbalıklı Hurda Kağıt Alımı | Bursa Hurdacı Geri Dönüşüm | Bursa Hurdacı Ayaz Metal Hurda Geridönüşüm | Bursa Hurda Kağıt | Bursa Hurda Karton | Bursa Geri Dönüşüm</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Torun Geri Dönüşüm - Küçükbalıklı Hurda Kağıt Alımı</t>
+        </is>
+      </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>77.41935483870968 | 77.41935483870968 | 39.34426229508197 | 77.41935483870968</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>CAN PLASTİK</t>
+        </is>
+      </c>
       <c r="AA7" s="2" t="n">
-        <v>68.12</v>
+        <v>151.25</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>6</v>
@@ -3189,27 +3253,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 09:56:00</t>
+          <t>2026-06-03 12:18:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>banka hesapları bloke</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bir anda banka hesabına 1 trilyon TL geldi! Hayatı altüst oldu: MASAK soruşturma başlattı</t>
+          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını!</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Bir anda banka hesabına 1 trilyon TL geldi! Hayatı altüst oldu: MASAK soruşturma başlattı Doğru Haber</t>
+          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını! Ege'de Sonsöz</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -3219,62 +3283,86 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı, masak</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Van'da yaşayan Azerbaycan kökenli Ahmad Jahangard Takalo, market alışverişi yaptığı sırada banka kartı reddedilince hesabını kontrol ettirmek için banka şubesine uğradı. Hesabından 1 trilyon liradan fazla para olduğu görülen Takalo'nun tüm hesapları bloke edildi. Azerbaycanlı Ahmad Jahangard Takalo, 10 yıl evvel Türkiye'ye gelip yerleşmiş. Van'da markette alışveriş yaparken kartı reddedilince yakın bir banka şubesine giden 32 yaşındaki adam, hesabını kontrol ettirdiğinde inanılmaz bir durumla karşılaştı. Adamın bakiyesinin 1 trilyon liradan fazla olduğu ortaya çıktı. HESABINDA 999 MİLYAR TL GÖRÜLDÜ 32 yaşındaki adamın banka hesabında nereden geldiği bilinmeyen 999 milyar 999 milyon 999bin 999 TL 99 kuruş tespit edildi. Bu inanılmaz tutar ortaya çıkınca MASAK tarafından tüm hesaplar derhal durduruldu. Bu olay nedeniyle hesaplarına ulaşamayan Takalo, bankadan açıklama istedi lakin inceleme devam ettiği için detay verilmediğini öğrendi. Yaşadıklarını anlatan Takalo, banka çalışanlarının da durum karşısında şaşkınlık yaşadığını belirterek, "Memur şefini çağırdı, şef banka müdürünü çağırdı. Herkes toplandı. Para gelmiş, MASAK tarafından bloke konmuş. Çok komik karşıladılar" dedi. BU PARAYLA NE YAPILABİLİR? YAPAY ZEKA CEVAPLADI Hesabındaki bu inanılmaz tutarı görüp şaşıran adam, yapay zekaya o parayla neler yapabileceğini sorduğunu anlattı. Aldığı yanıtlardan bazılarını pay</t>
+          <t>Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Akkale Mahallesi'nde saat 15.00 sıralarında bir kauçuk fabrikasında yangın çıktı. Alevler kısa sürede büyüdü. Fabrikadan yükselen siyah duman kentin birçok noktasından görüldü. Çevredekilerin ihbarı üzerine olay yerine itfaiye, acil sağlık ve polis ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi aldı. İtfaiye ekipleri kimyasal ürünlerin bulunduğu kauçuk fabrikasındaki yangının çevredeki binalara sıçramaması için yangına müdahale etti. Yangın, ekiplerin yaklaşık 2 saatlik çalışmasıyla kontrol altına alındı. Yangında, fabrikada büyük çapta hasar oluştu. Soğutma çalışmalarının sürdüğü yangının çıkış nedenine ilişkin inceleme başlatıldı. (DHA) Kauçuk fabrikası küle döndü! Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Akkale Mahallesi'nde saat 15.00 sıralarında bir kauçuk fabrikasında yangın çıktı. Alevler kısa sürede büyüdü. Fabrikadan yükselen siyah duman kentin birçok noktasından görüldü. Çevredekilerin ihbarı üzerine olay yerine itfaiye, acil sağlık ve polis ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi aldı. İtfaiye ekipleri kimyasal ürünlerin bulunduğu kauçuk fabrikasındaki yangının çevredeki binalara sıçramaması için yangına müdahale etti. Yangın, ekiplerin yaklaşık 2 saatlik çalışmasıyla kontrol altına alındı. Yangında, fabrikada büyük çapta hasar oluştu. Soğutma çalışmalarının sürdüğü yangının çıkış nedenine ilişkin inceleme başlatıldı. (DHA)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Bir anda banka hesabına 1 trilyon TL geldi! Hayatı altüst oldu: MASAK soruşturma başlattı Bir anda banka hesabına 1 trilyon TL geldi! Hayatı altüst oldu: MASAK soruşturma başlattı Doğru Haber Van'da yaşayan Azerbaycan kökenli Ahmad Jahangard Takalo, market alışverişi yaptığı sırada banka kartı reddedilince hesabını kontrol ettirmek için banka şubesine uğradı. Hesabından 1 trilyon liradan fazla para olduğu görülen Takalo'nun tüm hesapları bloke edildi. Van'da markette alışveriş yaparken kartı reddedilince yakın bir banka şubesine giden 32 yaşındaki adam, hesabını kontrol ettirdiğinde inanılmaz bir durumla karşılaştı. Adamın bakiyesinin 1 trilyon liradan fazla olduğu ortaya çıktı. HESABINDA 999 MİLYAR TL GÖRÜLDÜ 32 yaşındaki adamın banka hesabında nereden geldiği bilinmeyen 999 milyar 999 milyon 999bin 999 TL 99 kuruş tespit edildi. Bu inanılmaz tutar ortaya çıkınca MASAK tarafından tüm hesaplar derhal durduruldu. Bu olay nedeniyle hesaplarına ulaşamayan Takalo, bankadan açıklama istedi lakin inceleme devam ettiği için detay verilmediğini öğrendi. Yaşadıklarını anlatan Takalo, banka çalışanlarının da durum karşısında şaşkınlık yaşadığını belirterek, "Memur şefini çağırdı, şef banka müdürünü çağırdı. Para gelmiş, MASAK tarafından bloke konmuş. Çok komik karşıladılar" dedi. BU PARAYLA NE YAPILABİLİR? YAPAY ZEKA CEVAPLADI Hesabındaki bu inanılmaz tutarı görüp şaşıran adam, yapay zekaya o parayla neler yapabileceğini sorduğunu anlattı.</t>
+          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını! Gökyüzü siyaha boyandı: Denizli'de fabrika yangını! Ege'de Sonsöz Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Akkale Mahallesi'nde saat 15.00 sıralarında bir kauçuk fabrikasında yangın çıktı. Alevler kısa sürede büyüdü. Fabrikadan yükselen siyah duman kentin birçok noktasından görüldü. Çevredekilerin ihbarı üzerine olay yerine itfaiye, acil sağlık ve polis ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi aldı. İtfaiye ekipleri kimyasal ürünlerin bulunduğu kauçuk fabrikasındaki yangının çevredeki binalara sıçramaması için yangına müdahale etti. Yangın, ekiplerin yaklaşık 2 saatlik çalışmasıyla kontrol altına alındı. Soğutma çalışmalarının sürdüğü yangının çıkış nedenine ilişkin inceleme başlatıldı. (DHA) Kauçuk fabrikası küle döndü!</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPelBUX0pfalNRSVVKZlZjSzdKWFJRNkxJVFY4TVczZmhacnZ4Ml80bFBOVmlDLTh6UHlfRloyYm4wYVUxNnl3ZE1SY0tvOUc5RDdrMjNLVUhBWU53U0QySzR1Y2xRTm9nYVAxdmdjdjZoNEg0WGJzcDBYdmRmTVJwUTR4NFJZaXl4R0Nnd2tmVjhmWUNQaU10Znc3d1pGd2hkSkU1M3B3OFZLSkJoMzBSOTlIQ2FZSndq0gG4AUFVX3lxTE96UFRfSl9qU1FJVUpmVmNLN0pYUlE2TElUVjhNVzNmaFpydngyXzRsUE5WaUMtOHpQeV9GWjJibjBhVTE2eXdkTVJjS285RzlEN2syM0tVSEFZTndTRDJLNHVjbFFOb2dhUDF2Z2N2Nmg0SDRYYnNwMFh2ZGZNUnBRNHg0UllpeXhHQ2d3a2ZWOGZZQ1BpTXRmdzd3WkZ3aGRKRTUzcHc4VktKQmgzMFI5OUhDYVlKd2o?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.egedesonsoz.com/gokyuzu-siyaha-boyandi-denizlide-fabrika-yangini/amp</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Akkale Mahallesi</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Kauçuk fabrikası</t>
+        </is>
+      </c>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
+          <t>ilçe yok | firma yok</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Kauçuk fabrikası Akkale Mahallesi Denizli Türkiye</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Denizli Kauçuk | Pakpol - Pamukkale Kauçuk ve Poliüretan Makina Sanayi Ticaret Limited Şirketi | TAPASAN KAUÇUK PLASTİK SAN. VE TİC. LTD. ŞTİ</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Denizli Kauçuk</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>60.0 | 54.54545454545455 | 54.54545454545455</t>
+        </is>
+      </c>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="n">
-        <v>99.65000000000001</v>
+        <v>162.75</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>7</v>
@@ -3283,27 +3371,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:56:26</t>
+          <t>2026-06-04 02:27:59</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Van'da 999 Milyar TL'lik bakiye ortaya çıktı, MASAK devrede</t>
+          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Van'da 999 Milyar TL'lik bakiye ortaya çıktı, MASAK devrede Vansesi Gazetesi</t>
+          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri bolgegundemi.com</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -3313,33 +3401,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
+          <t>tesis</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Van'da 999 Milyar TL'lik bakiye ortaya çıktı, MASAK devrede Vansesi Gazetesi</t>
+          <t>05:27 Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri 03:40 Google’a Büyük Engel: Yayıncılar İsyan Etti 03:37 Otizmde Devrim Yaratan Keşif: Beyinde İki Alt Tip! 03:34 Tuz Gölü’ne piyango vurdu: Milyarlık lityum müjdesi 03:32 Şeflerin sakladığı o humus sırrı ifşa oldu</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Van'da 999 Milyar TL'lik bakiye ortaya çıktı, MASAK devrede Van'da 999 Milyar TL'lik bakiye ortaya çıktı, MASAK devrede Vansesi Gazetesi Van'da 999 Milyar TL'lik bakiye ortaya çıktı, MASAK devrede Vansesi Gazetesi</t>
+          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri bolgegundemi.com 05:27 Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri 03:40 Google’a Büyük Engel: Yayıncılar İsyan Etti 03:37 Otizmde Devrim Yaratan Keşif: Beyinde İki Alt Tip! 03:34 Tuz Gölü’ne piyango vurdu: Milyarlık lityum müjdesi 03:32 Şeflerin sakladığı o humus sırrı ifşa oldu</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQYVllZTZBUU9Jd3hobUh2S1cteUF5YlVJOVRNOXZodmZLOW9yNnBid1FWZE13OWxTeVNVbDhfRXZiQTY2WkZ3WV9VdTVjcGxtc2ZfNTFxaFJzdGMxWHZzSXVsNEgycExScmpFOTZNRElqUUoydHlWRmU2aXFDSG1mOHBLbzVPNUUwbFk2U0c4eW9LcDBGbmdiZjMzTkluQlHSAaQBQVVfeXFMT3dvVm9YTEdLMlcwUVJCQWZUeGhwRlFadVgxVzFMbTVYQ3NtMXYxWDQ0Z3ViTFprcVhac1Y3ejI1UmZQZ0xWeWlNWmpIMmtaM0lNcjJnR2kzbnJ4aUFKMDhaTVhfRjZMRkVvellMZWlsc2xOSDNBeGtoNnB2S1U0QXFnbC1ETllETVVURGRfVHhjb3poaEx1cFB3cXJyVlp2ZHZ5YU0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNMUNuMHIzYWdWa2ZHRm9DLXVIQ3VfRUJNSU91X3I2cnhIR0ZmSjlLaGljaUJtN0tVTnpWQVVWQWI2cnpYMnNaaXNXTXRaeW5lbjJmYk11MU9DMlJEZjd1d25Bc3ZVem5OTHVHc3RnNTVlWFphYTZrdDZMVUVMQWduZWtlbXJ0c3hQZE9DOGNnaTZ2UzZxemJ3UktR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Bursa</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr"/>
@@ -3364,7 +3452,7 @@
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="n">
-        <v>67.26000000000001</v>
+        <v>61.69</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>8</v>
@@ -3373,12 +3461,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:57:00</t>
+          <t>2026-06-04 06:18:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>banka soruşturma</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3388,12 +3476,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti"</t>
+          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti" tv100 Haber</t>
+          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Amed Haber</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3403,36 +3491,40 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
+          <t>el konuldu</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>TV100 Banka kartındaki sorun nedeniyle hesabını kontrol ettiren Ahmad Jahangard Takalo'nun hesabında 1 trilyon liraya yakın para bulunduğu görüldü. Kaynağı araştırılan para nedeniyle MASAK devreye girerken, hesaplar inceleme süresince bloke edildi Y.aklaşık 21,8 milyar dolarlık servetle Takalo'nun dünyanın en zenginleri listesinde 116'ncı sıraya yerleşebileceği belirtiliyor. TV100 Haberler Türkiye Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti" Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti" Banka kartındaki sorun nedeniyle hesabını kontrol ettiren Ahmad Jahangard Takalo'nun hesabında 1 trilyon liraya yakın para bulunduğu görüldü. Kaynağı araştırılan para nedeniyle MASAK devreye girerken, hesaplar inceleme süresince bloke edildi Y.aklaşık 21,8 milyar dolarlık servetle Takalo'nun dünyanın en zenginleri listesinde 116'ncı sıraya yerleşebileceği belirtiliyor. 02.06.2026 13:57 Güncelleme: 02.06.2026 14:17 Van'da yaşayan Azerbaycan asıllı Ahmad Jahangard Takalo, market alışverişi sırasında banka kartının hata vermesi üzerine hesabını kontrol ettirdi. Hesabında 1 trilyon liranın üzerinde para gören Takalo'nun tüm hesapları bloke edildi. BANKA KARTINDAN İŞLEM YAPAMADI NTV'nin haberine göre, yaklaşık 10 yıl önce Türkiye'ye yerleşen Azerbaycan asıllı Ahmad Jahangard Takalo, Van'da market alışverişi yaptığı sırada banka kartının işlem yapmaması üzerine en yakın banka şubesine gitti. 32 yaşındaki Takalo, hesabının kontrol edilmesiyle hayatının şokunu yaşadı. Banka kayıtlarında kullanılabilir bakiyesinin 1 trilyon liranın üzerinde olduğu görüldü. HESABINDA 999 MİLYAR LİRA GÖRÜNDÜ, MASAK DEVREYE GİRDİ Takalo'nun hesabında, kaynağını bilmediğ i 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğu tespit edildi. Devasa tutarın görülmesinin ardından hesaplara MASAK tarafından bloke konuldu. Yaşanan gelişme nedeniyle tüm hesaplarına erişimi kesilen Takalo, bankadan bilgi talep etti ancak yürütülen inceleme nedeniyle detay payla</t>
+          <t>Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik çalışma başlatıldı. Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda şüphelilerin, uyuşturucu satışından elde ettikleri gelirleri farklı yöntemlerle akladıkları yönünde bulgulara ulaşıldı. Elde edilen deliller doğrultusunda 18 şüpheli hakkında “suçtan kaynaklanan malvarlığı değerlerini aklama” suçundan 5 ayrı soruşturma dosyası oluşturuldu. Jandarma ekiplerince düzenlenen operasyonda şüpheliler hakkında yasal işlem yapılırken, çeşitli miktarlarda uyuşturucu madde de ele geçirildi. Soruşturma kapsamında şüphelilere ait olduğu değerlendirilen mal varlıklarına da el konuldu. Tedbir kararı kapsamında İzmir'in Çeşme ilçesinde bulunan 4 yıldızlı bir otel, 3 özel halk otobüsü ve işletme hatları, 2 taksi ve taksi hatları, Diyarbakır'da toplam 970 dönümlük 109 arsa ve tarla, Çeşme'de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ile 128 banka hesabı hakkında el koyma işlemi uygulandı. Yetkililer, el konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğunu açıklarken, soruşturmaya ilişkin çalışmaların sürdüğü öğrenildi. Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Diyarbakır'da narkotik madde satışından elde edilen gelirlerin aklandığı iddiasına yönelik yürütülen soruşturma kapsamında 18 şüpheli hakkında işlem yapıldı. Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik çalışma başlatıldı. Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda şüphelilerin, uyuşturucu satışından elde ettikleri gelirleri farklı yöntemlerle akladıkları yönünde bulgulara ulaşıldı. Elde edilen deliller doğrultusunda 18 şüpheli hakkında “suçtan kaynaklanan malvarlığı değerlerini aklama” suçundan 5 ayrı soruşturma dosyası oluşturuldu. Jandarma ekiplerince düzenlenen operasyonda şüpheliler hakkında yasal işlem yapılırken, çeşitli miktarlarda uyuşturucu madde de ele geçirildi. Soruşturma kapsamında şüphelilere ait olduğu değerlendirilen mal varlıklarına da el konuldu. Tedbir kararı kapsamında İzmir'in Çeşme ilçesinde bulunan 4 yıldızlı bir otel, 3 özel halk otobüsü ve işletme hatları, 2 taksi ve taksi hatları, Diyarbakır'da toplam 970 dönümlük 109 arsa ve tarla, Çeşme'de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ile 128 banka hesabı hakkında el koyma işlemi uygulandı. Yetkililer, el konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğunu açıklarken, soruşturmaya ilişkin çalışmaların sürdüğü öğrenildi.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti" Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti" tv100 Haber TV100 Banka kartındaki sorun nedeniyle hesabını kontrol ettiren Ahmad Jahangard Takalo'nun hesabında 1 trilyon liraya yakın para bulunduğu görüldü. Kaynağı araştırılan para nedeniyle MASAK devreye girerken, hesaplar inceleme süresince bloke edildi Y.aklaşık 21,8 milyar dolarlık servetle Takalo'nun dünyanın en zenginleri listesinde 116'ncı sıraya yerleşebileceği belirtiliyor. TV100 Haberler Türkiye Bir günde dünyanın en zenginleri arasına girdi! Yapay zekaya sordu: Bu parayla ülke kurabilirsin! "MASAK harekete geçti" Bir günde dünyanın en zenginleri arasına girdi! "MASAK harekete geçti" Banka kartındaki sorun nedeniyle hesabını kontrol ettiren Ahmad Jahangard Takalo'nun hesabında 1 trilyon liraya yakın para bulunduğu görüldü. 02.06.2026 13:57 Güncelleme: 02.06.2026 14:17 Van'da yaşayan Azerbaycan asıllı Ahmad Jahangard Takalo, market alışverişi sırasında banka kartının hata vermesi üzerine hesabını kontrol ettirdi. Hesabında 1 trilyon liranın üzerinde para gören Takalo'nun tüm hesapları bloke edildi. BANKA KARTINDAN İŞLEM YAPAMADI NTV'nin haberine göre, yaklaşık 10 yıl önce Türkiye'ye yerleşen Azerbaycan asıllı Ahmad Jahangard Takalo, Van'da market alışverişi yaptığı sırada banka kartının işlem yapmaması üzerine en yakın banka şubesine gitti. 32 yaşındaki Takalo, hesabının kontrol edilmesiyle hayatının şokunu yaşadı. HESABINDA 999 MİLYAR LİRA GÖRÜNDÜ, MASAK DEVREYE GİRDİ Takalo'nun hesabında, kaynağını bilmediğ i 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğu tespit edildi. Devasa tutarın görülmesinin ardından hesaplara MASAK tarafından bloke konuldu.</t>
+          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Amed Haber Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik çalışma başlatıldı. Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda şüphelilerin, uyuşturucu satışından elde ettikleri gelirleri farklı yöntemlerle akladıkları yönünde bulgulara ulaşıldı. Elde edilen deliller doğrultusunda 18 şüpheli hakkında “suçtan kaynaklanan malvarlığı değerlerini aklama” suçundan 5 ayrı soruşturma dosyası oluşturuldu. Jandarma ekiplerince düzenlenen operasyonda şüpheliler hakkında yasal işlem yapılırken, çeşitli miktarlarda uyuşturucu madde de ele geçirildi. Soruşturma kapsamında şüphelilere ait olduğu değerlendirilen mal varlıklarına da el konuldu. Tedbir kararı kapsamında İzmir'in Çeşme ilçesinde bulunan 4 yıldızlı bir otel, 3 özel halk otobüsü ve işletme hatları, 2 taksi ve taksi hatları, Diyarbakır'da toplam 970 dönümlük 109 arsa ve tarla, Çeşme'de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ile 128 banka hesabı hakkında el koyma işlemi uygulandı. Yetkililer, el konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğunu açıklarken, soruşturmaya ilişkin çalışmaların sürdüğü öğrenildi. Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Diyarbakır'da narkotik madde satışından elde edilen gelirlerin aklandığı iddiasına yönelik yürütülen soruşturma kapsamında 18 şüpheli hakkında işlem yapıldı.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.tv100.com/bir-gunde-dunyanin-en-zenginleri-arasina-girdi-yapay-zekaya-sordu-bu-parayla-ulke-kurabilirsin-masak-harekete-gecti-haber-859090</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPUlIyaFdTcHE2RjI3NmFtOThwZ2tUejNVMUVVamRiU2w5X1dYckJLREtrWDFaYWotdU1uUkFPT0FGMkxyZ2FEeHQ1M1dRTHQxNGZBazZfbnp4eER1YnpUTFU1SGkwREdpMElfanJqa2Z2LXJBSTZucEpxOGg1S1JsMnhJZ3dMX21ad0lnYmsybTdDMHBKNkR5NdIBmAFBVV95cUxPUlIyaFdTcHE2RjI3NmFtOThwZ2tUejNVMUVVamRiU2w5X1dYckJLREtrWDFaYWotdU1uUkFPT0FGMkxyZ2FEeHQ1M1dRTHQxNGZBazZfbnp4eER1YnpUTFU1SGkwREdpMElfanJqa2Z2LXJBSTZucEpxOGg1S1JsMnhJZ3dMX21ad0lnYmsybTdDMHBKNkR5NQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>Diyarbakır | İzmir</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Çeşme</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -3440,7 +3532,7 @@
       <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr"/>
@@ -3454,7 +3546,7 @@
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="n">
-        <v>134</v>
+        <v>102.5</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>9</v>
@@ -3463,12 +3555,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 09:43:00</t>
+          <t>2026-06-04 06:00:00</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>kara para</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3478,12 +3570,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Van'da bir kişinin hesabına '1 trilyon' lira yattı, MASAK harekete geçti!</t>
+          <t>15 milyar liralık kara para ağı! Hepsine el konuldu</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Van'da bir kişinin hesabına '1 trilyon' lira yattı, MASAK harekete geçti! Elips Haber</t>
+          <t>15 milyar liralık kara para ağı! Hepsine el konuldu babaocagi.com.tr</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3493,36 +3585,40 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
+          <t>el konuldu</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Van'da bir kişinin hesabına '1 trilyon' lira yattı, MASAK harekete geçti! Elips Haber</t>
+          <t>Güncel 15 milyar liralık kara para ağı! Hepsine el konuldu Diyarbakır'da uyuşturucu ticaretinden elde edilen gelirleri aklayan 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. 04.06.2026 - 09:00 04.06.2026 - 09:00 Uyuşturucu satışından elde edilen geliri aklayan şüpheliler yakalandı. Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu veya uyarıcı madde imal ve ticareti ile suç gelirlerinin aklanmasına yönelik çalışma yürütüldü. 8 AY ADIM ADIM İZLENDİ Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda, uyuşturucu ticaretinden elde ettikleri gelirleri çeşitli yöntemlerle akladıkları değerlendirilen şüpheliler hakkında soruşturma başlatıldı. Çalışmalar kapsamında, “Uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama” ile “2313 Sayılı Kanuna Muhalefet” suçlarından elde edilen gelirlerle mal varlığı edindikleri değerlendirilen 18 şüpheli hakkında, “Suçtan kaynaklanan malvarlığı değerlerini aklama’” suçundan 5 ayrı soruşturma dosyası açıldı. UYUŞTURUCU MADDELER ELE GEÇİRİLDİ Jandarma ekiplerinin düzenlediği operasyonda 18 şüpheli hakkında yasal işlem yapılırken, yüklü miktarda uyuşturucu madde ele geçirildi. Operasyon kapsamında şüphelilere ait olduğu belirlenen İzmir’in Çeşme ilçesindeki 4 yıldızlı bir otel, 3 özel halk otobüsü ve hatları, 2 taksi ve hatları, Diyarbakır’da toplam 970 dönüm büyüklüğünde 109 arsa ve tarla, Çeşme’de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ve 128 banka hesabına el konuldu. El konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğu belirtildi. Bunlar</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Van'da bir kişinin hesabına '1 trilyon' lira yattı, MASAK harekete geçti! Van'da bir kişinin hesabına '1 trilyon' lira yattı, MASAK harekete geçti! Elips Haber Van'da bir kişinin hesabına '1 trilyon' lira yattı, MASAK harekete geçti!</t>
+          <t>15 milyar liralık kara para ağı! Hepsine el konuldu 15 milyar liralık kara para ağı! Hepsine el konuldu babaocagi.com.tr Güncel 15 milyar liralık kara para ağı! Hepsine el konuldu Diyarbakır'da uyuşturucu ticaretinden elde edilen gelirleri aklayan 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. 04.06.2026 - 09:00 04.06.2026 - 09:00 Uyuşturucu satışından elde edilen geliri aklayan şüpheliler yakalandı. Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu veya uyarıcı madde imal ve ticareti ile suç gelirlerinin aklanmasına yönelik çalışma yürütüldü. 8 AY ADIM ADIM İZLENDİ Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda, uyuşturucu ticaretinden elde ettikleri gelirleri çeşitli yöntemlerle akladıkları değerlendirilen şüpheliler hakkında soruşturma başlatıldı. Çalışmalar kapsamında, “Uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama” ile “2313 Sayılı Kanuna Muhalefet” suçlarından elde edilen gelirlerle mal varlığı edindikleri değerlendirilen 18 şüpheli hakkında, “Suçtan kaynaklanan malvarlığı değerlerini aklama’” suçundan 5 ayrı soruşturma dosyası açıldı. UYUŞTURUCU MADDELER ELE GEÇİRİLDİ Jandarma ekiplerinin düzenlediği operasyonda 18 şüpheli hakkında yasal işlem yapılırken, yüklü miktarda uyuşturucu madde ele geçirildi. Operasyon kapsamında şüphelilere ait olduğu belirlenen İzmir’in Çeşme ilçesindeki 4 yıldızlı bir otel, 3 özel halk otobüsü ve hatları, 2 taksi ve hatları, Diyarbakır’da toplam 970 dönüm büyüklüğünde 109 arsa ve tarla, Çeşme’de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ve 128 banka hesabına el konuldu. El konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğu belirtildi.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQdTJkWUpyMXFzMzVWcjk3U1lmVmlQOS1NVm4xSUV1SDZIXzZ2cnJwQmpsejJmdWFQUHVMR0RUWU5wcjYzSkVBREEyU1FVaFZOQUF3X1l5dUp6Umc3T0IxbDdEeXlKS3Vvdy1JeS01eER4Vk01a29JZkJrakxPcFpEalNWbkRrT2V1eWRyWFQwaTV1SXZGQ1NEMFlVWQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOcVY3YzJGSWRqM1VLWXQ5blh0UF9aVk1JaHRBaHFZTmhQYTQteUpRTnptamk5MmYxdEtNVXU1QU5VM3dXbWkzNnhPeGt1al95QUh2ci1RcGdmb0dSV1RYdmY4aWhHczQ2ZU5yNTRBcXctMTdFbDN2VHZ1SjRKS0NOZnFFZ25sNEtUdnNr0gGLAUFVX3lxTE5xVjdjMkZJZGozVUtZdDluWHRQX1pWTUlodEFocVlOaFBhNC15SlFOem1qaTkyZjF0S01VdTVBTlUzd1dtaTM2eE94a3VqX3lBSHZyLVFwZ2ZvR1JXVFh2ZjhpaEdzNDZlTnI1NEFxdy0xN0VsM3ZUdnVKNEpLQ05mcUVnbmw0S1R2c2s?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>Diyarbakır | İzmir</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Çeşme</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -3530,7 +3626,7 @@
       <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr"/>
@@ -3544,7 +3640,7 @@
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="n">
-        <v>84.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>10</v>
@@ -3553,27 +3649,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 09:48:38</t>
+          <t>2026-06-04 07:25:29</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CHP’de MASAK Depremi: Yeni Parti mi Kuruluyor?</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CHP’de MASAK Depremi: Yeni Parti mi Kuruluyor? bolgegundemi.com</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3583,40 +3679,32 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
+          <t>el konuldu, mal varlığı</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13:07 Karaman’da 3 Günlük Seferberlik! Rota Belli Oldu 13:05 Erman Toroğlu Hakkında Şok Hapis İstemi! 13:04 KMÜ Sıralamaya Girebildi mi? Dünya Devleri Belli Oldu 13:02 Aksaray’da sessiz kahramanlar ilk kez sahneye çıktı! 13:01 Selçuklu’da Okullara Müjde: 90 Bin TL Ödül Dağıtılıyor</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>CHP’de MASAK Depremi: Yeni Parti mi Kuruluyor? CHP’de MASAK Depremi: Yeni Parti mi Kuruluyor? bolgegundemi.com 13:07 Karaman’da 3 Günlük Seferberlik! Rota Belli Oldu 13:05 Erman Toroğlu Hakkında Şok Hapis İstemi! 13:04 KMÜ Sıralamaya Girebildi mi? Dünya Devleri Belli Oldu 13:02 Aksaray’da sessiz kahramanlar ilk kez sahneye çıktı! 13:01 Selçuklu’da Okullara Müjde: 90 Bin TL Ödül Dağıtılıyor</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPb0lXb2VNUFY0alNWaHlDemlrWkstd2JiQ21FbXFtWHNiWHRaSllRZUhZak9DS2J1MjRUOFBNNFdtVFZyUmdIYzhaS3ozbUtzdlUzcFZpYVp0X2ZjdnBnX1N2QmRYZ0V0bXBKTVdXa19zc2VJaXJEV0tLbXFPYUlMOG4xVDFuYVJ4U2x3U0phTkhzZzg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Aksaray | Karaman | Konya</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Selçuklu</t>
-        </is>
-      </c>
+          <t>https://www.msn.com/tr-tr/video/populer/uyu%C5%9Fturucu-gelirlerini-aklayan-%C5%9Febekeye-operasyon-15-milyar-tl-lik-mal-varl%C4%B1%C4%9F%C4%B1na-el-konuldu/vi-AA24Obdw</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -3624,7 +3712,7 @@
       <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr"/>
@@ -3638,7 +3726,7 @@
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="n">
-        <v>77.56</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>11</v>
@@ -3647,27 +3735,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:20:40</t>
+          <t>2026-06-04 06:07:14</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: MASAK tüm hesaplarını dondurdu</t>
+          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: MASAK tüm hesaplarını dondurdu YatırımX</t>
+          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -3677,22 +3765,18 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı, masak</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>el konuldu</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: MASAK tüm hesaplarını dondurdu YatırımX</t>
+          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: MASAK tüm hesaplarını dondurdu Banka hesabına 1 trilyon TL yattı: MASAK tüm hesaplarını dondurdu YatırımX Banka hesabına 1 trilyon TL yattı: MASAK tüm hesaplarını dondurdu YatırımX</t>
+          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -3702,10 +3786,14 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxORm15ZVpzaVRtRnZMaU9wcWdIN19PWVM1N3hZalFYbkFyTGNrcXVHdXpFZjNnTHJ3aDNqam16a3NycTlKaW9jeV94M0dmckI5cTZjMjZlSjR0djJ1V0VvMXRGUWRzVHZhQjMzVkhTOE1hSkFMRXBzWXpMMXFYblNjTWFXeFU2MjRYV1BfT3hjYkswbkZrZDcxZmtPUGRkczNiYjZNU1ZYWFVqUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcnNhWWJvcURkWVRWdHBTQTVWQ3Z3Z2Y0VTlBc1BudVVoRWpWZHFmaFd0azBkRGlhRUx6aHFsYVRZMGVTWVRQTTZUVWxNbFZkY3g1ZXk3WHFpX2d2blQyZFdpZHdheTFlT1UxWDc0eGlUbzFURl9LbEE1RUthUmNpc2lSS21aS25wdjlPSTN0MUdMaW5yMHp6dDNTZkdCdS1sV1lBVVhHUG9BQ0FyVWZ1WTAxdWt0dUpxNjBYU0RUREV2Y3M?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -3714,7 +3802,7 @@
       <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr"/>
@@ -3728,7 +3816,7 @@
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="n">
-        <v>49.74</v>
+        <v>94.98</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>12</v>
@@ -3737,27 +3825,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 13:13:00</t>
+          <t>2026-06-04 06:17:45</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>sahtecilik</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti</t>
+          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti Sözcü Gazetesi</t>
+          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -3767,90 +3855,54 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>sağlık</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Haberler - Ekonomi 75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti Konya'nın Karapınar ilçesinde tarım ve zirai ilaç sektörünün önde gelen firmalarından Salih Karakaya Tarım Ürünleri Ltd. Şti., konkordato talebinin reddedilmesinin ardından mahkeme kararıyla iflas etti. Yayınlanma: 02 Haziran 2026 - 16:13 Güncellenme: Konya'nın Karapınar ilçesinde uzun yıllardır tarım, hayvancılık ve zirai ilaç alanlarında faaliyet gösteren Salih Karakaya Tarım Ürünleri Limited Şirketi hakkında iflas kararı verildi. Mali yapısını yeniden düzenlemek ve borçlarını yapılandırmak amacıyla konkordato başvurusunda bulunan şirketin talebi mahkeme tarafından değerlendirildi. Yapılan incelemeler sonucunda sunulan iyileştirme ve kurtuluş planının yeterli bulunmadığı belirtilerek konkordato talebi reddedildi. 75 MİLYON TL SERMAYELİ ŞİRKET İFLAS ETTİ Karapınar Ticaret Sicili'ne kayıtlı olan ve tek ortaklı limited şirket statüsünde faaliyet gösteren firmanın 75 milyon TL sermayeye sahip olduğu öğrenildi. Mahkeme, konkordato başvurusunun reddiyle birlikte şirketin 13 Mayıs 2026 günü saat 14.00 itibarıyla iflasına hükmetti. Mahkeme kararında, "Davacı Salih Karakaya Tarım Ürünleri Zirai İlaç Gıda İnşaat Nakliye Ticaret ve Sanayi Limited Şirketi tarafından açılan konkordato davasının reddine, şirket hakkında verilen geçici mühlet ve ihtiyati tedbir kararlarının derhal kaldırılmasına, şirketin 13/05/2026 günü saat 14:00 itibariyle İFLASINA karar verilmiştir" ifadelerine yer verildi. YASAL KORUMA KALKTI Kararın ardından şirketi alacaklılara karşı koruyan geçici mühlet ve ihtiyati tedbir kararları beklenmeksizin yürürlükten kaldırıldı. Böylece alacaklıların yasal takip süreçlerinin önündeki engeller de ortadan kalkmış oldu. KOMİSERİN GÖREVİ SONA ERDİ Konkordato sürecinde geçici komiser olarak görev yapan Abdurrahman Gümrah'ın yetkileri de mahkeme kararıyla sona erdirildi. Böylece şirketin konkordato kapsamındaki tüm işlemleri resmen son buldu. İFLAS MASASI OLUŞTURULDU İflas sürecinin yürütülmesi, şirket varlıklarının tasfiyesi ve alacaklıların haklarının belirlenmesi amacıyla Karapınar İcra Müdürlüğü bünyesinde 2026/1 İflas sayılı dosya kapsamında iflas masası kuruldu. Bundan sonraki süreçte şirketin mal varlığı üzerindeki işlemler iflas idaresi tarafından yürütülecek. 75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti Konya'nın Karapınar ilçesinde tarım ve zirai ilaç sektörünün önde gelen firmalarından Salih Karakaya Tarım Ürünleri Ltd. Şti., konkordato talebinin reddedilmesinin ardından mahkeme kararıyla iflas etti. Yayınlanma: 02 Haziran 2026 - 16:13 Güncellenme: Yayınlanma: 02 Haziran 2026 - 16:13 Güncellenme: Konya'nın Karapınar ilçesinde uzun yıllardır tarım, hayvancılık ve zirai ilaç alanlarında faaliyet gösteren Salih Karakaya Tarım Ürünleri Limited Şirketi hakkında iflas kararı verildi. Mali yapısını yeniden düzenlemek ve borçlarını yapılandırmak amacıyla konkordato başvurusunda bulunan şirketin talebi mahkeme tarafından değerlendirildi. Yapılan incelemeler sonucunda sunulan iyileştirme ve kurtuluş planının yeterli bulunmadığı belirtilerek konkordato talebi reddedildi. 75 MİLYON TL SERMAYELİ ŞİRKET İFLAS ETTİ Karapınar Ticaret Sicili'ne kayıtlı olan ve tek ortaklı limited şirket statüsünde faaliyet gösteren firmanın 75 milyon TL sermayeye sahip olduğu öğrenildi. Mahkeme, konkordato başvurusunun reddiyle birlikte şirketin 13 Mayıs 2026 günü saat 14.00 itibarıyla iflasına hükmetti. Mahkeme kararında, "Davacı Salih Karakaya Tarım Ürünleri Zirai İlaç Gıda İnşaat Nakliye Ticaret ve Sanayi Limited Şirketi tarafından açılan konkordato davasının reddine, şirket hakkında verilen geçici mühlet ve ihtiyati tedbir kararlarının derhal kaldırılmasına, şirketin 13/05/2026 günü saat 14:00 itibariyle İFLASINA karar verilmiştir" ifadelerine yer verildi. YASAL KORUMA KALKTI Kararın ardından şirketi alacaklılara karşı koruyan geçici mühlet ve ihtiyati tedbir kararları beklenmeksizin yürürlükten kaldırıldı. Böylece alacaklıların yasal takip süreçlerinin önündeki engeller de ortadan kalkmış oldu. KOMİSERİN GÖREVİ SONA ERDİ Konkordato sürecinde geçici komiser olarak görev yapan Abdurrahman Gümrah'ın yetkileri de mahkeme kararıyla sona erdirildi. Böylece şirketin konkordato kapsamındaki tüm işlemleri resmen son buldu. İFLAS MASASI OLUŞTURULDU İflas sürecinin yürütülmesi, şirket varlıklarının tasfiyesi ve alacaklıların haklarının belirlenmesi amacıyla Karapınar İcra Müdürlüğü bünyesinde 2026/1 İflas sayılı dosya kapsamında iflas masası kuruldu. Bundan sonraki süreçte şirketin mal varlığı üzerindeki işlemler iflas idaresi tarafından yürütülecek. 75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti Konya'nın Karapınar ilçesinde tarım ve zirai ilaç sektörünün önde gelen firmalarından Salih Karakaya Tarım Ürünleri Ltd. Şti., konkordato talebinin reddedilmesinin ardından mahkeme kararıyla iflas etti. Konya'nın Karapınar ilçesinde uzun yıllardır tarım, hayvancılık ve zirai ilaç alanlarında faaliyet gösteren Salih Karakaya Tarım Ürünleri Limited Şirketi hakkında iflas kararı verildi. Mali yapısını yeniden düzenlemek ve borçlarını yapılandırmak amacıyla konkordato başvurusunda bulunan şirketin talebi mahkeme tarafından değerlendirildi. Yapılan incelemeler sonucunda sunulan iyileştirme ve kurtuluş planının yeterli bulunmadığı belirtilerek konkordato talebi reddedildi. 75 MİLYON TL SERMAYELİ ŞİRKET İFLAS ETTİ Karapınar Ticaret Sicili'ne kayıtlı olan ve tek ortaklı limited şirket statüsünde faaliyet gösteren firmanın 75 milyon TL sermayeye sahip olduğu öğrenildi. Mahkeme, konkordato başvurusunun reddiyle birlikte şirketin 13 Mayıs 2026 günü saat 14.00 itibarıyla iflasına hükmetti. Mahkeme kararında, "Davacı Salih Karakaya Tarım Ürünleri Zirai İlaç Gıda İnşaat Nakliye Ticaret ve Sanayi Limited Şirketi tarafından açılan konkordato davasının reddine, şirket hakkında verilen geçici mühlet ve ihtiyati tedbir kararlarının derhal kaldırılmasına, şirketin 13/05/2026 günü saat 14:00 itibariyle İFLASINA karar verilmiştir" ifadelerine yer verildi. Kararın ardından şirketi alacaklılara karşı koruyan geçici mühlet ve ihtiyati tedbir kararları beklenmeksizin yürürlükten kaldırıldı. Böylece alacaklıların yasal takip süreçlerinin önündeki engeller de ortadan kalkmış oldu. KOMİSERİN GÖREVİ SONA ERDİ Konkordato sürecinde geçici komiser olarak görev yapan Abdurrahman Gümrah'ın yetkileri de mahkeme kararıyla sona erdirildi. Böylece şirketin konkordato kapsamındaki tüm işlemleri resmen son buldu. İflas sürecinin yürütülmesi, şirket varlıklarının tasfiyesi ve alacaklıların haklarının belirlenmesi amacıyla Karapınar İcra Müdürlüğü bünyesinde 2026/1 İflas sayılı dosya kapsamında iflas masası kuruldu. Bundan sonraki süreçte şirketin mal varlığı üzerindeki işlemler iflas idaresi tarafından yürütülecek.</t>
+          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti 75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti Sözcü Gazetesi Haberler - Ekonomi 75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti Konya'nın Karapınar ilçesinde tarım ve zirai ilaç sektörünün önde gelen firmalarından Salih Karakaya Tarım Ürünleri Ltd. Şti., konkordato talebinin reddedilmesinin ardından mahkeme kararıyla iflas etti. Yayınlanma: 02 Haziran 2026 - 16:13 Güncellenme: Konya'nın Karapınar ilçesinde uzun yıllardır tarım, hayvancılık ve zirai ilaç alanlarında faaliyet gösteren Salih Karakaya Tarım Ürünleri Limited Şirketi hakkında iflas kararı verildi. Mali yapısını yeniden düzenlemek ve borçlarını yapılandırmak amacıyla konkordato başvurusunda bulunan şirketin talebi mahkeme tarafından değerlendirildi. Yapılan incelemeler sonucunda sunulan iyileştirme ve kurtuluş planının yeterli bulunmadığı belirtilerek konkordato talebi reddedildi. 75 MİLYON TL SERMAYELİ ŞİRKET İFLAS ETTİ Karapınar Ticaret Sicili'ne kayıtlı olan ve tek ortaklı limited şirket statüsünde faaliyet gösteren firmanın 75 milyon TL sermayeye sahip olduğu öğrenildi. Mahkeme, konkordato başvurusunun reddiyle birlikte şirketin 13 Mayıs 2026 günü saat 14.00 itibarıyla iflasına hükmetti. Mahkeme kararında, "Davacı Salih Karakaya Tarım Ürünleri Zirai İlaç Gıda İnşaat Nakliye Ticaret ve Sanayi Limited Şirketi tarafından açılan konkordato davasının reddine, şirket hakkında verilen geçici mühlet ve ihtiyati tedbir kararlarının derhal kaldırılmasına, şirketin 13/05/2026 günü saat 14:00 itibariyle İFLASINA karar verilmiştir" ifadelerine yer verildi. YASAL KORUMA KALKTI Kararın ardından şirketi alacaklılara karşı koruyan geçici mühlet ve ihtiyati tedbir kararları beklenmeksizin yürürlükten kaldırıldı. Böylece alacaklıların yasal takip süreçlerinin önündeki engeller de ortadan kalkmış oldu. KOMİSERİN GÖREVİ SONA ERDİ Konkordato sürecinde geçici komiser olarak görev yapan Abdurrahman Gümrah'ın yetkileri de mahkeme kararıyla sona erdirildi. Böylece şirketin konkordato kapsamındaki tüm işlemleri resmen son buldu. İFLAS MASASI OLUŞTURULDU İflas sürecinin yürütülmesi, şirket varlıklarının tasfiyesi ve alacaklıların haklarının belirlenmesi amacıyla Karapınar İcra Müdürlüğü bünyesinde 2026/1 İflas sayılı dosya kapsamında iflas masası kuruldu. Bundan sonraki süreçte şirketin mal varlığı üzerindeki işlemler iflas idaresi tarafından yürütülecek. 75 milyon lira sermaye ile kurulan Türk tarım şirketi iflas etti Konya'nın Karapınar ilçesinde tarım ve zirai ilaç sektörünün önde gelen firmalarından Salih Karakaya Tarım Ürünleri Ltd. Şti., konkordato talebinin reddedilmesinin ardından mahkeme kararıyla iflas etti. Yayınlanma: 02 Haziran 2026 - 16:13 Güncellenme: Yayınlanma: 02 Haziran 2026 - 16:13 Güncellenme: Konya'nın Karapınar ilçesinde uzun yıllardır tarım, hayvancılık ve zirai ilaç alanlarında faaliyet gösteren Salih Karakaya Tarım Ürünleri Limited Şirketi hakkında iflas kararı verildi. Konya'nın Karapınar ilçesinde uzun yıllardır tarım, hayvancılık ve zirai ilaç alanlarında faaliyet gösteren Salih Karakaya Tarım Ürünleri Limited Şirketi hakkında iflas kararı verildi. Kararın ardından şirketi alacaklılara karşı koruyan geçici mühlet ve ihtiyati tedbir kararları beklenmeksizin yürürlükten kaldırıldı. İflas sürecinin yürütülmesi, şirket varlıklarının tasfiyesi ve alacaklıların haklarının belirlenmesi amacıyla Karapınar İcra Müdürlüğü bünyesinde 2026/1 İflas sayılı dosya kapsamında iflas masası kuruldu.</t>
+          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.sozcu.com.tr/amp/75-milyon-lira-sermaye-ile-kurulan-turk-tarim-sirketi-iflas-etti-p324594</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Konya</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Karapınar</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNEZZZnA4aUtMdGtTM2dLd3FxUXJiZ0tDb2VORkdSSVdnX21hWHVfaXBMV2lwRnA3RC1OYTJSN1UzZldDdkUwRk9QQlc5d19hRDJXMHVPMk1vVXJ4ZHJFT3dfMmRINDk0ZkVubmlqOFBjVWt3Tkc2RWo4VzlnM0xFbmVtWGZybDM4bHBsS091REQyVGVTZzFiRDdvZUtOcHBKQ0FaSE9qTnVNMW9xRW1lWlNFYko3UQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>Salih Karakaya Tarım Ürünleri Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>Salih Karakaya Tarım Ürünleri Ltd. Şti:134:body | Salih Karakaya Tarım Ürünleri Limited Şirketi:raw_legal</t>
-        </is>
-      </c>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>Salih Karakaya Tarım Ürünleri Limited Şirketi Karapınar Konya Türkiye</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Salih Karakaya Tarim Ürünleri</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>Salih Karakaya Tarim Ürünleri</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="n">
-        <v>205.55</v>
+        <v>84.64</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>13</v>
@@ -3859,27 +3911,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 04:06:14</t>
+          <t>2026-06-03 12:19:00</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devi iflas bayrağını çekti</t>
+          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devi iflas bayrağını çekti Bold Medya</t>
+          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu STAR - Haberler</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -3889,18 +3941,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>inşaat</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Ankara'da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Mahkeme, Ankara'da 2016 yılından bu yana konut ve bina inşaatı sektöründe faaliyet gösteren Çakıroğulları İnşaat, mali krizden çıkamadı. Ankara'da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Mahkeme, TCDD’de 35,5 milyar TL’lik zarar AİHM’den hükumete 15 Temmuz soruları Rüşvetle tahliye dağıtan hakime 3 ay uzaklaştırma verildi Türkiye’deki hukuksuzluklar ABD Kongresi’nde konuşulacak Türkan’ın son anları kamerada: Aile adalet bekliyor Ayhan Bora Kaplan’dan hakime: Bizi katlediyorsunuz AİHM’den tüm 15 Temmuz dosyalarını etkileyecek hamle Bu Hesabı Sen Yap : 1 LİTRE MAZOT = 15 KG PATATES! Home Ekonomi Türk inşaat devi iflas bayrağını çekti Ankara'da 2016 yılından bu yana konut ve bina inşaatı sektöründe faaliyet gösteren Çakıroğulları İnşaat, mali krizden çıkamadı. 03/06/2026 A A A A Reset Facebook Twitter Bluesky Threads Whatsapp Ankara’da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Mahkeme, şirketin ve ortaklarının konkordato talebini reddederek firmanın iflasına hükmetti. Ankara Ticaret Sicil Müdürlüğü’nün 68176 sicil numarasına kayıtlı olan ve 2016 yılından bu yana başkentte ikamet amaçlı binalar, lüks konutlar ve çok aileli yapılar inşa eden Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi, mali krizini aşamayarak iflas bayrağını çekti. ADVERTISEMENT MAHKEME NOKTAYI KOYDU Yeniçağ’da yer alan habere göre mahkeme, şirket ortakları Adil Görkem ve Emre Altıntaş ile firmanın açtığı konkordato davasında son noktayı koydu. Ankara’da ilgili ticaret mahkemesinde görülen 2025/1029 Esas sayılı davanın 21/05/2026 tarihli duruşmasında, daha önce şirketi korumak amacıyla verilen tüm tedbirler kaldırıldı. Mahkeme heyeti; 04.12.2025 tarihinde şirket hakkında verilen kesin mühlet kararını ve tüm ihtiyati tedbirleri iptal etti. Şirketi denetleyen Komiserler Kurulu’nun görevine son verdi. Bu Haberler İlginizi Çekebilir TCDD’de 35,5 milyar TL’lik zarar AİHM’den hükumete 15 Temmuz soruları Rüşvetle tahliye dağıtan hakime 3 ay uzaklaştırma verildi Türkiye’deki hukuksuzluklar ABD Kongresi’nde konuşulacak Mahkeme, Çakıroğulları İnşaat’ın İİK’nun 292/1-b maddesi uyarınca iflasına hükmetti. Şirketin iflası resmi olarak 21/05/2026 tarihi, saat 12.12 itibarıyla açıldı. Tags: Ankara iflas inşaat Share Tweet Share Share Send Son Haberler Türkan’ın son anları kamerada: Aile adalet bekliyor Ayhan Bora Kaplan’dan hakime: Bizi katlediyorsunuz AİHM’den tüm 15 Temmuz dosyalarını etkileyecek hamle Bu Hesabı Sen Yap : 1 LİTRE MAZOT = 15 KG PATATES! Home Ekonomi Türk inşaat devi iflas bayrağını çekti Ankara'da 2016 yılından bu yana konut ve bina inşaatı sektöründe faaliyet gösteren Çakıroğulları İnşaat, mali krizden çıkamadı. 03/06/2026 A A A A Reset Facebook Twitter Bluesky Threads Whatsapp Ankara’da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Mahkeme, şirketin ve ortaklarının konkordato talebini reddederek firmanın iflasına hükmetti. Ankara Ticaret Sicil Müdürlüğü’nün 68176 sicil numarasına kayıtlı olan ve 2016 yılından bu yana başkentte ikamet amaçlı binalar, lüks konutlar ve çok aileli yapılar inşa eden Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi, mali krizini aşamayarak iflas bayrağını çekti. ADVERTISEMENT MAHKEME NOKTAYI KOYDU Yeniçağ’da yer alan habere göre mahkeme, şirket ortakları Adil Görkem ve Emre Altıntaş ile firmanın açtığı konkordato davasında son noktayı koydu. Ankara’da ilgili ticaret mahkemesinde görülen 2025/1029 Esas sayılı davanın 21/05/2026 tarihli duruşmasında, daha önce şirketi korumak amacıyla verilen tüm tedbirler kaldırıldı. Mahkeme heyeti; 04.12.2025 tarihinde şirket hakkında verilen kesin mühlet kararını ve tüm ihtiyati tedbirleri iptal etti. Şirketi denetleyen Komiserler Kurulu’nun görevine son verdi. Bu Haberler İlginizi Çekebilir TCDD’de 35,5 milyar TL’lik zarar AİHM’den hükumete 15 Temmuz soruları Rüşvetle tahliye dağıtan hakime 3 ay uzaklaştırma verildi Türkiye’deki hukuksuzluklar ABD Kongresi’nde konuşulacak Mahkeme, Çakıroğulları İnşaat’ın İİK’nun 292/1-b maddesi uyarınca iflasına hükmetti. Şirketin iflası resmi olarak 21/05/2026 tarihi, saat 12.12 itibarıyla açıldı. Tags: Ankara iflas inşaat Share Tweet Share Share Send Ankara’da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Mahkeme, şirketin ve ortaklarının konkordato talebini reddederek firmanın iflasına hükmetti. Ankara Ticaret Sicil Müdürlüğü’nün 68176 sicil numarasına kayıtlı olan ve 2016 yılından bu yana başkentte ikamet amaçlı binalar, lüks konutlar ve çok aileli yapılar inşa eden Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi, mali krizini aşamayarak iflas bayrağını çekti. ADVERTISEMENT MAHKEME NOKTAYI KOYDU Yeniçağ’da yer alan habere göre mahkeme, şirket ortakları Adil Görkem ve Emre Altıntaş ile firmanın açtığı konkordato davasında son noktayı koydu. Ankara’da ilgili ticaret mahkemesinde görülen 2025/1029 Esas sayılı davanın 21/05/2026 tarihli duruşmasında, daha önce şirketi korumak amacıyla verilen tüm tedbirler kaldırıldı. Mahkeme heyeti; 04.12.2025 tarihinde şirket hakkında verilen kesin mühlet kararını ve tüm ihtiyati tedbirleri iptal etti. Şirketi denetleyen Komiserler Kurulu’nun görevine son verdi. Bu Haberler İlginizi Çekebilir TCDD’de 35,5 milyar TL’lik zarar AİHM’den hükumete 15 Temmuz soruları Rüşvetle tahliye dağıtan hakime 3 ay uzaklaştırma verildi Türkiye’deki hukuksuzluklar ABD Kongresi’nde konuşulacak Mahkeme, Çakıroğulları İnşaat’ın İİK’nun 292/1-b maddesi uyarınca iflasına hükmetti. Şirketin iflası resmi olarak 21/05/2026 tarihi, saat 12.12 itibarıyla açıldı. Tags: Ankara iflas inşaat Boldmedya.com bir International Journalists Association e.V. kuruluşudur. https://www.youtube.com/boldmedya kanalından görsel içerik de üretmektedir. Bizi Takip Edin Türk inşaat devi iflas bayrağını çekti Ankara'da 2016 yılından bu yana konut ve bina inşaatı sektöründe faaliyet gösteren Çakıroğulları İnşaat, mali krizden çıkamadı. Ankara’da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Mahkeme, şirketin ve ortaklarının konkordato talebini reddederek firmanın iflasına hükmetti. Ankara Ticaret Sicil Müdürlüğü’nün 68176 sicil numarasına kayıtlı olan ve 2016 yılından bu yana başkentte ikamet amaçlı binalar, lüks konutlar ve çok aileli yapılar inşa eden Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi, mali krizini aşamayarak iflas bayrağını çekti. Yeniçağ’da yer alan habere göre mahkeme, şirket ortakları Adil Görkem ve Emre Altıntaş ile firmanın açtığı konkordato davasında son noktayı koydu. Ankara’da ilgili ticaret mahkemesinde görülen 2025/1029 Esas sayılı davanın 21/05/2026 tarihli duruşmasında, daha önce şirketi korumak amacıyla verilen tüm tedbirler kaldırıldı. Mahkeme heyeti; 04.12.2025 tarihinde şirket hakkında verilen kesin mühlet kararını ve tüm ihtiyati tedbirleri iptal etti. Şirketi denetleyen Komiserler Kurulu’nun görevine son verdi. Mahkeme, Çakıroğulları İnşaat’ın İİK’nun 292/1-b maddesi uyarınca iflasına hükmetti. Şirketin iflası resmi olarak 21/05/2026 tarihi, saat 12.12 itibarıyla açıldı. Boldmedya.com bir International Journalists Association e.V. kuruluşudur. https://www.youtube.com/boldmedya kanalından görsel içerik de üretmektedir. © 2018 - 2022 Bold Medya - Designed by INCREASES</t>
+          <t>﻿Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangına müdahale ediliyor. ﻿ Kale Mahallesi'ndeki kauçuk fabrikasında henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Ekiplerin yangını kontrol altına alma çalışmaları sürüyor. Öte yandan fabrikadan yükselen siyah duman kentin birçok yerinden görülüyor. ﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu ﻿Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangına müdahale ediliyor. Kale Mahallesi'ndeki kauçuk fabrikasında henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Ekiplerin yangını kontrol altına alma çalışmaları sürüyor. Öte yandan fabrikadan yükselen siyah duman kentin birçok yerinden görülüyor.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devi iflas bayrağını çekti Türk inşaat devi iflas bayrağını çekti Bold Medya Ankara'da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Mahkeme, Ankara'da 2016 yılından bu yana konut ve bina inşaatı sektöründe faaliyet gösteren Çakıroğulları İnşaat, mali krizden çıkamadı. Mahkeme, TCDD’de 35,5 milyar TL’lik zarar AİHM’den hükumete 15 Temmuz soruları Rüşvetle tahliye dağıtan hakime 3 ay uzaklaştırma verildi Türkiye’deki hukuksuzluklar ABD Kongresi’nde konuşulacak Türkan’ın son anları kamerada: Aile adalet bekliyor Ayhan Bora Kaplan’dan hakime: Bizi katlediyorsunuz AİHM’den tüm 15 Temmuz dosyalarını etkileyecek hamle Bu Hesabı Sen Yap : 1 LİTRE MAZOT = 15 KG PATATES! Home Ekonomi Türk inşaat devi iflas bayrağını çekti Ankara'da 2016 yılından bu yana konut ve bina inşaatı sektöründe faaliyet gösteren Çakıroğulları İnşaat, mali krizden çıkamadı. 03/06/2026 A A A A Reset Facebook Twitter Bluesky Threads Whatsapp Ankara’da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Mahkeme, şirketin ve ortaklarının konkordato talebini reddederek firmanın iflasına hükmetti. Ankara Ticaret Sicil Müdürlüğü’nün 68176 sicil numarasına kayıtlı olan ve 2016 yılından bu yana başkentte ikamet amaçlı binalar, lüks konutlar ve çok aileli yapılar inşa eden Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi, mali krizini aşamayarak iflas bayrağını çekti. ADVERTISEMENT MAHKEME NOKTAYI KOYDU Yeniçağ’da yer alan habere göre mahkeme, şirket ortakları Adil Görkem ve Emre Altıntaş ile firmanın açtığı konkordato davasında son noktayı koydu. Ankara’da ilgili ticaret mahkemesinde görülen 2025/1029 Esas sayılı davanın 21/05/2026 tarihli duruşmasında, daha önce şirketi korumak amacıyla verilen tüm tedbirler kaldırıldı. Mahkeme heyeti; 04.12.2025 tarihinde şirket hakkında verilen kesin mühlet kararını ve tüm ihtiyati tedbirleri iptal etti. Şirketi denetleyen Komiserler Kurulu’nun görevine son verdi. Bu Haberler İlginizi Çekebilir TCDD’de 35,5 milyar TL’lik zarar AİHM’den hükumete 15 Temmuz soruları Rüşvetle tahliye dağıtan hakime 3 ay uzaklaştırma verildi Türkiye’deki hukuksuzluklar ABD Kongresi’nde konuşulacak Mahkeme, Çakıroğulları İnşaat’ın İİK’nun 292/1-b maddesi uyarınca iflasına hükmetti. Şirketin iflası resmi olarak 21/05/2026 tarihi, saat 12.12 itibarıyla açıldı. Tags: Ankara iflas inşaat Share Tweet Share Share Send Son Haberler Türkan’ın son anları kamerada: Aile adalet bekliyor Ayhan Bora Kaplan’dan hakime: Bizi katlediyorsunuz AİHM’den tüm 15 Temmuz dosyalarını etkileyecek hamle Bu Hesabı Sen Yap : 1 LİTRE MAZOT = 15 KG PATATES! Tags: Ankara iflas inşaat Share Tweet Share Share Send Ankara’da dev konut projelerine imza atan ve bir süredir mali darboğazla mücadele eden Çakıroğulları İnşaat için yolun sonu göründü. Tags: Ankara iflas inşaat Boldmedya.com bir International Journalists Association e.V. Bizi Takip Edin Türk inşaat devi iflas bayrağını çekti Ankara'da 2016 yılından bu yana konut ve bina inşaatı sektöründe faaliyet gösteren Çakıroğulları İnşaat, mali krizden çıkamadı. Yeniçağ’da yer alan habere göre mahkeme, şirket ortakları Adil Görkem ve Emre Altıntaş ile firmanın açtığı konkordato davasında son noktayı koydu. Mahkeme, Çakıroğulları İnşaat’ın İİK’nun 292/1-b maddesi uyarınca iflasına hükmetti. Boldmedya.com bir International Journalists Association e.V. © 2018 - 2022 Bold Medya - Designed by INCREASES</t>
+          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu ﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu STAR - Haberler ﻿Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangına müdahale ediliyor. ﻿ Kale Mahallesi'ndeki kauçuk fabrikasında henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Ekiplerin yangını kontrol altına alma çalışmaları sürüyor. Öte yandan fabrikadan yükselen siyah duman kentin birçok yerinden görülüyor. ﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu ﻿Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangına müdahale ediliyor.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -3910,61 +3966,45 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://boldmedya.com/2026/06/03/turk-insaat-devi-iflas-bayragini-cekti/</t>
+          <t>https://m.star.com.tr/amp/guncel/denizlide-korkutan-yangin-fabrika-alevlere-teslim-oldu-haber-2019953/</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Ankara</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>Denizli | Malatya</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Kale</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Kale Mahallesi</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi:104:body | Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi:raw_legal</t>
-        </is>
-      </c>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>Çakıroğulları İnşaat Turizm ve Ticaret Limited Şirketi Ankara Türkiye</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Çakıroğulları İnşaat | Çakır İnşaat İth. İhr. San. ve Tic. Ltd. Şti</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>Çakıroğulları İnşaat</t>
-        </is>
-      </c>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>100.0 | 64.51612903225806</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="n">
-        <v>161.05</v>
+        <v>113.2</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>14</v>
@@ -3973,27 +4013,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:11:43</t>
+          <t>2026-06-03 17:21:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dev ilaç şirketi iflasın eşiğinde: Konkardota talebinde bulundu!</t>
+          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Dev ilaç şirketi iflasın eşiğinde: Konkardota talebinde bulundu! GZT</t>
+          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü İnegöl Online</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -4003,44 +4043,56 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>fabrika, osb, tekstil</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Dev ilaç şirketi iflasın eşiğinde: Konkardota talebinde bulundu! GZT</t>
+          <t>Bursa İnegöl Organize Sanayi Bölgesi’ndeki bir tekstil fabrikasının bölümünde çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alındı. Bursa İnegöl Organize Sanayi Bölgesi’ndeki bir tekstil fabrikasının bölümünde çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alındı. Bursa İnegöl Organize Sanayi Bölgesi’ndeki bir tekstil fabrikasının bölümünde çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alındı.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Dev ilaç şirketi iflasın eşiğinde: Konkardota talebinde bulundu! Dev ilaç şirketi iflasın eşiğinde: Konkardota talebinde bulundu! GZT Dev ilaç şirketi iflasın eşiğinde: Konkardota talebinde bulundu!</t>
+          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü İnegöl Online Bursa İnegöl Organize Sanayi Bölgesi’ndeki bir tekstil fabrikasının bölümünde çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxNTFNDOWlhQmRzVFJqRXRoWW5YQ2ZJV21iOUtJeE9DR0wyYkNhdzRvdW9LOVdoUHZ1b2hXdkRtTF9jaGszV3BEcmNIU0xDbjdaMFJxUy11dzlNUWpfam9JMmpSdzJkX01BczFpdUVMXzNNRTJPZmg3bmRhTXlBb3Bvc3NWR0RCV21ySVZGeXVXelBiRjRvYmRDMHZsdzdvWFhESlZYc2NMWG5ESkV6YzBVdTJwejdtUEJ6ckgzVEVBS0g3cjQtOGRuOUQ2TnVaazFncXE2WTZHVElNWnlXREJEaTgzMHNvS1E4N2JyNHFFU1VpZmg0NkdvbVFWc3Z2WE5kQ3FjYU5uaDZkQVBmbDN3NXZaUnN6UU9mblpNOHVR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
+          <t>https://www.inegolonline.com/haber/inegol-osb-de-tekstil-fabrikasinda-cikan-yangin-kisa-surede-sonduruldu-355721</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>İnegöl</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>İnegöl OSB | kısa sürede söndürüldü İnegöl OSB</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr"/>
@@ -4054,7 +4106,7 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="n">
-        <v>57.68</v>
+        <v>126.94</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>15</v>
@@ -4063,7 +4115,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:44:50</t>
+          <t>2026-06-04 07:48:14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -4078,12 +4130,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devinden kötü haber: Mahkeme biletini kesti, resmen iflas etti</t>
+          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devinden kötü haber: Mahkeme biletini kesti, resmen iflas etti Yeni Akit Gazetesi</t>
+          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -4093,18 +4145,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>inşaat</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>inşaat, şirket</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devinden kötü haber: Mahkeme biletini kesti, resmen iflas etti Yeni Akit Gazetesi</t>
+          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat devinden kötü haber: Mahkeme biletini kesti, resmen iflas etti Türk inşaat devinden kötü haber: Mahkeme biletini kesti, resmen iflas etti Yeni Akit Gazetesi Türk inşaat devinden kötü haber: Mahkeme biletini kesti, resmen iflas etti Yeni Akit Gazetesi</t>
+          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7 Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -4114,7 +4170,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPOUF5UGNhSEdHVWtZTVNoeWlRcC10bTlOVWVTWUI5akRUbk90NW5fX2Qzc0NQazRwbExOMDNNdnVJMUxCcURvZjB0S0o1R2E3SHljOUV2M2pUUlpkMThfVEJiVFJLVEpWOWk0S1ZTbFZ4WGUtZ255WmlYaGZpcDJYNkIwZVU2bU9LUUJhbWRjQnNmdUxoVFp2N0J4UXZyWFRoN25iZm1GM0JVazY2bVZGOFIyNVJkSGZGblZz0gG-AUFVX3lxTE5WUDJYT3NJajZJd1NEdHliblBqLUJMck5WTEpQZ000X3VJZVNzWmlhRTRmSS1WLWc4YVktQkV4SkdVLW9LRUlPaTgxQzhub0VBMlQ3alBYN0V3d0lYbHdhSncyMEw1R3VoS0pzdklJekFqazBOa0J4Nm1HR1RiOGJWVlRZR3RhcFptaS1aTkVHUjlWQVRnNnp3TXlaZm1kekhtSmN3c2lySVp5Q1FJWnVUT0RrOUFpRGRfWE84U3c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQZzNLMFdlUURuR004Mk9ScmtLbTZUbHNqak1aUWZFcVpBNjViYmZRWDVTcTJWLWNlZEs5ZEFIQ0lkUHBEUDFVLXBpd1dhb0VpemJzY3lZWmVsdjI0WVM3dzVZRmFndVlSNVQ1cERGS1ZaVjMzUGg0MGNuNFJXSFVjOExEcGRZNUx4MzVnclhFUlI1eHlRUlRXcGdEUmZnUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
@@ -4140,7 +4196,7 @@
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="n">
-        <v>67.18000000000001</v>
+        <v>50.36</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>16</v>
@@ -4149,27 +4205,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:44:00</t>
+          <t>2026-06-04 03:41:40</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>nitelikli dolandırıcılık</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17 ilde nitelikli dolandırıcılık şebekelerine operasyon! 261 tutuklama... 1 milyar 50 milyon liralık taşınmaz varlığına el konuldu</t>
+          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17 ilde nitelikli dolandırıcılık şebekelerine operasyon! 261 tutuklama... 1 milyar 50 milyon liralık taşınmaz varlığına el konuldu Yirmidört Tv</t>
+          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Vietnam.vn</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -4179,35 +4235,31 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
+          <t>işletme</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Haberin devamı için tıklayınız... Dolandırıcılıkla mücadele kapsamında 17 ilde yürütülen operasyonlarda gözaltına alınan 503 şüpheliden 261'i tutuklandı. Şüphelilere ait 1 milyar 50 milyon lira değerindeki taşınmaz varlığına el konuldu Haberin devamı için tıklayınız... AA - Haziran 03, 2026 11:44 | Son Güncelleme Tarihi: Haziran 03, 2026 11:46 İçişleri Bakanlığının açıklamasına göre, dolandırıcılık şebekelerine yönelik Emniyet Genel Müdürlüğü Asayiş Daire Başkanlığı ile cumhuriyet başsavcılıkları koordinesinde çalışma yürütüldü. Teknik takibi yapılan şüphelilerin "kendilerini kamu/banka görevlisi olarak tanıtarak", "güzellik merkezlerinde fahiş bedelli sözleşme imzalatarak", "iş bulma vaadinde bulunarak" ve "sahte internet siteleri üzerinden araç kiralama ilanları vererek" vatandaşları dolandırdıkları belirlendi. Bu yöntemlerle toplam 985 milyon 507 bin lira dolandırdıkları öğrenilen şüphelilere yönelik, Ankara, Adana, Amasya, Antalya, Bingöl, Diyarbakır, Erzurum, İstanbul, Kocaeli, Konya, Muğla, Osmaniye, Samsun, Şanlıurfa, Tunceli, Yalova ve Zonguldak'ta operasyonlar düzenlendi. Operasyonlarda yakalanan 503 şüpheliden 261'i tutuklandı, 242'si hakkında adli kontrol hükümleri uygulandı. RUHSATSIZ SİLAHLAR VE FİŞEKLER ELE GEÇİRİLDİ MASAK raporlarına göre şüphelilerin banka hesaplarında 1 milyar 135 milyon 707 bin liralık işlem hacmi tespit edildi. Operasyonlar kapsamında ruhsatsız silahlar ve fişekler, çok sayıda cep telefonu, dijital materyal, elektronik cihaz, sim kart, çek ve senet, yüklü miktarda Türk lirası ve döviz ile çeşitli ziynet eşyaları ele geçirildi. Şüphelilere ait 1 milyar 50 milyon lira değerindeki taşınmaz varlığına el konuldu. 17 ilde dolandırıcılık operasyonu: 261 tutuklama! 1 milyar 50 milyon liralık taşınmaz varlığına el konuldu Dolandırıcılıkla mücadele kapsamında 17 ilde yürütülen operasyonlarda gözaltına alınan 503 şüpheliden 261'i tutuklandı. Şüphelilere ait 1 milyar 50 milyon lira değerindeki taşınmaz varlığına el konuldu İçişleri Bakanlığının açıklamasına göre, dolandırıcılık şebekelerine yönelik Emniyet Genel Müdürlüğü Asayiş Daire Başkanlığı ile cumhuriyet başsavcılıkları koordinesinde çalışma yürütüldü. Teknik takibi yapılan şüphelilerin "kendilerini kamu/banka görevlisi olarak tanıtarak", "güzellik merkezlerinde fahiş bedelli sözleşme imzalatarak", "iş bulma vaadinde bulunarak" ve "sahte internet siteleri üzerinden araç kiralama ilanları vererek" vatandaşları dolandırdıkları belirlendi. Bu yöntemlerle toplam 985 milyon 507 bin lira dolandırdıkları öğrenilen şüphelilere yönelik, Ankara, Adana, Amasya, Antalya, Bingöl, Diyarbakır, Erzurum, İstanbul, Kocaeli, Konya, Muğla, Osmaniye, Samsun, Şanlıurfa, Tunceli, Yalova ve Zonguldak'ta operasyonlar düzenlendi. Operasyonlarda yakalanan 503 şüpheliden 261'i tutuklandı, 242'si hakkında adli kontrol hükümleri uygulandı. RUHSATSIZ SİLAHLAR VE FİŞEKLER ELE GEÇİRİLDİ MASAK raporlarına göre şüphelilerin banka hesaplarında 1 milyar 135 milyon 707 bin liralık işlem hacmi tespit edildi. Operasyonlar kapsamında ruhsatsız silahlar ve fişekler, çok sayıda cep telefonu, dijital materyal, elektronik cihaz, sim kart, çek ve senet, yüklü miktarda Türk lirası ve döviz ile çeşitli ziynet eşyaları ele geçirildi. Şüphelilere ait 1 milyar 50 milyon lira değerindeki taşınmaz varlığına el konuldu.</t>
+          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Vietnam.vn</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17 ilde nitelikli dolandırıcılık şebekelerine operasyon! 261 tutuklama... 1 milyar 50 milyon liralık taşınmaz varlığına el konuldu 17 ilde nitelikli dolandırıcılık şebekelerine operasyon! 261 tutuklama... 1 milyar 50 milyon liralık taşınmaz varlığına el konuldu Yirmidört Tv Dolandırıcılıkla mücadele kapsamında 17 ilde yürütülen operasyonlarda gözaltına alınan 503 şüpheliden 261'i tutuklandı. Şüphelilere ait 1 milyar 50 milyon lira değerindeki taşınmaz varlığına el konuldu Haberin devamı için tıklayınız... AA - Haziran 03, 2026 11:44 | Son Güncelleme Tarihi: Haziran 03, 2026 11:46 İçişleri Bakanlığının açıklamasına göre, dolandırıcılık şebekelerine yönelik Emniyet Genel Müdürlüğü Asayiş Daire Başkanlığı ile cumhuriyet başsavcılıkları koordinesinde çalışma yürütüldü. Teknik takibi yapılan şüphelilerin "kendilerini kamu/banka görevlisi olarak tanıtarak", "güzellik merkezlerinde fahiş bedelli sözleşme imzalatarak", "iş bulma vaadinde bulunarak" ve "sahte internet siteleri üzerinden araç kiralama ilanları vererek" vatandaşları dolandırdıkları belirlendi. Bu yöntemlerle toplam 985 milyon 507 bin lira dolandırdıkları öğrenilen şüphelilere yönelik, Ankara, Adana, Amasya, Antalya, Bingöl, Diyarbakır, Erzurum, İstanbul, Kocaeli, Konya, Muğla, Osmaniye, Samsun, Şanlıurfa, Tunceli, Yalova ve Zonguldak'ta operasyonlar düzenlendi. Operasyonlarda yakalanan 503 şüpheliden 261'i tutuklandı, 242'si hakkında adli kontrol hükümleri uygulandı. RUHSATSIZ SİLAHLAR VE FİŞEKLER ELE GEÇİRİLDİ MASAK raporlarına göre şüphelilerin banka hesaplarında 1 milyar 135 milyon 707 bin liralık işlem hacmi tespit edildi. Operasyonlar kapsamında ruhsatsız silahlar ve fişekler, çok sayıda cep telefonu, dijital materyal, elektronik cihaz, sim kart, çek ve senet, yüklü miktarda Türk lirası ve döviz ile çeşitli ziynet eşyaları ele geçirildi. Şüphelilere ait 1 milyar 50 milyon lira değerindeki taşınmaz varlığına el konuldu. 17 ilde dolandırıcılık operasyonu: 261 tutuklama! 1 milyar 50 milyon liralık taşınmaz varlığına el konuldu Dolandırıcılıkla mücadele kapsamında 17 ilde yürütülen operasyonlarda gözaltına alınan 503 şüpheliden 261'i tutuklandı. Şüphelilere ait 1 milyar 50 milyon lira değerindeki taşınmaz varlığına el konuldu İçişleri Bakanlığının açıklamasına göre, dolandırıcılık şebekelerine yönelik Emniyet Genel Müdürlüğü Asayiş Daire Başkanlığı ile cumhuriyet başsavcılıkları koordinesinde çalışma yürütüldü.</t>
+          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Vietnam.vn Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.yirmidort.tv/gundem/17-ilde-nitelikli-dolandiricilik-sebekelerine-operasyon-261-tutuklama-1-milyar-50-milyon-l-278097</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Zonguldak</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVmpWeXVfOE81SzFkZkdVRUlTeHhpUTNYamdkLU1JYXlfeGNWRGRQcFFjQXRQcnJ3VlJrdnpoTHZTQWR3bE5HVGZNbVloaWxmQU9CNlp1dFptOGtyZWFMeXZpeU5HUVJKQWlpT3licFVEakdidm5aX0pObDZON2ZmV0VnRjhwSGxCNjZuRHp4dDY1ZlVuRUd2WFcwT09DMWxi?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -4216,7 +4268,7 @@
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr"/>
@@ -4230,7 +4282,7 @@
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="n">
-        <v>141.75</v>
+        <v>137.42</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>17</v>
@@ -4239,12 +4291,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:55:56</t>
+          <t>2026-06-03 09:30:00</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>tasfiye</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4254,12 +4306,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Tasfiye halindeki şirketin o ürününe satış yasağı getirildi: İşte dikkat çeken karar!</t>
+          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Tasfiye halindeki şirketin o ürününe satış yasağı getirildi: İşte dikkat çeken karar! Kayseri Anadolu Haber</t>
+          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -4269,22 +4321,18 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>inşaat</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Tasfiye halindeki şirketin o ürününe satış yasağı getirildi: İşte dikkat çeken karar! Kayseri Anadolu Haber</t>
+          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Tasfiye halindeki şirketin o ürününe satış yasağı getirildi: İşte dikkat çeken karar! Tasfiye halindeki şirketin o ürününe satış yasağı getirildi: İşte dikkat çeken karar! Kayseri Anadolu Haber Tasfiye halindeki şirketin o ürününe satış yasağı getirildi: İşte dikkat çeken karar!</t>
+          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -4294,7 +4342,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQUkZHdXpwSUxUREdNYkhtQXNaNTVUVi13aHhQVU51SFNlTWVGenJUSzlBS1hDSjQyT1Q3TzhIcktHY1pnOTJBeWRsMzhwblpaS2U4ZVZnZmFHZVVDXzRvd0hFOUtfZnA0cEZhQUJ3cmRVUVdGLWdROUs3NjBHdlhONloweE53SEQwUXlNanZhUU1SclUteXFsUk9PTjI5Q2lYVW5QM3dLdzRJck9lRFZUVTlmNlRKMTUyeENqeXdndkMyREM4dFlHX2FR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.yenicaggazetesi.com/aluminyum-ve-insaat-sektorunun-koklu-ismi-iflas-etti-15-yillik-tecrubesi-vardi-1036532h.htm</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
@@ -4320,7 +4368,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>18</v>
@@ -4329,7 +4377,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:40:00</t>
+          <t>2026-06-03 14:41:37</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -4344,12 +4392,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi</t>
+          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi T24</t>
+          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi Foreks.com</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -4359,18 +4407,18 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>sanayi</t>
+          <t>tekstil</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi Magazin Çevre Sağlık Eğitim T24 Ekonomi Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Ankara 3. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Kamuyu Aydınlatma Platformu'nda (KAP) yayımlanan açıklamaya göre Türk İlaç ve Serum Sanayi A.Ş., Yönetim Kurulu Başkanı Mehmet Berat Battal ve şirkette pay sahibi olan Battal Holding A.Ş. ile birlikte konkordato talebinde bulundu. Başvuru sonucunda Ankara 3. Asliye Ticaret Mahkemesi tarafından 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verildi. Şirket açıklamasında, krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin konkordato başvurusunun temel nedenleri arasında yer aldığı belirtildi. KAP açıklamasında, 14 Mayıs 2026 tarihinde başlayan kredi geri ödeme gecikmelerinin devam ettiği ifade edildi. Ayrıca 20 Mayıs 2026 tarihinde oluşan karşılıksız çek kayıtlarının da henüz kapatılamadığı bilgisi paylaş</t>
+          <t>Akın Tekstil A.Ş., konkordato sürecine ilişkin Kamuyu Aydınlatma Platformu'na açıklama yaptı. Akın Tekstil A.Ş., konkordato sürecine ilişkin Kamuyu Aydınlatma Platformu'na açıklama yaptı. Akın Tekstil A.Ş., konkordato sürecine ilişkin Kamuyu Aydınlatma Platformu'na açıklama yaptı.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi T24 Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi Borsada işlem görüyordu: Türk İlaç ve Serum Sanayi konkordato istedi Magazin Çevre Sağlık Eğitim T24 Ekonomi Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Kamuyu Aydınlatma Platformu'nda (KAP) yayımlanan açıklamaya göre Türk İlaç ve Serum Sanayi A.Ş., Yönetim Kurulu Başkanı Mehmet Berat Battal ve şirkette pay sahibi olan Battal Holding A.Ş. ile birlikte konkordato talebinde bulundu. Başvuru sonucunda Ankara 3. Asliye Ticaret Mahkemesi tarafından 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verildi. Şirket açıklamasında, krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin konkordato başvurusunun temel nedenleri arasında yer aldığı belirtildi. KAP açıklamasında, 14 Mayıs 2026 tarihinde başlayan kredi geri ödeme gecikmelerinin devam ettiği ifade edildi.</t>
+          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi Foreks.com Akın Tekstil A.Ş., konkordato sürecine ilişkin Kamuyu Aydınlatma Platformu'na açıklama yaptı.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -4380,46 +4428,42 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://t24.com.tr/ekonomi/borsada-islem-goruyordu-turk-ilac-ve-serum-sanayi-konkordato-istedi,1326143</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
+          <t>https://www.foreks.com/haber/detay/akin-tekstil-in-konkordato-talebine-iliskin-durusma-tarihi-belirlendi-03-06-26/?haber_id=6a203d2167ad3132ebe399d5&amp;lang=tr&amp;category=PICNEWS/</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Battal Holding A.Ş</t>
+          <t>Akın Tekstil A.Ş</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Battal Holding A.Ş:120:body | Battal Holding A.Ş:raw_legal</t>
+          <t>Akın Tekstil:292:body+summary+title | Akın Tekstil A.Ş:raw_legal</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>Battal Holding A.Ş İstanbul Türkiye</t>
+          <t>Akın Tekstil A.Ş Türkiye</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Battal Group</t>
+          <t>AKIN TEKSTİL | Akın Tekstil</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>Battal Group</t>
+          <t>AKIN TEKSTİL</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -4429,12 +4473,12 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82.75862068965517 | 100.0</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="n">
-        <v>182.59</v>
+        <v>171.31</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>19</v>
@@ -4443,12 +4487,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:40:00</t>
+          <t>2026-06-04 06:30:00</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4458,12 +4502,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>KAP duyurdu: Türk İlaç ve Serum Sanayi A.Ş.'den konkordato başvurusu</t>
+          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>KAP duyurdu: Türk İlaç ve Serum Sanayi A.Ş.'den konkordato başvurusu 24 Saat Gazetesi Ankara</t>
+          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı Kanal 46</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -4473,31 +4517,39 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A.Ş., sanayi</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t>firma, tekstil</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>KAP duyurdu: Türk İlaç ve Serum Sanayi A.Ş.'den konkordato başvurusu 24 Saat Gazetesi Ankara</t>
+          <t>www.kanal46.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.kanal46.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.kanal46.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>KAP duyurdu: Türk İlaç ve Serum Sanayi A.Ş.'den konkordato başvurusu KAP duyurdu: Türk İlaç ve Serum Sanayi A.Ş.'den konkordato başvurusu 24 Saat Gazetesi Ankara KAP duyurdu: Türk İlaç ve Serum Sanayi A.Ş.'den konkordato başvurusu 24 Saat Gazetesi Ankara</t>
+          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı Kanal 46 www.kanal46.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.kanal46.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.kanal46.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeWZMd3hzLVRsN1N2TXNFcmZMS01LbTdMcVNobEd6TU1JQTdDdER2ek5kRXNyMEc4WnBSNmFJZnNmcUJqYWxmbHh1dS1ud2sybEZvdVhLX215aHVUb3U4emdWby1fVnRpMHEyREhDVTlLRW16TkllUHBpSjlYUEdRNTJFcHgyS2pKTVRveWd4RXkzeXdBN2hCTXZSRQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>https://www.kanal46.com/kahramanmarasta-bir-tekstil-firmasi-daha-iflas-bayragini-cekti-alacaklilara-cagri</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Kahramanmaraş</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
@@ -4506,7 +4558,7 @@
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr"/>
@@ -4520,7 +4572,7 @@
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="n">
-        <v>73.92</v>
+        <v>95.81</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>20</v>
@@ -4529,12 +4581,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:48:11</t>
+          <t>2026-06-03 10:44:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4544,12 +4596,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Borsadaki Şirkete Konkordato Şoku! Halka açık şirket konkordato ilan etti!</t>
+          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Borsadaki Şirkete Konkordato Şoku! Halka açık şirket konkordato ilan etti! ParaMedya</t>
+          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor Mavi Marmara Gazetesi</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -4559,22 +4611,18 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>mal varlığı</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>www.paramedya.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.paramedya.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.paramedya.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarıl... Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarılıyor. Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarıl...</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Borsadaki Şirkete Konkordato Şoku! Halka açık şirket konkordato ilan etti! Borsadaki Şirkete Konkordato Şoku! Halka açık şirket konkordato ilan etti! ParaMedya www.paramedya.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.paramedya.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.paramedya.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor Mavi Marmara Gazetesi Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarıl... Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarılıyor.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -4584,10 +4632,14 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.paramedya.com/devami/141989/borsadaki-sirkete-konkordato-soku-halka-acik-sirket-konkordato-ilan-etti/</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>https://www.mavimarmaragazetesi.com/haber/28105561/kocaelide-dev-iflas-satisi-198-milyonluk-mal-varligi-ihaleye-cikiyor</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Kocaeli</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
@@ -4596,7 +4648,7 @@
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr"/>
@@ -4610,7 +4662,7 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="n">
-        <v>79.37</v>
+        <v>78.33</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>21</v>
@@ -4619,27 +4671,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:37:23</t>
+          <t>2026-06-03 09:47:15</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>yasa dışı bahis</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Borsa İstanbul konkordato ilan eden şirket hakkında yeni kararını açıkladı</t>
+          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon!</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Borsa İstanbul konkordato ilan eden şirket hakkında yeni kararını açıkladı Rota Borsa</t>
+          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! GDH.Digital</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -4649,22 +4701,22 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Borsa İstanbul konkordato ilan eden şirket hakkında yeni kararını açıkladı Rota Borsa</t>
+          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! GDH.Digital</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Borsa İstanbul konkordato ilan eden şirket hakkında yeni kararını açıkladı Borsa İstanbul konkordato ilan eden şirket hakkında yeni kararını açıkladı Rota Borsa Borsa İstanbul konkordato ilan eden şirket hakkında yeni kararını açıkladı Rota Borsa</t>
+          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! GDH.Digital Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon!</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -4674,7 +4726,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQTlNkb2xSOTBwN2RlV2RTYTluc3h3azJNbGJyLXBDWklza21FZjVCUzVaejNHd1lMLW9BM2sxQTlIMGtjUWFPRGRFTGRFOVJBTnNzVWQ4S3pHU1pMU2FRUmlIRWdCR3IwLWZ4M0xaVEx6OXRKQ1BjYUdDQmlZVEwxbFVBbUdrenZmaURjdW9IYlpwcEpZZUJtTE5aRFIydw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUnpMclpncDllUXJ2V0pzdUhJaTNhZDhPSVFRZlJLTldlVjQyLWNPT1FTTDNVOE9iNEh6Y3NSb3I0VzR6dE5FY210eU9rb2tKZ0RYRTF6dk5jN2ZTc2tXak4wMG1ZZnVtRUh0WS00UE9CWXdUdFZhY3VtY1lqc2R0VkROeVhCd2E0U0d0LW9mRmxaS0tlcXFkOGUwTFBtV3ZDM1A2NzA5cUFNR0FZclliOEFKd2lZTGVpcFU2QWxCb0twRXphemc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
@@ -4700,7 +4752,7 @@
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>78.28</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>22</v>
@@ -4709,7 +4761,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 20:12:00</t>
+          <t>2026-06-04 07:49:41</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -4724,12 +4776,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Borsada İşlem Gören Şirketten Konkordato Başvurusu</t>
+          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor!</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Borsada İşlem Gören Şirketten Konkordato Başvurusu Paranın Yönü</t>
+          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! EmlakDream</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -4739,22 +4791,18 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>inşaat</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Borsada İşlem Gören Şirketten Konkordato Başvurusu Paranın Yönü</t>
+          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! EmlakDream</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Borsada İşlem Gören Şirketten Konkordato Başvurusu Borsada İşlem Gören Şirketten Konkordato Başvurusu Paranın Yönü Borsada İşlem Gören Şirketten Konkordato Başvurusu Paranın Yönü</t>
+          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! EmlakDream Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor!</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -4764,7 +4812,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXJtenk2clE3YVVUcEhtSnJNWHRLekpwM3p4SWZUNEJRRTdlT1B0cjcwazdNWmpFMmhwNXdqR0JOYzdqYldjcWhDUE1DalRpS01IUkhXblJoeURKTnFrdXhtSDl5VncwN1VUYjljdnMwWXZVWGhqSzdOeDQzRHc3LVlJUUg3QUFiQ1dpQUZKakdUR1ZNRVJvQTBDRVdwRUlpZXRXcQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOWXd2TXoyZ19TaDRzR1hCbEpPbDM5OHJNUUpyWkxjVzRkckxjMWdfR1BGekJnWVpYZW1PbHVYejN1UHc1aVNsWUlLTHNrREN6NG1wNVctYmtJR2dXN3NvMmRZUkdzY1pZOEJDQ2Y4Q1JSVlhRbkk3QmNsUDhzZEplWUM4cE5rS0cxN0g5REFxS05BWDhwVERDM3pyN1NFcU0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
@@ -4790,7 +4838,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="n">
-        <v>49.38</v>
+        <v>74.34</v>
       </c>
       <c r="AB24" s="2" t="n">
         <v>23</v>
@@ -4799,27 +4847,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 05:01:51</t>
+          <t>2026-06-03 17:54:22</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>usulsüzlük</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp…</t>
+          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç</t>
+          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -4829,22 +4877,18 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>gıda</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç</t>
+          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç Buca’da vahim iddialar: Suç örgütü kurmak, rüşvet, imar ve ihalelerde usülsüzlük, bankamatik personel, darp… Erhan Gülenç</t>
+          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -4854,19 +4898,11 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPbXM5VzU2ZnFuUGhEcXdzemhyVUdVaFVNNXMzRkZicklFZjAtT0tCRkVBTlp6TmJyYmp4eEI2eS1PQU04NVNHVHpvazVXYWstdi1HTWVCV3hzbm5ONmZMZXZUanhwY2EtVGUxNkhOS3QzQmhkWS00cG9pU3RncUJMSC15LWVJTTVyTl9jQzluWnI2Y2RxSS1iNDdBbWFENkRlaGNmNGpxaFNCTTh6OUV1Tk9aRlgtdmtBb2l3WjREODkzbkt5akNpV01iRmktWEdNVXc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>Buca</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOR1VCUHAySXZLbVJKcXIwYUMtcHVHd2RBTnF4dXpETDFSbDAzUU1sNDNPS3JmUFRhWElFZ2pReXJONV9YYm9SSk9GeG90akR3d1NPT2RhcDZ1eTQ2MmVuNHp3M0I3NVg1cC1nN1phUi1CNmVBUzFaYnRQd2Y1VFBFcTFYZ3Y3dDdWX1dTdFFaN2FfcWF1amZpOTVmLTNqWnJJb0pTQjYyMmRaNUdydGphQW5qclEwajJ2c1U4VkRnYUJTTTJlaFFjVTJCSzJybUVwd21hc2ZJdzEyOGdRZnF4ag?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -4874,7 +4910,7 @@
       <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr"/>
@@ -4888,7 +4924,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="n">
-        <v>119.46</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>24</v>
@@ -4897,27 +4933,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 17:00:00</t>
+          <t>2026-06-04 04:11:41</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>zimmet</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anlaştığım ücreti aldım; CHP’li vekille polemiğe girmem</t>
+          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anlaştığım ücreti aldım; CHP’li vekille polemiğe girmem T24</t>
+          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4927,44 +4963,36 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anl Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anl Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anl</t>
+          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anlaştığım ücreti aldım; CHP’li vekille polemiğe girmem Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anlaştığım ücreti aldım; CHP’li vekille polemiğe girmem T24 Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anl Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anl Kılıçdaroğlu’nun basın danışmanı Atakan Sönmez’den “zimmet” ve “bankamatik personeli” iddialarına yanıt: Kartal’da başkana danışmanlık yaptım, Cumhuriyet’te anl</t>
+          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://t24.com.tr/gundem/kilicdaroglunun-basin-danismani-atakan-sonmezden-zimmet-ve-bankamatik-personeli-iddialarina-yanit-kartalda-baskana-danismanlik-yaptim-cumhuriyette-anlastigim-ucreti-aldim-chpli-vekille-polemige-girmem,1325960</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Kartal</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNTnp3SmRXLU1DOWl6azAyLTdmaUNWcjFPRkxrM2dwQlFGM0R1cVU1aTctcGNIc0FSZjQtQkgtck5KQXhPNlIxXzFLQW1YcTZ5RlcyOU9rWEI0bU4yVXpLbmh3S3pfSVlHdXd3YmxQalNIWE1JYTRxTks2V0tJZEY5QVRIYTZpY0hxbnNHMk01VEdNaXZWV1p0YWxrNHZqbTRUQjM4eDRfX0RQVVhpREJRQVlOeTl5UG9JS3NiLVZqNkhxX1MzUEhvNXhINzNUNVdDMW5QVHI4SlJWdTU3U01B?oc=5</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -4972,7 +5000,7 @@
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr"/>
@@ -4986,7 +5014,7 @@
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="n">
-        <v>206.82</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="AB26" s="2" t="n">
         <v>25</v>
@@ -4995,27 +5023,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:12:00</t>
+          <t>2026-06-03 09:08:15</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>suç örgütü</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi.</t>
+          <t>İzmirli üç medikal şirkete konkordato uzatması</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi. Mersin Haber</t>
+          <t>İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -5025,82 +5053,58 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>A.Ş.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi. Haber Merkezi • 02 Haziran 2026 21:12 • Güncellendi: 02 Haziran 2026 21:14 İstanbul'da, "Ekrem İmamoğlu Çıkar Amaçlı Suç Örgütü" davasının 43. duruşmasında tutuklu sanık Yunus Göçer, Kültür A.Ş.’den yalnızca bir ihale aldığını belirtti. Göçer, iddiaları reddederek, şirketinin birçok işte faaliyet gösterdiğini ifade etti. Duruşmada başka sanıklar da savunmalarını yaptı. Haber Merkezi • 02 Haziran 2026 21:12 • Güncellendi: 02 Haziran 2026 21:14 İstanbul'da, "Ekrem İmamoğlu Çıkar Amaçlı Suç Örgütü" davasının 43. duruşmasında tutuklu sanık Yunus Göçer, Kültür A.Ş.’den yalnızca bir ihale aldığını belirtti. Göçer, iddiaları reddederek, şirketinin birçok işte faaliyet gösterdiğini ifade etti. Duruşmada başka sanıklar da savunmalarını yaptı. İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi. Göçer'in İddiaları Reddettiği Savunma Yunus Göçer, savunmasında, "Huzurda bulunduğum davada, yaklaşık 143 eylem mevcut. Ben bu eylemlerden yalnızca biriyle yargılanmaktayım. Temsilcisi olduğum şirket, 2011 yılında kurulmuş olup, gerek kamuda gerekse özel sektörde birçok iş yapmıştır. Diğer firma yetkilisiyle, Wolf Medya’nın sahibiyle gözaltına alındık. O serbest bırakıldı, ben tutuklandım. İddianameyi incelediğimde, iddia makamı beni bir eylemle yargılarken, onu 14 eylemle yargılamaktadır." ifadelerini kullandı. Göçer, Kültür A.Ş. ile yaptığı sözleşmeye dair herhangi bir hileli davranışının olmadığını belirterek, "Ben 2020 yılında Kültür A.Ş.’den bir ihale aldım. Ondan sonra başka bir ihale almadım. İşimizi hatasız bir şekilde yaptık ve zamanında ödeme alamadık" dedi. Diğer Sanıkların Savunmaları Duruşmada başka bir tutuklu sanık olan Hasan Yalaz, Baraka Yapımcılık’ın kurucusu olduğunu belirtti. Yalaz, "Medya A.Ş. ile çalıştım, ancak etkin pişmanlıkçı Deniz Dörtyol’u tanımıyorum. Baraka Yapımcılık, Medya A.Ş.’den aldığı ihaleleri almadan önce de başarılı bir şirkettir" dedi. Sonrasında tutuklu sanık Onur Aldı'nın savunmasına geçildi. Aldı, Kültür A.Ş.’de Genel Müdür Yardımcısı olarak çalıştığını ve imzalarının hiçbirisinin kamu zararı yaratmadığını savundu. Duruşma, Aldı’nın avukatının savunmasının ardından yarına ertelendi.</t>
+          <t>İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi. İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi. Mersin Haber İstanbul'da Yunus Göçer, Kültür A.Ş. ile yaptığı ihaleye dair savunma yaptı ve suçlamalara yanıt verdi. Haber Merkezi • 02 Haziran 2026 21:12 • Güncellendi: 02 Haziran 2026 21:14 İstanbul'da, "Ekrem İmamoğlu Çıkar Amaçlı Suç Örgütü" davasının 43. duruşmasında tutuklu sanık Yunus Göçer, Kültür A.Ş.’den yalnızca bir ihale aldığını belirtti. Göçer, iddiaları reddederek, şirketinin birçok işte faaliyet gösterdiğini ifade etti. Duruşmada başka sanıklar da savunmalarını yaptı. Göçer'in İddiaları Reddettiği Savunma Yunus Göçer, savunmasında, "Huzurda bulunduğum davada, yaklaşık 143 eylem mevcut. Ben bu eylemlerden yalnızca biriyle yargılanmaktayım. Temsilcisi olduğum şirket, 2011 yılında kurulmuş olup, gerek kamuda gerekse özel sektörde birçok iş yapmıştır. Diğer firma yetkilisiyle, Wolf Medya’nın sahibiyle gözaltına alındık. Göçer, Kültür A.Ş. ile yaptığı sözleşmeye dair herhangi bir hileli davranışının olmadığını belirterek, "Ben 2020 yılında Kültür A.Ş.’den bir ihale aldım. İşimizi hatasız bir şekilde yaptık ve zamanında ödeme alamadık" dedi. Diğer Sanıkların Savunmaları Duruşmada başka bir tutuklu sanık olan Hasan Yalaz, Baraka Yapımcılık’ın kurucusu olduğunu belirtti. Yalaz, "Medya A.Ş. ile çalıştım, ancak etkin pişmanlıkçı Deniz Dörtyol’u tanımıyorum. Baraka Yapımcılık, Medya A.Ş.’den aldığı ihaleleri almadan önce de başarılı bir şirkettir" dedi. Sonrasında tutuklu sanık Onur Aldı'nın savunmasına geçildi. Aldı, Kültür A.Ş.’de Genel Müdür Yardımcısı olarak çalıştığını ve imzalarının hiçbirisinin kamu zararı yaratmadığını savundu. Duruşma, Aldı’nın avukatının savunmasının ardından yarına ertelendi.</t>
+          <t>İzmirli üç medikal şirkete konkordato uzatması İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPYVFHUmttdFB4d1JqcmlzR3FMXzAwZm1KWHdVblFKOGRlMlpwZWZxSXlqQjhSLWlQNkRSX1lXYlFPTzAwakZUT3l5VHM0TUN3NXpuRVpFUFJkNEZ2MTRvUG1Fc2oyc1NXbGgwZFRhSGttYjFHRURZVWR5MEEyZW9vZFlfVzhLcFhEbTFqamh4dVJ2ZzFNeHBfZ2Frb3ktWHRZb0NVWDdZX0NpbnZxdXlPR3d4QjBSeWRsV1JQenM4OFFYTkJfdjFlV25JUXFUZWh5ZUJYMEpB0gFXQVVfeXFMUGZrMzdVc09UQjRka05WeU1JS0FPa0U0RHlOTEp6RDNNT3NPd0FnME44alZwMGpMeXZzTVpmU1ZRcXIwUEFNTXlOZUxKTm1raG9PZURLR3Vr?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbDZieWNoN3hwV1RSbTdBQzBrNW9ZSExSWjNzYklrTDFYMm9rTHV3RDhCckk0aHdqREU0YnNPaFJkb0tfdVpkOUdReDc1ZGNvUzRpLXB3U3dnMzhfQlFnQXlNUTB4a3JONnlsTm9mcTJnN3h5TUNNdnphSjJOSy01cEJ5VzFHV2NY0gGOAUFVX3lxTE53LUZVNGdfZW9VMy0zSXhhYm9yS1U3SGswYlNIWFppdlJfUV9YZlU0VjZwNzBYaUtVM0V0eWE5ZDBEVzVoUUdkdkxsd1NiRERjeVBXazN0aXB5UjN0T0RNMGlHZjlEcjRLZ3Rvd0l0WXNjMXRfY2JGNHBLdFRBd1JPZ19PRTdKZFZsclJuV1E?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Kültür A.Ş | Medya A.Ş</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>Kültür A.Ş:328:body+summary+title | Kültür A.Ş:raw_legal | Medya A.Ş:raw_legal</t>
-        </is>
-      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>Kültür A.Ş İstanbul Türkiye | Medya A.Ş İstanbul Türkiye</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Kültür A.Ş Genel Müdürlüğü | İstanbul Dijital Medya A.Ş</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>Kültür A.Ş Genel Müdürlüğü</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t>100.0 | 100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="n">
-        <v>217.5</v>
+        <v>47.12</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>26</v>
@@ -5109,27 +5113,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 06:23:00</t>
+          <t>2026-06-03 12:12:35</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>suç örgütü</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Rüşvetle tahliye: Mahkeme başkanı hakim görevden uzaklaştırıldı</t>
+          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Rüşvetle tahliye: Mahkeme başkanı hakim görevden uzaklaştırıldı Personel Sağlık Personeli Haber NET</t>
+          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -5139,82 +5143,58 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>sağlık</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Son Dakika Rüşvetle tahliye: Mahkeme başkanı hakim görevden uzaklaştırıldı Adana Adliyesi'nde görevli bir Ağır Ceza Mahkemesi Başkanının, maddi menfaat karşılığında organize suç örgütü üyeleri de dahil olmak üzere birden fazla zanlıyı usulsüz şekilde tahliye ettiği iddia edildi. Hakimler ve Savcılar Kurulu (HSK), hazırlanan raporun ardından şüpheli hakimi 3 ay süreyle görevden uzaklaştırdı. 03.06.2026 - 09:23 03.06.2026 - 09:23 Rüşvet ile tahliye iddiası Adana Adliyesi'ni karıştırdı. NTV'nin haberine göre; Adana Cumhuriyet Başsavcılığı'nda görevli ağır ceza mahkemesi başkanı ve aynı zamanda hakimin "maddi menfaat" karşılığında tahliye kararları verdiği iddia edildi. RAPORLARA YANSIDI İlgili iddialar, Hakimler ve Savcılar Kurulu (HSK) 2. Dairesi tarafından tutulan raporda yer aldı. İddiaların odağındaki hakimin 4 avukatla ortak hareket ettiği ve birden fazla suça karışan 8 zanlının rüşvet karşılığı tahliye ettiği öne sürüldü. Şüpheli hakim hakkında Baygaralar suç örgütü üyesi olduğu tespit edilen zanlının "nitelikli yağma" suçu kapsamında gözaltına alındığı ve maddi menfaat karşılığı tahliye edildiği iddiası yer aldı. "Görevli memura direnme", "ruhsatsız silah", "kumar oynanması için yer ve imkan sağlama" iddiasıyla yürütülen soruşturma kapsamında tutuklama talebiyle mahkemeye sevk edilmesine rağmen iddialar odağındaki söz konusu hakimin tutuklama kararı vermediği de öne sürüldü. GÖREVDEN UZAKLAŞTIRILDI HSK, 3 ay süreyle ilgili hakimi görevden uzaklaştırıldı. Şüpheli hakim ilerleyen günlerde ifade verecek. Bu</t>
+          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Rüşvetle tahliye: Mahkeme başkanı hakim görevden uzaklaştırıldı Rüşvetle tahliye: Mahkeme başkanı hakim görevden uzaklaştırıldı Personel Sağlık Personeli Haber NET Son Dakika Rüşvetle tahliye: Mahkeme başkanı hakim görevden uzaklaştırıldı Adana Adliyesi'nde görevli bir Ağır Ceza Mahkemesi Başkanının, maddi menfaat karşılığında organize suç örgütü üyeleri de dahil olmak üzere birden fazla zanlıyı usulsüz şekilde tahliye ettiği iddia edildi. Hakimler ve Savcılar Kurulu (HSK), hazırlanan raporun ardından şüpheli hakimi 3 ay süreyle görevden uzaklaştırdı. 03.06.2026 - 09:23 03.06.2026 - 09:23 Rüşvet ile tahliye iddiası Adana Adliyesi'ni karıştırdı. NTV'nin haberine göre; Adana Cumhuriyet Başsavcılığı'nda görevli ağır ceza mahkemesi başkanı ve aynı zamanda hakimin "maddi menfaat" karşılığında tahliye kararları verdiği iddia edildi. RAPORLARA YANSIDI İlgili iddialar, Hakimler ve Savcılar Kurulu (HSK) 2. Dairesi tarafından tutulan raporda yer aldı. İddiaların odağındaki hakimin 4 avukatla ortak hareket ettiği ve birden fazla suça karışan 8 zanlının rüşvet karşılığı tahliye ettiği öne sürüldü. Şüpheli hakim hakkında Baygaralar suç örgütü üyesi olduğu tespit edilen zanlının "nitelikli yağma" suçu kapsamında gözaltına alındığı ve maddi menfaat karşılığı tahliye edildiği iddiası yer aldı. "Görevli memura direnme", "ruhsatsız silah", "kumar oynanması için yer ve imkan sağlama" iddiasıyla yürütülen soruşturma kapsamında tutuklama talebiyle mahkemeye sevk edilmesine rağmen iddialar odağındaki söz konusu hakimin tutuklama kararı vermediği de öne sürüldü. GÖREVDEN UZAKLAŞTIRILDI HSK, 3 ay süreyle ilgili hakimi görevden uzaklaştırıldı. Şüpheli hakim ilerleyen günlerde ifade verecek.</t>
+          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNMENGNmJzWlpLUlZjU2JYZzBrWEtUU05acjg2UmF1czFtNzdiODlEVWQ0Y19zOWpEWHdFbC14R2N6bjZ6UGkwRUhuek5zNWZ3Xy12SWJ0REh3MTljbVFjOTZOTnFvNWZFdjFBdEdIYU94ejdxUHNjWmVpWG51eDk3OVFRV205b3dWZDlwZ20xbndkTWRoN1d3QnpPVzFmc0Z1NFJz0gGjAUFVX3lxTE0wQ0Y2YnNaWktSVmNTYlhnMGtYS1RTTlpyODZSYXVzMW03N2I4OURVZDRjX3M5akRYd0VsLXhHY3puNnpQaTBFSG56TnM1ZndfLXZJYnRESHcxOWNtUWM5Nk5OcW81ZkV2MUF0R0hhT3h6N3FQc2NaZWlYbnV4OTc5UVFXbTlvd1ZkOXBnbTFud2RNZGg3V3dCek9XMWZzRnU0UnM?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Adana</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOblFrNWVVVVVxZ0tSbjNYek5xOUhLcl9RZzJ1ZzhSclFNOTVaY3B0WUk0ODhYSVhJMUVjcVlueUpOMnlBMFVSdFBMRk54T0pxQ240WllDZnBiU0xlVWlrT1BKb1oyX0FlaGZndmg4eDR2T3lrUnNrTWxEZjltU0VqajYwc0tQTDFnTFNvSU51bDFaT3pHbjVEYThwRTlCQVdZQ1k1ZGdR0gGmAUFVX3lxTE5uUWs1ZVVVVXFnS1JuM1h6TnE5SEtyX1FnMnVnOFJyUU05NVpjcHRZSTQ4OFhJWEkxRWNxWW55Sk4yeUEwVVJ0UExGTnhPSnFDbjRaWUNmcGJTTGVVaWtPUEpvWjJfQWVoZmd2aDh4NHZPeWtSc2tNbERmOW1TRWpqNjBzS1BMMWdMU29JTnVsMVpPekduNURhOHBFOUJBV1lDWTVkZ1E?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>Personel Sağlık</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>Personel Sağlık:174:body+summary</t>
-        </is>
-      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>Personel Sağlık Adana Türkiye</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Personel Sağlık | Özel Platform Sağlık Hizmetleri ve Dan. Org. A.Ş</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>Personel Sağlık</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>100.0 | 57.142857142857146</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="n">
-        <v>203.25</v>
+        <v>37.84</v>
       </c>
       <c r="AB28" s="2" t="n">
         <v>27</v>
@@ -5223,27 +5203,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 01:00:00</t>
+          <t>2026-06-03 10:50:38</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>yasa dışı bahis</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Yasa dışı bahisçiler yoğun para transferine takıldı</t>
+          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Yasa dışı bahisçiler yoğun para transferine takıldı Yeni Şafak</t>
+          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün Merhaba Gazetesi</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -5253,37 +5233,45 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>para transferi</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>fabrika, sanayi</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Yasa dışı bahis şebekelerine geçit yok. Nevşehir Cumhuriyet Başsavcılığı’nca yürütülen yasa dışı bahis soruşturması kapsamında, Nevşehir merkezli 28 ilde dev operasyon gerçekleştirildi. Yasa dışı bahis şebekelerine geçit yok. Nevşehir Cumhuriyet Başsavcılığı’nca yürütülen yasa dışı bahis soruşturması kapsamında, Nevşehir merkezli 28 ilde dev operasyon gerçekleştirildi. Yasa dışı bahis şebekelerine geçit yok. Nevşehir Cumhuriyet Başsavcılığı’nca yürütülen yasa dışı bahis soruşturması kapsamında, Nevşehir merkezli 28 ilde dev operasyon gerçekleştirildi.</t>
+          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün 03 Haziran 2026 Çarşamba 13:50 Ekonomik krizin etkisiyle konkordato ilan eden firmalara bir yenisi daha eklendi. Konya sanayisindeki dev fabrikanın konkordato süreci 2 gün sonra netleşecek. Ekonomik kriz Türkiye'deki birçok üretim tesisini olumsuz etkiledi. Nakit para akışının durmasıyla konkordato ve iflaslar patladı. Son olarak 2011 yılında Konya Büsan Özel Sanayi Bölgesi'nde kurulan ART Endüstri konkordato ilan etti. 2016 yılından itibaren Konya 2. Organize Sanayi Bölgesi'nde üretime devam eden ART Endüstri , seramik teşhir sistemlerinden depo raf sistemlerine ve uyku merkezlerinin özel ihtiyaçlarına kadar geniş bir uygulama yelpazesinde özgün çözümler sunan, kalite odaklı ve yenilikçi bir üretim şirketi. Piyasada tanınan firmayla ilgili konkordato haberini görenler üzüldü. Öte yandan mahkemenin konkordato sürecine ilişkin kararını 5 Haziran 2026 tarihinde vereceği öğrenildi. Buna göre, ART Endüstri ile ilgili karar 2 gün sonra verilecek. T.c. Konya 3.asliye Ticaret Mahkemesi Başkanlığı'nın duyurusu</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Yasa dışı bahisçiler yoğun para transferine takıldı Yasa dışı bahisçiler yoğun para transferine takıldı Yeni Şafak Yasa dışı bahis şebekelerine geçit yok. Nevşehir Cumhuriyet Başsavcılığı’nca yürütülen yasa dışı bahis soruşturması kapsamında, Nevşehir merkezli 28 ilde dev operasyon gerçekleştirildi.</t>
+          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün Merhaba Gazetesi Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün 03 Haziran 2026 Çarşamba 13:50 Ekonomik krizin etkisiyle konkordato ilan eden firmalara bir yenisi daha eklendi. Konya sanayisindeki dev fabrikanın konkordato süreci 2 gün sonra netleşecek. Ekonomik kriz Türkiye'deki birçok üretim tesisini olumsuz etkiledi. Nakit para akışının durmasıyla konkordato ve iflaslar patladı. Son olarak 2011 yılında Konya Büsan Özel Sanayi Bölgesi'nde kurulan ART Endüstri konkordato ilan etti. 2016 yılından itibaren Konya 2. Organize Sanayi Bölgesi'nde üretime devam eden ART Endüstri , seramik teşhir sistemlerinden depo raf sistemlerine ve uyku merkezlerinin özel ihtiyaçlarına kadar geniş bir uygulama yelpazesinde özgün çözümler sunan, kalite odaklı ve yenilikçi bir üretim şirketi. Piyasada tanınan firmayla ilgili konkordato haberini görenler üzüldü. Öte yandan mahkemenin konkordato sürecine ilişkin kararını 5 Haziran 2026 tarihinde vereceği öğrenildi. Konya 3.asliye Ticaret Mahkemesi Başkanlığı'nın duyurusu</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.yenisafak.com/gundem/yasa-disi-bahisciler-yogun-para-transferine-takildi-4829231</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNaWpwcnFFcXdzRS1VczM4TVAzVXI3anZEU3IxTm5aS2JMRlV6cDhRVEpMeXc5TEpOdlBMLWU4NmxZUWZiMU5CenNFSUROOVdoZnlaV0NBREZMcjN2aFVFaFlLTWd6cmFGQndIQWFKMnliWmhiXzE5d0JOeXkzTWs4LWhKWW1EaFdIa1RjWHhWcjdlX1k2UUM4bHdsNEt1eXdrSXE5YVVlVmt1WktVbUdQQm1aRFZZU2_SAbcBQVVfeXFMTWlqcHJxRXF3c0UtVXMzOE1QM1VyN2p2RFNyMU5uWktiTEZVenA4UVRKTHl3OUxKTnZQTC1lODZsWVFmYjFOQnpzRUlETjlXaGZ5WldDQURGTHIzdmhVRWhZS01nenJhRkJ3SEFhSjJ5YlpoYl8xOXdCTnl5M01rOC1oSlltRGhXSGtUY1h4VnI3ZV9ZNlFDOGx3bDRLdXl3a0lxOWFVZVZrdVpLVW1HUEJtWkRWWVNv?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Nevşehir</t>
+          <t>Konya</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>Büsan</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr"/>
@@ -5304,7 +5292,7 @@
       <c r="Y29" s="2" t="inlineStr"/>
       <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="n">
-        <v>64.56999999999999</v>
+        <v>102.31</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>28</v>
@@ -5313,27 +5301,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 17:28:51</t>
+          <t>2026-06-03 14:41:47</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ordu'da mobilya atölyesinde yangın</t>
+          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Ordu'da mobilya atölyesinde yangın Sözcü Gazetesi</t>
+          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -5343,44 +5331,36 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>atölye</t>
+          <t>firma</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>atölye</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Haberler - Gündem Ordu'da mobilya atölyesinde yangın Ordu’nun Çatalpınar ilçesindeki bir mobilya atölyesinde çıkan yangın paniğe neden oldu. Kısa sürede çatıyı saran alevler, itfaiye ekiplerinin müdahalesiyle kontrol altına alınırken iş yerinde maddi hasar oluştu Yayınlanma: 02 Haziran 2026 - 20:28 Güncellenme: Ordu'nun Çatalpınar ilçesinde bulunan bir mobilya atölyesinde çıkan yangın, ekiplerin hızlı müdahalesi sayesinde büyümeden söndürüldü. Yangın, sabah saatlerinde Çatalpınar Sanayi Sitesi'nde faaliyet gösteren bir mobilya üretim atölyesinin çatı bölümünde meydana geldi. İddiaya göre elektrik tesisatındaki bir arızadan kaynaklanan yangın, kısa sürede büyüyerek çatının büyük bölümünü etkisi altına aldı. Yükselen duman ve alevleri fark eden çevredekilerin ihbarı üzerine bölgeye itfaiye ekipleri sevk edildi. Olay yerine ulaşan ekipler, yangına kısa sürede müdahale ederek alevlerin iş yerinin diğer bölümlerine sıçramasını önledi. Yoğun çalışma sonucu kontrol altına alınan yangın tamamen söndürülürken, atölyenin çatı kısmında ve bazı bölümlerinde maddi hasar meydana geldi. Yangında can kaybı ya da yaralanma yaşanmazken, ekipler olay yerinde soğutma çalışması gerçekleştirdi. Yangının kesin çıkış nedeninin belirlenmesi için inceleme başlatıldığı bildirildi. Ordu'da mobilya atölyesinde yangın Ordu’nun Çatalpınar ilçesindeki bir mobilya atölyesinde çıkan yangın paniğe neden oldu. Kısa sürede çatıyı saran alevler, itfaiye ekiplerinin müdahalesiyle kontrol altına alınırken iş yerinde maddi hasar oluştu Yayınlanma: 02 Haziran 2026 - 20:28 Güncellenme: Yayınlanma: 02 Haziran 2026 - 20:28 Güncellenme: Ordu'nun Çatalpınar ilçesinde bulunan bir mobilya atölyesinde çıkan yangın, ekiplerin hızlı müdahalesi sayesinde büyümeden söndürüldü. Yangın, sabah saatlerinde Çatalpınar Sanayi Sitesi'nde faaliyet gösteren bir mobilya üretim atölyesinin çatı bölümünde meydana geldi. İddiaya göre elektrik tesisatındaki bir arızadan kaynaklanan yangın, kısa sürede büyüyerek çatının büyük bölümünü etkisi altına aldı. Yükselen duman ve alevleri fark eden çevredekilerin ihbarı üzerine bölgeye itfaiye ekipleri sevk edildi. Olay yerine ulaşan ekipler, yangına kısa sürede müdahale ederek alevlerin iş yerinin diğer bölümlerine sıçramasını önledi. Yoğun çalışma sonucu kontrol altına alınan yangın tamamen söndürülürken, atölyenin çatı kısmında ve bazı bölümlerinde maddi hasar meydana geldi. Yangında can kaybı ya da yaralanma yaşanmazken, ekipler olay yerinde soğutma çalışması gerçekleştirdi. Yangının kesin çıkış nedeninin belirlenmesi için inceleme başlatıldığı bildirildi. Ordu'da mobilya atölyesinde yangın Ordu’nun Çatalpınar ilçesindeki bir mobilya atölyesinde çıkan yangın paniğe neden oldu. Kısa sürede çatıyı saran alevler, itfaiye ekiplerinin müdahalesiyle kontrol altına alınırken iş yerinde maddi hasar oluştu Ordu'nun Çatalpınar ilçesinde bulunan bir mobilya atölyesinde çıkan yangın, ekiplerin hızlı müdahalesi sayesinde büyümeden söndürüldü. Yangın, sabah saatlerinde Çatalpınar Sanayi Sitesi'nde faaliyet gösteren bir mobilya üretim atölyesinin çatı bölümünde meydana geldi. İddiaya göre elektrik tesisatındaki bir arızadan kaynaklanan yangın, kısa sürede büyüyerek çatının büyük bölümünü etkisi altına aldı. Yükselen duman ve alevleri fark eden çevredekilerin ihbarı üzerine bölgeye itfaiye ekipleri sevk edildi. Olay yerine ulaşan ekipler, yangına kısa sürede müdahale ederek alevlerin iş yerinin diğer bölümlerine sıçramasını önledi. Yoğun çalışma sonucu kontrol altına alınan yangın tamamen söndürülürken, atölyenin çatı kısmında ve bazı bölümlerinde maddi hasar meydana geldi. Yangında can kaybı ya da yaralanma yaşanmazken, ekipler olay yerinde soğutma çalışması gerçekleştirdi. Yangının kesin çıkış nedeninin belirlenmesi için inceleme başlatıldığı bildirildi.</t>
+          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Ordu'da mobilya atölyesinde yangın Ordu'da mobilya atölyesinde yangın Sözcü Gazetesi Haberler - Gündem Ordu'da mobilya atölyesinde yangın Ordu’nun Çatalpınar ilçesindeki bir mobilya atölyesinde çıkan yangın paniğe neden oldu. Kısa sürede çatıyı saran alevler, itfaiye ekiplerinin müdahalesiyle kontrol altına alınırken iş yerinde maddi hasar oluştu Yayınlanma: 02 Haziran 2026 - 20:28 Güncellenme: Ordu'nun Çatalpınar ilçesinde bulunan bir mobilya atölyesinde çıkan yangın, ekiplerin hızlı müdahalesi sayesinde büyümeden söndürüldü. Yangın, sabah saatlerinde Çatalpınar Sanayi Sitesi'nde faaliyet gösteren bir mobilya üretim atölyesinin çatı bölümünde meydana geldi. İddiaya göre elektrik tesisatındaki bir arızadan kaynaklanan yangın, kısa sürede büyüyerek çatının büyük bölümünü etkisi altına aldı. Yükselen duman ve alevleri fark eden çevredekilerin ihbarı üzerine bölgeye itfaiye ekipleri sevk edildi. Olay yerine ulaşan ekipler, yangına kısa sürede müdahale ederek alevlerin iş yerinin diğer bölümlerine sıçramasını önledi. Yoğun çalışma sonucu kontrol altına alınan yangın tamamen söndürülürken, atölyenin çatı kısmında ve bazı bölümlerinde maddi hasar meydana geldi. Yangında can kaybı ya da yaralanma yaşanmazken, ekipler olay yerinde soğutma çalışması gerçekleştirdi. Yangının kesin çıkış nedeninin belirlenmesi için inceleme başlatıldığı bildirildi. Ordu'da mobilya atölyesinde yangın Ordu’nun Çatalpınar ilçesindeki bir mobilya atölyesinde çıkan yangın paniğe neden oldu. Kısa sürede çatıyı saran alevler, itfaiye ekiplerinin müdahalesiyle kontrol altına alınırken iş yerinde maddi hasar oluştu Yayınlanma: 02 Haziran 2026 - 20:28 Güncellenme: Yayınlanma: 02 Haziran 2026 - 20:28 Güncellenme: Ordu'nun Çatalpınar ilçesinde bulunan bir mobilya atölyesinde çıkan yangın, ekiplerin hızlı müdahalesi sayesinde büyümeden söndürüldü. Kısa sürede çatıyı saran alevler, itfaiye ekiplerinin müdahalesiyle kontrol altına alınırken iş yerinde maddi hasar oluştu Ordu'nun Çatalpınar ilçesinde bulunan bir mobilya atölyesinde çıkan yangın, ekiplerin hızlı müdahalesi sayesinde büyümeden söndürüldü.</t>
+          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE55Mk84ZXBpY05QSEpyQ3BEbTZkSTBvQmc5Z1pSQ0ktRkJQVUgxX1NkMERzckhGNTRCWjVQZGx1RU1GSTJzeE1IaTN0TW5PMU1NbEJDQXJxV2g3VDBRamNaaE9mQ2FTdG1fSDl6ZHRCN0tKNGFMLXl5YWtCYw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>Ordu</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>Çatalpınar</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVi1QOUJuTzhBaU1haWNwd3B6OVRjSHktVWlKQ25USktQZmpnZEZiMHZuRW5aN1VmZVRJVWNaMFhubmVWdjh3TmItWHgtVlJpRGNtSWZWTnY5OTBNTXhITjl1d2hPZlNKa0ZGN0RJcUR4djBRdF9CUTFnZlh2TU9ZcHZVUks2QmMwMklIcTVaQzZkRjYyMy1kc1hYcW10Q3RmUy1vNHduOHFTSFVnWlpNRHNuUVJVUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -5388,7 +5368,7 @@
       <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr"/>
@@ -5402,7 +5382,7 @@
       <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr"/>
       <c r="AA30" s="2" t="n">
-        <v>80.25</v>
+        <v>71.28</v>
       </c>
       <c r="AB30" s="2" t="n">
         <v>29</v>
@@ -5411,27 +5391,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 04:00:08</t>
+          <t>2026-06-03 15:46:28</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Vietnamlı işletmeler yangın önleme ve yangın söndürme alanındaki teknolojik yeteneklerini sergiliyor.</t>
+          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Vietnamlı işletmeler yangın önleme ve yangın söndürme alanındaki teknolojik yeteneklerini sergiliyor. Vietnam.vn</t>
+          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -5441,18 +5421,22 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>işletme</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+          <t>firma</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Vietnamlı işletmeler yangın önleme ve yangın söndürme alanındaki teknolojik yeteneklerini sergiliyor. Vietnam.vn</t>
+          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Vietnamlı işletmeler yangın önleme ve yangın söndürme alanındaki teknolojik yeteneklerini sergiliyor. Vietnamlı işletmeler yangın önleme ve yangın söndürme alanındaki teknolojik yeteneklerini sergiliyor. Vietnam.vn Vietnamlı işletmeler yangın önleme ve yangın söndürme alanındaki teknolojik yeteneklerini sergiliyor.</t>
+          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365 Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -5462,7 +5446,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOcnVscVdvVzlVbW5ZNFNfOU9LNEdOTzVSUWxDUW1GR3FnVFRxWXVoWGp3UGFxZTNWdWxYbWMzM2hNcEFrMXNpZFhxYktWZWhMTW8xR2RNT3FXQW1vNk11Z09FYTNvWW8zOG1EQ2RSVkwybGpoWlpwdDZKN0thS0lEeE8xc2w4Wm10eEJWdDFXblZhUVBsbTQxS2xSOGVfU1JVVzNZ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPc0FMTk9yb21xWXRueTBWTTltZTVOdlRoU1RIaHdzQWM5QUR0WFdJWGpkSW02dWpGUkFJRXdPclRvb3dPMHVlSGVWbkZUVlpPY2hTWFB4cUoxWjUtWHpPclExdllIQm5XVE5zdXp4SjhRRnRWUzRmUFNMd3MyVlpLM1FzdElRaUg00gGOAUFVX3lxTFBDeFIteWxqTzRua1BLVDhOMThnM3hZQUFZdENiTll4SEFrMWpGODZWbGJRVlNYT045YTg2SklVVktVVVpqenY5Z0dyd3FFNkp4YlRBR3piS3otTFlDbXp5blV4dDhBODZIN0xoMHJTQzZyaHpNSjl4eThpYW1aTVpaNHdoaXAtZTdibXNBYkE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
@@ -5488,7 +5472,7 @@
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="n">
-        <v>95.62</v>
+        <v>46.32</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>30</v>
@@ -5497,27 +5481,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:55:00</t>
+          <t>2026-06-03 09:45:31</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>İTÜ’de dolandırıcılık iddiası: Spor tesisleri çalışanlarına operasyon</t>
+          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>İTÜ’de dolandırıcılık iddiası: Spor tesisleri çalışanlarına operasyon birgun.net</t>
+          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu velev.press</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -5527,18 +5511,18 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
+          <t>sanayi</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Teknik Üniversitesi’nin spor tesislerini yönetmek için kurulan şirketin çalışanları, üyelik aidatlarını kendi hesaplarına yönlendirdikleri iddiasıyla gözaltına alındı. Aralarında şirket yöneticileri, yüzme antrenörleri, spor uzmanı ve büro memurlarının da bulunduğu 8 şüpheli adliyeye sevk edildi. İstanbul Teknik Üniversitesi’nin spor tesislerini yönetmek için kurulan şirketin çalışanları, üyelik aidatlarını kendi hesaplarına yönlendirdikleri iddiasıyla gözaltına alındı. Aralarında şirket yöneticileri, yüzme antrenörleri, spor uzmanı ve büro memurlarının da bulunduğu 8 şüpheli adliyeye sevk edildi. İstanbul Teknik Üniversitesi’nin spor tesislerini yönetmek için kurulan şirketin çalışanları, üyelik aidatlarını kendi hesaplarına yönlendirdikleri iddiasıyla gözaltına alındı. Aralarında şirket yöneticileri, yüzme antrenörleri, spor uzmanı ve büro memurlarının da bulunduğu 8 şüpheli adliyeye sevk edildi. İstanbul Ankara İzmir Adana Adıyaman Afyon Ağrı Aksaray Amasya Antalya Ardahan Artvin Aydın Balıkesir Bartın Batman Bayburt Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Düzce Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Iğdır Isparta Mersin K.Maraş Karabük Karaman Kars Kastamonu Kayseri Kırıkkale Kırklareli Kırşehir Kilis Kocaeli Konya Kütahya Malatya Manisa Mardin Muğla Muş Nevşehir Niğde Ordu Osmaniye Rize Sakarya Samsun Siirt Sinop Sivas Şırnak Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yalova Yozgat Zonguldak 23° Parçalı Az Bulutlu İTÜ’de dolandırıcılık iddiası: Spor tesisleri çalışanlarına operasyon İstanbul Teknik Üniversitesi’nin spor tesislerini yönetmek için kurulan şirketin çalışanları, üyelik aidatlarını kendi hesaplarına yönlendirdikleri iddiasıyla gözaltına alındı. Aralarında şirket yöneticileri, yüzme antrenörleri, spor uzmanı ve büro memurlarının da bulunduğu 8 şüpheli adliyeye sevk edildi. Güncel 03.06.2026 11:55 Giriş: 03.06.2026 11:55 Güncelleme: 03.06.2026 11:59 Kaynak: DHA A- A A+ Fotoğraf: DHA BirGün'ü Google'da favori kaynak olarak tanımlayın. Tıkla ve anında ekle İstanbul Teknik Üniversitesi’nin spor tesislerini yönetmek için kurulan şirketin çalışanları, üniversiteyi 4,4 milyon lira dolandırdıkları iddiasıyla gözaltına alındı. Şüphelilerin üniversitenin banka İBAN numarasını, kendi İBAN numaralarıyla değiştirerek, üyelik aidatlarını hesaplarına gönderilmesini sağladıkları öğrenildi. Gözaltına alınanlar arasında iki şirket yöneticisi, yüzme antrenörleri, spor uzmanı ve büro memurları ile, kısa bir süre özel üniversitede öğretim görevlisi olarak çalışmaya başlayan bir kişinin bulunduğu belirtildi. Şüpheliler işlemlerinin ardından adliyeye sevk edildi. İstanbul Cumhuriyet Savcılığı’na üniversite yöneticilerinin yaptığı şikayet üzerine Asayiş Şube Müdürlüğü ekipleri tarafından soruşturma başlatıldı. Dolandırıcılık Büro Amirliği ekipleri tarafından yapılan çalışmalarda üniversitenin yöneticileri, spor tesislerinde kayıtlı üye sayısı azaldığının görülmesine rağmen, giderlerin hızla yükseldiği, spor alanlarının aşırı kalabalık olduğu belirtildi. Dolandırıcılık Büro Amirliği ekipleri yaptıkları araştırmada spor tesislerine üyelik işlemleri için Üniversite iştiraki olarak kurulan şirket çalışanlarını takibe aldı. Yapılan çalışmalarda Üniversitenin spor tesislerine son aylarda neredeyse yok denecek kadar üye kaydedildiğini, bu rağmen havlu, duş gibi giderlerinde büyük artış yaşandığı tespit edildi. Özellikle tesislerde kullanılan havlu sayısının, kağıt üzerinde gözüken üye sayısından çok fazla olduğunu belirledi. 4 ,4 MİLYON LİRALIK VURGUN İDDİASI Dolandırıcılık Büro Amirliği ekipleri incelemeye aldıkları şirket çalışanlarının ödemenin yapıldığı internet sitesi üzerinden üniversiteye ait İBAN numaralarını, kendi şahsi hesaplarının İBAN numarası ile değiştirdiklerini, bu sayede ödenen üyelik aidatlarının kendi hesaplarına gelmesini sağladıklarını tespit etti. Yapılan incelemede şüphelilerin üniversiteyi 4 milyon 400 bin lira zarara uğrattıkları belirlendi. Asayiş Şube Müdürlüğüne bağlı ekipler gerekli delillerin toplanmasının ardından şüphelileri yakalamak için operasyon düzenledi. Şirket yöneticileri G.K. ile M.İ.’nin aralarında bulunduğu biri kadın 8 şüpheli gözaltına alındı. Gözaltına alınlar arasında yüzme antrenörleri, spor uzmanları büro memurları ile kısa süre önce dolandırılan üniversitede çalışırken işten çıkarılan ve özel bir üniversitede öğretim görevlisi olarak çalışmaya başlayan bir kişinin bulunduğu öğrenildi. ADLİYEYE SEVK EDİLDİLER Dolandırıcılık Büro Amirliği tarafından yapılan çalışmalarda şirket yöneticisi G.K.’ya bağlı çalışan kişilerinde İBAN bilgilerini kullanarak para topladığını tespit etti. Şirket yöneticisi G.K. poliste susma hakkını kullanırken, diğer şüphelilerin hesaplarına gelen paraları çekerek G.K.’ya teslim ettiklerini, dolandırıcılık olayından haberleri olmadıklarını iddia ettiler. Şüpheliler işlemlerinin ardından adliyeye sevk edildiler. (DHA) #itü #dolandırıcı #gözaltı #operasyon #istanbul #tesis #spor Sıradaki Haber İTÜ’de</t>
+          <t>Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Ankara 3. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Şirket, yüksek finansman maliyetleri, kredi geri ödeme sorunları ve bozulan nakit akışı nedeniyle mahkemeye başvurduğunu açıkladı. Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Ankara 3. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Şirket, yüksek finansman maliyetleri, kredi geri ödeme sorunları ve bozulan nakit akışı nedeniyle mahkemeye başvurduğunu açıkladı. Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Ankara 3. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Şirket, yüksek finansman maliyetleri, kredi geri ödeme sorunları ve bozulan nakit akışı nedeniyle mahkemeye başvurduğunu açıkladı. Kamuyu Aydınlatma Platformu’nda (KAP) yayımlanan açıklamaya göre Türk İlaç ve Serum Sanayi A.Ş., Yönetim Kurulu Başkanı Mehmet Berat Battal ve şirkette pay sahibi olan Battal Holding A.Ş. ile birlikte konkordato talebinde bulundu. Başvuru sonucunda Ankara 3. Asliye Ticaret Mahkemesi tarafından 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verildi. Şirket açıklamasında , krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin konkordato başvurusunun temel nedenleri arasında yer aldığı belirtildi. KAP açıklamasında, 14 Mayıs 2026 tarihinde başlayan kredi geri ödeme gecikmelerinin devam ettiği ifade edildi. Ayrıca 20 Mayıs 2026 tarihinde oluşan karşılıksız çek kayıtlarının da henüz kapatılamadığı bilgisi paylaşı</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>İTÜ’de dolandırıcılık iddiası: Spor tesisleri çalışanlarına operasyon İTÜ’de dolandırıcılık iddiası: Spor tesisleri çalışanlarına operasyon birgun.net İstanbul Teknik Üniversitesi’nin spor tesislerini yönetmek için kurulan şirketin çalışanları, üyelik aidatlarını kendi hesaplarına yönlendirdikleri iddiasıyla gözaltına alındı. Aralarında şirket yöneticileri, yüzme antrenörleri, spor uzmanı ve büro memurlarının da bulunduğu 8 şüpheli adliyeye sevk edildi. İstanbul Ankara İzmir Adana Adıyaman Afyon Ağrı Aksaray Amasya Antalya Ardahan Artvin Aydın Balıkesir Bartın Batman Bayburt Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Düzce Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Iğdır Isparta Mersin K.Maraş Karabük Karaman Kars Kastamonu Kayseri Kırıkkale Kırklareli Kırşehir Kilis Kocaeli Konya Kütahya Malatya Manisa Mardin Muğla Muş Nevşehir Niğde Ordu Osmaniye Rize Sakarya Samsun Siirt Sinop Sivas Şırnak Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yalova Yozgat Zonguldak 23° Parçalı Az Bulutlu İTÜ’de dolandırıcılık iddiası: Spor tesisleri çalışanlarına operasyon İstanbul Teknik Üniversitesi’nin spor tesislerini yönetmek için kurulan şirketin çalışanları, üyelik aidatlarını kendi hesaplarına yönlendirdikleri iddiasıyla gözaltına alındı. Güncel 03.06.2026 11:55 Giriş: 03.06.2026 11:55 Güncelleme: 03.06.2026 11:59 Kaynak: DHA A- A A+ Fotoğraf: DHA BirGün'ü Google'da favori kaynak olarak tanımlayın. Tıkla ve anında ekle İstanbul Teknik Üniversitesi’nin spor tesislerini yönetmek için kurulan şirketin çalışanları, üniversiteyi 4,4 milyon lira dolandırdıkları iddiasıyla gözaltına alındı. Şüphelilerin üniversitenin banka İBAN numarasını, kendi İBAN numaralarıyla değiştirerek, üyelik aidatlarını hesaplarına gönderilmesini sağladıkları öğrenildi. Gözaltına alınanlar arasında iki şirket yöneticisi, yüzme antrenörleri, spor uzmanı ve büro memurları ile, kısa bir süre özel üniversitede öğretim görevlisi olarak çalışmaya başlayan bir kişinin bulunduğu belirtildi. İstanbul Cumhuriyet Savcılığı’na üniversite yöneticilerinin yaptığı şikayet üzerine Asayiş Şube Müdürlüğü ekipleri tarafından soruşturma başlatıldı. Dolandırıcılık Büro Amirliği ekipleri tarafından yapılan çalışmalarda üniversitenin yöneticileri, spor tesislerinde kayıtlı üye sayısı azaldığının görülmesine rağmen, giderlerin hızla yükseldiği, spor alanlarının aşırı kalabalık olduğu belirtildi. Dolandırıcılık Büro Amirliği ekipleri yaptıkları araştırmada spor tesislerine üyelik işlemleri için Üniversite iştiraki olarak kurulan şirket çalışanlarını takibe aldı. Yapılan çalışmalarda Üniversitenin spor tesislerine son aylarda neredeyse yok denecek kadar üye kaydedildiğini, bu rağmen havlu, duş gibi giderlerinde büyük artış yaşandığı tespit edildi. Özellikle tesislerde kullanılan havlu sayısının, kağıt üzerinde gözüken üye sayısından çok fazla olduğunu belirledi. 4 ,4 MİLYON LİRALIK VURGUN İDDİASI Dolandırıcılık Büro Amirliği ekipleri incelemeye aldıkları şirket çalışanlarının ödemenin yapıldığı internet sitesi üzerinden üniversiteye ait İBAN numaralarını, kendi şahsi hesaplarının İBAN numarası ile değiştirdiklerini, bu sayede ödenen üyelik aidatlarının kendi hesaplarına gelmesini sağladıklarını tespit etti. Asayiş Şube Müdürlüğüne bağlı ekipler gerekli delillerin toplanmasının ardından şüphelileri yakalamak için operasyon düzenledi. Gözaltına alınlar arasında yüzme antrenörleri, spor uzmanları büro memurları ile kısa süre önce dolandırılan üniversitede çalışırken işten çıkarılan ve özel bir üniversitede öğretim görevlisi olarak çalışmaya başlayan bir kişinin bulunduğu öğrenildi. ADLİYEYE SEVK EDİLDİLER Dolandırıcılık Büro Amirliği tarafından yapılan çalışmalarda şirket yöneticisi G.K.’ya bağlı çalışan kişilerinde İBAN bilgilerini kullanarak para topladığını tespit etti. poliste susma hakkını kullanırken, diğer şüphelilerin hesaplarına gelen paraları çekerek G.K.’ya teslim ettiklerini, dolandırıcılık olayından haberleri olmadıklarını iddia ettiler.</t>
+          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu velev.press Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Şirket, yüksek finansman maliyetleri, kredi geri ödeme sorunları ve bozulan nakit akışı nedeniyle mahkemeye başvurduğunu açıkladı. Kamuyu Aydınlatma Platformu’nda (KAP) yayımlanan açıklamaya göre Türk İlaç ve Serum Sanayi A.Ş., Yönetim Kurulu Başkanı Mehmet Berat Battal ve şirkette pay sahibi olan Battal Holding A.Ş. ile birlikte konkordato talebinde bulundu. Başvuru sonucunda Ankara 3. Asliye Ticaret Mahkemesi tarafından 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verildi. Şirket açıklamasında , krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin konkordato başvurusunun temel nedenleri arasında yer aldığı belirtildi. KAP açıklamasında, 14 Mayıs 2026 tarihinde başlayan kredi geri ödeme gecikmelerinin devam ettiği ifade edildi.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -5548,33 +5532,61 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.birgun.net/haber/itude-dolandiricilik-iddiasi-spor-tesisleri-calisanlarina-operasyon-716216</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>https://velev.press/ekonomi/turk-ilac-ve-serum-sanayi-konkordato-istedi-borsada-islem-goruyordu/</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Battal Holding A.Ş</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Battal Holding A.Ş:120:body | Battal Holding A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr"/>
-      <c r="V32" s="2" t="inlineStr"/>
-      <c r="W32" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>Battal Holding A.Ş İstanbul Türkiye</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Battal Group</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Battal Group</t>
+        </is>
+      </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="inlineStr"/>
       <c r="AA32" s="2" t="n">
-        <v>77.5</v>
+        <v>195.75</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>31</v>
@@ -5583,27 +5595,27 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 07:53:00</t>
+          <t>2026-06-03 10:24:46</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var</t>
+          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var tele1.com.tr</t>
+          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı Samanyolu Haber</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -5613,28 +5625,32 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>inşaat</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Gündem Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var 03.06.2026 - 10:53 03.06.2026 - 10:53 Canan İLARSLAN- Şevval CİNDİR / İSTANBUL, (DHA)- Esenyurt'ta bir gayrimenkul firması tarafından 2011'de temeli atılan 7 bloktan oluşan yaklaşık 5 bin dairelik konut projesinde iddiaya göre binlerce kişi mağdur oldu. Evlerini teslim alanlar ise, içi tamamlanmamış ve metrekaresi küçük dairelerle karşılaştı. Firma 15 yıl içinde 7 bloktan sadece 3 bloğu tamamladı; yaklaşık 2 bin kişi evlerine kavuşurken aralarında hala tapularını teslim alamayanlar da var. İnşaatı bitmeyen 4 blokta hak sahibi olan 4 binden fazla kişi ise mağdur. Muhammed Özata, tapularını alırken kendilerinden bir daire bedeli kadar para istendiğini söyleyerek, '2019-2020 yıllarında teslim edildi. Tapuyu ilk etapta almadık. Tapunun üzerinde 500-600 tane haciz vardı. 2-3 tane de banka ipoteği vardı. Biz ilk etapta Tüketici Mahkemesi'nde bu ipotekleri ve takyidatları kaldırmak için dava açtık. Akabinde bir sulh süreci oldu. Biz de davamızdan feragat edip ekstra 3 katı tapu ücreti ödeyerek, biz tapumuzu aldık. Burada da açıkçası dolandırıldık, 3 katı tapu masrafı ödedik' dedi. Mağdurlar konuyu yargıya taşırken Büyükçekmece Cumhuriyet Başsavcılığı tarafından yürütülen soruşturmanın sürdüğü öğrenildi. Avukat Mehmet Demircioğlu firmanın aynı metodu yurt dışında da kullandığını belirterek, 'Daire büyüklüklerine göre 1 milyon liradan aşağı olmamak üzere 4, 5, 6 milyon liralara varan 'Gel daireni tekrar satın al' dedirten bir zorlamayla karşı karşıyayız. Bitirilmemiş halen 3 bin konuttan bahsediyoruz. Toplamda 7 blokluk bir proje burası. 3 bloğu teslim ettiler; Kınalı, Sedef ve Burgaz; ama 4 blok halen bekliyor. Bunlardan bir tanesi teslim edilecek diye 5 yıldan beri insanlar oyalanıyor' ifadelerini kullandı. Esenyurt'ta 2010'da satışına başlanan temeli 2011'de atılan konut projesinde hak sahiplerine daireleri 2015 Aralık ayında teslim edilecekti. Firma daireleri teslim etmediği gibi tapularını almak isteyenlerden de bir daire bedeli kadar para istedi. Mağdurların şikayeti üzerine açılan davalar yaklaşık 13 yıldır sürerken, Büyükçekmece Cumhuriyet Başsavcılığı tarafından örgütlü suçlar kapsamında soruşturma başlatıldı. Site yönetimine ilişkin iddiaların konu edildiği hukuk davası devam ederken, yönetimin yaklaşık 10 yıldır genel kurul yapmadan faaliyette olduğu, yüksek aidatlar topladığı iddia edildi. Binlerce kişinin şikayetçi olduğu, yurtdışından da binin üzerinde kişinin daire satın alarak mağdur olduğu olayda, ticari dükkan sahiplerinden da tapusunu alamayanlar olduğu öğrenildi. Şirket 2021 yılında iflasını ilan etti. 2022 yılında ise ikinci alacaklılar toplantısında iflas masası oluşturuldu. 'BİNLERCE MAĞDUR; BİTİRİLMEYEN BİR İNŞAAT VAR' Projede yıllardır çözülemeyen bir mağduriyet yaşandığını belirten avukat Mehmet Demircioğlu, 'Burada 13 yıldan beri devam eden bir mağduriyet vakası var. Yüzlerce, hatta yurt dışındaki mağdurlarla birlikte binlerce mağdur var. Bitmeyen bir inşaat var, bitirilmeyen bir inşaat var. Biz burada mağdurların avukatları olarak birçok defa kendilerinden bilgi, belge istememize rağmen şirket hiçbir şekilde uzlaşmıyor. Sebebine gelince; burada hileli biçimde oluşturulmuş bir iflas düzeneği var. İflas masası şirketin eski çalışanları ve tanıdıklarından oluşturulmuş. Bir özel bankayla da anlaşarak bu iflas masasını oluşturdukları için elleri çok güçlü. Şu anda bütün borcunu ödemiş ve malik olması gerekirken kendi hakkı olan tapuyu tekrar bedeline yakın bir para istenilerek, buna da 'Sulh sözleşmesi' ile bir kılıf bulunarak insanların mağdur edildiği bir faciayla karşı karşıyayız' dedi. 'İNSANLARA HAKKI OLAN TAPU TEKRAR PARAYLA SATILMAK İSTENİYOR' Hak sahiplerinin tüm yükümlülüklerini yerine getirmelerine rağmen yeni ödeme talepleriyle karşı karşıya kaldığını belirten Demircioğlu, 'Farklı daire tipleri için farklı fiyatlar öngörmüşler. En küçük daire olan 1+1 daire için bile bugün güncel değerinin çok daha altında seyrediyor, 2,5 milyona bile satılamıyor. Olması gerekenin çok altında bir rakam bu. Burada bile insanlardan milyon liranın üzerinde para talep ediliyor ve insanlara hakkı olan tapu, tekrar parayla satılmak isteniyor. Burada bunu iflas masasının yetkisine dayanarak yapıyorlar. İflas masasını oluşturanlar yine kendileri. Daire büyüklüklerine göre 1 milyon liradan aşağı olmamak üzere 4, 5, 6 milyon liralara varan, adama 'Gel, daireni tekrar satın al' dedirten bir zorlamayla karşı karşıyayız. Bitirilmemiş halen 3 bin konuttan bahsediyoruz. Toplamda 7 blokluk bir proje burası. 3 bloğu teslim ettiler; Kınalı, Sedef ve Burgaz; ama 4 blok hala bekliyor. Bunlardan bir tanesi teslim edilecek diye 5 yıldan beri insanlar oyalanıyor' ifadelerini kullandı. 'FAHİŞ AİDATLAR TOPLANIYOR HESAP VERİLMİYOR' Demircioğlu, 'Davada aslında belli bir aşama yok. Çünkü hukuki olarak insanların önünü tamamen kesmişler. Hukuk davaları sonuçsuz kalıyor. Burada biz kalan tek yolun üzerine gittik. Burada örgütlü bir yapı var. Bu örgütlü yapı, sistemli biçimde burayı yavaş yavaş ele geçirmiş. Mağdurların haklarını savunduğunu, kendilerinin atadığını kağıt üzerinde düşündükleri iflas masasının üyeleri, aslında hiçbir şekilde mağdurlarla bağlantılı değiller. Mağdurların bu insanların kim olduğuyla ilgili en ufak bir fikri yok. Bu yüzden biz bu örgütlü yapıyı, örgüt şemasıyla birlikte ortaya koyduk. Mesela burada tapusunu almış ama halen o biten 3 tane blokta oturup şu anda iflas eden ve iflas ettikten sonra bu sistemin başında kontrolsüz biçimde kalan bu şirketin ellerindeler. Yönetim bu şirketin elinde. Fahiş aidatlar toplanıyor, bu aidatların nereye gittiği belli değil, hesap verilmiyor. İçeride yapılan herhangi birşey yok, hizmet yok' diye konuştu. 'AYNI METODLA YUNANİSTAN VE BULGARİSTAN'DA DA PARA ALMIŞLAR' Yurtdışında da mağdurların olduğundan bahseden avukat Demircioğlu, 'Bu firma bunu sadece Türkiye'de de yapmıyor. Aynı firma Bulgaristan'da, Yunanistan'da ve Kıbrıs'ta benzer değil, aynı şekilde, aynı yöntemle, aynı metodla insanların paralarını alıp evlerini teslim etmedi. Buradaki dolandırıcılık vakası, yurt içi ve yurt dışını da işin içerisine kattığımızda 1 milyar doların kesinlikle üzerinde. Ben bütün mağdurlara şunu syledim. Eğer siz bu sözleşmeyi imzaladığınızda işlemin noterden olmasını isteseydiniz ve bugün tapuya şerh koysaydınız bugün anlaştıkları özel bankayla anlaşamayacaklardı. Bu işin patronu halen Türkiye'ye rahat bir şekilde girip çıkabiliyor. Herhangi bir arama, herhangi bir yakalama kararı da henüz mevcut değil. Bu şirketin patronu bu proje başladığında en yüksek emlak satış bedelini emlakçılara vererek burada ciddi bir hareket sağladı. O zaman çok konuşuldu, üzerinde çok tartışıldı. Geldiğimiz noktada bu insanlar bu yükümlülüklerini yerine getirmeyip burada sadece para ödemeye başladıkları için şirket boşta kalan daireleri, bahsettiğimiz özel bankaya ipotekleyerek buradan büyük bir kredi alıyor. Aslında olay biraz da orada başlıyor. Banka tekrar kendi parasını istediğinde, malik olması beklenen insanlardan tapularını alamadığı anda bu sebep gösteriliyor ve bir karışıklık ortaya çıkıyor' dedi. 'İFLAS MASASINI OLUŞTURANLAR ŞİRKETİN ESKİ ÇALIŞANLARI' Demircioğlu, 'Burada iflas ettiğini ortaya koyan şirket, ikinci alacaklılar toplantısını yapıp iki özel bankayla özel bir anlaşma yaparak buradaki mağdurların, hak sahibi olması gereken insanların ellerindeki sözleşmeleri hiçe sayacak bir yola girdiler. İflas masasını birlikte oluşturdular. İflas masasını oluşturan kişiler, bu şahıslar, bu şirketin eski çalışanları. Bu şirketin akrabaları, tanıdıkları. Mağdurların tarafında herhangi bir isim yokken sanki mağdurları temsilen bu masadalarmış gibi bu anlaşmaları yaptılar. Daha sonra da 'Mağdurların sadece sözleşmelerindeki paraları ödeyeceğiz, tapular bizimdir' dediler ve bu tapuları bir hileli ihaleyle aynı özel bankaya teslim ettiler. Bu özel banka da anlaşmanın gereğini yerine getirerek zannediyorum buraların satış hakkını bu iflas eden şirkete verdi. Bu şirket bu daireleri insanlara sattı. Sattığında parasının yarısını bu özel bankanın hesabına, yarısını ise elden aldı. Böyle yüzlerce daire satıldı. Şimdi geldiğimiz bu noktada insanlar çaresiz çünkü iflas masasının yetkileri kullanılıyor. İflas masasını ortaya sürerek, bu yetkileri kullanarak insanları mağdur ettikleri bir ortamdayız' diye konuştu. '4 BLOK HİÇ BİTMEMİŞ' Demircioğlu, 'Toplamda bitmeyen daire sayısı 3 bin. 4 blok hiç bitmemiş. Dış cepheleri yapılmış ama içleri bitmemiş. Tapuları da teslim edilen var, edilmeyen var. Diğer bloklarda tapularını alamayanlar da işin içerisine katıldığında bu rakam 4 binler civarında. Binlerce insan şu anda mağdur. Bu konut içerisinde 4 binden fazla mağdur var ve bu mağduriyetlerin giderilmesi de gerçekten şu anki gidişatla pek mümkün gözükmüyor. Sulh sözleşmesi adı altında, bu insanlar bütün borçlarını ödemiş olmalarına rağmen tapularını almaları gerekirken bize 'Bu bedeli ödeyeceksin' ki bu bedel daire parasına yakın 'Biz daha sonra senin tapunu veririz. Yoksa alacağın para 350-400 bin' diyorlar. Buradaki dolandırıcılık vakası yurt içi ve yurt dışını da işin içine katarsak 1 milyon doların üzerinde.Burada normal bir hileli iflas söz konusu değil. Hileli iflas tek başına büyük bir sorun ve ispatı zor iken burada işin içerisinde örgütlü bir yapı var. Sistemli biçimde, on yıllarca süre içerisinde yavaş bir şekilde bu işi dokumuşlar' dedi. 'ARADAN 10 YIL GEÇTİ DAİREYİ TESLİM ALAMADIK' Projeye 2013 yılında dahil olduğunu anlatan mağdur Ali Talaş, 'Yoldan geçerken bilboardlarda gördüm. Daireyi maketten, ilk topraktan aldım. Hiçbir daire yokken, proje ortada yokken aldık. Bu projeye 2013'te dahil olduk, 2013'te Heybeli Blok'tan aldık. Orada 5. kat, 2F tipi daire aldık. 2015 Aralık'ta teslim etmeleri lazımdı. Aradan 10 yıl geçti, henüz daire ortada yok, teslim alamadık. Bugünkü parayla toplam 415 bin lira bedelle aldık. 2015 Aralık'ta teslim olacaktı. 2015 Aralık teslim olmadığı sürece o günkü parayla kira bedeli ödeyeceklerdi. Ne kira bedeli ne daire hiçbir şey teslim alamadık' diye konuştu. 'EKSTRA 3 MİLYON 600 BİN LİRA TALEP EDİYORLAR' Talaş, '10 yıldır biz hakkımızı arıyoruz. Üstelik bizden ekstra para talep ediyorlar. Bir daire parasından fazla para talep ediyorlar. Bize 'Mahkemede dava verebilirsiniz' dediler. Bu daireyi 415 bin lira bedelle aldık. 415 bin lira bedelle almamıza rağmen, bu parayı ödememize rağmen ekstra bizden 3 milyon 600 bin lira daha talep ediyorlar. Burada mağdur olan sıkıntı çeken benim. Bir de benim dairede 20 metre eksik var, onu da kabullenmiyorlar; çünkü mimarla biz ölçtük. Normalde mağdur olan ben, bu arkadaşlar tekrar ekstra bizden 3 milyon 600 bin lira para istiyorlar. Bu parayı ne diye istiyorlar cevap da vermiyorlar. Firma burada tekrar ekstra bizi üçüncü, dördüncü defa dolandırmaya çalışıyor. Böyle bir hakları yok. Beklentimiz bir an önce bizim tapuların verilmesi, dairelerimizin teslim edilmesidir. En kısa sürede bunun neticelenmesini istiyoruz. 2013'te başka bir firmadan veya başka bir inşaat firmasından bugünkü şartlarda 415 bin liraya bir daire almış olsaydım, bugünkü bu dairenin değeri 25 milyondu. Buradan şu anda biz hukukun çok kısa bir sürede neticelenmesini istiyoruz' dedi. '3 KATI ÜCRET ÖDEYEREK TAPUMUZU ALDIK' Yaşadıkları sorunları anlatan Muhammed Özata ise, 'Emlakçıların öneri ve tavsiyesiyle bu projeyi öğrendik. 2013 yılında projeye dahil olduk. Sedef Blok'ta 2+1 bir adet daire satın aldım. 24 taksitli ödeme planıyla, yaklaşık 240 bin lira civarındaydı ama natamam daireler. Daireyi teslim aldıktan sonra ekstra içini biz kendimiz tamamladık. Daire normalde bizim elimize 2015'te teslim edilecekti. Biz bu arada bütün parayı ödedik. 2019-2020 yıllarında teslim edildi. Tapuyu ilk etapta almadık. Tapunun üzerinde 500-600 tane haciz vardı. 2-3 tane de banka ipoteği vardı. Biz ilk etapta Tüketici Mahkemesi'nde bu ipotekleri ve takyidatları kaldırmak için dava açtık. Akabinde bir sulh süreci oldu. Biz de davamızdan feragat edip ekstra 3 katı tapu ücreti ödeyerek tapumuzu aldık. Burada da açıkçası dolandırıldık, 3 katı tapu masrafı ödedik. Bunun karşılığında da bizden yüksek aidatlar istiyorlar. Net 70 metrekarelerden 10 bin lira civarı bizden aidat istiyorlar. Biz bu konuda da mağduruz. Bize vaat edilen o gerçeklerle, yaşadığımız gerçekler arasında çok ciddi fark var. Sitede hiçbir kalite sözkonusu değildir. Hiçbir temizlik, hiçbir güvenlik sözkonusu değildir. Biz şu anda site yönetiminden ciddi anlamda mağduruz' ifadelerini kullandı.(DHA) Bunlar da ilginizi çekebilir Kağıthane'de</t>
+          <t>Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Borsa İstanbul’da işlem gören Türk İlaç ve Serum Sanayi A.Ş., finansal baskılar nedeniyle konkordato başvurusunda bulundu. Ankara 3. Asliye Ticaret Mahkemesi, 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verdi. KONKORDATO BAŞVURUSUNUN NEDENLERİ Şirket açıklamasında krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin başvurunun temel gerekçeleri olduğu belirtildi. 14 Mayıs 2026’da başlayan kredi geri ödeme gecikmeleri devam ederken 20 Mayıs 2026’da oluşan karşılıksız çek kayıtları da henüz kapatılamadı. KISA VADELİ BORÇ YÜKÜ BASKIYI ARTIRDI Kısa vadede yoğunlaşan yüksek tutarlı çek ödeme yükümlülükleri ile banka kredilerinin ağırlıklı olarak kısa vadeli yapıda olması finansal baskıyı daha da artırdı. 2026’nın ilk çeyreğinde kâr elde edilmesine karşın 2025 yılında oluşan yüksek zararın etkileri sürüyor. ÜRETİM KESİNTİSİZ DEVAM EDECEK Şirket konkordato başvurusunun varlıkların korunması, üretimin kesintisiz sürdürülmesi ve alacaklılar tarafından başlatılabilecek haciz işlemlerinin önüne geçilmesi amacıyla yapıldığını duyurdu. Kamu hizmeti niteliğindeki faaliyetlerin devam ettirilmesi hedefleniyor. YENİDEN YAPILANDIRMA GÖRÜŞMELERİ BAŞLAYACAK Mahkeme kararının ardından başta bankalar olmak üzere tüm alacaklılarla borçların yeniden yapılandırılması için görüşmeler başlatılacak. Nakit akışının düzenlenmesi ve finansman giderlerinin azaltılması için gerekli çalışmalar yürütülecek. Şirket tüm önemli gelişmeleri sermaye piyasası mevzuatı çerçevesinde kamuoyuyla paylaşmaya</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var tele1.com.tr Gündem Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var 03.06.2026 - 10:53 03.06.2026 - 10:53 Canan İLARSLAN- Şevval CİNDİR / İSTANBUL, (DHA)- Esenyurt'ta bir gayrimenkul firması tarafından 2011'de temeli atılan 7 bloktan oluşan yaklaşık 5 bin dairelik konut projesinde iddiaya göre binlerce kişi mağdur oldu. Evlerini teslim alanlar ise, içi tamamlanmamış ve metrekaresi küçük dairelerle karşılaştı. Firma 15 yıl içinde 7 bloktan sadece 3 bloğu tamamladı; yaklaşık 2 bin kişi evlerine kavuşurken aralarında hala tapularını teslim alamayanlar da var. İnşaatı bitmeyen 4 blokta hak sahibi olan 4 binden fazla kişi ise mağdur. Muhammed Özata, tapularını alırken kendilerinden bir daire bedeli kadar para istendiğini söyleyerek, '2019-2020 yıllarında teslim edildi. Tapuyu ilk etapta almadık. Tapunun üzerinde 500-600 tane haciz vardı. Biz ilk etapta Tüketici Mahkemesi'nde bu ipotekleri ve takyidatları kaldırmak için dava açtık. Akabinde bir sulh süreci oldu. Biz de davamızdan feragat edip ekstra 3 katı tapu ücreti ödeyerek, biz tapumuzu aldık. Burada da açıkçası dolandırıldık, 3 katı tapu masrafı ödedik' dedi. Mağdurlar konuyu yargıya taşırken Büyükçekmece Cumhuriyet Başsavcılığı tarafından yürütülen soruşturmanın sürdüğü öğrenildi. Avukat Mehmet Demircioğlu firmanın aynı metodu yurt dışında da kullandığını belirterek, 'Daire büyüklüklerine göre 1 milyon liradan aşağı olmamak üzere 4, 5, 6 milyon liralara varan 'Gel daireni tekrar satın al' dedirten bir zorlamayla karşı karşıyayız. Toplamda 7 blokluk bir proje burası. Esenyurt'ta 2010'da satışına başlanan temeli 2011'de atılan konut projesinde hak sahiplerine daireleri 2015 Aralık ayında teslim edilecekti. Firma daireleri teslim etmediği gibi tapularını almak isteyenlerden de bir daire bedeli kadar para istedi. Mağdurların şikayeti üzerine açılan davalar yaklaşık 13 yıldır sürerken, Büyükçekmece Cumhuriyet Başsavcılığı tarafından örgütlü suçlar kapsamında soruşturma başlatıldı. Site yönetimine ilişkin iddiaların konu edildiği hukuk davası devam ederken, yönetimin yaklaşık 10 yıldır genel kurul yapmadan faaliyette olduğu, yüksek aidatlar topladığı iddia edildi. Binlerce kişinin şikayetçi olduğu, yurtdışından da binin üzerinde kişinin daire satın alarak mağdur olduğu olayda, ticari dükkan sahiplerinden da tapusunu alamayanlar olduğu öğrenildi. Şirket 2021 yılında iflasını ilan etti. 2022 yılında ise ikinci alacaklılar toplantısında iflas masası oluşturuldu. 'BİNLERCE MAĞDUR; BİTİRİLMEYEN BİR İNŞAAT VAR' Projede yıllardır çözülemeyen bir mağduriyet yaşandığını belirten avukat Mehmet Demircioğlu, 'Burada 13 yıldan beri devam eden bir mağduriyet vakası var. Yüzlerce, hatta yurt dışındaki mağdurlarla birlikte binlerce mağdur var. Bitmeyen bir inşaat var, bitirilmeyen bir inşaat var. Biz burada mağdurların avukatları olarak birçok defa kendilerinden bilgi, belge istememize rağmen şirket hiçbir şekilde uzlaşmıyor. Sebebine gelince; burada hileli biçimde oluşturulmuş bir iflas düzeneği var. İflas masası şirketin eski çalışanları ve tanıdıklarından oluşturulmuş. Bir özel bankayla da anlaşarak bu iflas masasını oluşturdukları için elleri çok güçlü. Şu anda bütün borcunu ödemiş ve malik olması gerekirken kendi hakkı olan tapuyu tekrar bedeline yakın bir para istenilerek, buna da 'Sulh sözleşmesi' ile bir kılıf bulunarak insanların mağdur edildiği bir faciayla karşı karşıyayız' dedi. 'İNSANLARA HAKKI OLAN TAPU TEKRAR PARAYLA SATILMAK İSTENİYOR' Hak sahiplerinin tüm yükümlülüklerini yerine getirmelerine rağmen yeni ödeme talepleriyle karşı karşıya kaldığını belirten Demircioğlu, 'Farklı daire tipleri için farklı fiyatlar öngörmüşler. En küçük daire olan 1+1 daire için bile bugün güncel değerinin çok daha altında seyrediyor, 2,5 milyona bile satılamıyor. Olması gerekenin çok altında bir rakam bu. Burada bile insanlardan milyon liranın üzerinde para talep ediliyor ve insanlara hakkı olan tapu, tekrar parayla satılmak isteniyor. Burada bunu iflas masasının yetkisine dayanarak yapıyorlar. İflas masasını oluşturanlar yine kendileri. Daire büyüklüklerine göre 1 milyon liradan aşağı olmamak üzere 4, 5, 6 milyon liralara varan, adama 'Gel, daireni tekrar satın al' dedirten bir zorlamayla karşı karşıyayız. 'FAHİŞ AİDATLAR TOPLANIYOR HESAP VERİLMİYOR' Demircioğlu, 'Davada aslında belli bir aşama yok. Bu örgütlü yapı, sistemli biçimde burayı yavaş yavaş ele geçirmiş. Mağdurların haklarını savunduğunu, kendilerinin atadığını kağıt üzerinde düşündükleri iflas masasının üyeleri, aslında hiçbir şekilde mağdurlarla bağlantılı değiller. Bu yüzden biz bu örgütlü yapıyı, örgüt şemasıyla birlikte ortaya koyduk. Mesela burada tapusunu almış ama halen o biten 3 tane blokta oturup şu anda iflas eden ve iflas ettikten sonra bu sistemin başında kontrolsüz biçimde kalan bu şirketin ellerindeler. Yönetim bu şirketin elinde. 'AYNI METODLA YUNANİSTAN VE BULGARİSTAN'DA DA PARA ALMIŞLAR' Yurtdışında da mağdurların olduğundan bahseden avukat Demircioğlu, 'Bu firma bunu sadece Türkiye'de de yapmıyor. Aynı firma Bulgaristan'da, Yunanistan'da ve Kıbrıs'ta benzer değil, aynı şekilde, aynı yöntemle, aynı metodla insanların paralarını alıp evlerini teslim etmedi. Buradaki dolandırıcılık vakası, yurt içi ve yurt dışını da işin içerisine kattığımızda 1 milyar doların kesinlikle üzerinde. Ben bütün mağdurlara şunu syledim. Eğer siz bu sözleşmeyi imzaladığınızda işlemin noterden olmasını isteseydiniz ve bugün tapuya şerh koysaydınız bugün anlaştıkları özel bankayla anlaşamayacaklardı. Bu şirketin patronu bu proje başladığında en yüksek emlak satış bedelini emlakçılara vererek burada ciddi bir hareket sağladı. Geldiğimiz noktada bu insanlar bu yükümlülüklerini yerine getirmeyip burada sadece para ödemeye başladıkları için şirket boşta kalan daireleri, bahsettiğimiz özel bankaya ipotekleyerek buradan büyük bir kredi alıyor. Aslında olay biraz da orada başlıyor. 'İFLAS MASASINI OLUŞTURANLAR ŞİRKETİN ESKİ ÇALIŞANLARI' Demircioğlu, 'Burada iflas ettiğini ortaya koyan şirket, ikinci alacaklılar toplantısını yapıp iki özel bankayla özel bir anlaşma yaparak buradaki mağdurların, hak sahibi olması gereken insanların ellerindeki sözleşmeleri hiçe sayacak bir yola girdiler. İflas masasını birlikte oluşturdular. İflas masasını oluşturan kişiler, bu şahıslar, bu şirketin eski çalışanları. Bu şirketin akrabaları, tanıdıkları. Mağdurların tarafında herhangi bir isim yokken sanki mağdurları temsilen bu masadalarmış gibi bu anlaşmaları yaptılar. Bu özel banka da anlaşmanın gereğini yerine getirerek zannediyorum buraların satış hakkını bu iflas eden şirkete verdi. Bu şirket bu daireleri insanlara sattı. Şimdi geldiğimiz bu noktada insanlar çaresiz çünkü iflas masasının yetkileri kullanılıyor. İflas masasını ortaya sürerek, bu yetkileri kullanarak insanları mağdur ettikleri bir ortamdayız' diye konuştu. Binlerce insan şu anda mağdur. Bu konut içerisinde 4 binden fazla mağdur var ve bu mağduriyetlerin giderilmesi de gerçekten şu anki gidişatla pek mümkün gözükmüyor. Sulh sözleşmesi adı altında, bu insanlar bütün borçlarını ödemiş olmalarına rağmen tapularını almaları gerekirken bize 'Bu bedeli ödeyeceksin' ki bu bedel daire parasına yakın 'Biz daha sonra senin tapunu veririz. Buradaki dolandırıcılık vakası yurt içi ve yurt dışını da işin içine katarsak 1 milyon doların üzerinde.Burada normal bir hileli iflas söz konusu değil. Hileli iflas tek başına büyük bir sorun ve ispatı zor iken burada işin içerisinde örgütlü bir yapı var. Sistemli biçimde, on yıllarca süre içerisinde yavaş bir şekilde bu işi dokumuşlar' dedi. 'ARADAN 10 YIL GEÇTİ DAİREYİ TESLİM ALAMADIK' Projeye 2013 yılında dahil olduğunu anlatan mağdur Ali Talaş, 'Yoldan geçerken bilboardlarda gördüm. 'EKSTRA 3 MİLYON 600 BİN LİRA TALEP EDİYORLAR' Talaş, '10 yıldır biz hakkımızı arıyoruz. Bir daire parasından fazla para talep ediyorlar. Burada mağdur olan sıkıntı çeken benim. Normalde mağdur olan ben, bu arkadaşlar tekrar ekstra bizden 3 milyon 600 bin lira para istiyorlar. Firma burada tekrar ekstra bizi üçüncü, dördüncü defa dolandırmaya çalışıyor. En kısa sürede bunun neticelenmesini istiyoruz. 2013'te başka bir firmadan veya başka bir inşaat firmasından bugünkü şartlarda 415 bin liraya bir daire almış olsaydım, bugünkü bu dairenin değeri 25 milyondu. '3 KATI ÜCRET ÖDEYEREK TAPUMUZU ALDIK' Yaşadıkları sorunları anlatan Muhammed Özata ise, 'Emlakçıların öneri ve tavsiyesiyle bu projeyi öğrendik. 24 taksitli ödeme planıyla, yaklaşık 240 bin lira civarındaydı ama natamam daireler. Burada da açıkçası dolandırıldık, 3 katı tapu masrafı ödedik. Bize vaat edilen o gerçeklerle, yaşadığımız gerçekler arasında çok ciddi fark var.</t>
+          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı Samanyolu Haber Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Borsa İstanbul’da işlem gören Türk İlaç ve Serum Sanayi A.Ş., finansal baskılar nedeniyle konkordato başvurusunda bulundu. Asliye Ticaret Mahkemesi, 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verdi. KONKORDATO BAŞVURUSUNUN NEDENLERİ Şirket açıklamasında krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin başvurunun temel gerekçeleri olduğu belirtildi. 14 Mayıs 2026’da başlayan kredi geri ödeme gecikmeleri devam ederken 20 Mayıs 2026’da oluşan karşılıksız çek kayıtları da henüz kapatılamadı. KISA VADELİ BORÇ YÜKÜ BASKIYI ARTIRDI Kısa vadede yoğunlaşan yüksek tutarlı çek ödeme yükümlülükleri ile banka kredilerinin ağırlıklı olarak kısa vadeli yapıda olması finansal baskıyı daha da artırdı. 2026’nın ilk çeyreğinde kâr elde edilmesine karşın 2025 yılında oluşan yüksek zararın etkileri sürüyor. ÜRETİM KESİNTİSİZ DEVAM EDECEK Şirket konkordato başvurusunun varlıkların korunması, üretimin kesintisiz sürdürülmesi ve alacaklılar tarafından başlatılabilecek haciz işlemlerinin önüne geçilmesi amacıyla yapıldığını duyurdu. Kamu hizmeti niteliğindeki faaliyetlerin devam ettirilmesi hedefleniyor. YENİDEN YAPILANDIRMA GÖRÜŞMELERİ BAŞLAYACAK Mahkeme kararının ardından başta bankalar olmak üzere tüm alacaklılarla borçların yeniden yapılandırılması için görüşmeler başlatılacak. Nakit akışının düzenlenmesi ve finansman giderlerinin azaltılması için gerekli çalışmalar yürütülecek. Şirket tüm önemli gelişmeleri sermaye piyasası mevzuatı çerçevesinde kamuoyuyla paylaşmaya</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQVE40YW9MVHpyS1pEOG8tWUNtaGZtT1VidFdjYmFHZHFObnVaVzlBWU1HRlU5RG1ZMXhDcjJpdXc0ZkxMcmZIUWlOeDBIaS1xel9ETmZxU0Rsck1EMVFVbXk0UVBHR09UTms4ak5BaXhiczQ2WVRIcGZjSGVhaDlndDlSQ2JjcTlvcTMzLV90MEFUV2FoZjZSYWhoNmJXNFV2bEd0Nk9HNS1pSDR1TkNUMEM3QkxCM01IaUtV0gG7AUFVX3lxTFBUTjRhb0xUenJLWkQ4by1ZQ21oZm1PVWJ0V2NiYUdkcU5udVpXOUFZTUdGVTlEbVkxeENyMml1dzRmTExyZkhRaU54MEhpLXF6X0ROZnFTRGxyTUQxUVVteTRRUEdHT1ROazhqTkFpeGJzNDZZVEhwZmNIZWFoOWd0OVJDYmNxOW9xMzMtX3QwQVRXYWhmNlJhaGg2Ylc0VXZsR3Q2T0c1LWlINHVOQ1QwQzdCTEIzTUhpS1U?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.samanyoluhaber.com/borsa-sirketi-konkordatoya-basvurdu-ilac-sektoru-sarsildi/1488760</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -5642,11 +5658,7 @@
           <t>İstanbul</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Esenyurt</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -5654,7 +5666,7 @@
       <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr"/>
@@ -5668,7 +5680,7 @@
       <c r="Y33" s="2" t="inlineStr"/>
       <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" s="2" t="n">
-        <v>131.25</v>
+        <v>80.5</v>
       </c>
       <c r="AB33" s="2" t="n">
         <v>32</v>
@@ -5677,27 +5689,27 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 12:14:00</t>
+          <t>2026-06-03 15:49:03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>tasfiye</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>60 milyarlık dolandırıcılık ağına operasyon: 4 şirkete kayyum atandı</t>
+          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>60 milyarlık dolandırıcılık ağına operasyon: 4 şirkete kayyum atandı Ortadoğu Gazetesi</t>
+          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5717,42 +5729,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğü ekipleri, Anadolu Cumhuriyet Başsavcılığı koordinesinde yürütülen soruşturma kapsamında büyük bir operasyona imza attı. İstanbul merkezli 27 ilde eş zamanlı gerçekleştirilen baskınlarda 89 şüpheli gözaltına alındı. Sahte yatırım grupları kurdukları öne sürüldü Soruşturma kapsamında şüphelilerin, banka ve finans kuruluşlarının isimlerini kullanarak dijital platformlarda sahte yatırım grupları oluşturduğu belirlendi. Zanlıların, yatırım danışmanı ve uzman görüntüsü vererek çok sayıda kişiyi dolandırdığı iddia edildi. 60 milyar liralık işlem hacmi tespit edildi Yapılan incelemelerde şüphelilere ait kişisel ve şirket hesaplarında yaklaşık 60 milyar liralık işlem hacmi bulunduğu ortaya çıktı. Mali hareketlerin detaylı şekilde incelenmesi üzerine operasyon kararı alındığı bildirildi. 4 şirkete kayyum atandı Soruşturma kapsamında suçtan elde edildiği değerlendirilen mal varlıklarına yönelik tedbirler de uygulandı. Toplam değeri 4 milyar 606 milyon lira olarak hesaplanan 4 şirkete kayyum atanırken, 15 akaryakıt istasyonu ile bir akaryakıt ve LPG dolum tesisi de kayyum yönetimine devredildi. Mal varlıklarına el konuldu Operasyon kapsamında bir taşınmaz, 11 araç, şirket ortaklık payları, banka hesapları ve kripto varlıklara yönelik bloke işlemleri gerçekleştirildi. Yetkililer, suç gelirlerinin tespit edilmesine yönelik mali incelemelerin sürdüğünü belirtti. Soruşturma çok yönlü devam ediyor Gözaltına alınan şüphelilerin emniyetteki işlemleri sürerken, soruşturmanın yeni gözaltılar ve mali incelemelerle genişleyebileceği ifade edildi. Yetkililer, dijital platformlar üzerinden gerçekleştirilen dolandırıcılık faaliyetlerine karşı vatandaşların dikkatli olması gerektiğini vurguladı. İstanbul Parçalı az bulutlu 23° Adana Adıyaman Afyonkarahisar Ağrı Amasya Ankara Antalya Artvin Aydın Balıkesir Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Isparta Mersin İstanbul İzmir Kars Kastamonu Kayseri Kırklareli Kırşehir Kocaeli Konya Kütahya Malatya Manisa Kahramanmaraş Mardin Muğla Muş Nevşehir Niğde Ordu Rize Sakarya Samsun Siirt Sinop Sivas Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yozgat Zonguldak Aksaray Bayburt Karaman Kırıkkale Batman Şırnak Bartın Ardahan Iğdır Yalova Karabük Kilis Osmaniye Düzce Emine Koç Genel Yayın Yönetmeni Ortadoğu Gazetesi artık WhatsApp’ta! Gündemin en önemli gelişmeleri anında cebinize gelsin istiyorsanız tıklayın ve katılın. Payla</t>
+          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>60 milyarlık dolandırıcılık ağına operasyon: 4 şirkete kayyum atandı 60 milyarlık dolandırıcılık ağına operasyon: 4 şirkete kayyum atandı Ortadoğu Gazetesi İstanbul Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğü ekipleri, Anadolu Cumhuriyet Başsavcılığı koordinesinde yürütülen soruşturma kapsamında büyük bir operasyona imza attı. İstanbul merkezli 27 ilde eş zamanlı gerçekleştirilen baskınlarda 89 şüpheli gözaltına alındı. Sahte yatırım grupları kurdukları öne sürüldü Soruşturma kapsamında şüphelilerin, banka ve finans kuruluşlarının isimlerini kullanarak dijital platformlarda sahte yatırım grupları oluşturduğu belirlendi. Zanlıların, yatırım danışmanı ve uzman görüntüsü vererek çok sayıda kişiyi dolandırdığı iddia edildi. 60 milyar liralık işlem hacmi tespit edildi Yapılan incelemelerde şüphelilere ait kişisel ve şirket hesaplarında yaklaşık 60 milyar liralık işlem hacmi bulunduğu ortaya çıktı. Mali hareketlerin detaylı şekilde incelenmesi üzerine operasyon kararı alındığı bildirildi. 4 şirkete kayyum atandı Soruşturma kapsamında suçtan elde edildiği değerlendirilen mal varlıklarına yönelik tedbirler de uygulandı. Toplam değeri 4 milyar 606 milyon lira olarak hesaplanan 4 şirkete kayyum atanırken, 15 akaryakıt istasyonu ile bir akaryakıt ve LPG dolum tesisi de kayyum yönetimine devredildi. Mal varlıklarına el konuldu Operasyon kapsamında bir taşınmaz, 11 araç, şirket ortaklık payları, banka hesapları ve kripto varlıklara yönelik bloke işlemleri gerçekleştirildi. Yetkililer, suç gelirlerinin tespit edilmesine yönelik mali incelemelerin sürdüğünü belirtti. Soruşturma çok yönlü devam ediyor Gözaltına alınan şüphelilerin emniyetteki işlemleri sürerken, soruşturmanın yeni gözaltılar ve mali incelemelerle genişleyebileceği ifade edildi. Yetkililer, dijital platformlar üzerinden gerçekleştirilen dolandırıcılık faaliyetlerine karşı vatandaşların dikkatli olması gerektiğini vurguladı. İstanbul Parçalı az bulutlu 23° Adana Adıyaman Afyonkarahisar Ağrı Amasya Ankara Antalya Artvin Aydın Balıkesir Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Isparta Mersin İstanbul İzmir Kars Kastamonu Kayseri Kırklareli Kırşehir Kocaeli Konya Kütahya Malatya Manisa Kahramanmaraş Mardin Muğla Muş Nevşehir Niğde Ordu Rize Sakarya Samsun Siirt Sinop Sivas Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yozgat Zonguldak Aksaray Bayburt Karaman Kırıkkale Batman Şırnak Bartın Ardahan Iğdır Yalova Karabük Kilis Osmaniye Düzce Emine Koç Genel Yayın Yönetmeni Ortadoğu Gazetesi artık WhatsApp’ta!</t>
+          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNTWxRRTFyUUlnZjVoSmVuUUg3VmY5emhZWjhweEtPYW9OWG4xNWlkSjFkUGdiam01X3MxZk9YV0FROW1UYWZvS054d2hHaTNqZmctV2pVZVZESDNiUHJCaGowSVpqR0dMUGZhWXZCM3Zjek11cFJ6LWYxOGFWemZSYW8zUmZCRzNueF9DcE9HY1dKcFlzbEU4UHF6Vk5QeExKcVZXbk9CWFhNaC0ycS1fXzdSUVI?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOS19FeHZ4UlU4WUdxQnk1WjRUWFBIcS1HenVpdmNJd2Jkd1lreWdNNVplbm1hN3RtRlo3cWdtWk5Zb2tfcG5iZ0Y3RGJkbFAwcy1aMXlmVjhrQnA4Nkh5VTNzZ3EyMHZBNkJ5MzI4V2lxQXFIdWRVWUlJWTlZVmZYbkNSa2FXMzZjNHVIUml0WkUydnM0TThOT2tjNlhlZw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>LPG dolum tesisi | 15 akaryakıt istasyonu</t>
-        </is>
-      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr"/>
@@ -5766,7 +5770,7 @@
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="n">
-        <v>120.5</v>
+        <v>65.06</v>
       </c>
       <c r="AB34" s="2" t="n">
         <v>33</v>
@@ -5775,27 +5779,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 14:54:00</t>
+          <t>2026-06-04 06:39:17</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>örgütlü suç</t>
+          <t>usulsüzlük</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Yargıda rüşvet iddiası : HSK, Hakim Mustafa Ece'yi görevden uzaklaştırdı</t>
+          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Yargıda rüşvet iddiası : HSK, Hakim Mustafa Ece'yi görevden uzaklaştırdı İşçi Haber</t>
+          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -5805,18 +5809,22 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>gıda</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Yargıda rüşvet iddiası : HSK, Hakim Mustafa Ece'yi görevden uzaklaştırdı İşçi Haber</t>
+          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Yargıda rüşvet iddiası : HSK, Hakim Mustafa Ece'yi görevden uzaklaştırdı Yargıda rüşvet iddiası : HSK, Hakim Mustafa Ece'yi görevden uzaklaştırdı İşçi Haber Yargıda rüşvet iddiası : HSK, Hakim Mustafa Ece'yi görevden uzaklaştırdı İşçi Haber</t>
+          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5826,7 +5834,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQOGU5ZEgwV3V4X2ZwZ2JNcEIwYVRXREtXM09Md2lKeFdXanFxMW8zZ2ZpUzNpdEJSWTh1RnQtZVhXTFp4VFFQazBHbXZITzR3TDFHVUZaakNMYjI2YmoyMUNaTUgxOFNuRHpvT3h0ME45YXNBQ1lScmdyU3NnSDhwczhCREdIU3gyQXZrS0FxWm9CYXBhNzlHSklqVFRRd1k0YnFWX284bzhnS1p0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQUlliVENTZ19BSUlYSmtXak83b2xMbkt0N0ZmSkhyVW1fdjZhRy1OU1ZWZ243MmtHNkYxekdDeUtBLXVTb2MzSTVHVzRvdnc2di1xdFM5X2JOa3FyeGtSOW1pdHBNN0FuUEc5TURram8xblI0Uk5jNEQ4eDQ4V0EzOGJRYU5wVXNYWUFPQ3dZV25RLTBtTGxkcDRvNVNKOU02SFozdjhWT2tHc1pwd1RhTFJoWmZDUU1rNFE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
@@ -5852,7 +5860,7 @@
       <c r="Y35" s="2" t="inlineStr"/>
       <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" s="2" t="n">
-        <v>73.58</v>
+        <v>83.66</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>34</v>
@@ -5861,27 +5869,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 14:33:00</t>
+          <t>2026-06-03 09:28:00</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>şirketlere operasyon</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'de sahte çek şoku: Bankada gerçek ortaya çıktı</t>
+          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'de sahte çek şoku: Bankada gerçek ortaya çıktı Yıldırım Gazetesi</t>
+          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı Cumhuriyet</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5891,22 +5899,22 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>firma, şirket</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Bursa'nın İnegöl ilçesinde sattığı arsanın karşılığında aldığı 3,5 milyon liralık çekle bankaya giden vatandaş, hayatının şokunu yaşadı. Bankada yapılan incelemede çekin sahte olduğu ortaya çıktı. Bursa'nın İnegöl ilçesinde sattığı arsanın karşılığında aldığı 3,5 milyon liralık çekle bankaya giden vatandaş, hayatının şokunu yaşadı. Bankada yapılan incelemede çekin sahte olduğu ortaya çıktı. Bursa'nın İnegöl ilçesinde sattığı arsanın karşılığında aldığı 3,5 milyon liralık çekle bankaya giden vatandaş, hayatının şokunu yaşadı. Bankada yapılan incelemede çekin sahte olduğu ortaya çıktı.</t>
+          <t>Schengen vizesi başvurularında randevuların bot yazılımlarla kapatılıp ticari amaçla satıldığı iddiaları TBMM gündemine taşındı. Ticaret Bakanı Ömer Bolat, gelen şikayetler üzerine Reklam Kurulu'nun 7 şirket hakkında inceleme başlattığını açıkladı. Schengen vizesi başvurularında randevuların bot yazılımlarla kapatılıp ticari amaçla satıldığı iddiaları TBMM gündemine taşındı. Ticaret Bakanı Ömer Bolat, gelen şikayetler üzerine Reklam Kurulu'nun 7 şirket hakkında inceleme başlattığını açıkladı. Schengen vizesi başvurularında randevuların bot yazılımlarla kapatılıp ticari amaçla satıldığı iddiaları TBMM gündemine taşındı. Ticaret Bakanı Ömer Bolat, gelen şikayetler üzerine Reklam Kurulu'nun 7 şirket hakkında inceleme başlattığını açıkladı.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'de sahte çek şoku: Bankada gerçek ortaya çıktı İnegöl'de sahte çek şoku: Bankada gerçek ortaya çıktı Yıldırım Gazetesi Bursa'nın İnegöl ilçesinde sattığı arsanın karşılığında aldığı 3,5 milyon liralık çekle bankaya giden vatandaş, hayatının şokunu yaşadı. Bankada yapılan incelemede çekin sahte olduğu ortaya çıktı.</t>
+          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı Cumhuriyet Schengen vizesi başvurularında randevuların bot yazılımlarla kapatılıp ticari amaçla satıldığı iddiaları TBMM gündemine taşındı. Ticaret Bakanı Ömer Bolat, gelen şikayetler üzerine Reklam Kurulu'nun 7 şirket hakkında inceleme başlattığını açıkladı.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -5916,19 +5924,11 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.yildirimgazetesi.com/inegolde-sahte-cek-soku-bankada-gercek-ortaya-cikti</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl</t>
-        </is>
-      </c>
+          <t>https://www.cumhuriyet.com.tr/ekonomi/schengen-vizesinde-randevu-satan-sirketlere-sorusturma-7-firma-mercek-altina-alindi-2508910</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
       <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr"/>
@@ -5950,7 +5950,7 @@
       <c r="Y36" s="2" t="inlineStr"/>
       <c r="Z36" s="2" t="inlineStr"/>
       <c r="AA36" s="2" t="n">
-        <v>76.15000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="AB36" s="2" t="n">
         <v>35</v>
@@ -5959,27 +5959,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:29:46</t>
+          <t>2026-06-03 16:43:00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>banka dolandırıcılığı</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>27 ilde yatırım dolandırıcılığı operasyonu: 89 gözaltı, 4 şirket ve 15 akaryakıt istasyonuna kayyım</t>
+          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>27 ilde yatırım dolandırıcılığı operasyonu: 89 gözaltı, 4 şirket ve 15 akaryakıt istasyonuna kayyım Gaziantep Sabah Gazetesi</t>
+          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5989,22 +5989,22 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>akaryakıt istasyonu, istasyon, şirket</t>
+          <t>fabrika, organize sanayi, sanayi</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>akaryakıt tesisi | şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27 ilde yatırım dolandırıcılığı operasyonu: 89 gözaltı, 4 şirket ve 15 akaryakıt istasyonuna kayyım Gaziantep Sabah Gazetesi</t>
+          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>27 ilde yatırım dolandırıcılığı operasyonu: 89 gözaltı, 4 şirket ve 15 akaryakıt istasyonuna kayyım 27 ilde yatırım dolandırıcılığı operasyonu: 89 gözaltı, 4 şirket ve 15 akaryakıt istasyonuna kayyım Gaziantep Sabah Gazetesi 27 ilde yatırım dolandırıcılığı operasyonu: 89 gözaltı, 4 şirket ve 15 akaryakıt istasyonuna kayyım Gaziantep Sabah Gazetesi</t>
+          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -6014,33 +6014,65 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPM00tdl83NzFTTnI2aFpoaWNsOTF0MXMyNUNSeDdKQ2w5WjJYbmF1REJaWDBCUVJoVmtKY3M1ZzR5S2l3clVLV24yU292a0ZpNktIZHRzRTFtMGcyNmNqeEJKWGZIRHlTcTYtT24wX1pZZGozZ3lUUkZMVndvZmNGdklJeEh4OXRXdE12LXc5YTQyVW5fOUR2ejZycU9UYlY5bUhPWGROUEk0WUFjZjM5c0FjMHZPVEFJdldEd2xnVXo0ang0R0MxTnUyc19BNlc3Z3lGMw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxORHRmYXNUalRQUXNLOHhTS2xRRm02MmVBZGZ6QnpSN3g0TGRJRGo2cXZFaUtmVjFESUgtZVc3S3VseHR2ZEdjUmg3Wm54MzhsMVJEQW1NT2NwN25tcURsYXByRUtZWmNyTlZKSkRKZDFWX09MZThDcl9yQWwtQnhEUFBkcEJkWG9ENlHSAY8BQVVfeXFMUGMycjBkQVY5a0lhb2k0a19oMWoyTWN0YTB3T2I4Y3U3N3JmdGVXaHRTN3BJMkVsdUZGTEp4V21lMFFRZUx1LWxuUXBYT0k1VGVTb3pESUUyVHM1U0xZY2g5RlVfcTA2UUltNXVlWmdWc3VvNXkyMGR2SGs0VVVMNDJjTlNPQ1FpSE9ybkh6ZVU?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Bitlis</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>te Organize Sanayi</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Organize Sanayi:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr"/>
-      <c r="V37" s="2" t="inlineStr"/>
-      <c r="W37" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>Organize Sanayi te Organize Sanayi Bitlis Türkiye</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Bitlis Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Bitlis Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y37" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="n">
-        <v>97.73999999999999</v>
+        <v>190.42</v>
       </c>
       <c r="AB37" s="2" t="n">
         <v>36</v>
@@ -6049,12 +6081,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:45:00</t>
+          <t>2026-06-03 22:06:29</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>banka hesapları bloke</t>
+          <t>bankaya soruşturma</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -6064,12 +6096,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: Bütün hesapları donduruldu</t>
+          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: Bütün hesapları donduruldu Ekonomim</t>
+          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Vietnam.vn</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -6079,7 +6111,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -6089,12 +6121,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: Bütün hesapları donduruldu Ekonomim</t>
+          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Vietnam.vn</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabına 1 trilyon TL yattı: Bütün hesapları donduruldu Banka hesabına 1 trilyon TL yattı: Bütün hesapları donduruldu Ekonomim Banka hesabına 1 trilyon TL yattı: Bütün hesapları donduruldu Ekonomim</t>
+          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Vietnam.vn Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -6104,7 +6136,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxONUo5X2dydDhjTmM3enhwTUJ0c0xGaFdhNjdhbTZDcnRHSERrdGN1MXNndWVUS2p2SzRjcnFkLVZZbHRVZVhJcmVBcFlyMHczdU5PRVVBM3gxZEhvb2lZSDNsaVdpVFN4UUpxNzRPNU0tWl9RNFVxUjAxMWdFWVo1ZzlkSVdHb3NnVTdfQkVvaTNpMlpEcmRzRThRZHRsdUtjVE91elhQUGM1UdIBrwFBVV95cUxNdFFxMFBfcmlZd0xLMUpIbWJRdFQwUWFld2M4S0E2VDRERlc5UG0xWGJ4dDVqZUdBOGV1U2Vycklxd2JJa0FObWI3V094ekg1MVBlZlFtWGNNZHVwSW9aM2VxUVJwc3BUMjRjdGVvU2l4ZTNEVWlfbHlBaXhHVG9hWnphWmtiY3R2NXh1S3N4V3RWS3YwRVpOVVpOSlRRLWZkM0dfUEJkd282WUo1NDNj?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBENG9hNkpudTZwY2E2MGRhQWRucXFnSWF5VzViQUo0Z3FpZ0F4aVRnR0hmc1ZUWG1wdG5QMy1wVnZELWpXUFdDdXdkaS1qNlVkc29jQmlWaThMN0ViMWFiM0FlTVM5UlB1VnlHMmNnazZvNkh5UFFTOGVKOXFVdw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
@@ -6130,7 +6162,7 @@
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="AB38" s="2" t="n">
         <v>37</v>
@@ -6139,27 +6171,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:53:00</t>
+          <t>2026-06-03 11:32:00</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>hesaplara bloke</t>
+          <t>banka dolandırıcılığı</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Jahangar Takalo Kimdir? Banka Hesabında 1 Trilyon TL Görünen Şaşırtan Olay Gündem Oldu</t>
+          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Jahangar Takalo Kimdir? Banka Hesabında 1 Trilyon TL Görünen Şaşırtan Olay Gündem Oldu Uyan 32</t>
+          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek sonhaber.eu</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6169,7 +6201,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -6179,12 +6211,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Van’da yaşayan Azerbaycan asıllı Ahmad Jahangar Takalo, banka hesabında ortaya çıkan olağan dışı bakiye nedeniyle Türkiye gündemine oturdu. İddiaya göre market alışverişi sırasında kartının hata vermesiyle başlayan süreç, bankada yapılan kontrol sonrası milyonları değil, milyarları aşan bir hesap bakiyesinin görülmesiyle bambaşka bir boyuta ulaştı. Hesapta görülen rakam şok etkisi yarattı Bankada yapılan incelemede, hesabında 999 milyar TL’yi aşan bir bakiye olduğu görüldü. Bu durum hem banka çalışanlarını hem de hesap sahibini şaşkına çevirdi. Kaynağı henüz açıklanmayan tutar nedeniyle hesaplara güvenlik amaçlı bloke uygulandığı öne sürüldü. “Hata mı, sistem açığı mı?” sorusu gündemde Olayın ardından en çok merak edilen konu, bu devasa tutarın hesaba nasıl geçtiği oldu. Uzman olmayan kullanıcılar arasında “sistem hatası”, “veri kayması” veya “yanlış işlem” ihtimalleri konuşulurken, resmi açıklama yapılmadı. Hesaplara erişim kısıtlandı İddialara göre, bankanın inceleme süreci başlatmasının ardından Takalo’nun tüm hesaplarına geçici blokeler konuldu. Bu nedenle hem görünen yüksek tutara hem de kendi normal bakiyesine erişemediği belirtildi. Sosyal medyada viral oldu Kısa sürede sosyal medyada yayılan olay, “1 trilyon TL gerçekten yatmış olabilir mi?” sorusunu gündeme taşıdı. Kullanıcılar arasında hem esprili yo</t>
+          <t>Belçika’da dolandırıcıların hedefi haline gelen ve phishing (oltalama) mağduru olan kişiler için emsal bir karar alındı. Antwerp Mahkemesi, phishing dolandırıcılığına uğrayan müşterilerin zararlarının bankalar tarafından gecikmeden karşılanması gerektiğine hükmetti. Belçika’nın Antwerp kentinde hızlı yargılama usulüyle görülen davada mahkeme, phishing (oltalama) dolandırıcılığı mağdurlarının zararlarının bankalar tarafından öncelikle karşılanması gerektiğine karar verdi. Karar, yaklaşık 50 bin euro dolandırılan yaşlı bir çiftin açtığı dava sonucunda alındı. Banka’dan ağır ihmal değerlendirmesi Olayda çift, kendisini banka çalışanı olarak tanıtan bir dolandırıcının yönlendirmesiyle Portekiz’deki bir hesaba para transferi yaptı. Banka ise müşterilerin parayı kendi rızalarıyla göndermesini “ağır ihmal” olarak değerlendirerek zararı karşılamayı reddetti. Mahkeme bankanın bu yaklaşımını kabul etmedi. Karara göre bankalar, phishing mağdurlarının zararını derhal ödemekle yükümlü olacak. Banka, müşterinin ağır ihmalde bulunduğunu düşünüyorsa bunu kanıtlamak için kendisi tekrar mahkemeye başvurmak ve bunu kanıtlamak zorunda olacak. Phishing (oltalama) nedir? Phishing, dolandırıcıların banka, resmi kurum veya güvenilir bir kuruluş gibi davranarak kişilerin şifre, banka bilgisi veya güvenlik kodlarını ele geçirmeye çalıştığı bir siber dolandırıcılık yöntemidir. Bankacılık sektöründe çığır açan karar Bankacılık hukuku uzmanı Avukat Geert Lenssens, kararı “çığır açıcı bir emsal” olarak değerlendirdi. Lenssens’e göre bankalar bugüne kadar çoğu dosyada müşterinin ağır hata yaptığını varsayarak ödeme yapmaktan kaçınıyordu. Mahkeme ise ispat yükünün bankada olduğuna hükmetti. Uzman avukat, phishing vakalarında ağır ihmalin oldukça istisnai bir durum olduğunu belirterek, dolandırıcıların yönlendirmesiyle güvenlik kodu</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Jahangar Takalo Kimdir? Banka Hesabında 1 Trilyon TL Görünen Şaşırtan Olay Gündem Oldu Ahmad Jahangar Takalo Kimdir? Banka Hesabında 1 Trilyon TL Görünen Şaşırtan Olay Gündem Oldu Uyan 32 Van’da yaşayan Azerbaycan asıllı Ahmad Jahangar Takalo, banka hesabında ortaya çıkan olağan dışı bakiye nedeniyle Türkiye gündemine oturdu. İddiaya göre market alışverişi sırasında kartının hata vermesiyle başlayan süreç, bankada yapılan kontrol sonrası milyonları değil, milyarları aşan bir hesap bakiyesinin görülmesiyle bambaşka bir boyuta ulaştı. Hesapta görülen rakam şok etkisi yarattı Bankada yapılan incelemede, hesabında 999 milyar TL’yi aşan bir bakiye olduğu görüldü. Bu durum hem banka çalışanlarını hem de hesap sahibini şaşkına çevirdi. Kaynağı henüz açıklanmayan tutar nedeniyle hesaplara güvenlik amaçlı bloke uygulandığı öne sürüldü. “Hata mı, sistem açığı mı?” sorusu gündemde Olayın ardından en çok merak edilen konu, bu devasa tutarın hesaba nasıl geçtiği oldu. Uzman olmayan kullanıcılar arasında “sistem hatası”, “veri kayması” veya “yanlış işlem” ihtimalleri konuşulurken, resmi açıklama yapılmadı. Hesaplara erişim kısıtlandı İddialara göre, bankanın inceleme süreci başlatmasının ardından Takalo’nun tüm hesaplarına geçici blokeler konuldu. Bu nedenle hem görünen yüksek tutara hem de kendi normal bakiyesine erişemediği belirtildi. Sosyal medyada viral oldu Kısa sürede sosyal medyada yayılan olay, “1 trilyon TL gerçekten yatmış olabilir mi?” sorusunu gündeme taşıdı. Kullanıcılar arasında hem esprili yo</t>
+          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek sonhaber.eu Belçika’da dolandırıcıların hedefi haline gelen ve phishing (oltalama) mağduru olan kişiler için emsal bir karar alındı. Antwerp Mahkemesi, phishing dolandırıcılığına uğrayan müşterilerin zararlarının bankalar tarafından gecikmeden karşılanması gerektiğine hükmetti. Belçika’nın Antwerp kentinde hızlı yargılama usulüyle görülen davada mahkeme, phishing (oltalama) dolandırıcılığı mağdurlarının zararlarının bankalar tarafından öncelikle karşılanması gerektiğine karar verdi. Karar, yaklaşık 50 bin euro dolandırılan yaşlı bir çiftin açtığı dava sonucunda alındı. Mahkeme bankanın bu yaklaşımını kabul etmedi. Karara göre bankalar, phishing mağdurlarının zararını derhal ödemekle yükümlü olacak. Banka, müşterinin ağır ihmalde bulunduğunu düşünüyorsa bunu kanıtlamak için kendisi tekrar mahkemeye başvurmak ve bunu kanıtlamak zorunda olacak. Phishing (oltalama) nedir? Phishing, dolandırıcıların banka, resmi kurum veya güvenilir bir kuruluş gibi davranarak kişilerin şifre, banka bilgisi veya güvenlik kodlarını ele geçirmeye çalıştığı bir siber dolandırıcılık yöntemidir. Bankacılık sektöründe çığır açan karar Bankacılık hukuku uzmanı Avukat Geert Lenssens, kararı “çığır açıcı bir emsal” olarak değerlendirdi.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -6194,14 +6226,10 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQaVdDa1lnbWtVNHdiVkJUaGJ0Z3RrRTJwSGZOR3dBTDhXRmZpUldiZkRqMjVIcE1UWlQ3eGlqU3NPT01MNVNIN3VlbVJqM1VvQUtGWFFmNGl0RXZ0MFl3N2dDc0xUbDdyNlBHSTJyTk5vY2FTWE1oa3o2aVJ6ZzlQcjNzY2Q0ZUlKM0NVR0cyeVdoeGhyQVluOFR5WFdEQkFmTEF4TnZDcXViUEM4SUF3UmthbGRkSk9PalHSAboBQVVfeXFMUGlXQ2tZZ21rVTR3YlZCVGhidGd0a0UycEhmTkd3QUw4V0ZmaVJXYmZEajI1SHBNVFpUN3hpalNzT09NTDVTSDd1ZW1SajNVb0FLRlhRZjRpdEV2dDBZdzdnQ3NMVGw3cjZQR0kyck5Ob2NhU1hNaGt6NmlSemc5UHIzc2NkNGVJSjNDVUdHMnlXaHhockFZbjhUeVhXREJBZkxBeE52Q3F1YlBDOElBd1JrYWxkZEpPT2pR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Van</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPSWhvaFFoTkFwM0xNTXdoVXBjQkZKb0V1Slk3dkJkYXJmRV9lV1A3eEhaaWR4REIzc1M4Yy1MRVlpSHZRQzFDb3dqQkJ6ZDlqTjdzTlpPaUZOZ3ZndmZrY0VJTmt4VE9XLXJqVkJKQVJnSDN0Z1ZzTHdRdDRpdGNJckRMc0xKQUo1dEpEd21fZUJ0aDllSk9id1pkVkNDdFR0MmREVFdBRHXSAagBQVVfeXFMT0lob2hRaE5BcDNMTU13aFVwY0JGSm9FdUpZN3ZCZGFyZkVfZVdQN3hIWmlkeERCM3NTOGMtTEVZaUh2UUMxQ293akJCemQ5ak43c05aT2lGTmd2Z3Zma2NFSU5reFRPVy1yalZCSkFSZ0gzdGdWc0x3UXQ0aXRjSXJETHNMSkFKNXRKRHdtX2VCdGg5ZUpPYndaZFZDQ3RUdDJkRFRXQUR1?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
@@ -6210,7 +6238,7 @@
       <c r="S39" s="2" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr"/>
@@ -6224,7 +6252,7 @@
       <c r="Y39" s="2" t="inlineStr"/>
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="n">
-        <v>100.31</v>
+        <v>83.25</v>
       </c>
       <c r="AB39" s="2" t="n">
         <v>38</v>
@@ -6233,27 +6261,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:10:23</t>
+          <t>2026-06-03 11:38:00</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>rüşvet</t>
+          <t>banka hesapları bloke</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CHP’li Özgür Özel ve milletvekilleri hakkında rüşvet fezlekesi: Muhittin Böcek’ten para istendiği iddiası yargıda</t>
+          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CHP’li Özgür Özel ve milletvekilleri hakkında rüşvet fezlekesi: Muhittin Böcek’ten para istendiği iddiası yargıda ehamedya.com.tr</t>
+          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -6263,18 +6291,22 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>gıda</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>banka, banka hesabı</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>CHP’li Özgür Özel ve milletvekilleri hakkında rüşvet fezlekesi: Muhittin Böcek’ten para istendiği iddiası yargıda ehamedya.com.tr</t>
+          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>CHP’li Özgür Özel ve milletvekilleri hakkında rüşvet fezlekesi: Muhittin Böcek’ten para istendiği iddiası yargıda CHP’li Özgür Özel ve milletvekilleri hakkında rüşvet fezlekesi: Muhittin Böcek’ten para istendiği iddiası yargıda ehamedya.com.tr CHP’li Özgür Özel ve milletvekilleri hakkında rüşvet fezlekesi: Muhittin Böcek’ten para istendiği iddiası yargıda ehamedya.com.tr</t>
+          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -6284,10 +6316,14 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOY1hmR1NkTHZOS1BBWDg3VXFTdkpqWW93QjhHaDBMbFdja0ZUZzlVLXljWi1lV1hLSDIxU29uenFlN1Q5MUcyUkx4S0pySVZGaWVVLTNwUWt2VjBVUk10b3NnSFNLQ29EQ1RUT0Npc1ZZTzVYM2RVUXdvbmV2Q2wxOWNUOEFUUlNPVjZvVlllX0Y1bXNFSi1xeHNiaF9LS3RHLV9wNDRCZERDbTRPbDVRLXp4TUQtcVo2S0NmMlNaRkZnVjRMdmlLRmY1ZnZFTmlJdVJtbzRWVUozZTVybVlVeUNXZ3A?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>https://gazeteoksijen.com/turkiye/banka-hesabinda-21-milyar-dolar-gordu-vanda-bir-gunde-milyarderler-listesine-giren-kisi-277613</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
@@ -6296,7 +6332,7 @@
       <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr"/>
@@ -6310,7 +6346,7 @@
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="n">
-        <v>106.04</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="AB40" s="2" t="n">
         <v>39</v>
@@ -6319,12 +6355,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 05:30:00</t>
+          <t>2026-06-03 15:26:35</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ödeme kuruluşu</t>
+          <t>banka hesapları bloke</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -6334,12 +6370,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Emekliye Büyük Rekabet: Haziran Promosyonlarında Bankalar Rakamları Güncelledi!</t>
+          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü?</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Emekliye Büyük Rekabet: Haziran Promosyonlarında Bankalar Rakamları Güncelledi! konyayenigun.com</t>
+          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6349,7 +6385,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>banka, banka hesabı</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -6359,22 +6395,22 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Yılın ilk yarısının son ayına girilmesiyle birlikte bankacılık sektöründe emekli maaşı alan vatandaşlara yönelik rekabet ortamı benzeri görülmemiş bir seviyeye ulaştı. Milyonlarca emeklinin gelirlerini artırma arayışında olduğu bu dönemde, kamu ve özel sermayeli finans kuruluşları müşteri tabanlarını büyütmek amacıyla kesenin ağzını iyice açtı. Sektör temsilcileri tarafından yapılan peş peşe açıklamalarla nakit destek tutarları baştan aşağı yenilenirken, maaş transferi sürecini başlatan hak sahipleri için adeta yeni bir kazanç kapısı aralandı. Yaşanan bu hareketlilik sadece geleneksel nakit ödemeleriyle sınırlı kalmayıp, yan finansal ürünlerin kullanımıyla desteklenen çok boyutlu bir pazarlama stratejisine dönüştü. Bankalar, emekli vatandaşları kendi bünyelerine katabilmek adına fatura ödeme taahhütlerinden kredi kartı harcama sözlerine kadar geniş bir yelpazede ek fayda paketleri hazırladı. Bu durum, bütçesine katkı sağlamak isteyen tasarruf sahiplerinin alternatifleri çok daha detaylı bir şekilde analiz etmesini mecbur kıldı. Katılım Finans Kurumları Ve Özel Bankalar Yarışta Öne Çıkıyor Piyasadaki hareketliliğin öncüsü konumundaki katılım finans kuruluşları, bu dönemde geleneksel bankaların bir adım önüne geçerek dikkat çekici teklifler sundu. Vakıf Katılım, temel ödeme tutarının üzerine eklediği yan desteklerle toplam avantaj paketini kırk bin Türk Lirası seviyesine kadar yükselterek sektörün en yüksek oranlarından birine imza attı. Benzer şekilde Türkiye Finans ve ING gibi güçlü oyuncular da otuz iki bin Türk Lirasına ulaşan paket baremleriyle maaş müşterilerini kendilerine çekmek için yoğun bir mesai harcıyor. Özel bankacılık alanının köklü temsilcileri olan Albaraka Türk, Yapı Kredi ve VakıfBank ise otuz bin Türk Lirası sınırına dayanan cazip teklif paketleriyle yarışta geri kalmayacaklarını açıkça ortaya koydu. Şekerbank ve DenizBank cephesinde de durum pek farklı değil; bu kurumlar da nakit promosyon baremlerini yirmi yedi bin beş yüz ile yirmi yedi bin Türk Lirası civarına sabitleyerek pazardaki paylarını korumaya çalışıyor. Garanti BBVA ile İş Bankası ise ek ödüller ve puan sistemleriyle destekledikleri yirmi beş bin Türk Liralık paketleriyle sürece dahil oldu. Ekstra Kazanım Koşulları Dikkatle İncelenmesi Gereken Detaylar Arasında Finansal kurumların ilan ettiği bu yüksek tutarlara ulaşabilmek için sadece maaş yazısını ilgili kuruma taşımak her zaman yeterli kriter sayılmıyor. Sektör uzmanları, ilan edilen tavan rakamların arkasında genellikle otomatik fatura ödeme talimatı verilmesi, belirli tutarda kredi kartı harcaması yapılması veya yeni müşteri davet edilmesi gibi yan şartların bulunduğunu ifade ediyor. Bu sebeple hak sahiplerinin sadece ana rakama odaklanmak yerine, sözleşmelerde yer alan taahhüt maddelerini ve yerine getirilmesi gereken finansal operasyonları derinlemesine incelemesi büyük önem taşıyor. Kampanyaların içeriğinde yer alan faiz avantajlı nakit avans kullanımları, alışverişlerde geçerli puan yüklemeleri ve sigorta ürünleri gibi unsurlar toplam fayda algısını doğrudan etkiliyor. TEB, QNB ve Akbank gibi kurumlar on altı bin ile otuz bir bin Türk Lirası arasında esneyen geniş baremli alternatif programlar hazırlayarak her bütçe grubuna hitap etmeyi amaçlıyor. Hiçbir ek koşul sunmadan sadece net maaş tutarına göre doğrudan ham ödeme yapan Ziraat Bankası gibi kamu kurumları ise sadelikten yana olan vatandaşlar için ayrı bir alternatif oluşturuyor. Temmuz Zammı Öncesi Stratejik Tercih Dönemi Devam Ediyor Ekonomi çevrelerinde, önümüzdeki ay netleşecek olan memur ve emekli maaş artış oranlarının ardından bankaların mevcut rakamları bir kez daha yukarı yönlü revize edebileceği konuşuluyor. Mevcut süreçte bütçesini rahatlatmak isteyen vatandaşlar, Temmuz ayındaki yasal düzenlemeleri beklemeden şimdiden en yüksek verimi alabileceği kuruluşu seçmek için şubelerin ve dijital kanalların yollarını tutuyor. Uzmanlar ise acele karar vermek yerine bankaların resmi bilgilendirme kanalları üzerinden tüm şartların mukayese edilmesi gerektiğini sıklıkla hatırlatıyor. Piyasadaki bu dinamik yapının yaz ayları boyunca etkisini sürdüreceği ve müşteri kapma mücadelesinin daha da sertleşeceği tahmin ediliyor. Emeklilerin yapacağı doğru hamleler, üç yıllık taahhüt süresi boyunca elde edecekleri yan gelir kalemi üzerinde doğrudan belirleyici bir rol oynayacak. Finans kuruluşlarının müşteri sadakatini sağlamak adına sunduğu bu imkanlar, haziran ayı boyunca piyasanın en canlı ve en çok konuşulan gündem maddesi olmaya devam edecek gibi görünüyor. Kaynak: Zeki Ersin Yıldırım Emekliye Büyük Rekabet: Haziran Promosyonlarında Bankalar Rakamları Güncelledi! Yılın ilk yarısının son ayına girilmesiyle birlikte bankacılık sektöründe emekli maaşı alan vatandaşlara yönelik rekabet ortamı benzeri görülmemiş bir seviyeye ulaştı. Katılım Finans Kurumları Ve Özel Bankalar Yarışta Öne Çıkıyor Ekstra Kazanım Koşulları Dikkatle İncelenmesi Gereken Detaylar Arasında Temmuz Zammı Öncesi Stratejik Tercih Dönemi Devam Ediyor Yılın ilk yarısının son ayına girilmesiyle birlikte bankacılık sektöründe emekli maaşı alan vatandaşlara yönelik rekabet ortamı benzeri görülmemiş bir seviyeye ulaştı. Milyonlarca emeklinin gelirlerini artırma arayışında olduğu bu dönemde, kamu ve özel sermayeli finans kuruluşları müşteri tabanlarını büyütmek amacıyla kesenin ağzını iyice açtı. Sektör temsilcileri tarafından yapılan peş peşe açıklamalarla nakit destek tutarları baştan aşağı yenilenirken, maaş transferi sürecini başlatan hak sahipleri için adeta yeni bir kazanç kapısı aralandı. Yaşanan bu hareketlilik sadece geleneksel nakit ödemeleriyle sınırlı kalmayıp, yan finansal ürünlerin kullanımıyla desteklenen çok boyutlu bir pazarlama stratejisine dönüştü. Bankalar, emekli vatandaşları kendi bünyelerine katabilmek adına fatura ödeme taahhütlerinden kredi kartı harcama sözlerine kadar geniş bir yelpazede ek fayda paketleri hazırladı. Bu durum, bütçesine katkı sağlamak isteyen tasarruf sahiplerinin alternatifleri çok daha detaylı bir şekilde analiz etmesini mecbur kıldı. Piyasadaki hareketliliğin öncüsü konumundaki katılım finans kuruluşları, bu dönemde geleneksel bankaların bir adım önüne geçerek dikkat çekici teklifler sundu. Vakıf Katılım, temel ödeme tutarının üzerine eklediği yan desteklerle toplam avantaj paketini kırk bin Türk Lirası seviyesine kadar yükselterek sektörün en yüksek oranlarından birine imza attı. Benzer şekilde Türkiye Finans ve ING gibi güçlü oyuncular da otuz iki bin Türk Lirasına ulaşan paket baremleriyle maaş müşterilerini kendilerine çekmek için yoğun bir mesai harcıyor. Özel bankacılık alanının köklü temsilcileri olan Albaraka Türk, Yapı Kredi ve VakıfBank ise otuz bin Türk Lirası sınırına dayanan cazip teklif paketleriyle yarışta geri kalmayacaklarını açıkça ortaya koydu. Şekerbank ve DenizBank cephesinde de durum pek farklı değil; bu kurumlar da nakit promosyon baremlerini yirmi yedi bin beş yüz ile yirmi yedi bin Türk Lirası civarına sabitleyerek pazardaki paylarını korumaya çalışıyor. Garanti BBVA ile İş Bankası ise ek ödüller ve puan sistemleriyle destekledikleri yirmi beş bin Türk Liralık paketleriyle sürece dahil oldu. Finansal kurumların ilan ettiği bu yüksek tutarlara ulaşabilmek için sadece maaş yazısını ilgili kuruma taşımak her zaman yeterli kriter sayılmıyor. Sektör uzmanları, ilan edilen tavan rakamların arkasında genellikle otomatik fatura ödeme talimatı verilmesi, belirli tutarda kredi kartı harcaması yapılması veya yeni müşteri davet edilmesi gibi yan şartların bulunduğunu ifade ediyor. Bu sebeple hak sahiplerinin sadece ana rakama odaklanmak yerine, sözleşmelerde yer alan taahhüt maddelerini ve yerine getirilmesi gereken finansal operasyonları derinlemesine incelemesi büyük önem taşıyor. Kampanyaların içeriğinde yer alan faiz avantajlı nakit avans kullanımları, alışverişlerde geçerli puan yüklemeleri ve sigorta ürünleri gibi unsurlar toplam fayda algısını doğrudan etkiliyor. TEB, QNB ve Akbank gibi kurumlar on altı bin ile otuz bir bin Türk Lirası arasında esneyen geniş baremli alternatif programlar hazırlayarak her bütçe grubuna hitap etmeyi amaçlıyor. Hiçbir ek koşul sunmadan sadece net maaş tutarına göre doğrudan ham ödeme yapan Ziraat Bankası gibi kamu kurumları ise sadelikten yana olan vatandaşlar için ayrı bir alternatif oluşturuyor. Ekonomi çevrelerinde, önümüzdeki ay netleşecek olan memur ve emekli maaş artış oranlarının ardından bankaların mevcut rakamları bir kez daha yukarı yönlü revize edebileceği konuşuluyor. Mevcut süreçte bütçesini rahatlatmak isteyen vatandaşlar, Temmuz ayındaki yasal düzenlemeleri beklemeden şimdiden en yüksek verimi alabileceği kuruluşu seçmek için şubelerin ve dijital kanalların yollarını tutuyor. Uzmanlar ise acele karar vermek yerine bankaların resmi bilgilendirme kanalları üzerinden tüm şartların mukayese edilmesi gerektiğini sıklıkla hatırlatıyor. Piyasadaki bu dinamik yapının yaz ayları boyunca etkisini sürdüreceği ve müşteri kapma mücadelesinin daha da sertleşeceği tahmin ediliyor. Emeklilerin yapacağı doğru hamleler, üç yıllık taahhüt süresi boyunca elde edecekleri yan gelir kalemi üzerinde doğrudan belirleyici bir rol oynayacak. Finans kuruluşlarının müşteri sadakatini sağlamak adına sunduğu bu imkanlar, haziran ayı boyunca piyasanın en canlı ve en çok konuşulan gündem maddesi olmaya devam edecek gibi görünüyor. Kaynak: Zeki Ersin Yıldırım</t>
+          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Emekliye Büyük Rekabet: Haziran Promosyonlarında Bankalar Rakamları Güncelledi! Emekliye Büyük Rekabet: Haziran Promosyonlarında Bankalar Rakamları Güncelledi! konyayenigun.com Yılın ilk yarısının son ayına girilmesiyle birlikte bankacılık sektöründe emekli maaşı alan vatandaşlara yönelik rekabet ortamı benzeri görülmemiş bir seviyeye ulaştı. Milyonlarca emeklinin gelirlerini artırma arayışında olduğu bu dönemde, kamu ve özel sermayeli finans kuruluşları müşteri tabanlarını büyütmek amacıyla kesenin ağzını iyice açtı. Sektör temsilcileri tarafından yapılan peş peşe açıklamalarla nakit destek tutarları baştan aşağı yenilenirken, maaş transferi sürecini başlatan hak sahipleri için adeta yeni bir kazanç kapısı aralandı. Yaşanan bu hareketlilik sadece geleneksel nakit ödemeleriyle sınırlı kalmayıp, yan finansal ürünlerin kullanımıyla desteklenen çok boyutlu bir pazarlama stratejisine dönüştü. Bankalar, emekli vatandaşları kendi bünyelerine katabilmek adına fatura ödeme taahhütlerinden kredi kartı harcama sözlerine kadar geniş bir yelpazede ek fayda paketleri hazırladı. Bu durum, bütçesine katkı sağlamak isteyen tasarruf sahiplerinin alternatifleri çok daha detaylı bir şekilde analiz etmesini mecbur kıldı. Katılım Finans Kurumları Ve Özel Bankalar Yarışta Öne Çıkıyor Piyasadaki hareketliliğin öncüsü konumundaki katılım finans kuruluşları, bu dönemde geleneksel bankaların bir adım önüne geçerek dikkat çekici teklifler sundu. Vakıf Katılım, temel ödeme tutarının üzerine eklediği yan desteklerle toplam avantaj paketini kırk bin Türk Lirası seviyesine kadar yükselterek sektörün en yüksek oranlarından birine imza attı. Benzer şekilde Türkiye Finans ve ING gibi güçlü oyuncular da otuz iki bin Türk Lirasına ulaşan paket baremleriyle maaş müşterilerini kendilerine çekmek için yoğun bir mesai harcıyor. Özel bankacılık alanının köklü temsilcileri olan Albaraka Türk, Yapı Kredi ve VakıfBank ise otuz bin Türk Lirası sınırına dayanan cazip teklif paketleriyle yarışta geri kalmayacaklarını açıkça ortaya koydu. Şekerbank ve DenizBank cephesinde de durum pek farklı değil; bu kurumlar da nakit promosyon baremlerini yirmi yedi bin beş yüz ile yirmi yedi bin Türk Lirası civarına sabitleyerek pazardaki paylarını korumaya çalışıyor. Garanti BBVA ile İş Bankası ise ek ödüller ve puan sistemleriyle destekledikleri yirmi beş bin Türk Liralık paketleriyle sürece dahil oldu. Ekstra Kazanım Koşulları Dikkatle İncelenmesi Gereken Detaylar Arasında Finansal kurumların ilan ettiği bu yüksek tutarlara ulaşabilmek için sadece maaş yazısını ilgili kuruma taşımak her zaman yeterli kriter sayılmıyor. Sektör uzmanları, ilan edilen tavan rakamların arkasında genellikle otomatik fatura ödeme talimatı verilmesi, belirli tutarda kredi kartı harcaması yapılması veya yeni müşteri davet edilmesi gibi yan şartların bulunduğunu ifade ediyor. Bu sebeple hak sahiplerinin sadece ana rakama odaklanmak yerine, sözleşmelerde yer alan taahhüt maddelerini ve yerine getirilmesi gereken finansal operasyonları derinlemesine incelemesi büyük önem taşıyor. TEB, QNB ve Akbank gibi kurumlar on altı bin ile otuz bir bin Türk Lirası arasında esneyen geniş baremli alternatif programlar hazırlayarak her bütçe grubuna hitap etmeyi amaçlıyor. Temmuz Zammı Öncesi Stratejik Tercih Dönemi Devam Ediyor Ekonomi çevrelerinde, önümüzdeki ay netleşecek olan memur ve emekli maaş artış oranlarının ardından bankaların mevcut rakamları bir kez daha yukarı yönlü revize edebileceği konuşuluyor. Mevcut süreçte bütçesini rahatlatmak isteyen vatandaşlar, Temmuz ayındaki yasal düzenlemeleri beklemeden şimdiden en yüksek verimi alabileceği kuruluşu seçmek için şubelerin ve dijital kanalların yollarını tutuyor. Piyasadaki bu dinamik yapının yaz ayları boyunca etkisini sürdüreceği ve müşteri kapma mücadelesinin daha da sertleşeceği tahmin ediliyor. Finans kuruluşlarının müşteri sadakatini sağlamak adına sunduğu bu imkanlar, haziran ayı boyunca piyasanın en canlı ve en çok konuşulan gündem maddesi olmaya devam edecek gibi görünüyor. Kaynak: Zeki Ersin Yıldırım Emekliye Büyük Rekabet: Haziran Promosyonlarında Bankalar Rakamları Güncelledi! Katılım Finans Kurumları Ve Özel Bankalar Yarışta Öne Çıkıyor Ekstra Kazanım Koşulları Dikkatle İncelenmesi Gereken Detaylar Arasında Temmuz Zammı Öncesi Stratejik Tercih Dönemi Devam Ediyor Yılın ilk yarısının son ayına girilmesiyle birlikte bankacılık sektöründe emekli maaşı alan vatandaşlara yönelik rekabet ortamı benzeri görülmemiş bir seviyeye ulaştı. Finansal kurumların ilan ettiği bu yüksek tutarlara ulaşabilmek için sadece maaş yazısını ilgili kuruma taşımak her zaman yeterli kriter sayılmıyor. Ekonomi çevrelerinde, önümüzdeki ay netleşecek olan memur ve emekli maaş artış oranlarının ardından bankaların mevcut rakamları bir kez daha yukarı yönlü revize edebileceği konuşuluyor.</t>
+          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPbnd5Qm1mU19aLXQ4b18wRGp2dFV1V0tER3Y1LWdodWlKbnNTb25abUQxb3l1VFBOcXVjWXJIdEZCTWJMT3ZORWdlVDNqUmJjZ0VaX0gzSnFNWDAxQldkbDF6Z3JUM04wdEVYZ0lVZG1yeWV4RkZtZXFSS1FYV1VGUXFTR25rUnFfaHZqUUhXdXJ5WW5MRUhJNlA5d2ExYk42NWplbFV2SWdMTGZ0UDJJ0gGvAUFVX3lxTE9ud3lCbWZTX1otdDhvXzBEanZ0VXVXS0RHdjUtZ2h1aUpuc1NvblptRDFveXVUUE5xdWNZckh0RkJNYkxPdk5FZ2VUM2pSYmNnRVpfSDNKcU1YMDFCV2RsMXpnclQzTjB0RVhnSVVkbXJ5ZXhGRm1lcVJLUVhXVUZRcVNHbmtScV9odmpRSFd1cnlZbkxFSEk2UDl3YTFiTjY1amVsVXZJZ0xMZnRQMkk?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNR0hibXFPY0FKOVpVa2ZxWmFyNDhhSmhPWE85OWRGOXhRUDJDTGkzZDBNN0Iwcnk4cFpnV1F1cXgzMmNuU0hQSWxVNS1RZzFyTUEteGhESHUtYk8zNDcwQVZwS05RdWNSa3ZrNWgteFdWa0NyNFlUa2hvZGpqNzM2ZFNfVHhHOTdKb2Y4MWVxeE4?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
@@ -6400,7 +6436,7 @@
       <c r="Y41" s="2" t="inlineStr"/>
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="n">
-        <v>84.5</v>
+        <v>57.38</v>
       </c>
       <c r="AB41" s="2" t="n">
         <v>40</v>
@@ -6409,12 +6445,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 00:10:08</t>
+          <t>2026-06-03 13:28:43</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>banka soruşturma</t>
+          <t>şüpheli işlem</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -6424,12 +6460,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Beş kişi, Kamboçya'daki suçlulara satış yapmak amacıyla "paravan şirketler" kurmak ve 100'den fazla banka hesabı açmakla suçlandı.</t>
+          <t>Sürekli banka kartı kullananlar yandı</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Beş kişi, Kamboçya'daki suçlulara satış yapmak amacıyla "paravan şirketler" kurmak ve 100'den fazla banka hesabı açmakla suçlandı. Vietnam.vn</t>
+          <t>Sürekli banka kartı kullananlar yandı Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6439,32 +6475,32 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı, şirket</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş | şirket / firma</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Beş kişi, Kamboçya'daki suçlulara satış yapmak amacıyla "paravan şirketler" kurmak ve 100'den fazla banka hesabı açmakla suçlandı. Vietnam.vn</t>
+          <t>Haberler - Gündem Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Siber güvenlik ve finans uzmanları, kredi kartlarına kıyasla banka kartlarının dolandırıcılık vakalarında telafisi zor finansal kayıplara yol açabileceğini belirterek tüketicileri dikkatli olmaları konusunda uyardı. Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Gelişen teknolojiyle birlikte alışveriş alışkanlıklarımız tamamen değişti. Günlük en küçük harcamalarda Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Siber güvenlik ve finans uzmanları, kredi kartlarına kıyasla banka kartlarının dolandırıcılık vakalarında telafisi zor finansal kayıplara yol açabileceğini belirterek tüketicileri dikkatli olmaları konusunda uyardı. Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Gelişen teknolojiyle birlikte alışveriş alışkanlıklarımız tamamen değişti. Günlük en küçük harcamalarda Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Siber güvenlik ve finans uzmanları, kredi kartlarına kıyasla banka kartlarının dolandırıcılık vakalarında telafisi zor finansal kayıplara yol açabileceğini belirterek tüketicileri dikkatli olmaları konusunda uyardı.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Beş kişi, Kamboçya'daki suçlulara satış yapmak amacıyla "paravan şirketler" kurmak ve 100'den fazla banka hesabı açmakla suçlandı. Beş kişi, Kamboçya'daki suçlulara satış yapmak amacıyla "paravan şirketler" kurmak ve 100'den fazla banka hesabı açmakla suçlandı. Vietnam.vn Beş kişi, Kamboçya'daki suçlulara satış yapmak amacıyla "paravan şirketler" kurmak ve 100'den fazla banka hesabı açmakla suçlandı.</t>
+          <t>Sürekli banka kartı kullananlar yandı Sürekli banka kartı kullananlar yandı Sözcü Gazetesi Haberler - Gündem Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Siber güvenlik ve finans uzmanları, kredi kartlarına kıyasla banka kartlarının dolandırıcılık vakalarında telafisi zor finansal kayıplara yol açabileceğini belirterek tüketicileri dikkatli olmaları konusunda uyardı. Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Gelişen teknolojiyle birlikte alışveriş alışkanlıklarımız tamamen değişti. Günlük en küçük harcamalarda Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Gelişen teknolojiyle birlikte alışveriş alışkanlıklarımız tamamen değişti.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQaVZ6V0NPdHdsNURTdHV2MWRGelQ4MjBCNVJfMWlYdFNrLW5CY195dDBMT3A4QUsxWmtadHBPYXRvOFhVbEpQa0s0SXdsNm5FUG1QLUpJdS1Md09Ob1FJUGFjbkFCOE9iUllGUFJMWjhuSWpydEpqQzM0T3Y5eWt0MDcxVzRFbWh6MDZRU3NuUy1CWF9rdHFzS2tTbFpZd3VwTTZQNjlpaG9faF9zbHdRUTE4Wk94WE44V2J4dA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5UdlFFR1docl9DUlI0UEthUlFmaXJQVVlhQUQtSFRPMUNkYnV4bzlyN21IZU1ldlBJbTUwV0s2bkh1eFlxQXotUnNLTU40RHdXQTlISUdHU1ZzWm5fdkFoMThDQl92TnhQQ0lHYkhHUnVxX0hXZWQyWnMwZy0xYXc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
@@ -6490,7 +6526,7 @@
       <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr"/>
       <c r="AA42" s="2" t="n">
-        <v>107.66</v>
+        <v>44.5</v>
       </c>
       <c r="AB42" s="2" t="n">
         <v>41</v>
@@ -6499,27 +6535,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 09:50:16</t>
+          <t>2026-06-03 13:33:47</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>banka soruşturma</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CHP delegelerinin banka kayıtları incelenecek: Denizli’den 15 isim var</t>
+          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu!</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CHP delegelerinin banka kayıtları incelenecek: Denizli’den 15 isim var Denizli Haber</t>
+          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! Erzincan Birlik Medya</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -6529,22 +6565,18 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>el konuldu</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>CHP delegelerinin banka kayıtları incelenecek: Denizli’den 15 isim var Denizli Haber</t>
+          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! Erzincan Birlik Medya</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>CHP delegelerinin banka kayıtları incelenecek: Denizli’den 15 isim var CHP delegelerinin banka kayıtları incelenecek: Denizli’den 15 isim var Denizli Haber CHP delegelerinin banka kayıtları incelenecek: Denizli’den 15 isim var Denizli Haber</t>
+          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! 17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! Erzincan Birlik Medya 17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu!</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -6554,14 +6586,10 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNT1BtV0VLR3JsQlpXS05kamt6MUpzWFU0a1hDeW44MlcwX0ZOZ043S1dVWV9OYzZoU0JpcERsZnRKMHJZUlIzMG5obFNQZFlWZ3FMOHl4OHhhMXo5ZEh5WUJmZVhaUmhPYW1UdVhnWU04emQtVTBQLTRwR2lzdHBiLVdyUTgyZ2ZIWnpsV0hucTlkX09yand4T0ozZm5YR3cyWlhiV2lqMnZFREU?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Denizli</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMk0xWXlORzVyNHpSSDNpWEZRVFRNLVRvSGpQYVVCZVdTLWxIVC12MkswazMtMG9CX2lDbmFlQzNuY0ljb1I2eU80Zmd4MmdaTWh5anpkRFk5YWtQeU9mQ3QzVlYwenlSR3o4aWdSVG5QVVMzQUhyZzAweUpDVTV6bHI1RVRral9mdFBsd1ZqT3NRb00zSHhSMWlGNGRSV1NScWhGVEZnY29HQzZ2MW9BOF9xamVrZFQ0cDJ1Mm5YRQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
@@ -6570,7 +6598,7 @@
       <c r="S43" s="2" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr"/>
@@ -6584,7 +6612,7 @@
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="n">
-        <v>72.84</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="AB43" s="2" t="n">
         <v>42</v>
@@ -6593,27 +6621,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 10:43:02</t>
+          <t>2026-06-03 11:14:00</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>banka soruşturma</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Bankacı ve Uzman Kılığıyla Vurgun: 89 Şüpheli Yakalandı</t>
+          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Bankacı ve Uzman Kılığıyla Vurgun: 89 Şüpheli Yakalandı Ajans Balıklıgöl</t>
+          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -6623,22 +6651,18 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>inşaat</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Bankacı ve Uzman Kılığıyla Vurgun: 89 Şüpheli Yakalandı Ajans Balıklıgöl</t>
+          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Bankacı ve Uzman Kılığıyla Vurgun: 89 Şüpheli Yakalandı Bankacı ve Uzman Kılığıyla Vurgun: 89 Şüpheli Yakalandı Ajans Balıklıgöl Bankacı ve Uzman Kılığıyla Vurgun: 89 Şüpheli Yakalandı Ajans Balıklıgöl</t>
+          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -6648,11 +6672,19 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQYnRHbUx2dTRBaGZLT3laLU9rUWFnUl9JZWJNQmdWYlJscGdNTDZ0c2V5cGFCdnZCd1RyUjVYLXhmenNUdkVDdWZLdmRnd0tKNEJoWkdNLUxtZ0xFVDB3Sjk5T3JZMVVLbnZTMkF1ejF2Yi1CZ3B6YkNOZ1luRnNkRXJvZTVTN1N5b3ZIS0lIaWNVS3BTMlFr?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQODJNbTY0NWFiUFpVMzUyclBFZUZDZlJfVmtDRmtKeTlUSnNjMGlMWnZHMnp1MHZtdTN1UFRiNUVyZVgweVRsUWZNY1ZmVzBTU0NpX3N2Q05GNVJxcmpGdmZHVmxiNW85NnI2QVEzbFhBWVAtdGtuZEpLR3E0OHFrX3pEZlp5d2loYlNIaW9qMVRpd1VzTFowd3AzVHlVWFR4bFo5S05uU2ttSzg3c0tjSmNVR0xLUGtjMlZaSU9CYkZPTGt2b2FTQ2xzZkRfc0J6QVlPOFJPTnNlQ1hidEJTdmpuQ2h1cGZ3?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Esenyurt</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -6660,7 +6692,7 @@
       <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr"/>
@@ -6674,7 +6706,7 @@
       <c r="Y44" s="2" t="inlineStr"/>
       <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" s="2" t="n">
-        <v>44.22</v>
+        <v>117.04</v>
       </c>
       <c r="AB44" s="2" t="n">
         <v>43</v>
@@ -6683,7 +6715,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 07:02:23</t>
+          <t>2026-06-03 09:31:16</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -6698,12 +6730,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Havai Fişek Fabrikasındaki Patlama Sonrası Gıda Alarmı: Yetkililer Soruşturma Başlattı</t>
+          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede!</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Havai Fişek Fabrikasındaki Patlama Sonrası Gıda Alarmı: Yetkililer Soruşturma Başlattı Malta Haber</t>
+          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6713,32 +6745,32 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>fabrika, gıda</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Malta’da havai fişek fabrikasında meydana gelen patlamanın ardından gıda güvenliği yetkilileri harekete geçti. Tarım ürünleri, hayvan yemleri ve gıda maddelerinde olası kirlilik riskine karşı kapsamlı inceleme başlatıldı. Food Safety and Security Authority (FSSA), Magħtab’daki havai fişek fabrikasında meydana gelen patlamanın ardından acil önleyici tedbirleri devreye aldığını açıkladı. Kurum tarafından yapılan açıklamada, olayın hemen ardından müdahale […]</t>
+          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Havai Fişek Fabrikasındaki Patlama Sonrası Gıda Alarmı: Yetkililer Soruşturma Başlattı Havai Fişek Fabrikasındaki Patlama Sonrası Gıda Alarmı: Yetkililer Soruşturma Başlattı Malta Haber Malta’da havai fişek fabrikasında meydana gelen patlamanın ardından gıda güvenliği yetkilileri harekete geçti. Tarım ürünleri, hayvan yemleri ve gıda maddelerinde olası kirlilik riskine karşı kapsamlı inceleme başlatıldı. Food Safety and Security Authority (FSSA), Magħtab’daki havai fişek fabrikasında meydana gelen patlamanın ardından acil önleyici tedbirleri devreye aldığını açıkladı. Kurum tarafından yapılan açıklamada, olayın hemen ardından müdahale […]</t>
+          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede! Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://www.maltahaber.com/havai-fisek-fabrikasindaki-patlama-sonrasi-gida-alarmi-yetkililer-sorusturma-baslatti/</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPajZ1VV9UV3E4MGlfeUFOeWdVbTdLLURCQVVmVmFKaFdSeDFmMVNZc3U3UlFUeS1Na0FOZ1ZQYUVwdXgzLWtGTEtHcHRqazlfRkthanBKdFJ2cUtNTzQzTWQyWXJ2aDhZcFJRdDRFY3ZXWFhUcG5qbkEwaEFzT2JMWEUtVjRjNUk0X1hjQnpGc0xyb0JaYjZXSndxVlFCVUEyVHZBSHVHRjhKQdIBmAFBVV95cUxQNjg0aFc2OXhMbDRLVG1WdEhqNGtRVGpISk05X1I3YXg2YUpMQ2M1MFpOdG9JdzZja2lwTS00RThYdEQ3VnRHT1g2dWMteHVZWUFCSURzYnBIc0FSbjJ5UnFPRHFXUEZuZWwwb1dXaURjdk95UlgyRURuM1V6R2dEM0c4dk1PSjFGdTJUS0psaVgtRjRMMkJsVg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
@@ -6746,19 +6778,11 @@
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>Fişek Fabrikasındaki Patlama Sonrası Gıda</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>Fişek Fabrikasındaki Patlama Sonrası Gıda:292:body+summary+title</t>
-        </is>
-      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr"/>
@@ -6772,7 +6796,7 @@
       <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="n">
-        <v>152.1</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="AB45" s="2" t="n">
         <v>44</v>
@@ -6781,7 +6805,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 21:25:46</t>
+          <t>2026-06-03 12:50:00</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -6796,12 +6820,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Kosmos 5 Milyon Dolar Yatırım Aldı ve Şirketlerin Gizli IT Soruşturma Maliyetlerini Ortadan Kaldırmalarına Yardımcı Oluyor</t>
+          <t>Yedi vize şirketine soruşturma</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Kosmos 5 Milyon Dolar Yatırım Aldı ve Şirketlerin Gizli IT Soruşturma Maliyetlerini Ortadan Kaldırmalarına Yardımcı Oluyor Unite.AI</t>
+          <t>Yedi vize şirketine soruşturma Memurlar.Net</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6821,25 +6845,29 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Kosmos 5 Milyon Dolar Yatırım Aldı ve Şirketlerin Gizli IT Soruşturma Maliyetlerini Ortadan Kaldırmalarına Yardımcı Oluyor Unite.AI</t>
+          <t>Ticaret Bakanı Ömer Bolat, "Vize başvuru aracılığı hizmeti sunan firmaların hizmet ve tanıtımlarına ilişkin olarak, Reklam Kurulu tarafından 7 farklı şirket hakkında 6502 sayılı Kanun'un 61'inci ve 62'nci maddeleri kapsamında incelemeler devam etmektedir" dedi. Ticaret Bakanı Ömer Bolat, "Vize başvuru aracılığı hizmeti sunan firmaların hizmet ve tanıtımlarına ilişkin olarak, Reklam Kurulu tarafından 7 farklı şirket hakkında 6502 sayılı Kanun'un 61'inci ve 62'nci maddeleri kapsamında incelemeler devam etmektedir" dedi. Ticaret Bakanı Ömer Bolat, "Vize başvuru aracılığı hizmeti sunan firmaların hizmet ve tanıtımlarına ilişkin olarak, Reklam Kurulu tarafından 7 farklı şirket hakkında 6502 sayılı Kanun'un 61'inci ve 62'nci maddeleri kapsamında incelemeler devam etmektedir" dedi. Önemli Uyarı : Bu servisi gereksiz kullananların şikayet etme hakkı geri alınacaktır. Adınız Soyadınız E-Posta Adresiniz Şikayet Nedeninizi Küfür / Hakaret Kışkırtıcı içerik Küçük düşürücü içerik Asılsız itham Diğer Güvenlik kodu Kapat Şikayet Et Bakan Kurum: 20 bine yakın konutu 64 ilde satışa çıkarıyoruz Süresiz nafaka için AYM'den karar çıktı! Tutuklu bulunan Mühittin Böcek yeni bir ifade daha verdi İşsizlik rakamları açıklandı Kültür ve Turizm Bakanlığı 569 Sözleşmeli Personel Alacak Yıldırımtürk: Altında esas yükseliş Ağustos'ta başlayacak En düşük emekli aylığı temmuzda 22 bin liraya mı yükselecek? Emekliler arasındaki zam farkı kapanıyor Sahillerde sigara yasağı yarın başlıyor Bahçeli'den CHP açıklaması: Olaylar sokağa taşıp kanunsuzluğa dönüşmemeli Maliye, Vergi Konseyinin yeni yönetimini belirledi 'Her 5 çocuktan 1'i siber zorbalığa maruz kalıyor' Sıfır Atık Festivali İstanbul'da başlıyor Ankara, 40 bin personelle havadan ve karadan korunacak Avukatlara büyük kolaylık: İstinafta 'E-Duruşma' dönemi Ergün Atalay: İşçi, memur ve emeklinin enflasyon kayıpları telafi edilmeli İstanbul CBS'den Özgür Özel ve Veli Ağbaba açıklaması Komisyondan geçti: Emniyet kadroları yeniden şekilleniyor Adalet Bakanlığı Görevde Yükselme ve Ünvan Değişikliği Tercih Sonuçları açıklandı KARDEMİR beyaz yaka personel alacak: İşte başvuru şartları! İTÜ yönetimi şikayet etti: 2 çalışan dolandırıcılıktan tutuklandı Bakan Gürlek paylaştı</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Kosmos 5 Milyon Dolar Yatırım Aldı ve Şirketlerin Gizli IT Soruşturma Maliyetlerini Ortadan Kaldırmalarına Yardımcı Oluyor Kosmos 5 Milyon Dolar Yatırım Aldı ve Şirketlerin Gizli IT Soruşturma Maliyetlerini Ortadan Kaldırmalarına Yardımcı Oluyor Unite.AI Kosmos 5 Milyon Dolar Yatırım Aldı ve Şirketlerin Gizli IT Soruşturma Maliyetlerini Ortadan Kaldırmalarına Yardımcı Oluyor Unite.AI</t>
+          <t>Yedi vize şirketine soruşturma Yedi vize şirketine soruşturma Memurlar.Net Ticaret Bakanı Ömer Bolat, "Vize başvuru aracılığı hizmeti sunan firmaların hizmet ve tanıtımlarına ilişkin olarak, Reklam Kurulu tarafından 7 farklı şirket hakkında 6502 sayılı Kanun'un 61'inci ve 62'nci maddeleri kapsamında incelemeler devam etmektedir" dedi. Önemli Uyarı : Bu servisi gereksiz kullananların şikayet etme hakkı geri alınacaktır. Adınız Soyadınız E-Posta Adresiniz Şikayet Nedeninizi Küfür / Hakaret Kışkırtıcı içerik Küçük düşürücü içerik Asılsız itham Diğer Güvenlik kodu Kapat Şikayet Et Bakan Kurum: 20 bine yakın konutu 64 ilde satışa çıkarıyoruz Süresiz nafaka için AYM'den karar çıktı! Tutuklu bulunan Mühittin Böcek yeni bir ifade daha verdi İşsizlik rakamları açıklandı Kültür ve Turizm Bakanlığı 569 Sözleşmeli Personel Alacak Yıldırımtürk: Altında esas yükseliş Ağustos'ta başlayacak En düşük emekli aylığı temmuzda 22 bin liraya mı yükselecek? Emekliler arasındaki zam farkı kapanıyor Sahillerde sigara yasağı yarın başlıyor Bahçeli'den CHP açıklaması: Olaylar sokağa taşıp kanunsuzluğa dönüşmemeli Maliye, Vergi Konseyinin yeni yönetimini belirledi 'Her 5 çocuktan 1'i siber zorbalığa maruz kalıyor' Sıfır Atık Festivali İstanbul'da başlıyor Ankara, 40 bin personelle havadan ve karadan korunacak Avukatlara büyük kolaylık: İstinafta 'E-Duruşma' dönemi Ergün Atalay: İşçi, memur ve emeklinin enflasyon kayıpları telafi edilmeli İstanbul CBS'den Özgür Özel ve Veli Ağbaba açıklaması Komisyondan geçti: Emniyet kadroları yeniden şekilleniyor Adalet Bakanlığı Görevde Yükselme ve Ünvan Değişikliği Tercih Sonuçları açıklandı KARDEMİR beyaz yaka personel alacak: İşte başvuru şartları! İTÜ yönetimi şikayet etti: 2 çalışan dolandırıcılıktan tutuklandı Bakan Gürlek paylaştı</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://www.unite.ai/tr/kosmos-raises-5m-to-help-enterprises-eliminate-the-hidden-cost-of-it-incident-investigations/</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>https://www.memurlar.net/haber/1168995/yedi-vize-sirketine-sorusturma.html</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
@@ -6848,7 +6876,7 @@
       <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr"/>
@@ -6862,7 +6890,7 @@
       <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr"/>
       <c r="AA46" s="2" t="n">
-        <v>111.06</v>
+        <v>58.75</v>
       </c>
       <c r="AB46" s="2" t="n">
         <v>45</v>
@@ -6871,7 +6899,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 20:37:00</t>
+          <t>2026-06-04 06:47:24</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -6881,17 +6909,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Yenidoğan Yoğun Bakım Ünitesinde Kötü Muamele İddiasına Soruşturma Açıldı</t>
+          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu!</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Yenidoğan Yoğun Bakım Ünitesinde Kötü Muamele İddiasına Soruşturma Açıldı Personel Sağlık Personeli Haber NET</t>
+          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Takvim</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -6901,31 +6929,35 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>sağlık</t>
+          <t>el konuldu</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Yenidoğan Yoğun Bakım Ünitesinde Kötü Muamele İddiasına Soruşturma Açıldı Personel Sağlık Personeli Haber NET</t>
+          <t>Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Giriş Tarihi: 04 Haziran 2026 09:47 Facebook X NSosyal Linki Kopyala Yazı Boyutu Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Diyarbakır Cumhuriyet Başsavcılığı koordinesinde; Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri, uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik asrın operasyonlarından birine imza attı. Yaklaşık 8 ay süren titiz teknik ve fiziki takibin ardından, zehir ticaretinden kazandıkları paraları piyasada aklamaya çalışan 18 şüpheli kıskıvrak yakalandı. 5 Ayrı Soruşturma Dosyası Açıldı "Uyuşturucu veya uyarıcı madde imal ve ticareti" ile "2313 Sayılı Kanuna Muhalefet" suçlarını işleyen şebeke üyeleri hakkında, bu kez de "Suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan 5 ayrı soruşturma dosyası açıldı. Operasyon kapsamında gözaltına alınan 18 şüpheli hakkında yasal işlemler sürerken, baskın yapılan adreslerde yüklü miktarda uyuşturucu maddenin de ele geçirildiği bildirildi. Emirhan Ceylan Takvim.com.tr Güncel Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Diyarbakır Cumhuriyet Başsavcılığı koordinesinde; Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri, uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik asrın operasyonlarından birine imza attı. Yaklaşık 8 ay süren titiz teknik ve fiziki takibin ardından, zehir ticaretinden kazandıkları paraları piyasada aklamaya çalışan 18 şüpheli kıskıvrak yakalandı. 5 Ayrı Soruşturma Dosyası Açıldı "Uyuşturucu veya uyarıcı madde imal ve ticareti" ile "2313 Sayılı Kanuna Muhalefet" suçlarını işleyen şebeke üyeleri hakkında, bu kez de "Suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan 5 ayrı soruşturma dosyası açıldı. Operasyon kapsamında gözaltına alınan 18 şüpheli hakkında yasal işlemler sürerken, baskın yapılan adreslerde yüklü miktarda uyuşturucu maddenin de ele geçirildiği bildirildi. Samsun'da fabrikada feci ölüm! Elektrik akımına kapılan 3 işçi hayatını kaybetti 04.06.2026 Perşembe Tırın altına ok gibi saplanan otomobilde feci kaza: 1'i ağır 2 yaralı 03.06.2026 Çarşamba Dilan Polat'ın koruması Can Polat'ın vurulma anı ortaya çıktı | VİDEO 03.06.2026 Çarşamba İstanbul'un göbeğinde yabancı uyrukluların bıçaklı kavgası | VİDEO 03.06.2026 Çarşamba Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Diyarbakır Cumhuriyet Başsavcılığı koordinesinde; Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri, uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik asrın operasyonlarından birine imza attı. Yaklaşık 8 ay süren titiz teknik ve fiziki takibin ardından, zehir ticaretinden kazandıkları paraları piyasada aklamaya çalışan 18 şüpheli kıskıvrak yakalandı. 5 Ayrı Soruşturma Dosyası Açıldı "Uyuşturucu veya uyarıcı madde imal ve ticareti" ile "2313 Sayılı Kanuna Muhalefet" suçlarını işleyen şebeke üyeleri hakkında, bu kez de "Suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan 5 ayrı soruşturma dosyası açıldı. Operasyon kapsamında gözaltına alınan 18 şüpheli hakkında yasal işlemler sürerken, baskın yapılan adreslerde yüklü miktarda uyuşturucu maddenin de ele geçirildiği bildirildi.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Yenidoğan Yoğun Bakım Ünitesinde Kötü Muamele İddiasına Soruşturma Açıldı Yenidoğan Yoğun Bakım Ünitesinde Kötü Muamele İddiasına Soruşturma Açıldı Personel Sağlık Personeli Haber NET Yenidoğan Yoğun Bakım Ünitesinde Kötü Muamele İddiasına Soruşturma Açıldı Personel Sağlık Personeli Haber NET</t>
+          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Takvim Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Giriş Tarihi: 04 Haziran 2026 09:47 Facebook X NSosyal Linki Kopyala Yazı Boyutu Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Diyarbakır Cumhuriyet Başsavcılığı koordinesinde; Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri, uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik asrın operasyonlarından birine imza attı. Yaklaşık 8 ay süren titiz teknik ve fiziki takibin ardından, zehir ticaretinden kazandıkları paraları piyasada aklamaya çalışan 18 şüpheli kıskıvrak yakalandı. 5 Ayrı Soruşturma Dosyası Açıldı "Uyuşturucu veya uyarıcı madde imal ve ticareti" ile "2313 Sayılı Kanuna Muhalefet" suçlarını işleyen şebeke üyeleri hakkında, bu kez de "Suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan 5 ayrı soruşturma dosyası açıldı. Operasyon kapsamında gözaltına alınan 18 şüpheli hakkında yasal işlemler sürerken, baskın yapılan adreslerde yüklü miktarda uyuşturucu maddenin de ele geçirildiği bildirildi. Emirhan Ceylan Takvim.com.tr Güncel Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Samsun'da fabrikada feci ölüm! Elektrik akımına kapılan 3 işçi hayatını kaybetti 04.06.2026 Perşembe Tırın altına ok gibi saplanan otomobilde feci kaza: 1'i ağır 2 yaralı 03.06.2026 Çarşamba Dilan Polat'ın koruması Can Polat'ın vurulma anı ortaya çıktı | VİDEO 03.06.2026 Çarşamba İstanbul'un göbeğinde yabancı uyrukluların bıçaklı kavgası | VİDEO 03.06.2026 Çarşamba Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu!</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOM2RReWdEMkREcW5LeFBSNUNNYko2c1dCU3NmRmU5aVZwSzlQaXlIeDdDbFVsQ0hVUFpiaG43OWo1TjZ5ek85ekYwZFFHNms0ZGUzb0pnbXExY1plSHN1TjVQTlA3TWtHN2o4cmNxMmtfTXhUTTlwUzU2NE1Ja2tDYjRHSkE2N3BwdW15ZVdkb3diT29vSVFIb2JhY3RrNGZqcmdYcXNzU2p1SFNT0gGyAUFVX3lxTE1KVkNUblRuMkw5THB1Ym5nS0xYRHZWcDVsanVnWWVFblluSGJWQ1NQb3dhUldKSkNMRi1pc0JVX2ZZX3JuZmZfWWFodml3M3B5ZFBJSUFOWkkzS2Q2NFFzVW4wX2xEZV94RThqdFo4Y0VlTzVybXRNbEtIQ1JOUERiU3VCdFMtRkFyODc4VXJmNTVoY2VLb2xvLUVNR1JJdnc4SWFZQ0NTMUFyc2JBTWlVc2c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>https://www.takvim.com.tr/video/guncel-videolari/diyarbakirda-suc-gelirlerine-kilit-18-supheli-yakalandi-otel-ve-arsalara-el-konuldu</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul | Samsun</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
@@ -6934,7 +6966,7 @@
       <c r="S47" s="2" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr"/>
@@ -6948,7 +6980,7 @@
       <c r="Y47" s="2" t="inlineStr"/>
       <c r="Z47" s="2" t="inlineStr"/>
       <c r="AA47" s="2" t="n">
-        <v>80.84</v>
+        <v>107.25</v>
       </c>
       <c r="AB47" s="2" t="n">
         <v>46</v>
@@ -6957,27 +6989,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 15:25:00</t>
+          <t>2026-06-03 11:30:50</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>lisans iptali</t>
+          <t>soruşturma</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Sanayide gizli kapaklı dönem bitti: Bildirmeyene 75 bin TL ceza ve lisans iptali!</t>
+          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sanayide gizli kapaklı dönem bitti: Bildirmeyene 75 bin TL ceza ve lisans iptali! Bu Sabah Malatya</t>
+          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Vietnam.vn</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -6987,28 +7019,28 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>sanayi</t>
+          <t>gıda</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Doğanın korunması ve sanayi tesislerinin mevzuata uygun çalışması için çevre denetim sisteminde yepyeni bir dönem başladı. Resmî Gazete’de yayımlanan karara göre, çevre danışmanlık firmaları artık sadece hizmet verdikleri şirketlerin haklarını korumakla kalmayacak, aynı zamanda devlet adına birer denetçi gibi çalışacak. Tesislerdeki çevre ihlallerini raporlarında gizleyen danışmanlık firmaları ağır yaptırımlarla karşı karşıya kalacak. CEZA PUANI VERİLECEK Yeni yasal düzenleme uyarınca çevre danışmanlık firmaları, aylık faaliyet raporlarında tespit ettikleri tüm çevre mevzuatına aykırı fiilleri Çevre, Şehircilik ve İklim Değişikliği Bakanlığına bildirmekle yükümlü kılındı. Bu bildirim yükümlülüğünü yerine getirmeyen ve aykırılıkları gizleyen firmalara ilk etapta 75 bin TL idari para cezası uygulanacak. Ayrıca bu firmalara ceza puanı verilecek; 4 yıl içinde ceza puanı 100’e ulaşanların belgeleri 180 gün süreyle askıya alınacak, 200 puana ulaşanların ise yeterlik belgeleri tamamen iptal edilecek. OTOKONTROL SİSTEMİ HAYATA GEÇTİ Bu düzenleme ile çevre danışmanlık firmalarının "danışmanlık" rollerinin yanı sıra kamusal bir denetim mekanizmasına dönüşmesi sağlandı. Fabrikaların çevre kirliliğine yol açan faaliyetlerinin örtbas edilmesinin önüne geçmeyi amaçlayan bu kanun, sanayileşirken doğanın korunması noktasında otokontrol sistemini hayata geçirmiş oldu. Sanayide gizli kapaklı dönem bitti: Bildirmeyene 75 bin TL ceza ve lisans iptali! Çevre Kanunu’nda yapılan yeni düzenlemeyle, fabrikalara ve sanayi tesislerine çevre yönetimi hizmeti sunan danışmanlık firmalarına "ihbar" zorunluluğu getirildi. Hizmet verdiği tesisin çevre mevzuatına aykırı ve kirletici faaliyetini Bakanlığa bildirmeyen firmalara 75 bin TL ceza kesilecek, usulsüzlüğe devam edenin lisansı iptal edilecek. Doğanın korunması ve sanayi tesislerinin mevzuata uygun çalışması için çevre denetim sisteminde yepyeni bir dönem başladı. Resmî Gazete’de yayımlanan karara göre, çevre danışmanlık firmaları artık sadece hizmet verdikleri şirketlerin haklarını korumakla kalmayacak, aynı zamanda devlet adına birer denetçi gibi çalışacak. Tesislerdeki çevre ihlallerini raporlarında gizleyen danışmanlık firmaları ağır yaptırımlarla karşı karşıya kalacak. Yeni yasal düzenleme uyarınca çevre danışmanlık firmaları, aylık faaliyet raporlarında tespit ettikleri tüm çevre mevzuatına aykırı fiilleri Çevre, Şehircilik ve İklim Değişikliği Bakanlığına bildirmekle yükümlü kılındı. Bu bildirim yükümlülüğünü yerine getirmeyen ve aykırılıkları gizleyen firmalara ilk etapta 75 bin TL idari para cezası uygulanacak. Ayrıca bu firmalara ceza puanı verilecek; 4 yıl içinde ceza puanı 100’e ulaşanların belgeleri 180 gün süreyle askıya alınacak, 200 puana ulaşanların ise yeterlik belgeleri tamamen iptal edilecek. OTOKONTROL SİSTEMİ HAYATA GEÇTİ Bu düzenleme ile çevre danışmanlık firmalarının "danışmanlık" rollerinin yanı sıra kamusal bir denetim mekanizmasına dönüşmesi sağlandı. Fabrikaların çevre kirliliğine yol açan faaliyetlerinin örtbas edilmesinin önüne geçmeyi amaçlayan bu kanun, sanayileşirken doğanın korunması noktasında otokontrol sistemini hayata geçirmiş oldu.</t>
+          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Vietnam.vn</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Sanayide gizli kapaklı dönem bitti: Bildirmeyene 75 bin TL ceza ve lisans iptali! Sanayide gizli kapaklı dönem bitti: Bildirmeyene 75 bin TL ceza ve lisans iptali! Bu Sabah Malatya Doğanın korunması ve sanayi tesislerinin mevzuata uygun çalışması için çevre denetim sisteminde yepyeni bir dönem başladı. Resmî Gazete’de yayımlanan karara göre, çevre danışmanlık firmaları artık sadece hizmet verdikleri şirketlerin haklarını korumakla kalmayacak, aynı zamanda devlet adına birer denetçi gibi çalışacak. Tesislerdeki çevre ihlallerini raporlarında gizleyen danışmanlık firmaları ağır yaptırımlarla karşı karşıya kalacak. CEZA PUANI VERİLECEK Yeni yasal düzenleme uyarınca çevre danışmanlık firmaları, aylık faaliyet raporlarında tespit ettikleri tüm çevre mevzuatına aykırı fiilleri Çevre, Şehircilik ve İklim Değişikliği Bakanlığına bildirmekle yükümlü kılındı. Bu bildirim yükümlülüğünü yerine getirmeyen ve aykırılıkları gizleyen firmalara ilk etapta 75 bin TL idari para cezası uygulanacak. Ayrıca bu firmalara ceza puanı verilecek; 4 yıl içinde ceza puanı 100’e ulaşanların belgeleri 180 gün süreyle askıya alınacak, 200 puana ulaşanların ise yeterlik belgeleri tamamen iptal edilecek. OTOKONTROL SİSTEMİ HAYATA GEÇTİ Bu düzenleme ile çevre danışmanlık firmalarının "danışmanlık" rollerinin yanı sıra kamusal bir denetim mekanizmasına dönüşmesi sağlandı. Fabrikaların çevre kirliliğine yol açan faaliyetlerinin örtbas edilmesinin önüne geçmeyi amaçlayan bu kanun, sanayileşirken doğanın korunması noktasında otokontrol sistemini hayata geçirmiş oldu. Sanayide gizli kapaklı dönem bitti: Bildirmeyene 75 bin TL ceza ve lisans iptali! Çevre Kanunu’nda yapılan yeni düzenlemeyle, fabrikalara ve sanayi tesislerine çevre yönetimi hizmeti sunan danışmanlık firmalarına "ihbar" zorunluluğu getirildi. Hizmet verdiği tesisin çevre mevzuatına aykırı ve kirletici faaliyetini Bakanlığa bildirmeyen firmalara 75 bin TL ceza kesilecek, usulsüzlüğe devam edenin lisansı iptal edilecek. Yeni yasal düzenleme uyarınca çevre danışmanlık firmaları, aylık faaliyet raporlarında tespit ettikleri tüm çevre mevzuatına aykırı fiilleri Çevre, Şehircilik ve İklim Değişikliği Bakanlığına bildirmekle yükümlü kılındı.</t>
+          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Vietnam.vn Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOVkp3Y2YyZG1ULVFzVjVpVjZ6cnhJNmNNT1VDcVZZZ2RJT19mV1MwcFZPNUVUYl9GS0tnck54Q29ETlVqSF9lelpCX2hIeGxNblRzNEpTRENXYWxkcHFQV0ZXci1ZeHczbGtVSWlnNzVLZzVleEd1b1QzdGF0Xy1ZYUo1RUJYTmh6d1duZ2EzQXo1MEVqM0wyVXotNG8zS0VPS25PYl9vX2QzZ2hEU2RoVW1IREfSAbQBQVVfeXFMTlZKd2NmMmRtVC1Rc1Y1aVY2enJ4STZjTU9VQ3FWWWdkSU9fZldTMHBWTzVFVGJfRktLZ3JOeENvRE5VakhfZXpaQl9oSHhsTW5UczRKU0RDV2FsZHBxUFdGV3ItWXh3M2xrVUlpZzc1S2c1ZXhHdW9UM3RhdF8tWWFKNUVCWE5oendXbmdhM0F6NTBFajNMMlV6LTRvM0tFT0tuT2Jfb19kM2doRFNkaFVtSERH?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOd0pOZmVyUTBIcklIUzd6UHhReGtvNmsyRTdYRjlTUk05MGRPVUJjYWRfN092cmNGbXR6WXZJMmRjUlgzYXo3OHBfTXNfOUtyeFBLaFlyVVFoaWFkMHIyc19ERTdaV0dIT2pMS3E5Y0ZxMGhlWjQ5UTdHSnB5cnhQNDVfMXl2UGd5bWZ1a0c0TlgtM1lGSmpjb2tQWG9kbHM?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
@@ -7034,7 +7066,7 @@
       <c r="Y48" s="2" t="inlineStr"/>
       <c r="Z48" s="2" t="inlineStr"/>
       <c r="AA48" s="2" t="n">
-        <v>96</v>
+        <v>103.22</v>
       </c>
       <c r="AB48" s="2" t="n">
         <v>47</v>
@@ -7043,27 +7075,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02 15:00:01</t>
+          <t>2026-06-03 09:38:09</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>elektronik para ve ödeme kuruluşları</t>
+          <t>gözaltı</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümle 1</t>
+          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümle 1 Donanım Günlüğü</t>
+          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Habertürk</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -7073,36 +7105,40 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>ticaret</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Genel İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümlerini Bir Araya Getiren Uygulama GenelGundemHaber Ecevit BIKTIM 2 Haziran 2026 Türkiye İş Bankası, Maximum İşyerim uygulamasını, işletmelerin ödeme alma ve POS işlemlerini tek noktadan yönetmesini sağlayacak çözümleri bir arada sunan İşPOS’a dönüştürdü. İşPOS ile işletmeler, cep telefonları üzerinden kolayca ödeme alırken tüm POS işlemlerini anlık olarak takip edebiliyor. Türkiye İş Bankası, işletmelerin dijitalleşme yolculuğuna katkı sağlamak ve ticari hayatı daha kolay ve erişilebilir hale getirmek hedefiyle mevcut Maximum İşyerim uygulamasını İşPOS’a dönüştürdü. İşPOS; kullanıcı dostu yapısıyla işletmelere POS’um Cepte, Linkle Tahsilat ve TR Karekod ile Ödeme Alma gibi farklı ödeme seçenekleri sunma esnekliği kazandırarak dijital ve hızlı ödeme alma deneyimi sunuyor. Mobil ödeme alma çözümlerinin yanı sıra uygulama üzerinden geçen işlemleri yönetme imkânı da veren İşPOS, ödeme süreçlerini kolaylaştırırken işletmelerin operasyonel yükünü azaltıyor. İşPOS’ta tüm işlemler anlık olarak görüntülenirken, POS yönetimi tek uygulamadan zahmetsizce gerçekleştirilebiliyor. İş Bankası Genel Müdür Yardımcısı Sn. Sezgin Lüle, bankacılığı yalnızca finansal bir hizmet olarak değil, müşterilerin günlük yaşamını ve ticari faaliyetlerini kolaylaştıran bütüncül bir deneyim olarak ele aldıklarını belirterek şöyle konuştu: “Teknolojiye yaptığımız yatırımlar ve yenilikçi bakış açımızla, müşterilerimizin beklentilerine hızlı, pratik ve güvenilir çözümler sunmayı önceliklendiriyoruz. Bu anlayışla, işletmelerin dijitalleşme yolculuğunu sadeleştiren ve finansal işlemleri daha hızlı ve pratik yapabilmelerine olanak tanıyan bir uygulama olarak Maximum İşyerim uygulamasını bir adım öteye taşıyarak İşPOS’u hayata geçirdik. Önümüzdeki dönemde de dijital dönüşümü destekleyen, müşteri deneyimini sürekli iyileştiren uygulamalar geliştirmeye ve ticari hayatı kolaylaştıran çözümler üretmeye devam edeceğiz.” Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi İlgili SCHLAGWORTE İş Bankası işpos Ecevit BIKTIM 2 Haziran 2026 Yazı dolaşımı Siber Casuslukta Yeni Hedefler Yapay Zekâ, Enerji Ve Savunma Sektörleri Meta’nın Yapay Zekası Hackerlara Instagram’ın Kapılarını Sonuna Kadar Açtı İnceleme Govee Table Lamp 2 Pro x JBL : Bir Masa Lambasından Çok Daha Fazlası ttec AirBeat Dream : Uyku Kalitesinde Yeni Nesil Dokunuş Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi TCL A1s : Akıllı, Kompakt ve Şık Logitech Flip Folio : Apple Magic Keyboard’a Dişli Rakip Geldi Dosya Konusu Govee Table Lamp 2 Pro x JBL : Bir Masa Lambasından Çok Daha Fazlası ttec AirBeat Dream : Uyku Kalitesinde Yeni Nesil Dokunuş Dreame Pocket : Cebinize Sığan Profesyonel Saç Tasarımcısı Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi TCL A1s : Akıllı, Kompakt ve Şık İlginizi çekebilir: Trendyol Yemek ’te MultiNet ile ödeme dönemi başlad İlginizi çekebilir Gundem PayPal tam 2.2 milyar dolara satın aldı! ABD merkezli online ödeme sistemi Paypal, piyasadaki etki alanını hızla genişletiyor. Şirket geçtiğimiz günlerde İsveçli finans teknoloji şirketi iZettle’ı tam 2.2 milyar dolara satın almaya karar verdi. Son dönemde halka açılmayı planlayan iZetlle, İsveç-Stockholm... Abdullah Özten | 20 Mayıs 2018 Genel Türk Telekom’dan İşyerim İnternette Türk Telekom esnaf ve KOBİ’lerin web sitelerinden satış yapmalarını sağlamak, işlerini büyütmelerini desteklemek için İşyerim İnternette kampanyasını hayata geçirdi. İnternette kolayca işyeri açma imkânı sağlayan İşyerim İnternette ile e-ticaret sitesi, kesintisiz internet ve sektörünün en önemli markalarından... Mutlu Çavuş | 21 Aralık 2016 Genel Hepsipay hem vakit hem de nakit kazandıracak! Hepsipay, e-ticaret platformlarına uygun ödeme çözümleri ve fırsatları ile kısa süre önce hizmet vermeye başladı. Hepsipay, Şubat 2016’da 6493 numaralı kanun kapsamında Ödeme ve Menkul Kıymet Mutabakat Sistemleri, Ödeme Hizmetleri ve Elektronik Para Kuruluşları... Ecevit BIKTIM | 07 Ekim 2016 Dosya Konusu Elleri Kullanmadan Ödeme Yapma Dönemi Başlıyor! Gelişen e-ticaret ve ticaret faktörleri markaları ve işletmeleri daimi olarak ödeme işlemlerini kolaylaştırarak müşteri yakalama olgusuna doğru itiyor. Geçtiğimiz günlerde yeni bir gelişme daha yaşandı. Bahsi geçen elleri kullanmadan ödeme yapma konusunda ki hamle... Ahmet Yasin Küçüksakal | 04 Mart 2016 Akıllı Telefon Samsung akıllı telefonları birer POS cihazına dönüşüyor Samsung sadece sunduğu üstün teknolojiye sahip ürün ve çözümleriyle değil; alanının öncü isimleriyle gerçekleştirdiği işbirlikleriyle de tüketicilerin hayatında fark yaratmayı sürdürüyor. Samsung, cep telefonları aracılığıyla kredi kartı tahsilatı yapmayı sağlayan ‘Ödeal’ uygulamasıyla özel bir... Mutlu Çavuş | 01 Eylül 2015 Genel Cepten Fatura Ödeme Dönemi Başlıyor CLK Boğaziçi Elektrik, Digiturk, Turkcell Superonline gibi kurumlarla yapılan iş birliği sayesinde, Turkcell Cüzdan kullanıcıları artık hem Turkcell faturalarını hem de bu kurumlara ait faturaları herhangi bir ödeme noktasına gitmeden cep telefonları ile ödeme... Süleyman Sertkaya | 25 Ocak 2014 Önceki Sonraki Gundem PayPal tam 2.2 milyar dolara satın aldı! ABD merkezli online ödeme sistemi Paypal, piyasadaki etki alanını hızla genişletiyor. Şirket geçtiğimiz günlerde İsveçli finans teknoloji şirketi iZettle’ı tam 2.2 milyar dolara satın almaya karar verdi. Son dönemde halka açılmayı planlayan iZetlle, İsveç-Stockholm... Abdullah Özten | 20 Mayıs 2018 Genel Türk Telekom’dan İşyerim İnternette Türk Telekom esnaf ve KOBİ’lerin web sitelerinden satış yapmalarını sağlamak, işlerini büyütmelerini desteklemek için İşyerim İnternette kampanyasını hayata geçirdi. İnternette kolayca işyeri açma imkânı sağlayan İşyerim İnternette ile e-ticaret sitesi, kesintisiz internet ve sektörünün en önemli markalarından... Mutlu Çavuş | 21 Aralık 2016 Genel Hepsipay hem vakit hem de nakit kazandıracak! Hepsipay, e-ticaret platformlarına uygun ödeme çözümleri ve fırsatları ile kısa süre önce hizmet vermeye başladı. Hepsipay, Şubat 2016’da 6493 numaralı kanun kapsamında Ödeme ve Menkul Kıymet Mutabakat Sistemleri, Ödeme Hizmetleri ve Elektronik Para Kuruluşları... Ecevit BIKTIM | 07 Ekim 2016 Dosya Konusu Elleri Kullanmadan Ödeme Yapma Dönemi Başlıyor! Gelişen e-ticaret ve ticaret faktörleri markaları ve işletmeleri daimi olarak ödeme işlemlerini kolaylaştırarak müşteri yakalama olgusuna doğru itiyor. Geçtiğimiz günlerde yeni bir gelişme daha yaşandı. Bahsi geçen elleri kullanmadan ödeme yapma konusunda ki hamle... Ahmet Yasin Küçüksakal | 04 Mart 2016 Akıllı Telefon Samsung akıllı telefonları birer POS cihazına dönüşüyor Samsung sadece sunduğu üstün teknolojiye sahip ürün ve çözümleriyle değil; alanının öncü isimleriyle gerçekleştirdiği işbirlikleriyle de tüketicilerin hayatında fark yaratmayı sürdürüyor. Samsung, cep telefonları aracılığıyla kredi kartı tahsilatı yapmayı sağlayan ‘Ödeal’ uygulamasıyla özel bir... Mutlu Çavuş | 01 Eylül 2015 Genel Cepten Fatura Ödeme Dönemi Başlıyor CLK Boğaziçi Elektrik, Digiturk, Turkcell Superonline gibi kurumlarla yapılan iş birliği sayesinde, Turkcell Cüzdan kullanıcıları artık hem Turkcell faturalarını hem de bu kurumlara ait faturaları herhangi bir ödeme noktasına gitmeden cep telefonları ile ödeme... Süleyman Sertkaya | 25 Ocak 2014 Genel İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümlerini Bir Araya Getiren Uygulama GenelGundemHaber Ecevit BIKTIM 2 Haziran 2026 Türkiye İş Bankası, Maximum İşyerim uygulamasını, işletmelerin ödeme alma ve POS işlemlerini tek noktadan yönetmesini sağlayacak çözümleri bir arada sunan İşPOS’a dönüştürdü. İşPOS ile işletmeler, cep telefonları üzerinden kolayca ödeme alırken tüm POS işlemlerini anlık olarak takip edebiliyor. Türkiye İş Bankası, işletmelerin dijitalleşme yolculuğuna katkı sağlamak ve ticari hayatı daha kolay ve erişilebilir hale getirmek hedefiyle mevcut Maximum İşyerim uygulamasını İşPOS’a dönüştürdü. İşPOS; kullanıcı dostu yapısıyla işletmelere POS’um Cepte, Linkle Tahsilat ve TR Karekod ile Ödeme Alma gibi farklı ödeme seçenekleri sunma esnekliği kazandırarak dijital ve hızlı ödeme alma deneyimi sunuyor. Mobil ödeme alma çözümlerinin yanı sıra uygulama üzerinden geçen işlemleri yönetme imkânı da veren İşPOS, ödeme süreçlerini kolaylaştırırken işletmelerin operasyonel yükünü azaltıyor. İşPOS’ta tüm işlemler anlık olarak görüntülenirken, POS yönetimi tek uygulamadan zahmetsizce gerçekleştirilebiliyor. İş Bankası Genel Müdür Yardımcısı Sn. Sezgin Lüle, bankacılığı yalnızca finansal bir hizmet olarak değil, müşterilerin günlük yaşamını ve ticari faaliyetlerini kolaylaştıran bütüncül bir deneyim olarak ele aldıklarını belirterek şöyle konuştu: “Teknolojiye yaptığımız yatırımlar ve yenilikçi bakış açımızla, müşterilerimizin beklentilerine hızlı, pratik ve güvenilir çözümler sunmayı önceliklendiriyoruz. Bu anlayışla, işletmelerin dijitalleşme yolculuğunu sadeleştiren ve finansal işlemleri daha hızlı ve pratik yapabilmelerine olanak tanıyan bir uygulama olarak Maximum İşyerim uygulamasını bir adım öteye taşıyarak İşPOS’u hayata geçirdik. Önümüzdeki dönemde de dijital dönüşümü destekleyen, müşteri deneyimini sürekli iyileştiren uygulamalar geliştirmeye ve ticari hayatı kolaylaştıran çözümler üretmeye devam edeceğiz.” Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi İlgili SCHLAGWORTE İş Bankası işpos Ecevit BIKTIM 2 Haziran 2026 Yazı dolaşımı Siber Casuslukta Yeni Hedefler Yapay Zekâ, Enerji Ve Savunma Sektörleri Meta’nın Yapay Zekası Hackerlara Instagram’ın Kapılarını Sonuna Kadar Açtı Facebook Twitter YouTube ✕ Türkiye İş Bankası, Maximum İşyerim uygulamasını, işletmelerin ödeme alma ve POS işlemlerini tek noktadan yönetmesini sağlayacak çözümleri bir arada sunan İşPOS’a dönüştürdü. İşPOS ile işletmeler, cep telefonları üzerinden kolayca ödeme alırken tüm POS işlemlerini anlık olarak takip edebiliyor. Türkiye İş Bankası, işletmelerin dijitalleşme yolculuğuna katkı sağlamak ve ticari hayatı daha kolay ve erişilebilir hale getirmek hedefiyle mevcut Maximum İşyerim uygulamasını İşPOS’a dönüştürdü. İşPOS; kullanıcı dostu yapısıyla işletmelere POS’um Cepte, Linkle Tahsilat ve TR Karekod ile Ödeme Alma gibi farklı ödeme seçenekleri sunma esnekliği kazandırarak dijital ve hızlı ödeme alma deneyimi sunuyor. Mobil ödeme alma çözümlerinin yanı sıra uygulama üzerinden geçen işlemleri yönetme imkânı da veren İşPOS, ödeme süreçlerini kolaylaştırırken işletmelerin operasyonel yükünü azaltıyor. İşPOS’ta tüm işlemler anlık olarak görüntülenirken, POS yönetimi tek uygulamadan zahmetsizce gerçekleştirilebiliyor. İş Bankası Genel Müdür Yardımcısı Sn. Sezgin Lüle, bankacılığı yalnızca finansal bir hizmet olarak değil, müşterilerin günlük yaşamını ve ticari faaliyetlerini kolaylaştıran bütüncül bir deneyim olarak ele aldıklarını belirterek şöyle konuştu: “Teknolojiye yaptığımız yatırımlar ve yenilikçi bakış açımızla, müşterilerimizin beklentilerine hızlı, pratik ve güvenilir çözümler sunmayı önceliklendiriyoruz. Bu anlayışla, işletmelerin dijitalleşme yolculuğunu sadeleştiren ve finansal işlemleri daha hızlı ve pratik yapabilmelerine olanak tanıyan bir uygulama olarak Maximum İşyerim uygulamasını bir adım öteye taşıyarak İşPOS’u hayata geçirdik. Önümüzdeki dönemde de dijital dönüşümü destekleyen, müşteri deneyimini sürekli iyileştiren uygulamalar geliştirmeye ve ticari hayatı kolaylaştıran çözümler üretmeye devam edeceğiz.” Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi İlgili İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümlerini Bir Araya Getiren Uygulama Türkiye İş Bankası, Maximum İşyerim uygulamasını, işletmelerin ödeme alma ve POS işlemlerini tek noktadan yönetmesini sağlayacak çözümleri bir arada sunan İşPOS’a dönüştürdü. İşPOS ile işletmeler, cep telefonları üzerinden kolayca ödeme alırken tüm POS işlemlerini anlık olarak takip edebiliyor. Türkiye İş Bankası, işletmelerin dijitalleşme yolculuğuna katkı sağlamak ve ticari hayatı daha kolay ve erişilebilir hale getirmek hedefiyle mevcut Maximum İşyerim uygulamasını İşPOS’a dönüştürdü. İşPOS; kullanıcı dostu yapısıyla işletmelere POS’um Cepte, Linkle Tahsilat ve TR Karekod ile Ödeme Alma gibi farklı ödeme seçenekleri sunma esnekliği kazandırarak dijital ve hızlı ödeme alma deneyimi sunuyor. Mobil ödeme alma çözümlerinin yanı sıra uygulama üzerinden geçen işlemleri yönetme imkânı da veren İşPOS, ödeme süreçlerini kolaylaştırırken işletmelerin operasyonel yükünü azaltıyor. İşPOS’ta tüm işlemler anlık olarak görüntülenirken, POS yönetimi tek uygulamadan zahmetsizce gerçekleştirilebiliyor. İş Bankası Genel Müdür Yardımcısı Sn. Sezgin Lüle, bankacılığı yalnızca finansal bir hizmet olarak değil, müşterilerin günlük yaşamını ve ticari faaliyetlerini kolaylaştıran bütüncül bir deneyim olarak ele aldıklarını belirterek şöyle konuştu: “Teknolojiye yaptığımız yatırımlar ve yenilikçi bakış açımızla, müşterilerimizin beklentilerine hızlı, pratik ve güvenilir çözümler sunmayı önceliklendiriyoruz. Bu anlayışla, işletmelerin dijitalleşme yolculuğunu sadeleştiren ve finansal işlemleri daha hızlı ve pratik yapabilmelerine olanak tanıyan bir uygulama olarak Maximum İşyerim uygulamasını bir adım öteye taşıyarak İşPOS’u hayata geçirdik. Önümüzdeki dönemde de dijital dönüşümü destekleyen, müşteri deneyimini sürekli iyileştiren uygulamalar geliştirmeye ve ticari hayatı kolaylaştıran çözümler üretmeye devam edeceğiz.” Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi</t>
+          <t>Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor 8 kişi ölmüştü... Katliam gibi kazayla ilgili firmadan açıklama! Reha Muhtar yaşamını yitirdi Ticaret Bakanlığı'ndan 7 vize şirketine inceleme Osimhen'e Premier Lig kancası! Kılıçdaroğlu talimat verdi: CHP'li tüm belediyeler denetlenecek Varsa yoksa Can Uzun! İşte G.Saray'ın teklifi 28 yıl sonra eski eşinden özür diledi Jill Biden: Eşime gelen eleştiriler karşısında yıkıldık Sivas'ta Amazon manzarası KVKK kararı ne anlama geliyor? Dünya Kupası'na en çok oyuncu gönderenler! İki genç kadının yürek yakan sonu! BES kişinin geleceğine yatırım yaptığı sistem Prens adalarının kayıp onuncu üyesi! Dünyanın en iyi yoğurtlu yemekleri! Şiddetin failine bayıltan dayak! Annesini öldürdü! Taksiye kafa attı! Avrupalı devleri geride bıraktık Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Bursa'da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor Gün Başlıyor - 1 Haziran 2026 (İstanbul'da Kanye West Rüzgarı) Bursa’nın İnegöl ilçesinde 70 ayrı adrese düzenlenen eş zamanlı uyuşturucu operasyonunda 60 şüpheli, gözaltına alındı. DHA'daki habere göre; Bursa İl Jandarma Komutanlığı Narkotik Suçlarla Mücadele Şube Müdürlüğü ekipleri, uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik çalışma başlattı. Yürütülen çalışma kapsamında, sabah saatlerinde İnegöl ilçesinde yaklaşık 70 adrese eş zamanlı operasyon düzenlendi. Operasyona 500 jandarma personeli katıldı. Adreslerde yapılan aramalarda evler ve eklentileri detaylı şekilde incelenirken, çok miktarda uyuşturucu madde ele geçirildi. Baskınlarda 60 şüpheli, gözaltına alındı. Gözaltına alınan şüphelilerin jandarmadaki işlemlerinin sürdüğü öğrenilirken, soruşturma sürüyor.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümle 1 İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümle 1 Donanım Günlüğü Genel İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümlerini Bir Araya Getiren Uygulama GenelGundemHaber Ecevit BIKTIM 2 Haziran 2026 Türkiye İş Bankası, Maximum İşyerim uygulamasını, işletmelerin ödeme alma ve POS işlemlerini tek noktadan yönetmesini sağlayacak çözümleri bir arada sunan İşPOS’a dönüştürdü. İşPOS ile işletmeler, cep telefonları üzerinden kolayca ödeme alırken tüm POS işlemlerini anlık olarak takip edebiliyor. Türkiye İş Bankası, işletmelerin dijitalleşme yolculuğuna katkı sağlamak ve ticari hayatı daha kolay ve erişilebilir hale getirmek hedefiyle mevcut Maximum İşyerim uygulamasını İşPOS’a dönüştürdü. İşPOS; kullanıcı dostu yapısıyla işletmelere POS’um Cepte, Linkle Tahsilat ve TR Karekod ile Ödeme Alma gibi farklı ödeme seçenekleri sunma esnekliği kazandırarak dijital ve hızlı ödeme alma deneyimi sunuyor. Mobil ödeme alma çözümlerinin yanı sıra uygulama üzerinden geçen işlemleri yönetme imkânı da veren İşPOS, ödeme süreçlerini kolaylaştırırken işletmelerin operasyonel yükünü azaltıyor. İşPOS’ta tüm işlemler anlık olarak görüntülenirken, POS yönetimi tek uygulamadan zahmetsizce gerçekleştirilebiliyor. İş Bankası Genel Müdür Yardımcısı Sn. Sezgin Lüle, bankacılığı yalnızca finansal bir hizmet olarak değil, müşterilerin günlük yaşamını ve ticari faaliyetlerini kolaylaştıran bütüncül bir deneyim olarak ele aldıklarını belirterek şöyle konuştu: “Teknolojiye yaptığımız yatırımlar ve yenilikçi bakış açımızla, müşterilerimizin beklentilerine hızlı, pratik ve güvenilir çözümler sunmayı önceliklendiriyoruz. Bu anlayışla, işletmelerin dijitalleşme yolculuğunu sadeleştiren ve finansal işlemleri daha hızlı ve pratik yapabilmelerine olanak tanıyan bir uygulama olarak Maximum İşyerim uygulamasını bir adım öteye taşıyarak İşPOS’u hayata geçirdik. Önümüzdeki dönemde de dijital dönüşümü destekleyen, müşteri deneyimini sürekli iyileştiren uygulamalar geliştirmeye ve ticari hayatı kolaylaştıran çözümler üretmeye devam edeceğiz.” Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi İlgili SCHLAGWORTE İş Bankası işpos Ecevit BIKTIM 2 Haziran 2026 Yazı dolaşımı Siber Casuslukta Yeni Hedefler Yapay Zekâ, Enerji Ve Savunma Sektörleri Meta’nın Yapay Zekası Hackerlara Instagram’ın Kapılarını Sonuna Kadar Açtı İnceleme Govee Table Lamp 2 Pro x JBL : Bir Masa Lambasından Çok Daha Fazlası ttec AirBeat Dream : Uyku Kalitesinde Yeni Nesil Dokunuş Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi TCL A1s : Akıllı, Kompakt ve Şık Logitech Flip Folio : Apple Magic Keyboard’a Dişli Rakip Geldi Dosya Konusu Govee Table Lamp 2 Pro x JBL : Bir Masa Lambasından Çok Daha Fazlası ttec AirBeat Dream : Uyku Kalitesinde Yeni Nesil Dokunuş Dreame Pocket : Cebinize Sığan Profesyonel Saç Tasarımcısı Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi TCL A1s : Akıllı, Kompakt ve Şık İlginizi çekebilir: Trendyol Yemek ’te MultiNet ile ödeme dönemi başlad İlginizi çekebilir Gundem PayPal tam 2.2 milyar dolara satın aldı! ABD merkezli online ödeme sistemi Paypal, piyasadaki etki alanını hızla genişletiyor. Şirket geçtiğimiz günlerde İsveçli finans teknoloji şirketi iZettle’ı tam 2.2 milyar dolara satın almaya karar verdi. Abdullah Özten | 20 Mayıs 2018 Genel Türk Telekom’dan İşyerim İnternette Türk Telekom esnaf ve KOBİ’lerin web sitelerinden satış yapmalarını sağlamak, işlerini büyütmelerini desteklemek için İşyerim İnternette kampanyasını hayata geçirdi. İnternette kolayca işyeri açma imkânı sağlayan İşyerim İnternette ile e-ticaret sitesi, kesintisiz internet ve sektörünün en önemli markalarından... Hepsipay, e-ticaret platformlarına uygun ödeme çözümleri ve fırsatları ile kısa süre önce hizmet vermeye başladı. Hepsipay, Şubat 2016’da 6493 numaralı kanun kapsamında Ödeme ve Menkul Kıymet Mutabakat Sistemleri, Ödeme Hizmetleri ve Elektronik Para Kuruluşları... Ecevit BIKTIM | 07 Ekim 2016 Dosya Konusu Elleri Kullanmadan Ödeme Yapma Dönemi Başlıyor! Gelişen e-ticaret ve ticaret faktörleri markaları ve işletmeleri daimi olarak ödeme işlemlerini kolaylaştırarak müşteri yakalama olgusuna doğru itiyor. Geçtiğimiz günlerde yeni bir gelişme daha yaşandı. Bahsi geçen elleri kullanmadan ödeme yapma konusunda ki hamle... Samsung, cep telefonları aracılığıyla kredi kartı tahsilatı yapmayı sağlayan ‘Ödeal’ uygulamasıyla özel bir... Mutlu Çavuş | 01 Eylül 2015 Genel Cepten Fatura Ödeme Dönemi Başlıyor CLK Boğaziçi Elektrik, Digiturk, Turkcell Superonline gibi kurumlarla yapılan iş birliği sayesinde, Turkcell Cüzdan kullanıcıları artık hem Turkcell faturalarını hem de bu kurumlara ait faturaları herhangi bir ödeme noktasına gitmeden cep telefonları ile ödeme... Süleyman Sertkaya | 25 Ocak 2014 Genel İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümlerini Bir Araya Getiren Uygulama GenelGundemHaber Ecevit BIKTIM 2 Haziran 2026 Türkiye İş Bankası, Maximum İşyerim uygulamasını, işletmelerin ödeme alma ve POS işlemlerini tek noktadan yönetmesini sağlayacak çözümleri bir arada sunan İşPOS’a dönüştürdü. Önümüzdeki dönemde de dijital dönüşümü destekleyen, müşteri deneyimini sürekli iyileştiren uygulamalar geliştirmeye ve ticari hayatı kolaylaştıran çözümler üretmeye devam edeceğiz.” Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi İlgili SCHLAGWORTE İş Bankası işpos Ecevit BIKTIM 2 Haziran 2026 Yazı dolaşımı Siber Casuslukta Yeni Hedefler Yapay Zekâ, Enerji Ve Savunma Sektörleri Meta’nın Yapay Zekası Hackerlara Instagram’ın Kapılarını Sonuna Kadar Açtı Facebook Twitter YouTube ✕ Türkiye İş Bankası, Maximum İşyerim uygulamasını, işletmelerin ödeme alma ve POS işlemlerini tek noktadan yönetmesini sağlayacak çözümleri bir arada sunan İşPOS’a dönüştürdü. Önümüzdeki dönemde de dijital dönüşümü destekleyen, müşteri deneyimini sürekli iyileştiren uygulamalar geliştirmeye ve ticari hayatı kolaylaştıran çözümler üretmeye devam edeceğiz.” Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi İlgili İşPOS : İş Bankası’ndan İşletmeler İçin Ödeme Çözümlerini Bir Araya Getiren Uygulama Türkiye İş Bankası, Maximum İşyerim uygulamasını, işletmelerin ödeme alma ve POS işlemlerini tek noktadan yönetmesini sağlayacak çözümleri bir arada sunan İşPOS’a dönüştürdü. Önümüzdeki dönemde de dijital dönüşümü destekleyen, müşteri deneyimini sürekli iyileştiren uygulamalar geliştirmeye ve ticari hayatı kolaylaştıran çözümler üretmeye devam edeceğiz.” Logitech MX Master 4 : Üretkenlik Dünyasının Yeni Amiral Gemisi</t>
+          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Habertürk Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Şüphelilerin jandarmadaki işlemleri sürüyor 8 kişi ölmüştü... Katliam gibi kazayla ilgili firmadan açıklama! Reha Muhtar yaşamını yitirdi Ticaret Bakanlığı'ndan 7 vize şirketine inceleme Osimhen'e Premier Lig kancası! Kılıçdaroğlu talimat verdi: CHP'li tüm belediyeler denetlenecek Varsa yoksa Can Uzun! İşte G.Saray'ın teklifi 28 yıl sonra eski eşinden özür diledi Jill Biden: Eşime gelen eleştiriler karşısında yıkıldık Sivas'ta Amazon manzarası KVKK kararı ne anlama geliyor? Dünya Kupası'na en çok oyuncu gönderenler! Avrupalı devleri geride bıraktık Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Bursa'da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Şüphelilerin jandarmadaki işlemleri sürüyor Gün Başlıyor - 1 Haziran 2026 (İstanbul'da Kanye West Rüzgarı) Bursa’nın İnegöl ilçesinde 70 ayrı adrese düzenlenen eş zamanlı uyuşturucu operasyonunda 60 şüpheli, gözaltına alındı. DHA'daki habere göre; Bursa İl Jandarma Komutanlığı Narkotik Suçlarla Mücadele Şube Müdürlüğü ekipleri, uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik çalışma başlattı. Yürütülen çalışma kapsamında, sabah saatlerinde İnegöl ilçesinde yaklaşık 70 adrese eş zamanlı operasyon düzenlendi. Operasyona 500 jandarma personeli katıldı. Adreslerde yapılan aramalarda evler ve eklentileri detaylı şekilde incelenirken, çok miktarda uyuşturucu madde ele geçirildi. Baskınlarda 60 şüpheli, gözaltına alındı. Gözaltına alınan şüphelilerin jandarmadaki işlemlerinin sürdüğü öğrenilirken, soruşturma sürüyor.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9VSmhtT25pcDhBOHdYWXVOTllwbnAwLWpFaDBMcHJNbHdZcF9nemVFcHZqWTVaaHBDbk9vU1ZFN0RmSHR1RmotOTNtTUxtcHQ2WlNuZWhWYkF5Zk5kLV9lclZPR1B2V3p5el9pMUw3TTNEbFhtaTJSYS1wZ2NQNU0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
+          <t>https://www.haberturk.com/son-dakika-bursada-uyusturucu-ticareti-operasyonu-60-gozalti-3889008</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | İstanbul | Sivas | Tekirdağ | Van</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>İnegöl | Saray</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -7110,7 +7146,7 @@
       <c r="S49" s="2" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr"/>
@@ -7124,7 +7160,7 @@
       <c r="Y49" s="2" t="inlineStr"/>
       <c r="Z49" s="2" t="inlineStr"/>
       <c r="AA49" s="2" t="n">
-        <v>58.25</v>
+        <v>75.75</v>
       </c>
       <c r="AB49" s="2" t="n">
         <v>48</v>

--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,22 +512,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:27:08</t>
+          <t>2026-06-04 14:40:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon</t>
+          <t>İstanbul'da Korkutan Yangın! Esenyurt'ta İki Katlı Fabrika Alev Alev Yanıyor! İşte Olay Yerinden İlk Detaylar!</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Canlı Gaste</t>
+          <t>İstanbul'da Korkutan Yangın! Esenyurt'ta İki Katlı Fabrika Alev Alev Yanıyor! İşte Olay Yerinden İlk Detaylar! politikam.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -537,12 +537,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır | İzmir</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Çeşme</t>
+          <t>Esenyurt | Fatih</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -556,22 +556,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:05:00</t>
+          <t>2026-06-05 08:20:38</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu</t>
+          <t>Banka hesabındaki dekont notu ortaya çıktı: ROK'un 'katmanlama' oyunu... '50 binin yüzde 178'i'</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu birgun.net</t>
+          <t>Banka hesabındaki dekont notu ortaya çıktı: ROK'un 'katmanlama' oyunu... '50 binin yüzde 178'i' Odatv</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -579,16 +579,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Diyarbakır | İzmir</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Çeşme</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
@@ -600,22 +592,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:34:00</t>
+          <t>2026-06-04 09:55:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın</t>
+          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com</t>
+          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Malatya Güncel</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -623,8 +615,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Silivri</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 02:50:00</t>
+          <t>2026-06-04 12:42:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı</t>
+          <t>Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Evrensel.net</t>
+          <t>Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Mersin Haber</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -661,34 +661,26 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Bursa | İstanbul</t>
+          <t>Mersin | Samsun | Şanlıurfa</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Osmangazi | Küçükçekmece</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Ağaç AŞ</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>İSTANBUL AĞAÇ A.Ş</t>
-        </is>
-      </c>
+          <t>Atakum | Haliliye</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:11:56</t>
+          <t>2026-06-04 12:55:19</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -698,12 +690,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi</t>
+          <t>Şanlıurfa'da Depo Yangını: İtfaiye Ekipleri Hızla Müdahale Etti</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Haberler</t>
+          <t>Şanlıurfa'da Depo Yangını: İtfaiye Ekipleri Hızla Müdahale Etti Haber365</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -711,7 +703,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Şanlıurfa</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
@@ -724,7 +720,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 05:38:26</t>
+          <t>2026-06-04 12:32:42</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -734,12 +730,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bursa Haberleri</t>
+          <t>Mobilya deposunda yangın paniği</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bursa Haberleri - Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü - Yerel Haberler Hürriyet</t>
+          <t>Mobilya deposunda yangın paniği Gazette.com.tr</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -747,28 +743,20 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Torun Geri Dönüşüm - Küçükbalıklı Hurda Kağıt Alımı</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:18:00</t>
+          <t>2026-06-04 18:42:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -778,12 +766,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını!</t>
+          <t>Kocaeli Karamürsel'de Yangın! Yumurta Deposu Kül Oldu</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını! Ege'de Sonsöz</t>
+          <t>Kocaeli Karamürsel'de Yangın! Yumurta Deposu Kül Oldu politikam.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -793,14 +781,18 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Denizli</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Karamürsel</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Denizli Kauçuk</t>
+          <t>Birlik Yumurta</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -812,7 +804,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 02:27:59</t>
+          <t>2026-06-04 13:21:15</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -822,12 +814,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri</t>
+          <t>Yeni Delhi’de Otel Yangını: En Az 21 Ölü, Çok Sayıda Yaralı</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri bolgegundemi.com</t>
+          <t>Yeni Delhi’de Otel Yangını: En Az 21 Ölü, Çok Sayıda Yaralı Turizm Gazetesi</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -835,11 +827,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
@@ -852,22 +840,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:18:00</t>
+          <t>2026-06-04 17:38:32</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu</t>
+          <t>Eskişehir Organize Sanayi Bölgesi’nde fabrika yangını</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Amed Haber</t>
+          <t>Eskişehir Organize Sanayi Bölgesi’nde fabrika yangını havadis.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -877,26 +865,30 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır | İzmir</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Çeşme</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:00:00</t>
+          <t>2026-06-05 06:02:02</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -906,12 +898,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15 milyar liralık kara para ağı! Hepsine el konuldu</t>
+          <t>24 ilde kara para operasyonu: 350 milyon liralık mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15 milyar liralık kara para ağı! Hepsine el konuldu babaocagi.com.tr</t>
+          <t>24 ilde kara para operasyonu: 350 milyon liralık mal varlığına el konuldu Doviz.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -921,41 +913,45 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır | İzmir</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Çeşme</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Forinvest Yazılım ve Teknolojileri Hizmetleri A.Ş</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ForInvest Yazılım ve Teknoloji Hizmetleri A.Ş</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:25:29</t>
+          <t>2026-06-04 16:00:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu</t>
+          <t>Bankalardan milyonlarca kişiye kritik uyarı</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN</t>
+          <t>Bankalardan milyonlarca kişiye kritik uyarı Manisa Kulis Haber</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -976,22 +972,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:07:14</t>
+          <t>2026-06-04 11:00:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu</t>
+          <t>Bankalardan müşterilere kritik uyarı..!</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber</t>
+          <t>Bankalardan müşterilere kritik uyarı..! Düzcenin Sesi</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -999,11 +995,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Diyarbakır</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1016,22 +1008,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:17:45</t>
+          <t>2026-06-04 12:42:00</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı</t>
+          <t>Banka hesabını kullandıranlar dikkat! Bankalar uyarıyor: Hapis cezasına kadar gidiyor!</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv</t>
+          <t>Banka hesabını kullandıranlar dikkat! Bankalar uyarıyor: Hapis cezasına kadar gidiyor! Türk İnform</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1052,22 +1044,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:19:00</t>
+          <t>2026-06-04 23:22:40</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu</t>
+          <t>Muhittin Böcek ile oğlu ve gelininin mal varlıklarına el konuldu</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu STAR - Haberler</t>
+          <t>Muhittin Böcek ile oğlu ve gelininin mal varlıklarına el konuldu TRT Haber</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1077,14 +1069,10 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Denizli | Malatya</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Kale</t>
-        </is>
-      </c>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
@@ -1096,22 +1084,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 17:21:00</t>
+          <t>2026-06-05 05:47:49</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü</t>
+          <t>Bahis gelirlerini aklayan İstanbul merkezli suç ağına darbe! Milyonlarca liralık mal varlığına el konuldu: 80 gözaltı</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü İnegöl Online</t>
+          <t>Bahis gelirlerini aklayan İstanbul merkezli suç ağına darbe! Milyonlarca liralık mal varlığına el konuldu: 80 gözaltı Takvim</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1121,14 +1109,10 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl</t>
-        </is>
-      </c>
+          <t>İstanbul | Yalova</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
@@ -1140,22 +1124,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:48:14</t>
+          <t>2026-06-05 07:06:28</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı</t>
+          <t>11 şirkete el konuldu! 24 ilde yasa dışı bahis operasyonu: 80 gözaltı</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7</t>
+          <t>11 şirkete el konuldu! 24 ilde yasa dışı bahis operasyonu: 80 gözaltı Bizim Tv</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1163,8 +1147,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Bursa</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Yıldırım</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
@@ -1176,22 +1168,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:41:40</t>
+          <t>2026-06-04 09:29:00</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı.</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Vietnam.vn</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu Sosyal TV</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1199,7 +1191,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1212,22 +1208,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:30:00</t>
+          <t>2026-06-04 17:34:00</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı</t>
+          <t>UYUŞTURUCU PARASINI AKLIYORLARDI: 15 MİLYAR TL'LİK MAL VARLIĞINA EL KONULDU</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi</t>
+          <t>UYUŞTURUCU PARASINI AKLIYORLARDI: 15 MİLYAR TL'LİK MAL VARLIĞINA EL KONULDU Haber Alternatif</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1248,22 +1244,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 14:41:37</t>
+          <t>2026-06-04 15:13:55</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi</t>
+          <t>Siirt’te Telefonlara Peş Peşe Aynı Mesaj Geldi: Bankalardan “Hesabınızı Kullandırmayın” Uyarısı</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi Foreks.com</t>
+          <t>Siirt’te Telefonlara Peş Peşe Aynı Mesaj Geldi: Bankalardan “Hesabınızı Kullandırmayın” Uyarısı siirthaberci.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1271,28 +1267,24 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Siirt</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Akın Tekstil A.Ş</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>AKIN TEKSTİL</t>
-        </is>
-      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:30:00</t>
+          <t>2026-06-04 09:41:34</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1302,12 +1294,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı</t>
+          <t>Banka hesabına 1 trilyon lira geldi, hayatı kabusa döndü: Bu süreç iflasıma neden olabilir</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı Kanal 46</t>
+          <t>Banka hesabına 1 trilyon lira geldi, hayatı kabusa döndü: Bu süreç iflasıma neden olabilir SonDakika</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1317,7 +1309,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş</t>
+          <t>Balıkesir | Van</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1332,22 +1324,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:44:00</t>
+          <t>2026-06-04 11:05:34</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor</t>
+          <t>Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor Mavi Marmara Gazetesi</t>
+          <t>Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu avazturk.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1357,7 +1349,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli</t>
+          <t>Balıkesir | Hatay | Malatya</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1372,22 +1364,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:47:15</t>
+          <t>2026-06-05 07:12:00</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon!</t>
+          <t>Kapaklı OSB’de korkutan baca yangını ucuz atlatıldı</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! GDH.Digital</t>
+          <t>Kapaklı OSB’de korkutan baca yangını ucuz atlatıldı Trakya Gazetesi</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1395,8 +1387,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Kapaklı</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
@@ -1408,22 +1408,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:49:41</t>
+          <t>2026-06-04 13:57:00</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor!</t>
+          <t>Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! EmlakDream</t>
+          <t>Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi Milliyet</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1431,8 +1431,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Elazığ | İstanbul | Manisa</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Yıldırım | Başakşehir | Esenyurt | Sarıyer</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
@@ -1444,22 +1452,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 17:54:22</t>
+          <t>2026-06-05 00:00:00</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı</t>
+          <t>Fabrika Yangını: Fırın Bölümü Alev Aldı</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT</t>
+          <t>Fabrika Yangını: Fırın Bölümü Alev Aldı Kırşehir Çiğdem</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1480,22 +1488,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 04:11:41</t>
+          <t>2026-06-04 18:07:33</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi</t>
+          <t>Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası</t>
+          <t>Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1503,8 +1511,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Aydın | Düzce | İstanbul | Kırıkkale | Konya</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Bozdoğan | Nazilli | Alaca | Küçükçekmece</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
@@ -1516,22 +1532,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:08:15</t>
+          <t>2026-06-05 07:10:41</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>İzmirli üç medikal şirkete konkordato uzatması</t>
+          <t>Nazilli'de Geri Dönüşüm Fabrikasında Yangın</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi</t>
+          <t>Nazilli'de Geri Dönüşüm Fabrikasında Yangın SonDakika</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1539,8 +1555,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Aydın</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Nazilli</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
@@ -1552,22 +1576,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:12:35</t>
+          <t>2026-06-04 18:19:00</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı</t>
+          <t>Mersin'de Fabrika Yangını: İtfaiye Söndürdü, İş Yeri Kullanılamaz Halde</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com</t>
+          <t>Mersin'de Fabrika Yangını: İtfaiye Söndürdü, İş Yeri Kullanılamaz Halde politikam.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1575,7 +1599,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1588,22 +1616,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:50:38</t>
+          <t>2026-06-04 09:46:39</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün</t>
+          <t>Denizli’de Fabrika Yangını: Geriye Bu Görüntüler Kaldı</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün Merhaba Gazetesi</t>
+          <t>Denizli’de Fabrika Yangını: Geriye Bu Görüntüler Kaldı Denizli Sanal Basın</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1613,7 +1641,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1628,22 +1656,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 14:41:47</t>
+          <t>2026-06-04 15:54:26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı</t>
+          <t>Esenyurt’taki fabrika yangınından dönen itfaiye aracı devrildi: 3 yaralı</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri</t>
+          <t>Esenyurt’taki fabrika yangınından dönen itfaiye aracı devrildi: 3 yaralı TGRT Haber</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1664,7 +1692,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 15:46:28</t>
+          <t>2026-06-05 06:41:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1674,12 +1702,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı</t>
+          <t>Hürmüz kriziyle havada iflas korkusu</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365</t>
+          <t>Hürmüz kriziyle havada iflas korkusu İstanbul Ticaret Gazetesi</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1689,18 +1717,26 @@
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:45:31</t>
+          <t>2026-06-04 09:48:03</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1710,12 +1746,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu</t>
+          <t>Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu velev.press</t>
+          <t>Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti Patronlar Dünyası</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1725,30 +1761,22 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Battal Holding A.Ş</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Battal Group</t>
-        </is>
-      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:24:46</t>
+          <t>2026-06-05 07:50:18</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1758,12 +1786,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı</t>
+          <t>Bursa'da geri dönüşüm firması için iflas sürecinde kritik aşama! Sıra cetveli ilan edildi...</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı Samanyolu Haber</t>
+          <t>Bursa'da geri dönüşüm firması için iflas sürecinde kritik aşama! Sıra cetveli ilan edildi... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1773,7 +1801,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Bursa</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1788,7 +1816,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 15:49:03</t>
+          <t>2026-06-05 06:25:00</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1798,12 +1826,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor</t>
+          <t>Bursa'da konkordato dosyalarında kritik gün: Bir şirkete iflas, diğerine ek süre</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi</t>
+          <t>Bursa'da konkordato dosyalarında kritik gün: Bir şirkete iflas, diğerine ek süre Bursada Bugün</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1811,35 +1839,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Mattaş Endüstriyel Mutfak Sanayi A.Ş | Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Mattaş Endüstriyel Mutfak</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:39:17</t>
+          <t>2026-06-04 21:00:00</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay</t>
+          <t>Arz yönlü şoklarda kalkınma bankalarını düşünmek</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber</t>
+          <t>Arz yönlü şoklarda kalkınma bankalarını düşünmek Ekonomim</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1860,22 +1900,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:28:00</t>
+          <t>2026-06-04 12:26:00</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı</t>
+          <t>Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı Cumhuriyet</t>
+          <t>Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1885,33 +1925,41 @@
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Battal Holding A.Ş</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>BATTAL Holding A.Ş</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:00</t>
+          <t>2026-06-04 14:57:00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın</t>
+          <t>BİST’te işlem gören şirketin sahibinin oğlu payını sıfırladı, 22 gün sonra konkordato ilan edildi!</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber</t>
+          <t>BİST’te işlem gören şirketin sahibinin oğlu payını sıfırladı, 22 gün sonra konkordato ilan edildi! Elips Haber</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1921,45 +1969,37 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Bitlis</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Organize Sanayi</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Bitlis Organize Sanayi Bölgesi</t>
-        </is>
-      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 22:06:29</t>
+          <t>2026-06-04 16:41:00</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi.</t>
+          <t>Maden ocağında yangın faciası: Direnişteki işçilerin can güvenliği hiçe sayıldı!</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Vietnam.vn</t>
+          <t>Maden ocağında yangın faciası: Direnişteki işçilerin can güvenliği hiçe sayıldı! Haber Hürriyeti</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1967,8 +2007,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Edirne</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Uzunköprü</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
@@ -1980,22 +2028,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:32:00</t>
+          <t>2026-06-05 06:33:34</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek</t>
+          <t>Buca Belediyesi'nde skandal operasyon: Rüşvet, usulsüzlük ve 'bankamatikçi' vurgunu ortaya çıktı</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek sonhaber.eu</t>
+          <t>Buca Belediyesi'nde skandal operasyon: Rüşvet, usulsüzlük ve 'bankamatikçi' vurgunu ortaya çıktı Haberhergün</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2003,35 +2051,51 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Buca</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Boğaziçi A.Ş</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Boğaziçi Kuyumculuk</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:38:00</t>
+          <t>2026-06-04 21:07:04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi</t>
+          <t>Sri Lanka'da bakımevinde yangın: 12 kişi öldü, işletme sahibi gözaltında</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen</t>
+          <t>Sri Lanka'da bakımevinde yangın: 12 kişi öldü, işletme sahibi gözaltında Euronews.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2039,11 +2103,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Van</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2056,22 +2116,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 15:26:35</t>
+          <t>2026-06-05 06:48:00</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü?</t>
+          <t>Altın Kiraz’da çeyrek final biletleri sahiplerini buldu: Cenksan Yangın ve Maçka Otomotiv devrede!</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri</t>
+          <t>Altın Kiraz’da çeyrek final biletleri sahiplerini buldu: Cenksan Yangın ve Maçka Otomotiv devrede! Çağdaş Kocaeli Gazetesi</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2079,8 +2139,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Kiraz</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
@@ -2092,22 +2160,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 13:28:43</t>
+          <t>2026-06-05 06:21:38</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Sürekli banka kartı kullananlar yandı</t>
+          <t>İzmir’in çevre karnesi: Yangın, rant ve enerji baskısı</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sürekli banka kartı kullananlar yandı Sözcü Gazetesi</t>
+          <t>İzmir’in çevre karnesi: Yangın, rant ve enerji baskısı İlkses Gazetesi</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2115,7 +2183,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2128,22 +2200,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 13:33:47</t>
+          <t>2026-06-04 20:50:09</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu!</t>
+          <t>Mersin'de otomatik kepenk üretimi yapan işletmede çıkan yangın söndürüldü</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! Erzincan Birlik Medya</t>
+          <t>Mersin'de otomatik kepenk üretimi yapan işletmede çıkan yangın söndürüldü Habername.com</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2151,8 +2223,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Tarsus</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
@@ -2164,22 +2244,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:14:00</t>
+          <t>2026-06-04 18:14:00</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var</t>
+          <t>Şanlıurfa'da Motosiklet Deposunda Yangın: Her Şey Küle Döndü</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com</t>
+          <t>Şanlıurfa'da Motosiklet Deposunda Yangın: Her Şey Küle Döndü urfadasin.com</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2189,14 +2269,10 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Esenyurt</t>
-        </is>
-      </c>
+          <t>Şanlıurfa</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
@@ -2208,22 +2284,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:31:16</t>
+          <t>2026-06-05 07:13:17</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede!</t>
+          <t>Bursa Milletvekili Pala'dan, sağlık kuruluşlarında yangın riskine yönelik bakanlığa uyarı</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans</t>
+          <t>Bursa Milletvekili Pala'dan, sağlık kuruluşlarında yangın riskine yönelik bakanlığa uyarı Başka Gazete</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2231,7 +2307,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Gaziantep | İstanbul</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2244,22 +2324,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:50:00</t>
+          <t>2026-06-04 15:57:00</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Yedi vize şirketine soruşturma</t>
+          <t>Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Yedi vize şirketine soruşturma Memurlar.Net</t>
+          <t>Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2269,37 +2349,45 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İstanbul | Rize</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Efor Holding AŞ</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>EFOR HOLDİNG</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:47:24</t>
+          <t>2026-06-04 17:57:55</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu!</t>
+          <t>Futbolcu Uğurcan Bekçi cinayetinde yasa dışı bahis izi: Kiralık banka hesabı anlaşmazlığı</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Takvim</t>
+          <t>Futbolcu Uğurcan Bekçi cinayetinde yasa dışı bahis izi: Kiralık banka hesabı anlaşmazlığı Takvim</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2309,10 +2397,14 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır | İstanbul | Samsun</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>İzmit</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
@@ -2324,22 +2416,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:30:50</t>
+          <t>2026-06-05 04:21:04</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı.</t>
+          <t>Say Yenilenebilir Enerji'ye vergi cezası</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Vietnam.vn</t>
+          <t>Say Yenilenebilir Enerji'ye vergi cezası RHA Ajans</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2349,33 +2441,41 @@
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Say</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:38:09</t>
+          <t>2026-06-05 00:19:16</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı</t>
+          <t>3 yıl veya daha uzun süredir kullanılmayan banka hesapları kapatılabilir: Mali dolandırıcılığı önlemek için riskli hesaplar üzerindeki kontroller sıkılaştırılıyor.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Habertürk</t>
+          <t>3 yıl veya daha uzun süredir kullanılmayan banka hesapları kapatılabilir: Mali dolandırıcılığı önlemek için riskli hesaplar üzerindeki kontroller sıkılaştırılıyor. Vietnam.vn</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2383,16 +2483,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Bursa | İstanbul | Sivas | Tekirdağ | Van</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl | Saray</t>
-        </is>
-      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
@@ -2401,8 +2493,400 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:29:46</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>SPK’dan bir aracı kurum sahibine 6 ay işlem yasağı</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>SPK’dan bir aracı kurum sahibine 6 ay işlem yasağı Banka Dünyası</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 10:10:00</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Kara Para / MASAK / Bahis</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Hesabına kaynağı belirsiz 1 trilyon lira geçti: MASAK hesaplarını dondurdu</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Hesabına kaynağı belirsiz 1 trilyon lira geçti: MASAK hesaplarını dondurdu Cumhuriyet</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Balıkesir | Van</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 10:17:00</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Ahmad Jahangard Takalo Kimdir, Kaç Yaşında, Nereli, Ne İş Yapıyor? Banka Hesabındaki 1 Trilyon Lira Olayı Nedir?</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Ahmad Jahangard Takalo Kimdir, Kaç Yaşında, Nereli, Ne İş Yapıyor? Banka Hesabındaki 1 Trilyon Lira Olayı Nedir? Urfanatik</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 10:52:06</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Banka Hesabında 1 Trilyon Lira Gördü! Yaşadığı Şok Gündem Oldu</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Banka Hesabında 1 Trilyon Lira Gördü! Yaşadığı Şok Gündem Oldu yenidevirgazetesi.com</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:08:45</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>ABD’nin Dev Bankaları 2027’de Yeni Bir Blockchain Girişimi Başlatmaya Hazırlanıyor! İşte Detaylar</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>ABD’nin Dev Bankaları 2027’de Yeni Bir Blockchain Girişimi Başlatmaya Hazırlanıyor! İşte Detaylar Bitcoin Sistemi</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 06:55:00</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>6 aylık takip Şanlıurfa'da şebekenin sonu oldu; Banka ve kripto ağına darbe!</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>6 aylık takip Şanlıurfa'da şebekenin sonu oldu; Banka ve kripto ağına darbe! Şanlıurfa Gazetesi</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Nevşehir | Şanlıurfa</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 06:11:00</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Çeyrek asırlık banka satıldı! Arkasındaki isim tanıdık çıktı</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Çeyrek asırlık banka satıldı! Arkasındaki isim tanıdık çıktı Internet Haber</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:59:00</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding Banka Sahibi Oldu İşte Detaylar</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding Banka Sahibi Oldu İşte Detaylar Çay Haber</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding | Efor Holding AŞ</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Efor Çay San. Tic. A.Ş. Marmara Bölge Müdürlüğü</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:18:14</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Kaçak tütün ticareti yapan şebekeye operasyon: 22 gözaltı</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Kaçak tütün ticareti yapan şebekeye operasyon: 22 gözaltı DHA | Demirören Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Adıyaman | İstanbul</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:11:57</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Ankara’da kaçakçılara darbe! Araçtan çıkanlar şaşkına çevirdi! Ünlü markaların taklitleriyle ticaret yapıyorlardı! 3 gözaltı</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Ankara’da kaçakçılara darbe! Araçtan çıkanlar şaşkına çevirdi! Ünlü markaların taklitleriyle ticaret yapıyorlardı! 3 gözaltı Sabah</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Ankara | Samsun</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Atakum</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J49"/>
+  <autoFilter ref="A1:J59"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2452,6 +2936,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2463,7 +2957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB49"/>
+  <dimension ref="A1:AB59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2641,27 +3135,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:27:08</t>
+          <t>2026-06-04 14:40:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>banka soruşturma</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon</t>
+          <t>İstanbul'da Korkutan Yangın! Esenyurt'ta İki Katlı Fabrika Alev Alev Yanıyor! İşte Olay Yerinden İlk Detaylar!</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Canlı Gaste</t>
+          <t>İstanbul'da Korkutan Yangın! Esenyurt'ta İki Katlı Fabrika Alev Alev Yanıyor! İşte Olay Yerinden İlk Detaylar! politikam.com</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2671,18 +3165,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>mal varlığı</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Yerel Haberler Yayınlanma: 04 Haziran 2026 - 09:27 Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Yerel Haberler 04 Haziran 2026 - 09:27 TAKİP ET Dinle A Büyüt A Küçült Diyarbakır Haberleri — Diyarbakır'da uyuşturucu suçundan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon düzenlendi. ​​​​​​​Valilikten yapılan açıklamada, Diyarbakır Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında, Terörizmin Finansmanı ve Aklama Suçları Soruşturma Bürosu koordinesinde, İl Jandarma Komutanlığı, Jandarma Genel Komutanlığı Kaçakçılık ve Organize Suçlarla Mücadele (KOM) ve Narkotik Suçlarla Mücadele daire başkanlıkları ekiplerince, uyuşturucu veya uyarıcı madde imal ve ticareti ile kullanımına yönelik operasyonların devam ettiği bildirildi. Bu kapsamda uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama, yasa dışı kenevir ekimi ve tohumu temin etme, yasa dışı ekimi kolaylaştırma ve kenevir ekiminden elde ettikleri uyuşturucu maddeyi ülke genelinde piyasaya sürerek haksız kazanç elde eden ve çeşitli yöntemlerle parayı mal varlığı edinmeye dönüştürerek suç gelirlerini aklama suçlarını işleyenlere yönelik çalışma yürütüldüğü ifade edilen açıklamada, elde ettikleri uyuşturucuları Diyarbakır ve diğer illere sevk ederek ülkede uyuşturucu madde kullanımının artmasına neden olan, uyuşturucu imal ve ticareti yaparak haksız kazanç elde eden, elde ettikleri haksız kazançları (kara parayı) çeşitli yöntemlerle aklayarak finansal sisteme aktaran ve böylece hem vatandaşları zehirleyen hem de ülkenin finansal sistemine zarar verenlerin yakalanabilmesi ve faaliyetlerine son verilmesi amacıyla 8 aylık kapsamlı ve titiz çalışmalar yürütüldüğü belirtildi. Açıklamada, şunlar kaydedildi: Diyarbakır'da 'uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama' ve '2313 sayılı Kanun'a muhalefet' öncül suçlarından haksız kazanç elde ederek kendi adına ve birlikte yaşadığı aile fertleri veya bağlantılı oldukları üçüncü şahıslar adına taşınır veya taşınmaz mal varlığı edindiği değerlendirilen şüpheliler hakkında yapılan araştırma neticesinde TCK-282 suçtan kaynaklanan mal varlığı değerlerini aklama suçu kapsamında 5 soruşturma dosyası açılarak 18 şüpheli hakkında soruşturma başlatılmıştır. Soruşturma kapsamında, İl Jandarma Komutanlığı ekiplerince uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama ve 2313 sayılı Kanun'a muhalefet öncül suçlarını işleyen ve suçtan kaynaklanan mal varlığı değerlerini aklama suçuna karıştıkları tespit edilen 18 şüpheliye yönelik operasyon düzenlendiği bildirilen açıklamada, şunlar aktarıldı: Operasyonda 18 şüpheli hakkında gerekli yasal işlemler yapılarak fazla miktarda uyuşturucu madde ele geçirilmiştir. Ayrıca bu şahıslara ait İzmir'in Çeşme ilçesinde faaliyet gösteren dört yıldızlı otel, 3 özel halk otobüsü ve hatları, 2 ticari taksi ve hatları, Diyarbakır'da bulunan toplam 970 dönümlük 109 arsa ve tarla, Çeşme ilçesinde bulunan 9 dönümlük arsa, 7 araç, 33 daire, 4 dükkan, 128 banka hesabı olmak üzere piyasa değeri yaklaşık 15 milyar lira değerinde olan mal varlığına yönelik el koyma işlemi yapılmıştır. # Diyarbakır # İzmir # kara para # operasyon # uyuşturucu EDİTÖR Anadolu Ajansı Anadolu Ajansı haberleri, son da</t>
+          <t>Son dakika Esenyurt yangın haberi! Fatih Mahallesi 19 Mayıs Bulvarı üzerindeki fabrikada çıkan yangına müdahale sürüyor. İşte ilk bilgiler! Son dakika Esenyurt yangın haberi! Fatih Mahallesi 19 Mayıs Bulvarı üzerindeki fabrikada çıkan yangına müdahale sürüyor. İşte ilk bilgiler! Son dakika Esenyurt yangın haberi! Fatih Mahallesi 19 Mayıs Bulvarı üzerindeki fabrikada çıkan yangına müdahale sürüyor. İşte ilk bilgiler! İstanbul'da Korkutan Yangın! Esenyurt'ta İki Katlı Fabrika Alev Alev Yanıyor! İşte Olay Yerinden İlk Detaylar! Son dakika Esenyurt yangın haberi! Fatih Mahallesi 19 Mayıs Bulvarı üzerindeki fabrikada çıkan yangına müdahale sürüyor. İşte ilk bilgiler! Kevser Yoldaş Editör 04.06.2026 - 17:40 Yayınlanma 2 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Son Dakika: İstanbul Esenyurt'ta Dev Fabrika Yangını! Olay Yerine Çok Sayıda Ekip Sevk Edildi! İstanbul'un en yoğun sanayi ve üretim merkezlerinden biri olan Esenyurt ilçesinden korkutan bir son dakika haberi geldi. Edinilen bilgilere göre, Esenyurt'ta faaliyet gösteren iki katlı bir fabrikada henüz belirlenemeyen bir nedenle yangın çıktı. Kısa sürede büyüyen alevler fabrikanın büyük bir bölümünü sararken, gökyüzünü kaplayan yoğun dumanlar çevre ilçelerden de çıplak gözle görülebiliyor. Peki, Esenyurt'taki yangın nerede çıktı, hangi fabrikada yangın var? Can kaybı veya yaralı var mı? Esenyurt Fatih Mahallesi 19 Mayıs Bulvarı'nda Korkutan Dakikalar! Korkutan yangın, İstanbul Esenyurt ilçesi Fatih Mahallesi 19 Mayıs Bulvarı üzerinde konumlanan hidrofor tankı üretimi yapılan iki katlı bir fabrikada meydana geldi. Fabrika binasından yükselen alevleri ve dumanları gören işçiler ile çevredeki vatandaşlar büyük panik yaşadı. Durumun hemen bildirilmesi üzerine bölgeye adeta ekip yağdı. İhbarın ardından olay yerine İstanbul'un çevre ilçelerinden de destek olmak üzere çok sayıda itfaiye, polis ve sağlık ekibi sevk edildi. Polis ekipleri fabrikanın çevresinde geniş güvenlik önlemleri alarak bulvarı trafiğe kapatırken, sağlık ekipleri de olası bir dumandan etkilenme veya yaralanma ihtimaline karşı hazır bekletiliyor. İtfaiye Ekiplerinin Yoğun Müdahalesi Sürüyor İki katlı fabrikanın içerisindeki yanıcı maddelerin de etkisiyle alevlerin kontrol altına alınması için itfaiye erleri yoğun bir mesai harcıyor. Fabrikanın hidrofor tankı üretimi yapması nedeniyle içeride patlama riskine karşı ekiplerin son derece titiz ve koordineli bir şekilde yangına müdahale ettiği öğrenildi. Yangının çıkış nedeni henüz netlik kazanmazken, söndürme çalışmalarının tamamlanmasının ardından kundaklama, elektrik kontağı veya üretim hatası ihtimalleri üzerine geniş çaplı bir inceleme başlatılacağı belirtildi. Yangında ilk belirlemelere göre herhangi bir can kaybı veya yaralanma olup olmadığına dair resmi makamlardan henüz net bir açıklama yapılmadı. Kaynak: Anadolu Ajansı Editör Kevser Yoldaş Bunlar da ilgin</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Canlı Gaste Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Yerel Haberler Yayınlanma: 04 Haziran 2026 - 09:27 Diyarbakır'da suçtan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon Diyarbakır — Operasyonda, yaklaşık 15 milyar lira değerindeki otel, araç, arsa, tarla, daire ile banka hesaplarına el konuldu Yerel Haberler 04 Haziran 2026 - 09:27 TAKİP ET Dinle A Büyüt A Küçült Diyarbakır Haberleri — Diyarbakır'da uyuşturucu suçundan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon düzenlendi. ​​​​​​​Valilikten yapılan açıklamada, Diyarbakır Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında, Terörizmin Finansmanı ve Aklama Suçları Soruşturma Bürosu koordinesinde, İl Jandarma Komutanlığı, Jandarma Genel Komutanlığı Kaçakçılık ve Organize Suçlarla Mücadele (KOM) ve Narkotik Suçlarla Mücadele daire başkanlıkları ekiplerince, uyuşturucu veya uyarıcı madde imal ve ticareti ile kullanımına yönelik operasyonların devam ettiği bildirildi. Bu kapsamda uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama, yasa dışı kenevir ekimi ve tohumu temin etme, yasa dışı ekimi kolaylaştırma ve kenevir ekiminden elde ettikleri uyuşturucu maddeyi ülke genelinde piyasaya sürerek haksız kazanç elde eden ve çeşitli yöntemlerle parayı mal varlığı edinmeye dönüştürerek suç gelirlerini aklama suçlarını işleyenlere yönelik çalışma yürütüldüğü ifade edilen açıklamada, elde ettikleri uyuşturucuları Diyarbakır ve diğer illere sevk ederek ülkede uyuşturucu madde kullanımının artmasına neden olan, uyuşturucu imal ve ticareti yaparak haksız kazanç elde eden, elde ettikleri haksız kazançları (kara parayı) çeşitli yöntemlerle aklayarak finansal sisteme aktaran ve böylece hem vatandaşları zehirleyen hem de ülkenin finansal sistemine zarar verenlerin yakalanabilmesi ve faaliyetlerine son verilmesi amacıyla 8 aylık kapsamlı ve titiz çalışmalar yürütüldüğü belirtildi. Açıklamada, şunlar kaydedildi: Diyarbakır'da 'uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama' ve '2313 sayılı Kanun'a muhalefet' öncül suçlarından haksız kazanç elde ederek kendi adına ve birlikte yaşadığı aile fertleri veya bağlantılı oldukları üçüncü şahıslar adına taşınır veya taşınmaz mal varlığı edindiği değerlendirilen şüpheliler hakkında yapılan araştırma neticesinde TCK-282 suçtan kaynaklanan mal varlığı değerlerini aklama suçu kapsamında 5 soruşturma dosyası açılarak 18 şüpheli hakkında soruşturma başlatılmıştır. Soruşturma kapsamında, İl Jandarma Komutanlığı ekiplerince uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama ve 2313 sayılı Kanun'a muhalefet öncül suçlarını işleyen ve suçtan kaynaklanan mal varlığı değerlerini aklama suçuna karıştıkları tespit edilen 18 şüpheliye yönelik operasyon düzenlendiği bildirilen açıklamada, şunlar aktarıldı: Operasyonda 18 şüpheli hakkında gerekli yasal işlemler yapılarak fazla miktarda uyuşturucu madde ele geçirilmiştir. Ayrıca bu şahıslara ait İzmir'in Çeşme ilçesinde faaliyet gösteren dört yıldızlı otel, 3 özel halk otobüsü ve hatları, 2 ticari taksi ve hatları, Diyarbakır'da bulunan toplam 970 dönümlük 109 arsa ve tarla, Çeşme ilçesinde bulunan 9 dönümlük arsa, 7 araç, 33 daire, 4 dükkan, 128 banka hesabı olmak üzere piyasa değeri yaklaşık 15 milyar lira değerinde olan mal varlığına yönelik el koyma işlemi yapılmıştır. # Diyarbakır # İzmir # kara para # operasyon # uyuşturucu EDİTÖR Anadolu Ajansı Anadolu Ajansı haberleri, son da</t>
+          <t>İstanbul'da Korkutan Yangın! Esenyurt'ta İki Katlı Fabrika Alev Alev Yanıyor! İşte Olay Yerinden İlk Detaylar! İstanbul'da Korkutan Yangın! Esenyurt'ta İki Katlı Fabrika Alev Alev Yanıyor! İşte Olay Yerinden İlk Detaylar! politikam.com Son dakika Esenyurt yangın haberi! Fatih Mahallesi 19 Mayıs Bulvarı üzerindeki fabrikada çıkan yangına müdahale sürüyor. İstanbul'da Korkutan Yangın! Esenyurt'ta İki Katlı Fabrika Alev Alev Yanıyor! İşte Olay Yerinden İlk Detaylar!</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -2692,21 +3190,29 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.canligaste.com/diyarbakir-da-suctan-kaynaklanan-mal-varligini-akladigi-tespit-edilen-18-supheliye-yonelik-operasyon/857018/</t>
+          <t>https://www.politikam.com/istanbulda-korkutan-yangin-esenyurtta-iki-katli-fabrika-alev-alev-yaniyor-iste-olay-yerinden-ilk-detaylar</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır | İzmir</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Çeşme</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+          <t>Esenyurt | Fatih</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Fatih Mahallesi</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Fatih Mahallesi 19 Mayıs Bulvarı</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
@@ -2726,7 +3232,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -2735,27 +3241,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:05:00</t>
+          <t>2026-06-05 08:20:38</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>kara para</t>
+          <t>MASAK raporu</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu</t>
+          <t>Banka hesabındaki dekont notu ortaya çıktı: ROK'un 'katmanlama' oyunu... '50 binin yüzde 178'i'</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu birgun.net</t>
+          <t>Banka hesabındaki dekont notu ortaya çıktı: ROK'un 'katmanlama' oyunu... '50 binin yüzde 178'i' Odatv</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2765,40 +3271,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>el konuldu, mal varlığı</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>banka, banka hesabı</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. İstanbul Ankara İzmir Adana Adıyaman Afyon Ağrı Aksaray Amasya Antalya Ardahan Artvin Aydın Balıkesir Bartın Batman Bayburt Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Düzce Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Iğdır Isparta Mersin K.Maraş Karabük Karaman Kars Kastamonu Kayseri Kırıkkale Kırklareli Kırşehir Kilis Kocaeli Konya Kütahya Malatya Manisa Mardin Muğla Muş Nevşehir Niğde Ordu Osmaniye Rize Sakarya Samsun Siirt Sinop Sivas Şırnak Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yalova Yozgat Zonguldak 23° Parçalı Az Bulutlu Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. Güncel 04.06.2026 09:05 Giriş: 04.06.2026 09:05 Güncelleme: 04.06.2026 09:32 Kaynak: ANKA A- A A+ Fotoğraf: AA (Arşiv) BirGün'ü Google'da favori kaynak olarak tanımlayın. Tıkla ve anında ekle Diyarbakır 'da uyuşturucu suçundan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon düzenlendi. ​​​​​​​Valilikten yapılan açıklamada, Diyarbakır Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında, Terörizmin Finansmanı ve Aklama Suçları Soruşturma Bürosu koordinesinde, İl Jandarma Komutanlığı, Jandarma Genel Komutanlığı Kaçakçılık ve Organize Suçlarla Mücadele (KOM) ve Narkotik Suçlarla Mücadele daire başkanlıkları ekiplerince, uyuşturucu veya uyarıcı madde imal ve ticareti ile kullanımına yönelik operasyonların devam ettiği bildirildi. Bu kapsamda "uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama", "yasa dışı kenevir ekimi ve tohumu temin etme", "yasa dışı ekimi kolaylaştırma ve kenevir ekiminden elde ettikleri uyuşturucu maddeyi ülke genelinde piyasaya sürerek haksız kazanç elde eden ve çeşitli yöntemlerle parayı mal varlığı edinmeye dönüştürerek suç gelirlerini aklama" suçlarını işleyenlere yönelik çalışma yürütüldüğü ifade edilen açıklamada, elde ettikleri uyuşturucuları Diyarbakır ve diğer illere sevk ederek ülkede uyuşturucu madde kullanımının artmasına neden olan, uyuşturucu imal ve ticareti yaparak haksız kazanç elde eden, elde ettikleri haksız kazançları (kara parayı) çeşitli yöntemlerle aklayarak finansal sisteme aktaran ve böylece hem vatandaşları zehirleyen hem de ülkenin finansal sistemine zarar verenlerin yakalanabilmesi ve faaliyetlerine son verilmesi amacıyla 8 aylık kapsamlı ve titiz çalışmalar yürütüldüğü belirtildi. VALİLİKTEN AÇIKLAMA Açıklamada, şunlar kaydedildi: "Diyarbakır'da 'uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama' ve '2313 sayılı Kanun'a muhalefet' öncül suçlarından haksız kazanç elde ederek kendi adına ve birlikte yaşadığı aile fertleri veya bağlantılı oldukları üçüncü şahıslar adına taşınır veya taşınmaz mal varlığı edindiği değerlendirilen şüpheliler hakkında yapılan araştırma neticesinde TCK-282 suçtan kaynaklanan mal varlığı değerlerini aklama suçu kapsamında 5 soruşturma dosyası açılarak 18 şüpheli hakkında soruşturma başlatılmıştır." Soruşturma kapsamında, İl Jandarma Komutanlığı ekiplerince "uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama" ve "2313 sayılı Kanun'a muhalefet" öncül suçlarını işleyen ve "suçtan kaynaklanan mal varlığı değerlerini aklama" suçuna karıştıkları tespit edilen 18 şüpheliye yönelik operasyon düzenlendiği bildirilen açıklamada, şunlar aktarıldı: "Operasyonda 18 şüpheli hakkında gerekli yasal işlemler yapılarak fazla miktarda uyuşturucu madde ele geçirilmiştir. Ayrıca bu şahıslara ait İzmir'in Çeşme ilçesinde faaliyet gösteren dört yıldızlı otel, 3 özel halk otobüsü ve hatları, 2 ticari taksi ve hatları, Diyarbakır'da bulunan toplam 970 dönümlük 109 arsa ve tarla, Çeşme ilçesinde bulunan 9 dönümlük arsa, 7 araç, 33 daire, 4 dükkan, 128 banka hesabı olmak üzere piyasa değeri yaklaşık 15 milyar lira değerinde olan mal varlığına yönelik el koyma işlemi yapılmıştır." #uyuşturucu #operasyon #diyarbakır #el koyma #mal varlığı #gözaltı Sıradak</t>
+          <t>Banka hesabındaki dekont notu ortaya çıktı: ROK'un 'katmanlama' oyunu... '50 binin yüzde 178'i' Odatv</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu birgun.net Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. 8 aylık takip sonucu başlatılan soruşturmada, paranın 4 yıldızlı otellerden halk otobüsü hatlarına, yüzlerce dönüm arsadan lüks dairelere kadar aklandığı belirlendi. İstanbul Ankara İzmir Adana Adıyaman Afyon Ağrı Aksaray Amasya Antalya Ardahan Artvin Aydın Balıkesir Bartın Batman Bayburt Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Düzce Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Iğdır Isparta Mersin K.Maraş Karabük Karaman Kars Kastamonu Kayseri Kırıkkale Kırklareli Kırşehir Kilis Kocaeli Konya Kütahya Malatya Manisa Mardin Muğla Muş Nevşehir Niğde Ordu Osmaniye Rize Sakarya Samsun Siirt Sinop Sivas Şırnak Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yalova Yozgat Zonguldak 23° Parçalı Az Bulutlu Diyarbakır'da uyuşturucu ve kara para operasyonu: 15 milyar lira değerinde mal varlığına el konuldu Diyarbakır merkezli uyuşturucu ve karapara operasyonunda, elde edilen 15 milyar TL değerindeki mal varlığına el konuldu. Güncel 04.06.2026 09:05 Giriş: 04.06.2026 09:05 Güncelleme: 04.06.2026 09:32 Kaynak: ANKA A- A A+ Fotoğraf: AA (Arşiv) BirGün'ü Google'da favori kaynak olarak tanımlayın. Tıkla ve anında ekle Diyarbakır 'da uyuşturucu suçundan kaynaklanan mal varlığını akladığı tespit edilen 18 şüpheliye yönelik operasyon düzenlendi. ​​​​​​​Valilikten yapılan açıklamada, Diyarbakır Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında, Terörizmin Finansmanı ve Aklama Suçları Soruşturma Bürosu koordinesinde, İl Jandarma Komutanlığı, Jandarma Genel Komutanlığı Kaçakçılık ve Organize Suçlarla Mücadele (KOM) ve Narkotik Suçlarla Mücadele daire başkanlıkları ekiplerince, uyuşturucu veya uyarıcı madde imal ve ticareti ile kullanımına yönelik operasyonların devam ettiği bildirildi. Bu kapsamda "uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama", "yasa dışı kenevir ekimi ve tohumu temin etme", "yasa dışı ekimi kolaylaştırma ve kenevir ekiminden elde ettikleri uyuşturucu maddeyi ülke genelinde piyasaya sürerek haksız kazanç elde eden ve çeşitli yöntemlerle parayı mal varlığı edinmeye dönüştürerek suç gelirlerini aklama" suçlarını işleyenlere yönelik çalışma yürütüldüğü ifade edilen açıklamada, elde ettikleri uyuşturucuları Diyarbakır ve diğer illere sevk ederek ülkede uyuşturucu madde kullanımının artmasına neden olan, uyuşturucu imal ve ticareti yaparak haksız kazanç elde eden, elde ettikleri haksız kazançları (kara parayı) çeşitli yöntemlerle aklayarak finansal sisteme aktaran ve böylece hem vatandaşları zehirleyen hem de ülkenin finansal sistemine zarar verenlerin yakalanabilmesi ve faaliyetlerine son verilmesi amacıyla 8 aylık kapsamlı ve titiz çalışmalar yürütüldüğü belirtildi. VALİLİKTEN AÇIKLAMA Açıklamada, şunlar kaydedildi: "Diyarbakır'da 'uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama' ve '2313 sayılı Kanun'a muhalefet' öncül suçlarından haksız kazanç elde ederek kendi adına ve birlikte yaşadığı aile fertleri veya bağlantılı oldukları üçüncü şahıslar adına taşınır veya taşınmaz mal varlığı edindiği değerlendirilen şüpheliler hakkında yapılan araştırma neticesinde TCK-282 suçtan kaynaklanan mal varlığı değerlerini aklama suçu kapsamında 5 soruşturma dosyası açılarak 18 şüpheli hakkında soruşturma başlatılmıştır." Soruşturma kapsamında, İl Jandarma Komutanlığı ekiplerince "uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama" ve "2313 sayılı Kanun'a muhalefet" öncül suçlarını işleyen ve "suçtan kaynaklanan mal varlığı değerlerini aklama" suçuna karıştıkları tespit edilen 18 şüpheliye yönelik operasyon düzenlendiği bildirilen açıklamada, şunlar aktarıldı: "Operasyonda 18 şüpheli hakkında gerekli yasal işlemler yapılarak fazla miktarda uyuşturucu madde ele geçirilmiştir. Ayrıca bu şahıslara ait İzmir'in Çeşme ilçesinde faaliyet gösteren dört yıldızlı otel, 3 özel halk otobüsü ve hatları, 2 ticari taksi ve hatları, Diyarbakır'da bulunan toplam 970 dönümlük 109 arsa ve tarla, Çeşme ilçesinde bulunan 9 dönümlük arsa, 7 araç, 33 daire, 4 dükkan, 128 banka hesabı olmak üzere piyasa değeri yaklaşık 15 milyar lira değerinde olan mal varlığına yönelik el koyma işlemi yapılmıştır." #uyuşturucu #operasyon #diyarbakır #el koyma #mal varlığı #gözaltı Sıradak</t>
+          <t>Banka hesabındaki dekont notu ortaya çıktı: ROK'un 'katmanlama' oyunu... '50 binin yüzde 178'i' Banka hesabındaki dekont notu ortaya çıktı: ROK'un 'katmanlama' oyunu... '50 binin yüzde 178'i' Odatv Banka hesabındaki dekont notu ortaya çıktı: ROK'un 'katmanlama' oyunu... '50 binin yüzde 178'i' Odatv</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.birgun.net/haber/diyarbakir-da-uyusturucu-ve-kara-para-operasyonu-15-milyar-lira-degerinde-mal-varligina-el-konuldu-716349</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Diyarbakır | İzmir</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Çeşme</t>
-        </is>
-      </c>
+          <t>https://www.odatv.com/guncel/rasim-ozan-kutahyali-masak-raporu-parayi-nasil-aklayacagini-dekont-aciklamasina-yazmis-katmanlama-oyunu-120148916</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -2806,7 +3308,7 @@
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
@@ -2820,7 +3322,7 @@
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="n">
-        <v>136</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>2</v>
@@ -2829,27 +3331,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:34:00</t>
+          <t>2026-06-04 09:55:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>para aklama</t>
+          <t>MASAK raporu</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın</t>
+          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com</t>
+          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Malatya Güncel</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2859,36 +3361,40 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com</t>
+          <t>Silivri’de hayvan barınağı sorumlusu ve ‘Silivri Canları 2. Hayat Melekleri’ adlı derneğin MASAK raporu ortaya çıktı. Rapor’da derneğin hesaplarına 2021-2024 yılları arasında 37 Milyar 323 Milyon 777 Bin 21 TL tutarında para girişinin old... Silivri’de hayvan barınağı sorumlusu ve ‘Silivri Canları 2. Hayat Melekleri’ adlı derneğin MASAK raporu ortaya çıktı. Rapor’da derneğin hesaplarına 2021-2024 yılları arasında 37 Milyar 323 Milyon 777 Bin 21 TL tutarında para girişinin old... Silivri’de hayvan barınağı sorumlusu ve ‘Silivri Canları 2. Hayat Melekleri’ adlı derneğin MASAK raporu ortaya çıktı. Rapor’da derneğin hesaplarına 2021-2024 yılları arasında 37 Milyar 323 Milyon 777 Bin 21 TL tutarında para girişinin old...</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com Ziraat Bankası'ndan Müşterilere Kritik Uyarı: Hesaplarınızı Başkalarına Kullandırmayın kurtalangazetesi.com</t>
+          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Malatya Güncel Silivri’de hayvan barınağı sorumlusu ve ‘Silivri Canları 2. Hayat Melekleri’ adlı derneğin MASAK raporu ortaya çıktı. Rapor’da derneğin hesaplarına 2021-2024 yılları arasında 37 Milyar 323 Milyon 777 Bin 21 TL tutarında para girişinin old...</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNelBSVXlkY21jWlZtSVdxQzJ0cS1qM1BFay1TRTRUTTRlbjVWeXBWNzBZYl96elNBMWhuRWl5M2JSMnNrMTNPTzN1eXpiLXNETTVndFZHWEFxQXZPLTlEbkdEdk15VXFqby1BZDI0UGYxUkxGYUJVUXpSWHdFMTlDQll4YjdRRlNzXzItWENNdDBiTkRrUVk4dmJndDdZN0xCM1JROFRjbWItWko0clZLREtKR0N5bXIwY1VHdzNua0dCbFQtUmtrOXpsMDdfU2tWQ0czNTlqUzdtUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>https://www.malatyaguncel.com/silivride-hayvan-barinagi-adi-altinda-vurgun-yapan-dernegin-masak-raporu-ortaya-2600247h.htm</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Silivri</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -2896,7 +3402,7 @@
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr"/>
@@ -2910,7 +3416,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="n">
-        <v>76.81999999999999</v>
+        <v>119.5</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>3</v>
@@ -2919,12 +3425,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 02:50:00</t>
+          <t>2026-06-04 12:42:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2934,12 +3440,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı</t>
+          <t>Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Evrensel.net</t>
+          <t>Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Mersin Haber</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2949,18 +3455,22 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. 04.06.2026 05:50 Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Fotoğraf: DHA Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 05:50 Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Fotoğraf: DHA Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 22:03 Ağaç AŞ işçileri, işlerini geri istiyor Güvenlik soruşturması gerekçesiyle işten çıkarılan İBB’ye bağlı Ağaç AŞ işçileri işe iadelerini istedi. İçerik yükleniyor... (İşçi Sendika Servisi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 23:47 Emniyet ve vergi düzenlemeleri içeren kanun teklifi komisyondan geçti Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. Fotoğraf: ANKA İçerik yükleniyor... (ANKA) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 19:05 TBMM'de 'mutlak butlan' protestosu TBMM Genel Kurulunda 'mutlak butlan' kararının araştırılması amacıyla verilen önergenin görüşmeleri sırasında CHP grubu, AKP'li Adalet Komisyonu Başkanı Cüneyt Yüksel'i sıralara vurarak protesto etti. Fotoğraf: ANKA İçerik yükleniyor... (ANKA) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 03:04 / Güncelleme: 03:25 Meksika'da grevdeki öğretmenler Eğitim Bakanlığını bastı Meksika'da Dünya Kupası açılışına 10 gün kala çalışma koşullarının iyileştirilmesi talebiyle süresiz greve çıkan öğretmenler, dün başkentte Eğitim Bakanlığı binasını bastı. Fotoğraf: AA İçerik yükleniyor... (Dış Haberler) Devamını Oku Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 01:04 'Devlet, patronlar işçinin hakkını daha rahat yesin diye seferber oluyor' EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Fotoğraf: Evrensel İçerik yükleniyor... (Evrensel) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Fotoğraf: DHA Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin Güvenlik soruşturması gerekçesiyle işten çıkarılan İBB’ye bağlı Ağaç AŞ işçileri işe iadelerini istedi. Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. Fotoğraf: ANKA TBMM Genel Kurulunda 'mutlak butlan' kararının araştırılması amacıyla verilen önergenin görüşmeleri sırasında CHP grubu, AKP'li Adalet Komisyonu Başkanı Cüneyt Yüksel'i sıralara vurarak protesto etti. Fotoğraf: ANKA Meksika'da Dünya Kupası açılışına 10 gün kala çalışma koşullarının iyileştirilmesi talebiyle süresiz greve çıkan öğretmenler, dün başkentte Eğitim Bakanlığı binasını bastı. Fotoğraf: AA EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Fotoğraf: Evrensel Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) İçerik yükleniyor... (İşçi Sendika Servisi) İçerik yükleniyor... (ANKA) İçerik yükleniyor... (Dış Haberler) Devamını Oku İçerik yükleniyor... (Evrensel) Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Ağaç AŞ işçileri, işlerini geri istiyor Emniyet ve vergi düzenlemeleri içeren kanun teklifi komisyondan geçti Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. TBMM'de 'mutlak butlan' protestosu TBMM Genel Kurulunda 'mutlak butlan' kararının araştırılması amacıyla verilen önergenin görüşmeleri sırasında CHP grubu, AKP'li Adalet Komisyonu Başkanı Cüneyt Yüksel'i sıralara vurarak protesto etti. Meksika'da grevdeki öğretmenler Eğitim Bakanlığını bastı Meksika'da Dünya Kupası açılışına 10 gün kala çalışma koşullarının iyileştirilmesi talebiyle süresiz greve çıkan öğretmenler, dün başkentte Eğitim Bakanlığı binasını bastı. 'Devlet, patronlar işçinin hakkını daha rahat yesin diye seferber oluyor' EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Önemli haberlerden ve gelişmelerden haberdar olmak ister misiniz?</t>
+          <t>Mersin'den haberiniz olsun! Mersin ve ilçelerinden son dakika ve önemli haberler, gelişmeler olayları sunar. Şanlıurfa Haliliye'de bir depoda meydana gelen yangın, itfaiye ekiplerini harekete geçirdi. Olay, öğle saatlerinde Kamberiye Mahallesi'nde yaşandı. Mersin'den haberiniz olsun! Mersin ve ilçelerinden son dakika ve önemli haberler, gelişmeler olayları sunar. Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Haber Merkezi • 04 Haziran 2026 15:42 • Güncellendi: 04 Haziran 2026 15:45 Şanlıurfa Haliliye'de bir depoda meydana gelen yangın, itfaiye ekiplerini harekete geçirdi. Olay, öğle saatlerinde Kamberiye Mahallesi'nde yaşandı. Şanlıurfa Haliliye'de bir depoda meydana gelen yangın, itfaiye ekiplerini harekete geçirdi. Olay, öğle saatlerinde Kamberiye Mahallesi'nde yaşandı. Facebook X WhatsApp 20sa 2dk önce Edinilen bilgilere göre, yangın, Haliliye ilçesine bağlı Kamberiye Mahallesi Seyfettin Sucu Sokak'ta, giriş katında bulunan bir depoda, henüz belirlenemeyen bir sebepten dolayı başladı. Yangını gören mahalle sakinleri, durumu hemen yetkililere bildirdi. Olay yerine intikal eden itfaiye ekipleri, yangına müdahale ederek alevleri kontrol altına aldı. Yangın, ekiplerin hızlı müdahalesi sayesinde söndürüldü ancak çeşitli maddi hasara yol açtı. Yangının çıkış sebebiyle ilgili araştırmalar sürerken, ekipler olay yerinde detaylı incelemeler yapıyor. Yangının büyümesine engel olunması, itfaiye ekiplerinin etkin müdahalesiyle mümkün oldu. Yerel halk, müdahale sırasında ekiplerin hızlı davranışları için teşekkürlerini iletti. Samsun Atakum'da 19 Mayıs Stadyumu'nda Bakım ve Onarım Çalışmaları Başladı Samsun'da Prostat Kanseri Tedavisindeki Gecikmenin Sonuçları Üzerine Bilgilendirme Şanlıurfa Kaynak: Mersin Haber + IHA İlgili Haberler Edinilen bilgilere göre, yangın, Haliliye ilçesine bağlı Kamberiye Mahallesi Seyfettin Sucu Sokak'ta, giriş katında bulunan bir depoda, henüz belirlenemeyen bir sebepten dolayı başladı. Yangını gören mahalle sakinleri, durumu hemen yetkililere bildirdi. Olay yerine intikal eden itfaiye ekipleri, yangına müdahale ederek alevleri kontrol altına aldı. Yangın, ekiplerin hızlı müdahalesi sayesinde söndürüldü ancak çeşitli maddi hasara yol açtı. Yangının çıkış sebebiyle ilgili araştırmalar sürerken, ekipler olay yerinde detaylı incelemeler yapıyor. Yangının büyümesine engel olunması, itfaiye ekiplerinin etkin müdahalesiyle mümkün oldu. Yerel halk, müdahale sırasında ekiplerin hızlı davranışları için teşekkürlerini iletti. Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Haber Merkezi • 04 Haziran 2026 15:42 • Güncellendi: 04 Haziran 2026 15:45 Şanlıurfa Haliliye'de bir depoda meydana gelen yangın, itfaiye ekiplerini harekete geçirdi. Olay, öğle saatlerinde Kamberiye Mahallesi'nde yaşandı. Haber Merkezi • 04 Haziran 2026 15:42 • Güncellendi: 04 Haziran 2026 15:45 Şanlıurfa Haliliye'de bir depoda meydana gelen yangın, itfaiye ekiplerini harekete geçirdi. Olay, öğle saatlerinde Kamberiye Mahallesi'nde yaşandı. Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Edinilen bilgilere göre, yangın, Haliliye ilçesine bağlı Kamberiye Mahallesi Seyfettin Sucu Sokak'ta, giriş katında bulunan bir depoda, henüz belirlenemeyen bir sebepten dolayı başladı. Yangını gören mahalle sakinleri, durumu hemen yetkililere bildirdi. Olay yerine intikal eden itfaiye ekipleri, yangına müdahale ederek alevleri kontrol altına aldı. Yangın, ekiplerin hızlı müdahalesi sayesinde söndürüldü ancak çeşitli maddi hasara yol açtı. Yangının çıkış sebebiyle ilgili araştırmalar sürerken, ekipler olay yerinde detaylı incelemeler yapıyor. Yangının büyümesine engel olunması, itfaiye ekiplerinin etkin müdahalesiyle mümkün oldu. Yerel halk, müdahale sırasında ekiplerin hızlı davranışları için teşekkürlerini iletti.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Evrensel.net Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. 04.06.2026 05:50 Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Fotoğraf: DHA Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. DHA'da yer alan habere göre, Küçükbalıklı Mahallesi’ndeki bir geri dönüşüm tesisinde saat 01.30 sularında yangın çıktı. Alevler kısa sürede büyürken, tesiste zaman zaman küçük çaplı patlamalar meydana geldi. Yangın, itfaiyenin müdahalesiyle kısa sürede kontrol altına alınıp söndürüldü. Yangında ölen ya da yaralanan olmazken, geri dönüşüm tesisinde zarar meydana geldi. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 05:50 Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 22:03 Ağaç AŞ işçileri, işlerini geri istiyor Güvenlik soruşturması gerekçesiyle işten çıkarılan İBB’ye bağlı Ağaç AŞ işçileri işe iadelerini istedi. (İşçi Sendika Servisi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 03.06.2026 23:47 Emniyet ve vergi düzenlemeleri içeren kanun teklifi komisyondan geçti Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. (Dış Haberler) Devamını Oku Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin 04.06.2026 01:04 'Devlet, patronlar işçinin hakkını daha rahat yesin diye seferber oluyor' EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. (Evrensel) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin Güvenlik soruşturması gerekçesiyle işten çıkarılan İBB’ye bağlı Ağaç AŞ işçileri işe iadelerini istedi. Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. Fotoğraf: AA EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Fotoğraf: Evrensel Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü. Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü (Haber Merkezi) İçerik yükleniyor... (İşçi Sendika Servisi) İçerik yükleniyor... (Evrensel) Küçükçekmece'de geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa'da geri dönüşüm tesisinde yangın: Zaman zaman patlamalar yaşandı Bursa'nın Osmangazi ilçesinde gece saatlerinde bir geri dönüşüm tesisinde çıkan ve patlamalara yol açan yangın söndürüldü. Ağaç AŞ işçileri, işlerini geri istiyor Emniyet ve vergi düzenlemeleri içeren kanun teklifi komisyondan geçti Emniyet ve vergi düzenlemeleri içeren kanun teklifi Plan ve Bütçe Komisyonu'ndan geçti, basın yayın ilkeleri düzenlemesi ise geri çekildi. Meksika'da grevdeki öğretmenler Eğitim Bakanlığını bastı Meksika'da Dünya Kupası açılışına 10 gün kala çalışma koşullarının iyileştirilmesi talebiyle süresiz greve çıkan öğretmenler, dün başkentte Eğitim Bakanlığı binasını bastı. 'Devlet, patronlar işçinin hakkını daha rahat yesin diye seferber oluyor' EMEP Milletvekili Sevda Karaca, BİRTEK-SEN Genel Başkanı Mehmet Türkmen, KESK Yöneticileri Sevgi Yılmaz ve Bülent Türkmen ile EMEP Ankara İl Başkanı Rüstem Kahraman, Doruk Madencilik işçilerini ziyaret etti. Bursa - Osmangazi ilçesindeki bir geri dönüşüm tesisinde çıkan yangın söndürüldü.</t>
+          <t>Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Mersin Haber Mersin'den haberiniz olsun! Şanlıurfa Haliliye'de bir depoda meydana gelen yangın, itfaiye ekiplerini harekete geçirdi. Olay, öğle saatlerinde Kamberiye Mahallesi'nde yaşandı. Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Haber Merkezi • 04 Haziran 2026 15:42 • Güncellendi: 04 Haziran 2026 15:45 Şanlıurfa Haliliye'de bir depoda meydana gelen yangın, itfaiye ekiplerini harekete geçirdi. Facebook X WhatsApp 20sa 2dk önce Edinilen bilgilere göre, yangın, Haliliye ilçesine bağlı Kamberiye Mahallesi Seyfettin Sucu Sokak'ta, giriş katında bulunan bir depoda, henüz belirlenemeyen bir sebepten dolayı başladı. Yangını gören mahalle sakinleri, durumu hemen yetkililere bildirdi. Olay yerine intikal eden itfaiye ekipleri, yangına müdahale ederek alevleri kontrol altına aldı. Yangın, ekiplerin hızlı müdahalesi sayesinde söndürüldü ancak çeşitli maddi hasara yol açtı. Yangının çıkış sebebiyle ilgili araştırmalar sürerken, ekipler olay yerinde detaylı incelemeler yapıyor. Yangının büyümesine engel olunması, itfaiye ekiplerinin etkin müdahalesiyle mümkün oldu. Yerel halk, müdahale sırasında ekiplerin hızlı davranışları için teşekkürlerini iletti. Samsun Atakum'da 19 Mayıs Stadyumu'nda Bakım ve Onarım Çalışmaları Başladı Samsun'da Prostat Kanseri Tedavisindeki Gecikmenin Sonuçları Üzerine Bilgilendirme Şanlıurfa Kaynak: Mersin Haber + IHA İlgili Haberler Edinilen bilgilere göre, yangın, Haliliye ilçesine bağlı Kamberiye Mahallesi Seyfettin Sucu Sokak'ta, giriş katında bulunan bir depoda, henüz belirlenemeyen bir sebepten dolayı başladı. Haber Merkezi • 04 Haziran 2026 15:42 • Güncellendi: 04 Haziran 2026 15:45 Şanlıurfa Haliliye'de bir depoda meydana gelen yangın, itfaiye ekiplerini harekete geçirdi. Şanlıurfa Haliliye'de Depoda Çıkan Yangın İtfaiye Ekiplerini Alarm Durumuna Geçirdi Edinilen bilgilere göre, yangın, Haliliye ilçesine bağlı Kamberiye Mahallesi Seyfettin Sucu Sokak'ta, giriş katında bulunan bir depoda, henüz belirlenemeyen bir sebepten dolayı başladı.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2970,73 +3480,45 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.evrensel.net/haber/5986860/bursada-geri-donusum-tesisinde-yangin-zaman-zaman-patlamalar-yasandi</t>
+          <t>https://www.mersinhaber.com/haber-sanliurfa-haliliyede-depoda-cikan-yangin-itfaiye-ekiplerini-alarm-durumuna-gecirdi/660708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Bursa | İstanbul</t>
+          <t>Mersin | Samsun | Şanlıurfa</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Osmangazi | Küçükçekmece</t>
+          <t>Atakum | Haliliye</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Küçükbalıklı Mahallesi</t>
+          <t>öğle saatlerinde Kamberiye Mahallesi | Haliliye ilçesine bağlı Kamberiye Mahallesi</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>Ağaç AŞ</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>Ağaç AŞ:73:body | Ağaç AŞ:raw_legal</t>
-        </is>
-      </c>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>Ağaç AŞ Küçükbalıklı Mahallesi Osmangazi Bursa Türkiye</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>İSTANBUL AĞAÇ A.Ş</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>İSTANBUL AĞAÇ A.Ş</t>
-        </is>
-      </c>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>BURSA OSMANGAZİ KÜÇÜKBALIKLI</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="n">
-        <v>227.35</v>
+        <v>146.5</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>4</v>
@@ -3045,7 +3527,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:11:56</t>
+          <t>2026-06-04 12:55:19</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3060,12 +3542,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi</t>
+          <t>Şanlıurfa'da Depo Yangını: İtfaiye Ekipleri Hızla Müdahale Etti</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Haberler</t>
+          <t>Şanlıurfa'da Depo Yangını: İtfaiye Ekipleri Hızla Müdahale Etti Haber365</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -3085,25 +3567,29 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi. Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi. Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi. Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi.</t>
+          <t>Şanlıurfa'da Depo Yangını: İtfaiye Ekipleri Hızla Müdahale Etti Haber365</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Haberler Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi. Kütahya Orman Bölge Müdürü Karartı, yangın ekiplerini ve depo sahalarını denetledi Kütahya Orman Bölge Müdürü Yusuf Karartı, Tavşanlı ve Gediz orman işletme müdürlüklerine bağlı yangın söndürme ekipleri ile depo sahalarında incelemelerde bulundu, personelle bir araya gelerek yangın sezonu hazırlıklarını değerlendirdi.</t>
+          <t>Şanlıurfa'da Depo Yangını: İtfaiye Ekipleri Hızla Müdahale Etti Şanlıurfa'da Depo Yangını: İtfaiye Ekipleri Hızla Müdahale Etti Haber365 Şanlıurfa'da Depo Yangını: İtfaiye Ekipleri Hızla Müdahale Etti Haber365</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.haberler.com/amp/kutahya-da-orman-yangini-sezonu-oncesi-denetim-ve-hazirlik-19906604-haberi/</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQeGF0VEloU0diZ2tJU1ZoNzZGQ2J0LXRnQVJWZDdKRTk4T29ZWFZ6NGc0XzM4ajRjalJrelZpcFNFLVRhMnVRUXRiTUhkOGZNYmU0Z1UtMWh1TWdNNVZoRVVBWEtRa2JPbHgtVlc2Mm02d1VnQ1ZINUpyMk9RemdyMk1keFJhSVFPZWNsM2RVY3haeEJNMHl5ZkJwMmRyb1XSAZ8BQVVfeXFMUHhhdFRJaFNHYmdrSVNWaDc2RkNidC10Z0FSVmQ3SkU5OE9vWVhWejRnNF8zOGo0Y2pSa3pWaXBTRS1UYTJ1UVF0Yk1IZDhmTWJlNGdVLTFodU1nTTVWaEVVQVhLUWtiT2x4LVZXNjJtNndVZ0NWSDVKcjJPUXpncjJNZHhSYUlRT2VjbDNkVWN4WnhCTTB5eWZCcDJkcm9V?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Şanlıurfa</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
@@ -3112,7 +3598,7 @@
       <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr"/>
@@ -3126,7 +3612,7 @@
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="n">
-        <v>80.05</v>
+        <v>68.22</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>5</v>
@@ -3135,12 +3621,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 05:38:26</t>
+          <t>2026-06-04 12:32:42</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3150,12 +3636,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bursa Haberleri</t>
+          <t>Mobilya deposunda yangın paniği</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Bursa Haberleri - Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü - Yerel Haberler Hürriyet</t>
+          <t>Mobilya deposunda yangın paniği Gazette.com.tr</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3165,86 +3651,58 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü AA / Cem Şan Oluşturulma Tarihi: Haziran 04, 2026 03:39 Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Haberin Devamı BURSA (AA) - Bursa’nın Osmangazi ilçesindeki geri dönüşüm tesisinde çıkan yangın itfaiye ekiplerince söndürüldü. Küçükbalıklı Mahallesi’nde bulunan bir geri dönüşüm tesisinde bilinmeyen bir nedenle yangın çıktı. Yangını fark eden vatandaşların ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin kısa sürede kontrol altına aldığı yangın nedeniyle geri dönüşüm tesisinde maddi hasar meydana geldi. Haberle ilgili daha fazlası: #Bursa #Geri Dönüşüm Tesisi #Yangın AA / Cem Şan Oluşturulma Tarihi: Haziran 04, 2026 03:39 Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Haberin Devamı BURSA (AA) - Bursa’nın Osmangazi ilçesindeki geri dönüşüm tesisinde çıkan yangın itfaiye ekiplerince söndürüldü. Küçükbalıklı Mahallesi’nde bulunan bir geri dönüşüm tesisinde bilinmeyen bir nedenle yangın çıktı. Yangını fark eden vatandaşların ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin kısa sürede kontrol altına aldığı yangın nedeniyle geri dönüşüm tesisinde maddi hasar meydana geldi. × GÜNDEM DÜNYA BİGPARA ANASAYFA BORSA DÖVİZ ALTIN VİOP&amp;VARANT ANALİZ KOBİ KRİPTO PARALAR SPOR ARENA ANASAYFA FUTBOL BASKETBOL VOLEYBOL CANLI SKOR KELEBEK ANASAYFA EKRANDA HAYAT SEYAHAT STİL FAKİR HAUSGERATE İLE LEZZETLİ TARİFLER SAĞLIK YAŞAM ANASAYFA CUMARTESİ PAZAR LEZZETLİ HAYAT ÇOCUKLA HAYAT SEYAHAT YAZARLAR RESMİ İLANLAR ASTROLOJİ TÜMÜ EKONOMİ TV REHBERİ MAHMURE HÜRRİYET AİLE VİDEO ASTROLOJİ HESAPLAMA ARAÇLARI BULMACA EN İYİ ON CUMA LEZİZZ TEKNOLOJİ FOTO GALERİ RAMAZAN KİTAP</t>
+          <t>Mobilya deposunda yangın paniği Gazette.com.tr</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Bursa Haberleri Bursa Haberleri - Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü - Yerel Haberler Hürriyet Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü AA / Cem Şan Oluşturulma Tarihi: Haziran 04, 2026 03:39 Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Haberin Devamı BURSA (AA) - Bursa’nın Osmangazi ilçesindeki geri dönüşüm tesisinde çıkan yangın itfaiye ekiplerince söndürüldü. Küçükbalıklı Mahallesi’nde bulunan bir geri dönüşüm tesisinde bilinmeyen bir nedenle yangın çıktı. Yangını fark eden vatandaşların ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin kısa sürede kontrol altına aldığı yangın nedeniyle geri dönüşüm tesisinde maddi hasar meydana geldi. Haberle ilgili daha fazlası: #Bursa #Geri Dönüşüm Tesisi #Yangın AA / Cem Şan Oluşturulma Tarihi: Haziran 04, 2026 03:39 Bursa’da geri dönüşüm tesisinde çıkan yangın söndürüldü Haberin Devamı BURSA (AA) - Bursa’nın Osmangazi ilçesindeki geri dönüşüm tesisinde çıkan yangın itfaiye ekiplerince söndürüldü.</t>
+          <t>Mobilya deposunda yangın paniği Mobilya deposunda yangın paniği Gazette.com.tr Mobilya deposunda yangın paniği Gazette.com.tr</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.hurriyet.com.tr/yerel-haberler/bursa/bursada-geri-donusum-tesisinde-cikan-yangin-so-43192537</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOd3QxUi00WWlkbHdTZlkxMGx6TER4TnlNV1gzZVJITmREU2x0NUx2ODNIanpNdVpjckY1MTlJaFoySE94UW9ZbDNUVVB2VTFpclk5bUlSNGp6WjNjbDhjbVdDbm1Bc3FqUkRRUG9TYVpEdGRTVG9WSGpxdjd2SXgyWA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Küçükbalıklı Mahallesi</t>
-        </is>
-      </c>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Geri Dönüşüm Tesisi</t>
-        </is>
-      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>Geri Dönüşüm Tesisi Küçükbalıklı Mahallesi Bursa Türkiye</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Torun Geri Dönüşüm - Küçükbalıklı Hurda Kağıt Alımı | Bursa Hurdacı Geri Dönüşüm | Bursa Hurdacı Ayaz Metal Hurda Geridönüşüm | Bursa Hurda Kağıt | Bursa Hurda Karton | Bursa Geri Dönüşüm</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>Torun Geri Dönüşüm - Küçükbalıklı Hurda Kağıt Alımı</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>77.41935483870968 | 77.41935483870968 | 39.34426229508197 | 77.41935483870968</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>CAN PLASTİK</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="n">
-        <v>151.25</v>
+        <v>35.46</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>6</v>
@@ -3253,12 +3711,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:18:00</t>
+          <t>2026-06-04 18:42:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3268,12 +3726,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını!</t>
+          <t>Kocaeli Karamürsel'de Yangın! Yumurta Deposu Kül Oldu</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını! Ege'de Sonsöz</t>
+          <t>Kocaeli Karamürsel'de Yangın! Yumurta Deposu Kül Oldu politikam.com</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -3283,71 +3741,71 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Akkale Mahallesi'nde saat 15.00 sıralarında bir kauçuk fabrikasında yangın çıktı. Alevler kısa sürede büyüdü. Fabrikadan yükselen siyah duman kentin birçok noktasından görüldü. Çevredekilerin ihbarı üzerine olay yerine itfaiye, acil sağlık ve polis ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi aldı. İtfaiye ekipleri kimyasal ürünlerin bulunduğu kauçuk fabrikasındaki yangının çevredeki binalara sıçramaması için yangına müdahale etti. Yangın, ekiplerin yaklaşık 2 saatlik çalışmasıyla kontrol altına alındı. Yangında, fabrikada büyük çapta hasar oluştu. Soğutma çalışmalarının sürdüğü yangının çıkış nedenine ilişkin inceleme başlatıldı. (DHA) Kauçuk fabrikası küle döndü! Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Akkale Mahallesi'nde saat 15.00 sıralarında bir kauçuk fabrikasında yangın çıktı. Alevler kısa sürede büyüdü. Fabrikadan yükselen siyah duman kentin birçok noktasından görüldü. Çevredekilerin ihbarı üzerine olay yerine itfaiye, acil sağlık ve polis ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi aldı. İtfaiye ekipleri kimyasal ürünlerin bulunduğu kauçuk fabrikasındaki yangının çevredeki binalara sıçramaması için yangına müdahale etti. Yangın, ekiplerin yaklaşık 2 saatlik çalışmasıyla kontrol altına alındı. Yangında, fabrikada büyük çapta hasar oluştu. Soğutma çalışmalarının sürdüğü yangının çıkış nedenine ilişkin inceleme başlatıldı. (DHA)</t>
+          <t>Kocaeli Karamürsel'de Yangın! Yumurta Deposu Kül Oldu politikam.com</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Gökyüzü siyaha boyandı: Denizli'de fabrika yangını! Gökyüzü siyaha boyandı: Denizli'de fabrika yangını! Ege'de Sonsöz Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle yaklaşık 2 saatte kontrol altına alındı. Yangında fabrikada büyük çapta hasar oluştu. Akkale Mahallesi'nde saat 15.00 sıralarında bir kauçuk fabrikasında yangın çıktı. Alevler kısa sürede büyüdü. Fabrikadan yükselen siyah duman kentin birçok noktasından görüldü. Çevredekilerin ihbarı üzerine olay yerine itfaiye, acil sağlık ve polis ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi aldı. İtfaiye ekipleri kimyasal ürünlerin bulunduğu kauçuk fabrikasındaki yangının çevredeki binalara sıçramaması için yangına müdahale etti. Yangın, ekiplerin yaklaşık 2 saatlik çalışmasıyla kontrol altına alındı. Soğutma çalışmalarının sürdüğü yangının çıkış nedenine ilişkin inceleme başlatıldı. (DHA) Kauçuk fabrikası küle döndü!</t>
+          <t>Kocaeli Karamürsel'de Yangın! Yumurta Deposu Kül Oldu Kocaeli Karamürsel'de Yangın! Yumurta Deposu Kül Oldu politikam.com Kocaeli Karamürsel'de Yangın! Yumurta Deposu Kül Oldu politikam.com</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.egedesonsoz.com/gokyuzu-siyaha-boyandi-denizlide-fabrika-yangini/amp</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNdDJuWWxkbVphRVdiYTNWaERRQ2FmZkpFZXBLem14b2VYVEZMSlJWTU9SNlpNVVlvd0xWV2RTTFdTc2FRdi1DdHNlUlpucmV1ZzdKdjRBSk4zNi1abDFmSXM2T0FmNDJuUnJZNHdnQWFkR1JVY1F6bVhDYXAtYzdjQ3Rabw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Denizli</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Akkale Mahallesi</t>
-        </is>
-      </c>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Karamürsel</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Kauçuk fabrikası</t>
+          <t>Yumurta Deposu</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
+          <t>firma yok</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>Kauçuk fabrikası Akkale Mahallesi Denizli Türkiye</t>
+          <t>Yumurta Deposu Karamürsel Kocaeli Türkiye</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Denizli Kauçuk | Pakpol - Pamukkale Kauçuk ve Poliüretan Makina Sanayi Ticaret Limited Şirketi | TAPASAN KAUÇUK PLASTİK SAN. VE TİC. LTD. ŞTİ</t>
+          <t>Birlik Yumurta | Başaran Yumurta</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Denizli Kauçuk</t>
+          <t>Birlik Yumurta</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
@@ -3357,12 +3815,16 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>60.0 | 54.54545454545455 | 54.54545454545455</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr"/>
+          <t>66.66666666666666 | 66.66666666666666</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>KOCAELİ YALOVA CİVCİV TAVUK YARKA (Doğal Tavuk | Peynirci Baba Karamürsel | Karamursel Gida Kahvaltilik</t>
+        </is>
+      </c>
       <c r="AA8" s="2" t="n">
-        <v>162.75</v>
+        <v>145.92</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>7</v>
@@ -3371,7 +3833,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 02:27:59</t>
+          <t>2026-06-04 13:21:15</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3386,12 +3848,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri</t>
+          <t>Yeni Delhi’de Otel Yangını: En Az 21 Ölü, Çok Sayıda Yaralı</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri bolgegundemi.com</t>
+          <t>Yeni Delhi’de Otel Yangını: En Az 21 Ölü, Çok Sayıda Yaralı Turizm Gazetesi</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -3401,18 +3863,18 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
+          <t>turizm</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>05:27 Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri 03:40 Google’a Büyük Engel: Yayıncılar İsyan Etti 03:37 Otizmde Devrim Yaratan Keşif: Beyinde İki Alt Tip! 03:34 Tuz Gölü’ne piyango vurdu: Milyarlık lityum müjdesi 03:32 Şeflerin sakladığı o humus sırrı ifşa oldu</t>
+          <t>Haberler 04 Haziran 2026 0 1 DAKİKA OKUMA SÜRESİ Yeni Delhi’de Otel Yangını: En Az 21 Ölü, Çok Sayıda Yaralı Hindistan’ın başkenti Yeni Delhi’de çok katlı bir binada çıkan yangında en az 21 kişi hayatını kaybetti, onlarca kişi yaralandı. Ölenler arasında sağlık turizmi için ülkeye gelen yabancıların da bulunduğu bildirildi. Bu haberi dinleyin BBC’nin aktardığı bilgilere göre yangın, Yeni Delhi’nin güneyindeki Malviya Nagar bölgesinde bulunan çok katlı bir binada çıktı. “Flourish Stay B&amp;B” isimli yapının, yakınlardaki özel bir hastanede tedavi gören hastaların yakınlarına hizmet veren bir konaklama tesisi olarak kullanıldığı belirtildi. Yabancı hastalar ve yakınları da binadaydı Yerel basına göre, yaşamını yitirenler arasında Güney Asya ve Afrika ülkelerinden gelen yabancı uyruklu kişiler de bulunuyor. Bu kişilerin Hindistan’a çoğunlukla tıbbi tedavi amacıyla ya da hasta yakınlarını refakat etmek için geldikleri ifade edildi. Yetkililer, yangın sırasında binada kaç kişinin bulunduğunun henüz netleşmediğini, ancak 40’tan fazla kişinin kurtarılarak hastanelere sevk edildiğini açıkladı. Yangının nedeni araştırılıyor Yangının çıkış sebebi henüz belirlenemezken, Delhi itfaiye yetkilileri olayın kısa sürede kontrol altına alındığını ancak binanın tamamen kullanılamaz hale geldiğini bildirdi. Delhi Eyalet Bakanı Ashish Sood, tesisin “pansiyon (bed-and-breakfast)” olarak faaliyet göstermesi için gerekli izinlere sahip olup olmadığının da soruşturulduğunu, ihlal tespit edilmesi halinde sorumlular hakkında cezai işlem uygulanacağını söyledi. “En ölümcül yangınlardan biri” Olay, son yıllarda Hindistan başkentinde yaşanan en ölümcül yangınlardan biri olarak kayıtlara geçti. Başbakan Narendra Modi, hayatını kaybedenlerin ailelerine tazminat ödeneceğini açıkladı. Görgü tanıkları, binadan yükselen alevlerin metrelerce uzaktan görülebildiğini ve bazı kişilerin kurtulmak için üst katlardan atladığını aktardı. Kurtarma ekiplerinin olay yerinde bazı kişileri odalarda ya da banyolarda hareketsiz halde bulduğu bildirildi. Hindistan’da yangın güvenliği tartışması Hindistan’da yangınların sık yaşandığı, ancak bina güvenliği ve denetimlerinin çoğu zaman yetersiz kaldığı vurgulanıyor. Uzmanlar, bu tür olayların temelinde elektrik tesisatı sorunları, denetim eksikliği ve binaların izin dışı kullanımının bulunduğunu belirtiyor. Kaynak: BBC, Fotoğraf: Nikita Yadav,Delhiand Dilnawaz Pasha,BBC Hindi, Delhi Yo</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri bolgegundemi.com 05:27 Bursa’da Tesiste Korkutan Yangın: Patlama Sesleri 03:40 Google’a Büyük Engel: Yayıncılar İsyan Etti 03:37 Otizmde Devrim Yaratan Keşif: Beyinde İki Alt Tip! 03:34 Tuz Gölü’ne piyango vurdu: Milyarlık lityum müjdesi 03:32 Şeflerin sakladığı o humus sırrı ifşa oldu</t>
+          <t>Yeni Delhi’de Otel Yangını: En Az 21 Ölü, Çok Sayıda Yaralı Yeni Delhi’de Otel Yangını: En Az 21 Ölü, Çok Sayıda Yaralı Turizm Gazetesi Haberler 04 Haziran 2026 0 1 DAKİKA OKUMA SÜRESİ Yeni Delhi’de Otel Yangını: En Az 21 Ölü, Çok Sayıda Yaralı Hindistan’ın başkenti Yeni Delhi’de çok katlı bir binada çıkan yangında en az 21 kişi hayatını kaybetti, onlarca kişi yaralandı. Ölenler arasında sağlık turizmi için ülkeye gelen yabancıların da bulunduğu bildirildi. Bu haberi dinleyin BBC’nin aktardığı bilgilere göre yangın, Yeni Delhi’nin güneyindeki Malviya Nagar bölgesinde bulunan çok katlı bir binada çıktı. “Flourish Stay B&amp;B” isimli yapının, yakınlardaki özel bir hastanede tedavi gören hastaların yakınlarına hizmet veren bir konaklama tesisi olarak kullanıldığı belirtildi. Yabancı hastalar ve yakınları da binadaydı Yerel basına göre, yaşamını yitirenler arasında Güney Asya ve Afrika ülkelerinden gelen yabancı uyruklu kişiler de bulunuyor. Bu kişilerin Hindistan’a çoğunlukla tıbbi tedavi amacıyla ya da hasta yakınlarını refakat etmek için geldikleri ifade edildi. Yetkililer, yangın sırasında binada kaç kişinin bulunduğunun henüz netleşmediğini, ancak 40’tan fazla kişinin kurtarılarak hastanelere sevk edildiğini açıkladı. Yangının nedeni araştırılıyor Yangının çıkış sebebi henüz belirlenemezken, Delhi itfaiye yetkilileri olayın kısa sürede kontrol altına alındığını ancak binanın tamamen kullanılamaz hale geldiğini bildirdi. Delhi Eyalet Bakanı Ashish Sood, tesisin “pansiyon (bed-and-breakfast)” olarak faaliyet göstermesi için gerekli izinlere sahip olup olmadığının da soruşturulduğunu, ihlal tespit edilmesi halinde sorumlular hakkında cezai işlem uygulanacağını söyledi. “En ölümcül yangınlardan biri” Olay, son yıllarda Hindistan başkentinde yaşanan en ölümcül yangınlardan biri olarak kayıtlara geçti. Başbakan Narendra Modi, hayatını kaybedenlerin ailelerine tazminat ödeneceğini açıkladı. Görgü tanıkları, binadan yükselen alevlerin metrelerce uzaktan görülebildiğini ve bazı kişilerin kurtulmak için üst katlardan atladığını aktardı. Hindistan’da yangın güvenliği tartışması Hindistan’da yangınların sık yaşandığı, ancak bina güvenliği ve denetimlerinin çoğu zaman yetersiz kaldığı vurgulanıyor. Uzmanlar, bu tür olayların temelinde elektrik tesisatı sorunları, denetim eksikliği ve binaların izin dışı kullanımının bulunduğunu belirtiyor. Kaynak: BBC, Fotoğraf: Nikita Yadav,Delhiand Dilnawaz Pasha,BBC Hindi, Delhi Yo</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -3422,23 +3884,23 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNMUNuMHIzYWdWa2ZHRm9DLXVIQ3VfRUJNSU91X3I2cnhIR0ZmSjlLaGljaUJtN0tVTnpWQVVWQWI2cnpYMnNaaXNXTXRaeW5lbjJmYk11MU9DMlJEZjd1d25Bc3ZVem5OTHVHc3RnNTVlWFphYTZrdDZMVUVMQWduZWtlbXJ0c3hQZE9DOGNnaTZ2UzZxemJ3UktR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNTXFYNFI2bGt4amkwM011MlI4amlDbUhxT1I1bkk0NEI0MGZUZFk5azdnUFl2Zk5XSmhuR3BhQ3B1NmZySTBFMUJNVTdxV2Z4OHRPYzhhcU81ODV6UVRLcFlsMHM1c2M1Q2F0eU80OFJsNTk5cU5mNnphTERTdkxiMGJNeklLLTBKWlJESDV1NUFvYnhNR3pHRGVPRG1xRzM1Wmc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>bir konaklama tesisi</t>
+        </is>
+      </c>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr"/>
@@ -3452,7 +3914,7 @@
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="n">
-        <v>61.69</v>
+        <v>95.25</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>8</v>
@@ -3461,27 +3923,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:18:00</t>
+          <t>2026-06-04 17:38:32</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>banka soruşturma</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu</t>
+          <t>Eskişehir Organize Sanayi Bölgesi’nde fabrika yangını</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Amed Haber</t>
+          <t>Eskişehir Organize Sanayi Bölgesi’nde fabrika yangını havadis.com</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3491,62 +3953,90 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>fabrika, organize sanayi, sanayi</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik çalışma başlatıldı. Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda şüphelilerin, uyuşturucu satışından elde ettikleri gelirleri farklı yöntemlerle akladıkları yönünde bulgulara ulaşıldı. Elde edilen deliller doğrultusunda 18 şüpheli hakkında “suçtan kaynaklanan malvarlığı değerlerini aklama” suçundan 5 ayrı soruşturma dosyası oluşturuldu. Jandarma ekiplerince düzenlenen operasyonda şüpheliler hakkında yasal işlem yapılırken, çeşitli miktarlarda uyuşturucu madde de ele geçirildi. Soruşturma kapsamında şüphelilere ait olduğu değerlendirilen mal varlıklarına da el konuldu. Tedbir kararı kapsamında İzmir'in Çeşme ilçesinde bulunan 4 yıldızlı bir otel, 3 özel halk otobüsü ve işletme hatları, 2 taksi ve taksi hatları, Diyarbakır'da toplam 970 dönümlük 109 arsa ve tarla, Çeşme'de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ile 128 banka hesabı hakkında el koyma işlemi uygulandı. Yetkililer, el konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğunu açıklarken, soruşturmaya ilişkin çalışmaların sürdüğü öğrenildi. Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Diyarbakır'da narkotik madde satışından elde edilen gelirlerin aklandığı iddiasına yönelik yürütülen soruşturma kapsamında 18 şüpheli hakkında işlem yapıldı. Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik çalışma başlatıldı. Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda şüphelilerin, uyuşturucu satışından elde ettikleri gelirleri farklı yöntemlerle akladıkları yönünde bulgulara ulaşıldı. Elde edilen deliller doğrultusunda 18 şüpheli hakkında “suçtan kaynaklanan malvarlığı değerlerini aklama” suçundan 5 ayrı soruşturma dosyası oluşturuldu. Jandarma ekiplerince düzenlenen operasyonda şüpheliler hakkında yasal işlem yapılırken, çeşitli miktarlarda uyuşturucu madde de ele geçirildi. Soruşturma kapsamında şüphelilere ait olduğu değerlendirilen mal varlıklarına da el konuldu. Tedbir kararı kapsamında İzmir'in Çeşme ilçesinde bulunan 4 yıldızlı bir otel, 3 özel halk otobüsü ve işletme hatları, 2 taksi ve taksi hatları, Diyarbakır'da toplam 970 dönümlük 109 arsa ve tarla, Çeşme'de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ile 128 banka hesabı hakkında el koyma işlemi uygulandı. Yetkililer, el konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğunu açıklarken, soruşturmaya ilişkin çalışmaların sürdüğü öğrenildi.</t>
+          <t>Eskişehir’de bir yalıtım fabrikasında yangın çıktı. İtfaiye ekipleri alevleri büyümeden kontrol altına aldı. Eskişehir’de bir yalıtım fabrikasında yangın çıktı. İtfaiye ekipleri alevleri büyümeden kontrol altına aldı. Eskişehir’de bir yalıtım fabrikasında yangın çıktı. İtfaiye ekipleri alevleri büyümeden kontrol altına aldı. Eskişehir’de bir yalıtım fabrikasında yangın çıktı. İtfaiye ekipleri alevleri büyümeden kontrol altına aldı. Facebook'ta Paylaş X'de Paylaş Whatsapp'tan Gönder YAYINLAMA: 04 Haziran 2026 - 20:38 EDİTÖR: Havadis KAYNAK: İhlas Haber Ajansı Eskişehir OSB’deki 28. Cadde üzerinde bulunan bir yalıtım tesisinden dumanlar yükseldi. Çalışanların ihbarı üzerine bölgeye çok sayıda ekip sevk edildi. Alevler nasıl kontrol altına alındı Organize Sanayi Bölgesi itfaiye ekipleri yangına ilk müdahaleyi yaptı. Eskişehir Büyükşehir Belediyesi İtfaiye Daire Başkanlığı ekipleri de merdivenli araçlarla destek verdi. Ekipler yoğun çaba sarf ederek yangının diğer bölümlere sıçramasını engelledi. Yangın sonrası ne İtfaiyeciler alevleri söndürdü ve şu an bölgede soğutma çalışmaları yapıyor. Fabrikada yangının çıkış nedeni henüz belli değil. Soğutma işlemleri bitince uzmanlar binaya girip inceleme yapacak. Çalışanlar arasında yaralanan olup olmadığı ise henüz netleşmedi. Otomobiline asılan not sayesinde üç kedi ölümden döndü #Eskişehir / 05 Haziran 2026 Eskişehir’de kaza noktasına dönüşen sokağa acil çözüm talebi #Eskişehir / 05 Haziran 2026 Eskişehir’de 3 bin 500 dönüm arazi kavgası #Eskişehir / 05 Haziran 2026 Yorumlar</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Amed Haber Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik çalışma başlatıldı. Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda şüphelilerin, uyuşturucu satışından elde ettikleri gelirleri farklı yöntemlerle akladıkları yönünde bulgulara ulaşıldı. Elde edilen deliller doğrultusunda 18 şüpheli hakkında “suçtan kaynaklanan malvarlığı değerlerini aklama” suçundan 5 ayrı soruşturma dosyası oluşturuldu. Jandarma ekiplerince düzenlenen operasyonda şüpheliler hakkında yasal işlem yapılırken, çeşitli miktarlarda uyuşturucu madde de ele geçirildi. Soruşturma kapsamında şüphelilere ait olduğu değerlendirilen mal varlıklarına da el konuldu. Tedbir kararı kapsamında İzmir'in Çeşme ilçesinde bulunan 4 yıldızlı bir otel, 3 özel halk otobüsü ve işletme hatları, 2 taksi ve taksi hatları, Diyarbakır'da toplam 970 dönümlük 109 arsa ve tarla, Çeşme'de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ile 128 banka hesabı hakkında el koyma işlemi uygulandı. Yetkililer, el konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğunu açıklarken, soruşturmaya ilişkin çalışmaların sürdüğü öğrenildi. Diyarbakır'da kara para operasyonu: Milyarlarca liraya el konuldu Diyarbakır'da narkotik madde satışından elde edilen gelirlerin aklandığı iddiasına yönelik yürütülen soruşturma kapsamında 18 şüpheli hakkında işlem yapıldı.</t>
+          <t>Eskişehir Organize Sanayi Bölgesi’nde fabrika yangını Eskişehir Organize Sanayi Bölgesi’nde fabrika yangını havadis.com Eskişehir’de bir yalıtım fabrikasında yangın çıktı. İtfaiye ekipleri alevleri büyümeden kontrol altına aldı.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPUlIyaFdTcHE2RjI3NmFtOThwZ2tUejNVMUVVamRiU2w5X1dYckJLREtrWDFaYWotdU1uUkFPT0FGMkxyZ2FEeHQ1M1dRTHQxNGZBazZfbnp4eER1YnpUTFU1SGkwREdpMElfanJqa2Z2LXJBSTZucEpxOGg1S1JsMnhJZ3dMX21ad0lnYmsybTdDMHBKNkR5NdIBmAFBVV95cUxPUlIyaFdTcHE2RjI3NmFtOThwZ2tUejNVMUVVamRiU2w5X1dYckJLREtrWDFaYWotdU1uUkFPT0FGMkxyZ2FEeHQ1M1dRTHQxNGZBazZfbnp4eER1YnpUTFU1SGkwREdpMElfanJqa2Z2LXJBSTZucEpxOGg1S1JsMnhJZ3dMX21ad0lnYmsybTdDMHBKNkR5NQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.havadis.com/eskisehir/eskisehir-organize-sanayi-bolgesinde-fabrika-yangini/416198</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır | İzmir</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Çeşme</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir Organize Sanayi</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir Organize Sanayi</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir Organize Sanayi:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir Organize Sanayi Eskişehir Organize Sanayi Eskişehir Türkiye</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="n">
-        <v>102.5</v>
+        <v>203.75</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>9</v>
@@ -3555,12 +4045,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:00:00</t>
+          <t>2026-06-05 06:02:02</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>kara para</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3570,12 +4060,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15 milyar liralık kara para ağı! Hepsine el konuldu</t>
+          <t>24 ilde kara para operasyonu: 350 milyon liralık mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15 milyar liralık kara para ağı! Hepsine el konuldu babaocagi.com.tr</t>
+          <t>24 ilde kara para operasyonu: 350 milyon liralık mal varlığına el konuldu Doviz.com</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3585,62 +4075,82 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
+          <t>el konuldu, mal varlığı</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Güncel 15 milyar liralık kara para ağı! Hepsine el konuldu Diyarbakır'da uyuşturucu ticaretinden elde edilen gelirleri aklayan 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. 04.06.2026 - 09:00 04.06.2026 - 09:00 Uyuşturucu satışından elde edilen geliri aklayan şüpheliler yakalandı. Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu veya uyarıcı madde imal ve ticareti ile suç gelirlerinin aklanmasına yönelik çalışma yürütüldü. 8 AY ADIM ADIM İZLENDİ Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda, uyuşturucu ticaretinden elde ettikleri gelirleri çeşitli yöntemlerle akladıkları değerlendirilen şüpheliler hakkında soruşturma başlatıldı. Çalışmalar kapsamında, “Uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama” ile “2313 Sayılı Kanuna Muhalefet” suçlarından elde edilen gelirlerle mal varlığı edindikleri değerlendirilen 18 şüpheli hakkında, “Suçtan kaynaklanan malvarlığı değerlerini aklama’” suçundan 5 ayrı soruşturma dosyası açıldı. UYUŞTURUCU MADDELER ELE GEÇİRİLDİ Jandarma ekiplerinin düzenlediği operasyonda 18 şüpheli hakkında yasal işlem yapılırken, yüklü miktarda uyuşturucu madde ele geçirildi. Operasyon kapsamında şüphelilere ait olduğu belirlenen İzmir’in Çeşme ilçesindeki 4 yıldızlı bir otel, 3 özel halk otobüsü ve hatları, 2 taksi ve hatları, Diyarbakır’da toplam 970 dönüm büyüklüğünde 109 arsa ve tarla, Çeşme’de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ve 128 banka hesabına el konuldu. El konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğu belirtildi. Bunlar</t>
+          <t>Yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten suç ağı çökertildi. Operasyonda 80 şüpheli gözaltına alındı ve 350 milyon lira değerindeki gayrimenkullere el konuldu. Yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten suç ağı çökertildi. Operasyonda 80 şüpheli gözaltına alındı ve 350 milyon lira değerindeki gayrimenkullere el konuldu. Doviz.com 05 Haziran 2026 09:02 Yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten suç ağı çökertildi. Operasyonda 80 şüpheli gözaltına alındı ve 350 milyon lira değerindeki gayrimenkullere el konuldu. İstanbul merkezli 24 ilde gerçekleştirilen eş zamanlı operasyonda, yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten ve bunu kripto varlıklar üzerinden aklamakla suçlanan İ.Ö.Ö. liderliğindeki suç ağı çökertildi. MASAK raporlarından yola çıkılarak yapılan dev operasyonda 80 şüpheli gözaltına alınırken, 11 şirket, 45 araç, 16 konut ve 11 tarla/arsa olmak üzere yaklaşık 350 milyon lira değerindeki toplam 83 gayrimenkule el konuldu, şüphelilere ait banka ve kripto varlık hesaplarına bloke edildi. İLGİLİ HABER MASAK’tan “Türkiye kara para ağına sürükleniyor” iddiasına yanıt Türkiye'nin kara para ile mücadelede uluslararası standartları karşıladığına dikkat çeken MASAK, POS cihazları üzerinden suç gelirlerinin aklanmasını engellemek amacıyla denetimlerin artırıldığını duyurdu. Esenboğa'da uçak kabininde yangın çıktı İzmir-Ankara seferini yapan bir yolcu uçağında kabin içindeki taşınabilir güç kaynağından çıkan yangın üzerine yolcular tahliye edildi. Uçaktaki yangın, kontrol altına alındı. 9 saniye önce MSB'den bedelli askerlik yapacaklara temmuz uyarısı Bedelli askerlik hizmeti kapsamında geçerli olan bedelin 1 Temmuz'da memur aylık katsayısına göre güncelleneceğini duyuran Milli Savunma Bakanlığı, mevcut bedel tutarı üzerinden bedelli askerlik hizmetine müracaat etmek isteyen yükümlülerin 30 Haziran 2026 tarihine kadar müracaat ve ödeme işlemlerini tamamlamalarını istedi. 17 dakika önce Fatih Karahan: Katılım finansmanı ivme kazanarak büyüyor 3. Dünya İslam Ekonomi Zirvesi'nde konuşan Türkiye Cumhuriyet Merkez Bankası(TCMB) Başkanı Fatih Karahan, katılım finansmanın 2010’larda yüzde 4,5 seviyesinden bugün yüzde 9’a yükseldiğini ve bu alanın istikrarlı şekilde büyümeye devam ettiğini belirtti. 24 dakika önce Mayıs ayının zam şampiyonu belli oldu TÜİK, mayıs ayında bir önceki aya göre fiyatı en çok artan ve azalan ürünleri açıkladı. TÜİK'in listesine göre mayısta zam şampiyonu uçak bileti oldu. 44 dakika önce ÖSYM duyurdu: ALES sonuçları açıklandı Ölçme, Seçme ve Yerleştirme Merkezi (ÖSYM), 2026 Akademik Personel ve Lisansüstü Eğitimi Giriş Sınavı (2026-ALES/1) sonuçlarını açıkladı. 51 dakika önce İLGİLİ HABER MASAK’tan “Türkiye kara para ağına sürükleniyor” iddiasına yanıt Türkiye'nin kara para ile mücadelede uluslararası standartları karşıladığına dikkat çeken MASAK, POS cihazları üzerinden suç gelirlerinin aklanmasını engellemek amacıyla denetimlerin artırıldığını duyurdu. 24 ilde kara para operasyonu: 350 milyon liralık mal varlığına el konuldu Yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten suç ağı çökertildi. Operasyonda 80 şüpheli gözaltına alındı ve 350 milyon lira değerindeki gayrimenkullere el konuldu. İstanbul merkezli 24 ilde gerçekleştirilen eş zamanlı operasyonda, yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten ve bunu kripto varlıklar üzerinden aklamakla suçlanan İ.Ö.Ö. liderliğindeki suç ağı çökertildi. MASAK raporlarından yola çıkılarak yapılan dev operasyonda 80 şüpheli gözaltına alınırken, 11 şirket, 45 araç, 16 konut ve 11 tarla/arsa olmak üzere yaklaşık 350 milyon lira değerindeki toplam 83 gayrimenkule el konuldu, şüphelilere ait banka ve kripto varlık hesaplarına bloke edildi. Yasal Uyarı: Piyasa verileri Forinvest Yazılım ve Teknolojileri Hizmetleri A.Ş. tarafından sağlanmaktadır. Hisse senedi verileri 15 dakika, Tahvil-Bono-Repo özet verileri 15 dakika gecikmelidir. Burada yer alan yatırım bilgi, yorum ve tavsiyeleri yatırım danışmanlığı kapsamında değildir. Yatırım danışmanlığı hizmeti; aracı kurumlar, portföy yönetim şirketleri, mevduat kabul etmeyen bankalar ile müşteri arasında imzalanacak yatırım danışmanlığı sözleşmesi çerçevesinde sunulmaktadır. Burada yer alan yorum ve tavsiyeler, yorum ve tavsiyede bulunanların kişisel görüşlerine dayanmaktadır. Bu görüşler mali durumunuz ile risk ve getiri tercihlerinize uygun olmayabilir. Bu nedenle, sadece burada yer alan bilgilere dayanılarak yatırım kararı verilmesi beklentilerinize uygun sonuçlar doğurmayabilir. Gerek site üzerindeki, gerekse site için kullanılan kaynaklardaki hata ve eksikliklerden ve sitedeki bilgilerin kullanılması sonucunda yatırımcıların uğrayabilecekleri doğrudan ve/veya dolaylı zararlardan, kar yoksunluğundan, manevi zararlardan ve üçüncü kişilerin uğrayabileceği zararlardan Noktacom Medya İnternet Hizmetleri San. ve Tic. A.Ş hiçbir şekilde sorumlu tutulamaz. BİST isim ve logosu "Koruma Marka Belgesi" altında korunmakta olup izinsiz kullanılamaz, iktibas edilemez, değiştirilemez. BİST ismi altında açıklanan tüm bilgilerin telif hakları tamamen BİST'e ait olup, tekrar yayınlanamaz.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15 milyar liralık kara para ağı! Hepsine el konuldu 15 milyar liralık kara para ağı! Hepsine el konuldu babaocagi.com.tr Güncel 15 milyar liralık kara para ağı! Hepsine el konuldu Diyarbakır'da uyuşturucu ticaretinden elde edilen gelirleri aklayan 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. 04.06.2026 - 09:00 04.06.2026 - 09:00 Uyuşturucu satışından elde edilen geliri aklayan şüpheliler yakalandı. Diyarbakır Cumhuriyet Başsavcılığı koordinesinde, Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri tarafından uyuşturucu veya uyarıcı madde imal ve ticareti ile suç gelirlerinin aklanmasına yönelik çalışma yürütüldü. 8 AY ADIM ADIM İZLENDİ Yaklaşık 8 ay süren teknik ve fiziki takip sonucunda, uyuşturucu ticaretinden elde ettikleri gelirleri çeşitli yöntemlerle akladıkları değerlendirilen şüpheliler hakkında soruşturma başlatıldı. Çalışmalar kapsamında, “Uyuşturucu veya uyarıcı madde imal ve ticareti yapma veya sağlama” ile “2313 Sayılı Kanuna Muhalefet” suçlarından elde edilen gelirlerle mal varlığı edindikleri değerlendirilen 18 şüpheli hakkında, “Suçtan kaynaklanan malvarlığı değerlerini aklama’” suçundan 5 ayrı soruşturma dosyası açıldı. UYUŞTURUCU MADDELER ELE GEÇİRİLDİ Jandarma ekiplerinin düzenlediği operasyonda 18 şüpheli hakkında yasal işlem yapılırken, yüklü miktarda uyuşturucu madde ele geçirildi. Operasyon kapsamında şüphelilere ait olduğu belirlenen İzmir’in Çeşme ilçesindeki 4 yıldızlı bir otel, 3 özel halk otobüsü ve hatları, 2 taksi ve hatları, Diyarbakır’da toplam 970 dönüm büyüklüğünde 109 arsa ve tarla, Çeşme’de 9 dönümlük arsa, 7 araç, 33 daire, 4 iş yeri ve 128 banka hesabına el konuldu. El konulan mal varlıklarının toplam piyasa değerinin yaklaşık 15 milyar TL olduğu belirtildi.</t>
+          <t>24 ilde kara para operasyonu: 350 milyon liralık mal varlığına el konuldu 24 ilde kara para operasyonu: 350 milyon liralık mal varlığına el konuldu Doviz.com Yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten suç ağı çökertildi. Operasyonda 80 şüpheli gözaltına alındı ve 350 milyon lira değerindeki gayrimenkullere el konuldu. Doviz.com 05 Haziran 2026 09:02 Yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten suç ağı çökertildi. İstanbul merkezli 24 ilde gerçekleştirilen eş zamanlı operasyonda, yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten ve bunu kripto varlıklar üzerinden aklamakla suçlanan İ.Ö.Ö. liderliğindeki suç ağı çökertildi. MASAK raporlarından yola çıkılarak yapılan dev operasyonda 80 şüpheli gözaltına alınırken, 11 şirket, 45 araç, 16 konut ve 11 tarla/arsa olmak üzere yaklaşık 350 milyon lira değerindeki toplam 83 gayrimenkule el konuldu, şüphelilere ait banka ve kripto varlık hesaplarına bloke edildi. İLGİLİ HABER MASAK’tan “Türkiye kara para ağına sürükleniyor” iddiasına yanıt Türkiye'nin kara para ile mücadelede uluslararası standartları karşıladığına dikkat çeken MASAK, POS cihazları üzerinden suç gelirlerinin aklanmasını engellemek amacıyla denetimlerin artırıldığını duyurdu. Esenboğa'da uçak kabininde yangın çıktı İzmir-Ankara seferini yapan bir yolcu uçağında kabin içindeki taşınabilir güç kaynağından çıkan yangın üzerine yolcular tahliye edildi. Uçaktaki yangın, kontrol altına alındı. 9 saniye önce MSB'den bedelli askerlik yapacaklara temmuz uyarısı Bedelli askerlik hizmeti kapsamında geçerli olan bedelin 1 Temmuz'da memur aylık katsayısına göre güncelleneceğini duyuran Milli Savunma Bakanlığı, mevcut bedel tutarı üzerinden bedelli askerlik hizmetine müracaat etmek isteyen yükümlülerin 30 Haziran 2026 tarihine kadar müracaat ve ödeme işlemlerini tamamlamalarını istedi. 51 dakika önce İLGİLİ HABER MASAK’tan “Türkiye kara para ağına sürükleniyor” iddiasına yanıt Türkiye'nin kara para ile mücadelede uluslararası standartları karşıladığına dikkat çeken MASAK, POS cihazları üzerinden suç gelirlerinin aklanmasını engellemek amacıyla denetimlerin artırıldığını duyurdu. 24 ilde kara para operasyonu: 350 milyon liralık mal varlığına el konuldu Yasa dışı bahis ve sanal kumar sitelerinden elde edilen 192 milyar liralık kara para trafiğini yöneten suç ağı çökertildi. Yasal Uyarı: Piyasa verileri Forinvest Yazılım ve Teknolojileri Hizmetleri A.Ş. tarafından sağlanmaktadır. Yatırım danışmanlığı hizmeti; aracı kurumlar, portföy yönetim şirketleri, mevduat kabul etmeyen bankalar ile müşteri arasında imzalanacak yatırım danışmanlığı sözleşmesi çerçevesinde sunulmaktadır. Gerek site üzerindeki, gerekse site için kullanılan kaynaklardaki hata ve eksikliklerden ve sitedeki bilgilerin kullanılması sonucunda yatırımcıların uğrayabilecekleri doğrudan ve/veya dolaylı zararlardan, kar yoksunluğundan, manevi zararlardan ve üçüncü kişilerin uğrayabileceği zararlardan Noktacom Medya İnternet Hizmetleri San. A.Ş hiçbir şekilde sorumlu tutulamaz. BİST isim ve logosu "Koruma Marka Belgesi" altında korunmakta olup izinsiz kullanılamaz, iktibas edilemez, değiştirilemez.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOcVY3YzJGSWRqM1VLWXQ5blh0UF9aVk1JaHRBaHFZTmhQYTQteUpRTnptamk5MmYxdEtNVXU1QU5VM3dXbWkzNnhPeGt1al95QUh2ci1RcGdmb0dSV1RYdmY4aWhHczQ2ZU5yNTRBcXctMTdFbDN2VHZ1SjRKS0NOZnFFZ25sNEtUdnNr0gGLAUFVX3lxTE5xVjdjMkZJZGozVUtZdDluWHRQX1pWTUlodEFocVlOaFBhNC15SlFOem1qaTkyZjF0S01VdTVBTlUzd1dtaTM2eE94a3VqX3lBSHZyLVFwZ2ZvR1JXVFh2ZjhpaEdzNDZlTnI1NEFxdy0xN0VsM3ZUdnVKNEpLQ05mcUVnbmw0S1R2c2s?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://haber.doviz.com/gundem-haberleri/24-ilde-kara-para-operasyonu-350-milyon-liralik-mal-varligina-el-konuldu/879992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır | İzmir</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Çeşme</t>
-        </is>
-      </c>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Forinvest Yazılım ve Teknolojileri Hizmetleri A.Ş</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Forinvest Yazılım ve Teknolojileri Hizmetleri A.Ş:55:body | Forinvest Yazılım ve Teknolojileri Hizmetleri A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr"/>
-      <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>Forinvest Yazılım ve Teknolojileri Hizmetleri A.Ş İstanbul Türkiye</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>ForInvest Yazılım ve Teknoloji Hizmetleri A.Ş</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>ForInvest Yazılım ve Teknoloji Hizmetleri A.Ş</t>
+        </is>
+      </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>95.74468085106383</t>
+        </is>
+      </c>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="n">
-        <v>93.5</v>
+        <v>185.25</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>10</v>
@@ -3649,27 +4159,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:25:29</t>
+          <t>2026-06-04 16:00:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>mal varlığına el konuldu</t>
+          <t>kara para</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu</t>
+          <t>Bankalardan milyonlarca kişiye kritik uyarı</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN</t>
+          <t>Bankalardan milyonlarca kişiye kritik uyarı Manisa Kulis Haber</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3679,28 +4189,32 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>el konuldu, mal varlığı</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN</t>
+          <t>Banka hesaplarını para karşılığında üçüncü kişilere kullandıranlara yönelik adli işlemlerin artması üzerine bankalar müşterilerine uyarı mesajları göndermeye başladı. Banka hesaplarını para karşılığında üçüncü kişilere kullandıranlara yönelik adli işlemlerin artması üzerine bankalar müşterilerine uyarı mesajları göndermeye başladı. Banka hesaplarını para karşılığında üçüncü kişilere kullandıranlara yönelik adli işlemlerin artması üzerine bankalar müşterilerine uyarı mesajları göndermeye başladı. Bankalardan milyonlarca kişiye kritik uyarı Banka hesaplarını para karşılığında üçüncü kişilere kullandıranlara yönelik adli işlemlerin artması üzerine bankalar müşterilerine uyarı mesajları göndermeye başladı. 04.06.2026 - 19:00 Yayınlanma 2 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Son dönemde yasa dışı bahis, dolandırıcılık ve kara para aklama suçlarında banka hesaplarının kullanılmasıyla ilgili soruşturmalarda artış yaşanıyor. Suç örgütlerinin para karşılığında vatandaşların banka hesaplarını kullandığı ve bu hesaplar üzerinden para transferleri gerçekleştirdiği belirtiliyor. Artan vakalar üzerine bankalar da müşterilerini bilgilendirmek amacıyla uyarı mesajları göndermeye başladı. Suç Örgütleri Banka Hesaplarını Hedef Alıyor Son yıllarda yasa dışı bahis, dolandırıcılık ve suç gelirlerinin aklanması gibi faaliyetlerde banka hesaplarının kullanıldığı çok sayıda olay gündeme geldi. Özellikle maddi sıkıntı yaşayan kişilere ulaşan suç örgütlerinin, belirli bir ücret karşılığında banka hesaplarını kullanmak istediği belirtiliyor. Hesabını Kullandıranlar Hukuki Sorumlulukla Karşılaşabilir Uzmanlar, banka hesabının başka kişiler tarafından kullanılmasına izin verilmesinin ciddi sonuçlar doğurabileceğine dikkat çekiyor. Hesapların yasa dışı bahis, dolandırıcılık, kara para aklama veya terörün finansmanı gibi suçlarda kullanılması durumunda hesap sahiplerinin de adli işlemle karşılaşabileceği ifade ediliyor. Bankalar Müşterilerine Uyarı Mesajı Gönderdi Artan olaylar üzerine bankalar müşterilerine kısa mesaj yoluyla bilgilendirmelerde bulunmaya başladı. Gönderilen mesajlarda hesap güvenliğinin önemi hatırlatılırken, üçüncü kişilere hesap kullandırılmaması gerektiği ifade edildi. Ziraat Bankası'nın Uyarı Mesajı Ziraat Bankası tarafından müşterilere gönderilen bilgilendirme mesajında şu ifadelere yer verildi: "Hesaplarınızı hiçbir koşulda üçüncü kişilere kullandırmayınız. Hesabın bu şekilde kullandırılması; yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı gibi suçlara aracılık edilmesine ve hukuki sonuçlara sebep olabilir." Vatandaşlara Hesap Güvenliği Çağrısı Bankalar ve uzmanlar, vatandaşların IBAN, banka kartı, internet bankacılığı şifreleri ve hesap bilgilerini hiçbir şekilde başka kişilerle paylaşmaması gerektiğini belirtiyor. Özellikle kolay kazanç vaadiyle yapılan tekliflere karşı dikkatli olunması gerektiği ifade edilirken, hesapların üçüncü kişiler tarafından kullanılmasına izin verilmesinin ciddi cezai yaptırımlara yol açabileceği uyarısında bulunuluyor. Kaynak: Haber Merkezi</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu MSN</t>
+          <t>Bankalardan milyonlarca kişiye kritik uyarı Bankalardan milyonlarca kişiye kritik uyarı Manisa Kulis Haber Banka hesaplarını para karşılığında üçüncü kişilere kullandıranlara yönelik adli işlemlerin artması üzerine bankalar müşterilerine uyarı mesajları göndermeye başladı. Bankalardan milyonlarca kişiye kritik uyarı Banka hesaplarını para karşılığında üçüncü kişilere kullandıranlara yönelik adli işlemlerin artması üzerine bankalar müşterilerine uyarı mesajları göndermeye başladı. 04.06.2026 - 19:00 Yayınlanma 2 Dk Okunma Süresi</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.msn.com/tr-tr/video/populer/uyu%C5%9Fturucu-gelirlerini-aklayan-%C5%9Febekeye-operasyon-15-milyar-tl-lik-mal-varl%C4%B1%C4%9F%C4%B1na-el-konuldu/vi-AA24Obdw</t>
+          <t>https://www.manisakulishaber.com/bankalardan-milyonlarca-kisiye-kritik-uyari</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
@@ -3726,7 +4240,7 @@
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="n">
-        <v>86.95999999999999</v>
+        <v>50</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>11</v>
@@ -3735,27 +4249,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:07:14</t>
+          <t>2026-06-04 11:00:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>mal varlığına el konuldu</t>
+          <t>kara para</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu</t>
+          <t>Bankalardan müşterilere kritik uyarı..!</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber</t>
+          <t>Bankalardan müşterilere kritik uyarı..! Düzcenin Sesi</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -3765,35 +4279,35 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber</t>
+          <t>Banka hesaplarını para karşılığında suç örgütlerine kullandıran kişilerle ilgili adli işlemlerin artması üzerine banklar, müşterilerine uyarı mesajı gönderdi. Müşterilere gönderilen mesajlarda, hesapların kullandırılmasının yasa dışı bahis, kara para aklama, terörün finansmanı gibi suçlamalarla muhatap olmaya neden olabileceği vurgulandı. Banka hesaplarını para karşılığında suç örgütlerine kullandıran kişilerle ilgili adli işlemlerin artması üzerine banklar, müşterilerine uyarı mesajı gönderdi. M... Banka hesaplarını para karşılığında suç örgütlerine kullandıran kişilerle ilgili adli işlemlerin artması üzerine banklar, müşterilerine uyarı mesajı gönderdi. Müşterilere gönderilen mesajlarda, hesapların kullandırılmasının yasa dışı bahis, kara para aklama, terörün finansmanı gibi suçlamalarla muhatap olmaya neden olabileceği vurgulandı. Son dönemde yasa dışı bahis, dolandırıcılık, kara para aklama gibi suç faaliyetlerinde, para karşılığında banka hesaplarını suç şebekelerine kullandıran kişilerin de hapis cezası aldığı birçok örnek gündeme geldi. Suç örgütleri, paraya ihtiyacı olan kişilerin banka hesapları üzerinden suç faaliyetleriyle ilgili para transferleri yapıyor. Bu durum, para karşılığında banka hesabını suç örgütünün faaliyetlerinde kullanılmasına izin veren kişilerin de ceza almasının yolunu açıyor. BANKALARDAN UYARI MESAJLARI Benzer örneklerin artması üzerine bankalar, müşterilerine uyarı mesajları göndermeye başladı. Bankalardan müşterilere gönderilen uyarı mesajlarında, hiçbir koşulda hesaplarını üçüncü kişilere kullandırmama çağrısı yapıldı. "HUKUKİ SONUÇLARA SEBEP OLABİLİR" Bilgilendirme mesajlarında, hesapların kullandırılması sonucunda yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı gibi suçlardan işlem görme riski hatırlatıldı. Ziraat Bankası'ndan müşterilere gönderilen mesaj şöyle: "Değerli müşterimiz, hesaplarınızı hiçbir koşulda üçüncü kişilere kullandırmayınız. Hesabın bu şekilde kullandırılması; yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı gibi suçlara aracılık edilmesine ve hukuki sonuçlara sebep olabilir. Bilgilerinize sunar, sağlıklı günler dileriz." Bankalardan müşterilere kritik uyarı..! Banka hesaplarını para karşılığında suç örgütlerine kullandıran kişilerle ilgili adli işlemlerin artması üzerine banklar, müşterilerine uyarı mesajı gönderdi. Müşterilere gönderilen mesajlarda, hesapların kullandırılmasının yasa dışı bahis, kara para aklama, terörün finansmanı gibi suçlamalarla muhatap olmaya neden olabileceği vurgulandı. Son dönemde yasa dışı bahis, dolandırıcılık, kara para aklama gibi suç faaliyetlerinde, para karşılığında banka hesaplarını suç şebekelerine kullandıran kişilerin de hapis cezası aldığı birçok örnek gündeme geldi. Suç örgütleri, paraya ihtiyacı olan kişilerin banka hesapları üzerinden suç faaliyetleriyle ilgili para transferleri yapıyor. Bu durum, para karşılığında banka hesabını suç örgütünün faaliyetlerinde kullanılmasına izin veren kişilerin de ceza almasının yolunu açıyor. BANKALARDAN UYARI MESAJLARI Benzer örneklerin artması üzerine bankalar, müşterilerine uyarı mesajları göndermeye başladı. Bankalardan müşterilere gönderilen uyarı mesajlarında, hiçbir koşulda hesaplarını üçüncü kişilere kullandırmama çağrısı yapıldı. "HUKUKİ SONUÇLARA SEBEP OLABİLİR" Bilgilendirme mesajlarında, hesapların kullandırılması sonucunda yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı gibi suçlardan işlem görme riski hatırlatıldı. Ziraat Bankası'ndan müşterilere gönderilen mesaj şöyle: "Değerli müşterimiz, hesaplarınızı hiçbir koşulda üçüncü kişilere kullandırmayınız. Hesabın bu şekilde kullandırılması; yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı gibi suçlara aracılık edilmesine ve hukuki sonuçlara sebep olabilir. Bilgilerinize sunar, sağlıklı günler dileriz." 04 Haz 2026 - 14:00 - Gündem Yazdır Yorum yazarak Düzcenin Sesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yoruml</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber Diyarbakır'da zehir tacirlerine dev operasyon! 15 milyar TL'lik malvarlığına el konuldu TGRT Haber</t>
+          <t>Bankalardan müşterilere kritik uyarı..! Bankalardan müşterilere kritik uyarı..! Düzcenin Sesi Banka hesaplarını para karşılığında suç örgütlerine kullandıran kişilerle ilgili adli işlemlerin artması üzerine banklar, müşterilerine uyarı mesajı gönderdi. Müşterilere gönderilen mesajlarda, hesapların kullandırılmasının yasa dışı bahis, kara para aklama, terörün finansmanı gibi suçlamalarla muhatap olmaya neden olabileceği vurgulandı. Son dönemde yasa dışı bahis, dolandırıcılık, kara para aklama gibi suç faaliyetlerinde, para karşılığında banka hesaplarını suç şebekelerine kullandıran kişilerin de hapis cezası aldığı birçok örnek gündeme geldi. Bu durum, para karşılığında banka hesabını suç örgütünün faaliyetlerinde kullanılmasına izin veren kişilerin de ceza almasının yolunu açıyor. BANKALARDAN UYARI MESAJLARI Benzer örneklerin artması üzerine bankalar, müşterilerine uyarı mesajları göndermeye başladı. Bankalardan müşterilere gönderilen uyarı mesajlarında, hiçbir koşulda hesaplarını üçüncü kişilere kullandırmama çağrısı yapıldı. "HUKUKİ SONUÇLARA SEBEP OLABİLİR" Bilgilendirme mesajlarında, hesapların kullandırılması sonucunda yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı gibi suçlardan işlem görme riski hatırlatıldı. Ziraat Bankası'ndan müşterilere gönderilen mesaj şöyle: "Değerli müşterimiz, hesaplarınızı hiçbir koşulda üçüncü kişilere kullandırmayınız. Hesabın bu şekilde kullandırılması; yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı gibi suçlara aracılık edilmesine ve hukuki sonuçlara sebep olabilir. Bilgilerinize sunar, sağlıklı günler dileriz." Bankalardan müşterilere kritik uyarı..! Bilgilerinize sunar, sağlıklı günler dileriz." 04 Haz 2026 - 14:00 - Gündem Yazdır Yorum yazarak Düzcenin Sesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcnNhWWJvcURkWVRWdHBTQTVWQ3Z3Z2Y0VTlBc1BudVVoRWpWZHFmaFd0azBkRGlhRUx6aHFsYVRZMGVTWVRQTTZUVWxNbFZkY3g1ZXk3WHFpX2d2blQyZFdpZHdheTFlT1UxWDc0eGlUbzFURl9LbEE1RUthUmNpc2lSS21aS25wdjlPSTN0MUdMaW5yMHp6dDNTZkdCdS1sV1lBVVhHUG9BQ0FyVWZ1WTAxdWt0dUpxNjBYU0RUREV2Y3M?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Diyarbakır</t>
-        </is>
-      </c>
+          <t>https://www.duzceninsesi.com.tr/haber/28111599/bankalardan-musterilere-kritik-uyari</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -3802,7 +4316,7 @@
       <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr"/>
@@ -3816,7 +4330,7 @@
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="n">
-        <v>94.98</v>
+        <v>45.75</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>12</v>
@@ -3825,27 +4339,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:17:45</t>
+          <t>2026-06-04 12:42:00</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>sahtecilik</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı</t>
+          <t>Banka hesabını kullandıranlar dikkat! Bankalar uyarıyor: Hapis cezasına kadar gidiyor!</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv</t>
+          <t>Banka hesabını kullandıranlar dikkat! Bankalar uyarıyor: Hapis cezasına kadar gidiyor! Türk İnform</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -3855,28 +4369,32 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>sağlık</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>banka, banka hesabı</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv</t>
+          <t>Bankalar, kullanıcılarına hesapların hiçbir koşulda üçüncü kişilere kullandırılmaması konusunda uyarılarda bulunuyor. Birçok suçlamayla karşı karşıya kalınabileceği ve hapis cezasına kadar gidebileceği belirtiliyor. Bankalar, kullanıcılarına hesapların hiçbir koşulda üçüncü kişilere kullandırılmaması konusunda uyarılarda bulunuyor. Birçok suçlamayla karşı karşıya kalınabileceği ve hapis cezasına kadar gidebileceği belirtiliyor. Bankalar, kullanıcılarına hesapların hiçbir koşulda üçüncü kişilere kullandırılmaması konusunda uyarılarda bulunuyor. Birçok suçlamayla karşı karşıya kalınabileceği ve hapis cezasına kadar gidebileceği belirtiliyor. Banka hesabını kullandıranlar dikkat! Bankalar uyarıyor: Hapis cezasına kadar gidiyor! Bankalar, kullanıcılarına hesapların hiçbir koşulda üçüncü kişilere kullandırılmaması konusunda uyarılarda bulunuyor. Birçok suçlamayla karşı karşıya kalınabileceği ve hapis cezasına kadar gidebileceği belirtiliyor. Zülfinur Ecem Çetin Editör 04.06.2026 - 15:42 Yayınlanma 2 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Son dönemde yasa dışı bahis, dolandırıcılık ve kara para aklama suçlarında kullanılan yöntemlerden biri de başkalarına ait banka hesapları oldu. Özellikle maddi sıkıntı yaşayan vatandaşların hesaplarını para karşılığında suç şebekelerine kullandırdığı birçok olay yargıya taşınırken, hesap sahiplerinin de ciddi cezalarla karşı karşıya kaldığı görüldü. SUÇ ÖRGÜTLERİ BANKA HESAPLARINI HEDEF ALIYOR Yetkililerin aktardığına göre, suç örgütleri, farklı yöntemlerle ulaştıkları kişilerin banka hesapları üzerinden para transferleri gerçekleştiriyor. Böylece yasa dışı faaliyetlerden elde edilen paralar sistem içinde dolaştırılmaya çalışılıyor. Hesabını kullandıran kişiler ise çoğu zaman yalnızca “hesabını kiraladığını” düşünse de, yürütülen soruşturmalarda suçun bir parçası olarak değerlendirilebiliyor. “SADECE HESABIMI VERDİM” SAVUNMASI YETERLİ OLMUYOR Uzmanlar, banka hesabını başka kişilerin kullanımına açan vatandaşların; yasa dışı bahis, dolandırıcılık, kara para aklama ve terörün finansmanı gibi ağır suçlamalarla karşı karşıya kalabileceği konusunda uyarıyor. Son dönemde açılan birçok davada, hesap hareketleri nedeniyle hesap sahiplerinin de ceza aldığı örneklerin arttığı belirtiliyor. BANKALARDAN MÜŞTERİLERE PEŞ PEŞE UYARILAR Yaşanan olayların artması üzerine bankalar da müşterilerine bilgilendirme mesajları göndermeye başladı. Gönderilen mesajlarda, banka hesaplarının hiçbir koşulda üçüncü kişiler tarafından kullanılmaması gerektiği vurgulandı. Zam hesabı netleşti: Memur ve emeklinin 5 aylık enflasyon farkı belli oldu İçeriği Görüntüle SUÇ RİSKİ HATIRLATILDI Bankaların yaptığı uyarılarda, hesapların başka kişilere kullandırılması halinde yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı suçları kapsamında işlem yapılabileceği hatırlatıldı. Uzmanlar ise vatandaşların kısa vadeli maddi kazanç uğruna ciddi hukuki sorunlarla karşı karşıya kalabileceğine dikkat çekiyor. “HESAPLARINIZI HİÇBİR KOŞULDA ÜÇÜNCÜ KİŞİLERE KULLANDIRMAYINIZ” Ziraat Bankası, müşterilerine, “Değerli müşterimiz, hesaplarınızı hiçbir koşulda üçüncü kişilere kullandırmayınız. Hesabın bu şekilde kullandırılması; yasa dışı bahis ve kumar, dolandırıcılık, suç gelirlerinin aklanması ve terörün finansmanı gibi suçlara aracılık edilmesine ve hukuki sonuçlara sebep olabilir. Bilgilerinize sunar, sağlıklı günler dileriz” mesajını gönderdi. Kaynak: Haber Merkezi Editörün Seçtiği Acun Ilıcalı duyurdu: Survivor 2026 için final kararı Editörün Seçtiği Can Polat'ın cenazesinde Dilan Polat'a tepki: "Allah belanı versin" Editörün Seçtiği Bakan Fidan: "Netanyahu, bölgeyi savaş alanına çevirdi" Editör Hakkında Zülfinur Ecem Çetin Bunlar da i</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv Yaz geldi, sahte güneş kremi tuzağı başladı: Güneş kreminde sahtecilik uyarısı - Son Dakika Sağlık Haberleri Odatv</t>
+          <t>Banka hesabını kullandıranlar dikkat! Bankalar uyarıyor: Hapis cezasına kadar gidiyor! Banka hesabını kullandıranlar dikkat! Bankalar uyarıyor: Hapis cezasına kadar gidiyor! Türk İnform Bankalar, kullanıcılarına hesapların hiçbir koşulda üçüncü kişilere kullandırılmaması konusunda uyarılarda bulunuyor. Birçok suçlamayla karşı karşıya kalınabileceği ve hapis cezasına kadar gidebileceği belirtiliyor. Banka hesabını kullandıranlar dikkat! Bankalar uyarıyor: Hapis cezasına kadar gidiyor! Zülfinur Ecem Çetin Editör 04.06.2026 - 15:42 Yayınlanma 2 Dk Okunma Süresi</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNEZZZnA4aUtMdGtTM2dLd3FxUXJiZ0tDb2VORkdSSVdnX21hWHVfaXBMV2lwRnA3RC1OYTJSN1UzZldDdkUwRk9QQlc5d19hRDJXMHVPMk1vVXJ4ZHJFT3dfMmRINDk0ZkVubmlqOFBjVWt3Tkc2RWo4VzlnM0xFbmVtWGZybDM4bHBsS091REQyVGVTZzFiRDdvZUtOcHBKQ0FaSE9qTnVNMW9xRW1lWlNFYko3UQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://turkinform.com.tr/banka-hesabini-kullandiranlar-dikkat-bankalar-uyariyor-hapis-cezasina-kadar-gidiyor</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
@@ -3902,7 +4420,7 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="n">
-        <v>84.64</v>
+        <v>88.5</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>13</v>
@@ -3911,27 +4429,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:19:00</t>
+          <t>2026-06-04 23:22:40</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu</t>
+          <t>Muhittin Böcek ile oğlu ve gelininin mal varlıklarına el konuldu</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu STAR - Haberler</t>
+          <t>Muhittin Böcek ile oğlu ve gelininin mal varlıklarına el konuldu TRT Haber</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -3941,22 +4459,18 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>el konuldu</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>﻿Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangına müdahale ediliyor. ﻿ Kale Mahallesi'ndeki kauçuk fabrikasında henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Ekiplerin yangını kontrol altına alma çalışmaları sürüyor. Öte yandan fabrikadan yükselen siyah duman kentin birçok yerinden görülüyor. ﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu ﻿Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangına müdahale ediliyor. Kale Mahallesi'ndeki kauçuk fabrikasında henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Ekiplerin yangını kontrol altına alma çalışmaları sürüyor. Öte yandan fabrikadan yükselen siyah duman kentin birçok yerinden görülüyor.</t>
+          <t>İstanbul Cumhuriyet Başsavcılığınca yürütülen "rüşvet" soruşturması kapsamında, Antalya Büyükşehir Belediye Başkanlığı görevinden uzaklaştırılan Muhittin Böcek ile oğlu Mustafa Gökhan Böcek ve gelini Zuhal Böcek'in mal varlığına el konuldu. İstanbul Cumhuriyet Başsavcılığınca yürütülen "rüşvet" soruşturması kapsamında, Antalya Büyükşehir Belediye Başkanlığı görevinden uzaklaştırılan Muhittin Böcek ile oğlu Mustafa Gökhan Böcek ve gelini Zuhal Böcek'in mal varlığına el konuldu. İstanbul Cumhuriyet Başsavcılığınca yürütülen "rüşvet" soruşturması kapsamında, Antalya Büyükşehir Belediye Başkanlığı görevinden uzaklaştırılan Muhittin Böcek ile oğlu Mustafa Gökhan Böcek ve gelini Zuhal Böcek'in mal varlığına el konuldu. Gündem KAYNAK TRT Haber HABER GİRİŞ 06.05.2026 09:39 , 06.05.2026 10:26 Muhittin Böcek ile oğlu ve gelininin mal varlıklarına el konuldu İstanbul Cumhuriyet Başsavcılığınca yürütülen "rüşvet" soruşturması kapsamında, Antalya Büyükşehir Belediye Başkanlığı görevinden uzaklaştırılan Muhittin Böcek ile oğlu Mustafa Gökhan Böcek ve gelini Zuhal Böcek'in mal varlığına el konuldu. İstanbul Cumhuriyet Başsavcılığınca, Antalya Büyükşehir Belediye Başkanlığı görevinden uzaklaştırılan Muhittin Böcek hakkında belediye başkanlığına aday olmak için "rüşvet" verdiği iddiasıyla açılan soruşturma sürüyor. Soruşturma kapsamında, "rüşvet alma", "rüşveti temin etme", "irtikap", "suçtan kaynaklanan mal varlığı değerlerini aklama" suçlarından şüpheliler Muhittin Böcek ile oğlu Mustafa Gökhan Böcek ve gelini Zuhal Böcek'in mal varlığına el konuldu. Muhittin Böcek'in gelini Zuhal Böcek tutuklandı Rüşvet soruşturmasının detayları CHP'li Antalya Büyükşehir Belediyesi'ne yönelik yolsuzluk ve rüşvet davasında eski Antalya Büyükşehir Belediye Başkanı Muhittin Böcek ile oğlu Gökhan Böcek'in de aralarında bulunduğu 41 sanık yeniden hakim karşısında olacak. Antalya 6'ncı Ağır Ceza Mahkemesi'nde görülen davanın ilk duruşmasında Muhittin Böcek ve oğlu suçlamaları kabul etmemişti. Üçüncü duruşmada sanıklar savunmalarına devam edecek. Tanıkların da dinlenmesi bekleniyor. Mahkeme, geçen duruşmada Muhittin Böcek, Gökhan Böcek ve Fazlı Ateş'in tutukluluk hallerinin devamına karar vermişti. Davada Muhittin Böcek hakkında "icbar suretiyle irtikap", "haksız mal edinme" ve "suçtan kaynaklanan mal varlığı değerlerini aklama" suçlarından 15 yıl 6 aydan 44 yıla kadar hapis talep ediliyor. ETİKETLER Antalya Son Daki</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu ﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu STAR - Haberler ﻿Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangına müdahale ediliyor. ﻿ Kale Mahallesi'ndeki kauçuk fabrikasında henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Ekiplerin yangını kontrol altına alma çalışmaları sürüyor. Öte yandan fabrikadan yükselen siyah duman kentin birçok yerinden görülüyor. ﻿Denizli'de korkutan yangın: Fabrika alevlere teslim oldu ﻿Denizli'nin Pamukkale ilçesindeki bir kauçuk fabrikasında çıkan yangına müdahale ediliyor.</t>
+          <t>Muhittin Böcek ile oğlu ve gelininin mal varlıklarına el konuldu Muhittin Böcek ile oğlu ve gelininin mal varlıklarına el konuldu TRT Haber İstanbul Cumhuriyet Başsavcılığınca yürütülen "rüşvet" soruşturması kapsamında, Antalya Büyükşehir Belediye Başkanlığı görevinden uzaklaştırılan Muhittin Böcek ile oğlu Mustafa Gökhan Böcek ve gelini Zuhal Böcek'in mal varlığına el konuldu. Gündem KAYNAK TRT Haber HABER GİRİŞ 06.05.2026 09:39 , 06.05.2026 10:26 Muhittin Böcek ile oğlu ve gelininin mal varlıklarına el konuldu İstanbul Cumhuriyet Başsavcılığınca yürütülen "rüşvet" soruşturması kapsamında, Antalya Büyükşehir Belediye Başkanlığı görevinden uzaklaştırılan Muhittin Böcek ile oğlu Mustafa Gökhan Böcek ve gelini Zuhal Böcek'in mal varlığına el konuldu. İstanbul Cumhuriyet Başsavcılığınca, Antalya Büyükşehir Belediye Başkanlığı görevinden uzaklaştırılan Muhittin Böcek hakkında belediye başkanlığına aday olmak için "rüşvet" verdiği iddiasıyla açılan soruşturma sürüyor. Soruşturma kapsamında, "rüşvet alma", "rüşveti temin etme", "irtikap", "suçtan kaynaklanan mal varlığı değerlerini aklama" suçlarından şüpheliler Muhittin Böcek ile oğlu Mustafa Gökhan Böcek ve gelini Zuhal Böcek'in mal varlığına el konuldu. Muhittin Böcek'in gelini Zuhal Böcek tutuklandı Rüşvet soruşturmasının detayları CHP'li Antalya Büyükşehir Belediyesi'ne yönelik yolsuzluk ve rüşvet davasında eski Antalya Büyükşehir Belediye Başkanı Muhittin Böcek ile oğlu Gökhan Böcek'in de aralarında bulunduğu 41 sanık yeniden hakim karşısında olacak. Antalya 6'ncı Ağır Ceza Mahkemesi'nde görülen davanın ilk duruşmasında Muhittin Böcek ve oğlu suçlamaları kabul etmemişti. Üçüncü duruşmada sanıklar savunmalarına devam edecek. Tanıkların da dinlenmesi bekleniyor. Mahkeme, geçen duruşmada Muhittin Böcek, Gökhan Böcek ve Fazlı Ateş'in tutukluluk hallerinin devamına karar vermişti. Davada Muhittin Böcek hakkında "icbar suretiyle irtikap", "haksız mal edinme" ve "suçtan kaynaklanan mal varlığı değerlerini aklama" suçlarından 15 yıl 6 aydan 44 yıla kadar hapis talep ediliyor. ETİKETLER Antalya Son Daki</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -3966,31 +4480,23 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://m.star.com.tr/amp/guncel/denizlide-korkutan-yangin-fabrika-alevlere-teslim-oldu-haber-2019953/</t>
+          <t>https://www.trthaber.com/haber/gundem/muhittin-bocek-ile-oglu-ve-gelininin-mal-varliklarina-el-konuldu-944155.html</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Denizli | Malatya</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Kale</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Kale Mahallesi</t>
-        </is>
-      </c>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr"/>
@@ -4004,7 +4510,7 @@
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="n">
-        <v>113.2</v>
+        <v>83.5</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>14</v>
@@ -4013,27 +4519,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 17:21:00</t>
+          <t>2026-06-05 05:47:49</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü</t>
+          <t>Bahis gelirlerini aklayan İstanbul merkezli suç ağına darbe! Milyonlarca liralık mal varlığına el konuldu: 80 gözaltı</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü İnegöl Online</t>
+          <t>Bahis gelirlerini aklayan İstanbul merkezli suç ağına darbe! Milyonlarca liralık mal varlığına el konuldu: 80 gözaltı Takvim</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -4043,22 +4549,18 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>fabrika, osb, tekstil</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>el konuldu, mal varlığı</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Bursa İnegöl Organize Sanayi Bölgesi’ndeki bir tekstil fabrikasının bölümünde çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alındı. Bursa İnegöl Organize Sanayi Bölgesi’ndeki bir tekstil fabrikasının bölümünde çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alındı. Bursa İnegöl Organize Sanayi Bölgesi’ndeki bir tekstil fabrikasının bölümünde çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alındı.</t>
+          <t>İstanbul merkezli iki ayrı soruşturmada yasa dışı bahis ve suç gelirlerinin aklanmasına yönelik Türkiye çapında düğmeye basıldı. MASAK raporlarıyla ortaya... İstanbul merkezli iki ayrı soruşturmada yasa dışı bahis ve suç gelirlerinin aklanmasına yönelik Türkiye çapında düğmeye basıldı. MASAK raporlarıyla ortaya... İstanbul merkezli iki ayrı soruşturmada yasa dışı bahis ve suç gelirlerinin aklanmasına yönelik Türkiye çapında düğmeye basıldı. MASAK raporlarıyla ortaya... "Havuz Hesap" sistemiyle kurulan 193 milyarlık terör ağır çökertildi: 27 ilde eş zamanlı operasyon İstanbul merkezli iki ayrı soruşturmada yasa dışı bahis ve suç gelirlerinin aklanmasına yönelik Türkiye çapında düğmeye basıldı. MASAK raporlarıyla ortaya çıkarılan 193,3 milyar liralık dev para trafiğinin ardından 27 ilde eş zamanlı operasyon düzenlenirken, toplam 130 şüpheli hakkında adli işlem başlatıldı. Operasyonlarda milyonlarca liralık mal varlığına el konuldu, çok sayıda banka ve kripto hesap donduruldu. Takvim.com.tr Giriş Tarihi: 05 Haziran 2026 08:47 Güncelleme Tarihi: 05 Haziran 2026 10:53 Facebook X NSosyal Linki Kopyala Yazı Boyutu Hızlı Özet Göster İstanbul Emniyet Müdürlüğü Mali Suçlarla Mücadele Şube Müdürlüğü, Anadolu Cumhuriyet Başsavcılığı koordinesinde yasa dışı bahis gelirlerinin aklanmasına yönelik İstanbul merkezli 24 ilde operasyon düzenledi. Operasyonda şüpheli İ.Ö.Ö. tarafından yönetilen suç ağının yasal ve yasa dışı bahis faaliyetlerinden elde ettiği gelirleri kripto para cüzdanları üzerinden aktardığı tespit edildi. Soruşturmada gerçekleştirilen işlemlerin toplam hacminin yaklaşık 192 milyar liraya ulaştığı belirlendi. Operasyonda 80 şüpheli gözaltına alındı, 11 şirket, 45 araç, 16 konut, 11 tarla ve arsadan oluşan toplam 350 milyon liralık mal varlığına el konuldu. Şüphelilere ait banka hesapları ve kripto varlık hesapları hakkında bloke kararı uygulandı. İstanbul Anadolu Cumhuriyet Başsavcılığı koordinesinde yürütülen iki ayrı soruşturma kapsamında, yasa dışı bahis organizasyonları ve bu faaliyetlerden elde edilen suç gelirlerinin aklanmasına yönelik geniş çaplı operasyon gerçekleştirildi. Terörizmin Finansmanının Önlenmesi ve Aklama Suçu Soruşturma Bürosu ile Bilişim Suçları Soruşturma Bürosu tarafından yürütülen dosyalarda, yasa dışı bahis gelirlerinin banka hesapları, kripto varlık cüzdanları ve elektronik para sistemleri üzerinden dolaştırılarak aklanmaya çalışıldığı tespit edildi. MASAK RAPORU 193 MİLYAR LİRALIK TRAFİĞİ ORTAYA ÇIKARDI Terörizmin Finansmanının Önlenmesi ve Aklama Suçu Soruşturma Bürosu'nun yürüttüğü soruşturmada, MASAK tarafından hazırlanan rapor doğrultusunda liderliğini İbrahim Özgür Özel'in yaptığı değerlendirilen suç örgütü mercek altına alındı. Soruşturmada, aralarında Kapalıçarşı'da faaliyet gösteren döviz büroları ve kuyumculuk işletmelerinin sahiplerinin de bulunduğu çok sayıda kişinin örgütle bağlantılı hareket ettiği belirlendi. Yapılan incelemelerde örgütün, gelir düzeyi düşük, işsiz veya ekonomik sıkıntı yaşayan kişilere ait banka hesaplarını "havuz hesap" olarak kullandığı ortaya çıktı. Yasa dışı bahis gelirlerinin bu hesaplarda toplandığı, hesap sahiplerine ise hesaplarını kullandırmaları karşılığında yaklaşık 100 bin lira komisyon ödendiği tespit edildi. MASAK raporuna göre bazı hesaplarda kişi başına işlem hacminin 90 milyon liradan başladığı belirlendi. 27 ilde 193 milyarlık yasa dışı bahis operasyonu! PARA KRİPTO CÜZDANLAR VE YURT DIŞINA AKTARILDI Soruşturma kapsamında örgüt üyelerinin talimatları doğrultusunda hem yasal hem de yasa dışı bahis platformlarında yüksek tutarlı bahis işlemleri gerçekleştirildiği saptandı. Elde edilen gelirlerin önce örgüt yöneticileri ve üyelerinin hesaplarında dolaştırıldığı, ardından çok sayıda kripto varlık cüzdanı ve yurt dışındaki hesaplara aktarılıp izinin kaybettirilmeye çalışıldığı belirlendi. MASAK'ın tespitlerine göre; Yasal bahis şirketleri üzerinden elde edilen yüksek tutarlı kazançların bir bölümü yurt dışına gönderildi. Yasa dışı bahis gelirleri çok sayıda hesap arasında dolaştırıldı. Paralar daha sonra kaynağı belirlenemeyen kripto cüzdanlara ve yurt dışındaki hesaplara transfer edildi. Böylece suç gelirlerinin aklanmasına yönelik sistematik bir yapı kuruldu. Yapılan analizlerde yasa dışı bahis faaliyetlerine ilişkin toplam işlem hacminin 193 milyar 367 milyon 615 bin 703 liraya, yani yaklaşık 4 milyar dolara ulaştığı belirlendi. 27 İLDE EŞ ZAMANLI OPERASYON Soruşturma kapsamında elde edilen deliller doğrultusunda 5 Haziran 2026 sabahı İstanbul merkezli 27 ilde eş zamanlı operasyon düzenlendi. Haklarında gözaltı kararı bulunan 104 şüpheliden 13'ünün cezaevinde, 9'unun ise yurt dışında olduğu tespit edildi. Diğer şüphelilerin yakalanmasına yönelik çalışmalar sürüyor. Operasyon, İstanbul Emniyet Müdürlüğü Mali Suçlarla Mücadele Şube Müdürlüğü ekipleri tarafından gerçekleştirildi. ELEKTRONİK PARA ŞİRKETİ DE SORUŞTURMA KAPSAMINDA İstanbul Anadolu Cumhuriyet Başsavcılığı Bilişim Suçları Soruşturma Bürosu tarafından yürütülen ikinci soruşturmada ise Parolapara Elektronik Para ve Ödeme Hizmetleri A.Ş.'nin faaliyetleri incelendi. Türkiye Cumhuriyet Merkez Bankası tarafından hazırlanan raporda şirketin; Asgari öz kaynak yükümlülüğünü ihlal ettiği, Bankalara yapılması gereken bildirimlerde eksiklikler bulunduğu, İç kontrol ve risk yönetimi süreçlerinde mevzuata aykırı uygulamalar yaptığı, Müşteri tanıma (KYC) ve riskli işlemlerin takibinde ciddi eksiklikler bulunduğu tespit edildi. Yapılan incelemelerde şirket üzerinden örgütlü şekilde yürütülen faaliyetler kapsamında yasa dışı bahis ve suç gelirlerinin aklanmasına ilişkin kuvvetli şüphelere ulaşıldı. İŞLEM HACMİ BİR YILDA 100 KAT ARTTI Soruşturma dosyasına giren bilgilere göre şirketin kullandığı POS cihazları üzerinden gerçekleştirilen işlem hacmi 2023 yılında yaklaşık 22 milyon lira seviyesindeyken, 2024 yılında 2,1 milyar liraya yükseldi. Bu kapsamda 26 şüpheli hakkında iletişimin tespiti, dinlenmesi ve teknik takip tedbirleri uygulandı. Elde edilen deliller doğrultusunda İstanbul, Kocaeli ve Yalova'da eş zamanlı operasyon düzenlenerek 26 şüpheli hakkında gözaltı, arama, el koyma ve dijital materyal inceleme işlemleri gerçekleştirildi. Operasyon İstanbul İl Jandarma Komutanlığı ekiplerince yürütüldü. AKIN GÜRLEK'TAN SUÇLA MÜCADELEDE KARARLILIK MESAJI Adalet Bakanı Akın Gürlek, operasyonlara ilişkin yaptığı açıklamada Başkan Erdoğan'ın talimatları doğrultusunda ilgili kurumlarla koordinasyon içinde yasa dışı bahis, sanal kumar ve suç gelirlerinin aklanmasına karşı mücadelenin sürdürüldüğünü belirtti. Tunç, toplumun özellikle gençleri hedef alan yasa dışı bahis ve sanal kumar yapılanmalarına karşı mücadelenin tavizsiz şekilde devam edeceğini vurguladı. SONRAKİ HABER CHP'deki krizde bomba kulis ÖNCEKİ HABER Yeni nafaka formülü Meryem Kartal Takvim.com.tr Güncel Günün Manşetleri Tüm Manşetler</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü İnegöl OSB’de tekstil fabrikasında çıkan yangın kısa sürede söndürüldü İnegöl Online Bursa İnegöl Organize Sanayi Bölgesi’ndeki bir tekstil fabrikasının bölümünde çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alındı.</t>
+          <t>Bahis gelirlerini aklayan İstanbul merkezli suç ağına darbe! Milyonlarca liralık mal varlığına el konuldu: 80 gözaltı Bahis gelirlerini aklayan İstanbul merkezli suç ağına darbe! Milyonlarca liralık mal varlığına el konuldu: 80 gözaltı Takvim İstanbul merkezli iki ayrı soruşturmada yasa dışı bahis ve suç gelirlerinin aklanmasına yönelik Türkiye çapında düğmeye basıldı. MASAK raporlarıyla ortaya... "Havuz Hesap" sistemiyle kurulan 193 milyarlık terör ağır çökertildi: 27 ilde eş zamanlı operasyon İstanbul merkezli iki ayrı soruşturmada yasa dışı bahis ve suç gelirlerinin aklanmasına yönelik Türkiye çapında düğmeye basıldı. MASAK raporlarıyla ortaya çıkarılan 193,3 milyar liralık dev para trafiğinin ardından 27 ilde eş zamanlı operasyon düzenlenirken, toplam 130 şüpheli hakkında adli işlem başlatıldı. Operasyonlarda milyonlarca liralık mal varlığına el konuldu, çok sayıda banka ve kripto hesap donduruldu. Takvim.com.tr Giriş Tarihi: 05 Haziran 2026 08:47 Güncelleme Tarihi: 05 Haziran 2026 10:53 Facebook X NSosyal Linki Kopyala Yazı Boyutu Hızlı Özet Göster İstanbul Emniyet Müdürlüğü Mali Suçlarla Mücadele Şube Müdürlüğü, Anadolu Cumhuriyet Başsavcılığı koordinesinde yasa dışı bahis gelirlerinin aklanmasına yönelik İstanbul merkezli 24 ilde operasyon düzenledi. Operasyonda şüpheli İ.Ö.Ö. tarafından yönetilen suç ağının yasal ve yasa dışı bahis faaliyetlerinden elde ettiği gelirleri kripto para cüzdanları üzerinden aktardığı tespit edildi. Soruşturmada gerçekleştirilen işlemlerin toplam hacminin yaklaşık 192 milyar liraya ulaştığı belirlendi. Operasyonda 80 şüpheli gözaltına alındı, 11 şirket, 45 araç, 16 konut, 11 tarla ve arsadan oluşan toplam 350 milyon liralık mal varlığına el konuldu. İstanbul Anadolu Cumhuriyet Başsavcılığı koordinesinde yürütülen iki ayrı soruşturma kapsamında, yasa dışı bahis organizasyonları ve bu faaliyetlerden elde edilen suç gelirlerinin aklanmasına yönelik geniş çaplı operasyon gerçekleştirildi. Terörizmin Finansmanının Önlenmesi ve Aklama Suçu Soruşturma Bürosu ile Bilişim Suçları Soruşturma Bürosu tarafından yürütülen dosyalarda, yasa dışı bahis gelirlerinin banka hesapları, kripto varlık cüzdanları ve elektronik para sistemleri üzerinden dolaştırılarak aklanmaya çalışıldığı tespit edildi. MASAK RAPORU 193 MİLYAR LİRALIK TRAFİĞİ ORTAYA ÇIKARDI Terörizmin Finansmanının Önlenmesi ve Aklama Suçu Soruşturma Bürosu'nun yürüttüğü soruşturmada, MASAK tarafından hazırlanan rapor doğrultusunda liderliğini İbrahim Özgür Özel'in yaptığı değerlendirilen suç örgütü mercek altına alındı. Soruşturmada, aralarında Kapalıçarşı'da faaliyet gösteren döviz büroları ve kuyumculuk işletmelerinin sahiplerinin de bulunduğu çok sayıda kişinin örgütle bağlantılı hareket ettiği belirlendi. Yasa dışı bahis gelirlerinin bu hesaplarda toplandığı, hesap sahiplerine ise hesaplarını kullandırmaları karşılığında yaklaşık 100 bin lira komisyon ödendiği tespit edildi. MASAK raporuna göre bazı hesaplarda kişi başına işlem hacminin 90 milyon liradan başladığı belirlendi. 27 ilde 193 milyarlık yasa dışı bahis operasyonu! PARA KRİPTO CÜZDANLAR VE YURT DIŞINA AKTARILDI Soruşturma kapsamında örgüt üyelerinin talimatları doğrultusunda hem yasal hem de yasa dışı bahis platformlarında yüksek tutarlı bahis işlemleri gerçekleştirildiği saptandı. Elde edilen gelirlerin önce örgüt yöneticileri ve üyelerinin hesaplarında dolaştırıldığı, ardından çok sayıda kripto varlık cüzdanı ve yurt dışındaki hesaplara aktarılıp izinin kaybettirilmeye çalışıldığı belirlendi. MASAK'ın tespitlerine göre; Yasal bahis şirketleri üzerinden elde edilen yüksek tutarlı kazançların bir bölümü yurt dışına gönderildi. Yasa dışı bahis gelirleri çok sayıda hesap arasında dolaştırıldı. Paralar daha sonra kaynağı belirlenemeyen kripto cüzdanlara ve yurt dışındaki hesaplara transfer edildi. Böylece suç gelirlerinin aklanmasına yönelik sistematik bir yapı kuruldu. Yapılan analizlerde yasa dışı bahis faaliyetlerine ilişkin toplam işlem hacminin 193 milyar 367 milyon 615 bin 703 liraya, yani yaklaşık 4 milyar dolara ulaştığı belirlendi. 27 İLDE EŞ ZAMANLI OPERASYON Soruşturma kapsamında elde edilen deliller doğrultusunda 5 Haziran 2026 sabahı İstanbul merkezli 27 ilde eş zamanlı operasyon düzenlendi. Diğer şüphelilerin yakalanmasına yönelik çalışmalar sürüyor. Operasyon, İstanbul Emniyet Müdürlüğü Mali Suçlarla Mücadele Şube Müdürlüğü ekipleri tarafından gerçekleştirildi. ELEKTRONİK PARA ŞİRKETİ DE SORUŞTURMA KAPSAMINDA İstanbul Anadolu Cumhuriyet Başsavcılığı Bilişim Suçları Soruşturma Bürosu tarafından yürütülen ikinci soruşturmada ise Parolapara Elektronik Para ve Ödeme Hizmetleri A.Ş.'nin faaliyetleri incelendi. Türkiye Cumhuriyet Merkez Bankası tarafından hazırlanan raporda şirketin; Asgari öz kaynak yükümlülüğünü ihlal ettiği, Bankalara yapılması gereken bildirimlerde eksiklikler bulunduğu, İç kontrol ve risk yönetimi süreçlerinde mevzuata aykırı uygulamalar yaptığı, Müşteri tanıma (KYC) ve riskli işlemlerin takibinde ciddi eksiklikler bulunduğu tespit edildi. Yapılan incelemelerde şirket üzerinden örgütlü şekilde yürütülen faaliyetler kapsamında yasa dışı bahis ve suç gelirlerinin aklanmasına ilişkin kuvvetli şüphelere ulaşıldı. İŞLEM HACMİ BİR YILDA 100 KAT ARTTI Soruşturma dosyasına giren bilgilere göre şirketin kullandığı POS cihazları üzerinden gerçekleştirilen işlem hacmi 2023 yılında yaklaşık 22 milyon lira seviyesindeyken, 2024 yılında 2,1 milyar liraya yükseldi. Elde edilen deliller doğrultusunda İstanbul, Kocaeli ve Yalova'da eş zamanlı operasyon düzenlenerek 26 şüpheli hakkında gözaltı, arama, el koyma ve dijital materyal inceleme işlemleri gerçekleştirildi. Operasyon İstanbul İl Jandarma Komutanlığı ekiplerince yürütüldü. AKIN GÜRLEK'TAN SUÇLA MÜCADELEDE KARARLILIK MESAJI Adalet Bakanı Akın Gürlek, operasyonlara ilişkin yaptığı açıklamada Başkan Erdoğan'ın talimatları doğrultusunda ilgili kurumlarla koordinasyon içinde yasa dışı bahis, sanal kumar ve suç gelirlerinin aklanmasına karşı mücadelenin sürdürüldüğünü belirtti. Tunç, toplumun özellikle gençleri hedef alan yasa dışı bahis ve sanal kumar yapılanmalarına karşı mücadelenin tavizsiz şekilde devam edeceğini vurguladı.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -4068,31 +4570,23 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.inegolonline.com/haber/inegol-osb-de-tekstil-fabrikasinda-cikan-yangin-kisa-surede-sonduruldu-355721</t>
+          <t>https://www.takvim.com.tr/guncel/2026/06/05/bahis-gelirlerini-aklayan-istanbul-merkezli-suc-agina-darbe</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl OSB | kısa sürede söndürüldü İnegöl OSB</t>
-        </is>
-      </c>
+          <t>İstanbul | Yalova</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr"/>
@@ -4106,7 +4600,7 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="n">
-        <v>126.94</v>
+        <v>130.5</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>15</v>
@@ -4115,27 +4609,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:48:14</t>
+          <t>2026-06-05 07:06:28</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>banka hesaplarına bloke</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı</t>
+          <t>11 şirkete el konuldu! 24 ilde yasa dışı bahis operasyonu: 80 gözaltı</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7</t>
+          <t>11 şirkete el konuldu! 24 ilde yasa dışı bahis operasyonu: 80 gözaltı Bizim Tv</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -4145,7 +4639,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>inşaat, şirket</t>
+          <t>el konuldu, şirket</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -4155,26 +4649,34 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7</t>
+          <t>İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 kişi gözaltına alındı. Soruşturmada suç ağının 192 milyar liralık işlem hacmine ulaştığı belirlenirken, aralarında 11 şirketin de bulunduğu yaklaşık 350 milyon lira değerindeki mal varlığına el konuldu, banka ve kripto varlık hesapları bloke edildi. İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 kişi gözaltına alındı. Soruşturmada suç ağının 192 milyar liralık işlem hacmine ulaştığı belirlenirken, aralarında 11 şirketin de bulunduğu yaklaşık 350 milyon lira değerindeki mal varlığına el konuldu, banka ve kripto varlık hesapları bloke edildi. İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 kişi gözaltına alındı. Soruşturmada suç ağının 192 milyar liralık işlem hacmine ulaştığı belirlenirken, aralarında 11 şirketin de bulunduğu yaklaşık 350 milyon lira değerindeki mal varlığına el konuldu, banka ve kripto varlık hesapları bloke edildi. 11 şirkete el konuldu! 24 ilde yasa dışı bahis operasyonu: 80 gözaltı İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 kişi gözaltına alındı. Soruşturmada suç ağının 192 milyar liralık işlem hacmine ulaştığı belirlenirken, aralarında 11 şirketin de bulunduğu yaklaşık 350 milyon lira değerindeki mal varlığına el konuldu, banka ve kripto varlık hesapları bloke edildi. 05 Haziran 2026 Cuma 10:06 İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 şüpheli gözaltına alındı. Soruşturma kapsamında yaklaşık 350 milyon lira değerindeki mal varlığına el konulurken, şüphelilere ait banka ve kripto varlık hesapları da bloke edildi. İstanbul emniyeti Mali Suçlarla Mücadele Şube Müdürlüğü ekipleri, Anadolu Cumhuriyet Başsavcılığı koordinesinde yasa dışı bahis faaliyetlerinden elde edilen gelirlerin aklanmasına yönelik çalışma başlattı. Mali Suçları Araştırma Kurulu'nun (MASAK) yaptığı tespitlerde, şüpheli İ.Ö.Ö. tarafından koordine edilen suç ağının, önceden sonucu üzerinde anlaşma sağlanan müsabakalar ve yasal ile yasa dışı bahis faaliyetlerinden gelir elde ettiği belirlendi. Elde edilen gelirlerin kripto varlık cüzdanları aracılığıyla transfer edilerek kullanıcıları tespit edilemeyen farklı cüzdanlara aktarıldığı ortaya çıktı. Yapılan incelemelerde, suç ağı içerisinde döviz ve kuyumculuk sektöründe faaliyet gösteren kişilerin de yer aldığı, gerçekleştirilen işlemlerin toplam hacminin 192 milyar liraya ulaştığı belirlendi. BANKA VE KRİPTO HESAPLARINA BLOKE Soruşturma kapsamında bu sabah İstanbul merkezli 24 ilde düzenlenen eş zamanlı operasyonda 80 şüpheli yakalanarak gözaltına alındı. Operasyon kapsamında 11 şirkete, 45 araca, 16 konuta ve 11 tarla ile arsaya olmak üzere yaklaşık 350 milyon lira değerindeki toplam 83 menkul ve gayrimenkule el konuldu. Ayrıca şüphelilere ait banka hesapları ile kripto varlık hesaplarına bloke işlemi uygulandı. İlk yorum yazan siz olun Güncel Haberleri Akın Gürlek duyurdu... 27 ilde yasa dışı bahis operasyonu: 130 şüpheli hakkında adli işlem başlatıldı Buca Belediyesi soruşturması: Belediye başkanı Görkem Duman dahil 54 kişi adliyeye sevk edildi Meteoroloji açıkladı: Bugün hava nasıl olacak? 5 bin 300 yıllık mumyadan ekşi mayalı ekmek yaptılar Aziz Yıldırım'dan dikkat çeken Hakan Safi açıklaması: 'Fenerbahçe, gerçeklerle hayalleri ayırsın' İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 şüpheli gözaltına alındı. Soruşturma kapsamında yaklaşık 350 milyon lira değerindeki mal varlığına el konulurken, şüphelilere ait banka ve kripto varlık hesapları da bloke edildi. İstanbul emniyeti Mali Suçlarla Mücadele Şube Müdürlüğü ekipleri, Anadolu Cumhuriyet Başsavcılığı koordinesinde yasa dışı bahis faaliyetlerinden elde edilen gelirlerin aklanmasına yönelik çalışma başlattı. Mali Suçları Araştırma Kurulu'nun (MASAK) yaptığı tespitlerde, şüpheli İ.Ö.Ö. tarafından koordine edilen suç ağının, önceden sonucu üzerinde anlaşma sağlanan müsabakalar ve yasal ile yasa dışı bahis faaliyetlerinden gelir elde ettiği belirlendi. Elde edilen gelirlerin kripto varlık cüzdanları aracılığıyla transfer edilerek kullanıcıları tespit edilemeyen farklı cüzdanlara aktarıldığı ortaya çıktı. Yapılan incelemelerde, suç ağı içerisinde döviz ve kuyumculuk sektöründe faaliyet gösteren kişilerin de yer aldığı, gerçekleştirilen işlemlerin toplam hacminin 192 milyar liraya ulaştığı belirlendi. BANKA VE KRİPTO HESAPLARINA BLOKE Soruşturma kapsamında bu sabah İstanbul merkezli 24 ilde düzenlenen eş zamanlı operasyonda 80 şüpheli yakalanarak gözaltına alındı. Operasyon kapsamında 11 şirkete, 45 araca, 16 konuta ve 11 tarla ile arsaya olmak üzere yaklaşık 350 milyon lira değerindeki toplam 83 menkul ve gayrimenkule el konuldu. Ayrıca şüphelilere ait banka hesapları ile kripto varlık hesaplarına bloke işlemi uygulandı. 11 şirkete el konuldu! 24 ilde yasa dışı bahis operasyonu: 80 gözaltı İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 kişi gözaltına alındı. Soruşturmada suç ağının 192 milyar liralık işlem hacmine ulaştığı belirlenirken, aralarında 11 şirketin de bulunduğu yaklaşık 350 milyon lira değerindeki mal varlığına el konuldu, banka ve kripto varlık hesapları bloke edildi. İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 şüpheli gözaltına alındı. Soruşturma kapsamında yaklaşık 350 milyon lira değerindeki mal varlığına el konulurken, şüphelilere ait banka ve kripto varlık hesapları da bloke edildi. İstanbul emniyeti Mali Suçlarla Mücadele Şube Müdürlüğü ekipleri, Anadolu Cumhuriyet Başsavcılığı koordinesinde yasa dışı bahis faaliyetlerinden elde edilen gelirlerin aklanmasına yönelik çalışma başlattı. Mali Suçları Araştırma Kurulu'nun (MASAK) yaptığı tespitlerde, şüpheli İ.Ö.Ö. tarafından koordine edilen suç ağının, önceden sonucu üzerinde anlaşma sağlanan müsabakalar ve yasal ile yasa dışı bahis faaliyetlerinden gelir elde ettiği belirlendi. Elde edilen gelirlerin kripto varlık cüzdanları aracılığıyla transfer edilerek kullanıcıları tespit edilemeyen farklı cüzdanlara aktarıldığı ortaya çıktı. Yapılan incelemelerde, suç ağı içerisinde döviz ve kuyumculuk sektöründe faaliyet gösteren kişilerin de yer aldığı, gerçekleştirilen işlemlerin toplam hacminin 192 milyar liraya ulaştığı belirlendi. Soruşturma kapsamında bu sabah İstanbul merkezli 24 ilde düzenlenen eş zamanlı operasyonda 80 şüpheli yakalanarak gözaltına alındı. Operasyon kapsamında 11 şirkete, 45 araca, 16 konuta ve 11 tarla ile arsaya olmak üzere yaklaşık 350 milyon lira değerindeki toplam 83 menkul ve gayrimenkule el konuldu. Ayrıca şüphelilere ait banka hesapları ile kripto varlık hesaplarına bloke işlemi uygulandı.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7 Türk inşaat şirketi iflas etti: Mali krizden çıkamadı Haber 7</t>
+          <t>11 şirkete el konuldu! 24 ilde yasa dışı bahis operasyonu: 80 gözaltı 11 şirkete el konuldu! 24 ilde yasa dışı bahis operasyonu: 80 gözaltı Bizim Tv İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 kişi gözaltına alındı. Soruşturmada suç ağının 192 milyar liralık işlem hacmine ulaştığı belirlenirken, aralarında 11 şirketin de bulunduğu yaklaşık 350 milyon lira değerindeki mal varlığına el konuldu, banka ve kripto varlık hesapları bloke edildi. 24 ilde yasa dışı bahis operasyonu: 80 gözaltı İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 kişi gözaltına alındı. 05 Haziran 2026 Cuma 10:06 İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 şüpheli gözaltına alındı. Soruşturma kapsamında yaklaşık 350 milyon lira değerindeki mal varlığına el konulurken, şüphelilere ait banka ve kripto varlık hesapları da bloke edildi. İstanbul emniyeti Mali Suçlarla Mücadele Şube Müdürlüğü ekipleri, Anadolu Cumhuriyet Başsavcılığı koordinesinde yasa dışı bahis faaliyetlerinden elde edilen gelirlerin aklanmasına yönelik çalışma başlattı. Mali Suçları Araştırma Kurulu'nun (MASAK) yaptığı tespitlerde, şüpheli İ.Ö.Ö. tarafından koordine edilen suç ağının, önceden sonucu üzerinde anlaşma sağlanan müsabakalar ve yasal ile yasa dışı bahis faaliyetlerinden gelir elde ettiği belirlendi. Yapılan incelemelerde, suç ağı içerisinde döviz ve kuyumculuk sektöründe faaliyet gösteren kişilerin de yer aldığı, gerçekleştirilen işlemlerin toplam hacminin 192 milyar liraya ulaştığı belirlendi. BANKA VE KRİPTO HESAPLARINA BLOKE Soruşturma kapsamında bu sabah İstanbul merkezli 24 ilde düzenlenen eş zamanlı operasyonda 80 şüpheli yakalanarak gözaltına alındı. Operasyon kapsamında 11 şirkete, 45 araca, 16 konuta ve 11 tarla ile arsaya olmak üzere yaklaşık 350 milyon lira değerindeki toplam 83 menkul ve gayrimenkule el konuldu. 27 ilde yasa dışı bahis operasyonu: 130 şüpheli hakkında adli işlem başlatıldı Buca Belediyesi soruşturması: Belediye başkanı Görkem Duman dahil 54 kişi adliyeye sevk edildi Meteoroloji açıkladı: Bugün hava nasıl olacak? 5 bin 300 yıllık mumyadan ekşi mayalı ekmek yaptılar Aziz Yıldırım'dan dikkat çeken Hakan Safi açıklaması: 'Fenerbahçe, gerçeklerle hayalleri ayırsın' İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 şüpheli gözaltına alındı. İstanbul merkezli 24 ilde yasa dışı bahis gelirlerinin aklanmasına yönelik düzenlenen operasyonda 80 şüpheli gözaltına alındı. Soruşturma kapsamında bu sabah İstanbul merkezli 24 ilde düzenlenen eş zamanlı operasyonda 80 şüpheli yakalanarak gözaltına alındı.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQZzNLMFdlUURuR004Mk9ScmtLbTZUbHNqak1aUWZFcVpBNjViYmZRWDVTcTJWLWNlZEs5ZEFIQ0lkUHBEUDFVLXBpd1dhb0VpemJzY3lZWmVsdjI0WVM3dzVZRmFndVlSNVQ1cERGS1ZaVjMzUGg0MGNuNFJXSFVjOExEcGRZNUx4MzVnclhFUlI1eHlRUlRXcGdEUmZnUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>https://bizimtv.com.tr/service/amp/guncel/11-sirkete-el-konuldu-24-ilde-yasa-disi-bahis-operasyonu-80-gozalti-122706h</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Bursa</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Yıldırım</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -4182,7 +4684,7 @@
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr"/>
@@ -4196,7 +4698,7 @@
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="n">
-        <v>50.36</v>
+        <v>105</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>16</v>
@@ -4205,27 +4707,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:41:40</t>
+          <t>2026-06-04 09:29:00</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı.</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Vietnam.vn</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu Sosyal TV</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -4235,31 +4737,35 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>işletme</t>
+          <t>el konuldu, mal varlığı</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Vietnam.vn</t>
+          <t>Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı. Vietnam.vn Karides yetiştirmek için 100 milyar VND'den fazla borç alan işletme iflas etti ve bir dizi arazi mülkiyet belgesine el konulma riskiyle karşı karşıya kaldı.</t>
+          <t>Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu Uyuşturucu gelirlerini aklayan şebekeye operasyon: 15 milyar TL'lik mal varlığına el konuldu Sosyal TV Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVmpWeXVfOE81SzFkZkdVRUlTeHhpUTNYamdkLU1JYXlfeGNWRGRQcFFjQXRQcnJ3VlJrdnpoTHZTQWR3bE5HVGZNbVloaWxmQU9CNlp1dFptOGtyZWFMeXZpeU5HUVJKQWlpT3licFVEakdidm5aX0pObDZON2ZmV0VnRjhwSGxCNjZuRHp4dDY1ZlVuRUd2WFcwT09DMWxi?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>https://www.sosyaltv.com.tr/uyusturucu-gelirlerini-aklayan-sebekeye-operasyon-15-milyar-tllik-mal-varligina-el-konuldu</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -4268,7 +4774,7 @@
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr"/>
@@ -4282,7 +4788,7 @@
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="n">
-        <v>137.42</v>
+        <v>105.47</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>17</v>
@@ -4291,27 +4797,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:30:00</t>
+          <t>2026-06-04 17:34:00</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı</t>
+          <t>UYUŞTURUCU PARASINI AKLIYORLARDI: 15 MİLYAR TL'LİK MAL VARLIĞINA EL KONULDU</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi</t>
+          <t>UYUŞTURUCU PARASINI AKLIYORLARDI: 15 MİLYAR TL'LİK MAL VARLIĞINA EL KONULDU Haber Alternatif</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -4321,18 +4827,18 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>inşaat</t>
+          <t>el konuldu, mal varlığı</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi</t>
+          <t>UYUŞTURUCU PARASINI AKLIYORLARDI: 15 MİLYAR TL'LİK MAL VARLIĞINA EL KONULDU Haber Alternatif</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi Alüminyum ve inşaat sektörünün köklü ismi iflas etti: 15 yıllık tecrübesi vardı Yeniçağ Gazetesi</t>
+          <t>UYUŞTURUCU PARASINI AKLIYORLARDI: 15 MİLYAR TL'LİK MAL VARLIĞINA EL KONULDU UYUŞTURUCU PARASINI AKLIYORLARDI: 15 MİLYAR TL'LİK MAL VARLIĞINA EL KONULDU Haber Alternatif UYUŞTURUCU PARASINI AKLIYORLARDI: 15 MİLYAR TL'LİK MAL VARLIĞINA EL KONULDU Haber Alternatif</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -4342,7 +4848,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.yenicaggazetesi.com/aluminyum-ve-insaat-sektorunun-koklu-ismi-iflas-etti-15-yillik-tecrubesi-vardi-1036532h.htm</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNX1J3Q3R4X2hja1hSZHNyZTB3Um9ydDFUVUZUdGNNTHl5YlVHVXNEdkRrMXFfeElWQ0xfR1B0RzNBOF9udm5iS1VQSXB6ZEZNaWUzNzRXU0VSbGxFeW1qUXVIeW5zblo4RDlFMEVMS3VuZHlrNUJyNXVEcThPby12VW9zcGZwbVdMaTVRSzZFLUVXSV9fR0hyVURFcnMtTnBiU19JNg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
@@ -4368,7 +4874,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="n">
-        <v>80.45999999999999</v>
+        <v>77.42</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>18</v>
@@ -4377,27 +4883,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 14:41:37</t>
+          <t>2026-06-04 15:13:55</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>para aklama</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi</t>
+          <t>Siirt’te Telefonlara Peş Peşe Aynı Mesaj Geldi: Bankalardan “Hesabınızı Kullandırmayın” Uyarısı</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi Foreks.com</t>
+          <t>Siirt’te Telefonlara Peş Peşe Aynı Mesaj Geldi: Bankalardan “Hesabınızı Kullandırmayın” Uyarısı siirthaberci.com</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -4407,18 +4913,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>tekstil</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Akın Tekstil A.Ş., konkordato sürecine ilişkin Kamuyu Aydınlatma Platformu'na açıklama yaptı. Akın Tekstil A.Ş., konkordato sürecine ilişkin Kamuyu Aydınlatma Platformu'na açıklama yaptı. Akın Tekstil A.Ş., konkordato sürecine ilişkin Kamuyu Aydınlatma Platformu'na açıklama yaptı.</t>
+          <t>Bankalar, hesap ve IBAN bilgilerini başkalarına kullandıran vatandaşların ciddi hukuki ve mali sorunlarla karşı karşıya kalabileceğine dikkat çekti. Bankalar, hesap ve IBAN bilgilerini başkalarına kullandıran vatandaşların ciddi hukuki ve mali sorunlarla karşı karşıya kalabileceğine dikkat çekti. Bankalar, hesap ve IBAN bilgilerini başkalarına kullandıran vatandaşların ciddi hukuki ve mali sorunlarla karşı karşıya kalabileceğine dikkat çekti.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi Akın Tekstil'in konkordato talebine ilişkin duruşma tarihi belirlendi Foreks.com Akın Tekstil A.Ş., konkordato sürecine ilişkin Kamuyu Aydınlatma Platformu'na açıklama yaptı.</t>
+          <t>Siirt’te Telefonlara Peş Peşe Aynı Mesaj Geldi: Bankalardan “Hesabınızı Kullandırmayın” Uyarısı Siirt’te Telefonlara Peş Peşe Aynı Mesaj Geldi: Bankalardan “Hesabınızı Kullandırmayın” Uyarısı siirthaberci.com Bankalar, hesap ve IBAN bilgilerini başkalarına kullandıran vatandaşların ciddi hukuki ve mali sorunlarla karşı karşıya kalabileceğine dikkat çekti.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -4428,57 +4938,37 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.foreks.com/haber/detay/akin-tekstil-in-konkordato-talebine-iliskin-durusma-tarihi-belirlendi-03-06-26/?haber_id=6a203d2167ad3132ebe399d5&amp;lang=tr&amp;category=PICNEWS/</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>https://www.siirthaberci.com/haber/siirtte-telefonlara-pes-pese-ayni-mesaj-geldi-bankalardan-hesabinizi-kullandirmayin-uyarisi-131411</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Siirt</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>Akın Tekstil A.Ş</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>Akın Tekstil:292:body+summary+title | Akın Tekstil A.Ş:raw_legal</t>
-        </is>
-      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>Akın Tekstil A.Ş Türkiye</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>AKIN TEKSTİL | Akın Tekstil</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>AKIN TEKSTİL</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t>82.75862068965517 | 100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="n">
-        <v>171.31</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>19</v>
@@ -4487,12 +4977,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:30:00</t>
+          <t>2026-06-04 09:41:34</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4502,12 +4992,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı</t>
+          <t>Banka hesabına 1 trilyon lira geldi, hayatı kabusa döndü: Bu süreç iflasıma neden olabilir</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı Kanal 46</t>
+          <t>Banka hesabına 1 trilyon lira geldi, hayatı kabusa döndü: Bu süreç iflasıma neden olabilir SonDakika</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -4517,22 +5007,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>firma, tekstil</t>
+          <t>banka, banka hesabı</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>www.kanal46.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.kanal46.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.kanal46.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>İş için Van'a giden Ahmad Jahangard Takalo, banka hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu görünce büyük şaşkınlık yaşadı. Kaynağı belirsiz para nedeniyle MASAK tarafından tüm hesapları dondurulan Takalo, hesaplarına erişemediği için işlerinin aksadığını söyledi. İki Ar-Ge şirketi bulunan Takalo, sürecin bir-iki ay daha uzaması halinde iflas edebileceğini belirterek sorunun bir an önce çözülmesini istedi. İş için Van'a giden Ahmad Jahangard Takalo, banka hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu görünce büyük şaşkınlık yaşadı. Kaynağı belirsiz para nedeniyle MASAK tarafından tüm hesapları dondurulan Takalo, hesaplarına erişemediği için işlerinin aksadığını söyledi. İki Ar-Ge şirketi bulunan Takalo, sürecin bir-iki ay daha uzaması halinde iflas edebileceğini belirterek sorunun bir an önce çözülmesini istedi. İş için Van'a giden Ahmad Jahangard Takalo, banka hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu görünce büyük şaşkınlık yaşadı. Kaynağı belirsiz para nedeniyle MASAK tarafından tüm hesapları dondurulan Takalo, hesaplarına erişemediği için işlerinin aksadığını söyledi. İki Ar-Ge şirketi bulunan Takalo, sürecin bir-iki ay daha uzaması halinde iflas edebileceğini belirterek sorunun bir an önce çözülmesini istedi. Balıkesir 'de yaşayan ve iş gezisi için Van 'a giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakam karşısında büyük şaşkınlık yaşadı. Hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu öğrenen Takalo'nun tüm hesapları, kaynağı belirsiz para hareketi nedeniyle MASAK tarafından donduruldu. Yaklaşık 10 yıl önce Türkiye'ye yerleşen Takalo, olayın Van'da alışveriş yaptığı sırada kartlarının çalışmamasıyla ortaya çıktığını anlattı. Sorunun kartlardan kaynaklandığını düşünerek bankaya giden Takalo, hesabına yaklaşık 1 trilyon lira geçtiğini öğrenince hayatının şokunu yaşadığını söyledi. "HAYATIM 180 DERECE DEĞİŞTİ" Uluslararası mucit olduğunu ve Türkiye'de iki Ar-Ge şirketi bulunduğunu belirten Takalo, yaşadığı süreci "hem komik hem de korkunç" olarak tanımladı. Daha önce annesinin hesabına da yanlışlıkla milyonlarca lira gönderildiğini anlatan Takalo, o olayın kısa sürede çözüldüğünü ancak bu kez durumun çok daha karmaşık olduğunu ifade etti. Hesaplarının dondurulması nedeniyle işlerinin ciddi şekilde aksadığını söyleyen Takalo, "Hayatım 180 derece değişti. Normal hayatımı ve düzenimi özledim. Hesaplarımın kapalı olması faaliyetlerimi durma noktasına getirdi" dedi. "BİR ANDA HERKES AKRABAM OLDU" Olayın duyulmasının ardından yoğun telefon trafiği yaşadığını belirten Takalo, yeni telefon numarası almasına rağmen sürekli arandığını söyledi. Takalo, "Herkes para istiyor. Sanki bu parayı kullanabiliyormuşum gibi davranıyorlar. Bir anda herkes benimle akraba olmaya başladı" ifadelerini kullandı. "BU SÜREÇ İFLASIMA NEDEN OLABİLİR" Tüm hesaplarının bloke edilmesi nedeniyle mağdur olduğunu belirten Takalo, sürecin uzaması halinde şirketlerinin faaliyetlerinin ciddi zarar görebileceğini söyledi. Bir-iki ay daha bu şekilde devam etmesi halinde iflas riskiyle karşı karşıya kalabileceğini ifade eden Takalo, olayın bir an önce aydınlatılmasını ve hesaplarının yeniden açılmasını istedi. Konuyla ilgili hukuki sürecin devam ettiği öğrenilirken, Takalo gerçek para sahibinin bulunarak yaşanan karmaşanın sona ermesini beklediğini söyledi. Kaynak: ANKA Mali Suçları Araştırma Kurulu , Yerel Haberler , Azerbaycan , Balıkesir , Alışveriş , 3. Sayfa , Ekonomi , Finans , Güncel , Yaşam , Banka , Van , Son Dakika S</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı Kahramanmaraş'ta bir tekstil firması daha iflas bayrağını çekti! Alacaklılara çağrı Kanal 46 www.kanal46.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.kanal46.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.kanal46.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Banka hesabına 1 trilyon lira geldi, hayatı kabusa döndü: Bu süreç iflasıma neden olabilir Banka hesabına 1 trilyon lira geldi, hayatı kabusa döndü: Bu süreç iflasıma neden olabilir SonDakika İş için Van'a giden Ahmad Jahangard Takalo, banka hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu görünce büyük şaşkınlık yaşadı. Kaynağı belirsiz para nedeniyle MASAK tarafından tüm hesapları dondurulan Takalo, hesaplarına erişemediği için işlerinin aksadığını söyledi. İki Ar-Ge şirketi bulunan Takalo, sürecin bir-iki ay daha uzaması halinde iflas edebileceğini belirterek sorunun bir an önce çözülmesini istedi. Balıkesir 'de yaşayan ve iş gezisi için Van 'a giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakam karşısında büyük şaşkınlık yaşadı. Hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu öğrenen Takalo'nun tüm hesapları, kaynağı belirsiz para hareketi nedeniyle MASAK tarafından donduruldu. Yaklaşık 10 yıl önce Türkiye'ye yerleşen Takalo, olayın Van'da alışveriş yaptığı sırada kartlarının çalışmamasıyla ortaya çıktığını anlattı. Sorunun kartlardan kaynaklandığını düşünerek bankaya giden Takalo, hesabına yaklaşık 1 trilyon lira geçtiğini öğrenince hayatının şokunu yaşadığını söyledi. "HAYATIM 180 DERECE DEĞİŞTİ" Uluslararası mucit olduğunu ve Türkiye'de iki Ar-Ge şirketi bulunduğunu belirten Takalo, yaşadığı süreci "hem komik hem de korkunç" olarak tanımladı. Daha önce annesinin hesabına da yanlışlıkla milyonlarca lira gönderildiğini anlatan Takalo, o olayın kısa sürede çözüldüğünü ancak bu kez durumun çok daha karmaşık olduğunu ifade etti. Hesaplarının dondurulması nedeniyle işlerinin ciddi şekilde aksadığını söyleyen Takalo, "Hayatım 180 derece değişti. Hesaplarımın kapalı olması faaliyetlerimi durma noktasına getirdi" dedi. "BİR ANDA HERKES AKRABAM OLDU" Olayın duyulmasının ardından yoğun telefon trafiği yaşadığını belirten Takalo, yeni telefon numarası almasına rağmen sürekli arandığını söyledi. Bir anda herkes benimle akraba olmaya başladı" ifadelerini kullandı. "BU SÜREÇ İFLASIMA NEDEN OLABİLİR" Tüm hesaplarının bloke edilmesi nedeniyle mağdur olduğunu belirten Takalo, sürecin uzaması halinde şirketlerinin faaliyetlerinin ciddi zarar görebileceğini söyledi. Bir-iki ay daha bu şekilde devam etmesi halinde iflas riskiyle karşı karşıya kalabileceğini ifade eden Takalo, olayın bir an önce aydınlatılmasını ve hesaplarının yeniden açılmasını istedi. Konuyla ilgili hukuki sürecin devam ettiği öğrenilirken, Takalo gerçek para sahibinin bulunarak yaşanan karmaşanın sona ermesini beklediğini söyledi. Kaynak: ANKA Mali Suçları Araştırma Kurulu , Yerel Haberler , Azerbaycan , Balıkesir , Alışveriş , 3.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -4542,12 +5032,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.kanal46.com/kahramanmarasta-bir-tekstil-firmasi-daha-iflas-bayragini-cekti-alacaklilara-cagri</t>
+          <t>https://www.sondakika.com/guncel/haber-azerbaycanli-isadaminin-hesabinda-999-milyar-tl-sa-19910017/</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş</t>
+          <t>Balıkesir | Van</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr"/>
@@ -4572,7 +5062,7 @@
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="n">
-        <v>95.81</v>
+        <v>101</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>20</v>
@@ -4581,27 +5071,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:44:00</t>
+          <t>2026-06-04 11:05:34</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor</t>
+          <t>Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor Mavi Marmara Gazetesi</t>
+          <t>Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu avazturk.com</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -4611,18 +5101,22 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>mal varlığı</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>banka, banka hesabı</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarıl... Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarılıyor. Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarıl...</t>
+          <t>Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu fark eden Takalo’nun tüm hesapları, kaynağı belirsiz para hareketi nedeniyle MASAK tarafından donduruldu. Yaşanan gelişme sonrası Takalo, hesaplarına erişemediği için işlerinin aksadığını ve şirketlerinin risk altına girdiğini açıkladı. Kartı Çalışmadı, Gerçek Bankada Ortaya Çıktı Balıkesir’de yaşayan ve iş gezisi kapsamında Van’a giden Takalo, alışveriş sırasında kartlarının çalışmaması üzerine bankaya başvurdu. İlk etapta teknik bir sorun olduğunu düşünen girişimci, banka hesabında neredeyse 1 trilyon liraya yakın bir bakiye göründüğünü öğrenince şaşkınlık yaşadı. Yaklaşık 10 yıl önce Türkiye’ye yerleştiğini belirten Takalo’nun hesapları, söz konusu astronomik tutarın kaynağının belirsiz olması nedeniyle incelemeye alındı. MASAK tarafından yürütülen süreç kapsamında tüm banka hesaplarına bloke konuldu. “Hayatım 180 Derece Değişti” Uluslararası mucit olduğunu ve Türkiye’de iki Ar-Ge şirketi bulunduğunu dile getiren Takalo, yaşadıklarını “hem komik hem de korkunç” sözleriyle anlattı. Daha önce annesinin hesabına da yanlışlıkla milyonlarca lira gönderildiğini, ancak o olayın kısa sürede çözüldüğünü belirten girişimci, bu kez karşı karşıya kaldığı tablonun çok daha karmaşık olduğunu ifade etti. “Hayatım 180 derece değişti. Normal düzenimi özledim. Hesaplarım kapalı olduğu için işlerim durma noktasına geldi” diyen Takalo, sürecin uzamasından endişe duyduğunu vurguladı. “Bir Anda Herkes Akrabam Oldu” Olayın duyulmasının ardından yoğun telefon trafiği yaşadığını aktaran Takalo, yeni bir hat almak zorunda kaldığını söyledi. Yaşananların ardından çevresinden para talepleri aldığını ifade eden girişimci, “Sanki o parayı kullanabiliyormuşum gibi davranıyorlar. Bir anda herkes akrabam oldu” sözleriyle dikkat çekti. İflas Uyarısı Tüm hesaplarının bloke edilmesi nedeniyle ciddi mağduriyet yaşadığını belirten Takalo, sürecin bir ya da iki ay daha uzaması halinde şirketlerinin iflas riskiyle karşı karşıya kalabileceğini söyledi. İki Ar-Ge şirketinin faaliyetlerinin aksadığını ifade eden Takalo, olayın bir an önce netleşmesini ve gerçek para sahibinin bulunmasını beklediğini dile getirdi. Konuya ilişkin hukuki sürecin devam ettiği öğrenildi. Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu fark eden Takalo’nun tüm hesapları, kaynağı belirsiz para hareketi nedeniyle MASAK tarafından donduruldu. Yaşanan gelişme sonrası Takalo, hesaplarına erişemediği için işlerinin aksadığını ve şirketlerinin risk altına girdiğini açıkladı. Kartı Çalışmadı, Gerçek Bankada Ortaya Çıktı Balıkesir’de yaşayan ve iş gezisi kapsamında Van’a giden Takalo, alışveriş sırasında kartlarının çalışmaması üzerine bankaya başvurdu. İlk etapta teknik bir sorun olduğunu düşünen girişimci, banka hesabında neredeyse 1 trilyon liraya yakın bir bakiye göründüğünü öğrenince şaşkınlık yaşadı. Yaklaşık 10 yıl önce Türkiye’ye yerleştiğini belirten Takalo’nun hesapları, söz konusu astronomik tutarın kaynağının belirsiz olması nedeniyle incelemeye alındı. MASAK tarafından yürütülen süreç kapsamında tüm banka hesaplarına bloke konuldu. “Hayatım 180 Derece Değişti” Uluslararası mucit olduğunu ve Türkiye’de iki Ar-Ge şirketi bulunduğunu dile getiren Takalo, yaşadıklarını “hem komik hem de korkunç” sözleriyle anlattı. Daha önce annesinin hesabına da yanlışlıkla milyonlarca lira gönderildiğini, ancak o olayın kısa sürede çözüldüğünü belirten girişimci, bu kez karşı karşıya kaldığı tablonun çok daha karmaşık olduğunu ifade etti. “Hayatım 180 derece değişti. Normal düzenimi özledim. Hesaplarım kapalı olduğu için işlerim durma noktasına geldi” diyen Takalo, sürecin uzamasından endişe duyduğunu vurguladı. “Bir Anda Herkes Akrabam Oldu” Olayın duyulmasının ardından yoğun telefon trafiği yaşadığını aktaran Takalo, yeni bir hat almak zorunda kaldığını söyledi. Yaşananların ardından çevresinden para talepleri aldığını ifade eden girişimci, “Sanki o parayı kullanabiliyormuşum gibi davranıyorlar. Bir anda herkes akrabam oldu” sözleriyle dikkat çekti. İflas Uyarısı Tüm hesaplarının bloke edilmesi nedeniyle ciddi mağduriyet yaşadığını belirten Takalo, sürecin bir ya da iki ay daha uzaması halinde şirketlerinin iflas riskiyle karşı karşıya kalabileceğini söyledi. İki Ar-Ge şirketinin faaliyetlerinin aksadığını ifade eden Takalo, olayın bir an önce netleşmesini ve gerçek para sahibinin bulunmasını beklediğini dile getirdi. Konuya ilişkin hukuki sürecin devam ettiği öğrenildi. Yaşam Bozcaada, National Geographic’in 2026 “Dünyanın En İyi 15 Yemek Destinasyonu” Listesinde Hatay’da Korku Dolu Gece! Heyelan Evi Yıktı, Acı Haber Geldi Prof. Dr. Oytun Erbaş’tan Hantavirüs Uyarısı: “Kovidin Öldürücülüğüyle Hantavirüs Kıyaslanamaz Bile” Malatya’da Okullar Tatil mi? 5.6’lık Deprem Sonrası Son Durum Meteoroloji’den 81 İle Sağanak Uyarısı: 5 İlde Sarı Kodlu Sel Alarmı Meteoroloji'den Sarı Kodlu Uyarı: Yaz Gelmeden Soğuk Hava ve Kuvvetli Sağanak Kapıda TÜVTÜRK’te “5 Milyon Dolar” Şakası! Rus Kadın Ters Köşe Oldu Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu fark eden Takalo’nun tüm hesapları, kaynağı belirsiz para hareketi nedeniyle MASAK tarafından donduruldu. Yaşanan gelişme sonrası Takalo, hesaplarına erişemediği için işlerinin aksadığını ve şirketlerinin risk altına girdiğini açıkladı. Kartı Çalışmadı, Gerçek Bankada Ortaya Çıktı Balıkesir’de yaşayan ve iş gezisi kapsamında Van’a giden Takalo, alışveriş sırasında kartlarının çalışmaması üzerine bankaya başvurdu. İlk etapta teknik bir sorun olduğunu düşünen girişimci, banka hesabında neredeyse 1 trilyon liraya yakın bir bakiye göründüğünü öğrenince şaşkınlık yaşadı. Yaklaşık 10 yıl önce Türkiye’ye yerleştiğini belirten Takalo’nun hesapları, söz konusu astronomik tutarın kaynağının belirsiz olması nedeniyle incelemeye alındı. MASAK tarafından yürütülen süreç kapsamında tüm banka hesaplarına bloke konuldu. “Hayatım 180 Derece Değişti” Uluslararası mucit olduğunu ve Türkiye’de iki Ar-Ge şirketi bulunduğunu dile getiren Takalo, yaşadıklarını “hem komik hem de korkunç” sözleriyle anlattı. Daha önce annesinin hesabına da yanlışlıkla milyonlarca lira gönderildiğini, ancak o olayın kısa sürede çözüldüğünü belirten girişimci, bu kez karşı karşıya kaldığı tablonun çok daha karmaşık olduğunu ifade etti. “Hayatım 180 derece değişti. Normal düzenimi özledim. Hesaplarım kapalı olduğu için işlerim durma noktasına geldi” diyen Takalo, sürecin uzamasından endişe duyduğunu vurguladı. “Bir Anda Herkes Akrabam Oldu” Olayın duyulmasının ardından yoğun telefon trafiği yaşadığını aktaran Takalo, yeni bir hat almak zorunda kaldığını söyledi. Yaşananların ardından çevresinden para talepleri aldığını ifade eden girişimci, “Sanki o parayı kullanabiliyormuşum gibi davranıyorlar. Bir anda herkes akrabam oldu” sözleriyle dikkat çekti. İflas Uyarısı Tüm hesaplarının bloke edilmesi nedeniyle ciddi mağduriyet yaşadığını belirten Takalo, sürecin bir ya da iki ay daha uzaması halinde şirketlerinin iflas riskiyle karşı karşıya kalabileceğini söyledi. İki Ar-Ge şirketinin faaliyetlerinin aksadığını ifade eden Takalo, olayın bir an önce netleşmesini ve gerçek para sahibinin bulunmasını beklediğini dile getirdi. Konuya ilişkin hukuki sürecin devam ettiği öğrenildi. Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu Kartı Çalışmadı, Gerçek Bankada Ortaya Çıktı “Hayatım 180 Derece Değişti” “Bir Anda Herkes Akrabam Oldu” Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu fark eden Takalo’nun tüm hesapları, kaynağı belirsiz para hareketi nedeniyle MASAK tarafından donduruldu. Yaşanan gelişme sonrası Takalo, hesaplarına erişemediği için işlerinin aksadığını ve şirketlerinin risk altına girdiğini açıkladı. Balıkesir’de yaşayan ve iş gezisi kapsamında Van’a giden Takalo, alışveriş sırasında kartlarının çalışmaması üzerine bankaya başvurdu. İlk etapta teknik bir sorun olduğunu düşünen girişimci, banka hesabında neredeyse 1 trilyon liraya yakın bir bakiye göründüğünü öğrenince şaşkınlık yaşadı. Yaklaşık 10 yıl önce Türkiye’ye yerleştiğini belirten Takalo’nun hesapları, söz konusu astronomik tutarın kaynağının belirsiz olması nedeniyle incelemeye alındı. MASAK tarafından yürütülen süreç kapsamında tüm banka hesaplarına bloke konuldu. Uluslararası mucit olduğunu ve Türkiye’de iki Ar-Ge şirketi bulunduğunu dile getiren Takalo, yaşadıklarını “hem komik hem de korkunç” sözleriyle anlattı. Daha önce annesinin hesabına da yanlışlıkla milyonlarca lira gönderildiğini, ancak o olayın kısa sürede çözüldüğünü belirten girişimci, bu kez karşı karşıya kaldığı tablonun çok daha karmaşık olduğunu ifade etti. “Hayatım 180 derece değişti. Normal düzenimi özledim. Hesaplarım kapalı olduğu için işlerim durma noktasına geldi” diyen Takalo, sürecin uzamasından endişe duyduğunu vurguladı. Olayın duyulmasının ardından yoğun telefon trafiği yaşadığını aktaran Takalo, yeni bir hat almak zorunda kaldığını söyledi. Yaşananların ardından çevresinden para talepleri aldığını ifade eden girişimci, “Sanki o parayı kullanabiliyormuşum gibi davranıyorlar. Bir anda herkes akrabam oldu” sözleriyle dikkat çekti. Tüm hesaplarının bloke edilmesi nedeniyle ciddi mağduriyet yaşadığını belirten Takalo, sürecin bir ya da iki ay daha uzaması halinde şirketlerinin iflas riskiyle karşı karşıya kalabileceğini söyledi. İki Ar-Ge şirketinin faaliyetlerinin aksadığını ifade eden Takalo, olayın bir an önce netleşmesini ve gerçek para sahibinin bulunmasını beklediğini dile getirdi. Konuya ilişkin hukuki sürecin devam ettiği öğrenildi.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor Kocaeli’de dev iflas satışı: 198 milyonluk mal varlığı ihaleye çıkıyor Mavi Marmara Gazetesi Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarıl... Kocaeli İcra Dairesi tarafından yürütülen iflas dosyası kapsamında toplam değeri 198 milyon lirayı aşan 628 kalem taşınır mal satışa çıkarılıyor.</t>
+          <t>Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu avazturk.com Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş bulunduğunu fark eden Takalo’nun tüm hesapları, kaynağı belirsiz para hareketi nedeniyle MASAK tarafından donduruldu. Yaşanan gelişme sonrası Takalo, hesaplarına erişemediği için işlerinin aksadığını ve şirketlerinin risk altına girdiğini açıkladı. Kartı Çalışmadı, Gerçek Bankada Ortaya Çıktı Balıkesir’de yaşayan ve iş gezisi kapsamında Van’a giden Takalo, alışveriş sırasında kartlarının çalışmaması üzerine bankaya başvurdu. İlk etapta teknik bir sorun olduğunu düşünen girişimci, banka hesabında neredeyse 1 trilyon liraya yakın bir bakiye göründüğünü öğrenince şaşkınlık yaşadı. Yaklaşık 10 yıl önce Türkiye’ye yerleştiğini belirten Takalo’nun hesapları, söz konusu astronomik tutarın kaynağının belirsiz olması nedeniyle incelemeye alındı. MASAK tarafından yürütülen süreç kapsamında tüm banka hesaplarına bloke konuldu. “Hayatım 180 Derece Değişti” Uluslararası mucit olduğunu ve Türkiye’de iki Ar-Ge şirketi bulunduğunu dile getiren Takalo, yaşadıklarını “hem komik hem de korkunç” sözleriyle anlattı. Daha önce annesinin hesabına da yanlışlıkla milyonlarca lira gönderildiğini, ancak o olayın kısa sürede çözüldüğünü belirten girişimci, bu kez karşı karşıya kaldığı tablonun çok daha karmaşık olduğunu ifade etti. Hesaplarım kapalı olduğu için işlerim durma noktasına geldi” diyen Takalo, sürecin uzamasından endişe duyduğunu vurguladı. “Bir Anda Herkes Akrabam Oldu” Olayın duyulmasının ardından yoğun telefon trafiği yaşadığını aktaran Takalo, yeni bir hat almak zorunda kaldığını söyledi. Yaşananların ardından çevresinden para talepleri aldığını ifade eden girişimci, “Sanki o parayı kullanabiliyormuşum gibi davranıyorlar. İflas Uyarısı Tüm hesaplarının bloke edilmesi nedeniyle ciddi mağduriyet yaşadığını belirten Takalo, sürecin bir ya da iki ay daha uzaması halinde şirketlerinin iflas riskiyle karşı karşıya kalabileceğini söyledi. İki Ar-Ge şirketinin faaliyetlerinin aksadığını ifade eden Takalo, olayın bir an önce netleşmesini ve gerçek para sahibinin bulunmasını beklediğini dile getirdi. Yaşam Bozcaada, National Geographic’in 2026 “Dünyanın En İyi 15 Yemek Destinasyonu” Listesinde Hatay’da Korku Dolu Gece! Oytun Erbaş’tan Hantavirüs Uyarısı: “Kovidin Öldürücülüğüyle Hantavirüs Kıyaslanamaz Bile” Malatya’da Okullar Tatil mi? 5.6’lık Deprem Sonrası Son Durum Meteoroloji’den 81 İle Sağanak Uyarısı: 5 İlde Sarı Kodlu Sel Alarmı Meteoroloji'den Sarı Kodlu Uyarı: Yaz Gelmeden Soğuk Hava ve Kuvvetli Sağanak Kapıda TÜVTÜRK’te “5 Milyon Dolar” Şakası! Rus Kadın Ters Köşe Oldu Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Banka Hesabında 1 Trilyona Yakın Para Göründü, Hayatı Altüst Oldu Kartı Çalışmadı, Gerçek Bankada Ortaya Çıktı “Hayatım 180 Derece Değişti” “Bir Anda Herkes Akrabam Oldu” Van’a iş için giden Azerbaycan asıllı girişimci Ahmad Jahangard Takalo, banka hesabında gördüğü rakamla adeta hayatının şokunu yaşadı. Balıkesir’de yaşayan ve iş gezisi kapsamında Van’a giden Takalo, alışveriş sırasında kartlarının çalışmaması üzerine bankaya başvurdu. Uluslararası mucit olduğunu ve Türkiye’de iki Ar-Ge şirketi bulunduğunu dile getiren Takalo, yaşadıklarını “hem komik hem de korkunç” sözleriyle anlattı. Olayın duyulmasının ardından yoğun telefon trafiği yaşadığını aktaran Takalo, yeni bir hat almak zorunda kaldığını söyledi. Tüm hesaplarının bloke edilmesi nedeniyle ciddi mağduriyet yaşadığını belirten Takalo, sürecin bir ya da iki ay daha uzaması halinde şirketlerinin iflas riskiyle karşı karşıya kalabileceğini söyledi.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -4632,12 +5126,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.mavimarmaragazetesi.com/haber/28105561/kocaelide-dev-iflas-satisi-198-milyonluk-mal-varligi-ihaleye-cikiyor</t>
+          <t>https://www.avazturk.com/banka-hesabinda-1-trilyona-yakin-para-gorundu-hayati-altust-oldu-93590h.htm</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli</t>
+          <t>Balıkesir | Hatay | Malatya</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
@@ -4662,7 +5156,7 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="n">
-        <v>78.33</v>
+        <v>75</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>21</v>
@@ -4671,27 +5165,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:47:15</t>
+          <t>2026-06-05 07:12:00</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>yasa dışı bahis</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon!</t>
+          <t>Kapaklı OSB’de korkutan baca yangını ucuz atlatıldı</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! GDH.Digital</t>
+          <t>Kapaklı OSB’de korkutan baca yangını ucuz atlatıldı Trakya Gazetesi</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -4701,44 +5195,56 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>osb</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! GDH.Digital</t>
+          <t>Tekirdağ’ın Kapaklı ilçesinde yürekleri ağza getiren bir fabrika yangını meydana geldi. Organize Sanayi Bölgesi (OSB) Atatürk Caddesi üzerinde faaliyet gösteren bir tekstil fabrikasının baca kısmında aniden alevler yükseldi. Çalışanların zamanında fark ettiği yangın, itfaiyenin hızlı müdahalesi sayesinde üretim alanına sıçramadan söndürüldü. Tekirdağ’ın Kapaklı ilçesinde yürekleri ağza getiren bir fabrika yangını meydana geldi. Organize Sanayi Bölgesi (OSB) Atatürk Caddesi üzerinde faaliyet gösteren... Tekirdağ’ın Kapaklı ilçesinde yürekleri ağza getiren bir fabrika yangını meydana geldi. Organize Sanayi Bölgesi (OSB) Atatürk Caddesi üzerinde faaliyet gösteren bir tekstil fabrikasının baca kısmında aniden alevler yükseldi. Çalışanların zamanında fark ettiği yangın, itfaiyenin hızlı müdahalesi sayesinde üretim alanına sıçramadan söndürüldü. Tekirdağ’ın Kapaklı ilçesinde bir tekstil fabrikasının bacasında yangın meydana geldi. Yangın itfaiye ekiplerince söndürülerek kontrol altına alındı. Henüz belirlenemeyen bir sebeple fabrikanın bacasında başlayan yangın, kısa süreli bir paniğe neden oldu. Yoğun dumanı ve alevleri fark eden fabrika personelinin durumu bildirmesi üzerine, olay yerine çok sayıda itfaiye ve polis ekibi sevk edildi. Kısa sürede OSB'ye ulaşan itfaiye ekipleri, yangının fabrikanın diğer bölümlerine yayılmaması için adeta zamanla yarıştı. Ekiplerin koordineli ve profesyonel müdahalesiyle alevler kontrol altına alınarak söndürüldü. Herhangi bir can kaybı ya da yaralanmanın yaşanmadığı olayda, sadece maddi hasar meydana geldi. Yangının tamamen söndürülmesinin ardından fabrikada soğutma çalışmaları yapıldı. Polis ekipleri, tekstil fabrikasının bacasında çıkan yangının kesin nedenini belirleyebilmek amacıyla olay yerinde inceleme başlattı. Konuyla ilgili başlatılan tahkikat devam ediyor. Kapaklı OSB’de korkutan baca yangını ucuz atlatıldı Tekirdağ’ın Kapaklı ilçesinde yürekleri ağza getiren bir fabrika yangını meydana geldi. Organize Sanayi Bölgesi (OSB) Atatürk Caddesi üzerinde faaliyet gösteren bir tekstil fabrikasının baca kısmında aniden alevler yükseldi. Çalışanların zamanında fark ettiği yangın, itfaiyenin hızlı müdahalesi sayesinde üretim alanına sıçramadan söndürüldü. Tekirdağ’ın Kapaklı ilçesinde bir tekstil fabrikasının bacasında yangın meydana geldi. Yangın itfaiye ekiplerince söndürülerek kontrol altına alındı. Henüz belirlenemeyen bir sebeple fabrikanın bacasında başlayan yangın, kısa süreli bir paniğe neden oldu. Yoğun dumanı ve alevleri fark eden fabrika personelinin durumu bildirmesi üzerine, olay yerine çok sayıda itfaiye ve polis ekibi sevk edildi. Kısa sürede OSB'ye ulaşan itfaiye ekipleri, yangının fabrikanın diğer bölümlerine yayılmaması için adeta zamanla yarıştı. Ekiplerin koordineli ve profesyonel müdahalesiyle alevler kontrol altına alınarak söndürüldü. Herhangi bir can kaybı ya da yaralanmanın yaşanmadığı olayda, sadece maddi hasar meydana geldi. Yangının tamamen söndürülmesinin ardından fabrikada soğutma çalışmaları yapıldı. Polis ekipleri, tekstil fabrikasının bacasında çıkan yangının kesin nedenini belirleyebilmek amacıyla olay yerinde inceleme başlattı. Konuyla ilgili başlatılan tahkikat devam ediyor. 05 Haz 2026 - 10:12 Tekirdağ / Kapakli - 3. Sayfa Yazdır Yorum yazarak Trakya Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon! GDH.Digital Ünlü bankacıların ismiyle sahte yatırım tuzağı kuran o şebekeye 70 milyarlık dev operasyon!</t>
+          <t>Kapaklı OSB’de korkutan baca yangını ucuz atlatıldı Kapaklı OSB’de korkutan baca yangını ucuz atlatıldı Trakya Gazetesi Tekirdağ’ın Kapaklı ilçesinde yürekleri ağza getiren bir fabrika yangını meydana geldi. Organize Sanayi Bölgesi (OSB) Atatürk Caddesi üzerinde faaliyet gösteren bir tekstil fabrikasının baca kısmında aniden alevler yükseldi. Çalışanların zamanında fark ettiği yangın, itfaiyenin hızlı müdahalesi sayesinde üretim alanına sıçramadan söndürüldü. Organize Sanayi Bölgesi (OSB) Atatürk Caddesi üzerinde faaliyet gösteren... Tekirdağ’ın Kapaklı ilçesinde bir tekstil fabrikasının bacasında yangın meydana geldi. Yangın itfaiye ekiplerince söndürülerek kontrol altına alındı. Henüz belirlenemeyen bir sebeple fabrikanın bacasında başlayan yangın, kısa süreli bir paniğe neden oldu. Yoğun dumanı ve alevleri fark eden fabrika personelinin durumu bildirmesi üzerine, olay yerine çok sayıda itfaiye ve polis ekibi sevk edildi. Kısa sürede OSB'ye ulaşan itfaiye ekipleri, yangının fabrikanın diğer bölümlerine yayılmaması için adeta zamanla yarıştı. Herhangi bir can kaybı ya da yaralanmanın yaşanmadığı olayda, sadece maddi hasar meydana geldi. Yangının tamamen söndürülmesinin ardından fabrikada soğutma çalışmaları yapıldı. Polis ekipleri, tekstil fabrikasının bacasında çıkan yangının kesin nedenini belirleyebilmek amacıyla olay yerinde inceleme başlattı. Konuyla ilgili başlatılan tahkikat devam ediyor. Kapaklı OSB’de korkutan baca yangını ucuz atlatıldı Tekirdağ’ın Kapaklı ilçesinde yürekleri ağza getiren bir fabrika yangını meydana geldi. 05 Haz 2026 - 10:12 Tekirdağ / Kapakli - 3. Sayfa Yazdır Yorum yazarak Trakya Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUnpMclpncDllUXJ2V0pzdUhJaTNhZDhPSVFRZlJLTldlVjQyLWNPT1FTTDNVOE9iNEh6Y3NSb3I0VzR6dE5FY210eU9rb2tKZ0RYRTF6dk5jN2ZTc2tXak4wMG1ZZnVtRUh0WS00UE9CWXdUdFZhY3VtY1lqc2R0VkROeVhCd2E0U0d0LW9mRmxaS0tlcXFkOGUwTFBtV3ZDM1A2NzA5cUFNR0FZclliOEFKd2lZTGVpcFU2QWxCb0twRXphemc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
+          <t>https://www.trakyagazetesi.com.tr/haber/28115559/kapakli-osbde-korkutan-baca-yangini-ucuz-atlatildi</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Tekirdağ</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Kapaklı</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Kapaklı OSB | yangını ucuz atlatıldı Kapaklı OSB | Kısa sürede OSB</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Atatürk Caddesi</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr"/>
@@ -4752,7 +5258,7 @@
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="n">
-        <v>78.28</v>
+        <v>127.25</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>22</v>
@@ -4761,27 +5267,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:49:41</t>
+          <t>2026-06-04 13:57:00</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor!</t>
+          <t>Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! EmlakDream</t>
+          <t>Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi Milliyet</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -4791,32 +5297,44 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>inşaat</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! EmlakDream</t>
+          <t>Esenyurt’ta bulunan bir fabrikada bilinmeyen bir nedenle yangın çıktı. Olay yerine itfaiye ekipleri sevk edildi. Esenyurt’ta bulunan bir fabrikada bilinmeyen bir nedenle yangın çıktı. Olay yerine itfaiye ekipleri sevk edildi. Esenyurt’ta bulunan bir fabrikada bilinmeyen bi... 01:23 Cumhurbaşkanı Erdoğan, Nijer Cumhurbaşkanı Tchiani'yi resmi törenle karşıladı 02:34 Kılıçdaroğlu'ndan grup toplantısı açıklaması: Umarım yapacağım 01:04 Daha 17’nin karavan güzeli! Leyla rüzgârı esiyor 02:03 Eşref ve Nisan’ın büyük savaşı başladı! Büyük finale doğru heyecan dorukta 01:27 Can Polat cinayetinin ardından acı veda! Kızlarından yürek yakan feryat: Babamı bizden aldınız 01:12 Atatürk Havalimanı'nda büyük buluşma! Sıfır Atık Festivali başladı: 4 gün boyunca ünlü sanatçılar sahnede 02:04 Fenerbahçe Başkanı Sadettin Saran'a 2 yıl 6 ay hapis 00:33 İş yerine saldırının arkasından alacak kavgası çıktı! 4 kişi adliyede 00:53 3 işçinin can verdiği fabrika faciasında detaylar belli oldu 00:20 Nefes kesen av... Pençeleriyle kavrayarak havalandı! 01:26 Anayasa Mahkemesi süresiz nafaka düzenlemesini iptal etti! 04:29 TOKİ'den 64 ilde yeni konut kampanyası! Bakan Kurum şartları ve fiyatı açıkladı 00:52 İhbar ABD'den geldi, operasyon Sarıyer'de başladı! Canlı konum takibiyle kurtarıldı 03:20 Muhittin Böcek'ten 950 bin euro itirafı! Özgür Özel'in talebiyle Ferdi Zeyrek'e teslim ettim 01:13 Sıfır kilometre araç aldılar, sadece 6 ay kullanabildiler: Binmeye korkuyoruz 01:29 İstanbul’da ürküten manzara! Mavi ile kahverenginin sınırı havadan görüntülendi 01:54 Kavurucu yaz kapıda! 50 dereceyi görebiliriz 01:51 Dili boğazına kaçan kız kardeşini kurtardı, kendisi dakikalar sonra öldü! Randevuya saatler kala... 00:44 Galata Kulesi'nde 'Sıfır Atık' heyecanı! 01:36 A Milli Futbol Takımı, Miami'deki ilk antrenmanını yaptı 00:31 Tüfekle açılan ateş sonucu oluşan kimyasal sızıntıdan 6 polis etkilendi 05:11 Yüksek gerilim hattından akıma kapılıp, kuyuya düşen 3 işçi öldü 00:17 Elazığ’da ilginç anlar kameraya yansıdı! Kargadan kaçarken taklalar attı 01:01 Manisa’da pompalı tüfekli saldırıda 2 kişi yaralandı 04:59 Fenerbahçe'de Aziz Yıldırım'dan Hakan Safi'ye tepki! 'Oyuncular adaylarla anlaşmaz' 00:17 Dilan Polat'ın koruması Can Polat'a kanlı pusu! Saldırının görüntüleri ortaya çıktı 00:25 Milli Takım'dan antrenman öncesi Miami turu! 02:54 ABD Başkanı Trump, Türkiye'deki NATO Zirvesi'ne katılacak 00:37 Başakşehir'de iş yerine silahlı saldırı düzenleyen şüpheliler suçüstü yakalandı 01:05 Bursa'da kan donduran cinayet! 10 yaşındaki oğlunun gözü önünde eşini katletti Sitene Ekle Aşağıdaki kodu kopyalayıp sitenize ekleyebilirsiniz &lt;iframe src="https://www.milliyet.com.tr/video/embed/?vid=7599564&amp;resizable=1&amp;autostart=true" width="584px" height="326px" frameborder="0" scrolling="0" allow="autoplay; fullscreen" allowfullscreen&gt;&lt;/iframe&gt; Video Otomatik Olarak Başlasın Otomatik Boyut Genişlik: Yükseklik: X Haberler Video Haberler Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi Esenyurt 'ta bir fabrikada henüz bilinmeyen nedenle yangın çıktı.İhbar üzerine olay yerine itfaiye, sağlık ve polis ekipleri sevk edildi. Ekiplerin alevlere müdahalesi sürüyor.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor! EmlakDream Borsada konkordato paniği.. En riskli sektörlerin başında inşaat geliyor!</t>
+          <t>Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi Milliyet Esenyurt’ta bulunan bir fabrikada bilinmeyen bir nedenle yangın çıktı. Olay yerine itfaiye ekipleri sevk edildi. Esenyurt’ta bulunan bir fabrikada bilinmeyen bi... 01:23 Cumhurbaşkanı Erdoğan, Nijer Cumhurbaşkanı Tchiani'yi resmi törenle karşıladı 02:34 Kılıçdaroğlu'ndan grup toplantısı açıklaması: Umarım yapacağım 01:04 Daha 17’nin karavan güzeli! Leyla rüzgârı esiyor 02:03 Eşref ve Nisan’ın büyük savaşı başladı! Büyük finale doğru heyecan dorukta 01:27 Can Polat cinayetinin ardından acı veda! Kızlarından yürek yakan feryat: Babamı bizden aldınız 01:12 Atatürk Havalimanı'nda büyük buluşma! Sıfır Atık Festivali başladı: 4 gün boyunca ünlü sanatçılar sahnede 02:04 Fenerbahçe Başkanı Sadettin Saran'a 2 yıl 6 ay hapis 00:33 İş yerine saldırının arkasından alacak kavgası çıktı! 4 kişi adliyede 00:53 3 işçinin can verdiği fabrika faciasında detaylar belli oldu 00:20 Nefes kesen av... Pençeleriyle kavrayarak havalandı! 01:26 Anayasa Mahkemesi süresiz nafaka düzenlemesini iptal etti! 04:29 TOKİ'den 64 ilde yeni konut kampanyası! Bakan Kurum şartları ve fiyatı açıkladı 00:52 İhbar ABD'den geldi, operasyon Sarıyer'de başladı! Özgür Özel'in talebiyle Ferdi Zeyrek'e teslim ettim 01:13 Sıfır kilometre araç aldılar, sadece 6 ay kullanabildiler: Binmeye korkuyoruz 01:29 İstanbul’da ürküten manzara! Randevuya saatler kala... 01:36 A Milli Futbol Takımı, Miami'deki ilk antrenmanını yaptı 00:31 Tüfekle açılan ateş sonucu oluşan kimyasal sızıntıdan 6 polis etkilendi 05:11 Yüksek gerilim hattından akıma kapılıp, kuyuya düşen 3 işçi öldü 00:17 Elazığ’da ilginç anlar kameraya yansıdı! Kargadan kaçarken taklalar attı 01:01 Manisa’da pompalı tüfekli saldırıda 2 kişi yaralandı 04:59 Fenerbahçe'de Aziz Yıldırım'dan Hakan Safi'ye tepki! 'Oyuncular adaylarla anlaşmaz' 00:17 Dilan Polat'ın koruması Can Polat'a kanlı pusu! 02:54 ABD Başkanı Trump, Türkiye'deki NATO Zirvesi'ne katılacak 00:37 Başakşehir'de iş yerine silahlı saldırı düzenleyen şüpheliler suçüstü yakalandı 01:05 Bursa'da kan donduran cinayet! 10 yaşındaki oğlunun gözü önünde eşini katletti Sitene Ekle Aşağıdaki kodu kopyalayıp sitenize ekleyebilirsiniz &lt;iframe src="https://www.milliyet.com.tr/video/embed/?vid=7599564&amp;resizable=1&amp;autostart=true" width="584px" height="326px" frameborder="0" scrolling="0" allow="autoplay; fullscreen" allowfullscreen&gt;&lt;/iframe&gt; Video Otomatik Olarak Başlasın Otomatik Boyut Genişlik: Yükseklik: X Haberler Video Haberler Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi Esenyurt’ta fabrika yangını! Çok sayıda ekip sevk edildi Esenyurt 'ta bir fabrikada henüz bilinmeyen nedenle yangın çıktı.İhbar üzerine olay yerine itfaiye, sağlık ve polis ekipleri sevk edildi.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOWXd2TXoyZ19TaDRzR1hCbEpPbDM5OHJNUUpyWkxjVzRkckxjMWdfR1BGekJnWVpYZW1PbHVYejN1UHc1aVNsWUlLTHNrREN6NG1wNVctYmtJR2dXN3NvMmRZUkdzY1pZOEJDQ2Y4Q1JSVlhRbkk3QmNsUDhzZEplWUM4cE5rS0cxN0g5REFxS05BWDhwVERDM3pyN1NFcU0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>https://www.milliyet.com.tr/milliyet-tv/esenyurtta-fabrika-yangini-cok-sayida-ekip-sevk-edildi-video-7599564</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Elazığ | İstanbul | Manisa</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Yıldırım | Başakşehir | Esenyurt | Sarıyer</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -4824,7 +5342,7 @@
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr"/>
@@ -4838,7 +5356,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="n">
-        <v>74.34</v>
+        <v>95.25</v>
       </c>
       <c r="AB24" s="2" t="n">
         <v>23</v>
@@ -4847,27 +5365,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 17:54:22</t>
+          <t>2026-06-05 00:00:00</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı</t>
+          <t>Fabrika Yangını: Fırın Bölümü Alev Aldı</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT</t>
+          <t>Fabrika Yangını: Fırın Bölümü Alev Aldı Kırşehir Çiğdem</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -4877,18 +5395,22 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>gıda</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT</t>
+          <t>Fabrika Yangını: Fırın Bölümü Alev Aldı Kırşehir Çiğdem</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT Baktat Zeytincilik konkordato ilan etti: Mahkemeden köklü gıda markasına 3 aylık koruma kararı | Ekonomi Haberleri GZT</t>
+          <t>Fabrika Yangını: Fırın Bölümü Alev Aldı Fabrika Yangını: Fırın Bölümü Alev Aldı Kırşehir Çiğdem Fabrika Yangını: Fırın Bölümü Alev Aldı Kırşehir Çiğdem</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -4898,7 +5420,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOR1VCUHAySXZLbVJKcXIwYUMtcHVHd2RBTnF4dXpETDFSbDAzUU1sNDNPS3JmUFRhWElFZ2pReXJONV9YYm9SSk9GeG90akR3d1NPT2RhcDZ1eTQ2MmVuNHp3M0I3NVg1cC1nN1phUi1CNmVBUzFaYnRQd2Y1VFBFcTFYZ3Y3dDdWX1dTdFFaN2FfcWF1amZpOTVmLTNqWnJJb0pTQjYyMmRaNUdydGphQW5qclEwajJ2c1U4VkRnYUJTTTJlaFFjVTJCSzJybUVwd21hc2ZJdzEyOGdRZnF4ag?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBVeHJjaFBnY2pseG04b3VfbW1DOGJBejVUSVZJNEFCeGI1b2t6WTAweXM1Rl85eFd6ZmN1YnNaQ2ZKX1JpVHlJVzcxbzFlV182UktmZlpMbzNnclhONXBnR1ZoOFM0eWVtay1IM1Q0SmpyOWZ5c3FQcdIBfkFVX3lxTE5OOHoxd1VIXzc2X3VOOV9fb0ZiTy1CaVdQMmctRUVXRUNDRmlNTDdtSzBOWk5iMWc2Ny04cWt4TG5lUGxRQWRhdzVHT3EwbURGeU5ZYjk3S3dLZGF0TUNVX0hvUzdkZmp3N2JFQ29WR0lkb1VoY3JaNWh5dTAxUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
@@ -4924,7 +5446,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="n">
-        <v>83.68000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>24</v>
@@ -4933,27 +5455,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 04:11:41</t>
+          <t>2026-06-04 18:07:33</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi</t>
+          <t>Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası</t>
+          <t>Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4963,36 +5485,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası</t>
+          <t>Aydın'ın Nazilli ilçesindeki bir fabrikada akşam çıkan yangın, Aydın Büyükşehir Belediyesi İtfaiye ekiplerinin müdahalesiyle söndürüldü; inceleme sürüyor. Aydın'ın Nazilli ilçesindeki bir fabrikada akşam çıkan yangın, Aydın Büyükşehir Belediyesi İtfaiye ekiplerinin müdahalesiyle söndürüldü; inceleme sürüyor. Aydın'ın Nazilli ilçesindeki bir fabrikada akşam çıkan yangın, Aydın Büyükşehir Belediyesi İtfaiye ekiplerinin müdahalesiyle söndürüldü; inceleme sürüyor. Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu Olayın ayrıntıları Aydın'ın Nazilli ilçesinde, Nazilli Bozdoğan karayolu üzerindeki bir fabrikada akşam saatlerinde yangın çıktı. Yangının çıkış nedeni henüz belirlenemedi. Bölgeye sevk edilen Aydın Büyükşehir Belediyesi İtfaiye ekipleri olay yerine ulaşarak müdahale etti ve alevleri söndürdü. Müdahale sonucu can kaybı veya yaralanma yaşanmadı. Yangında fabrikanın bazı bölümlerinde maddi hasar meydana geldi. Olayla ilgili teknik inceleme ve soruşturma devam ediyor; yetkililer yangının nedeni ve hasarın boyutuna ilişkin değerlendirmeler yapıyor. Değerlendirme Erken müdahale sayesinde yangının çevre işletmelere daha fazla yayılmasının önlendiği bildirildi. Soruşturma sonuçları netleşene kadar fabrikada hasar tespit çalışmaları ve güvenlik önlemleri öncelikli olacak. FABRİKADA ÇIKAN YANGIN SÖNDÜRÜLDÜ 1 Konya'da ayrılık aşamasındaki kadın eşi tarafından bıçaklandı, ağır yaralı Konya'da ayrılık aşamasındaki kadın eşi tarafından bıçaklandı, ağır yaralı 2 Adıyaman Kuyulu Köyü yakınlarında silahlı saldırı: 1 kişi hayatını kaybetti Adıyaman Kuyulu Köyü yakınlarında silahlı saldırı: 1 kişi hayatını kaybetti 3 Konya'da ayrılık aşamasındaki eşi tarafından bıçaklanan kadın ağır yaralandı Konya'da ayrılık aşamasındaki eşi tarafından bıçaklanan kadın ağır yaralandı 4 Küçükçekmece'de otomobil motosiklete çarpmamak için manevra yaptı, karşı şeride geçip İETT otobüsüne çarptı: 1 yaralı Küçükçekmece'de otomobil motosiklete çarpmamak için manevra yaptı, karşı şeride geçip İETT otobüsüne çarptı: 1 yaralı 5 Çorum Alaca'da sağanak tarım arazilerini su altında bıraktı; belediye yolu açtı Çorum Alaca'da sağanak tarım arazilerini su altında bıraktı; belediye yolu açtı 6 Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu 7 Kırıkkale'de jandarma, kesinleşmiş hapis cezası bulunan 2 hükümlüyü yakalayıp cezaevine teslim etti Kırıkkale'de jandarma, kesinleşmiş hapis cezası bulunan 2 hükümlüyü yakalayıp cezaevine teslim etti Aydın'ın Nazilli ilçesindeki bir fabrikada akşam çıkan yangın, Aydın Büyükşehir Belediyesi İtfaiye ekiplerinin müdahalesiyle söndürüldü; inceleme sürüyor. Aydın'ın Nazilli ilçesinde, Nazilli Bozdoğan karayolu üzerindeki bir fabrikada akşam saatlerinde yangın çıktı. Yangının çıkış nedeni henüz belirlenemedi. Bölgeye sevk edilen Aydın Büyükşehir Belediyesi İtfaiye ekipleri olay yerine ulaşarak müdahale etti ve alevleri söndürdü. Müdahale sonucu can kaybı veya yaralanma yaşanmadı. Yangında fabrikanın bazı bölümlerinde maddi hasar meydana geldi. Olayla ilgili teknik inceleme ve soruşturma devam ediyor; yetkililer yangının nedeni ve hasarın boyutuna ilişkin değerlendirmeler yapıyor. Erken müdahale sayesinde yangının çevre işletmelere daha fazla yayılmasının önlendiği bildirildi. Soruşturma sonuçları netleşene kadar fabrikada hasar tespit çalışmaları ve güvenlik önlemleri öncelikli olacak. FABRİKADA ÇIKAN YANGIN SÖNDÜRÜLDÜ Ben Hüseyin Aydın, 34 yaşındayım, İstanbul'dayım. aksiyon.com.tr'nin Gündem ekibinde adliye ve hukuk muhabiriyim. Karmaşık dava dosyalarını alıp, herkesin anlayacağı şekilde sadeleştirmek benim işim. Detaylara çok önem veririm, titiz çalışırım. 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası Türk İlaç Serum şirketi aldığı konkordato kararı öncesinde hissede ralli, patron ve fonlardan satış gerçekleştirdi Patronlar Dünyası</t>
+          <t>Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu Aksiyon.com.TR Aydın'ın Nazilli ilçesindeki bir fabrikada akşam çıkan yangın, Aydın Büyükşehir Belediyesi İtfaiye ekiplerinin müdahalesiyle söndürüldü; inceleme sürüyor. Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu Olayın ayrıntıları Aydın'ın Nazilli ilçesinde, Nazilli Bozdoğan karayolu üzerindeki bir fabrikada akşam saatlerinde yangın çıktı. Yangının çıkış nedeni henüz belirlenemedi. Bölgeye sevk edilen Aydın Büyükşehir Belediyesi İtfaiye ekipleri olay yerine ulaşarak müdahale etti ve alevleri söndürdü. Müdahale sonucu can kaybı veya yaralanma yaşanmadı. Yangında fabrikanın bazı bölümlerinde maddi hasar meydana geldi. Olayla ilgili teknik inceleme ve soruşturma devam ediyor; yetkililer yangının nedeni ve hasarın boyutuna ilişkin değerlendirmeler yapıyor. Değerlendirme Erken müdahale sayesinde yangının çevre işletmelere daha fazla yayılmasının önlendiği bildirildi. Soruşturma sonuçları netleşene kadar fabrikada hasar tespit çalışmaları ve güvenlik önlemleri öncelikli olacak. FABRİKADA ÇIKAN YANGIN SÖNDÜRÜLDÜ 1 Konya'da ayrılık aşamasındaki kadın eşi tarafından bıçaklandı, ağır yaralı Konya'da ayrılık aşamasındaki kadın eşi tarafından bıçaklandı, ağır yaralı 2 Adıyaman Kuyulu Köyü yakınlarında silahlı saldırı: 1 kişi hayatını kaybetti Adıyaman Kuyulu Köyü yakınlarında silahlı saldırı: 1 kişi hayatını kaybetti 3 Konya'da ayrılık aşamasındaki eşi tarafından bıçaklanan kadın ağır yaralandı Konya'da ayrılık aşamasındaki eşi tarafından bıçaklanan kadın ağır yaralandı 4 Küçükçekmece'de otomobil motosiklete çarpmamak için manevra yaptı, karşı şeride geçip İETT otobüsüne çarptı: 1 yaralı Küçükçekmece'de otomobil motosiklete çarpmamak için manevra yaptı, karşı şeride geçip İETT otobüsüne çarptı: 1 yaralı 5 Çorum Alaca'da sağanak tarım arazilerini su altında bıraktı; belediye yolu açtı Çorum Alaca'da sağanak tarım arazilerini su altında bıraktı; belediye yolu açtı 6 Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu Nazilli'de Fabrika Yangını Söndürüldü: Can Kaybı Yok, Maddi Hasar Oluştu 7 Kırıkkale'de jandarma, kesinleşmiş hapis cezası bulunan 2 hükümlüyü yakalayıp cezaevine teslim etti Kırıkkale'de jandarma, kesinleşmiş hapis cezası bulunan 2 hükümlüyü yakalayıp cezaevine teslim etti Aydın'ın Nazilli ilçesindeki bir fabrikada akşam çıkan yangın, Aydın Büyükşehir Belediyesi İtfaiye ekiplerinin müdahalesiyle söndürüldü; inceleme sürüyor. Aydın'ın Nazilli ilçesinde, Nazilli Bozdoğan karayolu üzerindeki bir fabrikada akşam saatlerinde yangın çıktı. Erken müdahale sayesinde yangının çevre işletmelere daha fazla yayılmasının önlendiği bildirildi. FABRİKADA ÇIKAN YANGIN SÖNDÜRÜLDÜ Ben Hüseyin Aydın, 34 yaşındayım, İstanbul'dayım. Karmaşık dava dosyalarını alıp, herkesin anlayacağı şekilde sadeleştirmek benim işim. 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNTnp3SmRXLU1DOWl6azAyLTdmaUNWcjFPRkxrM2dwQlFGM0R1cVU1aTctcGNIc0FSZjQtQkgtck5KQXhPNlIxXzFLQW1YcTZ5RlcyOU9rWEI0bU4yVXpLbmh3S3pfSVlHdXd3YmxQalNIWE1JYTRxTks2V0tJZEY5QVRIYTZpY0hxbnNHMk01VEdNaXZWV1p0YWxrNHZqbTRUQjM4eDRfX0RQVVhpREJRQVlOeTl5UG9JS3NiLVZqNkhxX1MzUEhvNXhINzNUNVdDMW5QVHI4SlJWdTU3U01B?oc=5</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>https://www.aksiyon.com.tr/nazilli-de-fabrika-yangini-sonduruldu-can-kaybi-yok-maddi-hasar-olustu-288217</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Aydın | Düzce | İstanbul | Kırıkkale | Konya</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Bozdoğan | Nazilli | Alaca | Küçükçekmece</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -5000,7 +5530,7 @@
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr"/>
@@ -5014,7 +5544,7 @@
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>116.75</v>
       </c>
       <c r="AB26" s="2" t="n">
         <v>25</v>
@@ -5023,27 +5553,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:08:15</t>
+          <t>2026-06-05 07:10:41</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>İzmirli üç medikal şirkete konkordato uzatması</t>
+          <t>Nazilli'de Geri Dönüşüm Fabrikasında Yangın</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi</t>
+          <t>Nazilli'de Geri Dönüşüm Fabrikasında Yangın SonDakika</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -5053,44 +5583,56 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi</t>
+          <t>Aydın'ın Nazilli ilçesindeki geri dönüşüm fabrikasında çıkan yangın hasara neden oldu. Aydın'ın Nazilli ilçesindeki geri dönüşüm fabrikasında çıkan yangın hasara neden oldu. Aydın'ın Nazilli ilçesindeki geri dönüşüm fabrikasında çıkan yangın hasara neden oldu. Nazilli'de Geri Dönüşüm Fabrikasında Yangın Son Güncelleme: 05.06.2026 10:10 Aydın'ın Nazilli ilçesindeki geri dönüşüm fabrikasında çıkan yangın hasara neden oldu. Aydın 'ın Nazilli ilçesinde bir geri dönüşüm fabrikasında çıkan yangın hasara yol açtı. Sümer Mahallesi'nde faaliyet gösteren geri dönüşüm fabrikasından alevlerin yükseldiğini gören çalışanlar, durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine itfaiye ve jandarma ekipleri sevk edildi. İtfaiye ekiplerinin müdahalesiyle alevler kısa sürede söndürüldü. Kaynak: AA Aydın 'ın Nazilli ilçesinde bir geri dönüşüm fabrikasında çıkan yangın hasara yol açtı. Sümer Mahallesi'nde faaliyet gösteren geri dönüşüm fabrikasından alevlerin yükseldiğini gören çalışanlar, durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine itfaiye ve jandarma ekipleri sevk edildi. İtfaiye ekiplerinin müdahalesiyle alevler kısa sürede söndürüldü. Nazilli'de Geri Dönüşüm Fabrikasında Yangın Aydın'ın Nazilli ilçesindeki geri dönüşüm fabrikasında çıkan yangın hasara neden oldu. Aydın 'ın Nazilli ilçesinde bir geri dönüşüm fabrikasında çıkan yangın hasara yol açtı. Sümer Mahallesi'nde faaliyet gösteren geri dönüşüm fabrikasından alevlerin yükseldiğini gören çalışanlar, durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine itfaiye ve jandarma ekipleri sevk edildi. İtfaiye ekiplerinin müdahalesiyle alevler kısa sürede söndürüldü.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>İzmirli üç medikal şirkete konkordato uzatması İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi İzmirli üç medikal şirkete konkordato uzatması İlkses Gazetesi</t>
+          <t>Nazilli'de Geri Dönüşüm Fabrikasında Yangın Nazilli'de Geri Dönüşüm Fabrikasında Yangın SonDakika Aydın'ın Nazilli ilçesindeki geri dönüşüm fabrikasında çıkan yangın hasara neden oldu. Nazilli'de Geri Dönüşüm Fabrikasında Yangın Son Güncelleme: 05.06.2026 10:10 Aydın'ın Nazilli ilçesindeki geri dönüşüm fabrikasında çıkan yangın hasara neden oldu. Aydın 'ın Nazilli ilçesinde bir geri dönüşüm fabrikasında çıkan yangın hasara yol açtı. Sümer Mahallesi'nde faaliyet gösteren geri dönüşüm fabrikasından alevlerin yükseldiğini gören çalışanlar, durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine itfaiye ve jandarma ekipleri sevk edildi. İtfaiye ekiplerinin müdahalesiyle alevler kısa sürede söndürüldü. Kaynak: AA Aydın 'ın Nazilli ilçesinde bir geri dönüşüm fabrikasında çıkan yangın hasara yol açtı. Nazilli'de Geri Dönüşüm Fabrikasında Yangın Aydın'ın Nazilli ilçesindeki geri dönüşüm fabrikasında çıkan yangın hasara neden oldu.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbDZieWNoN3hwV1RSbTdBQzBrNW9ZSExSWjNzYklrTDFYMm9rTHV3RDhCckk0aHdqREU0YnNPaFJkb0tfdVpkOUdReDc1ZGNvUzRpLXB3U3dnMzhfQlFnQXlNUTB4a3JONnlsTm9mcTJnN3h5TUNNdnphSjJOSy01cEJ5VzFHV2NY0gGOAUFVX3lxTE53LUZVNGdfZW9VMy0zSXhhYm9yS1U3SGswYlNIWFppdlJfUV9YZlU0VjZwNzBYaUtVM0V0eWE5ZDBEVzVoUUdkdkxsd1NiRERjeVBXazN0aXB5UjN0T0RNMGlHZjlEcjRLZ3Rvd0l0WXNjMXRfY2JGNHBLdFRBd1JPZ19PRTdKZFZsclJuV1E?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
+          <t>https://www.sondakika.com/amp/haber-nazilli-de-geri-donusum-fabrikasinda-yangin-19913386/</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Aydın</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Nazilli</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Sümer Mahallesi</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr"/>
@@ -5104,7 +5646,7 @@
       <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="n">
-        <v>47.12</v>
+        <v>107.75</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>26</v>
@@ -5113,27 +5655,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:12:35</t>
+          <t>2026-06-04 18:19:00</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı</t>
+          <t>Mersin'de Fabrika Yangını: İtfaiye Söndürdü, İş Yeri Kullanılamaz Halde</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com</t>
+          <t>Mersin'de Fabrika Yangını: İtfaiye Söndürdü, İş Yeri Kullanılamaz Halde politikam.com</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -5143,22 +5685,22 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com</t>
+          <t>Mersin'de Fabrika Yangını: İtfaiye Söndürdü, İş Yeri Kullanılamaz Halde politikam.com</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com Vatandaşın bankalara borcu 6,3 trilyon TL'yi aştı Doviz.com</t>
+          <t>Mersin'de Fabrika Yangını: İtfaiye Söndürdü, İş Yeri Kullanılamaz Halde Mersin'de Fabrika Yangını: İtfaiye Söndürdü, İş Yeri Kullanılamaz Halde politikam.com Mersin'de Fabrika Yangını: İtfaiye Söndürdü, İş Yeri Kullanılamaz Halde politikam.com</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -5168,10 +5710,14 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOblFrNWVVVVVxZ0tSbjNYek5xOUhLcl9RZzJ1ZzhSclFNOTVaY3B0WUk0ODhYSVhJMUVjcVlueUpOMnlBMFVSdFBMRk54T0pxQ240WllDZnBiU0xlVWlrT1BKb1oyX0FlaGZndmg4eDR2T3lrUnNrTWxEZjltU0VqajYwc0tQTDFnTFNvSU51bDFaT3pHbjVEYThwRTlCQVdZQ1k1ZGdR0gGmAUFVX3lxTE5uUWs1ZVVVVXFnS1JuM1h6TnE5SEtyX1FnMnVnOFJyUU05NVpjcHRZSTQ4OFhJWEkxRWNxWW55Sk4yeUEwVVJ0UExGTnhPSnFDbjRaWUNmcGJTTGVVaWtPUEpvWjJfQWVoZmd2aDh4NHZPeWtSc2tNbERmOW1TRWpqNjBzS1BMMWdMU29JTnVsMVpPekduNURhOHBFOUJBV1lDWTVkZ1E?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPOUVXNGV6T0pjU0VHZTR3bE1kTk51VVpkRkg1SFNYeTdHczFCcVNlSjRhVjVyY2RnaUlzRktleDJlcklIRTBEREtpSXphLUdhRS0ySk5DcHJWSGJqZlZ6V3RqMExVeEg2WWl4bDNxNU1lOEZlQXA4clN5WS14NGd5R2RfYWFQWUJMZE00R3p6cEo3dEdSUDhEeVlR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
@@ -5180,7 +5726,7 @@
       <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr"/>
@@ -5194,7 +5740,7 @@
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="n">
-        <v>37.84</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AB28" s="2" t="n">
         <v>27</v>
@@ -5203,27 +5749,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:50:38</t>
+          <t>2026-06-04 09:46:39</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün</t>
+          <t>Denizli’de Fabrika Yangını: Geriye Bu Görüntüler Kaldı</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün Merhaba Gazetesi</t>
+          <t>Denizli’de Fabrika Yangını: Geriye Bu Görüntüler Kaldı Denizli Sanal Basın</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -5233,7 +5779,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>fabrika, sanayi</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -5243,35 +5789,31 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün 03 Haziran 2026 Çarşamba 13:50 Ekonomik krizin etkisiyle konkordato ilan eden firmalara bir yenisi daha eklendi. Konya sanayisindeki dev fabrikanın konkordato süreci 2 gün sonra netleşecek. Ekonomik kriz Türkiye'deki birçok üretim tesisini olumsuz etkiledi. Nakit para akışının durmasıyla konkordato ve iflaslar patladı. Son olarak 2011 yılında Konya Büsan Özel Sanayi Bölgesi'nde kurulan ART Endüstri konkordato ilan etti. 2016 yılından itibaren Konya 2. Organize Sanayi Bölgesi'nde üretime devam eden ART Endüstri , seramik teşhir sistemlerinden depo raf sistemlerine ve uyku merkezlerinin özel ihtiyaçlarına kadar geniş bir uygulama yelpazesinde özgün çözümler sunan, kalite odaklı ve yenilikçi bir üretim şirketi. Piyasada tanınan firmayla ilgili konkordato haberini görenler üzüldü. Öte yandan mahkemenin konkordato sürecine ilişkin kararını 5 Haziran 2026 tarihinde vereceği öğrenildi. Buna göre, ART Endüstri ile ilgili karar 2 gün sonra verilecek. T.c. Konya 3.asliye Ticaret Mahkemesi Başkanlığı'nın duyurusu</t>
+          <t>Denizli’de Fabrika Yangını: Geriye Bu Görüntüler Kaldı Denizli Sanal Basın</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün Merhaba Gazetesi Konya sanayisindeki dev fabrika konkordato ilan etti: Son 2 gün 03 Haziran 2026 Çarşamba 13:50 Ekonomik krizin etkisiyle konkordato ilan eden firmalara bir yenisi daha eklendi. Konya sanayisindeki dev fabrikanın konkordato süreci 2 gün sonra netleşecek. Ekonomik kriz Türkiye'deki birçok üretim tesisini olumsuz etkiledi. Nakit para akışının durmasıyla konkordato ve iflaslar patladı. Son olarak 2011 yılında Konya Büsan Özel Sanayi Bölgesi'nde kurulan ART Endüstri konkordato ilan etti. 2016 yılından itibaren Konya 2. Organize Sanayi Bölgesi'nde üretime devam eden ART Endüstri , seramik teşhir sistemlerinden depo raf sistemlerine ve uyku merkezlerinin özel ihtiyaçlarına kadar geniş bir uygulama yelpazesinde özgün çözümler sunan, kalite odaklı ve yenilikçi bir üretim şirketi. Piyasada tanınan firmayla ilgili konkordato haberini görenler üzüldü. Öte yandan mahkemenin konkordato sürecine ilişkin kararını 5 Haziran 2026 tarihinde vereceği öğrenildi. Konya 3.asliye Ticaret Mahkemesi Başkanlığı'nın duyurusu</t>
+          <t>Denizli’de Fabrika Yangını: Geriye Bu Görüntüler Kaldı Denizli’de Fabrika Yangını: Geriye Bu Görüntüler Kaldı Denizli Sanal Basın Denizli’de Fabrika Yangını: Geriye Bu Görüntüler Kaldı Denizli Sanal Basın</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNaWpwcnFFcXdzRS1VczM4TVAzVXI3anZEU3IxTm5aS2JMRlV6cDhRVEpMeXc5TEpOdlBMLWU4NmxZUWZiMU5CenNFSUROOVdoZnlaV0NBREZMcjN2aFVFaFlLTWd6cmFGQndIQWFKMnliWmhiXzE5d0JOeXkzTWs4LWhKWW1EaFdIa1RjWHhWcjdlX1k2UUM4bHdsNEt1eXdrSXE5YVVlVmt1WktVbUdQQm1aRFZZU2_SAbcBQVVfeXFMTWlqcHJxRXF3c0UtVXMzOE1QM1VyN2p2RFNyMU5uWktiTEZVenA4UVRKTHl3OUxKTnZQTC1lODZsWVFmYjFOQnpzRUlETjlXaGZ5WldDQURGTHIzdmhVRWhZS01nenJhRkJ3SEFhSjJ5YlpoYl8xOXdCTnl5M01rOC1oSlltRGhXSGtUY1h4VnI3ZV9ZNlFDOGx3bDRLdXl3a0lxOWFVZVZrdVpLVW1HUEJtWkRWWVNv?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPeUxrSUs2VmlrY1V3Tjl6TW9qbUU2UU1rWnE5TGNSVThteEc5OGpENUc4aGI1SkQ0Nm44TmR3aFNDcEtjb1NUVEZrMnQ3OHhJSUYyODhzaE5KUm1TMTdZZllXbGNfZHJqVWp0V2dCMlF3ODY0Qk1nSTlOclFmZUdvVVlVZ0VNZlVYWnNF?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>Büsan</t>
-        </is>
-      </c>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr"/>
@@ -5292,7 +5834,7 @@
       <c r="Y29" s="2" t="inlineStr"/>
       <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="n">
-        <v>102.31</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>28</v>
@@ -5301,27 +5843,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 14:41:47</t>
+          <t>2026-06-04 15:54:26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı</t>
+          <t>Esenyurt’taki fabrika yangınından dönen itfaiye aracı devrildi: 3 yaralı</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri</t>
+          <t>Esenyurt’taki fabrika yangınından dönen itfaiye aracı devrildi: 3 yaralı TGRT Haber</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -5331,22 +5873,22 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri</t>
+          <t>Esenyurt’taki fabrika yangınından dönen itfaiye aracı devrildi: 3 yaralı TGRT Haber</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri Türkiye'nin ilaç devi iflasın eşiğine geldi! Firma hakkında konkordato kararı Kamu Son Dakika Haberleri</t>
+          <t>Esenyurt’taki fabrika yangınından dönen itfaiye aracı devrildi: 3 yaralı Esenyurt’taki fabrika yangınından dönen itfaiye aracı devrildi: 3 yaralı TGRT Haber Esenyurt’taki fabrika yangınından dönen itfaiye aracı devrildi: 3 yaralı TGRT Haber</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -5356,7 +5898,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVi1QOUJuTzhBaU1haWNwd3B6OVRjSHktVWlKQ25USktQZmpnZEZiMHZuRW5aN1VmZVRJVWNaMFhubmVWdjh3TmItWHgtVlJpRGNtSWZWTnY5OTBNTXhITjl1d2hPZlNKa0ZGN0RJcUR4djBRdF9CUTFnZlh2TU9ZcHZVUks2QmMwMklIcTVaQzZkRjYyMy1kc1hYcW10Q3RmUy1vNHduOHFTSFVnWlpNRHNuUVJVUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOdVVZR3FfRmdMNENEc3gtMUg0TWxvR0J1anVfTGUtRGtSRXg2YTNjN3c5MVhGMXJ4QTU2eVBWZ0p2QVkxbG4waTJrSHlaQ1JHRTUtTXItM1FMbXFNdDc2dzloVE9MTll1TDFmME1aenZPTGY2QTRjdW5aWTBGT0xVTEhzZnJLMzkzZVB4enBiZkU0b2xxeVNDVVZpcE5jYmR4ZnF5R2R2WGh0SDZKLWNXTmRndEM1WElYd2QxN2FBa0xnZ1pR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
@@ -5382,7 +5924,7 @@
       <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr"/>
       <c r="AA30" s="2" t="n">
-        <v>71.28</v>
+        <v>73.58</v>
       </c>
       <c r="AB30" s="2" t="n">
         <v>29</v>
@@ -5391,12 +5933,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 15:46:28</t>
+          <t>2026-06-05 06:41:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>mali kriz</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -5406,12 +5948,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı</t>
+          <t>Hürmüz kriziyle havada iflas korkusu</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365</t>
+          <t>Hürmüz kriziyle havada iflas korkusu İstanbul Ticaret Gazetesi</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -5421,22 +5963,18 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>firma</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>ticaret</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365</t>
+          <t>Hürmüz kriziyle havada iflas korkusu İstanbul Ticaret Gazetesi</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Dev İlaç Firması İçin Konkordato Süreci Başladı Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365 Dev İlaç Firması İçin Konkordato Süreci Başladı Memur 365</t>
+          <t>Hürmüz kriziyle havada iflas korkusu Hürmüz kriziyle havada iflas korkusu İstanbul Ticaret Gazetesi Hürmüz kriziyle havada iflas korkusu İstanbul Ticaret Gazetesi</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -5446,7 +5984,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPc0FMTk9yb21xWXRueTBWTTltZTVOdlRoU1RIaHdzQWM5QUR0WFdJWGpkSW02dWpGUkFJRXdPclRvb3dPMHVlSGVWbkZUVlpPY2hTWFB4cUoxWjUtWHpPclExdllIQm5XVE5zdXp4SjhRRnRWUzRmUFNMd3MyVlpLM1FzdElRaUg00gGOAUFVX3lxTFBDeFIteWxqTzRua1BLVDhOMThnM3hZQUFZdENiTll4SEFrMWpGODZWbGJRVlNYT045YTg2SklVVktVVVpqenY5Z0dyd3FFNkp4YlRBR3piS3otTFlDbXp5blV4dDhBODZIN0xoMHJTQzZyaHpNSjl4eThpYW1aTVpaNHdoaXAtZTdibXNBYkE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5EQmI1Q2lmdGRic3dhRjVfdEtrbmZQYml6by1sNVA0TXZDSXkybF9YdTVodHZvNk9wQ1V5bmpaWEo2NHpIdHBXbnN4M0ZmZXNtaFpOc1pQTnZYS0RCWmMyNTRRMnowbVRoNWxNSmhTSktIbWtDRnhnbnNOOEo?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
@@ -5454,25 +5992,49 @@
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret:161:body+summary</t>
+        </is>
+      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr"/>
-      <c r="V31" s="2" t="inlineStr"/>
-      <c r="W31" s="2" t="inlineStr"/>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Türkiye</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi | İstanbul Ticaret Merkezi | İstanbul Ticaret İl Müdürlüğü | İstanbul Ticaret İş Güvenliği ve Endüstriyel Ürünler San. A.Ş | İstanbul Ticaret Üniversitesi Küçükyalı Kampüsü</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi</t>
+        </is>
+      </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>100.0 | 100.0 | 100.0 | 100.0 | 100.0</t>
+        </is>
+      </c>
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="n">
-        <v>46.32</v>
+        <v>148.12</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>30</v>
@@ -5481,12 +6043,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:45:31</t>
+          <t>2026-06-04 09:48:03</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -5496,12 +6058,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu</t>
+          <t>Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu velev.press</t>
+          <t>Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti Patronlar Dünyası</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -5511,82 +6073,62 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>sanayi</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Ankara 3. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Şirket, yüksek finansman maliyetleri, kredi geri ödeme sorunları ve bozulan nakit akışı nedeniyle mahkemeye başvurduğunu açıkladı. Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Ankara 3. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Şirket, yüksek finansman maliyetleri, kredi geri ödeme sorunları ve bozulan nakit akışı nedeniyle mahkemeye başvurduğunu açıkladı. Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Ankara 3. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Şirket, yüksek finansman maliyetleri, kredi geri ödeme sorunları ve bozulan nakit akışı nedeniyle mahkemeye başvurduğunu açıkladı. Kamuyu Aydınlatma Platformu’nda (KAP) yayımlanan açıklamaya göre Türk İlaç ve Serum Sanayi A.Ş., Yönetim Kurulu Başkanı Mehmet Berat Battal ve şirkette pay sahibi olan Battal Holding A.Ş. ile birlikte konkordato talebinde bulundu. Başvuru sonucunda Ankara 3. Asliye Ticaret Mahkemesi tarafından 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verildi. Şirket açıklamasında , krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin konkordato başvurusunun temel nedenleri arasında yer aldığı belirtildi. KAP açıklamasında, 14 Mayıs 2026 tarihinde başlayan kredi geri ödeme gecikmelerinin devam ettiği ifade edildi. Ayrıca 20 Mayıs 2026 tarihinde oluşan karşılıksız çek kayıtlarının da henüz kapatılamadığı bilgisi paylaşı</t>
+          <t>Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti Fransa Cumhurbaşkanı Emmanuel Macron’un Davos’ta taktığı ve sosyal medyada gündem olan lüks güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti. Şirket, artan mali baskılar karşısında ayakta kalamadı. 04.06.2026 09:48 • Güncelleme: 04.06.2026 09:57 #Emmanuel Macron#Davos#Dalloz Creations Haberi paylaşın Yazı Boyutu: 16px 32px Yazdır Davos’ta Emmanuel Macron’un taktığı ve dünya çapında ilgi gören güneş gözlüklerinin camlarını üreten Fransız Dalloz Creations, mali sıkıntılara yenik düştü. 69 YILLIK HİKAYENİN SONUNA GELİNDİ Fransa’nın Jura bölgesindeki Saint-Claude kentinde faaliyet gösteren Dalloz Creations hakkında Lons-le-Saunier Ticaret Mahkemesi tarafından tasfiye kararı verildi. Kararla birlikte 69 yıllık şirketin faaliyetleri sona ererken, 29 çalışan da işini kaybedecek. DAVOS'TA MACRON'UN TAKTIĞI GÖZLÜĞÜN CAMINI ÜRETMİŞTİ Dalloz Creations’ın adı, Ocak ayında İsviçre’nin Davos kentinde düzenlenen Dünya Ekonomik Forumu sırasında yeniden gündeme gelmişti. Macron’un kullandığı yaklaşık 650 euro değerindeki mavi aynalı güneş gözlüklerinin camlarının şirket tarafından üretildiğinin ortaya çıkması, Fransız üreticiye uluslararası ölçekte dikkat çekmişti. Ancak bu tanıtım etkisi şirketin mali sorunlarını çözmeye yetmedi. Mahkeme kayıtlarına göre şirketin ödeme güçlüğüne düştüğü tarih 20 Mart 2026 olarak belirlendi. Ticari varlıkları satışa çıkarılan şirket için kurtarma formülü bulunamadı. AVRUPA'NIN ÖNEMLİ GÜNEŞ GÖZLÜĞÜ CAMI ÜRETİCİLERİNDEN BİRİYDİ 1957 yılında Christian Dalloz tarafından kurulan Dalloz Creations, Avrupa’nın önemli güneş gözlüğü camı üreticileri arasında yer alıyordu. Polikarbonat gözlük camlarının geliştirilmesinde öncü rol üstlenen şirket, son yıllarda biyolojik döngüsel malzemeler ve değerli metallerin camlara entegre edilmesi gibi yüksek katma değerli ürünlere yönelmişti. Buna rağmen satışlar düzenli olarak geriledi. Şirketin cirosu 2023’te 3,8 milyon euro seviyesindeyken, 2024’te 3,6 milyon euroya düştü. Gelirler 2025 yılında ise 2,5 milyon euroya kadar geriledi. Uzmanlar, Asya merkezli üreticilerden gelen rekabet, yükselen üretim maliyetleri ve optik sektöründeki dönüşümün şirket üzerindeki baskıyı artırdığına dikkat çekiyor. Dalloz Creations’ın kapanışı, yalnızca 29 kişinin işsiz kalması anlamına gelmiyor. Karar aynı zamanda Fransa’nın geleneksel gözlük üretim merkezi olarak bilinen Jura bölgesindeki sanayinin yaşadığı zorlukların da son örneklerinden biri olarak görülüyor. patronlardunyasi.com Dolar 45,9595 0,04% Euro 53,351 -0,13% Sterlin 61,7774 -0,18% Bitcoin 3.078.112 -0,94% BİST-100 14.139,71 -0,43% Gram Altın 6.590,036 -0,59% Gümüş 74,23 -1,21% Faiz 43,45 0,12% Yazı Boyutu: 16px 32px Yazdır Davos’ta Emmanuel Macron’un taktığı ve dünya çapında ilgi gören güneş gözlüklerinin camlarını üreten Fransız Dalloz Creations, mali sıkıntılara yenik düştü. 69 YILLIK HİKAYENİN SONUNA GELİNDİ Fransa’nın Jura bölgesindeki Saint-Claude kentinde faaliyet gösteren Dalloz Creations hakkında Lons-le-Saunier Ticaret Mahkemesi tarafından tasfiye kararı verildi. Kararla birlikte 69 yıllık şirketin faaliyetleri sona ererken, 29 çalışan da işini kaybedecek. DAVOS'TA MACRON'UN TAKTIĞI GÖZLÜĞÜN CAMINI ÜRETMİŞTİ Dalloz Creations’ın adı, Ocak ayında İsviçre’nin Davos kentinde düzenlenen Dünya Ekonomik Forumu sırasında yeniden gündeme gelmişti. Macron’un kullandığı yaklaşık 650 euro değerindeki mavi aynalı güneş gözlüklerinin camlarının şirket tarafından üretildiğinin ortaya çıkması, Fransız üreticiye uluslararası ölçekte dikkat çekmişti. Ancak bu tanıtım etkisi şirketin mali sorunlarını çözmeye yetmedi. Mahkeme kayıtlarına göre şirketin ödeme güçlüğüne düştüğü tarih 20 Mart 2026 olarak belirlendi. Ticari varlıkları satışa çıkarılan şirket için kurtarma formülü bulunamadı. AVRUPA'NIN ÖNEMLİ GÜNEŞ GÖZLÜĞÜ CAMI ÜRETİCİLERİNDEN BİRİYDİ 1957 yılında Christian Dalloz tarafından kurulan Dalloz Creations, Avrupa’nın önemli güneş gözlüğü camı üreticileri arasında yer alıyordu. Polikarbonat gözlük camlarının geliştirilmesinde öncü rol üstlenen şirket, son yıllarda biyolojik döngüsel malzemeler ve değerli metallerin camlara entegre edilmesi gibi yüksek katma değerli ürünlere yönelmişti. Buna rağmen satışlar düzenli olarak geriledi. Şirketin cirosu 2023’te 3,8 milyon euro seviyesindeyken, 2024’te 3,6 milyon euroya düştü. Gelirler 2025 yılında ise 2,5 milyon euroya kadar geriledi. Uzmanlar, Asya merkezli üreticilerden gelen rekabet, yükselen üretim maliyetleri ve optik sektöründeki dönüşümün şirket üzerindeki baskıyı artırdığına dikkat çekiyor. Dalloz Creations’ın kapanışı, yalnızca 29 kişinin işsiz kalması anlamına gelmiyor. Karar aynı zamanda Fransa’nın geleneksel gözlük üretim merkezi olarak bilinen Jura bölgesindeki sanayinin yaşadığı zorlukların da son örneklerinden biri olarak görülüyor. patronlardunyasi.com Davos’ta Emmanuel Macron’un taktığı ve dünya çapında ilgi gören güneş gözlüklerinin camlarını üreten Fransız Dalloz Creations, mali sıkıntılara yenik düştü. 69 YILLIK HİKAYENİN SONUNA GELİNDİ Fransa’nın Jura bölgesindeki Saint-Claude kentinde faaliyet gösteren Dalloz Creations hakkında Lons-le-Saunier Ticaret Mahkemesi tarafından tasfiye kararı verildi. Kararla birlikte 69 yıllık şirketin faaliyetleri sona ererken, 29 çalışan da işini kaybedecek. DAVOS'TA MACRON'UN TAKTIĞI GÖZLÜĞÜN CAMINI ÜRETMİŞTİ Dalloz Creations’ın adı, Ocak ayında İsviçre’nin Davos kentinde düzenlenen Dünya Ekonomik Forumu sırasında yeniden gündeme gelmişti. Macron’un kullandığı yaklaşık 650 euro değerindeki mavi aynalı güneş gözlüklerinin camlarının şirket tarafından üretildiğinin ortaya çıkması, Fransız üreticiye uluslararası ölçekte dikkat çekmişti. Ancak bu tanıtım etkisi şirketin mali sorunlarını çözmeye yetmedi. Mahkeme kayıtlarına göre şirketin ödeme güçlüğüne düştüğü tarih 20 Mart 2026 olarak belirlendi. Ticari varlıkları satışa çıkarılan şirket için kurtarma formülü bulunamadı. AVRUPA'NIN ÖNEMLİ GÜNEŞ GÖZLÜĞÜ CAMI ÜRETİCİLERİNDEN BİRİYDİ 1957 yılında Christian Dalloz tarafından kurulan Dalloz Creations, Avrupa’nın önemli güneş gözlüğü camı üreticileri arasında yer alıyordu. Polikarbonat gözlük camlarının geliştirilmesinde öncü rol üstlenen şirket, son yıllarda biyolojik döngüsel malzemeler ve değerli metallerin camlara entegre edilmesi gibi yüksek katma değerli ürünlere yönelmişti. Buna rağmen satışlar düzenli olarak geriledi. Şirketin cirosu 2023’te 3,8 milyon euro seviyesindeyken, 2024’te 3,6 milyon euroya düştü. Gelirler 2025 yılında ise 2,5 milyon euroya kadar geriledi. Uzmanlar, Asya merkezli üreticilerden gelen rekabet, yükselen üretim maliyetleri ve optik sektöründeki dönüşümün şirket üzerindeki baskıyı artırdığına dikkat çekiyor. Dalloz Creations’ın kapanışı, yalnızca 29 kişinin işsiz kalması anlamına gelmiyor. Karar aynı zamanda Fransa’nın geleneksel gözlük üretim merkezi olarak bilinen Jura bölgesindeki sanayinin yaşadığı zorlukların da son örneklerinden biri olarak görülüyor. patronlardunyasi.com Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti Fransa Cumhurbaşkanı Emmanuel Macron’un Davos’ta taktığı ve sosyal medyada gündem olan lüks güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti. Şirket, artan mali baskılar karşısında ayakta kalamadı. Davos’ta Emmanuel Macron’un taktığı ve dünya çapında ilgi gören güneş gözlüklerinin camlarını üreten Fransız Dalloz Creations, mali sıkıntılara yenik düştü. 69 YILLIK HİKAYENİN SONUNA GELİNDİ Fransa’nın Jura bölgesindeki Saint-Claude kentinde faaliyet gösteren Dalloz Creations hakkında Lons-le-Saunier Ticaret Mahkemesi tarafından tasfiye kararı verildi. Kararla birlikte 69 yıllık şirketin faaliyetleri sona ererken, 29 çalışan da işini kaybedecek. DAVOS'TA MACRON'UN TAKTIĞI GÖZLÜĞÜN CAMINI ÜRETMİŞTİ Dalloz Creations’ın adı, Ocak ayında İsviçre’nin Davos kentinde düzenlenen Dünya Ekonomik Forumu sırasında yeniden gündeme gelmişti. Macron’un kullandığı yaklaşık 650 euro değerindeki mavi aynalı güneş gözlüklerinin camlarının şirket tarafından üretildiğinin ortaya çıkması, Fransız üreticiye uluslararası ölçekte dikkat çekmişti. Ancak bu tanıtım etkisi şirketin mali sorunlarını çözmeye yetmedi. Mahkeme kayıtlarına göre şirketin ödeme güçlüğüne düştüğü tarih 20 Mart 2026 olarak belirlendi. Ticari varlıkları satışa çıkarılan şirket için kurtarma formülü bulunamadı. AVRUPA'NIN ÖNEMLİ GÜNEŞ GÖZLÜĞÜ CAMI ÜRETİCİLERİNDEN BİRİYDİ 1957 yılında Christian Dalloz tarafından kurulan Dalloz Creations, Avrupa’nın önemli güneş gözlüğü camı üreticileri arasında yer alıyordu. Polikarbonat gözlük camlarının geliştirilmesinde öncü rol üstlenen şirket, son yıllarda biyolojik döngüsel malzemeler ve değerli metallerin camlara entegre edilmesi gibi yüksek katma değerli ürünlere yönelmişti. Buna rağmen satışlar düzenli olarak geriledi. Şirketin cirosu 2023’te 3,8 milyon euro seviyesindeyken, 2024’te 3,6 milyon euroya düştü. Gelirler 2025 yılında ise 2,5 milyon euroya kadar geriledi. Uzmanlar, Asya merkezli üreticilerden gelen rekabet, yükselen üretim maliyetleri ve optik sektöründeki dönüşümün şirket üzerindeki baskıyı artırdığına dikkat çekiyor. Dalloz Creations’ın kapanışı, yalnızca 29 kişinin işsiz kalması anlamına gelmiyor. Karar aynı zamanda Fransa’nın geleneksel gözlük üretim merkezi olarak bilinen Jura bölgesindeki sanayinin yaşadığı zorlukların da son örneklerinden biri olarak görülüyor. Koç Holding’in 100’üncü yıl resepsiyonu Ankara’da siyaset dünyasını buluştururken, Güler Sabancı ve Cavit Çağlar’ın da aralarında olduğu iş dünyasının birçok önemli ismi Aydın Doğan ailesinin Hilton davetinde bir araya geldi. Gecenin esprisi ise Güler Sabancı’nın 70’nci yaşını kutlayan Hilton ile yaşıt çıkması oldu. Epstein bağlantıları ortaya çıkınca İngiliz Kraliyet Ailesi'ndeki tüm görevlerinden el çektirilen Prens Andrew'un, kraliyete ait Royal Lodge malikanesinde çok düşük bir bedelle oturması ve çevresindeki mülkleri gizlice kiraya vermesi İngiltere'de yeni bir tartışma başlattı. The Telegraph gazetesi bugün, "Andrew gizli kira anlaşmalarıyla kazanç sağladı" manşetiyle yayımlandı. PATRONLAR DÜNYASI 2004 yılında kuruldu. İş dünyası, patronlar, finans ve genel ekonomi haberciliği alanında özgün yayıncılık yapmaktadır.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu Türk İlaç ve Serum Sanayi konkordato istedi: Borsa’da işlem görüyordu velev.press Borsa İstanbul'da işlem gören Türk İlaç ve Serum Sanayi A.Ş. hakkında konkordato süreci başlatıldı. Asliye Ticaret Mahkemesi, şirketin başvurusu üzerine 3 ay süreyle geçici mühlet kararı verdi. Şirket, yüksek finansman maliyetleri, kredi geri ödeme sorunları ve bozulan nakit akışı nedeniyle mahkemeye başvurduğunu açıkladı. Kamuyu Aydınlatma Platformu’nda (KAP) yayımlanan açıklamaya göre Türk İlaç ve Serum Sanayi A.Ş., Yönetim Kurulu Başkanı Mehmet Berat Battal ve şirkette pay sahibi olan Battal Holding A.Ş. ile birlikte konkordato talebinde bulundu. Başvuru sonucunda Ankara 3. Asliye Ticaret Mahkemesi tarafından 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verildi. Şirket açıklamasında , krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin konkordato başvurusunun temel nedenleri arasında yer aldığı belirtildi. KAP açıklamasında, 14 Mayıs 2026 tarihinde başlayan kredi geri ödeme gecikmelerinin devam ettiği ifade edildi.</t>
+          <t>Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti Patronlar Dünyası Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti Fransa Cumhurbaşkanı Emmanuel Macron’un Davos’ta taktığı ve sosyal medyada gündem olan lüks güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti. Şirket, artan mali baskılar karşısında ayakta kalamadı. 04.06.2026 09:48 • Güncelleme: 04.06.2026 09:57 #Emmanuel Macron#Davos#Dalloz Creations Haberi paylaşın Yazı Boyutu: 16px 32px Yazdır Davos’ta Emmanuel Macron’un taktığı ve dünya çapında ilgi gören güneş gözlüklerinin camlarını üreten Fransız Dalloz Creations, mali sıkıntılara yenik düştü. 69 YILLIK HİKAYENİN SONUNA GELİNDİ Fransa’nın Jura bölgesindeki Saint-Claude kentinde faaliyet gösteren Dalloz Creations hakkında Lons-le-Saunier Ticaret Mahkemesi tarafından tasfiye kararı verildi. Kararla birlikte 69 yıllık şirketin faaliyetleri sona ererken, 29 çalışan da işini kaybedecek. DAVOS'TA MACRON'UN TAKTIĞI GÖZLÜĞÜN CAMINI ÜRETMİŞTİ Dalloz Creations’ın adı, Ocak ayında İsviçre’nin Davos kentinde düzenlenen Dünya Ekonomik Forumu sırasında yeniden gündeme gelmişti. Macron’un kullandığı yaklaşık 650 euro değerindeki mavi aynalı güneş gözlüklerinin camlarının şirket tarafından üretildiğinin ortaya çıkması, Fransız üreticiye uluslararası ölçekte dikkat çekmişti. Ancak bu tanıtım etkisi şirketin mali sorunlarını çözmeye yetmedi. Mahkeme kayıtlarına göre şirketin ödeme güçlüğüne düştüğü tarih 20 Mart 2026 olarak belirlendi. Ticari varlıkları satışa çıkarılan şirket için kurtarma formülü bulunamadı. AVRUPA'NIN ÖNEMLİ GÜNEŞ GÖZLÜĞÜ CAMI ÜRETİCİLERİNDEN BİRİYDİ 1957 yılında Christian Dalloz tarafından kurulan Dalloz Creations, Avrupa’nın önemli güneş gözlüğü camı üreticileri arasında yer alıyordu. Polikarbonat gözlük camlarının geliştirilmesinde öncü rol üstlenen şirket, son yıllarda biyolojik döngüsel malzemeler ve değerli metallerin camlara entegre edilmesi gibi yüksek katma değerli ürünlere yönelmişti. Şirketin cirosu 2023’te 3,8 milyon euro seviyesindeyken, 2024’te 3,6 milyon euroya düştü. Uzmanlar, Asya merkezli üreticilerden gelen rekabet, yükselen üretim maliyetleri ve optik sektöründeki dönüşümün şirket üzerindeki baskıyı artırdığına dikkat çekiyor. Dalloz Creations’ın kapanışı, yalnızca 29 kişinin işsiz kalması anlamına gelmiyor. Karar aynı zamanda Fransa’nın geleneksel gözlük üretim merkezi olarak bilinen Jura bölgesindeki sanayinin yaşadığı zorlukların da son örneklerinden biri olarak görülüyor. patronlardunyasi.com Dolar 45,9595 0,04% Euro 53,351 -0,13% Sterlin 61,7774 -0,18% Bitcoin 3.078.112 -0,94% BİST-100 14.139,71 -0,43% Gram Altın 6.590,036 -0,59% Gümüş 74,23 -1,21% Faiz 43,45 0,12% Yazı Boyutu: 16px 32px Yazdır Davos’ta Emmanuel Macron’un taktığı ve dünya çapında ilgi gören güneş gözlüklerinin camlarını üreten Fransız Dalloz Creations, mali sıkıntılara yenik düştü. patronlardunyasi.com Davos’ta Emmanuel Macron’un taktığı ve dünya çapında ilgi gören güneş gözlüklerinin camlarını üreten Fransız Dalloz Creations, mali sıkıntılara yenik düştü. patronlardunyasi.com Davos’ta Emmanuel Macron’un taktığı güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti Fransa Cumhurbaşkanı Emmanuel Macron’un Davos’ta taktığı ve sosyal medyada gündem olan lüks güneş gözlüklerinin camlarını üreten Fransız şirket Dalloz Creations iflas etti. Davos’ta Emmanuel Macron’un taktığı ve dünya çapında ilgi gören güneş gözlüklerinin camlarını üreten Fransız Dalloz Creations, mali sıkıntılara yenik düştü. Koç Holding’in 100’üncü yıl resepsiyonu Ankara’da siyaset dünyasını buluştururken, Güler Sabancı ve Cavit Çağlar’ın da aralarında olduğu iş dünyasının birçok önemli ismi Aydın Doğan ailesinin Hilton davetinde bir araya geldi. Gecenin esprisi ise Güler Sabancı’nın 70’nci yaşını kutlayan Hilton ile yaşıt çıkması oldu. Epstein bağlantıları ortaya çıkınca İngiliz Kraliyet Ailesi'ndeki tüm görevlerinden el çektirilen Prens Andrew'un, kraliyete ait Royal Lodge malikanesinde çok düşük bir bedelle oturması ve çevresindeki mülkleri gizlice kiraya vermesi İngiltere'de yeni bir tartışma başlattı. PATRONLAR DÜNYASI 2004 yılında kuruldu. İş dünyası, patronlar, finans ve genel ekonomi haberciliği alanında özgün yayıncılık yapmaktadır.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://velev.press/ekonomi/turk-ilac-ve-serum-sanayi-konkordato-istedi-borsada-islem-goruyordu/</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNeWE0WHJIVDBFZVRKZTgtN1NiZ3lqYWt5OUllSlBTdlFfYkU1T3EycnpBUGJUc1JuMFdyUkRKTWJZR19BdGVOUXFMQU1TMnJxUVI2bEctQVlMY2doRTRuRzZaNUtCQXFZVERlRWpKWjBuX2J3RG1YZUpYRTRJdmNrcWNwNll0czJzYktrYkdEMzRWMzM5SUhBblhvU1BxeWNDWTlNSERwbXZxbktYTXljVGlrN1FNYml3VGp6ckhBMmdXVTQ1Sk9XcV82OGJTR09EVS1Mb3JWQTZqZVZ2VzZj?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>Battal Holding A.Ş</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>Battal Holding A.Ş:120:body | Battal Holding A.Ş:raw_legal</t>
-        </is>
-      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>Battal Holding A.Ş İstanbul Türkiye</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Battal Group</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>Battal Group</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr"/>
       <c r="AA32" s="2" t="n">
-        <v>195.75</v>
+        <v>131.75</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>31</v>
@@ -5595,12 +6137,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:24:46</t>
+          <t>2026-06-05 07:50:18</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -5610,12 +6152,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı</t>
+          <t>Bursa'da geri dönüşüm firması için iflas sürecinde kritik aşama! Sıra cetveli ilan edildi...</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı Samanyolu Haber</t>
+          <t>Bursa'da geri dönüşüm firması için iflas sürecinde kritik aşama! Sıra cetveli ilan edildi... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -5625,7 +6167,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>firma</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -5635,27 +6177,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Borsa İstanbul’da işlem gören Türk İlaç ve Serum Sanayi A.Ş., finansal baskılar nedeniyle konkordato başvurusunda bulundu. Ankara 3. Asliye Ticaret Mahkemesi, 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verdi. KONKORDATO BAŞVURUSUNUN NEDENLERİ Şirket açıklamasında krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin başvurunun temel gerekçeleri olduğu belirtildi. 14 Mayıs 2026’da başlayan kredi geri ödeme gecikmeleri devam ederken 20 Mayıs 2026’da oluşan karşılıksız çek kayıtları da henüz kapatılamadı. KISA VADELİ BORÇ YÜKÜ BASKIYI ARTIRDI Kısa vadede yoğunlaşan yüksek tutarlı çek ödeme yükümlülükleri ile banka kredilerinin ağırlıklı olarak kısa vadeli yapıda olması finansal baskıyı daha da artırdı. 2026’nın ilk çeyreğinde kâr elde edilmesine karşın 2025 yılında oluşan yüksek zararın etkileri sürüyor. ÜRETİM KESİNTİSİZ DEVAM EDECEK Şirket konkordato başvurusunun varlıkların korunması, üretimin kesintisiz sürdürülmesi ve alacaklılar tarafından başlatılabilecek haciz işlemlerinin önüne geçilmesi amacıyla yapıldığını duyurdu. Kamu hizmeti niteliğindeki faaliyetlerin devam ettirilmesi hedefleniyor. YENİDEN YAPILANDIRMA GÖRÜŞMELERİ BAŞLAYACAK Mahkeme kararının ardından başta bankalar olmak üzere tüm alacaklılarla borçların yeniden yapılandırılması için görüşmeler başlatılacak. Nakit akışının düzenlenmesi ve finansman giderlerinin azaltılması için gerekli çalışmalar yürütülecek. Şirket tüm önemli gelişmeleri sermaye piyasası mevzuatı çerçevesinde kamuoyuyla paylaşmaya</t>
+          <t>Bursa'da geri dönüşüm firması için iflas sürecinde kritik aşama! Sıra cetveli ilan edildi... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı Borsa şirketi konkordatoya başvurdu, ilaç sektörü sarsıldı Samanyolu Haber Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Borsa İstanbul’da işlem gören Türk İlaç ve Serum Sanayi A.Ş., finansal baskılar nedeniyle konkordato başvurusunda bulundu. Asliye Ticaret Mahkemesi, 2 Haziran 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet kararı verdi. KONKORDATO BAŞVURUSUNUN NEDENLERİ Şirket açıklamasında krediye erişimde yaşanan zorluklar, yüksek faiz ortamı, bozulan nakit akışı ve artan finansman maliyetlerinin başvurunun temel gerekçeleri olduğu belirtildi. 14 Mayıs 2026’da başlayan kredi geri ödeme gecikmeleri devam ederken 20 Mayıs 2026’da oluşan karşılıksız çek kayıtları da henüz kapatılamadı. KISA VADELİ BORÇ YÜKÜ BASKIYI ARTIRDI Kısa vadede yoğunlaşan yüksek tutarlı çek ödeme yükümlülükleri ile banka kredilerinin ağırlıklı olarak kısa vadeli yapıda olması finansal baskıyı daha da artırdı. 2026’nın ilk çeyreğinde kâr elde edilmesine karşın 2025 yılında oluşan yüksek zararın etkileri sürüyor. ÜRETİM KESİNTİSİZ DEVAM EDECEK Şirket konkordato başvurusunun varlıkların korunması, üretimin kesintisiz sürdürülmesi ve alacaklılar tarafından başlatılabilecek haciz işlemlerinin önüne geçilmesi amacıyla yapıldığını duyurdu. Kamu hizmeti niteliğindeki faaliyetlerin devam ettirilmesi hedefleniyor. YENİDEN YAPILANDIRMA GÖRÜŞMELERİ BAŞLAYACAK Mahkeme kararının ardından başta bankalar olmak üzere tüm alacaklılarla borçların yeniden yapılandırılması için görüşmeler başlatılacak. Nakit akışının düzenlenmesi ve finansman giderlerinin azaltılması için gerekli çalışmalar yürütülecek. Şirket tüm önemli gelişmeleri sermaye piyasası mevzuatı çerçevesinde kamuoyuyla paylaşmaya</t>
+          <t>Bursa'da geri dönüşüm firması için iflas sürecinde kritik aşama! Sıra cetveli ilan edildi... Bursa'da geri dönüşüm firması için iflas sürecinde kritik aşama! Sıra cetveli ilan edildi... Bursa Hakimiyet Bursa'da geri dönüşüm firması için iflas sürecinde kritik aşama! Sıra cetveli ilan edildi...</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.samanyoluhaber.com/borsa-sirketi-konkordatoya-basvurdu-ilac-sektoru-sarsildi/1488760</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOSzhhX211MFlteGNYUk1ELVZDQXplYmlKVm5pUXFwcWdLRGRFY3k2Z2pGSlMxbGVnaTBCNHBuWDFFR3pYV19WcFNZNS02SUhDWVRkS25KMy14Z1lKbjZ4ZDE0NEg4TUVWQk11MzhrelR6dUt3bjl2RFRBbnBQSEVWbG1kTzA5d2w2UjM4TWp4WWpsUENyT21lMVBRaWxJdmxrWHA3LUJaVU03dzZIVHJlYTNlMFVsMExxSnBVVUNxOEtJalA4TFJnbDU4Nkx6ZHNwZkE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Bursa</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
@@ -5680,7 +6222,7 @@
       <c r="Y33" s="2" t="inlineStr"/>
       <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" s="2" t="n">
-        <v>80.5</v>
+        <v>100.08</v>
       </c>
       <c r="AB33" s="2" t="n">
         <v>32</v>
@@ -5689,12 +6231,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 15:49:03</t>
+          <t>2026-06-05 06:25:00</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>tasfiye</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5704,12 +6246,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor</t>
+          <t>Bursa'da konkordato dosyalarında kritik gün: Bir şirkete iflas, diğerine ek süre</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi</t>
+          <t>Bursa'da konkordato dosyalarında kritik gün: Bir şirkete iflas, diğerine ek süre Bursada Bugün</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5729,48 +6271,76 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi</t>
+          <t>Bursa iş dünyasını yakından ilgilendiren iki önemli konkordato dosyasında mahkemeden dikkat çeken kararlar çıktı. Bursa 3. Asliye Ticaret Mahkemesi, Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Ltd. Şti. hakkında iflas kararı verirken, Mattaş Endüstriyel Mutfak Sanayi A.Ş.'nin geçici konkordato mühletini iki ay uzattı. Bursa iş dünyasını yakından ilgilendiren iki önemli konkordato dosyasında mahkemeden dikkat çeken kararlar çıktı. Bursa 3. Asliye Ticaret Mahkemesi, Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Ltd. Şti. hakkında iflas kararı verirken, Mattaş Endüstriyel Mutfak Sanayi A.Ş.'nin geçici konkordato mühletini iki ay uzattı. Bursa iş dünyasını yakından ilgilendiren iki önemli konkordato dosyasında mahkemeden dikkat çeken kararlar çıktı. Bursa 3. Asliye Ticaret Mahkemesi, Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Ltd. Şti. hakkında iflas kararı verirken, Mattaş Endüstriyel Mutfak Sanayi A.Ş.'nin geçici konkordato mühletini iki ay uzattı. Bursa'da konkordato dosyalarında kritik gün: Bir şirkete iflas, diğerine ek süre Bursa'da Tekstil Sektörünü Etkileyen İflas Kararı Endüstriyel Mutfak Sektöründeki Şirkete Ek Süre Verildi Şirketin Geleceği Temmuz Ayındaki Duruşmada Netleşecek Bursa İş Dünyasında Konkordato Dosyaları Yakın Takipte Bursa iş dünyasını yakından ilgilendiren iki önemli konkordato dosyasında mahkemeden dikkat çeken kararlar çıktı. Bursa 3. Asliye Ticaret Mahkemesi, Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Ltd. Şti. hakkında iflas kararı verirken, Mattaş Endüstriyel Mutfak Sanayi A.Ş.'nin geçici konkordato mühletini iki ay uzattı. Bursa'da ekonomik zorluklarla mücadele eden şirketlerin konkordato süreçlerine ilişkin yargı kararları iş dünyasında yankı uyandırdı. Aynı mahkemede görülen iki ayrı dosyada birbirinden farklı sonuçlar ortaya çıkarken, bir şirket için iflas süreci resmen başlatıldı, diğer şirkete ise mali yapısını toparlayabilmesi amacıyla ek süre tanındı. Kentte son dönemde artan konkordato başvuruları yakından takip edilirken, Bursa 3. Asliye Ticaret Mahkemesi tarafından verilen kararlar hem alacaklılar hem de ticari çevreler açısından dikkatle değerlendiriliyor. Mahkemenin açıkladığı son kararlar, şirketlerin finansal sürdürülebilirlik süreçlerinde ne kadar kritik bir dönemeçte olduklarını da gözler önüne serdi. Mahkemenin değerlendirdiği dosyalardan birinde faaliyetlerini tekstil ve deri alanında sürdüren Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi hakkında önemli bir karar verildi. Şirket yönetimi tarafından daha önce yapılan konkordato talebi yargı sürecinde beklenen sonucu alamadı. Yapılan incelemeler, mali tablolar ve şirketin ekonomik durumu dikkate alınarak hazırlanan raporlar doğrultusunda konkordato isteminin uygun olmadığı kanaatine varıldı. Mahkeme, şirketin mali yükümlülüklerini karşılayamayacak durumda bulunduğunu değerlendirerek konkordato talebini reddetti. Kararla birlikte daha önce tanınan geçici mühlet uygulaması sona ererken, şirket lehine yürürlükte bulunan koruyucu tedbirler de kaldırıldı. Böylece alacaklıları korumaya yönelik yeni bir hukuki süreç devreye girerken, şirket açısından iflas süreci resmiyet kazandı. Mahkeme kayıtlarına göre iflas kararı 3 Haziran 2026 tarihi itibarıyla yürürlüğe girdi. Sürecin, ilgili mevzuat kapsamında adi tasfiye hükümlerine göre yürütüleceği belirtildi. Bu gelişme özellikle tekstil ve deri sektöründe faaliyet gösteren firmalar tarafından yakından takip edilmeye başlandı. Aynı mahkemede görüşülen bir diğer dosyada ise farklı bir tablo ortaya çıktı. Endüstriyel mutfak ekipmanları alanında faaliyet gösteren Mattaş Endüstriyel Mutfak Sanayi A.Ş. için daha önce verilen geçici konkordato mühleti yeniden değerlendirildi. Mahkeme, şirketin mali durumuna ilişkin sürecin henüz tamamlanmadığı ve mevcut koşulların yeniden incelenmesi gerektiği görüşüyle geçici mühlet süresinin uzatılmasına karar verdi. Böylece şirket, mali yapısını güçlendirebilmek ve borçlarını yeniden yapılandırabilmek adına ek zaman kazanmış oldu. Karar kapsamında konkordato koruması da devam edecek. Şirket hakkında uygulanmakta olan tedbirlerin yürürlükte kalması sayesinde alacaklılar tarafından yeni icra işlemleri başlatılamayacak ve mevcut takipler de konkordato hükümleri çerçevesinde değerlendirilmeyi sürdürecek. Mahkeme tarafından verilen uzatma kararı geçici nitelik taşıyor. Şirketin konkordato talebine ilişkin nihai değerlendirme önümüzdeki süreçte yapılacak duruşmada ele alınacak. Temmuz ayında gerçekleştirilecek duruşmada şirketin mali tabloları, ödeme planları ve konkordato komiserlerinin hazırlayacağı raporlar yeniden incelenecek. Mahkemenin vereceği karar, şirketin faaliyetlerini mevcut yapısıyla sürdürebilip sürdüremeyeceği açısından belirleyici olacak. Bu nedenle hem sektör temsilcileri hem de şirketin ticari ilişkide bulunduğu kurumlar, duruşmadan çıkacak sonucu yakından izliyor. Son kararlarla birlikte Bursa'da aynı dönemde konkordato koruması talep eden iki şirketin yolları ayrılmış oldu. Bir şirket için ekonomik sıkıntılar iflas kararıyla sonuçlanırken, diğer şirkete faaliyetlerini sürdürebilmesi ve finansal dengesini yeniden kurabilmesi amacıyla ek fırsat tanındı. Özellikle son yıllarda artan maliyetler, finansmana erişimde yaşanan güçlükler ve piyasalardaki dalgalanmalar nedeniyle birçok şirket konkordato yoluna başvuruyor. Mahkemelerin verdiği kararlar ise yalnızca ilgili firmaları değil, tedarik zincirinden çalışanlara, alacaklılardan sektör paydaşlarına kadar geniş bir kesimi doğrudan etkiliyor. Bursa'da görülen son iki dosya da konkordato süreçlerinin her şirket için farklı sonuçlar doğurabileceğini ortaya koyarken, iş dünyasının önümüzdeki dönemde açıklanacak yeni mahkeme kararlarına odaklanmasına neden oldu. Diğer Bursa Haberleri - Bölge Haberleri için tıklayın Melisa Döngel yaz sezonunu açtı! Tekne tatilinden pa</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi Kapanan ve tasfiye edilen şirket sayısında düşüş sürüyor Gaziantep Sabah Gazetesi</t>
+          <t>Bursa'da konkordato dosyalarında kritik gün: Bir şirkete iflas, diğerine ek süre Bursa'da konkordato dosyalarında kritik gün: Bir şirkete iflas, diğerine ek süre Bursada Bugün Bursa iş dünyasını yakından ilgilendiren iki önemli konkordato dosyasında mahkemeden dikkat çeken kararlar çıktı. Asliye Ticaret Mahkemesi, Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Ltd. Şti. hakkında iflas kararı verirken, Mattaş Endüstriyel Mutfak Sanayi A.Ş.'nin geçici konkordato mühletini iki ay uzattı. Bursa'da konkordato dosyalarında kritik gün: Bir şirkete iflas, diğerine ek süre Bursa'da Tekstil Sektörünü Etkileyen İflas Kararı Endüstriyel Mutfak Sektöründeki Şirkete Ek Süre Verildi Şirketin Geleceği Temmuz Ayındaki Duruşmada Netleşecek Bursa İş Dünyasında Konkordato Dosyaları Yakın Takipte Bursa iş dünyasını yakından ilgilendiren iki önemli konkordato dosyasında mahkemeden dikkat çeken kararlar çıktı. Bursa'da ekonomik zorluklarla mücadele eden şirketlerin konkordato süreçlerine ilişkin yargı kararları iş dünyasında yankı uyandırdı. Aynı mahkemede görülen iki ayrı dosyada birbirinden farklı sonuçlar ortaya çıkarken, bir şirket için iflas süreci resmen başlatıldı, diğer şirkete ise mali yapısını toparlayabilmesi amacıyla ek süre tanındı. Kentte son dönemde artan konkordato başvuruları yakından takip edilirken, Bursa 3. Asliye Ticaret Mahkemesi tarafından verilen kararlar hem alacaklılar hem de ticari çevreler açısından dikkatle değerlendiriliyor. Mahkemenin açıkladığı son kararlar, şirketlerin finansal sürdürülebilirlik süreçlerinde ne kadar kritik bir dönemeçte olduklarını da gözler önüne serdi. Mahkemenin değerlendirdiği dosyalardan birinde faaliyetlerini tekstil ve deri alanında sürdüren Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi hakkında önemli bir karar verildi. Şirket yönetimi tarafından daha önce yapılan konkordato talebi yargı sürecinde beklenen sonucu alamadı. Yapılan incelemeler, mali tablolar ve şirketin ekonomik durumu dikkate alınarak hazırlanan raporlar doğrultusunda konkordato isteminin uygun olmadığı kanaatine varıldı. Mahkeme, şirketin mali yükümlülüklerini karşılayamayacak durumda bulunduğunu değerlendirerek konkordato talebini reddetti. Kararla birlikte daha önce tanınan geçici mühlet uygulaması sona ererken, şirket lehine yürürlükte bulunan koruyucu tedbirler de kaldırıldı. Böylece alacaklıları korumaya yönelik yeni bir hukuki süreç devreye girerken, şirket açısından iflas süreci resmiyet kazandı. Mahkeme kayıtlarına göre iflas kararı 3 Haziran 2026 tarihi itibarıyla yürürlüğe girdi. Sürecin, ilgili mevzuat kapsamında adi tasfiye hükümlerine göre yürütüleceği belirtildi. Bu gelişme özellikle tekstil ve deri sektöründe faaliyet gösteren firmalar tarafından yakından takip edilmeye başlandı. Endüstriyel mutfak ekipmanları alanında faaliyet gösteren Mattaş Endüstriyel Mutfak Sanayi A.Ş. için daha önce verilen geçici konkordato mühleti yeniden değerlendirildi. Mahkeme, şirketin mali durumuna ilişkin sürecin henüz tamamlanmadığı ve mevcut koşulların yeniden incelenmesi gerektiği görüşüyle geçici mühlet süresinin uzatılmasına karar verdi. Böylece şirket, mali yapısını güçlendirebilmek ve borçlarını yeniden yapılandırabilmek adına ek zaman kazanmış oldu. Karar kapsamında konkordato koruması da devam edecek. Şirket hakkında uygulanmakta olan tedbirlerin yürürlükte kalması sayesinde alacaklılar tarafından yeni icra işlemleri başlatılamayacak ve mevcut takipler de konkordato hükümleri çerçevesinde değerlendirilmeyi sürdürecek. Şirketin konkordato talebine ilişkin nihai değerlendirme önümüzdeki süreçte yapılacak duruşmada ele alınacak. Temmuz ayında gerçekleştirilecek duruşmada şirketin mali tabloları, ödeme planları ve konkordato komiserlerinin hazırlayacağı raporlar yeniden incelenecek. Mahkemenin vereceği karar, şirketin faaliyetlerini mevcut yapısıyla sürdürebilip sürdüremeyeceği açısından belirleyici olacak. Bu nedenle hem sektör temsilcileri hem de şirketin ticari ilişkide bulunduğu kurumlar, duruşmadan çıkacak sonucu yakından izliyor. Son kararlarla birlikte Bursa'da aynı dönemde konkordato koruması talep eden iki şirketin yolları ayrılmış oldu. Bir şirket için ekonomik sıkıntılar iflas kararıyla sonuçlanırken, diğer şirkete faaliyetlerini sürdürebilmesi ve finansal dengesini yeniden kurabilmesi amacıyla ek fırsat tanındı. Özellikle son yıllarda artan maliyetler, finansmana erişimde yaşanan güçlükler ve piyasalardaki dalgalanmalar nedeniyle birçok şirket konkordato yoluna başvuruyor. Mahkemelerin verdiği kararlar ise yalnızca ilgili firmaları değil, tedarik zincirinden çalışanlara, alacaklılardan sektör paydaşlarına kadar geniş bir kesimi doğrudan etkiliyor. Bursa'da görülen son iki dosya da konkordato süreçlerinin her şirket için farklı sonuçlar doğurabileceğini ortaya koyarken, iş dünyasının önümüzdeki dönemde açıklanacak yeni mahkeme kararlarına odaklanmasına neden oldu. Diğer Bursa Haberleri - Bölge Haberleri için tıklayın Melisa Döngel yaz sezonunu açtı!</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOS19FeHZ4UlU4WUdxQnk1WjRUWFBIcS1HenVpdmNJd2Jkd1lreWdNNVplbm1hN3RtRlo3cWdtWk5Zb2tfcG5iZ0Y3RGJkbFAwcy1aMXlmVjhrQnA4Nkh5VTNzZ3EyMHZBNkJ5MzI4V2lxQXFIdWRVWUlJWTlZVmZYbkNSa2FXMzZjNHVIUml0WkUydnM0TThOT2tjNlhlZw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>https://www.bursadabugun.com/haber/bursa-da-konkordato-dosyalarinda-kritik-gun-bir-sirkete-iflas-digerine-ek-sure-1926543.html</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Mattaş Endüstriyel Mutfak Sanayi A.Ş | Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Ltd. Şti:118:body | Mattaş Endüstriyel Mutfak Sanayi A.Ş:81:body | Mattaş Endüstriyel Mutfak Sanayi A.Ş:raw_legal | Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi:raw_legal</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr"/>
-      <c r="V34" s="2" t="inlineStr"/>
-      <c r="W34" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>Mattaş Endüstriyel Mutfak Sanayi A.Ş Bursa Türkiye | Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi Bursa Türkiye</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Mattaş Endüstriyel Mutfak | Güzeldağ Tekstil</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Mattaş Endüstriyel Mutfak</t>
+        </is>
+      </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>100.0 | 100.0</t>
+        </is>
+      </c>
       <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="n">
-        <v>65.06</v>
+        <v>204.1</v>
       </c>
       <c r="AB34" s="2" t="n">
         <v>33</v>
@@ -5779,27 +6349,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:39:17</t>
+          <t>2026-06-04 21:00:00</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>usulsüzlük</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay</t>
+          <t>Arz yönlü şoklarda kalkınma bankalarını düşünmek</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber</t>
+          <t>Arz yönlü şoklarda kalkınma bankalarını düşünmek Ekonomim</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -5819,12 +6389,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber</t>
+          <t>Arz yönlü şoklarda kalkınma bankalarını düşünmek Ekonomim</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber Belediye memurunun üzerine 13 yarış atı! Buca soruşturmasında çarpıcı detay | Bankamatik memuru doldurmuşlar A Haber</t>
+          <t>Arz yönlü şoklarda kalkınma bankalarını düşünmek Arz yönlü şoklarda kalkınma bankalarını düşünmek Ekonomim Arz yönlü şoklarda kalkınma bankalarını düşünmek Ekonomim</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5834,7 +6404,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQUlliVENTZ19BSUlYSmtXak83b2xMbkt0N0ZmSkhyVW1fdjZhRy1OU1ZWZ243MmtHNkYxekdDeUtBLXVTb2MzSTVHVzRvdnc2di1xdFM5X2JOa3FyeGtSOW1pdHBNN0FuUEc5TURram8xblI0Uk5jNEQ4eDQ4V0EzOGJRYU5wVXNYWUFPQ3dZV25RLTBtTGxkcDRvNVNKOU02SFozdjhWT2tHc1pwd1RhTFJoWmZDUU1rNFE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.ekonomim.com/kose-yazisi/arz-yonlu-soklarda-kalkinma-bankalarini-dusunmek/897959</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
@@ -5860,7 +6430,7 @@
       <c r="Y35" s="2" t="inlineStr"/>
       <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" s="2" t="n">
-        <v>83.66</v>
+        <v>36.82</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>34</v>
@@ -5869,27 +6439,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:28:00</t>
+          <t>2026-06-04 12:26:00</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>şirketlere operasyon</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı</t>
+          <t>Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı Cumhuriyet</t>
+          <t>Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5899,7 +6469,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>firma, şirket</t>
+          <t>firma</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5909,12 +6479,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Schengen vizesi başvurularında randevuların bot yazılımlarla kapatılıp ticari amaçla satıldığı iddiaları TBMM gündemine taşındı. Ticaret Bakanı Ömer Bolat, gelen şikayetler üzerine Reklam Kurulu'nun 7 şirket hakkında inceleme başlattığını açıkladı. Schengen vizesi başvurularında randevuların bot yazılımlarla kapatılıp ticari amaçla satıldığı iddiaları TBMM gündemine taşındı. Ticaret Bakanı Ömer Bolat, gelen şikayetler üzerine Reklam Kurulu'nun 7 şirket hakkında inceleme başlattığını açıkladı. Schengen vizesi başvurularında randevuların bot yazılımlarla kapatılıp ticari amaçla satıldığı iddiaları TBMM gündemine taşındı. Ticaret Bakanı Ömer Bolat, gelen şikayetler üzerine Reklam Kurulu'nun 7 şirket hakkında inceleme başlattığını açıkladı.</t>
+          <t>Ekonomi yönetiminin tepe ismi Mehmet Şimşek'le birlikte hayatımıza giren o sihirli "rasyonel zemin" kelimesi, nedense aylar geçmesine rağmen sadece dar gelirlinin, emeklinin ve esnafın sırtında ağır bir yüke dönüştü. Son iki günde 6 dev firma daha konkordato ilan etti. Ekonomi yönetiminin tepe ismi Mehmet Şimşek'le birlikte hayatımıza giren o sihirli "rasyonel zemin" kelimesi, nedense aylar geçmesine rağmen sadece dar gelirlinin, emeklinin ve esnafın sırtında ağır bir yüke dönüştü. Son iki günde 6 dev firma daha konkordato ilan etti. Ekonomi yönetiminin tepe ismi Mehmet Şimşek'le birlikte hayatımıza giren o sihirli "rasyonel zemin" kelimesi, nedense aylar geçmesine rağmen sadece dar gelirlinin, emeklinin ve esnafın sırtında ağır bir yüke dönüştü. Son iki günde 6 dev firma daha konkordato ilan etti. TÜİK Mayıs 2026 enflasyon oranını açıkladı Jakirovic Hull City'e Premier Lig'de kalmak için gereken transfer bütçesini açıkladı Survivor’da bireysel dönem başladı: Ramazan geri dönecek mi? ilk eleme adayı kim oldu? Meteoroloji açıkladı: Fırtına kopacak gök gürültülü sağanak yağış illeri saracak Haziran ayı kira artış oranı belli oldu Anasayfa Ekonomi Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti 04 Haziran 2026 15:26 Son Güncelleme: 04 Haziran 2026 15:41 Haberi Paylaş Yeniçağ'ı haber kaynağınız olarak eklemek için tıklayın! Mercek: Berna Can Ekonomi yönetiminin tepe ismi Mehmet Şimşek'le birlikte hayatımıza giren o sihirli "rasyonel zemin" kelimesi, nedense aylar geçmesine rağmen sadece dar gelirlinin, emeklinin ve esnafın sırtında ağır bir yüke dönüştü. Son iki günde 6 dev firma daha konkordato ilan etti. Ekonomi mizin her geçen gün daha da "şahlandığı" şu günlerde, şirket ler cephesinden gelen haberler AK Parti ve ekonomi yönetiminin sunduğu pembe tablolarla pek uyuşmuyor. Yüksek faiz, nakit akışındaki bozulmalar ve krediye ulaşmadaki zorluklar, köklü firmaları birer birer iflasın eşiğine sürüklüyor. Sadece son iki gün içerisinde, aralarında borsada işlem gören devlerin de bulunduğu 6 firma daha nefes alabilmek için konkordato kervanına katıldı. TÜRK İ̇LAÇ VE BATTAL HOLDİNG'DEN VEDA Borsa İstanbul'da işlem gören ve yatırımcıların yakından takip ettiği Türk İlaç ve Serum Sanayi A.Ş., yaşadığı mali darboğazı aşamayarak mahkemenin yolunu tuttu. KAP'a (Kamuyu Aydınlatma Platformu) yapılan resmi açıklamaya göre, şirket yönetim kurulu başkanı Mehmet Berat Battal ve şirketin önemli ortaklarından Battal Holding A.Ş. ile birlikte Ankara 3. Asliye Ticaret Mahkemesi'ne başvuruda bulunuldu. Mahkeme, hem Türk İlaç hem de Battal Holding için 3 aylık geçici mühlet kararı verdi. Kredi geri ödemelerinde yaşanan kriz ve peş peşe yazılan karşılıksız çekler, "uçan ekonomimizin" reel sektöre yansıyan acı faturalarından sadece biri olarak kayıtlara geçti. Türk İlaç Genel Müdürü konkordato'dan önce 444 milyon liralık hisse satışı yaptı mı? Ekonomi MARKETLERDEN MUTFAKLARA UZANAN KRİZ DALGASI Kriz sadece sağlık ve sanayi devlerini değil, perakende ve lojistik sektörünü de vurmaya devam ediyor. Giresun başta olmak üzere bölgesel çapta faaliyet gösteren Apak Nakliyat İnşaat ve bünyesindeki Espiye Semt Marketleri için de tehlike çanları çaldı. Aynı şekilde mutfak eşyaları sektörünün bilinen isimlerinden Qlux İdeas da mali yükümlülüklerini yerine getiremeyerek mahkemeden koruma talep eden firmalar arasına ismini yazdırdı. Mehmet Şimşek'e göre 23 çeyrektir büyüyoruz Ekonomi TEKSTİL VE DERİDE ÇÖKÜŞ DERİNLEŞİYOR Taksitli alışverişin bir dönem parlayan yıldızlarından olan ve 34 yıllık geçmişiyle bilinen Talipsan cephesinden de benzer bir haber geldi. Talipsan Deri Konfeksiyon Gıda ve Hediyelik Eşya Sanayi, artan maliyetler karşısında ayakta duramayarak konkordato ilan etmek zorunda kaldı. Konya merkezli olup 4 ilde 19 mağazasıyla faaliyet gösteren şirket için Bakırköy 3. Asliye Ticaret Mahkemesi tarafından 3 aylık geçici mühlet verildiği ve komiser heyeti atandığı resmi ilan portallarında yayımlandı. ŞİMŞEK'TEN PEMBE TABLO: SOKAKTA HİSSEDİLMEYEN 1.6 TRİLYON DOLAR MASALI Türkiye ekonomisinin 2026 yılı birinci çeyrek büyüme faturası kesildi ve sokağın yangını bir kez daha resmi verilere yansıdı. Beklentilerin gerisinde kalarak ancak yüzde 2,5 büyüyebilen, çeyreklik bazda ise yüzde 0,1 ile adeta yerinde sayan ekonomi, dar boğazın derinleştiğini kanıtlıyor. Ancak vatandaş iflas dalgaları, eriyen maaşlar ve hayat pahalılığı ile boğuşurken; Hazine ve Maliye Bakanı Mehmet Şimşek 'in "Şoklara rağmen 23 çeyrektir kesintisiz büyüyoruz" şeklindeki açıklaması, ekonomi yönetiminin sokağın gerçekliğinden ne kadar koptuğunu bir kez daha gözler önüne seriyor. TARIMDA BAZ ETKİLİ SANAL BAHAR Şimşek'in iyimser tablosuna dayanak yaptığı bir diğer kalem ise tarım sektöründeki yüzde 4,6'lık artış. Ancak burada da oldukça trajikomik bir gerçek gizli: Bu artış, büyük bir tarımsal kalkınmanın değil, bizzat Şimşek'in de itiraf ettiği gibi geçen yıl yaşanan don ve kuraklık nedeniyle dibe vuran üretimin yarattığı "baz etkisinin" doğal bir sonucu. Çiftçinin mazot, gübre ve tohum maliyetleri altında ezildiği bir dönemde, dipten gelen zorunlu ve ufak bir sıçramayı büyümeyi destekleyecek temel bir unsur olarak pazarlamak, tarımdaki çöküşü makyajlamaktan öteye geçemiyor. Kaynak: Haber Merkezi Etiketler ekonomi şi</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı Schengen vizesinde randevu satan şirketlere soruşturma: 7 firma mercek altına alındı Cumhuriyet Schengen vizesi başvurularında randevuların bot yazılımlarla kapatılıp ticari amaçla satıldığı iddiaları TBMM gündemine taşındı. Ticaret Bakanı Ömer Bolat, gelen şikayetler üzerine Reklam Kurulu'nun 7 şirket hakkında inceleme başlattığını açıkladı.</t>
+          <t>Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti Yeniçağ Gazetesi Ekonomi yönetiminin tepe ismi Mehmet Şimşek'le birlikte hayatımıza giren o sihirli "rasyonel zemin" kelimesi, nedense aylar geçmesine rağmen sadece dar gelirlinin, emeklinin ve esnafın sırtında ağır bir yüke dönüştü. Son iki günde 6 dev firma daha konkordato ilan etti. TÜİK Mayıs 2026 enflasyon oranını açıkladı Jakirovic Hull City'e Premier Lig'de kalmak için gereken transfer bütçesini açıkladı Survivor’da bireysel dönem başladı: Ramazan geri dönecek mi? ilk eleme adayı kim oldu? Meteoroloji açıkladı: Fırtına kopacak gök gürültülü sağanak yağış illeri saracak Haziran ayı kira artış oranı belli oldu Anasayfa Ekonomi Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti Mehmet Şimşek'in 'Rasyonel zemin' i : Son iki günde 6 firma konkordato ilan etti 04 Haziran 2026 15:26 Son Güncelleme: 04 Haziran 2026 15:41 Haberi P</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -5924,7 +6494,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.cumhuriyet.com.tr/ekonomi/schengen-vizesinde-randevu-satan-sirketlere-sorusturma-7-firma-mercek-altina-alindi-2508910</t>
+          <t>https://www.yenicaggazetesi.com/mehmet-simsekin-rasyonel-zemin-i-son-iki-gunde-6-firma-konkordato-ilan-etti-1036993h.htm</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
@@ -5932,25 +6502,49 @@
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Battal Holding A.Ş</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>Battal Holding A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr"/>
-      <c r="V36" s="2" t="inlineStr"/>
-      <c r="W36" s="2" t="inlineStr"/>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>Battal Holding A.Ş Türkiye</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>BATTAL Holding A.Ş</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>BATTAL Holding A.Ş</t>
+        </is>
+      </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z36" s="2" t="inlineStr"/>
       <c r="AA36" s="2" t="n">
-        <v>89.20999999999999</v>
+        <v>171.25</v>
       </c>
       <c r="AB36" s="2" t="n">
         <v>35</v>
@@ -5959,27 +6553,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:00</t>
+          <t>2026-06-04 14:57:00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın</t>
+          <t>BİST’te işlem gören şirketin sahibinin oğlu payını sıfırladı, 22 gün sonra konkordato ilan edildi!</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber</t>
+          <t>BİST’te işlem gören şirketin sahibinin oğlu payını sıfırladı, 22 gün sonra konkordato ilan edildi! Elips Haber</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5989,90 +6583,62 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>fabrika, organize sanayi, sanayi</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber</t>
+          <t>Borsa İstanbul'da işlem gören Türk İlaç'ın konkordato ilan etmesinden 22 gün önce, Genel Müdür Yunus Emre Battal'ın 444 milyon liralık satışla şirketteki payını sıfırladığı ortaya çıktı. Uzmanlar, kamuya açıklanmamış bilgilerle menfaat sağlandığı gerekçesiyle Sermaye Piyasası Kanunu'nun "bilgi suistimali" maddesinin işletilebileceğini belirtiyor. Borsa İstanbul'da işlem gören Türk İlaç'ın konkordato ilan etmesinden 22 gün önce, Genel Müdür Yunus Emre Battal'ın 444 milyon liralık satışla şirketteki payını sıfırladığı ortaya çıktı. Uzmanlar, kamuya açıklanmamış bilgilerle menfaat sağlandığı gerekçesiyle Sermaye Piyasası Kanunu'nun "bilgi suistimali" maddesinin işletilebileceğini belirtiyor. Borsa İstanbul'da işlem gören Türk İlaç'ın konkordato ilan etmesinden 22 gün önce, Genel Müdür Yunus Emre Battal'ın 444 milyon liralık satışla şirketteki payını sıfırladığı ortaya çıktı. Uzmanlar, kamuya açıklanmamış bilgilerle menfaat sağlandığı gerekçesiyle Sermaye Piyasası Kanunu'nun "bilgi suistimali" maddesinin işletilebileceğini belirtiyor. Gündem BİST’te işlem gören şirketin sahibinin oğlu payını sıfırladı, 22 gün sonra konkordato ilan edildi! Borsa İstanbul'da işlem gören Türk İlaç'ın konkordato ilan etmesinden 22 gün önce, Genel Müdür Yunus Emre Battal'ın 444 milyon liralık satışla şirketteki payını sıfırladığı ortaya çıktı. Uzmanlar, kamuya açıklanmamış bilgilerle menfaat sağlandığı gerekçesiyle Sermaye Piyasası Kanunu'nun "bilgi suistimali" maddesinin işletilebileceğini belirtiyor. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 04.06.2026 - 17:57 Okunma Süresi: 2 Dk Özgür Özel ve Kemal Kılıçdaroğlu'nun avukatları görüşecek İçeriği Görüntüle Borsa İstanbul'da (BİST) işlem gören firmaların mali sıkıntıları ve borç yapılandırma süreçleri piyasaların gündemindeki yerini koruyor. Kontrolmatik'in tahvil borçlarını ödeyememesinin ardından, 2021 yılında halka açılan Türk İlaç ve Serum Sanayi A.Ş. de konkordato talebinde bulundu. Habertürk'ten Rahim Ak'ın haberine göre, konkordato ilanı öncesinde şirket hisselerinde yaşanan sert düşüşler dikkat çekerken, Türk İlaç hisselerinin son bir yıl içinde %88 değer kaybederek 20 lira seviyesinden 2,5 liraya gerilediği ve şirketin Yakın İzleme Pazarı'na alındığı kaydedildi. Konkordato öncesi milyarlık pay sıfırlandı Türk İlaç bünyesinde yaşanan en kritik gelişme ise resmi konkordato ilanından 22 gün önce gerçekleşti. Şirket sahibinin oğlu ve aynı zamanda Genel Müdürlük görevini yürüten Yunus Emre Battal, şirketin %11,59’una denk gelen hisselerini yaklaşık 444 milyon lira bedelle satarak payını sıfırladı. Bu işlemin ardından aile ve bağlı holdingin şirketteki toplam hakim ortaklık payı %37 civarından %26 seviyesine geriledi. Aynı dönemde Pordüs Portföy'ün de 14 Mayıs 2026'da yaklaşık 75-80 milyon lira değerinde satış yaparak şirketteki payını %12'den %9,5'e düşürdüğü görüldü. Bilgi suistimali iddiası gündemde Şirket bilgilerine doğrudan erişimi bulunan genel müdürün gerçekleştirdiği bu zamanlamalı satış, piyasada "insider trading" (bilgi suistimali) tartışmalarını beraberinde getirdi. Hukuk ve finans uzmanları, Yunus Emre Battal’ın konumu itibarıyla 6362 sayılı Sermaye Piyasası Kanunu’nun 106. maddesi kapsamında değerlendirilebileceğini ifade ediyor. Sermaye Piyasası Kanunu’nun ilgili maddesi; ihraççıların yöneticileri veya pay sahiplerinin, sermaye piyasası araçlarının değerini etkileyecek ve henüz kamuya duyurulmamış bilgilere dayanarak alım-satım yapmasını ve bu yolla menfaat temin etmesini suç sayıyor. Maddede, bu suçu işleyenlerin üç yıldan beş yıla kadar hapis veya adli para cezası ile cezalandırılacağı öngörülüyor. Kaynak: Habertürk Bunlar da ilgini</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber Bitlis’te Organize Sanayi Bölgesi’nde Fabrikada Yangın Bitlis Haber</t>
+          <t>BİST’te işlem gören şirketin sahibinin oğlu payını sıfırladı, 22 gün sonra konkordato ilan edildi! BİST’te işlem gören şirketin sahibinin oğlu payını sıfırladı, 22 gün sonra konkordato ilan edildi! Elips Haber Borsa İstanbul'da işlem gören Türk İlaç'ın konkordato ilan etmesinden 22 gün önce, Genel Müdür Yunus Emre Battal'ın 444 milyon liralık satışla şirketteki payını sıfırladığı ortaya çıktı. Uzmanlar, kamuya açıklanmamış bilgilerle menfaat sağlandığı gerekçesiyle Sermaye Piyasası Kanunu'nun "bilgi suistimali" maddesinin işletilebileceğini belirtiyor. Gündem BİST’te işlem gören şirketin sahibinin oğlu payını sıfırladı, 22 gün sonra konkordato ilan edildi!</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxORHRmYXNUalRQUXNLOHhTS2xRRm02MmVBZGZ6QnpSN3g0TGRJRGo2cXZFaUtmVjFESUgtZVc3S3VseHR2ZEdjUmg3Wm54MzhsMVJEQW1NT2NwN25tcURsYXByRUtZWmNyTlZKSkRKZDFWX09MZThDcl9yQWwtQnhEUFBkcEJkWG9ENlHSAY8BQVVfeXFMUGMycjBkQVY5a0lhb2k0a19oMWoyTWN0YTB3T2I4Y3U3N3JmdGVXaHRTN3BJMkVsdUZGTEp4V21lMFFRZUx1LWxuUXBYT0k1VGVTb3pESUUyVHM1U0xZY2g5RlVfcTA2UUltNXVlWmdWc3VvNXkyMGR2SGs0VVVMNDJjTlNPQ1FpSE9ybkh6ZVU?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.elipshaber.com/bistte-islem-goren-sirketin-sahibinin-oglu-payini-sifirladi-22-gun-sonra-konkordato-ilan-edildi</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Bitlis</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>te Organize Sanayi</t>
-        </is>
-      </c>
+      <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>Organize Sanayi</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>Organize Sanayi:292:body+summary+title</t>
-        </is>
-      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>Organize Sanayi te Organize Sanayi Bitlis Türkiye</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Bitlis Organize Sanayi Bölgesi</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>Bitlis Organize Sanayi Bölgesi</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y37" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
       <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="n">
-        <v>190.42</v>
+        <v>117.5</v>
       </c>
       <c r="AB37" s="2" t="n">
         <v>36</v>
@@ -6081,27 +6647,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 22:06:29</t>
+          <t>2026-06-04 16:41:00</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi.</t>
+          <t>Maden ocağında yangın faciası: Direnişteki işçilerin can güvenliği hiçe sayıldı!</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Vietnam.vn</t>
+          <t>Maden ocağında yangın faciası: Direnişteki işçilerin can güvenliği hiçe sayıldı! Haber Hürriyeti</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -6111,36 +6677,40 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>maden</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Vietnam.vn</t>
+          <t>Edirne’nin Uzunköprü ilçesinde, ödenmeyen hakları için eylem yapan işçilerin direndiği Özşen Madencilik’e ait kömür ocağında yangın çıktı. Söndürme ekipmanının ve suyun bulunmadığı madende bir kepçe operatörü alevlerin arasında kalırken, işçiler yangına bakımsız bırakılan makinelerin yol açtığını belirterek ihmallere isyan etti. Edirne’nin Uzunköprü ilçesinde, ödenmeyen hakları için eylem yapan işçilerin direndiği Özşen Madencilik’e ait kömür ocağında yangın çıktı. Söndürme ekipmanının... Edirne’nin Uzunköprü ilçesinde, ödenmeyen hakları için eylem yapan işçilerin direndiği Özşen Madencilik’e ait kömür ocağında yangın çıktı. Söndürme ekipmanının ve suyun bulunmadığı madende bir kepçe operatörü alevlerin arasında kalırken, işçiler yangına bakımsız bırakılan makinelerin yol açtığını belirterek ihmallere isyan etti. haberhurriyeti.com / HABER MERKEZİ Edirne’nin Uzunköprü ilçesinde, haklarını alamadıkları için direnişte olan maden işçilerinin eylem yaptığı Özşen Madencilik’e ait kömür ocağında yangın çıktı. Kiremitçiler Grup bünyesinde faaliyet gösteren ve konkordato ilanıyla işçileri mağdur eden işletmede çıkan yangın, ihmaller zincirini bir kez daha gözler önüne serdi. Yangın esnasında ocakta ne su ne de itfaiye bulunması, facianın boyutunu artırdı. BAKIMSIZLIK VE EKİPMAN EKSİKLİĞİ YANGINA DAVETİYE ÇIKARDI Yangının çıkış nedeni henüz resmi olarak netleşmese de ocakta çalışan işçiler içerideki acı tabloyu anlattı. İşçi sayısının kasıtlı olarak eksik tutulduğunu belirten işçiler, personelin yetersiz olması sebebiyle makinelerin periyodik bakımlarının yapılmadığını vurguladı. Bakımsızlıktan dolayı aşırı ısınan makinelerin yangına yol açtığını ifade eden madenciler, ocakta ne bir yangın söndürme ekipmanının ne de müdahale edecek suyun bulunduğunu dile getirdi. Bu haberi kaçırmayın Eski eşinin yaşadığı evde yangın çıkardı Devamını Oku KEPÇE OPERATÖRÜ ALEVLERİN ORTASINDA KALDI Yangın esnasında maden sahasında bulunan bir kepçe operatörü, alevlerin bir anda büyümesiyle adeta ölümle burun buruna geldi. Ekipman yetersizliği nedeniyle söndürme çalışmalarının yapılamadığı ocağın önünde direnen işçiler, yaşanan duruma isyan etti. Maden işçileri, "Kapı önünde hakkımız için direniş varken, içerideki manzara tam bir felaket. Burada bir işçi arkadaşımız canından olabilirdi" diyerek tepkilerini dile getirdi. SENDİKADAN SERT TEPKİ: BİR CANIMIZ VAR, ONU DA KÂR HIRSINIZA KURBAN ETMEYECEĞİZ Mağduriyetlerin ardından Bağımsız Maden İş Sendikası'nda örgütlenerek direniş başlatan işçilere sendikadan tam destek geldi. Kömür madeninde alınmayan iş güvenliği önlemlerinin ve kötü çalışma koşullarının doğrudan işçi yaşamını tehdit ettiğini vurgulayan sendika, sert bir açıklama yayınladı: "Bir canımız var bize kalan, onu da kâr hırsınıza kurban etmemek için bütün kavgamız!" HEM TAZMİNATSIZ İŞTEN ÇIKARMA TEHDİDİ HEM İHMALKARLIK Özşen Madencilik’te sular uzun süredir durulmuyor. Ücretleri ödenmeyen ve şirketin konkordato ilanı sonrası hak gaspına uğrayan işçilerden, sendikalı olan 21'i daha önce işten çıkarılmıştı. İçeride çalışmaya devam eden diğer işçilerin ise sürekli olarak tazminatsız işten çıkarılmakla tehdit edildiği öğrenildi. İşçiler hem ekonomik hakları hem de can güvenlikleri için mücadele etmeye devam edeceklerini belirtiyor. Bu haberi kaçırmayın Özgür Özel: Erdoğan ‘ödedik’ dedi, madencilerin hesabına tek kuruş yatmadı! Devamını Oku Maden ocağında yangın faciası: Direnişteki işçilerin can güvenliği hiçe sayıldı! BAKIMSIZLIK VE EKİPMAN EKSİKLİĞİ YANGINA DAVETİYE ÇIKARDI KEPÇE OPERATÖRÜ ALEVLERİN ORTASINDA KALDI SENDİKADAN SERT TEPKİ: BİR CANIMIZ VAR, ONU DA KÂR HIRSINIZA KURBAN ETMEYECEĞİZ HEM TAZMİNATSIZ İŞTEN ÇIKARMA TEHDİDİ HEM İHMALKARLIK Edirne’nin Uzunköprü ilçesinde, ödenmeyen hakları için eylem yapan işçilerin direndiği Özşen Madencilik’e ait kömür ocağında yangın çıktı. Söndürme ekipmanının ve suyun bulunmadığı madende bir kepçe operatörü alevlerin arasında kalırken, işçiler yangına bakımsız bırakılan makinelerin yol açtığını belirterek ihmallere isyan etti. haberhurriyeti.com / HABER MERKEZİ Edirne’nin Uzunköprü ilçesinde, haklarını alamadıkları için direnişte olan maden işçilerinin eylem yaptığı Özşen Madencilik’e ait kömür ocağında yangın çıktı. Kiremitçiler Grup bünyesinde faaliyet gösteren ve konkordato ilanıyla işçileri mağdur eden işletmede çıkan yangın, ihmaller zincirini bir kez daha gözler önüne serdi. Yangın esnasında ocakta ne su ne de itfaiye bulunması, facianın boyutunu artırdı. Yangının çıkış nedeni henüz resmi olarak netleşmese de ocakta çalışan işçiler içerideki acı tabloyu anlattı. İşçi sayısının kasıtlı olarak eksik tutulduğunu belirten işçiler, personelin yetersiz olması sebebiyle makinelerin periyodik bakımlarının yapılmadığını vurguladı. Bakımsızlıktan dolayı aşırı ısınan makinelerin yangına yol açtığını ifade eden madenciler, ocakta ne bir yangın söndürme ekipmanının ne de müdahale edecek suyun bulunduğunu dile getirdi. Yangın esnasında maden sahasında bulunan bir kepçe operatörü, alevlerin bir anda büyümesiyle adeta ölümle burun buruna geldi. Ekipman yetersizliği nedeniyle söndürme çalışmalarının yapılamadığı ocağın önünde direnen işçiler, yaşanan duruma isyan etti. Maden işçileri, "Kapı önünde hakkımız için direniş varken, içerideki manzara tam bir felaket. Burada bir işçi arkadaşımız canından olabilirdi" diyerek tepkilerini dile getirdi. Mağduriyetlerin ardından Bağımsız Maden İş Sendikası'nda örgütlenerek direniş başlatan işçilere sendikadan tam destek geldi. Kömür madeninde alınmayan iş güvenliği önlemlerinin ve kötü çalışma koşullarının doğrudan işçi yaşamını tehdit ettiğini vurgulayan sendika, sert bir açıklama yayınladı: Özşen Madencilik’te sular uzun süredir durulmuyor. Ücretleri ödenmeyen ve şirketin konkordato ilanı sonrası hak gaspına uğrayan işçilerden, sendikalı olan 21'i daha önce işten çıkarılmıştı. İçeride çalışmaya devam eden diğer işçilerin ise sürekli olarak tazminatsız işten çıkarılmakla tehdit edildiği öğrenildi. İşçiler hem ekonomik hakları hem de can güvenlikleri için mücadele etmeye devam edeceklerini belirtiyor. 04 Haz 2026 - 19:41 - Gündem Yazdır Yorum yazarak Haber Hürriyeti Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yorumlardan Haber Hürriyeti hiçbir şekil</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi. Vietnam.vn Kaliforniya'daki banka rehine krizi, adeta bir filmden fırlamış gibi.</t>
+          <t>Maden ocağında yangın faciası: Direnişteki işçilerin can güvenliği hiçe sayıldı! Maden ocağında yangın faciası: Direnişteki işçilerin can güvenliği hiçe sayıldı! Haber Hürriyeti Edirne’nin Uzunköprü ilçesinde, ödenmeyen hakları için eylem yapan işçilerin direndiği Özşen Madencilik’e ait kömür ocağında yangın çıktı. Söndürme ekipmanının ve suyun bulunmadığı madende bir kepçe operatörü alevlerin arasında kalırken, işçiler yangına bakımsız bırakılan makinelerin yol açtığını belirterek ihmallere isyan etti. haberhurriyeti.com / HABER MERKEZİ Edirne’nin Uzunköprü ilçesinde, haklarını alamadıkları için direnişte olan maden işçilerinin eylem yaptığı Özşen Madencilik’e ait kömür ocağında yangın çıktı. Kiremitçiler Grup bünyesinde faaliyet gösteren ve konkordato ilanıyla işçileri mağdur eden işletmede çıkan yangın, ihmaller zincirini bir kez daha gözler önüne serdi. Yangın esnasında ocakta ne su ne de itfaiye bulunması, facianın boyutunu artırdı. BAKIMSIZLIK VE EKİPMAN EKSİKLİĞİ YANGINA DAVETİYE ÇIKARDI Yangının çıkış nedeni henüz resmi olarak netleşmese de ocakta çalışan işçiler içerideki acı tabloyu anlattı. İşçi sayısının kasıtlı olarak eksik tutulduğunu belirten işçiler, personelin yetersiz olması sebebiyle makinelerin periyodik bakımlarının yapılmadığını vurguladı. Bakımsızlıktan dolayı aşırı ısınan makinelerin yangına yol açtığını ifade eden madenciler, ocakta ne bir yangın söndürme ekipmanının ne de müdahale edecek suyun bulunduğunu dile getirdi. Bu haberi kaçırmayın Eski eşinin yaşadığı evde yangın çıkardı Devamını Oku KEPÇE OPERATÖRÜ ALEVLERİN ORTASINDA KALDI Yangın esnasında maden sahasında bulunan bir kepçe operatörü, alevlerin bir anda büyümesiyle adeta ölümle burun buruna geldi. Ekipman yetersizliği nedeniyle söndürme çalışmalarının yapılamadığı ocağın önünde direnen işçiler, yaşanan duruma isyan etti. Maden işçileri, "Kapı önünde hakkımız için direniş varken, içerideki manzara tam bir felaket. Burada bir işçi arkadaşımız canından olabilirdi" diyerek tepkilerini dile getirdi. SENDİKADAN SERT TEPKİ: BİR CANIMIZ VAR, ONU DA KÂR HIRSINIZA KURBAN ETMEYECEĞİZ Mağduriyetlerin ardından Bağımsız Maden İş Sendikası'nda örgütlenerek direniş başlatan işçilere sendikadan tam destek geldi. Kömür madeninde alınmayan iş güvenliği önlemlerinin ve kötü çalışma koşullarının doğrudan işçi yaşamını tehdit ettiğini vurgulayan sendika, sert bir açıklama yayınladı: "Bir canımız var bize kalan, onu da kâr hırsınıza kurban etmemek için bütün kavgamız!" HEM TAZMİNATSIZ İŞTEN ÇIKARMA TEHDİDİ HEM İHMALKARLIK Özşen Madencilik’te sular uzun süredir durulmuyor. Ücretleri ödenmeyen ve şirketin konkordato ilanı sonrası hak gaspına uğrayan işçilerden, sendikalı olan 21'i daha önce işten çıkarılmıştı. İçeride çalışmaya devam eden diğer işçilerin ise sürekli olarak tazminatsız işten çıkarılmakla tehdit edildiği öğrenildi. Devamını Oku Maden ocağında yangın faciası: Direnişteki işçilerin can güvenliği hiçe sayıldı! BAKIMSIZLIK VE EKİPMAN EKSİKLİĞİ YANGINA DAVETİYE ÇIKARDI KEPÇE OPERATÖRÜ ALEVLERİN ORTASINDA KALDI SENDİKADAN SERT TEPKİ: BİR CANIMIZ VAR, ONU DA KÂR HIRSINIZA KURBAN ETMEYECEĞİZ HEM TAZMİNATSIZ İŞTEN ÇIKARMA TEHDİDİ HEM İHMALKARLIK Edirne’nin Uzunköprü ilçesinde, ödenmeyen hakları için eylem yapan işçilerin direndiği Özşen Madencilik’e ait kömür ocağında yangın çıktı. Yangının çıkış nedeni henüz resmi olarak netleşmese de ocakta çalışan işçiler içerideki acı tabloyu anlattı. Yangın esnasında maden sahasında bulunan bir kepçe operatörü, alevlerin bir anda büyümesiyle adeta ölümle burun buruna geldi. Mağduriyetlerin ardından Bağımsız Maden İş Sendikası'nda örgütlenerek direniş başlatan işçilere sendikadan tam destek geldi. Kömür madeninde alınmayan iş güvenliği önlemlerinin ve kötü çalışma koşullarının doğrudan işçi yaşamını tehdit ettiğini vurgulayan sendika, sert bir açıklama yayınladı: Özşen Madencilik’te sular uzun süredir durulmuyor.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBENG9hNkpudTZwY2E2MGRhQWRucXFnSWF5VzViQUo0Z3FpZ0F4aVRnR0hmc1ZUWG1wdG5QMy1wVnZELWpXUFdDdXdkaS1qNlVkc29jQmlWaThMN0ViMWFiM0FlTVM5UlB1VnlHMmNnazZvNkh5UFFTOGVKOXFVdw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>https://www.haberhurriyeti.com/haber/28113893/maden-ocaginda-yangin-faciasi-direnisteki-iscilerin-can-guvenligi-hice-sayildi</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Edirne</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Uzunköprü</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -6148,7 +6718,7 @@
       <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr"/>
@@ -6162,7 +6732,7 @@
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="n">
-        <v>53.3</v>
+        <v>123</v>
       </c>
       <c r="AB38" s="2" t="n">
         <v>37</v>
@@ -6171,27 +6741,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:32:00</t>
+          <t>2026-06-05 06:33:34</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>banka dolandırıcılığı</t>
+          <t>usulsüzlük</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek</t>
+          <t>Buca Belediyesi'nde skandal operasyon: Rüşvet, usulsüzlük ve 'bankamatikçi' vurgunu ortaya çıktı</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek sonhaber.eu</t>
+          <t>Buca Belediyesi'nde skandal operasyon: Rüşvet, usulsüzlük ve 'bankamatikçi' vurgunu ortaya çıktı Haberhergün</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6211,48 +6781,80 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Belçika’da dolandırıcıların hedefi haline gelen ve phishing (oltalama) mağduru olan kişiler için emsal bir karar alındı. Antwerp Mahkemesi, phishing dolandırıcılığına uğrayan müşterilerin zararlarının bankalar tarafından gecikmeden karşılanması gerektiğine hükmetti. Belçika’nın Antwerp kentinde hızlı yargılama usulüyle görülen davada mahkeme, phishing (oltalama) dolandırıcılığı mağdurlarının zararlarının bankalar tarafından öncelikle karşılanması gerektiğine karar verdi. Karar, yaklaşık 50 bin euro dolandırılan yaşlı bir çiftin açtığı dava sonucunda alındı. Banka’dan ağır ihmal değerlendirmesi Olayda çift, kendisini banka çalışanı olarak tanıtan bir dolandırıcının yönlendirmesiyle Portekiz’deki bir hesaba para transferi yaptı. Banka ise müşterilerin parayı kendi rızalarıyla göndermesini “ağır ihmal” olarak değerlendirerek zararı karşılamayı reddetti. Mahkeme bankanın bu yaklaşımını kabul etmedi. Karara göre bankalar, phishing mağdurlarının zararını derhal ödemekle yükümlü olacak. Banka, müşterinin ağır ihmalde bulunduğunu düşünüyorsa bunu kanıtlamak için kendisi tekrar mahkemeye başvurmak ve bunu kanıtlamak zorunda olacak. Phishing (oltalama) nedir? Phishing, dolandırıcıların banka, resmi kurum veya güvenilir bir kuruluş gibi davranarak kişilerin şifre, banka bilgisi veya güvenlik kodlarını ele geçirmeye çalıştığı bir siber dolandırıcılık yöntemidir. Bankacılık sektöründe çığır açan karar Bankacılık hukuku uzmanı Avukat Geert Lenssens, kararı “çığır açıcı bir emsal” olarak değerlendirdi. Lenssens’e göre bankalar bugüne kadar çoğu dosyada müşterinin ağır hata yaptığını varsayarak ödeme yapmaktan kaçınıyordu. Mahkeme ise ispat yükünün bankada olduğuna hükmetti. Uzman avukat, phishing vakalarında ağır ihmalin oldukça istisnai bir durum olduğunu belirterek, dolandırıcıların yönlendirmesiyle güvenlik kodu</t>
+          <t>İzmir Buca Belediyesi'nde rüşvet, imar usulsüzlüğü, şahsi harcamalar için kamu kaynaklarının kullanımı ve 'bankamatik personeli' gibi skandalları ortaya çıkaran operasyonda 54 kişi adliyeye sevk edildi. İzmir Buca Belediyesi'nde rüşvet, imar usulsüzlüğü, şahsi harcamalar için kamu kaynaklarının kullanımı ve 'bankamatik personeli' gibi skandalları ortaya çıkaran operasyonda 54 kişi adliyeye sevk edildi. İzmir Buca Belediyesi'nde rüşvet, imar usulsüzlüğü, şahsi harcamalar için kamu kaynaklarının kullanımı ve 'bankamatik personeli' gibi skandalları ortaya çıkaran operasyonda 54 kişi adliyeye sevk edildi. GÜNDEM Yayınlanma : 05 Haziran 2026 09:33 Düzenleme : 05 Haziran 2026 09:33 Buca Belediyesi'nde skandal operasyon: Rüşvet, usulsüzlük ve 'bankamatikçi' vurgunu ortaya çıktı Paylaş Paylaş Paylaş A A Sesli Dinle İzmir Buca Belediyesi'nde rüşvet, imar usulsüzlüğü, şahsi harcamalar için kamu kaynaklarının kullanımı ve 'bankamatik personeli' gibi skandalları ortaya çıkaran operasyonda 54 kişi adliyeye sevk edildi. İzmir Cumhuriyet Başsavcılığı'nın koordine ettiği geniş çaplı soruşturma, Buca Belediyesi'nin derinliklerine uzanan yolsuzluk ağını gün yüzüne çıkardı. İl Emniyet Müdürlüğü Mali Suçlarla Mücadele Şubesi'nin titiz çalışmaları sonucunda, belediye imkanlarının bir suç örgütü tarafından nasıl kullanıldığına dair çarpıcı detaylar ortaya konuldu. RÜŞVET, İMAR USULSÜZLÜKLERİ VE ŞAHSİ HARCAMALAR Soruşturmada elde edilen deliller, belediye yöneticileri ve çalışanlarının, inşaat faaliyetlerinde bulunan müteahhitlerle işbirliği yaparak rüşvet aldığını ve imar süreçlerinde ciddi usulsüzlüklere imza attığını gösteriyor. Daha da vahimi, belediyeye ait kredi kartları, banka hesapları ve araçların, tamamen şahsi harcamalar ve konaklamalar için kullanıldığı tespit edildi. Bu durum, kamu kaynaklarının nasıl hoyratça çarçur edildiğini gözler önüne seriyor. 'BANKAMATİK PERSONELİ' VE BASINA DARP Operasyonun bir diğer boyutu ise, fiilen çalışmadığı halde maaş ve çeşitli ödemeler alan 'bankamatik personeli'nin varlığı. Bu kişilere yapılan ödemeler, belediye bütçesi üzerinde ek bir yük oluştururken, aynı zamanda gazetecilerin ve sosyal medya kullanıcılarının, belediye hakkındaki haberleri veya paylaşımları nedeniyle darp edilmesi de soruşturmanın kapsamını genişletiyor. 1 Haziran'da İzmir merkezli 6 ilde eş zamanlı düzenlenen operasyonlarda, aralarında Buca Belediye Başkanı Görkem Duman ve eski başkan Erhan Kılıç'ın da bulunduğu 54 kişi gözaltına alındı. Emniyetteki işlemlerinin ardından bu şüpheliler adliyeye sevk edildi. #Bucabelediyesi #Yolsuzlukoperasyonu HABER MERKEZİ Bakmadan Geçme Buca'da deprem: Belediye Başkanı Görkem Duman ve eski başkan dahil 62 kişi yolsuzluk operasyonunda gözaltında Boğaziçi A.Ş. ihalelerinde şok yolsuzluk operasyonu: 57 gözaltı! Antalya Büyükşehir Belediyesi'nde şok gelişme: 25 kişi gözaltında Tepebaşı Belediyesi'nde şok yolsuzluk operasyonu: 20 kişi adliyeye sevk edildi İstanbul'da İBB'ye yönelik yeni operasyon: 29 şüpheliyi ne bekliyor? 7 ilde büyük kamu ihalesi operasyonu: 23 kişi gözaltında! Son Dakika 11:3</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek Belçika’da emsal karar: Dolandırıcılık mağdurlarının zararını bankalar ödeyecek sonhaber.eu Belçika’da dolandırıcıların hedefi haline gelen ve phishing (oltalama) mağduru olan kişiler için emsal bir karar alındı. Antwerp Mahkemesi, phishing dolandırıcılığına uğrayan müşterilerin zararlarının bankalar tarafından gecikmeden karşılanması gerektiğine hükmetti. Belçika’nın Antwerp kentinde hızlı yargılama usulüyle görülen davada mahkeme, phishing (oltalama) dolandırıcılığı mağdurlarının zararlarının bankalar tarafından öncelikle karşılanması gerektiğine karar verdi. Karar, yaklaşık 50 bin euro dolandırılan yaşlı bir çiftin açtığı dava sonucunda alındı. Mahkeme bankanın bu yaklaşımını kabul etmedi. Karara göre bankalar, phishing mağdurlarının zararını derhal ödemekle yükümlü olacak. Banka, müşterinin ağır ihmalde bulunduğunu düşünüyorsa bunu kanıtlamak için kendisi tekrar mahkemeye başvurmak ve bunu kanıtlamak zorunda olacak. Phishing (oltalama) nedir? Phishing, dolandırıcıların banka, resmi kurum veya güvenilir bir kuruluş gibi davranarak kişilerin şifre, banka bilgisi veya güvenlik kodlarını ele geçirmeye çalıştığı bir siber dolandırıcılık yöntemidir. Bankacılık sektöründe çığır açan karar Bankacılık hukuku uzmanı Avukat Geert Lenssens, kararı “çığır açıcı bir emsal” olarak değerlendirdi.</t>
+          <t>Buca Belediyesi'nde skandal operasyon: Rüşvet, usulsüzlük ve 'bankamatikçi' vurgunu ortaya çıktı Buca Belediyesi'nde skandal operasyon: Rüşvet, usulsüzlük ve 'bankamatikçi' vurgunu ortaya çıktı Haberhergün İzmir Buca Belediyesi'nde rüşvet, imar usulsüzlüğü, şahsi harcamalar için kamu kaynaklarının kullanımı ve 'bankamatik personeli' gibi skandalları ortaya çıkaran operasyonda 54 kişi adliyeye sevk edildi. GÜNDEM Yayınlanma : 05 Haziran 2026 09:33 Düzenleme : 05 Haziran 2026 09:33 Buca Belediyesi'nde skandal operasyon: Rüşvet, usulsüzlük ve 'bankamatikçi' vurgunu ortaya çıktı Pay</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPSWhvaFFoTkFwM0xNTXdoVXBjQkZKb0V1Slk3dkJkYXJmRV9lV1A3eEhaaWR4REIzc1M4Yy1MRVlpSHZRQzFDb3dqQkJ6ZDlqTjdzTlpPaUZOZ3ZndmZrY0VJTmt4VE9XLXJqVkJKQVJnSDN0Z1ZzTHdRdDRpdGNJckRMc0xKQUo1dEpEd21fZUJ0aDllSk9id1pkVkNDdFR0MmREVFdBRHXSAagBQVVfeXFMT0lob2hRaE5BcDNMTU13aFVwY0JGSm9FdUpZN3ZCZGFyZkVfZVdQN3hIWmlkeERCM3NTOGMtTEVZaUh2UUMxQ293akJCemQ5ak43c05aT2lGTmd2Z3Zma2NFSU5reFRPVy1yalZCSkFSZ0gzdGdWc0x3UXQ0aXRjSXJETHNMSkFKNXRKRHdtX2VCdGg5ZUpPYndaZFZDQ3RUdDJkRFRXQUR1?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>https://www.haberhergun.com/haber/buca-belediyesi-nde-skandal-operasyon-rusvet-usulsuzluk-ve-bankamatikci-vurgunu-ortaya-cikti_74366/</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Buca</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Boğaziçi A.Ş</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Boğaziçi A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr"/>
-      <c r="V39" s="2" t="inlineStr"/>
-      <c r="W39" s="2" t="inlineStr"/>
+          <t>faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>Boğaziçi A.Ş Buca İzmir Türkiye</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Boğaziçi Kuyumculuk</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Boğaziçi Kuyumculuk</t>
+        </is>
+      </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="n">
-        <v>83.25</v>
+        <v>200</v>
       </c>
       <c r="AB39" s="2" t="n">
         <v>38</v>
@@ -6261,27 +6863,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:38:00</t>
+          <t>2026-06-04 21:07:04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>banka hesapları bloke</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi</t>
+          <t>Sri Lanka'da bakımevinde yangın: 12 kişi öldü, işletme sahibi gözaltında</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen</t>
+          <t>Sri Lanka'da bakımevinde yangın: 12 kişi öldü, işletme sahibi gözaltında Euronews.com</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -6291,39 +6893,31 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>işletme</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen</t>
+          <t>Yetkililer, Sri Lanka'da gece saatlerinde çıkan ve 12 bakımevi sakininin ölümüne neden olan yangının ardından kaçak işletilen tesisin sahibinin gözaltına alındığını açıkladı. Yetkililer, Sri Lanka'da gece saatlerinde çıkan ve 12 bakımevi sakininin ölümüne neden olan yangının ardından kaçak işletilen tesisin sahibinin gözaltına alındığını açıkladı. Yetkililer, Sri Lanka'da gece saatlerinde çıkan ve 12 bakımevi sakininin ölümüne neden olan yangının ardından kaçak işletilen tesisin sahibinin gözaltına alındığını açıkladı. Europe Today Costa'dan AB'ye katılım kurallarının 'basitleştirilmesi' çağrısı Kültür Ajandası Dünya 'Beatles Günü' için resmi tarih açıklandı: 25 Haziran No Comment Venezuela'nın Dans Eden Şeytanları asırlık Korpus Christi ritüelini canlandırdı No Comment Kudüs Onur Yürüyüşü'ne binlerce kişi sıkı güvenlik önlemleri altında katıldı Sri Lanka polisi ve yargı yetkilileri, Anguruwatota’da 4 Haziran 2026’da gece çıkan yangının ardından kül olmuş bir huzurevinde inceleme yapıyor. - © AP Photo © AP Photo Sri Lanka polisi ve yargı yetkilileri, Anguruwatota’da 4 Haziran 2026’da gece çıkan yangının ardından kül olmuş bir huzurevinde inceleme yapıyor. - © AP Photo By Gavin Blackburn Yayınlanma Tarihi 04/06/2026 - 23:07 GMT+2 Yayınlanma Tarihi 04/06/2026 - 23:07 GMT+2 Bu haberler de ilginizi çekebilir Sri Lanka, 40'tan fazla ülkenin turistlerine vize ücretini kaldırdı Sri Lanka sel ve toprak kaymalarıyla boğuşuyor: Devlet daireleri ve okullar kapatıldı Vatikan, Sri Lanka'daki Paskalya bombalamasının 167 kurbanını 'inanç tanıkları' olarak kabul etti Sri Lanka, 40'tan fazla ülkenin turistlerine vize ücretini kaldırdı Sri Lanka sel ve toprak kaymalarıyla boğuşuyor: Devlet daireleri ve okullar kapatıldı Vatikan, Sri Lanka'daki Paskalya bombalamasının 167 kurbanını 'inanç tanıkları' olarak kabul etti Sri Lankalı polisler, Anguruwatota’da gece çıkan yangının ardından küle dönmüş bir bakımevini inceliyor, 4 Haziran 2026 AP Photo Sri Lanka'da bakımevinde yangın: 12 kişi öldü, işletme sahibi gözaltında Yetkililer, Sri Lanka'da gece saatlerinde çıkan ve 12 bakımevi sakininin ölümüne neden olan yangının ardından kaçak işletilen tesisin sahibinin gözaltına alındığını açıkladı. Bu haberler de ilginizi çekebilir Önyargısız, sansürsüz, yorumsuz, No Comment. Haberleri yorumsuz izleyin. Size dünyanın önde gelen kaynaklarının son iklim verilerini sunuyoruz. İklim değişikliğinin etkilerini azaltmak için yeni stratejiler arayan uzmanlarla görüşerek, son durumu analiz ediyor ve gezegenimizin değişimini açıklıyoruz. Sri Lanka’nın başkenti Kolombo'nun güneyindeki 'Maupiya Sewana' adlı bakımevinde dün gece saatlerinde yangın çıktı. Yangında 12 kişi hayatını kaybederken, 6 kişi de yaralandı. Ülkede son yılların en ölümcül yangınlarından biri olarak kayıtlara geçen felakete ilişkin soruşturma sürerken, işletme sahibi Isuru Anushka'nın tutuklu yargılanmak üzere cezaevine gönderildiği bildirildi. Olayla ilgili yürütülen adli soruşturmada yetkililer, tesisin bakımevi olarak faaliyet gösterme izni bulunmadığını ve düzenleyici kurumların belirlediği asgari standartları karşılamadığını belirtti. İlk mahkeme duruşmasının ardından gazetecilere açıklama yapan bir polis memuru, "Polise, yaşlı bakımıyla ilgili yönetmeliklerin ihlal edilip edilmediğini araştırma talimatı verildi," dedi. Soruşturmada ayrıca, bakımevi sakinlerinden 11'inin olay yerinde yanarak can verdiği, 12'nci kurbanın ise kaldırıldığı yerel bir hastanede hayatını kaybettiği aktarıldı. Dumandan etkilenerek hastaneye kaldırılan diğer 6 kişinin ise hayati tehlikesinin sürdüğü bildirildi. Adli tıp uzmanları, tek katlı binanın enkazında yaptıkları incelemelerde perşembe sabahı 7 kişinin daha cansız bedenine ulaştı. Böylece çarşamba günü 5 olarak açıklanan ölü sayısı 12'ye yükseldi. AFP haber ajansı, polisin hayatta kalanlar ve komşularla görüştüğü sırada, kelepçeli tesis sahibinin olay yerine getirildiğini aktardı. Tesiste yaşlıların yanı sıra zihinsel sağlık sorunları olan gençlerin de barındığı öğrenildi. Polisin verdiği bilgiye göre, hayatını kaybeden en genç kurban 17 yaşında bir çocuktu. Polis, ilk tanık ifadelerine göre yangının, onlarca yatağın üst üste yığılı olduğu bir depoda başladığını belirtti. Polis Sözcüsü Frederick Wootler, çarşamba günü kurtarılan 51 sakin ve personelin yakınlardaki bir devlet okuluna yerleştirildiğini açıkladı.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen Banka hesabında 21 milyar dolar gördü: Van'da bir günde milyarderler listesine giren kişi Gazete Oksijen</t>
+          <t>Sri Lanka'da bakımevinde yangın: 12 kişi öldü, işletme sahibi gözaltında Sri Lanka'da bakımevinde yangın: 12 kişi öldü, işletme sahibi gözaltında Euronews.com Yetkililer, Sri Lanka'da gece saatlerinde çıkan ve 12 bakımevi sakininin ölümüne neden olan yangının ardından kaçak işletilen tesisin sahibinin gözaltına alındığını açıkladı. Europe Today Costa'dan AB'ye katılım kurallarının 'basitleştirilmesi' çağrısı Kültür Ajandası Dünya 'Beatles Günü' için resmi tarih açıklandı: 25 Haziran No Comment Venezuela'nın Dans Eden Şeytanları asırlık Korpus Christi ritüelini canlandırdı No Comment Kudüs Onur Yürüyüşü'ne binlerce kişi sıkı güvenlik önlemleri altında katıldı Sri Lanka polisi ve yargı yetkilileri, Anguruwatota’da 4 Haziran 2026’da gece çıkan yangının ardından kül olmuş bir huzurevinde inceleme yapıyor. - © AP Photo © AP Photo Sri Lanka polisi ve yargı yetkilileri, Anguruwatota’da 4 Haziran 2026’da gece çıkan yangının ardından kül olmuş bir huzurevinde inceleme yapıyor. - © AP Photo By Gavin Blackburn Yayınlanma Tarihi 04/06/2026 - 23:07 GMT+2 Yayınlanma Tarihi 04/06/2026 - 23:07 GMT+2 Bu haberler de ilginizi çekebilir Sri Lanka, 40'tan fazla ülkenin turistlerine vize ücretini kaldırdı Sri Lanka sel ve toprak kaymalarıyla boğuşuyor: Devlet daireleri ve okullar kapatıldı Vatikan, Sri Lanka'daki Paskalya bombalamasının 167 kurbanını 'inanç tanıkları' olarak kabul etti Sri Lanka, 40'tan fazla ülkenin turistlerine vize ücretini kaldırdı Sri Lanka sel ve toprak kaymalarıyla boğuşuyor: Devlet daireleri ve okullar kapatıldı Vatikan, Sri Lanka'daki Paskalya bombalamasının 167 kurbanını 'inanç tanıkları' olarak kabul etti Sri Lankalı polisler, Anguruwatota’da gece çıkan yangının ardından küle dönmüş bir bakımevini inceliyor, 4 Haziran 2026 AP Photo Sri Lanka'da bakımevinde yangın: 12 kişi öldü, işletme sahibi gözaltında Yetkililer, Sri Lanka'da gece saatlerinde çıkan ve 12 bakımevi sakininin ölümüne neden olan yangının ardından kaçak işletilen tesisin sahibinin gözaltına alındığını açıkladı. Size dünyanın önde gelen kaynaklarının son iklim verilerini sunuyoruz. İklim değişikliğinin etkilerini azaltmak için yeni stratejiler arayan uzmanlarla görüşerek, son durumu analiz ediyor ve gezegenimizin değişimini açıklıyoruz. Sri Lanka’nın başkenti Kolombo'nun güneyindeki 'Maupiya Sewana' adlı bakımevinde dün gece saatlerinde yangın çıktı. Yangında 12 kişi hayatını kaybederken, 6 kişi de yaralandı. Ülkede son yılların en ölümcül yangınlarından biri olarak kayıtlara geçen felakete ilişkin soruşturma sürerken, işletme sahibi Isuru Anushka'nın tutuklu yargılanmak üzere cezaevine gönderildiği bildirildi. Olayla ilgili yürütülen adli soruşturmada yetkililer, tesisin bakımevi olarak faaliyet gösterme izni bulunmadığını ve düzenleyici kurumların belirlediği asgari standartları karşılamadığını belirtti. Soruşturmada ayrıca, bakımevi sakinlerinden 11'inin olay yerinde yanarak can verdiği, 12'nci kurbanın ise kaldırıldığı yerel bir hastanede hayatını kaybettiği aktarıldı. Dumandan etkilenerek hastaneye kaldırılan diğer 6 kişinin ise hayati tehlikesinin sürdüğü bildirildi. Tesiste yaşlıların yanı sıra zihinsel sağlık sorunları olan gençlerin de barındığı öğrenildi. Polisin verdiği bilgiye göre, hayatını kaybeden en genç kurban 17 yaşında bir çocuktu. Polis, ilk tanık ifadelerine göre yangının, onlarca yatağın üst üste yığılı olduğu bir depoda başladığını belirtti.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://gazeteoksijen.com/turkiye/banka-hesabinda-21-milyar-dolar-gordu-vanda-bir-gunde-milyarderler-listesine-giren-kisi-277613</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Van</t>
-        </is>
-      </c>
+          <t>https://tr.euronews.com/2026/06/04/sri-lankada-bakimevinde-yangin-12-kisi-oldu-isletme-sahibi-gozaltinda</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
@@ -6332,7 +6926,7 @@
       <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr"/>
@@ -6346,7 +6940,7 @@
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="n">
-        <v>87.54000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="AB40" s="2" t="n">
         <v>39</v>
@@ -6355,27 +6949,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 15:26:35</t>
+          <t>2026-06-05 06:48:00</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>banka hesapları bloke</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü?</t>
+          <t>Altın Kiraz’da çeyrek final biletleri sahiplerini buldu: Cenksan Yangın ve Maçka Otomotiv devrede!</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri</t>
+          <t>Altın Kiraz’da çeyrek final biletleri sahiplerini buldu: Cenksan Yangın ve Maçka Otomotiv devrede! Çağdaş Kocaeli Gazetesi</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6385,36 +6979,40 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>otomotiv</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri</t>
+          <t>14. Altın Kiraz Dostluk Futbol Turnuvası’nda ikinci tur heyecanı, futbolseverlere unutulmaz anlar yaşatan kapanış maçlarıyla noktalandı. Körfez Belediyesi Çim Halı Tesisleri’nde oynanan eleme turunun son gününde sahadan galibiyetle ayrılan Cenksan Yangın ve Maçka Otomotiv, çeyrek finale yükselen son takımlar oldu. 14. Altın Kiraz Dostluk Futbol Turnuvası’nda ikinci tur heyecanı, futbolseverlere unutulmaz anlar yaşatan kapanış maçlarıyla noktalandı. Körfez Belediyesi Çim Halı Tesisleri’nde oynanan eleme turunun son gününde sahadan galibiyetle ayrılan Cenksan Yangın ve Maçka Otomotiv, çeyrek finale yükselen son takımlar oldu. 14. Altın Kiraz Dostluk Futbol Turnuvası’nda ikinci tur heyecanı, futbolseverlere unutulmaz anlar yaşatan kapanış maçlarıyla noktalandı. Körfez Belediyesi Çim Halı Tesisleri’nde oynanan eleme turunun son gününde sahadan galibiyetle ayrılan Cenksan Yangın ve Maçka Otomotiv, çeyrek finale yükselen son takımlar oldu. 05 Haziran 2026 - Spor Altın Kiraz’da çeyrek final biletleri sahiplerini buldu: Cenksan Yangın ve Maçka Otomotiv devrede! 14. Altın Kiraz Dostluk Futbol Turnuvası’nda ikinci tur heyecanı, futbolseverlere unutulmaz anlar yaşatan kapanış maçlarıyla noktalandı. Körfez Belediyesi Çim Halı Tesisleri’nde oynanan eleme turunun son gününde sahadan galibiyetle ayrılan Cenksan Yangın ve Maçka Otomotiv, çeyrek finale yükselen son takımlar oldu. FULL Medya ana sponsorluğunda düzenlenen ve bölgenin en saygın spor organizasyonları arasında yer alan turnuvada, çeyrek final öncesi son düzlük nefes kesti. Hakem Abdurrahman Uçak’ın başarıyla yönettiği karşılaşmalarda, oyuncuların sergilediği yüksek mücadele gücü tribünlerden tam not aldı. SON ŞAMPİYONUN GÜÇ GÖSTERİSİ Turnuvanın son şampiyonu unvanını taşıyan Cenksan Yangın, çeyrek final yolunda Ciğerci İbo ile karşılaştı. Sahaya şampiyonluk özgüveniyle çıkan Cenksan Yangın, baştan sona domine ettiği karşılaşmayı 10-3 gibi net bir skorla kazandı. Mücadeleye damgasını vuran isim ise rakip fileleri tam 7 kez havalandıran Erdi Söğüt oldu. Sefa Örgüç, Doğan Şirin ve Ömer Gören’in de skor katkısı sağladığı maçta, Ciğerci İbo cephesinde Mehmet Aktaş’ın 3 gollük çabası skoru değiştirmeye yetmedi. MAÇKA OTOMOTİV TAKTİK SAVAŞINI KAZANDI Günün diğer mücadelesinde ise Maçka Otomotiv ile Esser Yıkım İnşaat kozlarını paylaştı</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri Ahmad Takalo Banka Hesabında Neden 21 Milyar Dolar Gördü? TV de Bugün İnternet Haberleri</t>
+          <t>Altın Kiraz’da çeyrek final biletleri sahiplerini buldu: Cenksan Yangın ve Maçka Otomotiv devrede! Altın Kiraz’da çeyrek final biletleri sahiplerini buldu: Cenksan Yangın ve Maçka Otomotiv devrede! Çağdaş Kocaeli Gazetesi Altın Kiraz Dostluk Futbol Turnuvası’nda ikinci tur heyecanı, futbolseverlere unutulmaz anlar yaşatan kapanış maçlarıyla noktalandı. Körfez Belediyesi Çim Halı Tesisleri’nde oynanan eleme turunun son gününde sahadan galibiyetle ayrılan Cenksan Yangın ve Maçka Otomotiv, çeyrek finale yükselen son takımlar oldu. 05 Haziran 2026 - Spor Altın Kiraz’da çeyrek final biletleri sahiplerini buldu: Cenksan Yangın ve Maçka Otomotiv devrede! FULL Medya ana sponsorluğunda düzenlenen ve bölgenin en saygın spor organizasyonları arasında yer alan turnuvada, çeyrek final öncesi son düzlük nefes kesti. Hakem Abdurrahman Uçak’ın başarıyla yönettiği karşılaşmalarda, oyuncuların sergilediği yüksek mücadele gücü tribünlerden tam not aldı. SON ŞAMPİYONUN GÜÇ GÖSTERİSİ Turnuvanın son şampiyonu unvanını taşıyan Cenksan Yangın, çeyrek final yolunda Ciğerci İbo ile karşılaştı. Sahaya şampiyonluk özgüveniyle çıkan Cenksan Yangın, baştan sona domine ettiği karşılaşmayı 10-3 gibi net bir skorla kazandı. Mücadeleye damgasını vuran isim ise rakip fileleri tam 7 kez havalandıran Erdi Söğüt oldu. Sefa Örgüç, Doğan Şirin ve Ömer Gören’in de skor katkısı sağladığı maçta, Ciğerci İbo cephesinde Mehmet Aktaş’ın 3 gollük çabası skoru değiştirmeye yetmedi.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNR0hibXFPY0FKOVpVa2ZxWmFyNDhhSmhPWE85OWRGOXhRUDJDTGkzZDBNN0Iwcnk4cFpnV1F1cXgzMmNuU0hQSWxVNS1RZzFyTUEteGhESHUtYk8zNDcwQVZwS05RdWNSa3ZrNWgteFdWa0NyNFlUa2hvZGpqNzM2ZFNfVHhHOTdKb2Y4MWVxeE4?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>https://www.cagdaskocaeli.com.tr/amp/foto/28115330/altin-kirazda-ceyrek-final-biletleri-sahiplerini-buldu-cenksan-yangin-ve-macka-otomotiv-devrede</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Kiraz</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -6422,7 +7020,7 @@
       <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr"/>
@@ -6436,7 +7034,7 @@
       <c r="Y41" s="2" t="inlineStr"/>
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="n">
-        <v>57.38</v>
+        <v>138.5</v>
       </c>
       <c r="AB41" s="2" t="n">
         <v>40</v>
@@ -6445,27 +7043,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 13:28:43</t>
+          <t>2026-06-05 06:21:38</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>şüpheli işlem</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sürekli banka kartı kullananlar yandı</t>
+          <t>İzmir’in çevre karnesi: Yangın, rant ve enerji baskısı</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sürekli banka kartı kullananlar yandı Sözcü Gazetesi</t>
+          <t>İzmir’in çevre karnesi: Yangın, rant ve enerji baskısı İlkses Gazetesi</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6475,35 +7073,35 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>enerji</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Haberler - Gündem Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Siber güvenlik ve finans uzmanları, kredi kartlarına kıyasla banka kartlarının dolandırıcılık vakalarında telafisi zor finansal kayıplara yol açabileceğini belirterek tüketicileri dikkatli olmaları konusunda uyardı. Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Gelişen teknolojiyle birlikte alışveriş alışkanlıklarımız tamamen değişti. Günlük en küçük harcamalarda Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Siber güvenlik ve finans uzmanları, kredi kartlarına kıyasla banka kartlarının dolandırıcılık vakalarında telafisi zor finansal kayıplara yol açabileceğini belirterek tüketicileri dikkatli olmaları konusunda uyardı. Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Gelişen teknolojiyle birlikte alışveriş alışkanlıklarımız tamamen değişti. Günlük en küçük harcamalarda Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Siber güvenlik ve finans uzmanları, kredi kartlarına kıyasla banka kartlarının dolandırıcılık vakalarında telafisi zor finansal kayıplara yol açabileceğini belirterek tüketicileri dikkatli olmaları konusunda uyardı.</t>
+          <t>İzmir’in çevre karnesi: Yangın, rant ve enerji baskısı İlkses Gazetesi</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Sürekli banka kartı kullananlar yandı Sürekli banka kartı kullananlar yandı Sözcü Gazetesi Haberler - Gündem Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Siber güvenlik ve finans uzmanları, kredi kartlarına kıyasla banka kartlarının dolandırıcılık vakalarında telafisi zor finansal kayıplara yol açabileceğini belirterek tüketicileri dikkatli olmaları konusunda uyardı. Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Gelişen teknolojiyle birlikte alışveriş alışkanlıklarımız tamamen değişti. Günlük en küçük harcamalarda Sürekli banka kartı kullananlar yandı Nakit taşıma zorunluluğunu ortadan kaldıran ve günlük hayatın ayrılmaz bir parçası haline gelen banka kartları hakkında uzmanlardan önemli uyarılar geldi. Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Yayınlanma: 03 Haziran 2026 - 16:28 Güncellenme: Gelişen teknolojiyle birlikte alışveriş alışkanlıklarımız tamamen değişti.</t>
+          <t>İzmir’in çevre karnesi: Yangın, rant ve enerji baskısı İzmir’in çevre karnesi: Yangın, rant ve enerji baskısı İlkses Gazetesi İzmir’in çevre karnesi: Yangın, rant ve enerji baskısı İlkses Gazetesi</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5UdlFFR1docl9DUlI0UEthUlFmaXJQVVlhQUQtSFRPMUNkYnV4bzlyN21IZU1ldlBJbTUwV0s2bkh1eFlxQXotUnNLTU40RHdXQTlISUdHU1ZzWm5fdkFoMThDQl92TnhQQ0lHYkhHUnVxX0hXZWQyWnMwZy0xYXc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOcEcwNnJDb1ZnejdUbjhKUm1pNnJlZlVseTV1cGVCM2RQc0FtSE9VT0pPLVdROXJfTlZZekJMZng2V3VpUDQ5ZXJaeE5mZmdWYURjUzBIX21vQUtWLUNuNi05V0prOFlxRDQ1Y3BFMUtENE9xb21Femd1a3ZjNWduVjFQRHNMdk5aNVlmdC1hU3fSAZYBQVVfeXFMTzljSjZ3OVJfaGdvdGdIOG5ibDVOU3h6S2x4enpBSDRSSmJwa2FCMHlXTFdrWHJ0QWo5c19VZmFtMmM1Vm9IeFlnb0lUY1FnSVY3Ymc1R3NBZG5ROWZJeW1WVkJiOFl1a25zLU5fREdrUW4taDB1Z0ZXYUNvdVpCSVhsVDZVQWlNSEVGbXBHMWJCWDZJRzlB?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
@@ -6512,7 +7110,7 @@
       <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr"/>
@@ -6526,7 +7124,7 @@
       <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr"/>
       <c r="AA42" s="2" t="n">
-        <v>44.5</v>
+        <v>63.2</v>
       </c>
       <c r="AB42" s="2" t="n">
         <v>41</v>
@@ -6535,27 +7133,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 13:33:47</t>
+          <t>2026-06-04 20:50:09</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu!</t>
+          <t>Mersin'de otomatik kepenk üretimi yapan işletmede çıkan yangın söndürüldü</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! Erzincan Birlik Medya</t>
+          <t>Mersin'de otomatik kepenk üretimi yapan işletmede çıkan yangın söndürüldü Habername.com</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -6565,32 +7163,44 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
+          <t>işletme, üretim</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>üretim tesisi</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! Erzincan Birlik Medya</t>
+          <t>Mersin'in Tarsus ilçesinde otomatik kepenk üretimi yapan işletmede çıkan yangın, itfaiye ekiplerince söndürüldü Mersin'in Tarsus ilçesinde otomatik kepenk üretimi yapan işletmede çıkan yangın, itfaiye ekiplerince söndürüldü Mersin'in Tarsus ilçesinde otomatik kepenk üretimi yapan işletmede çıkan yangın, itfaiye ekiplerince söndürüldü</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! 17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu! Erzincan Birlik Medya 17 İlde Dev Dolandırıcılık Operasyonu: 503 Gözaltı, 1 Milyar Liralık Varlığa El Konuldu!</t>
+          <t>Mersin'de otomatik kepenk üretimi yapan işletmede çıkan yangın söndürüldü Mersin'de otomatik kepenk üretimi yapan işletmede çıkan yangın söndürüldü Habername.com Mersin'in Tarsus ilçesinde otomatik kepenk üretimi yapan işletmede çıkan yangın, itfaiye ekiplerince söndürüldü Mersin'in Tarsus ilçesinde otomatik kepenk üretimi yapan işletmede çıkan yangın, itfaiye ekiplerince söndürüldü Mersin'in Tarsus ilçesinde otomatik kepenk üretimi yapan işletmede çıkan yangın, itfaiye ekiplerince söndürüldü</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMk0xWXlORzVyNHpSSDNpWEZRVFRNLVRvSGpQYVVCZVdTLWxIVC12MkswazMtMG9CX2lDbmFlQzNuY0ljb1I2eU80Zmd4MmdaTWh5anpkRFk5YWtQeU9mQ3QzVlYwenlSR3o4aWdSVG5QVVMzQUhyZzAweUpDVTV6bHI1RVRral9mdFBsd1ZqT3NRb00zSHhSMWlGNGRSV1NScWhGVEZnY29HQzZ2MW9BOF9xamVrZFQ0cDJ1Mm5YRQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>https://www.habername.com/haber-mersinde-otomatik-kepenk-uretimi-yapan-isletmede-cikan-yangin-sonduruldu-280924.htm</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Mersin</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Tarsus</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -6598,7 +7208,7 @@
       <c r="S43" s="2" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr"/>
@@ -6612,7 +7222,7 @@
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="n">
-        <v>88.59999999999999</v>
+        <v>105.6</v>
       </c>
       <c r="AB43" s="2" t="n">
         <v>42</v>
@@ -6621,27 +7231,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:14:00</t>
+          <t>2026-06-04 18:14:00</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var</t>
+          <t>Şanlıurfa'da Motosiklet Deposunda Yangın: Her Şey Küle Döndü</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com</t>
+          <t>Şanlıurfa'da Motosiklet Deposunda Yangın: Her Şey Küle Döndü urfadasin.com</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -6651,18 +7261,22 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>inşaat</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com</t>
+          <t>Şanlıurfa'da Motosiklet Deposunda Yangın: Her Şey Küle Döndü urfadasin.com</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com Esenyurt'ta 15 yıl süren inşaat projesinde dolandırıcılık iddiası: 4 binden fazla mağdur var duzcetv.com</t>
+          <t>Şanlıurfa'da Motosiklet Deposunda Yangın: Her Şey Küle Döndü Şanlıurfa'da Motosiklet Deposunda Yangın: Her Şey Küle Döndü urfadasin.com Şanlıurfa'da Motosiklet Deposunda Yangın: Her Şey Küle Döndü urfadasin.com</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -6672,19 +7286,15 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQODJNbTY0NWFiUFpVMzUyclBFZUZDZlJfVmtDRmtKeTlUSnNjMGlMWnZHMnp1MHZtdTN1UFRiNUVyZVgweVRsUWZNY1ZmVzBTU0NpX3N2Q05GNVJxcmpGdmZHVmxiNW85NnI2QVEzbFhBWVAtdGtuZEpLR3E0OHFrX3pEZlp5d2loYlNIaW9qMVRpd1VzTFowd3AzVHlVWFR4bFo5S05uU2ttSzg3c0tjSmNVR0xLUGtjMlZaSU9CYkZPTGt2b2FTQ2xzZkRfc0J6QVlPOFJPTnNlQ1hidEJTdmpuQ2h1cGZ3?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQWVhiNlZvUENuRmJ4aENnenJCYW92SG1RR01rWWJTaVBRdEY4eW9SMHhZeW52UDJ2bWZ5c2tvcjZUQ2hrZUVuTDhDa1VGdWdzY3hONnNFa1VkZzl3Q2NHbGY3WlZza1p4ODI4b19yeDFUSDFBMEcxZnRCZEJZcHg0Mkt0MFVKQk9fbjZiU9IBkgFBVV95cUxQSHhNYUsxcy1lNnNDZGNVVW5JQlgzel9tOFZ2WDFkTHpVZmZsQU91WE1ud1BxQjlFeTUtNFlrdEhJem9NM3F0eVA2OHRYbkcxaUpPOURBYVh2WkMxem1Fb2doS0pLSHluUXJQSFNFekVmd2ZuU0tvU2tVNWpKMEpZeFhmazBmVUExY184alNjSGo1QQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>Esenyurt</t>
-        </is>
-      </c>
+          <t>Şanlıurfa</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -6692,7 +7302,7 @@
       <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr"/>
@@ -6706,7 +7316,7 @@
       <c r="Y44" s="2" t="inlineStr"/>
       <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" s="2" t="n">
-        <v>117.04</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="AB44" s="2" t="n">
         <v>43</v>
@@ -6715,27 +7325,27 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:31:16</t>
+          <t>2026-06-05 07:13:17</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>soruşturma</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede!</t>
+          <t>Bursa Milletvekili Pala'dan, sağlık kuruluşlarında yangın riskine yönelik bakanlığa uyarı</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans</t>
+          <t>Bursa Milletvekili Pala'dan, sağlık kuruluşlarında yangın riskine yönelik bakanlığa uyarı Başka Gazete</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6745,35 +7355,35 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>kuruluş, sağlık</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans</t>
+          <t>Cumhuriyet Halk Partisi Bursa Milletvekili Prof. Dr. Kayıhan Pala, son yıllarda sağlık kuruluşlarında meydana gelen yangınların, yangın müdahale sistemlerinin yeterliliği ve Sağlık Bakanlığı'nın bu alandaki denetimlerine dair kamuoyunda endişe yarattığını ifade etti. Pala, hastanelerin yüksek riskli yapılar olduğunu vurgulayarak, yangın güvenliğinin yalnızca teknik bir konu değil, doğrudan bir hasta güvenliği ve halk sağlığı sorunu olduğunu belirtti. Cumhuriyet Halk Partisi Bursa Milletvekili Prof. Dr. Kayıhan Pala, son yıllarda sağlık kuruluşlarında meydana gelen yangınların, yangın müdahale sistemlerinin yeterliliği ve Sağlık Bakanlığı'nın bu alandaki denetimlerine dair kamuoyunda endişe yarattığını ifade etti. Pala, hastanelerin yüksek riskli yapılar olduğunu vurgulayarak, yangın güvenliğinin yalnızca teknik bir konu değil, doğrudan bir hasta güvenliği ve halk sağlığı sorunu olduğunu belirtti. Cumhuriyet Halk Partisi Bursa Milletvekili Prof. Dr. Kayıhan Pala, son yıllarda sağlık kuruluşlarında meydana gelen yangınların, yangın müdahale sistemlerinin yeterliliği ve Sağlık Bakanlığı'nın bu alandaki denetimlerine dair kamuoyunda endişe yarattığını ifade etti. Pala, hastanelerin yüksek riskli yapılar olduğunu vurgulayarak, yangın güvenliğinin yalnızca teknik bir konu değil, doğrudan bir hasta güvenliği ve halk sağlığı sorunu olduğunu belirtti. Bursa Milletvekili Pala'dan, sağlık kuruluşlarında yangın riskine yönelik bakanlığa uyarı 2026.06.05 10:13 Son Güncellenme: 2026.06.05 10:18 - BURSA Cumhuriyet Halk Partisi Bursa Milletvekili Prof. Dr. Kayıhan Pala, son yıllarda sağlık kuruluşlarında meydana gelen yangınların, yangın müdahale sistemlerinin yeterliliği ve Sağlık Bakanlığı'nın bu alandaki denetimlerine dair kamuoyunda endişe yarattığını ifade etti. Pala, hastanelerin yüksek riskli yapılar olduğunu vurgulayarak, yangın güvenliğinin yalnızca teknik bir konu değil, doğrudan bir hasta güvenliği ve halk sağlığı sorunu olduğunu belirtti. Hastane yangınları hastaların ve sağlık çalışanlarının yaşamını tehdit ediyor. Örneğin 2009'da Bursa'da Şevket Yılmaz Devlet Hastanesi'nde çıkan yangında Yoğun Bakım Servisi'nde yatan 8 hasta; 2020'de Gaziantep'te SANKO Üniversitesi Özel Sani Konukoğlu Hastanesinde çıkan yangında 9 hasta; aynı yı l Ankara Üniversitesi Tıp Fakültesi Cebeci Hastanesi 'ne bağlı Ruh Sağlığı ve Hastalıkları Anabilim Dalı binasında çıkan yangın sonucu bir hasta ve 2023'te İstanbul'da Sultan Abdülhamid Han Eğitim ve Araştırma Hastanesi'nde çıkan yangında 3 kişi hayatını kaybetti. Bazı hastalar ve sağlık çalışanları da yaralandı. Konuya ilişkin Pala, "Hastaneler; yataklı tedavi hizmetlerinin sunulduğu, hareket kabiliyeti kısıtlı, yaşlı, çocuk, engelli, ameliyat sonrası bakım ve yoğun bakım hastalarının bulunduğu yüksek riskli yapılardır. Yangın anında kendi başına tahliye olamayacak hastaların bulunduğu sağlık kuruluşlarında yangın müdahale sistemlerinin ve acil çıkışların eksiksiz çalışması yaşamsal önemdedir. Özellikle, Binaların Yangından Korunması Hakkında Yönetmelik'te yapılan değişiklikler sonrası sağlık kuruluşlarında yaşanan yangınlar , Sağlık Bakanlığı'nın yönetmelik hükümlerine ne ölçüde uyabildiğine ve uygulamaları ne düzeyde denetleyebildiğine dair açıklama yapmasını gerektirmektedir" dedi. Prof. Dr. Pala, kamuya açık sağlık kuruluşlarındaki yangın müdahale sistemlerinin kapasitesi, personel eğitimleri ve denetimlerin detaylarına yönelik Sağlık Bakanlığı'na bir soru önergesi iletti. Buna karşın Bakan Kemal Memişoğlu, kendisine 3 Mart 2026 tarihinde iletilen soru önergesine Anayasa'nın 98. maddesince öngörülen on beş günlük yasal süre dolmasına rağmen yanıt vermedi. "Bakanlık, önergeyi yanıtlamayarak yangın riskine karşı sorumluluğunu gözden kaçırmaktadır! Riskli hastaneler derhal açıklanmalı!" Prof. Dr. Pala, soru önergesinde öncelikle son beş yıl içinde kaç hastanede yangın denetimi yapıldığını, kaç hastanede eksiklik tespit edildiğini ve yangın güvenliği açısından yetersiz bulunan hastaneler hakkında ne tür idari yaptırımlar uygulandığını sordu. Pala, "Bakanlık, ilgili soruları yanıtlamayarak hastanelerdeki yangın tehdidinin yarattığı hayati riske karşı sorumluluk almadığını göstermektedir. Yangın güvenliği açısından riskli olduğu tespit edilen hastanelerin açıklanamaması hem denetim hem de uygulama alanındaki zafiyetlerin kamuoyundan gizlendiği düşüncesini güçlendirmektedir." açıklamasında bulundu. "Yeni bir eylem planı şart; özellikle yoğun bakım gibi riskli birimler için çalışmalara derhal başlanmalı!" Pala, olası can kayıplarının ve yaralanmaların önlenmesi amacıyla, hastanelerin yangın güvenliği açısından gözden geçirileceği ve gerekli önlemlerin alınmasının sağlanacağı bir eylem planı hazırlanması gerektiğini ifade etti. "Yoğun bakım, ameliyathane ve acil servis gibi yüksek riskli birimler bu çalışmalar içinde önceliklendirilmelidir. Yüksek riskli birimlerde yangın anında uygulanacak tahliye planları hazırlanmalı; hareket kabiliyeti kısıtlı, yoğun bakım altındaki hastaların tahliyesi için özel ekipmanlar her hastanede bulundurulmalıdır. Sağlık personeline yangınla mücadele, tahliye ve acil durum yönetimi konusunda düzenli eğitim verilmesi de ertelenemez bir zorunluluktur. Bakanlık, sağlık kuruluşlarında olası bir yangının yaratacağı etkileri ciddiye almalı ve yürüttüğü çalışmaların hesabını kamuoyuna vermelidir" dedi. © Copyright 2026 Başka Gazete</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Sigorta devlerine soruşturma açıldı: 19 şirket listede! Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans Sigorta devlerine soruşturma açıldı: 19 şirket listede! - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Finans</t>
+          <t>Bursa Milletvekili Pala'dan, sağlık kuruluşlarında yangın riskine yönelik bakanlığa uyarı Bursa Milletvekili Pala'dan, sağlık kuruluşlarında yangın riskine yönelik bakanlığa uyarı Başka Gazete Cumhuriyet Halk Partisi Bursa Milletvekili Prof. Kayıhan Pala, son yıllarda sağlık kuruluşlarında meydana gelen yangınların, yangın müdahale sistemlerinin yeterliliği ve Sağlık Bakanlığı'nın bu alandaki denetimlerine dair kamuoyunda endişe yarattığını ifade etti. Pala, hastanelerin yüksek riskli yapılar olduğunu vurgulayarak, yangın güvenliğinin yalnızca teknik bir konu değil, doğrudan bir hasta güvenliği ve halk sağlığı sorunu olduğunu belirtti. Bursa Milletvekili Pala'dan, sağlık kuruluşlarında yangın riskine yönelik bakanlığa uyarı 2026.06.05 10:13 Son Güncellenme: 2026.06.05 10:18 - BURSA Cumhuriyet Halk Partisi Bursa Milletvekili Prof. Hastane yangınları hastaların ve sağlık çalışanlarının yaşamını tehdit ediyor. Örneğin 2009'da Bursa'da Şevket Yılmaz Devlet Hastanesi'nde çıkan yangında Yoğun Bakım Servisi'nde yatan 8 hasta; 2020'de Gaziantep'te SANKO Üniversitesi Özel Sani Konukoğlu Hastanesinde çıkan yangında 9 hasta; aynı yı l Ankara Üniversitesi Tıp Fakültesi Cebeci Hastanesi 'ne bağlı Ruh Sağlığı ve Hastalıkları Anabilim Dalı binasında çıkan yangın sonucu bir hasta ve 2023'te İstanbul'da Sultan Abdülhamid Han Eğitim ve Araştırma Hastanesi'nde çıkan yangında 3 kişi hayatını kaybetti. Bazı hastalar ve sağlık çalışanları da yaralandı. Konuya ilişkin Pala, "Hastaneler; yataklı tedavi hizmetlerinin sunulduğu, hareket kabiliyeti kısıtlı, yaşlı, çocuk, engelli, ameliyat sonrası bakım ve yoğun bakım hastalarının bulunduğu yüksek riskli yapılardır. Yangın anında kendi başına tahliye olamayacak hastaların bulunduğu sağlık kuruluşlarında yangın müdahale sistemlerinin ve acil çıkışların eksiksiz çalışması yaşamsal önemdedir. Özellikle, Binaların Yangından Korunması Hakkında Yönetmelik'te yapılan değişiklikler sonrası sağlık kuruluşlarında yaşanan yangınlar , Sağlık Bakanlığı'nın yönetmelik hükümlerine ne ölçüde uyabildiğine ve uygulamaları ne düzeyde denetleyebildiğine dair açıklama yapmasını gerektirmektedir" dedi. Pala, kamuya açık sağlık kuruluşlarındaki yangın müdahale sistemlerinin kapasitesi, personel eğitimleri ve denetimlerin detaylarına yönelik Sağlık Bakanlığı'na bir soru önergesi iletti. Buna karşın Bakan Kemal Memişoğlu, kendisine 3 Mart 2026 tarihinde iletilen soru önergesine Anayasa'nın 98. maddesince öngörülen on beş günlük yasal süre dolmasına rağmen yanıt vermedi. "Bakanlık, önergeyi yanıtlamayarak yangın riskine karşı sorumluluğunu gözden kaçırmaktadır! Riskli hastaneler derhal açıklanmalı!" Prof. Pala, soru önergesinde öncelikle son beş yıl içinde kaç hastanede yangın denetimi yapıldığını, kaç hastanede eksiklik tespit edildiğini ve yangın güvenliği açısından yetersiz bulunan hastaneler hakkında ne tür idari yaptırımlar uygulandığını sordu. Pala, "Bakanlık, ilgili soruları yanıtlamayarak hastanelerdeki yangın tehdidinin yarattığı hayati riske karşı sorumluluk almadığını göstermektedir. Yangın güvenliği açısından riskli olduğu tespit edilen hastanelerin açıklanamaması hem denetim hem de uygulama alanındaki zafiyetlerin kamuoyundan gizlendiği düşüncesini güçlendirmektedir." açıklamasında bulundu. "Yeni bir eylem planı şart; özellikle yoğun bakım gibi riskli birimler için çalışmalara derhal başlanmalı!" Pala, olası can kayıplarının ve yaralanmaların önlenmesi amacıyla, hastanelerin yangın güvenliği açısından gözden geçirileceği ve gerekli önlemlerin alınmasının sağlanacağı bir eylem planı hazırlanması gerektiğini ifade etti. Yüksek riskli birimlerde yangın anında uygulanacak tahliye planları hazırlanmalı; hareket kabiliyeti kısıtlı, yoğun bakım altındaki hastaların tahliyesi için özel ekipmanlar her hastanede bulundurulmalıdır. Sağlık personeline yangınla mücadele, tahliye ve acil durum yönetimi konusunda düzenli eğitim verilmesi de ertelenemez bir zorunluluktur. Bakanlık, sağlık kuruluşlarında olası bir yangının yaratacağı etkileri ciddiye almalı ve yürüttüğü çalışmaların hesabını kamuoyuna vermelidir" dedi. © Copyright 2026 Başka Gazete</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPajZ1VV9UV3E4MGlfeUFOeWdVbTdLLURCQVVmVmFKaFdSeDFmMVNZc3U3UlFUeS1Na0FOZ1ZQYUVwdXgzLWtGTEtHcHRqazlfRkthanBKdFJ2cUtNTzQzTWQyWXJ2aDhZcFJRdDRFY3ZXWFhUcG5qbkEwaEFzT2JMWEUtVjRjNUk0X1hjQnpGc0xyb0JaYjZXSndxVlFCVUEyVHZBSHVHRjhKQdIBmAFBVV95cUxQNjg0aFc2OXhMbDRLVG1WdEhqNGtRVGpISk05X1I3YXg2YUpMQ2M1MFpOdG9JdzZja2lwTS00RThYdEQ3VnRHT1g2dWMteHVZWUFCSURzYnBIc0FSbjJ5UnFPRHFXUEZuZWwwb1dXaURjdk95UlgyRURuM1V6R2dEM0c4dk1PSjFGdTJUS0psaVgtRjRMMkJsVg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>https://www.baskagazete.com/haber/bursa-milletvekili-pala-dan-saglik-kuruluslarinda-yangin-riskine-yonelik-bakanliga-uyari-237025.html</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Gaziantep | İstanbul</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
@@ -6782,7 +7392,7 @@
       <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr"/>
@@ -6796,7 +7406,7 @@
       <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="n">
-        <v>75.73999999999999</v>
+        <v>111</v>
       </c>
       <c r="AB45" s="2" t="n">
         <v>44</v>
@@ -6805,27 +7415,27 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:50:00</t>
+          <t>2026-06-04 15:57:00</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>soruşturma</t>
+          <t>banka soruşturma</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Yedi vize şirketine soruşturma</t>
+          <t>Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Yedi vize şirketine soruşturma Memurlar.Net</t>
+          <t>Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6835,22 +7445,22 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Ticaret Bakanı Ömer Bolat, "Vize başvuru aracılığı hizmeti sunan firmaların hizmet ve tanıtımlarına ilişkin olarak, Reklam Kurulu tarafından 7 farklı şirket hakkında 6502 sayılı Kanun'un 61'inci ve 62'nci maddeleri kapsamında incelemeler devam etmektedir" dedi. Ticaret Bakanı Ömer Bolat, "Vize başvuru aracılığı hizmeti sunan firmaların hizmet ve tanıtımlarına ilişkin olarak, Reklam Kurulu tarafından 7 farklı şirket hakkında 6502 sayılı Kanun'un 61'inci ve 62'nci maddeleri kapsamında incelemeler devam etmektedir" dedi. Ticaret Bakanı Ömer Bolat, "Vize başvuru aracılığı hizmeti sunan firmaların hizmet ve tanıtımlarına ilişkin olarak, Reklam Kurulu tarafından 7 farklı şirket hakkında 6502 sayılı Kanun'un 61'inci ve 62'nci maddeleri kapsamında incelemeler devam etmektedir" dedi. Önemli Uyarı : Bu servisi gereksiz kullananların şikayet etme hakkı geri alınacaktır. Adınız Soyadınız E-Posta Adresiniz Şikayet Nedeninizi Küfür / Hakaret Kışkırtıcı içerik Küçük düşürücü içerik Asılsız itham Diğer Güvenlik kodu Kapat Şikayet Et Bakan Kurum: 20 bine yakın konutu 64 ilde satışa çıkarıyoruz Süresiz nafaka için AYM'den karar çıktı! Tutuklu bulunan Mühittin Böcek yeni bir ifade daha verdi İşsizlik rakamları açıklandı Kültür ve Turizm Bakanlığı 569 Sözleşmeli Personel Alacak Yıldırımtürk: Altında esas yükseliş Ağustos'ta başlayacak En düşük emekli aylığı temmuzda 22 bin liraya mı yükselecek? Emekliler arasındaki zam farkı kapanıyor Sahillerde sigara yasağı yarın başlıyor Bahçeli'den CHP açıklaması: Olaylar sokağa taşıp kanunsuzluğa dönüşmemeli Maliye, Vergi Konseyinin yeni yönetimini belirledi 'Her 5 çocuktan 1'i siber zorbalığa maruz kalıyor' Sıfır Atık Festivali İstanbul'da başlıyor Ankara, 40 bin personelle havadan ve karadan korunacak Avukatlara büyük kolaylık: İstinafta 'E-Duruşma' dönemi Ergün Atalay: İşçi, memur ve emeklinin enflasyon kayıpları telafi edilmeli İstanbul CBS'den Özgür Özel ve Veli Ağbaba açıklaması Komisyondan geçti: Emniyet kadroları yeniden şekilleniyor Adalet Bakanlığı Görevde Yükselme ve Ünvan Değişikliği Tercih Sonuçları açıklandı KARDEMİR beyaz yaka personel alacak: İşte başvuru şartları! İTÜ yönetimi şikayet etti: 2 çalışan dolandırıcılıktan tutuklandı Bakan Gürlek paylaştı</t>
+          <t>Ad Haberler - Ekonomi Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı 14 Mart 2025 tarihinde yönetimi TMSF'ye devredilen BankPozitif, yapılan ihale sonucunda Efor Çay ve Ofçay'ın sahibi Efor Holding'e satıldı. Yayınlanma: 04 Haziran 2026 - 18:57 Güncellenme: 04 Haziran 2026 - 19:13 Yasadışı bahis soruşturması kapsamında 14 Mart 2025 tarihinde iş insanı Erkan Kork gözaltına alınmış, Kork'un sahibi olduğu şirketlerin yönetimi ise Tasarruf Mevduatı Sigorta Fonu'na (TMSF) devredilmişti. Yönetimi TMSF'ye geçen şirketler arasında dijital cüzdan uygulaması 'Payfix' ile Türkiye'de 24 yıldır bankacılık hizmeti veren BankPozitif yer aldı. Devam eden süreçte tutuklanan Kork hakkında İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma tamamlanmış ve Kork için 26 yıla kadar hapis talebiyle dava açılmıştı. Bu süreçte Kork'un sahibi olduğu bazı taşınmaz ve şirketler de TMSF tarafından ihaleye çıkarıldı. 24 YILLIK BANKANIN YENİ SAHİBİ BELLİ OLDU TMSF tarafından satışa çıkarılan şirketler arasında en dikkat çekeni ise Türkiye'de faaliyetlerine 2002 yılında başlayan BankPozitif oldu. Geçtiğimiz yıl duyurulan ihalenin, nedeni henüz bilinmeyen bir sebeple ertelenmesinin ardından geçtiğimiz aylarda yeniden 1 milyar 100 milyon TL muhammen bedelle ihaleye çıkarılan banka, Efor Çay ve Ofçay'ın sahibi Rize merkezli Efor Holding tarafından satın alındı. Yapılan incelemelerin ardından Rekabet Kurumu, 7145 sayılı Kanun'un Geçici 2. maddesi kapsamında Tasarruf Mevduatı Sigorta Fonu'nun (TMSF) kayyım olarak görevlendirildiği bankanın hisselerinin yeni sahibine geçişini onayladı. Bu kararla birlikte bankanın yeni sahibi resmen Efor Holding AŞ oldu. Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı 14 Mart 2025 tarihinde yönetimi TMSF'ye devredilen BankPozitif, yapılan ihale sonucunda Efor Çay ve Ofçay'ın sahibi Efor Holding'e satıldı. Yayınlanma: 04 Haziran 2026 - 18:57 Güncellenme: 04 Haziran 2026 - 19:13 Yayınlanma: 04 Haziran 2026 - 18:57 Güncellenme: 04 Haziran 2026 - 19:13 Yasadışı bahis soruşturması kapsamında 14 Mart 2025 tarihinde iş insanı Erkan Kork gözaltına alınmış, Kork'un sahibi olduğu şirketlerin yönetimi ise Tasarruf Mevduatı Sigorta Fonu'na (TMSF) devredilmişti. Yönetimi TMSF'ye geçen şirketler arasında dijital cüzdan uygulaması 'Payfix' ile Türkiye'de 24 yıldır bankacılık hizmeti veren BankPozitif yer aldı. Devam eden süreçte tutuklanan Kork hakkında İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma tamamlanmış ve Kork için 26 yıla kadar hapis talebiyle dava açılmıştı. Bu süreçte Kork'un sahibi olduğu bazı taşınmaz ve şirketler de TMSF tarafından ihaleye çıkarıldı. 24 YILLIK BANKANIN YENİ SAHİBİ BELLİ OLDU TMSF tarafından satışa çıkarılan şirketler arasında en dikkat çekeni ise Türkiye'de faaliyetlerine 2002 yılında başlayan BankPozitif oldu. Geçtiğimiz yıl duyurulan ihalenin, nedeni henüz bilinmeyen bir sebeple ertelenmesinin ardından geçtiğimiz aylarda yeniden 1 milyar 100 milyon TL muhammen bedelle ihaleye çıkarılan banka, Efor Çay ve Ofçay'ın sahibi Rize merkezli Efor Holding tarafından satın alındı. Yapılan incelemelerin ardından Rekabet Kurumu, 7145 sayılı Kanun'un Geçici 2. maddesi kapsamında Tasarruf Mevduatı Sigorta Fonu'nun (TMSF) kayyım olarak görevlendirildiği bankanın hisselerinin yeni sahibine geçişini onayladı. Bu kararla birlikte bankanın yeni sahibi resmen Efor Holding AŞ oldu. Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı 14 Mart 2025 tarihinde yönetimi TMSF'ye devredilen BankPozitif, yapılan ihale sonucunda Efor Çay ve Ofçay'ın sahibi Efor Holding'e satıldı. Yasadışı bahis soruşturması kapsamında 14 Mart 2025 tarihinde iş insanı Erkan Kork gözaltına alınmış, Kork'un sahibi olduğu şirketlerin yönetimi ise Tasarruf Mevduatı Sigorta Fonu'na (TMSF) devredilmişti. Yönetimi TMSF'ye geçen şirketler arasında dijital cüzdan uygulaması 'Payfix' ile Türkiye'de 24 yıldır bankacılık hizmeti veren BankPozitif yer aldı. Devam eden süreçte tutuklanan Kork hakkında İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma tamamlanmış ve Kork için 26 yıla kadar hapis talebiyle dava açılmıştı. Bu süreçte Kork'un sahibi olduğu bazı taşınmaz ve şirketler de TMSF tarafından ihaleye çıkarıldı. 24 YILLIK BANKANIN YENİ SAHİBİ BELLİ OLDU TMSF tarafından satışa çıkarılan şirketler arasında en dikkat çekeni ise Türkiye'de faaliyetlerine 2002 yılında başlayan BankPozitif oldu. Geçtiğimiz yıl duyurulan ihalenin, nedeni henüz bilinmeyen bir sebeple ertelenmesinin ardından geçtiğimiz aylarda yeniden 1 milyar 100 milyon TL muhammen bedelle ihaleye çıkarılan banka, Efor Çay ve Ofçay'ın sahibi Rize merkezli Efor Holding tarafından satın alındı. Yapılan incelemelerin ardından Rekabet Kurumu, 7145 sayılı Kanun'un Geçici 2. maddesi kapsamında Tasarruf Mevduatı Sigorta Fonu'nun (TMSF) kayyım olarak görevlendirildiği bankanın hisselerinin yeni sahibine geçişini onayladı. Bu kararla birlikte bankanın yeni sahibi resmen Efor Holding AŞ oldu.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Yedi vize şirketine soruşturma Yedi vize şirketine soruşturma Memurlar.Net Ticaret Bakanı Ömer Bolat, "Vize başvuru aracılığı hizmeti sunan firmaların hizmet ve tanıtımlarına ilişkin olarak, Reklam Kurulu tarafından 7 farklı şirket hakkında 6502 sayılı Kanun'un 61'inci ve 62'nci maddeleri kapsamında incelemeler devam etmektedir" dedi. Önemli Uyarı : Bu servisi gereksiz kullananların şikayet etme hakkı geri alınacaktır. Adınız Soyadınız E-Posta Adresiniz Şikayet Nedeninizi Küfür / Hakaret Kışkırtıcı içerik Küçük düşürücü içerik Asılsız itham Diğer Güvenlik kodu Kapat Şikayet Et Bakan Kurum: 20 bine yakın konutu 64 ilde satışa çıkarıyoruz Süresiz nafaka için AYM'den karar çıktı! Tutuklu bulunan Mühittin Böcek yeni bir ifade daha verdi İşsizlik rakamları açıklandı Kültür ve Turizm Bakanlığı 569 Sözleşmeli Personel Alacak Yıldırımtürk: Altında esas yükseliş Ağustos'ta başlayacak En düşük emekli aylığı temmuzda 22 bin liraya mı yükselecek? Emekliler arasındaki zam farkı kapanıyor Sahillerde sigara yasağı yarın başlıyor Bahçeli'den CHP açıklaması: Olaylar sokağa taşıp kanunsuzluğa dönüşmemeli Maliye, Vergi Konseyinin yeni yönetimini belirledi 'Her 5 çocuktan 1'i siber zorbalığa maruz kalıyor' Sıfır Atık Festivali İstanbul'da başlıyor Ankara, 40 bin personelle havadan ve karadan korunacak Avukatlara büyük kolaylık: İstinafta 'E-Duruşma' dönemi Ergün Atalay: İşçi, memur ve emeklinin enflasyon kayıpları telafi edilmeli İstanbul CBS'den Özgür Özel ve Veli Ağbaba açıklaması Komisyondan geçti: Emniyet kadroları yeniden şekilleniyor Adalet Bakanlığı Görevde Yükselme ve Ünvan Değişikliği Tercih Sonuçları açıklandı KARDEMİR beyaz yaka personel alacak: İşte başvuru şartları! İTÜ yönetimi şikayet etti: 2 çalışan dolandırıcılıktan tutuklandı Bakan Gürlek paylaştı</t>
+          <t>Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı Sözcü Gazetesi Ad Haberler - Ekonomi Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı 14 Mart 2025 tarihinde yönetimi TMSF'ye devredilen BankPozitif, yapılan ihale sonucunda Efor Çay ve Ofçay'ın sahibi Efor Holding'e satıldı. Yayınlanma: 04 Haziran 2026 - 18:57 Güncellenme: 04 Haziran 2026 - 19:13 Yasadışı bahis soruşturması kapsamında 14 Mart 2025 tarihinde iş insanı Erkan Kork gözaltına alınmış, Kork'un sahibi olduğu şirketlerin yönetimi ise Tasarruf Mevduatı Sigorta Fonu'na (TMSF) devredilmişti. Yönetimi TMSF'ye geçen şirketler arasında dijital cüzdan uygulaması 'Payfix' ile Türkiye'de 24 yıldır bankacılık hizmeti veren BankPozitif yer aldı. Devam eden süreçte tutuklanan Kork hakkında İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma tamamlanmış ve Kork için 26 yıla kadar hapis talebiyle dava açılmıştı. Bu süreçte Kork'un sahibi olduğu bazı taşınmaz ve şirketler de TMSF tarafından ihaleye çıkarıldı. 24 YILLIK BANKANIN YENİ SAHİBİ BELLİ OLDU TMSF tarafından satışa çıkarılan şirketler arasında en dikkat çekeni ise Türkiye'de faaliyetlerine 2002 yılında başlayan BankPozitif oldu. Geçtiğimiz yıl duyurulan ihalenin, nedeni henüz bilinmeyen bir sebeple ertelenmesinin ardından geçtiğimiz aylarda yeniden 1 milyar 100 milyon TL muhammen bedelle ihaleye çıkarılan banka, Efor Çay ve Ofçay'ın sahibi Rize merkezli Efor Holding tarafından satın alındı. Yapılan incelemelerin ardından Rekabet Kurumu, 7145 sayılı Kanun'un Geçici 2. maddesi kapsamında Tasarruf Mevduatı Sigorta Fonu'nun (TMSF) kayyım olarak görevlendirildiği bankanın hisselerinin yeni sahibine geçişini onayladı. Bu kararla birlikte bankanın yeni sahibi resmen Efor Holding AŞ oldu. Türkiye'nin 24 yıllık bankası satıldı: Yeni sahibi tanıdık çıktı 14 Mart 2025 tarihinde yönetimi TMSF'ye devredilen BankPozitif, yapılan ihale sonucunda Efor Çay ve Ofçay'ın sahibi Efor Holding'e satıldı. Yayınlanma: 04 Haziran 2026 - 18:57 Güncellenme: 04 Haziran 2026 - 19:13 Yayınlanma: 04 Haziran 2026 - 18:57 Güncellenme: 04 Haziran 2026 - 19:13 Yasadışı bahis soruşturması kapsamında 14 Mart 2025 tarihinde iş insanı Erkan Kork gözaltına alınmış, Kork'un sahibi olduğu şirketlerin yönetimi ise Tasarruf Mevduatı Sigorta Fonu'na (TMSF) devredilmişti. Yasadışı bahis soruşturması kapsamında 14 Mart 2025 tarihinde iş insanı Erkan Kork gözaltına alınmış, Kork'un sahibi olduğu şirketlerin yönetimi ise Tasarruf Mevduatı Sigorta Fonu'na (TMSF) devredilmişti.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -6860,37 +7470,61 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://www.memurlar.net/haber/1168995/yedi-vize-sirketine-sorusturma.html</t>
+          <t>https://www.sozcu.com.tr/amp/turkiye-nin-24-yillik-bankasi-satildi-yeni-sahibi-tanidik-cikti-p325284</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>İstanbul | Rize</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Efor Holding AŞ</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Efor Holding AŞ:63:body | Efor Holding AŞ:raw_legal</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr"/>
-      <c r="V46" s="2" t="inlineStr"/>
-      <c r="W46" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>Efor Holding AŞ İstanbul Türkiye</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>EFOR HOLDİNG</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>EFOR HOLDİNG</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="Z46" s="2" t="inlineStr"/>
       <c r="AA46" s="2" t="n">
-        <v>58.75</v>
+        <v>163.35</v>
       </c>
       <c r="AB46" s="2" t="n">
         <v>45</v>
@@ -6899,27 +7533,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 06:47:24</t>
+          <t>2026-06-04 17:57:55</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>soruşturma</t>
+          <t>yasadışı bahis</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu!</t>
+          <t>Futbolcu Uğurcan Bekçi cinayetinde yasa dışı bahis izi: Kiralık banka hesabı anlaşmazlığı</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Takvim</t>
+          <t>Futbolcu Uğurcan Bekçi cinayetinde yasa dışı bahis izi: Kiralık banka hesabı anlaşmazlığı Takvim</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -6929,18 +7563,22 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
+          <t>banka, banka hesabı</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Giriş Tarihi: 04 Haziran 2026 09:47 Facebook X NSosyal Linki Kopyala Yazı Boyutu Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Diyarbakır Cumhuriyet Başsavcılığı koordinesinde; Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri, uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik asrın operasyonlarından birine imza attı. Yaklaşık 8 ay süren titiz teknik ve fiziki takibin ardından, zehir ticaretinden kazandıkları paraları piyasada aklamaya çalışan 18 şüpheli kıskıvrak yakalandı. 5 Ayrı Soruşturma Dosyası Açıldı "Uyuşturucu veya uyarıcı madde imal ve ticareti" ile "2313 Sayılı Kanuna Muhalefet" suçlarını işleyen şebeke üyeleri hakkında, bu kez de "Suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan 5 ayrı soruşturma dosyası açıldı. Operasyon kapsamında gözaltına alınan 18 şüpheli hakkında yasal işlemler sürerken, baskın yapılan adreslerde yüklü miktarda uyuşturucu maddenin de ele geçirildiği bildirildi. Emirhan Ceylan Takvim.com.tr Güncel Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Diyarbakır Cumhuriyet Başsavcılığı koordinesinde; Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri, uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik asrın operasyonlarından birine imza attı. Yaklaşık 8 ay süren titiz teknik ve fiziki takibin ardından, zehir ticaretinden kazandıkları paraları piyasada aklamaya çalışan 18 şüpheli kıskıvrak yakalandı. 5 Ayrı Soruşturma Dosyası Açıldı "Uyuşturucu veya uyarıcı madde imal ve ticareti" ile "2313 Sayılı Kanuna Muhalefet" suçlarını işleyen şebeke üyeleri hakkında, bu kez de "Suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan 5 ayrı soruşturma dosyası açıldı. Operasyon kapsamında gözaltına alınan 18 şüpheli hakkında yasal işlemler sürerken, baskın yapılan adreslerde yüklü miktarda uyuşturucu maddenin de ele geçirildiği bildirildi. Samsun'da fabrikada feci ölüm! Elektrik akımına kapılan 3 işçi hayatını kaybetti 04.06.2026 Perşembe Tırın altına ok gibi saplanan otomobilde feci kaza: 1'i ağır 2 yaralı 03.06.2026 Çarşamba Dilan Polat'ın koruması Can Polat'ın vurulma anı ortaya çıktı | VİDEO 03.06.2026 Çarşamba İstanbul'un göbeğinde yabancı uyrukluların bıçaklı kavgası | VİDEO 03.06.2026 Çarşamba Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Diyarbakır Cumhuriyet Başsavcılığı koordinesinde; Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri, uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik asrın operasyonlarından birine imza attı. Yaklaşık 8 ay süren titiz teknik ve fiziki takibin ardından, zehir ticaretinden kazandıkları paraları piyasada aklamaya çalışan 18 şüpheli kıskıvrak yakalandı. 5 Ayrı Soruşturma Dosyası Açıldı "Uyuşturucu veya uyarıcı madde imal ve ticareti" ile "2313 Sayılı Kanuna Muhalefet" suçlarını işleyen şebeke üyeleri hakkında, bu kez de "Suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan 5 ayrı soruşturma dosyası açıldı. Operasyon kapsamında gözaltına alınan 18 şüpheli hakkında yasal işlemler sürerken, baskın yapılan adreslerde yüklü miktarda uyuşturucu maddenin de ele geçirildiği bildirildi.</t>
+          <t>İzmit’te geçtiğimiz aralık ayında çıkan silahlı çatışmada eski futbolcu Uğurcan Bekçi’nin ölümüne neden olan sanıklar ilk kez hakim karşısına çıktı. SEGBİS... İzmit’te geçtiğimiz aralık ayında çıkan silahlı çatışmada eski futbolcu Uğurcan Bekçi’nin ölümüne neden olan sanıklar ilk kez hakim karşısına çıktı. SEGBİS... İzmit’te geçtiğimiz aralık ayında çıkan silahlı çatışmada eski futbolcu Uğurcan Bekçi’nin ölümüne neden olan sanıklar ilk kez hakim karşısına çıktı. SEGBİS... Futbolcu Uğurcan Bekçi cinayetinde yasa dışı bahis izi: Kiralık banka hesabı anlaşmazlığı İzmit'te geçtiğimiz aralık ayında çıkan silahlı çatışmada eski futbolcu Uğurcan Bekçi'nin ölümüne neden olan sanıklar ilk kez hakim karşısına çıktı. SEGBİS aracılığıyla duruşmaya katılan tutuklu sanıklar, olayın arkasında Karadağ bağlantılı bir yasa dışı bahis çetesinin banka hesabı anlaşmazlığı olduğunu iddia etti. Mağdur tarafın suçlamaları reddettiği ve şikayetçi olduğu duruşmada mahkeme, dosyadaki eksiklerin giderilmesi için ertelenirken sanıkların tahliye talepleri reddedildi. Takvim.com.tr Giriş Tarihi: 04 Haziran 2026 20:57 Güncelleme Tarihi: 04 Haziran 2026 21:30 Facebook X NSosyal Linki Kopyala Yazı Boyutu Hızlı Özet Göster Kocaeli'nin İzmit ilçesinde 17 Aralık 2025'te çıkan silahlı kavgada futbolcu Uğurcan Bekçi öldü, 2 kişi yaralandı. Olayla ilgili tutuklanan Furkan K. ve Ertuğrul S.'nin yargılandığı duruşmada sanıklar 'yasa dışı bahis ve kiralık banka hesabı' anlaşmazlığı iddiasını öne sürdü. Sanık Ertuğrul S., müştekileri ölümle tehdit ettiklerini ve 'kanlı para' olarak nitelendirdikleri 230 bin TL talep ettiklerini iddia etti. Tutuklu sanık Furkan K., Uğurcan Bekçi'ye ateş ettiğini itiraf ederken, Ertuğrul S. kendisinin ateş etmediğini öne sürdü. Müştekiler sanıkların iddialarını reddederken, mahkeme tutukluluk halinin devamına karar verip duruşmayı erteledi. Kocaeli'nin İzmit ilçesinde iki grup arasında çıkan silahlı kavgada futbolcu Uğurcan Bekçi'nin hayatını kaybettiği, 2 kişinin de yaralandığı olayın ilk duruşması görüldü. Sanık Ertuğrul S., olayın perde arkasının "yasa dışı bahis ve kiralık banka hesabı" anlaşmazlığı olduğunu iddia ederek, tehdit edildiğini öne sürdü. Futbolcu Uğurcan Bekçi cinayeti davasında ʺyasa dışı bahisʺ iddiası. (Haberin fotoğrafları İHA'dan alınmıştır.) Olay, 17 Aralık 2025'de gece saatlerinde Sanayi Mahallesi Ömer Türkçakal Bulvarı'nda meydana geldi. İki grup arasında çıkan tartışma kısa sürede silahlı kavgaya dönüştü. Olayda futbolcu Uğurcan Bekçi (27), E.K.B., (27) ve İ.A. (31) vücutlarına isabet eden mermilerle yaralandı. Hastaneye kaldırılan yaralılardan Bekçi, 3 gün süren yaşam mücadelesini kaybetti. Diğer 2 yaralı ise tedavilerinin ardından taburcu edildi. Olaya ilişkin gözaltına alınan Furkan K., Ertuğrul S. çıkarıldıkları mahkemece tutuklanarak cezaevine gönderildi, Emre S. ise adli kontrolle serbest bırakıldı. İLK DURUŞMA Kocaeli 3. Ağır Ceza Mahkemesinde görülen ilk duruşmaya, tutuklu sanıklar Furkan K. ve Ertuğrul S. bulundukları cezaevinden Ses ve Görüntü Bilişim Sistemi (SEGBİS) aracılığıyla katıldı. Tutuksuz sanık Emre S., olayda yaralanan müştekiler, maktulün ailesi ve taraf avukatları ise salonda hazır bulundu. "O PARA KANLI PARA, BİZ BU PARA İÇİN AİLE ÖLDÜRDÜK" İDDİASI Duruşmada ilk savunmayı yapan tutuklu sanık Ertuğrul S., olayın başlangıcının banka hesaplarının kullandırılmasına dayandığını öne sürdü. Müştekilerden İ.A.'nın kendisine "şirket hesabı başına 40 bin lira" teklif ettiğini iddia eden Ertuğrul S., şu ifadeleri kullandı: "İ.A., şirketimin aktif olup olmadığını sordu. Legal bir iş yaptıklarını, bankada açılan hesap başına 40 bin lira para vereceğini söyledi. Birkaç bankadan hesap açtım ve kendilerine teslim ettim, parayı peşin istedim. İlk gün sadece 10 bin TL para verdiler. Haftaya 130 bin TL'imi vereceklerini söylediler. Daha sonra bloke hesabında para olduğunu, onu almam gerektiğini söylediler. İ. ile bankaya gittik ve parayı çekerek Umut'un hesabına yatırıldı. Ancak bana vadedilen 130 bin TL verilmedi. Bankadan çıktık. Gümüş altın işi yaptıklarını sanıyordum ancak yasa dışı bahis yaptıklarını öğrendim. Şirket hesabım kapandı, her şeyim dondu. Hakkım olan 230 bin TL'yi istedim. Sonrasında hesaptaki 300 bin TL'yi çektim. Benden o 300 bin TL'yi istedi. Beni ölümle tehdit ettiler. Beni, 'O para kanlı para, biz bu para için aile öldürdük' diyen birisi ile görüştürdüler. Zaten 230 bini benim hakkım olan paraydı, 70 bin lira onlarındı. Amerika hatlı bir numara arayarak 800 bin TL para istedi, beni tehdit etti." "UĞURCAN'A ATEŞ ETMEDİM, FURKAN ATEŞ ETMİŞ OLABİLİR" Ertuğrul S., savunmasına şöyle devam etti: "E.K.B. ve İ.A. çetenin başı ve İ.A.'nın örgütü Karadağ'dan yönetiyor. Uğurcan'ı arayı bulması için aradım. Ancak sulh olmadı; Uğurcan, Furkan'ı darbetti. İ., '2'sini öldürün, sağ kalmasınlar' dedi. Silahın kabzasını görünce İ. ve E.K.'nın ayaklarına ateş ettim. Uğurcan'a ateş etmedim, Furkan ateş etmiş olabilir. Furkan ile biz teslim olduk. Mağdur olan benim, şirket hesaplarıma bloke koyduruldu. Niyetim öldürmek değildi" dedi. "ELİM AYAĞIM KIRIK OLSAYDI DA BU OLMASAYDI" Tutuklu sanık Furkan K. ise olay yerine, tehdit aldığını söyleyen arkadaşı Ertuğrul S.'yi yalnız bırakmamak için gittiğini belirterek, "Olay günü, uzlaşmak için buluşmaya gideceğini söyledi, kendisine bir şey yapabileceklerini söyleyerek, bir şey olursa isimleri polise vermemi istedi. Ben de kendisiyle gidersem bir şey olmayabileceğini söyledim. Beraber olay yerine gittik. Ancak orada 1 milyon 300 bin TL istediler. Biri orada beni kıskaca aldı, Uğurcan ise bana vurdu. İ., 'Öldürün, yaşatmayın bunları' dedi. Ben sadece bir kez Uğurcan'a doğru ateş ettim. Keşke böyle bir şey olmadaydı. Keşke dayağımı yeseydim, elim ayağım kırık olsaydı da bu olmasaydı. Amacım üzerimdeki tehlikeyi bertaraf etmekti" dedi. Tutuksuz yargılanan Emre S. ise olay yerinde olmadığını ve cinayetle ilgisinin bulunmadığını savundu. MÜŞTEKİLERDEN SUÇLAMALARI REDDETİ Olayda yaralanan E.K.B. ise sanıkların iddialarını reddetti. Ertuğrul S.'nin kendilerini "Önemli bir bilgi var" diyerek çağırdığını ve "Uğurcan olmadan olmaz" şartı koştuğunu belirten E.K.B., "Ertuğrul beni arayarak, 'İşine yarayacak çok önemli bilgi var' dedi ve beni buluşmaya çağırdı. İ.'yi de aradı. Biz zaten İ. ile beraberdik. 'Uğurcan'ı da çağırın' dedi. Uğurcan olmadan elindekileri göstermeyeceğini söyledi. Uğurcan da geldi. Furkan zaten etrafımızda eli belinde dolaşıyordu. Ertuğrul, Uğurcan'ın kendisine borcu olduğunu söyledi. Borcuna kefil olduğumu, ben ödeyeceğimi söyledim. Furkan, Uğurcan'a yumruk attı ve silah çekti. Ertuğrul beni vurdu. Herkes kaçmaya çalıştı. Sanıklardan şikayetçiyim" dedi. Müşteki Berkay K. ise, "Ertuğrul'un 130 bin TL borcu varmış. Zaten sürekli para alıp veriliyordu. Olay günü ben de oradaydım. E.K. vuruldu, ben onu hastaneye götürdüm, hepimiz hedef alındık, şikayetçiyim" ifadelerini kullandı. Müşteki Umut Ü. de, kendisinin de olay yerinde olduğunu, kaçarken bile arkalarından ateş açtıklarını aktararak, şikayetçi olduğunu ifade etti. Uğurcan Bekçi'nin annesi Şehriban Bekçi ise sanıklardan şikayetçi olduğunu ve oğlu ile Ertuğrul S. arasında husumet bulunmadığını söyledi. Mahkeme heyeti, sanıkların tutukluluk halinin devamına karar vererek, duruşmayı erteledi. SONRAKİ HABER TOKİ'nin satışa sunacağı konutlar görüntülendi ÖNCEKİ HABER Ankara'da NATO Zirvesi tedbirleri Ebru Bektaş Takvim.com.tr Güncel Günün Manşetleri Tüm Manşetler Memura 12.41</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Takvim Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Şüphelilerin piyasa değeri yaklaşık 15 milyar TL olan otel, arsa, tarla, daire, iş yeri, araç ve banka hesaplarına el konuldu. Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu! Giriş Tarihi: 04 Haziran 2026 09:47 Facebook X NSosyal Linki Kopyala Yazı Boyutu Diyarbakır’da uyuşturucu ticaretinden elde edilen gelirlerin aklanmasına yönelik düzenlenen operasyonda 18 şüpheli hakkında işlem yapıldı. Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Diyarbakır Cumhuriyet Başsavcılığı koordinesinde; Terörizmin Finansmanı ve Aklama Suçları Bürosu ile İl Jandarma Komutanlığı ekipleri, uyuşturucu ticareti ve suç gelirlerinin aklanmasına yönelik asrın operasyonlarından birine imza attı. Yaklaşık 8 ay süren titiz teknik ve fiziki takibin ardından, zehir ticaretinden kazandıkları paraları piyasada aklamaya çalışan 18 şüpheli kıskıvrak yakalandı. 5 Ayrı Soruşturma Dosyası Açıldı "Uyuşturucu veya uyarıcı madde imal ve ticareti" ile "2313 Sayılı Kanuna Muhalefet" suçlarını işleyen şebeke üyeleri hakkında, bu kez de "Suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan 5 ayrı soruşturma dosyası açıldı. Operasyon kapsamında gözaltına alınan 18 şüpheli hakkında yasal işlemler sürerken, baskın yapılan adreslerde yüklü miktarda uyuşturucu maddenin de ele geçirildiği bildirildi. Emirhan Ceylan Takvim.com.tr Güncel Uyuşturucu Parasıyla Servet Yapmışlar: 15 Milyar TL'lik Mal Varlığına El Konuldu! Samsun'da fabrikada feci ölüm! Elektrik akımına kapılan 3 işçi hayatını kaybetti 04.06.2026 Perşembe Tırın altına ok gibi saplanan otomobilde feci kaza: 1'i ağır 2 yaralı 03.06.2026 Çarşamba Dilan Polat'ın koruması Can Polat'ın vurulma anı ortaya çıktı | VİDEO 03.06.2026 Çarşamba İstanbul'un göbeğinde yabancı uyrukluların bıçaklı kavgası | VİDEO 03.06.2026 Çarşamba Diyarbakır’da suç gelirlerine kilit: 18 şüpheli yakalandı otel ve arsalara el konuldu!</t>
+          <t>Futbolcu Uğurcan Bekçi cinayetinde yasa dışı bahis izi: Kiralık banka hesabı anlaşmazlığı Futbolcu Uğurcan Bekçi cinayetinde yasa dışı bahis izi: Kiralık banka hesabı anlaşmazlığı Takvim İzmit’te geçtiğimiz aralık ayında çıkan silahlı çatışmada eski futbolcu Uğurcan Bekçi’nin ölümüne neden olan sanıklar ilk kez hakim karşısına çıktı. Futbolcu Uğurcan Bekçi cinayetinde yasa dışı bahis izi: Kiralık banka hesabı anlaşmazlığı İzmit'te geçtiğimiz aralık ayında çıkan silahlı çatışmada eski futbolcu Uğurcan Bekçi'nin ölümüne neden olan sanıklar ilk kez hakim karşısına çıktı. SEGBİS aracılığıyla duruşmaya katılan tutuklu sanıklar, olayın arkasında Karadağ bağlantılı bir yasa dışı bahis çetesinin banka hesabı anlaşmazlığı olduğunu iddia etti. Mağdur tarafın suçlamaları reddettiği ve şikayetçi olduğu duruşmada mahkeme, dosyadaki eksiklerin giderilmesi için ertelenirken sanıkların tahliye talepleri reddedildi. Takvim.com.tr Giriş Tarihi: 04 Haziran 2026 20:57 Güncelleme Tarihi: 04 Haziran 2026 21:30 Facebook X NSosyal Linki Kopyala Yazı Boyutu Hızlı Özet Göster Kocaeli'nin İzmit ilçesinde 17 Aralık 2025'te çıkan silahlı kavgada futbolcu Uğurcan Bekçi öldü, 2 kişi yaralandı. Olayla ilgili tutuklanan Furkan K. ve Ertuğrul S.'nin yargılandığı duruşmada sanıklar 'yasa dışı bahis ve kiralık banka hesabı' anlaşmazlığı iddiasını öne sürdü. Sanık Ertuğrul S., müştekileri ölümle tehdit ettiklerini ve 'kanlı para' olarak nitelendirdikleri 230 bin TL talep ettiklerini iddia etti. Tutuklu sanık Furkan K., Uğurcan Bekçi'ye ateş ettiğini itiraf ederken, Ertuğrul S. kendisinin ateş etmediğini öne sürdü. Kocaeli'nin İzmit ilçesinde iki grup arasında çıkan silahlı kavgada futbolcu Uğurcan Bekçi'nin hayatını kaybettiği, 2 kişinin de yaralandığı olayın ilk duruşması görüldü. Sanık Ertuğrul S., olayın perde arkasının "yasa dışı bahis ve kiralık banka hesabı" anlaşmazlığı olduğunu iddia ederek, tehdit edildiğini öne sürdü. Futbolcu Uğurcan Bekçi cinayeti davasında ʺyasa dışı bahisʺ iddiası. (Haberin fotoğrafları İHA'dan alınmıştır.) Olay, 17 Aralık 2025'de gece saatlerinde Sanayi Mahallesi Ömer Türkçakal Bulvarı'nda meydana geldi. İki grup arasında çıkan tartışma kısa sürede silahlı kavgaya dönüştü. Olayda futbolcu Uğurcan Bekçi (27), E.K.B., (27) ve İ.A. Hastaneye kaldırılan yaralılardan Bekçi, 3 gün süren yaşam mücadelesini kaybetti. "O PARA KANLI PARA, BİZ BU PARA İÇİN AİLE ÖLDÜRDÜK" İDDİASI Duruşmada ilk savunmayı yapan tutuklu sanık Ertuğrul S., olayın başlangıcının banka hesaplarının kullandırılmasına dayandığını öne sürdü. Müştekilerden İ.A.'nın kendisine "şirket hesabı başına 40 bin lira" teklif ettiğini iddia eden Ertuğrul S., şu ifadeleri kullandı: "İ.A., şirketimin aktif olup olmadığını sordu. Daha sonra bloke hesabında para olduğunu, onu almam gerektiğini söylediler. Gümüş altın işi yaptıklarını sanıyordum ancak yasa dışı bahis yaptıklarını öğrendim. Şirket hesabım kapandı, her şeyim dondu. Sonrasında hesaptaki 300 bin TL'yi çektim. Amerika hatlı bir numara arayarak 800 bin TL para istedi, beni tehdit etti." "UĞURCAN'A ATEŞ ETMEDİM, FURKAN ATEŞ ETMİŞ OLABİLİR" Ertuğrul S., savunmasına şöyle devam etti: "E.K.B. çetenin başı ve İ.A.'nın örgütü Karadağ'dan yönetiyor. Uğurcan'ı arayı bulması için aradım. Ancak sulh olmadı; Uğurcan, Furkan'ı darbetti. İ., '2'sini öldürün, sağ kalmasınlar' dedi. Silahın kabzasını görünce İ. Uğurcan'a ateş etmedim, Furkan ateş etmiş olabilir. Mağdur olan benim, şirket hesaplarıma bloke koyduruldu. "ELİM AYAĞIM KIRIK OLSAYDI DA BU OLMASAYDI" Tutuklu sanık Furkan K. ise olay yerine, tehdit aldığını söyleyen arkadaşı Ertuğrul S.'yi yalnız bırakmamak için gittiğini belirterek, "Olay günü, uzlaşmak için buluşmaya gideceğini söyledi, kendisine bir şey yapabileceklerini söyleyerek, bir şey olursa isimleri polise vermemi istedi. Biri orada beni kıskaca aldı, Uğurcan ise bana vurdu. İ., 'Öldürün, yaşatmayın bunları' dedi. Ben sadece bir kez Uğurcan'a doğru ateş ettim. Keşke dayağımı yeseydim, elim ayağım kırık olsaydı da bu olmasaydı. Ertuğrul S.'nin kendilerini "Önemli bir bilgi var" diyerek çağırdığını ve "Uğurcan olmadan olmaz" şartı koştuğunu belirten E.K.B., "Ertuğrul beni arayarak, 'İşine yarayacak çok önemli bilgi var' dedi ve beni buluşmaya çağırdı. 'Uğurcan'ı da çağırın' dedi. Uğurcan olmadan elindekileri göstermeyeceğini söyledi. Furkan zaten etrafımızda eli belinde dolaşıyordu. Ertuğrul, Uğurcan'ın kendisine borcu olduğunu söyledi. Furkan, Uğurcan'a yumruk attı ve silah çekti. vuruldu, ben onu hastaneye götürdüm, hepimiz hedef alındık, şikayetçiyim" ifadelerini kullandı. Uğurcan Bekçi'nin annesi Şehriban Bekçi ise sanıklardan şikayetçi olduğunu ve oğlu ile Ertuğrul S. arasında husumet bulunmadığını söyledi.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -6950,23 +7588,35 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://www.takvim.com.tr/video/guncel-videolari/diyarbakirda-suc-gelirlerine-kilit-18-supheli-yakalandi-otel-ve-arsalara-el-konuldu</t>
+          <t>https://www.takvim.com.tr/guncel/2026/06/04/futbolcu-ugurcan-bekci-cinayetinde-yasa-disi-bahis-izi</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır | İstanbul | Samsun</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr"/>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>İzmit</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>de gece saatlerinde Sanayi Mahallesi</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Sanayi Mahallesi Ömer Türkçakal Bulvarı</t>
+        </is>
+      </c>
       <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr"/>
       <c r="S47" s="2" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr"/>
@@ -6980,7 +7630,7 @@
       <c r="Y47" s="2" t="inlineStr"/>
       <c r="Z47" s="2" t="inlineStr"/>
       <c r="AA47" s="2" t="n">
-        <v>107.25</v>
+        <v>151.5</v>
       </c>
       <c r="AB47" s="2" t="n">
         <v>46</v>
@@ -6989,27 +7639,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:30:50</t>
+          <t>2026-06-05 04:21:04</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>soruşturma</t>
+          <t>vergi cezası</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı.</t>
+          <t>Say Yenilenebilir Enerji'ye vergi cezası</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Vietnam.vn</t>
+          <t>Say Yenilenebilir Enerji'ye vergi cezası RHA Ajans</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -7019,28 +7669,28 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>gıda</t>
+          <t>enerji</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Vietnam.vn</t>
+          <t>Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş'ye vergi cezası düzenledi. Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş'ye vergi cezası düzenledi. Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş'ye vergi cezası düzenledi. 05 Haziran 2026 - Gündem Say Yenilenebilir Enerji'ye vergi cezası Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş'ye vergi cezası düzenledi. Kamuyu Aydınlatma Platformuna (KAP) yapılan açıklamada, ''Hazine ve Maliye Bakanlığı tarafından 2023 dönemi kurumlar vergisi denetimi ile ilgili olarak yapılan inceleme sonucunda, şirketimize re'sen 16.045.733,46 TL kurumlar vergisi ile bir kat vergi ziyaı cezası ve 5.837.855,57 TL geçici vergiye ilişkin vergi ziyaı cezası düzenlenmiştir. Şirketimiz tarafından tarh edilen vergi ve cezalara ilişkin vergi davası açılmış olup, bu aşamada herhangi bir ödeme yapılmamıştır.'' denildi. Hibya Haber Ajansı YORUM YAP 14 Milletvekili Var, Urfa Çiftçisi Feryat Ediyor Panama’dan İsviçre’deki saldırıya kınama ve dayanışma mesajı Hukuk müşavirliği ve avukatlık sınav yönetmeliği yürürlükten kaldırıldı Meteoroloji’den kuvvetli yağış uyarısı 05 Haziran 2026 - Gündem Say Yenilenebilir Enerji'ye vergi cezası Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş'ye vergi cezası düzenledi. Kamuyu Aydınlatma Platformuna (KAP) yapılan açıklamada, ''Hazine ve Maliye Bakanlığı tarafından 2023 dönemi kurumlar vergisi denetimi ile ilgili olarak yapılan inceleme sonucunda, şirketimize re'sen 16.045.733,46 TL kurumlar vergisi ile bir kat vergi ziyaı cezası ve 5.837.855,57 TL geçici vergiye ilişkin vergi ziyaı cezası düzenlenmiştir. Şirketimiz tarafından tarh edilen vergi ve cezalara ilişkin vergi davası açılmış olup, bu aşamada herhangi bir ödeme yapılmamıştır.'' denildi. Hibya Haber Ajansı Say Yenilenebilir Enerji'ye vergi cezası Kamuyu Aydınlatma Platformuna (KAP) yapılan açıklamada, ''Hazine ve Maliye Bakanlığı tarafından 2023 dönemi kurumlar vergisi denetimi ile ilgili olarak yapılan inceleme sonucunda, şirketimize re'sen 16.045.733,46 TL kurumlar vergisi ile bir kat vergi ziyaı cezası ve 5.837.855,57 TL geçici vergiye ilişkin vergi ziyaı cezası düzenlenmiştir. Şirketimiz tarafından tarh edilen vergi ve cezalara ilişkin vergi davası açılmış olup, bu aşamada herhangi bir ödeme yapılmamıştır.'' denildi.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı. Vietnam.vn Endonezya, bir dizi gıda zehirlenmesi vakasının ardından ücretsiz yemek programıyla ilgili soruşturma başlattı.</t>
+          <t>Say Yenilenebilir Enerji'ye vergi cezası Say Yenilenebilir Enerji'ye vergi cezası RHA Ajans Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş'ye vergi cezası düzenledi. 05 Haziran 2026 - Gündem Say Yenilenebilir Enerji'ye vergi cezası Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş'ye vergi cezası düzenledi. Kamuyu Aydınlatma Platformuna (KAP) yapılan açıklamada, ''Hazine ve Maliye Bakanlığı tarafından 2023 dönemi kurumlar vergisi denetimi ile ilgili olarak yapılan inceleme sonucunda, şirketimize re'sen 16.045.733,46 TL kurumlar vergisi ile bir kat vergi ziyaı cezası ve 5.837.855,57 TL geçici vergiye ilişkin vergi ziyaı cezası düzenlenmiştir. Şirketimiz tarafından tarh edilen vergi ve cezalara ilişkin vergi davası açılmış olup, bu aşamada herhangi bir ödeme yapılmamıştır.'' denildi. Hibya Haber Ajansı YORUM YAP 14 Milletvekili Var, Urfa Çiftçisi Feryat Ediyor Panama’dan İsviçre’deki saldırıya kınama ve dayanışma mesajı Hukuk müşavirliği ve avukatlık sınav yönetmeliği yürürlükten kaldırıldı Meteoroloji’den kuvvetli yağış uyarısı 05 Haziran 2026 - Gündem Say Yenilenebilir Enerji'ye vergi cezası Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş'ye vergi cezası düzenledi. Hibya Haber Ajansı Say Yenilenebilir Enerji'ye vergi cezası Kamuyu Aydınlatma Platformuna (KAP) yapılan açıklamada, ''Hazine ve Maliye Bakanlığı tarafından 2023 dönemi kurumlar vergisi denetimi ile ilgili olarak yapılan inceleme sonucunda, şirketimize re'sen 16.045.733,46 TL kurumlar vergisi ile bir kat vergi ziyaı cezası ve 5.837.855,57 TL geçici vergiye ilişkin vergi ziyaı cezası düzenlenmiştir.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOd0pOZmVyUTBIcklIUzd6UHhReGtvNmsyRTdYRjlTUk05MGRPVUJjYWRfN092cmNGbXR6WXZJMmRjUlgzYXo3OHBfTXNfOUtyeFBLaFlyVVFoaWFkMHIyc19ERTdaV0dIT2pMS3E5Y0ZxMGhlWjQ5UTdHSnB5cnhQNDVfMXl2UGd5bWZ1a0c0TlgtM1lGSmpjb2tQWG9kbHM?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://rhaajans.com/amp/haber/28114821/say-yenilenebilir-enerjiye-vergi-cezasi</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
@@ -7048,25 +7698,53 @@
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr"/>
-      <c r="S48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>Say Yenilenebilir Enerji:292:body+summary+title | Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr"/>
-      <c r="V48" s="2" t="inlineStr"/>
-      <c r="W48" s="2" t="inlineStr"/>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>Say Yenilenebilir Enerji Ekipmanları Sanayi ve Ticaret A.Ş Türkiye</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Say | Sayron Enerji Sanayi ve Ticaret Limited Şirketi | Solares Yenilenebilir Enerji A.Ş</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Say</t>
+        </is>
+      </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y48" s="2" t="inlineStr"/>
-      <c r="Z48" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>100.0 | 68.57142857142857 | 85.71428571428571</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>SAY ELEKTROMEKANİK | Say Profil ve İnox Yer Süzgeçleri</t>
+        </is>
+      </c>
       <c r="AA48" s="2" t="n">
-        <v>103.22</v>
+        <v>161.5</v>
       </c>
       <c r="AB48" s="2" t="n">
         <v>47</v>
@@ -7075,27 +7753,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03 09:38:09</t>
+          <t>2026-06-05 00:19:16</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>gözaltı</t>
+          <t>banka dolandırıcılığı</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı</t>
+          <t>3 yıl veya daha uzun süredir kullanılmayan banka hesapları kapatılabilir: Mali dolandırıcılığı önlemek için riskli hesaplar üzerindeki kontroller sıkılaştırılıyor.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Habertürk</t>
+          <t>3 yıl veya daha uzun süredir kullanılmayan banka hesapları kapatılabilir: Mali dolandırıcılığı önlemek için riskli hesaplar üzerindeki kontroller sıkılaştırılıyor. Vietnam.vn</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -7105,40 +7783,36 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>ticaret</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor 8 kişi ölmüştü... Katliam gibi kazayla ilgili firmadan açıklama! Reha Muhtar yaşamını yitirdi Ticaret Bakanlığı'ndan 7 vize şirketine inceleme Osimhen'e Premier Lig kancası! Kılıçdaroğlu talimat verdi: CHP'li tüm belediyeler denetlenecek Varsa yoksa Can Uzun! İşte G.Saray'ın teklifi 28 yıl sonra eski eşinden özür diledi Jill Biden: Eşime gelen eleştiriler karşısında yıkıldık Sivas'ta Amazon manzarası KVKK kararı ne anlama geliyor? Dünya Kupası'na en çok oyuncu gönderenler! İki genç kadının yürek yakan sonu! BES kişinin geleceğine yatırım yaptığı sistem Prens adalarının kayıp onuncu üyesi! Dünyanın en iyi yoğurtlu yemekleri! Şiddetin failine bayıltan dayak! Annesini öldürdü! Taksiye kafa attı! Avrupalı devleri geride bıraktık Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Bursa'da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor Gün Başlıyor - 1 Haziran 2026 (İstanbul'da Kanye West Rüzgarı) Bursa’nın İnegöl ilçesinde 70 ayrı adrese düzenlenen eş zamanlı uyuşturucu operasyonunda 60 şüpheli, gözaltına alındı. DHA'daki habere göre; Bursa İl Jandarma Komutanlığı Narkotik Suçlarla Mücadele Şube Müdürlüğü ekipleri, uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik çalışma başlattı. Yürütülen çalışma kapsamında, sabah saatlerinde İnegöl ilçesinde yaklaşık 70 adrese eş zamanlı operasyon düzenlendi. Operasyona 500 jandarma personeli katıldı. Adreslerde yapılan aramalarda evler ve eklentileri detaylı şekilde incelenirken, çok miktarda uyuşturucu madde ele geçirildi. Baskınlarda 60 şüpheli, gözaltına alındı. Gözaltına alınan şüphelilerin jandarmadaki işlemlerinin sürdüğü öğrenilirken, soruşturma sürüyor.</t>
+          <t>3 yıl veya daha uzun süredir kullanılmayan banka hesapları kapatılabilir: Mali dolandırıcılığı önlemek için riskli hesaplar üzerindeki kontroller sıkılaştırılıyor. Vietnam.vn</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Son dakika: Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Habertürk Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Operasyonda 60 kişi gözaltına alınırken, çok miktarda uyuşturucu madde ele geçirildi. Şüphelilerin jandarmadaki işlemleri sürüyor Bursa’da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Şüphelilerin jandarmadaki işlemleri sürüyor 8 kişi ölmüştü... Katliam gibi kazayla ilgili firmadan açıklama! Reha Muhtar yaşamını yitirdi Ticaret Bakanlığı'ndan 7 vize şirketine inceleme Osimhen'e Premier Lig kancası! Kılıçdaroğlu talimat verdi: CHP'li tüm belediyeler denetlenecek Varsa yoksa Can Uzun! İşte G.Saray'ın teklifi 28 yıl sonra eski eşinden özür diledi Jill Biden: Eşime gelen eleştiriler karşısında yıkıldık Sivas'ta Amazon manzarası KVKK kararı ne anlama geliyor? Dünya Kupası'na en çok oyuncu gönderenler! Avrupalı devleri geride bıraktık Bursa’da uyuşturucu ticareti operasyonu: 60 gözaltı Bursa'da uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik 70 adrese eş zamanlı operasyon düzenlendi. Şüphelilerin jandarmadaki işlemleri sürüyor Gün Başlıyor - 1 Haziran 2026 (İstanbul'da Kanye West Rüzgarı) Bursa’nın İnegöl ilçesinde 70 ayrı adrese düzenlenen eş zamanlı uyuşturucu operasyonunda 60 şüpheli, gözaltına alındı. DHA'daki habere göre; Bursa İl Jandarma Komutanlığı Narkotik Suçlarla Mücadele Şube Müdürlüğü ekipleri, uyuşturucu ticareti yaptığı değerlendirilen şüphelilere yönelik çalışma başlattı. Yürütülen çalışma kapsamında, sabah saatlerinde İnegöl ilçesinde yaklaşık 70 adrese eş zamanlı operasyon düzenlendi. Operasyona 500 jandarma personeli katıldı. Adreslerde yapılan aramalarda evler ve eklentileri detaylı şekilde incelenirken, çok miktarda uyuşturucu madde ele geçirildi. Baskınlarda 60 şüpheli, gözaltına alındı. Gözaltına alınan şüphelilerin jandarmadaki işlemlerinin sürdüğü öğrenilirken, soruşturma sürüyor.</t>
+          <t>3 yıl veya daha uzun süredir kullanılmayan banka hesapları kapatılabilir: Mali dolandırıcılığı önlemek için riskli hesaplar üzerindeki kontroller sıkılaştırılıyor. 3 yıl veya daha uzun süredir kullanılmayan banka hesapları kapatılabilir: Mali dolandırıcılığı önlemek için riskli hesaplar üzerindeki kontroller sıkılaştırılıyor. Vietnam.vn 3 yıl veya daha uzun süredir kullanılmayan banka hesapları kapatılabilir: Mali dolandırıcılığı önlemek için riskli hesaplar üzerindeki kontroller sıkılaştırılıyor.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_timeout</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://www.haberturk.com/son-dakika-bursada-uyusturucu-ticareti-operasyonu-60-gozalti-3889008</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Bursa | İstanbul | Sivas | Tekirdağ | Van</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl | Saray</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUUlZd2dxdDJKTTB5TkFJd1oxZGE2RG1DdlN5Z0dodEFrZHhnN0dieU5aMmdhNld1eTF6TVBaNnI5LWFkLWpJcG0zbzl2eG5XVGZPZ2VMbm9RR2lzeFVNaVRseTJfV3g4VTNQVm1PY0NSdzBERXpkUENUa0p5UmtGS2VzNTV2Um1CUmRtVlJ3RVp3bHFFMTE5R3RodmhaTjFJTjdJMTlPZ2lkOExoVzU4ekxiNDM1LXVuczQ1MHlnMC1kZVk?oc=5&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -7146,7 +7820,7 @@
       <c r="S49" s="2" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr"/>
@@ -7160,14 +7834,954 @@
       <c r="Y49" s="2" t="inlineStr"/>
       <c r="Z49" s="2" t="inlineStr"/>
       <c r="AA49" s="2" t="n">
-        <v>75.75</v>
+        <v>132.74</v>
       </c>
       <c r="AB49" s="2" t="n">
         <v>48</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:29:46</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>banka dolandırıcılığı</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>SPK’dan bir aracı kurum sahibine 6 ay işlem yasağı</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>SPK’dan bir aracı kurum sahibine 6 ay işlem yasağı Banka Dünyası</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>SPK’dan bir aracı kurum sahibine 6 ay işlem yasağı Banka Dünyası</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>SPK’dan bir aracı kurum sahibine 6 ay işlem yasağı SPK’dan bir aracı kurum sahibine 6 ay işlem yasağı Banka Dünyası SPK’dan bir aracı kurum sahibine 6 ay işlem yasağı Banka Dünyası</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>browser_failed</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOZ1p6Tzd1Z29obnhmMFM2dWhqWjd6SUM2Zkc4ZnRfMHlVSWRmSnFCelVVbnNjR0V3dXRrOXVXVHdlT2RHRThlR3U4YTNEcUFVS05WR0w3MTFUNHdZNzBnU0JPVnZiLVRNZEtFYTVObmVDZ0lBbmprS3hIVjNreFdjUw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AB50" s="2" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 10:10:00</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>banka hesaplarına bloke</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Kara Para / MASAK / Bahis</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Hesabına kaynağı belirsiz 1 trilyon lira geçti: MASAK hesaplarını dondurdu</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Hesabına kaynağı belirsiz 1 trilyon lira geçti: MASAK hesaplarını dondurdu Cumhuriyet</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Balıkesir'de yaşayan ve iş gezisi için Van'a gelen Azerbaycan asıllı Ahmad Jahangard Takalo, banka hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş görünce büyük şaşkınlık yaşadı. Kaynağı belirsiz para nedeniyle tüm hesapları MASAK tarafından dondurulan Takalo, sürecin uzaması halinde iflas edebileceğini söyledi. Balıkesir'de yaşayan ve iş gezisi için Van'a gelen Azerbaycan asıllı Ahmad Jahangard Takalo, banka hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş görünce büyük şaşkınlık yaşadı. Kaynağı belirsiz para nedeniyle tüm hesapları MASAK tarafından dondurulan Takalo, sürecin uzaması halinde iflas edebileceğini söyledi. Balıkesir'de yaşayan ve iş gezisi için Van'a gelen Azerbaycan asıllı Ahmad Jahangard Takalo, banka hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş görünce büyük şaşkınlık yaşadı. Kaynağı belirsiz para nedeniyle tüm hesapları MASAK tarafından dondurulan Takalo, sürecin uzaması halinde iflas edebileceğini söyledi. Yaklaşık 10 yıl önce Türkiye'ye yerleşen Azerbaycan asıllı Ahmad Jahangard Takalo , geçen cumartesi günü Van'da marketten alışveriş yaparken banka kartı hata verdi. En yakın banka şubesine giden Takalo, hesabındaki parayı görünce inanamadı. Nereden geldiğini bilmediği 999 milyar 999 milyon 999 bin 999 TL 99 kuruş para Takalo'nun başına dert oldu. Durumu öğrenmek için bankaya giden Takolu, hayatının şokunu yaşadı. Hesabı, gelen kaynağı belirsiz para trafiği nedeniyle MASAK tarafından donduruldu. Başından geçenleri anlatan Ahmad Jahangard Takalo, yaşadığı durumu hem çok komik hem de bir o kadar korkunç olarak özetledi. Seyahat için Van’a geldiğini söyleyen Takalo, şunları kaydetti: "Ben uluslararası bir mucidim. Türkiye'de iki Ar-Ge şirketim var. Yaşanan süreç hem çok komik hem de bir o kadar korkunç. Bir iş seyahati için Van'a gitmiştim. Alışveriş sırasında kartımın çalışmadığını gördüm. Diğer kartımı kontrol ettiğimde onun da çalışmadığını fark ettim. Muhtemelen kartlarım telefonun yanında kaldığı için manyetik alandan etkilenip bozulduğunu düşündüm. Olay cumartesi günü yaşandı. Hafta sonunun geçmesinin ardından pazartesi sabahı ilk iş olarak kartımı değiştirmek için bankaya gittim ve bu şaşırtıcı olaydan haberdar oldum. Hesabıma gelen para tam 1 trilyon TL, yani 999 milyar 999 milyon 999 bin 999 lira 99 kuruştu. Annemin hesabına da yaklaşık 10 yıl önce benzer bir para transferi yapılmıştı. O dönemde Türkiye'ye yeni gelmiştim. Annemin hesabına 18 milyon lira yatırılmıştı. Ancak olay kısa sürede çözüldü, paranın sahibi bulundu. Biz de parayı iade ettik ve küçük bir ödül bırakıldı.” “HERKES PARA İSTİYOR, HERKES BENİMLE AKRABA OLMAYA BAŞLADI” Hesabına gelen parayla hayatının değiştiğini dile getiren Takalo, "Hayatım 180 derece değişti. Normal hayatımı ve düzenimi özledim. Hesaplarımın kapanması, işlerimin tehlikeye girmesi anlamına geliyor. Faaliyetlerim ciddi şekilde kısıtlandı. Telefon trafiğim arttı. Telefon numaramı değiştirmek zorunda kaldım. Yeni numaramı kimseye vermememe rağmen yoğun şekilde aranmaya başladım. Açıkçası huzurum kalmadı. Herkes para istiyor. Sanki bu parayı kullanabiliyormuşum gibi davranıyorlar. Maalesef bir anda herkes benimle akraba olmaya başladı. Şu an şirketimin avukatı ve şahsi avukatım bu konuyla ilgileniyor. Özellikle şahsi avukatım Emre Sandıkçı, gece gündüz demeden süreci yakından takip ediyor. Allah'tan dileğim, sorunların en kısa sürede çözülmesidir.” "BU SÜREÇ İFLASIMA NEDEN OLABİLİR" Hesabının MASAK tarafından dondurulmasından dolayı mağdur olduğunu söyleyen Takalo, “Hesaplarımın açılmasını istiyorum. Tüm hesaplarım kapalı. Eğer bu süreç bir-iki ay daha devam ederse iflas etmeme neden olabilir. Tek temennim olayın bir an önce aydınlatılması, gerçeklerin ortaya çıkması ve normal hayatıma dönebilmem. Son olarak teşekkür etmek istiyorum. Çevremdeki bazı insanlar para talep etse de bazı dostlarım desteklerini esirgemedi. Van halkı da yaşadığım mağduriyeti görerek elinden geldiğince yardımcı oldu. Umarım bu korkunç olay en kısa sürede çözüme kavuşur” şeklinde konuştu. Hava Durumu Namaz Vakitleri Hesabına kaynağı belirsiz 1 trilyon lira geçti: MASAK hesaplarını dondurdu Takip Et: Paylaş</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Hesabına kaynağı belirsiz 1 trilyon lira geçti: MASAK hesaplarını dondurdu Hesabına kaynağı belirsiz 1 trilyon lira geçti: MASAK hesaplarını dondurdu Cumhuriyet Balıkesir'de yaşayan ve iş gezisi için Van'a gelen Azerbaycan asıllı Ahmad Jahangard Takalo, banka hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş görünce büyük şaşkınlık yaşadı. Kaynağı belirsiz para nedeniyle tüm hesapları MASAK tarafından dondurulan Takalo, sürecin uzaması halinde iflas edebileceğini söyledi. Yaklaşık 10 yıl önce Türkiye'ye yerleşen Azerbaycan asıllı Ahmad Jahangard Takalo , geçen cumartesi günü Van'da marketten alışveriş yaparken banka kartı hata verdi. En yakın banka şubesine giden Takalo, hesabındaki parayı görünce inanamadı. Nereden geldiğini bilmediği 999 milyar 999 milyon 999 bin 999 TL 99 kuruş para Takalo'nun başına dert oldu. Durumu öğrenmek için bankaya giden Takolu, hayatının şokunu yaşadı. Hesabı, gelen kaynağı belirsiz para trafiği nedeniyle MASAK tarafından donduruldu. Başından geçenleri anlatan Ahmad Jahangard Takalo, yaşadığı durumu hem çok komik hem de bir o kadar korkunç olarak özetledi. Seyahat için Van’a geldiğini söyleyen Takalo, şunları kaydetti: "Ben uluslararası bir mucidim. Türkiye'de iki Ar-Ge şirketim var. Yaşanan süreç hem çok komik hem de bir o kadar korkunç. Bir iş seyahati için Van'a gitmiştim. Alışveriş sırasında kartımın çalışmadığını gördüm. Olay cumartesi günü yaşandı. Hafta sonunun geçmesinin ardından pazartesi sabahı ilk iş olarak kartımı değiştirmek için bankaya gittim ve bu şaşırtıcı olaydan haberdar oldum. Hesabıma gelen para tam 1 trilyon TL, yani 999 milyar 999 milyon 999 bin 999 lira 99 kuruştu. Annemin hesabına da yaklaşık 10 yıl önce benzer bir para transferi yapılmıştı. Annemin hesabına 18 milyon lira yatırılmıştı. Ancak olay kısa sürede çözüldü, paranın sahibi bulundu. Biz de parayı iade ettik ve küçük bir ödül bırakıldı.” “HERKES PARA İSTİYOR, HERKES BENİMLE AKRABA OLMAYA BAŞLADI” Hesabına gelen parayla hayatının değiştiğini dile getiren Takalo, "Hayatım 180 derece değişti. Hesaplarımın kapanması, işlerimin tehlikeye girmesi anlamına geliyor. Yeni numaramı kimseye vermememe rağmen yoğun şekilde aranmaya başladım. Açıkçası huzurum kalmadı. Maalesef bir anda herkes benimle akraba olmaya başladı. Şu an şirketimin avukatı ve şahsi avukatım bu konuyla ilgileniyor. Allah'tan dileğim, sorunların en kısa sürede çözülmesidir.” "BU SÜREÇ İFLASIMA NEDEN OLABİLİR" Hesabının MASAK tarafından dondurulmasından dolayı mağdur olduğunu söyleyen Takalo, “Hesaplarımın açılmasını istiyorum. Eğer bu süreç bir-iki ay daha devam ederse iflas etmeme neden olabilir. Tek temennim olayın bir an önce aydınlatılması, gerçeklerin ortaya çıkması ve normal hayatıma dönebilmem. Van halkı da yaşadığım mağduriyeti görerek elinden geldiğince yardımcı oldu. Umarım bu korkunç olay en kısa sürede çözüme kavuşur” şeklinde konuştu. Hava Durumu Namaz Vakitleri Hesabına kaynağı belirsiz 1 trilyon lira geçti: MASAK hesaplarını dondurdu Takip Et: Paylaş</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cumhuriyet.com.tr/turkiye/hesabina-kaynagi-belirsiz-1-trilyon-lira-gecti-masak-hesaplarini-dondurdu-2509250</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Balıkesir | Van</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="AB51" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 10:17:00</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>banka hesaplarına bloke</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Ahmad Jahangard Takalo Kimdir, Kaç Yaşında, Nereli, Ne İş Yapıyor? Banka Hesabındaki 1 Trilyon Lira Olayı Nedir?</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Ahmad Jahangard Takalo Kimdir, Kaç Yaşında, Nereli, Ne İş Yapıyor? Banka Hesabındaki 1 Trilyon Lira Olayı Nedir? Urfanatik</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>banka, banka hesabı</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Ahmad Jahangard Takalo kimdir, kaç yaşında, nereli, ne iş yapıyor, banka hesabındaki 1 trilyon lira olayı nedir, hesapları neden bloke edildi? Van’da yaşayan Azerbaycan asıllı Ahmad Takalo’nun yaşadığı sıra dışı banka süreci, hesabında görülen yüksek bakiye ve hakkında merak edilen tüm ayrıntılar. Ahmad Jahangard Takalo kimdir, kaç yaşında, nereli, ne iş yapıyor, banka hesabındaki 1 trilyon lira olayı nedir, hesapları neden bloke edildi? Van’da yaşayan Azerbaycan asıllı Ahmad Takalo’nun yaşadığı sıra dışı banka süreci, hesabında görülen yüksek bakiye ve hakkında merak edilen tüm ayrıntılar. Ahmad Jahangard Takalo kimdir, kaç yaşında, nereli, ne iş yapıyor, banka hesabındaki 1 trilyon lira olayı nedir, hesapları neden bloke edildi? Van’da yaşayan Azerbaycan asıllı Ahmad Takalo’nun yaşadığı sıra dışı banka süreci, hesabında görülen yüksek bakiye ve hakkında merak edilen tüm ayrıntılar. Ahmad Jahangard Takalo kimdir, kaç yaşında, nereli, ne iş yapıyor, banka hesabındaki 1 trilyon lira olayı nedir, hesapları neden bloke edildi? Van’da yaşayan Azerbaycan asıllı Ahmad Takalo’nun yaşadığı sıra dışı banka süreci, hesabında görülen yüksek bakiye ve hakkında merak edilen tüm ayrıntılar. Van’da yaşayan Ahmad Jahangard Takalo, banka hesabında görülen olağanüstü yüksek bakiye nedeniyle son günlerin en çok araştırılan isimlerinden biri haline geldi. Market alışverişi sırasında banka kartının işlem yapmamasıyla başlayan süreç, kısa sürede sıra dışı bir banka olayına dönüştü. Takalo’nun hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş seviyesinde bir tutarın görüntülendiği, ardından hesaplarına bloke konulduğu aktarıldı. Yaşanan gelişmenin ardından “Ahmad Jahangard Takalo kimdir?”, “Ahmad Takalo nereli?”, “Ahmad Takalo ne iş yapıyor?”, “Ahmad Takalo’nun hesabına para nereden geldi?” ve “Ahmad Takalo’nun hesapları neden bloke edildi?” soruları internet kullanıcıları tarafından yoğun şekilde araştırılmaya başlandı. Ahmad Jahangard Takalo Kimdir? Ahmad Jahangard Takalo, Van’da yaşayan Azerbaycan asıllı bir kişidir. Kamuoyuna yansıyan bilgilere göre 32 yaşındadır ve yaklaşık 10 yıl önce Türkiye’ye yerleşmiştir. Onu geniş kitlelerin tanımasına neden olan olay ise kişisel hayatı ya da mesleki kariyeri değil, banka hesabında görüntülendiği belirtilen yüksek tutar oldu. Takalo hakkında açık kaynaklarda yer alan bilgiler şimdilik sınırlıdır. Mesleği, iş hayatı, ailesi ya da eğitim geçmişine ilişkin doğrulanmış kapsamlı bir bilgi bulunmamaktadır. Bu nedenle hakkında yapılan haberlerde daha çok banka hesabı olayı, bloke süreci ve yaşadığı mağduriyet iddiası öne çıkmaktadır. Ahmad Takalo Kaç Yaşında? Ahmad Jahangard Takalo’nun 32 yaşında olduğu belirtilmektedir. Haberlerde Van’da yaşayan 32 yaşındaki Azerbaycan asıllı Takalo’nun, market alışverişi sırasında kartının hata vermesi üzerine bankaya gittiği ve hesabındaki yüksek bakiyeyi bu şekilde fark ettiği aktarılmıştır. Ahmad Jahangard Takalo Nereli? Ahmad Takalo’nun Azerbaycan asıllı olduğu bilgisi kamuoyuna yansımıştır. Türkiye’ye yaklaşık 10 yıl önce geldiği ve yaşamını Van’da sürdürdüğü ifade edilmektedir. Bu nedenle aramalarda “Ahmad Takalo Azerbaycanlı mı?”, “Ahmad Jahangard Takalo nereli?” ve “Ahmad Takalo Van’da mı yaşıyor?” soruları öne çıkmaktadır. Ahmad Takalo Ne İş Yapıyor? Ahmad Jahangard Takalo’nun mesleğiyle ilgili açık kaynaklarda doğrulanmış net bir bilgi bulunmamaktadır. Haberlerde Takalo’nun kimliğine ilişkin temel bilgiler aktarılırken, iş hayatı veya düzenli mesleği hakkında ayrıntılı bir bilgi p</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Ahmad Jahangard Takalo Kimdir, Kaç Yaşında, Nereli, Ne İş Yapıyor? Banka Hesabındaki 1 Trilyon Lira Olayı Nedir? Ahmad Jahangard Takalo Kimdir, Kaç Yaşında, Nereli, Ne İş Yapıyor? Banka Hesabındaki 1 Trilyon Lira Olayı Nedir? Urfanatik Ahmad Jahangard Takalo kimdir, kaç yaşında, nereli, ne iş yapıyor, banka hesabındaki 1 trilyon lira olayı nedir, hesapları neden bloke edildi? Van’da yaşayan Azerbaycan asıllı Ahmad Takalo’nun yaşadığı sıra dışı banka süreci, hesabında görülen yüksek bakiye ve hakkında merak edilen tüm ayrıntılar. Van’da yaşayan Ahmad Jahangard Takalo, banka hesabında görülen olağanüstü yüksek bakiye nedeniyle son günlerin en çok araştırılan isimlerinden biri haline geldi. Market alışverişi sırasında banka kartının işlem yapmamasıyla başlayan süreç, kısa sürede sıra dışı bir banka olayına dönüştü. Takalo’nun hesabında 999 milyar 999 milyon 999 bin 999 lira 99 kuruş seviyesinde bir tutarın görüntülendiği, ardından hesaplarına bloke konulduğu aktarıldı. Yaşanan gelişmenin ardından “Ahmad Jahangard Takalo kimdir?”, “Ahmad Takalo nereli?”, “Ahmad Takalo ne iş yapıyor?”, “Ahmad Takalo’nun hesabına para nereden geldi?” ve “Ahmad Takalo’nun hesapları neden bloke edildi?” soruları internet kullanıcıları tarafından yoğun şekilde araştırılmaya başlandı. Ahmad Jahangard Takalo Kimdir? Ahmad Jahangard Takalo, Van’da yaşayan Azerbaycan asıllı bir kişidir. Kamuoyuna yansıyan bilgilere göre 32 yaşındadır ve yaklaşık 10 yıl önce Türkiye’ye yerleşmiştir. Onu geniş kitlelerin tanımasına neden olan olay ise kişisel hayatı ya da mesleki kariyeri değil, banka hesabında görüntülendiği belirtilen yüksek tutar oldu. Takalo hakkında açık kaynaklarda yer alan bilgiler şimdilik sınırlıdır. Bu nedenle hakkında yapılan haberlerde daha çok banka hesabı olayı, bloke süreci ve yaşadığı mağduriyet iddiası öne çıkmaktadır. Ahmad Takalo Kaç Yaşında? Ahmad Jahangard Takalo’nun 32 yaşında olduğu belirtilmektedir. Haberlerde Van’da yaşayan 32 yaşındaki Azerbaycan asıllı Takalo’nun, market alışverişi sırasında kartının hata vermesi üzerine bankaya gittiği ve hesabındaki yüksek bakiyeyi bu şekilde fark ettiği aktarılmıştır. Ahmad Jahangard Takalo Nereli? Ahmad Takalo’nun Azerbaycan asıllı olduğu bilgisi kamuoyuna yansımıştır. Türkiye’ye yaklaşık 10 yıl önce geldiği ve yaşamını Van’da sürdürdüğü ifade edilmektedir. Bu nedenle aramalarda “Ahmad Takalo Azerbaycanlı mı?”, “Ahmad Jahangard Takalo nereli?” ve “Ahmad Takalo Van’da mı yaşıyor?” soruları öne çıkmaktadır. Ahmad Takalo Ne İş Yapıyor? Ahmad Jahangard Takalo’nun mesleğiyle ilgili açık kaynaklarda doğrulanmış net bir bilgi bulunmamaktadır.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.urfanatik.com/ahmad-jahangard-takalo-kimdir-kac-yasinda-nereli-ne-is-yapiyor-banka-hesabindaki-1-trilyon-lira-olayi-nedir/amp</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 10:52:06</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>banka hesaplarına bloke</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Banka Hesabında 1 Trilyon Lira Gördü! Yaşadığı Şok Gündem Oldu</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Banka Hesabında 1 Trilyon Lira Gördü! Yaşadığı Şok Gündem Oldu yenidevirgazetesi.com</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>banka, banka hesabı</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Banka Hesabında 1 Trilyon Lira Gördü! Yaşadığı Şok Gündem Oldu yenidevirgazetesi.com</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Banka Hesabında 1 Trilyon Lira Gördü! Yaşadığı Şok Gündem Oldu Banka Hesabında 1 Trilyon Lira Gördü! Yaşadığı Şok Gündem Oldu yenidevirgazetesi.com Banka Hesabında 1 Trilyon Lira Gördü! Yaşadığı Şok Gündem Oldu yenidevirgazetesi.com</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>browser_failed</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOS3U1dTFscDlFVDM5aEQxblBSdExYZmJBbjdHa3VWaVJwWEZLYmhKYlNxcFNFQ18xQmZ1OHowQnZMN3dTOXZuYXFKYUExRzRKZGNFV3hRdEdNMXRxVjZMeXMtVzBMa2pFaFJ1UE1kRFd4LXFBMnBvYjRJNTRoOEtBZkwzRnFKUnJhQk0xYUVocElvaWd3TUJ2TVF2VTkyZnVLV2ZPVEdFNjQyUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="AB53" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:08:45</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ödeme kuruluşu</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>ABD’nin Dev Bankaları 2027’de Yeni Bir Blockchain Girişimi Başlatmaya Hazırlanıyor! İşte Detaylar</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>ABD’nin Dev Bankaları 2027’de Yeni Bir Blockchain Girişimi Başlatmaya Hazırlanıyor! İşte Detaylar Bitcoin Sistemi</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>ABD’nin Dev Bankaları 2027’de Yeni Bir Blockchain Girişimi Başlatmaya Hazırlanıyor! İşte Detaylar Bitcoin Sistemi</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>ABD’nin Dev Bankaları 2027’de Yeni Bir Blockchain Girişimi Başlatmaya Hazırlanıyor! İşte Detaylar ABD’nin Dev Bankaları 2027’de Yeni Bir Blockchain Girişimi Başlatmaya Hazırlanıyor! İşte Detaylar Bitcoin Sistemi ABD’nin Dev Bankaları 2027’de Yeni Bir Blockchain Girişimi Başlatmaya Hazırlanıyor! İşte Detaylar Bitcoin Sistemi</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>browser_failed</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZEX1A1TVRHbjV0TVBta3c0RTIxQ01xTzYtMVJaeFpkY190RUU4M0VxMldWV09fQ3d4cXF4UEVDZmVvWmFNNHh0cVNURzNrTmg2OG95anR6cXRqZk5RVFU4NmFybmZyOXJWTDJfRVJuR2w4VDUxVWJqd0QxM3FWN2dYT0M5SmQ0cHhvckdZR0RoRHdPTUVNc2ZMb2ktNkkxY3hlc0pqUGtEVlFRNVl3RGIwV0FMV3FhTmw3YzFicG1QMERw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="AB54" s="2" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 06:55:00</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>banka soruşturma</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>6 aylık takip Şanlıurfa'da şebekenin sonu oldu; Banka ve kripto ağına darbe!</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>6 aylık takip Şanlıurfa'da şebekenin sonu oldu; Banka ve kripto ağına darbe! Şanlıurfa Gazetesi</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Nevşehir merkezli Şanlıurfa dahil 27 ilde yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı operasyonda gözaltına alınan 93 şüpheliden 79'u tutuklanarak cezaevine gönderildi. Emniyetin 6 aylık çalışmaları sonuç verdi. Nevşehir merkezli Şanlıurfa dahil 27 ilde yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı operasyonda gözaltına alınan 93 şüpheliden 79'u tutuklanarak cezaevine gönderildi. Emniyetin 6 aylık çalışmaları sonuç verdi. Nevşehir merkezli Şanlıurfa dahil 27 ilde yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı operasyonda gözaltına alınan 93 şüpheliden 79'u tutuklanarak cezaevine gönderildi. Emniyetin 6 aylık çalışmaları sonuç verdi. 6 aylık takip Şanlıurfa'da şebekenin sonu oldu; Banka ve kripto ağına darbe! Nevşehir merkezli Şanlıurfa dahil 27 ilde yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı operasyonda gözaltına alınan 93 şüpheliden 79'u tutuklanarak cezaevine gönderildi. Emniyetin 6 aylık çalışmaları sonuç verdi. 05.06.2026 - 09:55 Yayınlanma 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Nevşehir Cumhuriyet Başsavcılığı koordinesinde, Nevşehir İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğü ekiplerince yasa dışı bahis faaliyetlerine yönelik yaklaşık 6 ay süren teknik, fiziki ve mali takip gerçekleştirildi. Yapılan çalışmalarda yasa dışı bahis sitelerinde kullanılan banka hesapları ve IBAN numaraları detaylı şekilde incelendi. Yürütülen soruşturmada bahis organizasyonlarında kullanılan hesapların sahipleri belirlenirken, yaklaşık 10 milyar TL hacmindeki suç gelirinin hareketleri de takip edildi. Teknik ve mali incelemelerde yasa dışı bahis gelirlerinin banka hesaplarından şüphelilere ait kripto para hesaplarına aktarıldığı tespit edildi. Para transferlerinin izlenmesine yönelik çalışmaların sürdüğü öğrenildi. Soruşturma kapsamında paranın nakline aracılık ettiği değerlendirilen toplam 107 şüpheli belirlendi. Bunun üzerine Nevşehir merkezli İstanbul, Diyarbakır, Mardin, Bursa, Batman, Adana, Kırıkkale, Ankara, İzmir, Van, Antalya, Gaziantep, Hakkâri, Mersin, Şanlıurfa, Manisa, Aydın, Hatay, Karaman, Kütahya, Malatya, Niğde, Düzce, Siirt, Şırnak, Tokat ve Yalova'da eş zamanlı operasyon düzenlendi. Toplam 120 adrese yönelik gerçekleştirilen operasyonlara 550 polis katıldı. Operasyonlarda 93 şüpheli yakalanarak gözaltına alınırken, 14 şüphelinin yakalanmasına yönelik çalışmaların sürdüğü bildirildi. Şanlıurfa’da Göbeklitepe yolunda Buğday Tarlasında Yangın: İtfaiye Ekipleri Bölgeye Sevk Ediliyor İçeriği Görüntüle Operasyon kapsamında bir şüpheliye ait adreste yapılan aramada 1 milyon 500 bin TL nakit para ele geçirilirken, 1 tabanca, tabancaya ait 7 fişek ve çok sayıda dijital materyale el konuldu. Emniyetteki işlemlerinin tamamlanmasının ardından adliyeye sevk edilen 93 şüpheliden 79'u çıkarıldıkları mahkemece tutuklanarak cezaevine gönderildi. Şüphelilerden 9'u adli kontrol şartıyla serbest bırakılırken, 5 kişi ise savcılık tarafından serbest bırakıldı. Soruşturmanın çok yönlü olarak sürdürüldüğü bildirildi. Kaynak: İHA Editörün Seçtiği 2026 Yılı ÇKS Başvuruları 31 Aralık 2025’te Sona Eriyor Editörün Seçtiği Şanlıurfa’dan Gelen Kampçılar Hakkari’de Temel Kayak Eğitimine Katıldı Editörün Seçtiği Şanlıurfa’da Sahipsiz Hayvanlar İçin Çalışmalar Hız Kesmeden Devam Ediyor Bunlar</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>6 aylık takip Şanlıurfa'da şebekenin sonu oldu; Banka ve kripto ağına darbe! 6 aylık takip Şanlıurfa'da şebekenin sonu oldu; Banka ve kripto ağına darbe! Şanlıurfa Gazetesi Nevşehir merkezli Şanlıurfa dahil 27 ilde yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı operasyonda gözaltına alınan 93 şüpheliden 79'u tutuklanarak cezaevine gönderildi. Emniyetin 6 aylık çalışmaları sonuç verdi. 6 aylık takip Şanlıurfa'da şebekenin sonu oldu; Banka ve kripto ağına darbe! 05.06.2026 - 09:55 Yayınlanma 1 Dk Okunma Süresi</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sanliurfagazetesi.com/6-aylik-takip-sanliurfada-sebekenin-sonu-oldu-banka-ve-kripto-agina-darbe</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Nevşehir | Şanlıurfa</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="AB55" s="2" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 06:11:00</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>banka soruşturma</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Çeyrek asırlık banka satıldı! Arkasındaki isim tanıdık çıktı</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Çeyrek asırlık banka satıldı! Arkasındaki isim tanıdık çıktı Internet Haber</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>www.internethaber.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.internethaber.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.internethaber.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Çeyrek asırlık banka satıldı! Arkasındaki isim tanıdık çıktı Çeyrek asırlık banka satıldı! Arkasındaki isim tanıdık çıktı Internet Haber www.internethaber.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.internethaber.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.internethaber.com/ceyrek-asirlik-banka-satildi-arkasindaki-isim-tanidik-cikti-2445734h.htm</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="AB56" s="2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 16:59:00</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>elektronik para ve ödeme kuruluşu</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding Banka Sahibi Oldu İşte Detaylar</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding Banka Sahibi Oldu İşte Detaylar Çay Haber</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>banka, holding</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş | şirket / firma</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Geçtiğimiz yıl yürütülen büyük çaplı yasa dışı bahis soruşturması kapsamında yönetimi Tasarruf Mevduatı Sigorta Fonu’na (TMSF) devredilen BankPozitif'in satış süreci resmen tamamlandı Geçtiğimiz yıl yürütülen büyük çaplı yasa dışı bahis soruşturması kapsamında yönetimi Tasarruf Mevduatı Sigorta Fonu’na (TMSF) devredilen BankPozitif'in satış süreci resmen tamamlandı Geçtiğimiz yıl yürütülen büyük çaplı yasa dışı bahis soruşturması kapsamında yönetimi Tasarruf Mevduatı Sigorta Fonu’na (TMSF) devredilen BankPozitif'in satış süreci resmen tamamlandı Çay Devi Efor Holding Banka Sahibi Oldu İşte Detaylar Geçtiğimiz yıl yürütülen büyük çaplı yasa dışı bahis soruşturması kapsamında yönetimi Tasarruf Mevduatı Sigorta Fonu’na (TMSF) devredilen BankPozitif'in satış süreci resmen tamamlandı HABER MERKEZİ Editör 04.06.2026 - 19:59 Yayınlanma 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Bankanın yüzde 97’lik hisse paketi, Rize merkezli Efor Holding tarafından satın alındı. Şubat ayında gerçekleştirilen ihale sonucunda BankPozitif’in çoğunluk hisselerini almaya hak kazanan Efor Holding, gerekli idari ve yasal onayların tamamlanmasının ardından bankanın tek kontrol sahibi oldu. Rekabet Kurumu’ndan Onay Rekabet Kurumu tarafından bugün yapılan açıklamada, satış işleminin resmen onaylandığı duyuruldu. Açıklamada, “7145 sayılı Bazı Kanun Hükmünde Kararnamelerde Değişiklik Yapılmasına Dair Kanun’un Geçici 2. maddesi uyarınca Tasarruf Mevduatı Sigorta Fonu’nun kayyım olarak görevlendirildiği BankPozitif Kredi ve Kalkınma Bankası AŞ sermayesinin belirli bir kısmının ve tek kontrolünün Efor Holding AŞ tarafından devralınması işlemine izin verilmiştir” ifadelerine yer verildi. Köy Okulunda Başlayan Hikaye Dev Bir Şölene Dönüştü: Rize’de 4. Su Roketi Yarışması Coşkusu! İçeriği Görüntüle Efor Holding Bankacılık Sektörüne Girdi Efor Çay ve Ofçay markalarıyla tanınan Rize merkezli Efor Holding, bu satın almayla birlikte bankacılık sektörüne önemli bir adım atmış oldu. Öte yandan, Bankacılık Düzenleme ve Denetleme Kurumu (BDDK) tarafından 17 Mart 2025 tarihinde alınan kararla, BankPozitif’in Pay Fix Elektronik Para ve Ödeme Hizmetleri AŞ mülkiyetinde bulunan yüzde 79 oranındaki hissesine ilişkin temettü hariç ortaklık haklarının TMSF tarafından kullanılmasına karar verilmişti. Son olarak Rekabet Kurumu’nun onayıyla birlikte satış süreci tamamlanırken, BankPozitif’in yeni sahibi resmen Efor Holding oldu. Kaynak: HABER MERKEZİ Editörün Seçtiği Karadeniz Sahil Yolu'nda 'ters yön' kazası; 2 ölü, 3 yaralı Editörün Seçtiği İyidere'de kıyı temizliği etkinliği gerçekleştirildi Editörün Seçtiği Ovit Dağı'nda haziranda kar keyfi yaşanıyor Bunla</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding Banka Sahibi Oldu İşte Detaylar Çay Devi Efor Holding Banka Sahibi Oldu İşte Detaylar Çay Haber Geçtiğimiz yıl yürütülen büyük çaplı yasa dışı bahis soruşturması kapsamında yönetimi Tasarruf Mevduatı Sigorta Fonu’na (TMSF) devredilen BankPozitif'in satış süreci resmen tamamlandı Geçtiğimiz yıl yürütülen büyük çaplı yasa dışı bahis soruşturması kapsamında yönetimi Tasarruf Mevduatı Sigorta Fonu’na (TMSF) devredilen BankPozitif'in satış süreci resmen tamamlandı Geçtiğimiz yıl yürütülen büyük çaplı yasa dışı bahis soruşturması kapsamında yönetimi Tasarruf Mevduatı Sigorta Fonu’na (TMSF) devredilen BankPozitif'in satış süreci resmen tamamlandı Çay Devi Efor Holding Banka Sahibi Oldu İşte Detaylar Geçtiğimiz yıl yürütülen büyük çaplı yasa dışı bahis soruşturması kapsamında yönetimi Tasarruf Mevduatı Sigorta Fonu’na (TMSF) devredilen BankPozitif'in satış süreci resmen tamamlandı HABER MERKEZİ Editör 04.06.2026 - 19:59 Yayınlanma 1 Dk Okunma Süresi Pa</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cayhaber.net/cay-devi-efor-holding-banka-sahibi-oldu-iste-detaylar</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding | Efor Holding AŞ</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding:292:body+summary+title | Efor Holding AŞ:raw_legal</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>Çay Devi Efor Holding Türkiye | Efor Holding AŞ Türkiye</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Efor Çay San. Tic. A.Ş. Marmara Bölge Müdürlüğü | EFOR HOLDİNG</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>Efor Çay San. Tic. A.Ş. Marmara Bölge Müdürlüğü</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>100 | 100</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="n">
+        <v>161.25</v>
+      </c>
+      <c r="AB57" s="2" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:18:14</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>gözaltı</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Kaçak tütün ticareti yapan şebekeye operasyon: 22 gözaltı</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Kaçak tütün ticareti yapan şebekeye operasyon: 22 gözaltı DHA | Demirören Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>ticaret</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>05.06.2026 - 08:18 DHA Derya EVREN KORKMAZ / İSTANBUL, (DHA)- İstanbul'da kaçak tütün ve tütün mamulleri ticareti yaptığı belirlenen suç örgütüne yönelik düzenlenen operasyonda 22 şüpheli gözaltına alındı. Operasyonda milyonlarca makaron, tonlarca tütün ve çok sayıda kaçak ürün ele geçirildi. İstanbul emniyeti Kaçakçılık Suçlarla Mücadele Şube Müdürlüğü ekipleri, Bakırköy Cumhuriyet Başsavcılığı koordinesinde suç işlemek amacıyla örgüt kurmak, yönetmek ve örgüt faaliyeti kapsamında kaçakçılık suçlarının önlenmesine yönelik çalışma yürüttü. Yapılan çalışmalarda, örgütlü şekilde kaçak tütün ve tütün mamulleri ticareti yaparak haksız kazanç elde ettikleri ve devleti vergi kaybına uğrattıkları belirlenen şüpheliler takibe alındı. Çalışmalarını tamamlayan ekipler İstanbul ve Adıyaman'da belirlenen adreslere eş zamanlı operasyon düzenlendi. Operasyonda 22 şüpheli gözaltına alındı. Adreslerde yapılan aramalarda 1 milyon 762 bin 600 boş makaron, 684 bin 800 dolu makaron, 1 ton 486 kilogram kıyılmış tütün, 1 milyon 277 bin 338 sigara sarma kağıdı, 9 bin boş sigara paketi, 6 bin 520 paket gümrük kaçağı sigara, 237 kilogram nargile tütünü, 3 bin 923 paket elektronik sigara tütünü, 5 bin 786 puro, 511 elektronik sigara ve nargile cihazı, 195 elektronik sigara likiti, 4 kompresör, 8 sigara sarma makinesi ile hassas terazi ele geçirildi. Son</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Kaçak tütün ticareti yapan şebekeye operasyon: 22 gözaltı Kaçak tütün ticareti yapan şebekeye operasyon: 22 gözaltı DHA | Demirören Haber Ajansı 05.06.2026 - 08:18 DHA Derya EVREN KORKMAZ / İSTANBUL, (DHA)- İstanbul'da kaçak tütün ve tütün mamulleri ticareti yaptığı belirlenen suç örgütüne yönelik düzenlenen operasyonda 22 şüpheli gözaltına alındı. Operasyonda milyonlarca makaron, tonlarca tütün ve çok sayıda kaçak ürün ele geçirildi. İstanbul emniyeti Kaçakçılık Suçlarla Mücadele Şube Müdürlüğü ekipleri, Bakırköy Cumhuriyet Başsavcılığı koordinesinde suç işlemek amacıyla örgüt kurmak, yönetmek ve örgüt faaliyeti kapsamında kaçakçılık suçlarının önlenmesine yönelik çalışma yürüttü. Yapılan çalışmalarda, örgütlü şekilde kaçak tütün ve tütün mamulleri ticareti yaparak haksız kazanç elde ettikleri ve devleti vergi kaybına uğrattıkları belirlenen şüpheliler takibe alındı. Çalışmalarını tamamlayan ekipler İstanbul ve Adıyaman'da belirlenen adreslere eş zamanlı operasyon düzenlendi. Operasyonda 22 şüpheli gözaltına alındı. Adreslerde yapılan aramalarda 1 milyon 762 bin 600 boş makaron, 684 bin 800 dolu makaron, 1 ton 486 kilogram kıyılmış tütün, 1 milyon 277 bin 338 sigara sarma kağıdı, 9 bin boş sigara paketi, 6 bin 520 paket gümrük kaçağı sigara, 237 kilogram nargile tütünü, 3 bin 923 paket elektronik sigara tütünü, 5 bin 786 puro, 511 elektronik sigara ve nargile cihazı, 195 elektronik sigara likiti, 4 kompresör, 8 sigara sarma makinesi ile hassas terazi ele geçirildi.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article_dom</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPSFVBWmhndmhyRVRwU0Q2OWN4S3h4bDVqRk5OdExzazlHUXJxQlUzcTR4U1VRaDY3cUlxNEE2U1RlbTJLOXAtSFVNamdmdXNuNjBiOHliXzMyTk1mc1Q2ZGJGYWhIOE1EWVhkMFFveXJzTXRzOWlTTkpNVkpIMUxLd01OZ3hZMEp3ajBTWmExTk5mWGVoY21hZ3RXamJOd1N5d280T1930gGmAUFVX3lxTE9IVUFaaGd2aHJFVHBTRDY5Y3hLeHhsNWpGTk50THNrOUdRcnFCVTNxNHhTVVFoNjdxSXE0QTZTVGVtMks5cC1IVU1qZ2Z1c242MGI4eWJfMzJOTWZzVDZkYkZhaEg4TURZWGQwUW95cnNNdHM5aVNOSk1WSkgxTEt3TU5neFkwSndqMFNaYTFOTmZYZWhjbWFndFdqYk53U3l3bzRPX3c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Adıyaman | İstanbul</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="AB58" s="2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:11:57</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>gözaltı</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Ankara’da kaçakçılara darbe! Araçtan çıkanlar şaşkına çevirdi! Ünlü markaların taklitleriyle ticaret yapıyorlardı! 3 gözaltı</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Ankara’da kaçakçılara darbe! Araçtan çıkanlar şaşkına çevirdi! Ünlü markaların taklitleriyle ticaret yapıyorlardı! 3 gözaltı Sabah</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>ticaret</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Samsun'un Atakum ilçesinde apartmanın 5’inci katındaki dairenin penceresinden beton zemine düşen 1,5 yaşındaki Ebrar Yardımcı, hayatını kaybetti. Olay, saat 16.30 sıralarında Mevlana Mahallesi 732. Sokak'ta meydana geldi. 1,5 yaşındaki Ebrar Yardımcı, iddiaya göre annesi lavaboda olduğu sırada... Samsun'un Atakum ilçesinde apartmanın 5’inci katındaki dairenin penceresinden beton zemine düşen 1,5 yaşındaki Ebrar Yardımcı, hayatını kaybetti. Olay, saat 16.30 sıralarında Mevlana Mahallesi 732. Sokak'ta meydana geldi. 1,5 yaşındaki Ebrar Yardımcı, iddiaya göre annesi lavaboda olduğu sırada... Haberin devamı... Giriş Tarihi: 4.06.2026 17:11 Son Güncelleme: 4.06.2026 18:54 Bu acıya yürek dayanmaz! 5’inci kattan düşen bebek hayatını kaybetti Samsun'un Atakum ilçesinde apartmanın 5’inci katındaki dairenin penceresinden beton zemine düşen 1,5 yaşındaki Ebrar Yardımcı, hayatını kaybetti. Olay, saat 16.30 sıralarında Mevlana Mahallesi 732. Sokak'ta meydana geldi. 1,5 yaşındaki Ebrar Yardımcı, iddiaya göre annesi lavaboda olduğu sırada 5'inci kattaki evlerinin penceresinden beton zemine düştü. İhbar üzerine olay yerine polis ve sağlık ekipleri sevk edildi. Sağlık ekibinin ilk müdahalesi sonrası ambulans ile özel hastaneye kaldırılan ağır yaralı bebek, doktorların müdahalesine rağmen kurtarılamadı. Polis, olaya ilgili soruşturma başlattı Sabah.com.tr Uygulamamızı İndirin</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Ankara’da kaçakçılara darbe! Araçtan çıkanlar şaşkına çevirdi! Ünlü markaların taklitleriyle ticaret yapıyorlardı! 3 gözaltı Ankara’da kaçakçılara darbe! Araçtan çıkanlar şaşkına çevirdi! Ünlü markaların taklitleriyle ticaret yapıyorlardı! 3 gözaltı Sabah Samsun'un Atakum ilçesinde apartmanın 5’inci katındaki dairenin penceresinden beton zemine düşen 1,5 yaşındaki Ebrar Yardımcı, hayatını kaybetti. Olay, saat 16.30 sıralarında Mevlana Mahallesi 732. 1,5 yaşındaki Ebrar Yardımcı, iddiaya göre annesi lavaboda olduğu sırada... Giriş Tarihi: 4.06.2026 17:11 Son Güncelleme: 4.06.2026 18:54 Bu acıya yürek dayanmaz! 5’inci kattan düşen bebek hayatını kaybetti Samsun'un Atakum ilçesinde apartmanın 5’inci katındaki dairenin penceresinden beton zemine düşen 1,5 yaşındaki Ebrar Yardımcı, hayatını kaybetti. 1,5 yaşındaki Ebrar Yardımcı, iddiaya göre annesi lavaboda olduğu sırada 5'inci kattaki evlerinin penceresinden beton zemine düştü. İhbar üzerine olay yerine polis ve sağlık ekipleri sevk edildi. Sağlık ekibinin ilk müdahalesi sonrası ambulans ile özel hastaneye kaldırılan ağır yaralı bebek, doktorların müdahalesine rağmen kurtarılamadı. Polis, olaya ilgili soruşturma başlattı Sabah.com.tr Uygulamamızı İndirin</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sabah.com.tr/yasam/bu-aciya-yurek-dayanmaz-5inci-kattan-dusen-bebek-hayatini-kaybetti-7596687</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Ankara | Samsun</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Atakum</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>30 sıralarında Mevlana Mahallesi</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="AB59" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB49"/>
+  <autoFilter ref="A1:AB59"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -7217,6 +8831,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,22 +512,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 13:08:00</t>
+          <t>2026-06-08 07:20:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı</t>
+          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Malatya Güncel</t>
+          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu İhlas Haber Ajansı IHA</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -537,12 +537,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Isparta | Konya</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Silivri</t>
+          <t>Beyşehir</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -556,22 +556,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 08:45:00</t>
+          <t>2026-06-08 06:36:39</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Görkem Duman'ın savunması: "Örgüt Üyesi Değilim, Mal Varlığım Azaldı!"</t>
+          <t>Beyşehir'deki yangında depo ve garaj kullanılamaz hale geldi</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Görkem Duman'ın savunması: "Örgüt Üyesi Değilim, Mal Varlığım Azaldı!" dokuzeylul.com</t>
+          <t>Beyşehir'deki yangında depo ve garaj kullanılamaz hale geldi Haberler</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -579,8 +579,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Konya</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Beyşehir</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
@@ -592,7 +600,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:04:00</t>
+          <t>2026-06-08 07:23:58</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -602,12 +610,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA! Bursa Osmangazi’de Fabrika Yangını: Alevler Gökyüzünü Kapladı, Ekipler Müdahale Ediyor!</t>
+          <t>Konya'da depo yangını mahalleliyi sokağa döktü</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA! Bursa Osmangazi’de Fabrika Yangını: Alevler Gökyüzünü Kapladı, Ekipler Müdahale Ediyor! politikam.com</t>
+          <t>Konya'da depo yangını mahalleliyi sokağa döktü havadis.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -617,12 +625,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Konya</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Osmangazi</t>
+          <t>Beyşehir</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -636,7 +644,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:58:41</t>
+          <t>2026-06-08 08:10:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -646,12 +654,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Ayancık'ta Fabrika Depo Yangını</t>
+          <t>Konya’da korkutan yangın! Garaj ve depo kullanılamaz hale geldi</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ayancık'ta Fabrika Depo Yangını sondakika.com</t>
+          <t>Konya’da korkutan yangın! Garaj ve depo kullanılamaz hale geldi Anadolu'da Bugün</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -661,14 +669,10 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sinop</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Ayancık</t>
-        </is>
-      </c>
+          <t>Konya</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
@@ -680,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 05:40:01</t>
+          <t>2026-06-07 14:21:02</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -690,12 +694,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Plastik Eşya Deposunda Yangın</t>
+          <t>Sinop Ayancık'ta, Fabrikada çıkan yangın söndürüldü!</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Plastik Eşya Deposunda Yangın sondakika.com</t>
+          <t>Sinop Ayancık'ta, Fabrikada çıkan yangın söndürüldü! | Gündem Haber Meydan</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -705,45 +709,41 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Sinop</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi</t>
+          <t>Ayancık</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Yildiz Plastik Geri Dönüşüm</t>
-        </is>
-      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:06:33</t>
+          <t>2026-06-07 11:24:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Yetkililer, Hai Phong'daki bir ağaç işleme fabrikasında çıkan yangını hızla kontrol altına aldı.</t>
+          <t>Denizli'de "change" operasyonu: 11 lüks araca el konuldu, 3 tutuklama!</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Yetkililer, Hai Phong'daki bir ağaç işleme fabrikasında çıkan yangını hızla kontrol altına aldı. Vietnam.vn</t>
+          <t>Denizli'de "change" operasyonu: 11 lüks araca el konuldu, 3 tutuklama! gazetesehir.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -751,7 +751,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Denizli</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
@@ -764,22 +768,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 16:04:00</t>
+          <t>2026-06-08 07:24:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de şafak operasyonu! Elektronik para şirketine bahis baskını</t>
+          <t>Denizli'nin 'Change araç' çetesi 11 lüks otomobile el konuldu</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de şafak operasyonu! Elektronik para şirketine bahis baskını Demokrat Kocaeli</t>
+          <t>Denizli'nin 'Change araç' çetesi 11 lüks otomobile el konuldu Manşet Aydın</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -804,22 +808,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 05:32:00</t>
+          <t>2026-06-07 14:23:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Sultangazi'de korkutan yangın : Plastik eşya deposu alevlere teslim oldu</t>
+          <t>Dev hava yolu şirketi Europen Cargo resmen iflas etti: Jet yakıtı krizi büyüyor</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Sultangazi'de korkutan yangın : Plastik eşya deposu alevlere teslim oldu İşçi Haber</t>
+          <t>Dev hava yolu şirketi Europen Cargo resmen iflas etti: Jet yakıtı krizi büyüyor Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -827,47 +831,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Çanakkale | İstanbul</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Sultangazi</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Yildiz Plastik Geri Dönüşüm</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 14:13:31</t>
+          <t>2026-06-07 12:03:20</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Balıkesir-İzmir Karayolunda Depo Yangını: Ekipler Seferber Oldu</t>
+          <t>Havacılıkta kriz büyüyor: Ünlü havayolu şirketi de iflas bayrağını çekti!</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Balıkesir-İzmir Karayolunda Depo Yangını: Ekipler Seferber Oldu Balıkesir Haberci Gazetesi</t>
+          <t>Havacılıkta kriz büyüyor: Ünlü havayolu şirketi de iflas bayrağını çekti! GZT</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -888,22 +880,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 07:42:00</t>
+          <t>2026-06-07 15:23:53</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Yangın Merdivenleri Depoya Döndü: Hayati kaçış yolları işgal altında</t>
+          <t>Hürmüz Boğazı krizi bir şirketi daha vurdu: Dev uçak firması iflas etti!</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Yangın Merdivenleri Depoya Döndü: Hayati kaçış yolları işgal altında Gazete Detay</t>
+          <t>Hürmüz Boğazı krizi bir şirketi daha vurdu: Dev uçak firması iflas etti! GZT</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -924,22 +916,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:40:00</t>
+          <t>2026-06-08 07:38:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Niğde’de depo yangını korkuttu</t>
+          <t>Rahmi Koç'un "Kürt kadın fıkrasına" tepkiler sürüyor: Diyarbakır'da Koç Holding'e ait bankaya silahlı saldırı</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Niğde’de depo yangını korkuttu DMC Haber</t>
+          <t>Rahmi Koç'un "Kürt kadın fıkrasına" tepkiler sürüyor: Diyarbakır'da Koç Holding'e ait bankaya silahlı saldırı T24</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -949,37 +941,45 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Niğde</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>Antalya | Diyarbakır | İstanbul | İzmir</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:47:39</t>
+          <t>2026-06-07 12:27:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Sinop'ta fabrikanın depo bölümünde çıkan yangın hasara neden oldu</t>
+          <t>Buca belediyesinde 'bankamatik sevgili' İddiaları: SGK müfettiş raporu savcılıkta!</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sinop'ta fabrikanın depo bölümünde çıkan yangın hasara neden oldu Haberler</t>
+          <t>Buca belediyesinde 'bankamatik sevgili' İddiaları: SGK müfettiş raporu savcılıkta! Son Mühür</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -989,14 +989,10 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Sinop</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Ayancık</t>
-        </is>
-      </c>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
@@ -1008,22 +1004,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 06:20:58</t>
+          <t>2026-06-08 05:25:00</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Kars Polisi Banka Personeli ve Güvenlikçileri Bilgilendirdi: Şüpheli İşlemlerde Jet İhbar Dönemi</t>
+          <t>100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kars Polisi Banka Personeli ve Güvenlikçileri Bilgilendirdi: Şüpheli İşlemlerde Jet İhbar Dönemi igdirhaber.net</t>
+          <t>100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti Ekonomim</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1033,18 +1029,26 @@
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:25:00</t>
+          <t>2026-06-08 06:24:00</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1054,12 +1058,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Şimşek ‘Büyüyoruz’ Dedi, Son İki Günde 6 Şirket Konkordato İlan Etti</t>
+          <t>Dünya devine büyük şok: 6 kıtaya ihracat yapan Türk sanayi devi iflas etti!</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Şimşek ‘Büyüyoruz’ Dedi, Son İki Günde 6 Şirket Konkordato İlan Etti Habererk.com</t>
+          <t>Dünya devine büyük şok: 6 kıtaya ihracat yapan Türk sanayi devi iflas etti! Bursada Bugün</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1067,20 +1071,32 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 08:23:00</t>
+          <t>2026-06-08 06:25:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1090,12 +1106,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Gıda ve kahve şirketine 3 aylık konkordato mühleti</t>
+          <t>15 yıllık sanayi devi iflas etti! 100 ülkeye hizmet veriyordu</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Gıda ve kahve şirketine 3 aylık konkordato mühleti odakgazetesi.com</t>
+          <t>15 yıllık sanayi devi iflas etti! 100 ülkeye hizmet veriyordu Haber 7</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1105,18 +1121,26 @@
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Nokta Elektronik Medya A.Ş | Patrop Group İnşaat Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Nokta Elektronik ve Bilişim Sistemleri</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 17:34:27</t>
+          <t>2026-06-08 08:13:19</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1126,12 +1150,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'ün yarım asırlık tekstil devi iflas etti!</t>
+          <t>Kocaeli’de 3 şirket için konkordato süresi uzatıldı</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'ün yarım asırlık tekstil devi iflas etti! İnegöl Online</t>
+          <t>Kocaeli’de 3 şirket için konkordato süresi uzatıldı Kocaeli Barış Gazetesi</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1141,34 +1165,22 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Bursa | Çanakkale | Karabük</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl | Yenice</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Güzel Dağ Tekstil</t>
-        </is>
-      </c>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:36:22</t>
+          <t>2026-06-07 12:25:00</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1178,12 +1190,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Mahkemeden karar çıktı: Bursa’da üretim devi iflas etti</t>
+          <t>Mahkeme kararıyla üretim devinin iflası açıklandı!</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mahkemeden karar çıktı: Bursa’da üretim devi iflas etti Bursa Hayat Gazetesi</t>
+          <t>Mahkeme kararıyla üretim devinin iflası açıklandı! Manisa Kulis Haber</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1197,33 +1209,41 @@
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Güzeldağ Tekstil</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:14</t>
+          <t>2026-06-08 06:35:00</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Turizm sezonunda dolandırıcılık yöntemlerini tespit etme.</t>
+          <t>Dev alüminyum fabrikası iflas etti</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Turizm sezonunda dolandırıcılık yöntemlerini tespit etme. Vietnam.vn</t>
+          <t>Dev alüminyum fabrikası iflas etti Afyon Haber</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1244,7 +1264,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:34:11</t>
+          <t>2026-06-08 08:52:00</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1254,12 +1274,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Banka ve ATM'lerde Bilgilendirme Yapıldı.. Kars'ta Dolandırıcılığa Karşı Uyarı!</t>
+          <t>Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Banka ve ATM'lerde Bilgilendirme Yapıldı.. Kars'ta Dolandırıcılığa Karşı Uyarı! PolitiKARS</t>
+          <t>Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI Sakarya Yenihaber</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1269,7 +1289,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Kars</t>
+          <t>Sakarya</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1284,22 +1304,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 11:14:50</t>
+          <t>2026-06-07 14:50:16</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan 'Yeşil ve Geleceğin Şehirleri Projesi' için finansman</t>
+          <t>Ticaret Bakanlığından Kurban Bayramı Öncesi Dijital Dolandırıcılık Uyarısı</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan 'Yeşil ve Geleceğin Şehirleri Projesi' için finansman Ekonomi Gazetesi</t>
+          <t>Ticaret Bakanlığından Kurban Bayramı Öncesi Dijital Dolandırıcılık Uyarısı basvur.co</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1320,22 +1340,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 04:57:39</t>
+          <t>2026-06-07 14:12:47</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>3 yıl sonra kullanılmayan banka hesaplarının devre dışı bırakılması önerisi.</t>
+          <t>IATA, birçok havayolu şirketinin iflas riskiyle karşı karşıya olduğu konusunda uyarıda bulundu.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3 yıl sonra kullanılmayan banka hesaplarının devre dışı bırakılması önerisi. Vietnam.vn</t>
+          <t>IATA, birçok havayolu şirketinin iflas riskiyle karşı karşıya olduğu konusunda uyarıda bulundu. Vietnam.vn</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1356,22 +1376,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 08:37:17</t>
+          <t>2026-06-08 09:12:22</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>İBB iştiraki İSTTELKOM’a operasyon: Dijital materyallere el konuldu</t>
+          <t>Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>İBB iştiraki İSTTELKOM’a operasyon: Dijital materyallere el konuldu velev.press</t>
+          <t>Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı soL Haber</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1379,35 +1399,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul | Antalya</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Kepez | Maltepe</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding | Gelenek Basım Yayım ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 18:45:07</t>
+          <t>2026-06-08 06:14:59</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>KPK, banka bildirim hizmetlerindeki yolsuzluk iddialarını soruşturuyor</t>
+          <t>Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>KPK, banka bildirim hizmetlerindeki yolsuzluk iddialarını soruşturuyor samsunsporluyuz.com</t>
+          <t>Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı PolitiKARS</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1415,8 +1447,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul | Şırnak</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Cizre</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
@@ -1428,7 +1468,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 13:40:54</t>
+          <t>2026-06-08 08:48:31</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1438,12 +1478,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Kişisel verilerin sızdırılması ve banka hesaplarının ele geçirilmesi riskine karşı uyarı.</t>
+          <t>Diyarbakır'da banka şubesine silahlı saldırı! Gece yarısı ateş açıldı, polis ekipleri saldırganı arıyor</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Kişisel verilerin sızdırılması ve banka hesaplarının ele geçirilmesi riskine karşı uyarı. Vietnam.vn</t>
+          <t>Diyarbakır'da banka şubesine silahlı saldırı! Gece yarısı ateş açıldı, polis ekipleri saldırganı arıyor A Haber</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1451,8 +1491,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
@@ -1464,7 +1512,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 19:30:00</t>
+          <t>2026-06-08 08:07:00</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1474,12 +1522,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>24 yıllık banka el değiştirdi! Yeni sahibi belli oldu</t>
+          <t>Koç Grubu'na bir saldırı daha: Banka şubesini kurşunladılar!</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24 yıllık banka el değiştirdi! Yeni sahibi belli oldu Aydın Ses Gazetesi</t>
+          <t>Koç Grubu'na bir saldırı daha: Banka şubesini kurşunladılar! Haber Hürriyeti</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1487,8 +1535,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Antalya | Diyarbakır | İstanbul</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
@@ -1500,7 +1556,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:29:00</t>
+          <t>2026-06-08 05:49:49</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1510,12 +1566,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan Türkiye'ye 191,5 Milyon Euro Finansman</t>
+          <t>İstanbul merkezli 6 ilde banka ATM'lerine sahte dolar yatıran şebeke çökertildi: 9 kişi yakalandı</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan Türkiye'ye 191,5 Milyon Euro Finansman Paranın Yönü</t>
+          <t>İstanbul merkezli 6 ilde banka ATM'lerine sahte dolar yatıran şebeke çökertildi: 9 kişi yakalandı Sabah</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1523,7 +1579,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1536,7 +1596,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 18:24:37</t>
+          <t>2026-06-08 07:50:00</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1546,12 +1606,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti</t>
+          <t>Rahmi Koç'un fıkrası krize döndü! Bu kez banka hedef alındı: Diyarbakır'da Yapı Kredi binasına silahlı saldırı</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti Haberhergün</t>
+          <t>Rahmi Koç'un fıkrası krize döndü! Bu kez banka hedef alındı: Diyarbakır'da Yapı Kredi binasına silahlı saldırı SuperHaber</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1559,7 +1619,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1572,7 +1636,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 01:00:00</t>
+          <t>2026-06-08 05:30:00</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1582,12 +1646,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ATM’de kartını unutanlar yandı! önce kartı aramayın, bankayı arayın</t>
+          <t>60 Ay Vadeli Konut Kredisi Şaşırttı: 2 Milyon TL İçin Bankaların Yeni Oranları Netleşti!</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ATM’de kartını unutanlar yandı! önce kartı aramayın, bankayı arayın YeniSöke Gazetesi</t>
+          <t>60 Ay Vadeli Konut Kredisi Şaşırttı: 2 Milyon TL İçin Bankaların Yeni Oranları Netleşti! Afyon Ana Haber</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1595,16 +1659,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Aydın</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Efeler</t>
-        </is>
-      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
@@ -1616,7 +1672,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 14:34:00</t>
+          <t>2026-06-08 08:45:54</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1626,12 +1682,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>HAZİRAN 2026 İHTİYAÇ KREDİSİ FAİZ ORANLARI: BANKA BANKA GÜNCEL LİSTE</t>
+          <t>Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>HAZİRAN 2026 İHTİYAÇ KREDİSİ FAİZ ORANLARI: BANKA BANKA GÜNCEL LİSTE Bugün Kocaeli Gazetesi</t>
+          <t>Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor Medya Ege</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1652,22 +1708,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:56:23</t>
+          <t>2026-06-08 05:27:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Orman ürünleri fabrikasında yangın paniği</t>
+          <t>Banka ATM'lerini kullanan sahte para çetesi yakalandı</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Orman ürünleri fabrikasında yangın paniği Yeniçağ Gazetesi</t>
+          <t>Banka ATM'lerini kullanan sahte para çetesi yakalandı Aydınlık</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1688,7 +1744,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 17:35:00</t>
+          <t>2026-06-08 06:35:01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1698,12 +1754,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır yangın: Yenişehir’de oto tamir atölyesinde hasar oluştu</t>
+          <t>Bafra'da Sanayi Sitesinde Yangın</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır yangın: Yenişehir’de oto tamir atölyesinde hasar oluştu 24 Saat Gazetesi Ankara</t>
+          <t>Bafra'da Sanayi Sitesinde Yangın Son Dakika</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1713,12 +1769,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Bursa | Diyarbakır | Mersin</t>
+          <t>Artvin | Samsun | Çankırı</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Yenişehir</t>
+          <t>Kızılırmak | Bafra</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -1732,22 +1788,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 05:28:00</t>
+          <t>2026-06-08 07:03:00</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Meydana Gelen Plastik Eşya Deposundaki Yangında Maddi Hasar Oluştu</t>
+          <t>Son Dakika: Ziraat Bankası'ndan 1 Milyon liralık SMS Alanlar Paniğe Kapıldı! Sistem mi Hacklendi?</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Meydana Gelen Plastik Eşya Deposundaki Yangında Maddi Hasar Oluştu Mersin Haber</t>
+          <t>Son Dakika: Ziraat Bankası'ndan 1 Milyon liralık SMS Alanlar Paniğe Kapıldı! Sistem mi Hacklendi? Afyon Ana Haber</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1755,51 +1811,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Sultangazi</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Meydana Gelen Plastik</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>PLASTPET AMBALAJ - Plastik Polyester Çember Satış</t>
-        </is>
-      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 10:36:00</t>
+          <t>2026-06-08 07:21:00</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kullanılmayan akaryakıt istasyonunda yangın</t>
+          <t>Ayyıldız Teams mesajı vatandaşı yatağından fırlattı! Ziraat Bankası’nda sabaha karşı 1 Milyon TL'lik SMS şoku! Müşteri hizmetlerine ulaşılamıyor... Kim bu Ayyıldız Teams?</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Kullanılmayan akaryakıt istasyonunda yangın Tigris Haber</t>
+          <t>Ayyıldız Teams mesajı vatandaşı yatağından fırlattı! Ziraat Bankası’nda sabaha karşı 1 Milyon TL'lik SMS şoku! Müşteri hizmetlerine ulaşılamıyor... Kim bu Ayyıldız Teams? SuperHaber</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1807,11 +1847,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Batman</t>
-        </is>
-      </c>
+      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1824,22 +1860,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:16:14</t>
+          <t>2026-06-08 07:44:00</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de iş insanı Rahmi Koç'un hastane açılışındaki sözlerine ilişkin soruşturma başlatıldı</t>
+          <t>Ziraat Bankası Müşterileri Dikkat! SMS Sistemi Hacklendi mi?</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de iş insanı Rahmi Koç'un hastane açılışındaki sözlerine ilişkin soruşturma başlatıldı Anadolu Ajansı</t>
+          <t>Ziraat Bankası Müşterileri Dikkat! SMS Sistemi Hacklendi mi? Özgün Kocaeli Gazetesi</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1847,11 +1883,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
@@ -1861,8 +1893,128 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:01:43</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası'nda 1 Milyonluk Sahte İşlem Mesajları Vatandaşı Panikletti!</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası'nda 1 Milyonluk Sahte İşlem Mesajları Vatandaşı Panikletti! haber.com</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 06:43:01</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı Yeni Şafak</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07 20:42:00</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik gözaltında…</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik gözaltında… Enerji Günlüğü</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik Teknoloji</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J35"/>
+  <autoFilter ref="A1:J38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -1898,6 +2050,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1909,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB35"/>
+  <dimension ref="A1:AB38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2087,27 +2242,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 13:08:00</t>
+          <t>2026-06-08 07:20:06</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı</t>
+          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Malatya Güncel</t>
+          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu İhlas Haber Ajansı IHA</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2117,41 +2272,49 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Malatya Güncel</t>
+          <t>... Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde ASAYİŞ - 08 Haziran 2026 Pazartesi 10:20 Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu A A A Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde çıktı. Edinilen bilgiye göre, mahalle sakinlerinden N.G.’ye ait garaj ve depo olarak kullanılan yapıda henüz belirlenemeyen bir nedenle yangın başladı. Alevleri fark eden vatandaşların ihbarı üzerine adrese Kurucuova, Yeşildağ ve Beyşehir’den itfaiye ekiplerinin yanı sıra Isparta’nın Yenişarbademli ilçesinden de ekipler sevk edildi. Ekiplerin müdahalesi sayesinde yangın çevredeki evlere sıçramadan kontrol altına alındı. Yangının söndürülmesinin ardından soğutma çalışmaları gerçekleştirildi. Can kaybı ya da yaralanmanın yaşanmadığı yangında garaj ve depo olarak kullanılan yapıda büyük çapta maddi hasar meydana geldi. İtfaiye ekiplerinin yaptığı ilk incelemede, yangının elektrik kablolarının aşırı ısınmasından kaynaklandığının belirlendiği öğrenildi. Yangınla ilgili tahkikat sürüyor. Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde çıktı. Edinilen bilgiye göre, mahalle sakinlerinden N.G.’ye ait garaj ve depo olarak kullanılan yapıda henüz belirlenemeyen bir nedenle yangın başladı. Alevleri fark eden vatandaşların ihbarı üzerine adrese Kurucuova, Yeşildağ ve Beyşehir’den itfaiye ekiplerinin yanı sıra Isparta’nın Yenişarbademli ilçesinden de ekipler sevk edildi. Ekiplerin müdahalesi sayesinde yangın çevredeki evlere sıçramadan kontrol altına alındı. Yangının söndürülmesinin ardından soğutma çalışmaları gerçekleştirildi. Can kaybı ya da yaralanmanın yaşanmadığı yangında garaj ve depo olarak kullanılan yapıda büyük çapta maddi hasar meydana geldi. İtfaiye ekiplerinin yaptığı ilk incelemede, yangının elektrik kablolarının aşırı ısınmasından kaynaklandığının belirlendiği öğrenildi. Yangınla ilgili tahkikat sürüyor. Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde çıktı. Edinilen bilgiye göre, mahalle sakinlerinden N.G.’ye ait garaj ve depo olarak kullanılan yapıda henüz belirlenemeyen bir nedenle yangın başladı. Alevleri fark eden vatandaşların ihbarı üzerine adrese Kurucuova, Yeşildağ ve Beyşehir’den itfaiye ekiplerinin yanı sıra Isparta’nın Yenişarbademli ilçesinden de ekipler sevk edildi. Ekiplerin müdahalesi sayesinde yangın çevredeki evlere sıçramadan kontrol altına alındı. Yangının söndürülmesinin ardından soğutma çalışmaları gerçekleştirildi. Can kaybı ya da yaralanmanın yaşanmadığı yangında garaj ve depo olarak kullanılan yapıda büyük çapta maddi hasar meydana geldi. İtfaiye ekiplerinin yaptığı ilk incelemede, yangının elektrik kablolarının aşırı ısınmasından kaynaklandığının belirlendiği öğrenildi. Yangınla ilgili tahkikat sürüyor.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Malatya Güncel Silivri’de hayvan barınağı adı altında vurgun yapan derneğin MASAK raporu ortaya çıktı Malatya Güncel</t>
+          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu İhlas Haber Ajansı Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu İhlas Haber Ajansı IHA Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde ASAYİŞ - 08 Haziran 2026 Pazartesi 10:20 Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu A A A Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde çıktı. Edinilen bilgiye göre, mahalle sakinlerinden N.G.’ye ait garaj ve depo olarak kullanılan yapıda henüz belirlenemeyen bir nedenle yangın başladı. Alevleri fark eden vatandaşların ihbarı üzerine adrese Kurucuova, Yeşildağ ve Beyşehir’den itfaiye ekiplerinin yanı sıra Isparta’nın Yenişarbademli ilçesinden de ekipler sevk edildi. Ekiplerin müdahalesi sayesinde yangın çevredeki evlere sıçramadan kontrol altına alındı. Yangının söndürülmesinin ardından soğutma çalışmaları gerçekleştirildi. Can kaybı ya da yaralanmanın yaşanmadığı yangında garaj ve depo olarak kullanılan yapıda büyük çapta maddi hasar meydana geldi. İtfaiye ekiplerinin yaptığı ilk incelemede, yangının elektrik kablolarının aşırı ısınmasından kaynaklandığının belirlendiği öğrenildi. Yangınla ilgili tahkikat sürüyor. Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>browser_error</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWWdQbE9jWHZOUGFfN3d5VGpNWUgyYnMwamdHMTlPbmpjSjVlNVRzVFFxVkNBQkdGNU11LXhNUkxfNWs5ZDYyT0NYbGpWcFlfNGwzcnByVjRkbTk5bGR2Z2VtZzRKNksxbVRQQ1VIRHJnUjZhckludGFuNlFUN3duWGRtLWNLN0oxN0tuRkhJWlZXTElwMTAzeDlpVGw2UWRDaDVDZ3lyLUhFNWw1MU01RmdNb3Jqazd3aGdOdWJDMNIBxAFBVV95cUxQY2owaWdJRmUtc0NJWlFzbEJ0SzFZN1lpYzBDNkxDbDNPMDdRQnBZNlFtZ2JabE5vem5sUDg5aWlGaHdXM1RFNUNRUWVjSVZNcDRXU1lFdGVaa05hdlFZNGp4RU14dTIzQWNKenc3QjlHVVUxalJfRTRlVlRBclhXX09fbXFwWUpHeXFyRk4tOExxZVlHOUg2LXFwUnhGVGQyaEV1UzlFMF85YU1sc2NaWWc1YnlCQUZvd3pGNENpT3VNTEdK?oc=5&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+          <t>https://www.iha.com.tr/konya-haberleri/konyada-depo-olarak-kullanilan-alanda-cikan-yangin-korkuttu-435313933</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Isparta | Konya</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Silivri</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
+          <t>Beyşehir</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>ilçeye bağlı Kurucuova Mahallesi</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
@@ -2172,7 +2335,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="n">
-        <v>113.26</v>
+        <v>131.25</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -2181,27 +2344,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 08:45:00</t>
+          <t>2026-06-08 06:36:39</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MASAK raporu</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Görkem Duman'ın savunması: "Örgüt Üyesi Değilim, Mal Varlığım Azaldı!"</t>
+          <t>Beyşehir'deki yangında depo ve garaj kullanılamaz hale geldi</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Görkem Duman'ın savunması: "Örgüt Üyesi Değilim, Mal Varlığım Azaldı!" dokuzeylul.com</t>
+          <t>Beyşehir'deki yangında depo ve garaj kullanılamaz hale geldi Haberler</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2211,32 +2374,44 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>mal varlığı</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Görkem Duman'ın savunması: "Örgüt Üyesi Değilim, Mal Varlığım Azaldı!" dokuzeylul.com</t>
+          <t>Konya'nın Beyşehir ilçesinde henüz belirlenemeyen nedenle çıkan yangında bir depo ve garaj kullanılamaz hale geldi. İtfaiye ekiplerinin hızlı müdahalesiyle yangın çevredeki evlere sıçramadan söndürüldü, can kaybı yaşanmadı. Konya'nın Beyşehir ilçesinde henüz belirlenemeyen nedenle çıkan yangında bir depo ve garaj kullanılamaz hale geldi. İtfaiye ekiplerinin hızlı müdahalesiyle yangın çevredeki evlere sıçramadan söndürüldü, can kaybı yaşanmadı. Konya'nın Beyşehir ilçesinde henüz belirlenemeyen nedenle çıkan yangında bir depo ve garaj kullanılamaz hale geldi. İtfaiye ekiplerinin hızlı müdahalesiyle yangın çevredeki evlere sıçramadan söndürüldü, can kaybı yaşanmadı. Beyşehir'deki yangında depo ve garaj kullanılamaz hale geldi Konya'nın Beyşehir ilçesinde henüz belirlenemeyen nedenle çıkan yangında bir depo ve garaj kullanılamaz hale geldi. İtfaiye ekiplerinin hızlı müdahalesiyle yangın çevredeki evlere sıçramadan söndürüldü, can kaybı yaşanmadı.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Görkem Duman'ın savunması: "Örgüt Üyesi Değilim, Mal Varlığım Azaldı!" Görkem Duman'ın savunması: "Örgüt Üyesi Değilim, Mal Varlığım Azaldı!" dokuzeylul.com Görkem Duman'ın savunması: "Örgüt Üyesi Değilim, Mal Varlığım Azaldı!" dokuzeylul.com</t>
+          <t>Beyşehir'deki yangında depo ve garaj kullanılamaz hale geldi Beyşehir'deki yangında depo ve garaj kullanılamaz hale geldi Haberler Konya'nın Beyşehir ilçesinde henüz belirlenemeyen nedenle çıkan yangında bir depo ve garaj kullanılamaz hale geldi. İtfaiye ekiplerinin hızlı müdahalesiyle yangın çevredeki evlere sıçramadan söndürüldü, can kaybı yaşanmadı. Beyşehir'deki yangında depo ve garaj kullanılamaz hale geldi Konya'nın Beyşehir ilçesinde henüz belirlenemeyen nedenle çıkan yangında bir depo ve garaj kullanılamaz hale geldi.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQbk9lSUszcWZoLWV6WUViWlBiUzBZUzJwSDdqc3FtLXBLeFhsNGQwbnVSWWZDVWR0bnRtcUlZZHktMy1qRnlpejJzM2JfcG9rd2plXzNrZHFtS2JNaENQRlhLSTFLVGRGWmExSFlJX1FOYmU1cHhyQ0JtUHJmbzJFVDExd254QWh3OFZLa01aNmtiMlRKSmVYYXFkTXc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>https://www.haberler.com/amp/beysehir-de-depo-ve-garajda-yangin-buyuk-hasar-19923203-haberi/</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Konya</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Beyşehir</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -2244,7 +2419,7 @@
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
@@ -2258,7 +2433,7 @@
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>2</v>
@@ -2267,12 +2442,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:04:00</t>
+          <t>2026-06-08 07:23:58</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2282,12 +2457,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA! Bursa Osmangazi’de Fabrika Yangını: Alevler Gökyüzünü Kapladı, Ekipler Müdahale Ediyor!</t>
+          <t>Konya'da depo yangını mahalleliyi sokağa döktü</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA! Bursa Osmangazi’de Fabrika Yangını: Alevler Gökyüzünü Kapladı, Ekipler Müdahale Ediyor! politikam.com</t>
+          <t>Konya'da depo yangını mahalleliyi sokağa döktü havadis.com</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2297,22 +2472,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Bursa Osmangazi’de bir boya fabrikasında yangın çıktı. Küçükbalıklı Mahallesi'ndeki fabrikada ekiplerin müdahalesi sonrası son durum ne? Detaylar haberimizde. Bursa Osmangazi’de bir boya fabrikasında yangın çıktı. Küçükbalıklı Mahallesi'ndeki fabrikada ekiplerin müdahalesi sonrası son durum ne? Detaylar haberimizde. Bursa Osmangazi’de bir boya fabrikasında yangın çıktı. Küçükbalıklı Mahallesi'ndeki fabrikada ekiplerin müdahalesi sonrası son durum ne? Detaylar haberimizde. SON DAKİKA! Bursa Osmangazi’de Fabrika Yangını: Alevler Gökyüzünü Kapladı, Ekipler Müdahale Ediyor! Bursa Osmangazi’de bir boya fabrikasında yangın çıktı. Küçükbalıklı Mahallesi'ndeki fabrikada ekiplerin müdahalesi sonrası son durum ne? Detaylar haberimizde. AA Editör 06.06.2026 - 12:04 Yayınlanma 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Bursa'da Fabrika Yangını: Alevler Kısa Sürede Büyüdü! Bursa’nın Osmangazi ilçesinde bulunan bir boya fabrikasında, henüz belirlenemeyen bir nedenle yangın çıktı. Kısa sürede fabrikanın büyük bir bölümünü etkisi altına alan alevler, bölgede büyük paniğe yol açtı. Çevreden yükselen dumanları fark eden vatandaşların ihbarı üzerine bölgeye çok sayıda ekip sevk edildi. Hızla Müdahale Edildi Küçükbalıklı Mahallesi'nde bulunan fabrikada başlayan yangın için olay yerine itfaiye, AFAD, sağlık ve polis ekipleri intikal etti. İtfaiye ekiplerinin yoğun ve koordineli çalışması sonucu yangın, fabrikanın diğer bölümlerine sıçramadan kontrol altına alındı. Bölgedeki güvenlik önlemleri polis ekiplerince artırılırken, sağlık ekipleri olası bir dumandan etkilenme durumuna karşı hazır bekletildi. Soğutma Çalışmaları Sürüyor Yangının kontrol altına alınmasının ardından itfaiye ekipleri, alevlerin yeniden alevlenme riskine karşı fabrika içerisinde soğutma çalışmalarına başladı. Yangının çıkış nedeninin belirlenmesi için teknik ekiplerin detaylı inceleme yapacağı öğrenilirken, fabrikada maddi hasar meydana geldiği belirtildi. Muhabir: AA Editör Hakkında AA Bu</t>
+          <t>Beyşehir'de bir depoda çıkan yangın paniğe yol açtı. Ekipler alevlerin evlere sıçramasını son anda önledi. Beyşehir'de bir depoda çıkan yangın paniğe yol açtı. Ekipler alevlerin evlere sıçramasını son anda önledi. Beyşehir'de bir depoda çıkan yangın paniğe yol açtı. Ekipler alevlerin evlere sıçramasını son anda önledi. Beyşehir'de bir depoda çıkan yangın paniğe yol açtı. Ekipler alevlerin evlere sıçramasını son anda önledi. Facebook'ta Paylaş X'de Paylaş Whatsapp'tan Gönder YAYINLAMA: 08 Haziran 2026 - 10:23 EDİTÖR: Haber Editörü KAYNAK: İhlas Haber Ajansı Konya'nın Beyşehir ilçesinde bir garaj ve depoda başlayan yangın, çevre sakinlerini korkuttu. Alevler kısa sürede büyürken, çevre ilçelerden gelen itfaiye ekipleri büyük bir müdahale gerçekleştirdi. Alevlerin çıkış nedeni İtfaiye ekiplerinin yaptığı inceleme, yangının elektrik kablolarının aşırı ısınmasıyla başladığını gösterdi. Kurucuova, Yeşildağ ve Beyşehir'in yanı sıra Isparta'nın Yenişarbademli ilçesinden gelen ekipler, yangını evlere ulaşmadan kontrol altına aldı. Bölge halkı için sonuç Olayda herhangi bir can kaybı veya yaralanma yaşanmadı. Ancak depo ve içerisindeki eşyalar tamamen kullanılamaz hale geldi. Elektrik tesisatınızın eski olduğunu düşünüyorsanız, bir uzmana kontrol ettirmeniz olası benzer risklerin önüne geçebilir. Ekipler şu an bölgedeki soğutma çalışmalarını tamamladı ve olayla ilgili inceleme devam ediyor. Yetişkin halinin temeli çocuklukta atılıyor #Konya / 08 Haziran 2026 Konya’nın gizli doğa rotası Mavi Boğaz keşfedilmeyi bekliyor #Konya / 07 Haziran 2026 Konya’da eş dehşeti İşine giden kadını sokak ortasında vurdu #Konya / 06 Haziran 2026 Yoru</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA! Bursa Osmangazi’de Fabrika Yangını: Alevler Gökyüzünü Kapladı, Ekipler Müdahale Ediyor! SON DAKİKA! Bursa Osmangazi’de Fabrika Yangını: Alevler Gökyüzünü Kapladı, Ekipler Müdahale Ediyor! politikam.com Bursa Osmangazi’de bir boya fabrikasında yangın çıktı. Küçükbalıklı Mahallesi'ndeki fabrikada ekiplerin müdahalesi sonrası son durum ne? Bursa Osmangazi’de Fabrika Yangını: Alevler Gökyüzünü Kapladı, Ekipler Müdahale Ediyor! AA Editör 06.06.2026 - 12:04 Yayınlanma 1 Dk Okunma Süresi P</t>
+          <t>Konya'da depo yangını mahalleliyi sokağa döktü Konya'da depo yangını mahalleliyi sokağa döktü havadis.com Beyşehir'de bir depoda çıkan yangın paniğe yol açtı. Ekipler alevlerin evlere sıçramasını son anda önledi.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2322,24 +2497,20 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.politikam.com/son-dakika-bursa-osmangazide-fabrika-yangini-alevler-gokyuzunu-kapladi-ekipler-mudahale-ediyor</t>
+          <t>https://www.havadis.com/konya/konyada-depo-yangini-mahalleliyi-sokaga-doktu/418735</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Konya</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Osmangazi</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Küçükbalıklı Mahallesi</t>
-        </is>
-      </c>
+          <t>Beyşehir</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
@@ -2360,7 +2531,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="n">
-        <v>158.75</v>
+        <v>88.5</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>3</v>
@@ -2369,12 +2540,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:58:41</t>
+          <t>2026-06-08 08:10:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2384,12 +2555,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ayancık'ta Fabrika Depo Yangını</t>
+          <t>Konya’da korkutan yangın! Garaj ve depo kullanılamaz hale geldi</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ayancık'ta Fabrika Depo Yangını sondakika.com</t>
+          <t>Konya’da korkutan yangın! Garaj ve depo kullanılamaz hale geldi Anadolu'da Bugün</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2399,22 +2570,22 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>depo, fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>fabrika | depo</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Sinop'un Ayancık ilçesindeki fabrika depo yangını, itfaiye ekipleri tarafından kontrol altına alındı. Sinop'un Ayancık ilçesindeki fabrika depo yangını, itfaiye ekipleri tarafından kontrol altına alındı. Sinop'un Ayancık ilçesindeki fabrika depo yangını, itfaiye ekipleri tarafından kontrol altına alındı. Ayancık'ta Fabrika Depo Yangını Son Güncelleme: 06.06.2026 23:58 Sinop'un Ayancık ilçesindeki fabrika depo yangını, itfaiye ekipleri tarafından kontrol altına alındı. Sinop 'un Ayancık ilçesinde bir fabrikanın depo bölümünde çıkan yangın söndürüldü. İlçe merkezi Çayiçi Mahallesi'ndeki Sanayi Sitesi'nde faaliyet gösteren orman ürünleri üretimi yapan bir fabrikanın talaş deposunda yangın çıktı. Depodan dumanların yükseldiğini gören vatandaşların ihbarı üzerine olay yerine itfaiye ve emniyet ekipleri sevk edildi. Ayancık Belediyesi İtfaiye ekipleri ve Orman İşletme Müdürlüğü arazözleriyle müdahale edilen yangın, fabrikanın diğer bölümlerine sıçramadan söndürüldü. Yangın sonrası depoda hasar oluştu. Kaynak: AA Sinop 'un Ayancık ilçesinde bir fabrikanın depo bölümünde çıkan yangın söndürüldü. İlçe merkezi Çayiçi Mahallesi'ndeki Sanayi Sitesi'nde faaliyet gösteren orman ürünleri üretimi yapan bir fabrikanın talaş deposunda yangın çıktı. Depodan dumanların yükseldiğini gören vatandaşların ihbarı üzerine olay yerine itfaiye ve emniyet ekipleri sevk edildi. Ayancık Belediyesi İtfaiye ekipleri ve Orman İşletme Müdürlüğü arazözleriyle müdahale edilen yangın, fabrikanın diğer bölümlerine sıçramadan söndürüldü. Yangın sonrası depoda hasar oluştu. Ayancık'ta Fabrika Depo Yangını Sinop'un Ayancık ilçesindeki fabrika depo yangını, itfaiye ekipleri tarafından kontrol altına alındı. Sinop 'un Ayancık ilçesinde bir fabrikanın depo bölümünde çıkan yangın söndürüldü. İlçe merkezi Çayiçi Mahallesi'ndeki Sanayi Sitesi'nde faaliyet gösteren orman ürünleri üretimi yapan bir fabrikanın talaş deposunda yangın çıktı. Depodan dumanların yükseldiğini gören vatandaşların ihbarı üzerine olay yerine itfaiye ve emniyet ekipleri sevk edildi. Ayancık Belediyesi İtfaiye ekipleri ve Orman İşletme Müdürlüğü arazözleriyle müdahale edilen yangın, fabrikanın diğer bölümlerine sıçramadan söndürüldü. Yangın sonrası depoda hasar oluştu.</t>
+          <t>anadoludabugun.com.tr Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. anadoludabugun.com.tr adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. anadoludabugun.com.tr adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Ayancık'ta Fabrika Depo Yangını Ayancık'ta Fabrika Depo Yangını sondakika.com Sinop'un Ayancık ilçesindeki fabrika depo yangını, itfaiye ekipleri tarafından kontrol altına alındı. Ayancık'ta Fabrika Depo Yangını Son Güncelleme: 06.06.2026 23:58 Sinop'un Ayancık ilçesindeki fabrika depo yangını, itfaiye ekipleri tarafından kontrol altına alındı. Sinop 'un Ayancık ilçesinde bir fabrikanın depo bölümünde çıkan yangın söndürüldü. İlçe merkezi Çayiçi Mahallesi'ndeki Sanayi Sitesi'nde faaliyet gösteren orman ürünleri üretimi yapan bir fabrikanın talaş deposunda yangın çıktı. Depodan dumanların yükseldiğini gören vatandaşların ihbarı üzerine olay yerine itfaiye ve emniyet ekipleri sevk edildi. Ayancık Belediyesi İtfaiye ekipleri ve Orman İşletme Müdürlüğü arazözleriyle müdahale edilen yangın, fabrikanın diğer bölümlerine sıçramadan söndürüldü. Yangın sonrası depoda hasar oluştu. Kaynak: AA Sinop 'un Ayancık ilçesinde bir fabrikanın depo bölümünde çıkan yangın söndürüldü. Ayancık'ta Fabrika Depo Yangını Sinop'un Ayancık ilçesindeki fabrika depo yangını, itfaiye ekipleri tarafından kontrol altına alındı.</t>
+          <t>Konya’da korkutan yangın! Garaj ve depo kullanılamaz hale geldi Konya’da korkutan yangın! Garaj ve depo kullanılamaz hale geldi Anadolu'da Bugün anadoludabugun.com.tr Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. anadoludabugun.com.tr adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. anadoludabugun.com.tr adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2424,31 +2595,23 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.sondakika.com/amp/haber-ayancik-ta-fabrika-depo-yangini-19919905/</t>
+          <t>https://anadoludabugun.com.tr/konya-haberleri/konyada-korkutan-yangin-garaj-ve-depo-kullanilamaz-hale-geldi/416391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Sinop</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Ayancık</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>İlçe merkezi Çayiçi Mahallesi | ndeki Sanayi Sitesi</t>
-        </is>
-      </c>
+          <t>Konya</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr"/>
@@ -2462,7 +2625,7 @@
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="n">
-        <v>99.75</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>4</v>
@@ -2471,12 +2634,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 05:40:01</t>
+          <t>2026-06-07 14:21:02</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2486,12 +2649,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Plastik Eşya Deposunda Yangın</t>
+          <t>Sinop Ayancık'ta, Fabrikada çıkan yangın söndürüldü!</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Plastik Eşya Deposunda Yangın sondakika.com</t>
+          <t>Sinop Ayancık'ta, Fabrikada çıkan yangın söndürüldü! | Gündem Haber Meydan</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -2501,94 +2664,66 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de çıkan yangın sonrası itfaiye müdahale etti, can kaybı yok, maddi hasar var. Sultangazi'de çıkan yangın sonrası itfaiye müdahale etti, can kaybı yok, maddi hasar var. Sultangazi'de çıkan yangın sonrası itfaiye müdahale etti, can kaybı yok, maddi hasar var. Sultangazi'de Plastik Eşya Deposunda Yangın Son Güncelleme: 07.06.2026 08:40 Sultangazi'de çıkan yangın sonrası itfaiye müdahale etti, can kaybı yok, maddi hasar var. Sultangazi 'de tek katlı plastik eşya deposu sabah saatlerinde alevlere teslim oldu. Bölgede yoğun duman oluşurken, itfaiye ekiplerinin geniş kapsamlı müdahalesi sonrası yangın söndürüldü. Yangında ölen ya da yaralanan olmadı. Yangın, saat 06.00 sıralarında Habipler Mahallesi 2723. Sokak'ta bulunan tek katlı plastik eşya deposunda çıktı. Henüz bilinmeyen bir nedenle çıkan yangın, rüzgarın da etkisiyle kısa sürede büyüdü. Bölgedeki alevleri ve yoğun dumanı gören vatandaşlar durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine polis, sağlık ve çok sayıda itfaiye ekibi sevk edildi. Ekiplerin geniş kapsamlı çalışması ve duman tahliyesinin ardından yangın kontrol altına alınarak söndürüldü. Çıkan yangında ölen ya da yaralanan olmazken, depoda büyük çapta maddi hasar meydana geldi. Yangın ile ilgili inceleme başlatıldı. - İSTANBUL Kaynak: İHA Sultangazi 'de tek katlı plastik eşya deposu sabah saatlerinde alevlere teslim oldu. Bölgede yoğun duman oluşurken, itfaiye ekiplerinin geniş kapsamlı müdahalesi sonrası yangın söndürüldü. Yangında ölen ya da yaralanan olmadı. Yangın, saat 06.00 sıralarında Habipler Mahallesi 2723. Sokak'ta bulunan tek katlı plastik eşya deposunda çıktı. Henüz bilinmeyen bir nedenle çıkan yangın, rüzgarın da etkisiyle kısa sürede büyüdü. Bölgedeki alevleri ve yoğun dumanı gören vatandaşlar durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine polis, sağlık ve çok sayıda itfaiye ekibi sevk edildi. Ekiplerin geniş kapsamlı çalışması ve duman tahliyesinin ardından yangın kontrol altına alınarak söndürüldü. Çıkan yangında ölen ya da yaralanan olmazken, depoda büyük çapta maddi hasar meydana geldi. Yangın ile ilgili inceleme başlatıldı. - İSTANBUL Sultangazi'de Plastik Eşya Deposunda Yangın Sultangazi'de çıkan yangın sonrası itfaiye müdahale etti, can kaybı yok, maddi hasar var. Sultangazi 'de tek katlı plastik eşya deposu sabah saatlerinde alevlere teslim oldu. Bölgede yoğun duman oluşurken, itfaiye ekiplerinin geniş kapsamlı müdahalesi sonrası yangın söndürüldü. Yangında ölen ya da yaralanan olmadı. Yangın, saat 06.00 sıralarında Habipler Mahallesi 2723. Sokak'ta bulunan tek katlı plastik eşya deposunda çıktı. Henüz bilinmeyen bir nedenle çıkan yangın, rüzgarın da etkisiyle kısa sürede büyüdü. Bölgedeki alevleri ve yoğun dumanı gören vatandaşlar durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine polis, sağlık ve çok sayıda itfaiye ekibi sevk edildi. Ekiplerin geniş kapsamlı çalışması ve duman tahliyesinin ardından yangın kontrol altına alınarak söndürüldü. Çıkan yangında ölen ya da yaralanan olmazken, depoda büyük çapta maddi hasar meydana geldi. Yangın ile ilgili inceleme başlatıldı. - İSTANBUL</t>
+          <t>Sinop Ayancık'ta, Fabrikada çıkan yangın söndürüldü! | Gündem Haber Meydan</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Plastik Eşya Deposunda Yangın Sultangazi'de Plastik Eşya Deposunda Yangın sondakika.com Sultangazi'de çıkan yangın sonrası itfaiye müdahale etti, can kaybı yok, maddi hasar var. Sultangazi'de Plastik Eşya Deposunda Yangın Son Güncelleme: 07.06.2026 08:40 Sultangazi'de çıkan yangın sonrası itfaiye müdahale etti, can kaybı yok, maddi hasar var. Sultangazi 'de tek katlı plastik eşya deposu sabah saatlerinde alevlere teslim oldu. Bölgede yoğun duman oluşurken, itfaiye ekiplerinin geniş kapsamlı müdahalesi sonrası yangın söndürüldü. Yangında ölen ya da yaralanan olmadı. Yangın, saat 06.00 sıralarında Habipler Mahallesi 2723. Sokak'ta bulunan tek katlı plastik eşya deposunda çıktı. Henüz bilinmeyen bir nedenle çıkan yangın, rüzgarın da etkisiyle kısa sürede büyüdü. Bölgedeki alevleri ve yoğun dumanı gören vatandaşlar durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine polis, sağlık ve çok sayıda itfaiye ekibi sevk edildi. Ekiplerin geniş kapsamlı çalışması ve duman tahliyesinin ardından yangın kontrol altına alınarak söndürüldü. Çıkan yangında ölen ya da yaralanan olmazken, depoda büyük çapta maddi hasar meydana geldi. Yangın ile ilgili inceleme başlatıldı. - İSTANBUL Kaynak: İHA Sultangazi 'de tek katlı plastik eşya deposu sabah saatlerinde alevlere teslim oldu. - İSTANBUL Sultangazi'de Plastik Eşya Deposunda Yangın Sultangazi'de çıkan yangın sonrası itfaiye müdahale etti, can kaybı yok, maddi hasar var.</t>
+          <t>Sinop Ayancık'ta, Fabrikada çıkan yangın söndürüldü! Sinop Ayancık'ta, Fabrikada çıkan yangın söndürüldü! | Gündem Haber Meydan Sinop Ayancık'ta, Fabrikada çıkan yangın söndürüldü!</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.sondakika.com/amp/haber-sultangazi-de-plastik-esya-deposunda-yangin-19920069/</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQcVVYbmJCaElXbHFXY0R5blZqanJNYUZrVnJqeXVOYXNCd0hXNlYyUzdVd3c1dGFlZzZVOHJhQ1lxVVo3OGtmSDRoVFV4SzlUc2JPQ0ZTYTUydDVnNkFjcElCb21FVExjOHdWTzdwbkx2ZjhiNEdiNUNSZHVTVTdreU9qRF9FdUNrSnpLQU1vbG1yMHNpdVhDdNIBngFBVV95cUxPakFvOG1PWFlWQ0w0UG1SMHdLY19rdnh1M2lIaU9tYTVYcjFQOFluTFZsdXRMaVNuTjB5RVF1N2ltM0VZRzhINnQ2clQ4cXc2UmtkQXMwb1NOR0w3QnpWM1ZZOVlXQ1dpWXJoMUxWQnZhV3FQbTFKUW1CT3B0T3NudlBfdkZ4MG1YQjVPMTZ3TDlETXNIc0hla096NnN3UQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Sinop</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>00 sıralarında Habipler Mahallesi</t>
-        </is>
-      </c>
+          <t>Ayancık</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>plastik eşya deposu</t>
-        </is>
-      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>plastik eşya deposu 00 sıralarında Habipler Mahallesi Sultangazi İstanbul Türkiye</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Yildiz Plastik Geri Dönüşüm | ÖRNEK PLASTİK AMB. SAN.TİC.LTD.ŞTİ | Eşya Depolama - Turuncu Depo | İstanbul Kiralık Eşya Deposu | İdealDepo - Kiralık Depo - Eşya Depolama - Self Storage</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Yildiz Plastik Geri Dönüşüm</t>
-        </is>
-      </c>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>65.21739130434783 | 40.74074074074074 | 73.33333333333333 | 43.47826086956522</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>Sultangazi Ambalaj</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="n">
-        <v>174.75</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>5</v>
@@ -2597,27 +2732,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:06:33</t>
+          <t>2026-06-07 11:24:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>nitelikli dolandırıcılık</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Yetkililer, Hai Phong'daki bir ağaç işleme fabrikasında çıkan yangını hızla kontrol altına aldı.</t>
+          <t>Denizli'de "change" operasyonu: 11 lüks araca el konuldu, 3 tutuklama!</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Yetkililer, Hai Phong'daki bir ağaç işleme fabrikasında çıkan yangını hızla kontrol altına aldı. Vietnam.vn</t>
+          <t>Denizli'de "change" operasyonu: 11 lüks araca el konuldu, 3 tutuklama! gazetesehir.com</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -2627,35 +2762,35 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>el konuldu</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Yetkililer, Hai Phong'daki bir ağaç işleme fabrikasında çıkan yangını hızla kontrol altına aldı. Vietnam.vn</t>
+          <t>Denizli’de lüks otomobilleri hedef alan dev "Change" şebekesi çökertildi! Denizli İl Emniyet Müdürlüğü ekiplerinin düzenlediği operasyonda, hasarlı araçların motor ve şasi numaralarını lüks araçlarla değiştirerek sistemli dolandırıcılık yapan 6 şüpheli yakalandı. Operasyonda 11 lüks otomobile el konulurken, adliyeye sevk edilen zehirli şebekenin 3 üyesi tutuklanarak cezaevine gönderildi. Denizli’de lüks otomobilleri hedef alan dev "Change" şebekesi çökertildi! Denizli İl Emniyet Müdürlüğü ekiplerinin düzenlediği operasyonda, hasarlı araçların mo... Denizli’de lüks otomobilleri hedef alan dev "Change" şebekesi çökertildi! Denizli İl Emniyet Müdürlüğü ekiplerinin düzenlediği operasyonda, hasarlı araçların motor ve şasi numaralarını lüks araçlarla değiştirerek sistemli dolandırıcılık yapan 6 şüpheli yakalandı. Operasyonda 11 lüks otomobile el konulurken, adliyeye sevk edilen zehirli şebekenin 3 üyesi tutuklanarak cezaevine gönderildi. Denizli Cumhuriyet Başsavcılığı koordinesinde yürütülen büyük çaplı soruşturma kapsamında, Denizli İl Emniyet Müdürlüğü Asayiş Şube Müdürlüğü Oto Hırsızlık Büro Amirliği ekipleri nitelikli dolandırıcılık şebekelerine ağır bir darbe indirdi. Ekipler, yasal olmayan yollarla araçların kimliğini değiştirerek haksız kazanç elde eden "Change" çetesini yakın takibe aldı. Sistemli Olarak Hasarlı Araçları Kullandılar Oto Hırsızlık Büro Amirliği ekiplerince yapılan titiz çalışmalar neticesinde, şüphelilerin özellikle kaza nedeniyle ağır hasar görmüş (pert) araçları hedef aldığı belirlendi. Bu hasarlı araçların motor ve şasi numaralarını, yasa dışı yollarla temin ettikleri lüks marka araçlara sistemli bir şekilde entegre ederek "Resmi Belgede Sahtecilik" ve "Nitelikli Dolandırıcılık" suçlarını işledikleri tespit edildi. Lüks Otomobiller ve Çok Sayıda Parça Ele Geçirildi Gerçekleştirilen eş zamanlı operasyonlarda, change işlemi yapıldığı belirlenen tam 11 lüks marka araca polis ekipleri tarafından el konuldu. Şüpheli şahıslara ait iş yerlerinde ve ikametlerinde yapılan aramalarda ise piyasa değeri yüksek muhtelif sayıda araç parçası ele geçirilerek koruma altına alındı. 6 Şüpheliden 3'ü Demir Parmaklıklar Arkasında Operasyon kapsamında gözaltına alınan 6 şüpheli şahıs, emniyetteki işlemlerinin tamamlanmasının ardından “Nitelikli Dolandırıcılık ve Resmi Belgede Sahtecilik (Change Araç)” suçlarından adli makamlara sevk edildi. Mahkemeye çıkarılan 6 şüpheliden 3’ü tutuklanarak cezaevine gönderilirken, olayla ilgili geniş çaplı tahkikatın sürdüğü bildirildi. Denizli'de "change" operasyonu: 11 lüks araca el konuldu, 3 tutuklama! Denizli’de lüks otomobilleri hedef alan dev "Change" şebekesi çökertildi! Denizli İl Emniyet Müdürlüğü ekiplerinin düzenlediği operasyonda, hasarlı araçların motor ve şasi numaralarını lüks araçlarla değiştirerek sistemli dolandırıcılık yapan 6 şüpheli yakalandı. Operasyonda 11 lüks otomobile el konulurken, adliyeye sevk edilen zehirli şebekenin 3 üyesi tutuklanarak cezaevine gönderildi. Denizli Cumhuriyet Başsavcılığı koordinesinde yürütülen büyük çaplı soruşturma kapsamında, Denizli İl Emniyet Müdürlüğü Asayiş Şube Müdürlüğü Oto Hırsızlık Büro Amirliği ekipleri nitelikli dolandırıcılık şebekelerine ağır bir darbe indirdi. Ekipler, yasal olmayan yollarla araçların kimliğini değiştirerek haksız kazanç elde eden "Change" çetesini yakın takibe aldı. Sistemli Olarak Hasarlı Araçları Kullandılar Oto Hırsızlık Büro Amirliği ekiplerince yapılan titiz çalışmalar neticesinde, şüphelilerin özellikle kaza nedeniyle ağır hasar görmüş (pert) araçları hedef aldığı belirlendi. Bu hasarlı araçların motor ve şasi numaralarını, yasa dışı yollarla temin ettikleri lüks marka araçlara sistemli bir şekilde entegre ederek "Resmi Belgede Sahtecilik" ve "Nitelikli Dolandırıcılık" suçlarını işledikleri tespit edildi. Lüks Otomobiller ve Çok Sayıda Parça Ele Geçirildi Gerçekleştirilen eş zamanlı operasyonlarda, change işlemi yapıldığı belirlenen tam 11 lüks marka araca polis ekipleri tarafından el konuldu. Şüpheli şahıslara ait iş yerlerinde ve ikametlerinde yapılan aramalarda ise piyasa değeri yüksek muhtelif sayıda araç parçası ele geçirilerek koruma altına alındı. 6 Şüpheliden 3'ü Demir Parmaklıklar Arkasında Operasyon kapsamında gözaltına alınan 6 şüpheli şahıs, emniyetteki işlemlerinin tamamlanmasının ardından “Nitelikli Dolandırıcılık ve Resmi Belgede Sahtecilik (Change Araç)” suçlarından adli makamlara sevk edildi. Mahkemeye çıkarılan 6 şüpheliden 3’ü tutuklanarak cezaevine gönderilirken, olayla ilgili geniş çaplı tahkikatın sürdüğü bildirildi. 07 Haz 2026 - 14:24 Denizli - Asayiş Yazdır</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Yetkililer, Hai Phong'daki bir ağaç işleme fabrikasında çıkan yangını hızla kontrol altına aldı. Yetkililer, Hai Phong'daki bir ağaç işleme fabrikasında çıkan yangını hızla kontrol altına aldı. Vietnam.vn Yetkililer, Hai Phong'daki bir ağaç işleme fabrikasında çıkan yangını hızla kontrol altına aldı.</t>
+          <t>Denizli'de "change" operasyonu: 11 lüks araca el konuldu, 3 tutuklama! Denizli'de "change" operasyonu: 11 lüks araca el konuldu, 3 tutuklama! gazetesehir.com Denizli’de lüks otomobilleri hedef alan dev "Change" şebekesi çökertildi! Denizli İl Emniyet Müdürlüğü ekiplerinin düzenlediği operasyonda, hasarlı araçların motor ve şasi numaralarını lüks araçlarla değiştirerek sistemli dolandırıcılık yapan 6 şüpheli yakalandı. Operasyonda 11 lüks otomobile el konulurken, adliyeye sevk edilen zehirli şebekenin 3 üyesi tutuklanarak cezaevine gönderildi. Denizli İl Emniyet Müdürlüğü ekiplerinin düzenlediği operasyonda, hasarlı araçların mo... Denizli Cumhuriyet Başsavcılığı koordinesinde yürütülen büyük çaplı soruşturma kapsamında, Denizli İl Emniyet Müdürlüğü Asayiş Şube Müdürlüğü Oto Hırsızlık Büro Amirliği ekipleri nitelikli dolandırıcılık şebekelerine ağır bir darbe indirdi. Ekipler, yasal olmayan yollarla araçların kimliğini değiştirerek haksız kazanç elde eden "Change" çetesini yakın takibe aldı. Sistemli Olarak Hasarlı Araçları Kullandılar Oto Hırsızlık Büro Amirliği ekiplerince yapılan titiz çalışmalar neticesinde, şüphelilerin özellikle kaza nedeniyle ağır hasar görmüş (pert) araçları hedef aldığı belirlendi. Bu hasarlı araçların motor ve şasi numaralarını, yasa dışı yollarla temin ettikleri lüks marka araçlara sistemli bir şekilde entegre ederek "Resmi Belgede Sahtecilik" ve "Nitelikli Dolandırıcılık" suçlarını işledikleri tespit edildi. Lüks Otomobiller ve Çok Sayıda Parça Ele Geçirildi Gerçekleştirilen eş zamanlı operasyonlarda, change işlemi yapıldığı belirlenen tam 11 lüks marka araca polis ekipleri tarafından el konuldu. Şüpheli şahıslara ait iş yerlerinde ve ikametlerinde yapılan aramalarda ise piyasa değeri yüksek muhtelif sayıda araç parçası ele geçirilerek koruma altına alındı. 6 Şüpheliden 3'ü Demir Parmaklıklar Arkasında Operasyon kapsamında gözaltına alınan 6 şüpheli şahıs, emniyetteki işlemlerinin tamamlanmasının ardından “Nitelikli Dolandırıcılık ve Resmi Belgede Sahtecilik (Change Araç)” suçlarından adli makamlara sevk edildi. Denizli'de "change" operasyonu: 11 lüks araca el konuldu, 3 tutuklama! 07 Haz 2026 - 14:24 Denizli - Asayiş Yazdır</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE95RzZ4bl80YlVtdGlhYTR1SGhmRGJ2cjJnWkUxNG5fSmd1Y0t5UzdvZTF2eFh5SkVfN1dJbjJkZXhISDNTWVdkeHpNSUpGNkhENG5pd1V4OUplWVRGN1V5M3hwMnpnR2V5cmRic1Z2M3daNnJfRW5qYU9xTlY3QQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>https://gazetesehir.com/haber/28127398/denizlide-change-operasyonu-11-luks-araca-el-konuldu-3-tutuklama</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Denizli</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
@@ -2664,7 +2799,7 @@
       <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr"/>
@@ -2678,7 +2813,7 @@
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>6</v>
@@ -2687,27 +2822,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 16:04:00</t>
+          <t>2026-06-08 07:24:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>bahis operasyonu</t>
+          <t>sahtecilik</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de şafak operasyonu! Elektronik para şirketine bahis baskını</t>
+          <t>Denizli'nin 'Change araç' çetesi 11 lüks otomobile el konuldu</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de şafak operasyonu! Elektronik para şirketine bahis baskını Demokrat Kocaeli</t>
+          <t>Denizli'nin 'Change araç' çetesi 11 lüks otomobile el konuldu Manşet Aydın</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -2717,22 +2852,18 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>el konuldu</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>demokratkocaeli.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. demokratkocaeli.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. demokratkocaeli.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Denizli’de kazalı lüks araçları, başka araçlardan elde edilen parçalarla piyasaya sürmeye çalıştıkları iddia edilen 6 şüpheliden 3’ü tutuklandı. Denizli’de kazalı lüks araçları, başka araçlardan elde edilen parçalarla piyasaya sürmeye çalıştıkları iddia edilen 6 şüpheliden 3’ü tutuklandı. Denizli’de kazalı lüks araçları, başka araçlardan elde edilen parçalarla piyasaya sürmeye çalıştıkları iddia edilen 6 şüpheliden 3’ü tutuklandı. Haber albümü için resme tıklayın Kazalı lüks araçları change işlemiyle piyasaya süren şebeke çökertildi. Bu haberi kaçırmayın Damada işkence! Her eziyete katlandı Devamını Oku Denizli İl Emniyet Müdürlüğü Asayiş Şube Müdürlüğü Oto Hırsızlık Büro Amirliği ekipleri, "Nitelikli Dolandırıcılık, Resmi Belgede Sahtecilik (change araç) suçlarının önlenmesine yönelik yapılan çalışmalarda bir operasyona daha imza attı. Denizli Cumhuriyet Başsavcılığı koordinesinde yürütülen soruşturma kapsamında, başta kaza nedeniyle hasar görmüş araçlar olmak üzere change işlemini sistemli bir şekilde yapan 6 şüpheli yakalandı. 11 LÜKS ARACA EL KONULDU Operasyon çerçevesinde yapılan çalışmalarda neticesinde 11 adet lüks marka araca el konulurken, şüpheli şahıslara ait iş yeri ve ikametlerde yapılan aramalarda çok sayıda araç parçası ele geçildi. "Nitelikli Dolandırıcılık, Resmi Belgede Sahtecilik (Change Araç)" suçlarından adli makamlara sevk edilen 6 şüpheliden 3’ü tutuklanarak cezaevine gönderildi. # Soruşturma , kaza , Denizli 08 Haz 2026 - 10:24 - Asayiş Denizli'nin 'Change araç' çetesi 11 lüks otomobile el konuldu Denizli’de kazalı lüks araçları, başka araçlardan elde edilen parçalarla piyasaya sürmeye çalıştıkları iddia edilen 6 şüpheliden 3’ü tutuklandı. İhlas Haber Ajansı Tüm Haberleri Haber albümü için resme tıklayın Kazalı lüks araçları change işlemiyle piyasaya süren şebeke çökertildi. Bu haberi kaçırmayın Damada işkence! Her eziyete katlandı Devamını Oku Denizli İl Emniyet Müdürlüğü Asayiş Şube Müdürlüğü Oto Hırsızlık Büro Amirliği ekipleri, "Nitelikli Dolandırıcılık, Resmi Belgede Sahtecilik (change araç) suçlarının önlenmesine yönelik yapılan çalışmalarda bir operasyona daha imza attı. Denizli Cumhuriyet Başsavcılığı koordinesinde yürütülen soruşturma kapsamında, başta kaza nedeniyle hasar görmüş araçlar olmak üzere change işlemini sistemli bir şekilde yapan 6 şüpheli yakalandı. 11 LÜKS ARACA EL KONULDU Operasyon çerçevesinde yapılan çalışmalarda neticesinde 11 adet lüks marka araca el konulurken, şüpheli şahıslara ait iş yeri ve ikametlerde yapılan aramalarda çok sayıda araç parçası ele geçildi. "Nitelikli Dolandırıcılık, Resmi Belgede Sahtecilik (Change Araç)" suçlarından adli makamlara sevk edilen 6 şüpheliden 3’ü tutuklanarak cezaevine gönderildi. # Soruşturma , kaza , Denizli 08 Haz 2026 - 10:24 - Asayiş Yazdır Mahreç İhlas Haber Ajansı GİRİŞ YAP Yorum yazarak Manşet Aydın Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yoruml</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli’de şafak operasyonu! Elektronik para şirketine bahis baskını Kocaeli’de şafak operasyonu! Elektronik para şirketine bahis baskını Demokrat Kocaeli demokratkocaeli.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. demokratkocaeli.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. demokratkocaeli.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Denizli'nin 'Change araç' çetesi 11 lüks otomobile el konuldu Denizli'nin 'Change araç' çetesi 11 lüks otomobile el konuldu Manşet Aydın Denizli’de kazalı lüks araçları, başka araçlardan elde edilen parçalarla piyasaya sürmeye çalıştıkları iddia edilen 6 şüpheliden 3’ü tutuklandı. Haber albümü için resme tıklayın Kazalı lüks araçları change işlemiyle piyasaya süren şebeke çökertildi. Her eziyete katlandı Devamını Oku Denizli İl Emniyet Müdürlüğü Asayiş Şube Müdürlüğü Oto Hırsızlık Büro Amirliği ekipleri, "Nitelikli Dolandırıcılık, Resmi Belgede Sahtecilik (change araç) suçlarının önlenmesine yönelik yapılan çalışmalarda bir operasyona daha imza attı. Denizli Cumhuriyet Başsavcılığı koordinesinde yürütülen soruşturma kapsamında, başta kaza nedeniyle hasar görmüş araçlar olmak üzere change işlemini sistemli bir şekilde yapan 6 şüpheli yakalandı. 11 LÜKS ARACA EL KONULDU Operasyon çerçevesinde yapılan çalışmalarda neticesinde 11 adet lüks marka araca el konulurken, şüpheli şahıslara ait iş yeri ve ikametlerde yapılan aramalarda çok sayıda araç parçası ele geçildi. "Nitelikli Dolandırıcılık, Resmi Belgede Sahtecilik (Change Araç)" suçlarından adli makamlara sevk edilen 6 şüpheliden 3’ü tutuklanarak cezaevine gönderildi. # Soruşturma , kaza , Denizli 08 Haz 2026 - 10:24 - Asayiş Denizli'nin 'Change araç' çetesi 11 lüks otomobile el konuldu Denizli’de kazalı lüks araçları, başka araçlardan elde edilen parçalarla piyasaya sürmeye çalıştıkları iddia edilen 6 şüpheliden 3’ü tutuklandı. İhlas Haber Ajansı Tüm Haberleri Haber albümü için resme tıklayın Kazalı lüks araçları change işlemiyle piyasaya süren şebeke çökertildi. # Soruşturma , kaza , Denizli 08 Haz 2026 - 10:24 - Asayiş Yazdır Mahreç İhlas Haber Ajansı GİRİŞ YAP Yorum yazarak Manşet Aydın Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2742,12 +2873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://demokratkocaeli.com/haber/28124512/kocaelide-safak-operasyonu-elektronik-para-sirketine-bahis-baskini</t>
+          <t>https://www.mansetaydin.com/haber/28130806/denizlinin-change-arac-cetesi-11-luks-otomobile-el-konuldu</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
@@ -2772,7 +2903,7 @@
       <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="n">
-        <v>86.68000000000001</v>
+        <v>82</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>7</v>
@@ -2781,27 +2912,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 05:32:00</t>
+          <t>2026-06-07 14:23:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>mali kriz</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Sultangazi'de korkutan yangın : Plastik eşya deposu alevlere teslim oldu</t>
+          <t>Dev hava yolu şirketi Europen Cargo resmen iflas etti: Jet yakıtı krizi büyüyor</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Sultangazi'de korkutan yangın : Plastik eşya deposu alevlere teslim oldu İşçi Haber</t>
+          <t>Dev hava yolu şirketi Europen Cargo resmen iflas etti: Jet yakıtı krizi büyüyor Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2811,22 +2942,22 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Sultangazi’de sabahın erken saatlerinde korkutan bir yangın meydana geldi. Habipler Mahallesi'nde bulunan tek katlı bir plastik eşya deposu, henüz belirlenemeyen bir nedenle alevlere teslim oldu. Rüzgarın da şiddetiyle kısa sürede büyüyen ve gökyüzünü yoğun dumanla kaplayan yangın, bölgede büyük paniğe yol açtı. İstanbul Sultangazi’de sabahın erken saatlerinde korkutan bir yangın meydana geldi. Habipler Mahallesi'nde bulunan tek katlı bir plastik eşya deposu, henüz belirlenemeyen bir nedenle alevlere teslim oldu. Rüzgarın da şiddetiyle kısa sürede büyüyen ve gökyüzünü yoğun dumanla kaplayan yangın, bölgede büyük paniğe yol açtı. İstanbul Sultangazi’de sabahın erken saatlerinde korkutan bir yangın meydana geldi. Habipler Mahallesi'nde bulunan tek katlı bir plastik eşya deposu, henüz belirlenemeyen bir nedenle alevlere teslim oldu. Rüzgarın da şiddetiyle kısa sürede büyüyen ve gökyüzünü yoğun dumanla kaplayan yangın, bölgede büyük paniğe yol açtı. Sultangazi’de tek katlı plastik eşya deposu sabah saatlerinde alevlere teslim oldu. Yangın, saat 06.00 sıralarında Habipler Mahallesi 2723. Sokak’ta bulunan tek katlı plastik eşya deposunda çıktı. Henüz bilinmeyen bir nedenle çıkan yangın, rüzgârın da etkisiyle kısa sürede büyüdü. Bölgedeki alevleri ve yoğun dumanı gören vatandaşlar durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine polis, sağlık ve çok sayıda itfaiye ekibi sevk edildi. Ekiplerin geniş kapsamlı çalışması ve duman tahliyesinin ardından yangın kontrol altına alınarak söndürüldü. Çıkan yangında ölen ya da yaralanan olmazken, depoda büyük çapta maddi hasar meydana geldi. Yangın ile ilgili inceleme başlatıldı. Kaynak: İHA İstanbul Açık 20 ° Adana Adıyaman Afyonkarahisar Ağrı Amasya Ankara Antalya Artvin Aydın Balıkesir Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Isparta Mersin İstanbul İzmir Kars Kastamonu Kayseri Kırklareli Kırşehir Kocaeli Konya Kütahya Malatya Manisa Kahramanmaraş Mardin Muğla Muş Nevşehir Niğde Ordu Rize Sakarya Samsun Siirt Sinop Sivas Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yozgat Zonguldak Aksaray Bayburt Karaman Kırıkkale Batman Şırnak Bartın Ardahan Iğdır Yalova Karabük Kilis Osmaniye Düzce Selen Albayrak Demirtürk Editör KAYNAK: İHA Okunma Süresi: 1 dk Çanakkale'de evde yangın : 2 kedi telef oldu #Çanakkale / 06 Haziran 2026 Erzurum'daki yangın faciasında yaşamını yitiren kadın defnedildi #Erzurum / 06 Haziran 2026 Paylaş Ar</t>
+          <t>ABD-İran savaşı ve Hürmüz Boğazı'ndaki tıkanıklık nedeniyle fırlayan jet yakıtı fiyatları, küresel havacılık sektöründe domino etkisi yarattı. Mayıs ayında dünya devi Spirit Airlines'ın çöküşüyle başlayan iflas dalgasına son olarak İngiliz uzun menzilli kargo devi European Cargo da dahil oldu.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Sultangazi'de korkutan yangın : Plastik eşya deposu alevlere teslim oldu İstanbul Sultangazi'de korkutan yangın : Plastik eşya deposu alevlere teslim oldu İşçi Haber İstanbul Sultangazi’de sabahın erken saatlerinde korkutan bir yangın meydana geldi. Habipler Mahallesi'nde bulunan tek katlı bir plastik eşya deposu, henüz belirlenemeyen bir nedenle alevlere teslim oldu. Rüzgarın da şiddetiyle kısa sürede büyüyen ve gökyüzünü yoğun dumanla kaplayan yangın, bölgede büyük paniğe yol açtı. Sultangazi’de tek katlı plastik eşya deposu sabah saatlerinde alevlere teslim oldu. Yangın, saat 06.00 sıralarında Habipler Mahallesi 2723. Sokak’ta bulunan tek katlı plastik eşya deposunda çıktı. Henüz bilinmeyen bir nedenle çıkan yangın, rüzgârın da etkisiyle kısa sürede büyüdü. Bölgedeki alevleri ve yoğun dumanı gören vatandaşlar durumu 112 Acil Çağrı Merkezi'ne bildirdi. Ekiplerin geniş kapsamlı çalışması ve duman tahliyesinin ardından yangın kontrol altına alınarak söndürüldü. Çıkan yangında ölen ya da yaralanan olmazken, depoda büyük çapta maddi hasar meydana geldi. Yangın ile ilgili inceleme başlatıldı. Kaynak: İHA İstanbul Açık 20 ° Adana Adıyaman Afyonkarahisar Ağrı Amasya Ankara Antalya Artvin Aydın Balıkesir Bilecik Bingöl Bitlis Bolu Burdur Bursa Çanakkale Çankırı Çorum Denizli Diyarbakır Edirne Elazığ Erzincan Erzurum Eskişehir Gaziantep Giresun Gümüşhane Hakkari Hatay Isparta Mersin İstanbul İzmir Kars Kastamonu Kayseri Kırklareli Kırşehir Kocaeli Konya Kütahya Malatya Manisa Kahramanmaraş Mardin Muğla Muş Nevşehir Niğde Ordu Rize Sakarya Samsun Siirt Sinop Sivas Tekirdağ Tokat Trabzon Tunceli Şanlıurfa Uşak Van Yozgat Zonguldak Aksaray Bayburt Karaman Kırıkkale Batman Şırnak Bartın Ardahan Iğdır Yalova Karabük Kilis Osmaniye Düzce Selen Albayrak Demirtürk Editör KAYNAK: İHA Okunma Süresi: 1 dk Çanakkale'de evde yangın : 2 kedi telef oldu #Çanakkale / 06 Haziran 2026 Erzurum'daki yangın faciasında yaşamını yitiren kadın defnedildi #Erzurum / 06 Haziran 2026 Paylaş Ar</t>
+          <t>Dev hava yolu şirketi Europen Cargo resmen iflas etti: Jet yakıtı krizi büyüyor Dev hava yolu şirketi Europen Cargo resmen iflas etti: Jet yakıtı krizi büyüyor Yeniçağ Gazetesi ABD-İran savaşı ve Hürmüz Boğazı'ndaki tıkanıklık nedeniyle fırlayan jet yakıtı fiyatları, küresel havacılık sektöründe domino etkisi yarattı. Mayıs ayında dünya devi Spirit Airlines'ın çöküşüyle başlayan iflas dalgasına son olarak İngiliz uzun menzilli kargo devi European Cargo da dahil oldu.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2836,69 +2967,33 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.iscihaber.net/istanbul/istanbul-sultangazide-korkutan-yangin-plastik-esya-deposu-alevlere-teslim-oldu/235833</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Çanakkale | İstanbul</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Sultangazi</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Habipler Mahallesi | 00 sıralarında Habipler Mahallesi</t>
-        </is>
-      </c>
+          <t>https://www.yenicaggazetesi.com/dev-hava-yolu-sirketi-europen-cargo-resmen-iflas-etti-jet-yakiti-krizi-buyuyor-1038091h.htm</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Plastik eşya deposu | plastik eşya deposu</t>
-        </is>
-      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>Plastik eşya deposu Habipler Mahallesi Sultangazi Çanakkale Türkiye</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Yildiz Plastik Geri Dönüşüm | ÖRNEK PLASTİK AMB. SAN.TİC.LTD.ŞTİ | Eriş Plastik | Gold Plastik</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Yildiz Plastik Geri Dönüşüm</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>65.21739130434783 | 40.74074074074074 | 73.6842105263158 | 73.6842105263158</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>Sultangazi Ambalaj</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="n">
-        <v>210.5</v>
+        <v>82.44</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>8</v>
@@ -2907,27 +3002,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 14:13:31</t>
+          <t>2026-06-07 12:03:20</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>mali kriz</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Balıkesir-İzmir Karayolunda Depo Yangını: Ekipler Seferber Oldu</t>
+          <t>Havacılıkta kriz büyüyor: Ünlü havayolu şirketi de iflas bayrağını çekti!</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Balıkesir-İzmir Karayolunda Depo Yangını: Ekipler Seferber Oldu Balıkesir Haberci Gazetesi</t>
+          <t>Havacılıkta kriz büyüyor: Ünlü havayolu şirketi de iflas bayrağını çekti! GZT</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -2937,32 +3032,32 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>www.habercigazetesi.net Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.habercigazetesi.net adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.habercigazetesi.net adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Havacılıkta kriz büyüyor: Ünlü havayolu şirketi de iflas bayrağını çekti! GZT</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Balıkesir-İzmir Karayolunda Depo Yangını: Ekipler Seferber Oldu Balıkesir-İzmir Karayolunda Depo Yangını: Ekipler Seferber Oldu Balıkesir Haberci Gazetesi www.habercigazetesi.net Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.habercigazetesi.net adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı.</t>
+          <t>Havacılıkta kriz büyüyor: Ünlü havayolu şirketi de iflas bayrağını çekti! Havacılıkta kriz büyüyor: Ünlü havayolu şirketi de iflas bayrağını çekti! GZT Havacılıkta kriz büyüyor: Ünlü havayolu şirketi de iflas bayrağını çekti!</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.habercigazetesi.net/asayis/balikesir-izmir-karayolunda-depo-yangini-ekipler-seferber-oldu.html</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNcVVZMVZsdEdQVk5aOUpnMGNJWXBjMDRGVU9RMzFXLUN1SVd5Z1U2VWZ4ZHFqX2prbEJYLTY2aXl5Wm01Sk1ZcjNEQXp0V3RJUUJvbkJJTkIyU3cyMlhwV1NsQm5IM29RM1plWUt2U1BmbWpaNmI1Uzc0aWVKWkVJNllPaDgwWGdCdU9uX085Skd6cTIwNGItcW84QW50N01WSlFodWx3SVV5d1lUVWpOOW9fSDhjNHhHb1lNR3RnUnFaM3V5WW1FNWJ6MlhVUE9IOXhIcFB2NTdGNlRZLXhhd2RyMFpnenNYaFltMS1MTC1yMTNfbmVmRnVhRm1BOXFTSW15UGl3?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
@@ -2988,7 +3083,7 @@
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="n">
-        <v>75.55</v>
+        <v>64.52</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>9</v>
@@ -2997,27 +3092,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 07:42:00</t>
+          <t>2026-06-07 15:23:53</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>mali kriz</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Yangın Merdivenleri Depoya Döndü: Hayati kaçış yolları işgal altında</t>
+          <t>Hürmüz Boğazı krizi bir şirketi daha vurdu: Dev uçak firması iflas etti!</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Yangın Merdivenleri Depoya Döndü: Hayati kaçış yolları işgal altında Gazete Detay</t>
+          <t>Hürmüz Boğazı krizi bir şirketi daha vurdu: Dev uçak firması iflas etti! GZT</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3027,22 +3122,22 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>firma, şirket</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Yangın Merdivenleri Depoya Döndü: Hayati kaçış yolları işgal altında Gazete Detay</t>
+          <t>Hürmüz Boğazı krizi bir şirketi daha vurdu: Dev uçak firması iflas etti! GZT</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Yangın Merdivenleri Depoya Döndü: Hayati kaçış yolları işgal altında Yangın Merdivenleri Depoya Döndü: Hayati kaçış yolları işgal altında Gazete Detay Yangın Merdivenleri Depoya Döndü: Hayati kaçış yolları işgal altında Gazete Detay</t>
+          <t>Hürmüz Boğazı krizi bir şirketi daha vurdu: Dev uçak firması iflas etti! Hürmüz Boğazı krizi bir şirketi daha vurdu: Dev uçak firması iflas etti! GZT Hürmüz Boğazı krizi bir şirketi daha vurdu: Dev uçak firması iflas etti!</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -3052,7 +3147,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPRDlFX2FlcTBYQmJsQmlnd2lXa2VCakVJQ21yOF9KTWdsNERKWm1xMVRPQTZmWVE1TmlnUlFzYV9HZS1wd3RJQTB2X2ZzTTR2bUdMdE81SUlMMHhqczhXbFc5YUxjMGhlcG9qdUtUSkVYaWlsaGJjYWhKSG9NcWZqNmNJNEx5VkZ1SHFrU3NNc3d6SzN5VkHSAZsBQVVfeXFMTXpaODBSUlJJQ0gwNFZYQ0RYT1NIU0swaHhXb3BIZGVleF8xUkVRMDhMcnpqbXN0SWRCRHprQzJOSjBMM0xuSkM2RWFPZTlaV0x1NS1qTDVRSmY1MTdsa0NBT05TVHhmYUNjT3pNRE1KX2hvUjVWZTMwaWxYb0RsTkRwZmRFd2hRcDlQR0ZkVlkybjlFTGVuU2Q0ck0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTVo0UEFnR1hRbmR6a1FCVHRtSkVNbm53MHk0cnUycFdzVW5TWER2RTRTM1BMd0UyZWU5aGh6SWRVckRCUWJZU2oyeHprLTh2ZnZMd0RhTnlEM3JrU1VlMmFDbl8xNzh6ejR5Y3lxY3pjdkRsbUZGZS1zVFpIYm5KZlZSdkVjN1BXWHFXT0JTaUZYVXBqbXdxaWZZbDc1VjRORFNoWWtDZHBWZw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
@@ -3078,7 +3173,7 @@
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="n">
-        <v>71.06</v>
+        <v>63.76</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>10</v>
@@ -3087,27 +3182,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:40:00</t>
+          <t>2026-06-08 07:38:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>bankaya soruşturma</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Niğde’de depo yangını korkuttu</t>
+          <t>Rahmi Koç'un "Kürt kadın fıkrasına" tepkiler sürüyor: Diyarbakır'da Koç Holding'e ait bankaya silahlı saldırı</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Niğde’de depo yangını korkuttu DMC Haber</t>
+          <t>Rahmi Koç'un "Kürt kadın fıkrasına" tepkiler sürüyor: Diyarbakır'da Koç Holding'e ait bankaya silahlı saldırı T24</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3117,22 +3212,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>banka, holding</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>finansal kuruluş | şirket / firma</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Niğde’de bir apartmanın zemin katında bulunan depoda çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle kısa sürede söndürüldü. Niğde’de bir apartmanın zemin katında bulunan depoda çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle kısa sürede söndürüldü. Niğde’de bir apartmanın zemin katında bulunan depoda çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle kısa sürede söndürüldü. Niğde’de depo yangını korkuttu Niğde’de bir apartmanın zemin katında bulunan depoda çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle kısa sürede söndürüldü. Gülcan SONGUR İnternet Editörü 06.06.2026 - 15:40 Yayınlanma 06.06.2026 - 15:52 Güncelleme 1 Dk Okunma Süresi P</t>
+          <t>İstanbul ve Antalya'dan sonra Diyarbakır: Koç Holding'e ait bankaya silahlı saldırı! İstanbul ve Antalya'dan sonra Diyarbakır: Koç Holding'e ait bankaya silahlı saldırı! İstanbul ve Antalya'dan sonra Diyarbakır: Koç Holding'e ait bankaya silahlı saldırı! Magazin Çevre Sağlık Eğitim 8 Haziran 2026 10:38 Güncelleme: 8 Haziran 2026 11:18 İstanbul ve Antalya'daki saldırıların ardından Diyarbakır'da Koç Holding'e ait Yapı Kredi bankası şubesine silahlı saldırı düzenlendi. Polis ekipleri, yolu trafiğe kapattı ve olayla ilgili inceleme başlattı. İstanbul'un ardından Antalya'daki Koç Holding’e bağlı Otokoç galerisine de silahlı saldırı! Amida Haber'in aktardığına göre; İstanbul ve Antalya'dan sonra Koç Holding'e ait bir saldırı haberi de Diyarbakır’dan geldi. Olay, dün akşam 23.30 sularında Diyarbakır merkez Sur ilçesinde yaşandı. Kimliği belirsiz kişi ya da kişiler, Koç grubuna bağlı Yapı Kredi Bankası şubesine silahlı saldırı düzenledi. Sabah saatlerinde bankayı açan görevliler camlarda kurşun izi görünce durumu polise bildirdi. Polis ekipleri alanda inceleme yaparak Gazi Caddesi'ni trafiğe kapattı. Şube, geçici olarak kapatıldı. Ne olmuştu? Koç Holding Şeref Başkanı Rahmi Koç 'un İzmir'deki açılışta anlattığı 'Kürt kadın hasta' fıkrası tepkilere neden olmuştu. Tepkilerin ardından İzmir Cumhuriyet Başsavcılığı, Rahmi Koç hakkında "Halkın Bir Kesimini Sosyal Sınıf, Irk, Din, Mezhep, Cinsiyet veya Bölge Farklılığına Dayanarak Alenen Aşağılama' suçundan" soruşturma başlatılmıştı. Rahmi Koç özür mesajı yayımlarken, "Herhangi bir kimliği hedef alma niyeti taşımadığım sözlerim için içtenlikle özür diliyorum. Üzüntümü samimiyetle paylaşma</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Niğde’de depo yangını korkuttu Niğde’de depo yangını korkuttu DMC Haber Niğde’de bir apartmanın zemin katında bulunan depoda çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle kısa sürede söndürüldü. Niğde’de depo yangını korkuttu Niğde’de bir apartmanın zemin katında bulunan depoda çıkan yangın, itfaiye ekiplerinin hızlı müdahalesiyle kısa sürede söndürüldü. Gülcan SONGUR İnternet Editörü 06.06.2026 - 15:40 Yayınlanma 06.06.2026 - 15:52 Güncelleme 1 Dk Okunma Süresi P</t>
+          <t>Rahmi Koç'un "Kürt kadın fıkrasına" tepkiler sürüyor: Diyarbakır'da Koç Holding'e ait bankaya silahlı saldırı Rahmi Koç'un "Kürt kadın fıkrasına" tepkiler sürüyor: Diyarbakır'da Koç Holding'e ait bankaya silahlı saldırı T24 İstanbul ve Antalya'dan sonra Diyarbakır: Koç Holding'e ait bankaya silahlı saldırı! Magazin Çevre Sağlık Eğitim 8 Haziran 2026 10:38 Güncelleme: 8 Haziran 2026 11:18 İstanbul ve Antalya'daki saldırıların ardından Diyarbakır'da Koç Holding'e ait Yapı Kredi bankası şubesine silahlı saldırı düzenlendi. Polis ekipleri, yolu trafiğe kapattı ve olayla ilgili inceleme başlattı. İstanbul'un ardından Antalya'daki Koç Holding’e bağlı Otokoç galerisine de silahlı saldırı! Amida Haber'in aktardığına göre; İstanbul ve Antalya'dan sonra Koç Holding'e ait bir saldırı haberi de Diyarbakır’dan geldi. Olay, dün akşam 23.30 sularında Diyarbakır merkez Sur ilçesinde yaşandı. Kimliği belirsiz kişi ya da kişiler, Koç grubuna bağlı Yapı Kredi Bankası şubesine silahlı saldırı düzenledi. Polis ekipleri alanda inceleme yaparak Gazi Caddesi'ni trafiğe kapattı. Şube, geçici olarak kapatıldı. Koç Holding Şeref Başkanı Rahmi Koç 'un İzmir'deki açılışta anlattığı 'Kürt kadın hasta' fıkrası tepkilere neden olmuştu. Tepkilerin ardından İzmir Cumhuriyet Başsavcılığı, Rahmi Koç hakkında "Halkın Bir Kesimini Sosyal Sınıf, Irk, Din, Mezhep, Cinsiyet veya Bölge Farklılığına Dayanarak Alenen Aşağılama' suçundan" soruşturma başlatılmıştı. Rahmi Koç özür mesajı yayımlarken, "Herhangi bir kimliği hedef alma niyeti taşımadığım sözlerim için içtenlikle özür diliyorum.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -3142,37 +3237,61 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.dmchaber.com/nigdede-depo-yangini-korkuttu</t>
+          <t>https://t24.com.tr/gundem/diyarbakirda-koc-holdinge-ait-bankaya-silahli-saldiri,1327468?_t=1780910556011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Niğde</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>Antalya | Diyarbakır | İstanbul | İzmir</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>alanda inceleme yaparak Gazi Caddesi</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr"/>
+          <t>faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding alanda inceleme yaparak Gazi Caddesi Sur Antalya Türkiye</t>
+        </is>
+      </c>
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>Caffè Nero</t>
+        </is>
+      </c>
       <c r="AA12" s="2" t="n">
-        <v>49.66</v>
+        <v>207.75</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>11</v>
@@ -3181,27 +3300,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:47:39</t>
+          <t>2026-06-07 12:27:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>usulsüzlük</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sinop'ta fabrikanın depo bölümünde çıkan yangın hasara neden oldu</t>
+          <t>Buca belediyesinde 'bankamatik sevgili' İddiaları: SGK müfettiş raporu savcılıkta!</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Sinop'ta fabrikanın depo bölümünde çıkan yangın hasara neden oldu Haberler</t>
+          <t>Buca belediyesinde 'bankamatik sevgili' İddiaları: SGK müfettiş raporu savcılıkta! Son Mühür</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -3211,22 +3330,22 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>depo, fabrika</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>fabrika | depo</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Sinop'un Ayancık ilçesinde bir orman ürünleri fabrikasının talaş deposunda çıkan yangın, itfaiye ve orman ekiplerinin müdahalesiyle diğer bölümlere sıçramadan söndürüldü. Depoda hasar oluştu. Sinop'un Ayancık ilçesinde bir orman ürünleri fabrikasının talaş deposunda çıkan yangın, itfaiye ve orman ekiplerinin müdahalesiyle diğer bölümlere sıçramadan söndürüldü. Depoda hasar oluştu. Sinop'un Ayancık ilçesinde bir orman ürünleri fabrikasının talaş deposunda çıkan yangın, itfaiye ve orman ekiplerinin müdahalesiyle diğer bölümlere sıçramadan söndürüldü. Depoda hasar oluştu. Sinop'ta fabrikanın depo bölümünde çıkan yangın hasara neden oldu Sinop'un Ayancık ilçesinde bir orman ürünleri fabrikasının talaş deposunda çıkan yangın, itfaiye ve orman ekiplerinin müdahalesiyle diğer bölümlere sıçramadan söndürüldü. Depoda hasar oluştu.</t>
+          <t>Buca Belediyesi’ne yönelik yürütülen rüşvet ve usulsüzlük soruşturmasında 42 kişi tutuklanırken, SGK müfettişlerinin hazırladığı raporla yeni bir boyut kazandı. Gizlilik kararı bulunan dosyaya, işe gelmeden maaş alan 'bankamatikçi' personelin yanı sıra, belediye iştiraki şirketlere 'sevgili' kontenjanından usulsüz alımlar yapıldığı iddiaları girdi. Olayın geçmişte Uşak ve Bornova belediyelerinde yaşanan benzer skandallarla bağı araştırılıyor. Buca Belediyesi’ne yönelik yürütülen rüşvet ve usulsüzlük soruşturmasında 42 kişi tutuklanırken, SGK müfettişlerinin hazırladığı raporla yeni bir boyut kazandı. Gizlilik kararı bulunan dosyaya, işe gelmeden maaş alan 'bankamatikçi' personelin yanı sıra, belediye iştiraki şirketlere 'sevgili' kontenjanından usulsüz alımlar yapıldığı iddiaları girdi. Olayın geçmişte Uşak ve Bornova belediyelerinde yaşanan benzer skandallarla bağı araştırılıyor. Buca Belediyesi’ne yönelik yürütülen rüşvet ve usulsüzlük soruşturmasında 42 kişi tutuklanırken, SGK müfettişlerinin hazırladığı raporla yeni bir boyut kazandı. Gizlilik kararı bulunan dosyaya, işe gelmeden maaş alan 'bankamatikçi' personelin yanı sıra, belediye iştiraki şirketlere 'sevgili' kontenjanından usulsüz alımlar yapıldığı iddiaları girdi. Olayın geçmişte Uşak ve Bornova belediyelerinde yaşanan benzer skandallarla bağı araştırılıyor. SON MÜHÜR/Cumhur Erkek-İzmir Cumhuriyet Başsavcılığı koordinasyonunda Mali Şube ekipleri tarafından başlatılan operasyonda aralarında Buca Belediye Başkanı Görkem Dman, eski başkan Erhan Kılıç, çok sayıda belediye çalışanı ile müteahhitin olduğu 42 kişi tutuklanmıştı. Sahte ruhsat ve rüşvet iddialarıyla başlayan soruşturma, derinleştirilen incelemelerle birlikte kamuoyunda 'bankamatikçi' olarak bilinen haksız kazanç ve usulsüz personel istihdamı alanına kaydı. SGK Müfettişleri Raporu Dosyada Soruşturma dosyasında en dikkat çeken iddia ise istihdam edilen bazı kişilerin profilleri oldu. İddialara göre, Buca Belediyesi’nin iştirak şirketlerine, liyakata aykırı şekilde bazı yetkililerin yakın ilişkide olduğu kişilerin 'sevgili' kontenjanından işe yerleştirildiği ileri sürüldü. Nisan ayında Buca Belediyesi’nde geniş çaplı bir denetim başlatan Sosyal Güvenlik Kurumu (SGK) müfettişleri, bir ay gibi kısa bir sürede incelemelerini tamamlayarak hazırladıkları raporu soruşturma savcısına teslim etti. Raporda, işe gelmediği halde çalışıyor gibi gösterilen personeller ve bu duruma göz yuman yetkililer tek tek listelendi. Soruşturma kapsamında, belediyede fiilen çalışmayan bu kişileri bildikleri halde duruma müdahale etmeyen, kendi aralarında bu konuda yazışmalar yapan ve sahte puantaj cetvellerine imza atarak kamuyu zarara uğratan kamu görevlileri tutuklanarak cezaevine gönderildi. Uşak ve Bornova Örneği Bu yöntem, daha önce Uşak Belediyesi'nde yaşanan ve ardından İzmir’e sıçrayan 'bankamatik sevgili' skandalını akıllara getirdi. Uşak’taki soruşturmanın ucu Bornova Belediyesi’ne kadar uzanmış, süreçte Bornova Belediye Başkanı gözaltına alınarak adli kontrol şartıyla serbest bırakılmıştı. Savcılığın, Buca'daki sistemin de bu geçmiş organizasyonlarla bir bağlantısı olup olmadığını titizlikle araştırdığı öğrenildi. Dosyada 'İtirafçı' Hareketliliği Gizlilik kararı bulunan soruşturma dosyasında, teknik takip verileri ve WhatsApp yazışmalarının yanı sıra yeni itirafçıların ortaya çıktığı belirtiliyor. İlk operasyonda etkin pişmanlıktan yararlanarak rüşvet çarkının şifrelerini veren S.K.'nın ardından, bankamatik ve usulsüz personel sürecine dahil olan bazı isimlerin de adliyede itirafçı olmak için savcılığa başvurduğu kulislere yansıyan bilgiler arasında yer alıyor. Buca belediyesinde 'bankamatik sevgili' İddiaları: SGK müfettiş raporu savcılıkta! Buca Belediyesi’ne yönelik yürütülen rüşvet ve usulsüzlük soruşturmasında 42 kişi tutuklanırken, SGK müfettişlerinin hazırladığı raporla yeni bir boyut kazandı. Gizlilik kararı bulunan dosyaya, işe gelmeden maaş alan 'bankamatikçi' personelin yanı sıra, belediye iştiraki şirketlere 'sevgili' kontenjanından usulsüz alımlar yapıldığı iddiaları girdi. Olayın geçmişte Uşak ve Bornova belediyelerinde yaşanan benzer skandallarla bağı araştırılıyor. SGK Müfettişleri Raporu Dosyada Dosyada 'İtirafçı' Hareketliliği SON MÜHÜR/Cumhur Erkek-İzmir Cumhuriyet Başsavcılığı koordinasyonunda Mali Şube ekipleri tarafından başlatılan operasyonda aralarında Buca Belediye Başkanı Görkem Dman, eski başkan Erhan Kılıç, çok sayıda belediye çalışanı ile müteahhitin olduğu 42 kişi tutuklanmıştı. Sahte ruhsat ve rüşvet iddialarıyla başlayan soruşturma, derinleştirilen incelemelerle birlikte kamuoyunda 'bankamatikçi' olarak bilinen haksız kazanç ve usulsüz personel istihdamı alanına kaydı. Soruşturma dosyasında en dikkat çeken iddia ise istihdam edilen bazı kişilerin profilleri oldu. İddialara göre, Buca Belediyesi’nin iştirak şirketlerine, liyakata aykırı şekilde bazı yetkililerin yakın ilişkide olduğu kişilerin 'sevgili' kontenjanından işe yerleştirildiği ileri sürüldü. Nisan ayında Buca Belediyesi’nde geniş çaplı bir denetim başlatan Sosyal Güvenlik Kurumu (SGK) müfettişleri, bir ay gibi kısa bir sürede incelemelerini tamamlayarak hazırladıkları raporu soruşturma savcısına teslim etti. Raporda, işe gelmediği halde çalışıyor gibi gösterilen personeller ve bu duruma göz yuman yetkililer tek tek listelendi. Soruşturma kapsamında, belediyede fiilen çalışmayan bu kişileri bildikleri halde duruma müdahale etmeyen, kendi aralarında bu konuda yazışmalar yapan ve sahte puantaj cetvellerine imza atarak kamuyu zarara uğratan kamu görevlileri tutuklanarak cezaevine gönderildi. Bu yöntem, daha önce Uşak Belediyesi'nde yaşanan ve ardından İzmir’e sıçrayan 'bankamatik sevgili' skandalını akıllara getirdi. Uşak’taki soruşturmanın ucu Bornova Belediyesi’ne kadar uzanmış, süreçte Bornova Belediye Başkanı gözaltına alınarak adli kontrol şartıyla serbest bırakılmıştı. Savcılığın, Buca'daki sistemin de bu geçmiş organizasyonlarla bir bağlantısı olup olmadığını titizlikle araştırdığı öğrenildi. Gizlilik kararı bulunan soruşturma dosyasında, teknik takip verileri ve WhatsApp yazışmalarının yanı sıra yeni itirafçıların ortaya çıktığı belirtiliyor. İlk operasyonda etkin pişmanlıktan yararlanarak rüşvet çarkının şifrelerini veren S.K.'nın ardından, bankamatik ve usulsüz personel sürecine dahil olan bazı isimlerin de adliyede itirafçı olmak için savcılığa başvurduğu kulislere yansıyan bilgiler arasında yer alıyor.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Sinop'ta fabrikanın depo bölümünde çıkan yangın hasara neden oldu Sinop'ta fabrikanın depo bölümünde çıkan yangın hasara neden oldu Haberler Sinop'un Ayancık ilçesinde bir orman ürünleri fabrikasının talaş deposunda çıkan yangın, itfaiye ve orman ekiplerinin müdahalesiyle diğer bölümlere sıçramadan söndürüldü. Sinop'ta fabrikanın depo bölümünde çıkan yangın hasara neden oldu Sinop'un Ayancık ilçesinde bir orman ürünleri fabrikasının talaş deposunda çıkan yangın, itfaiye ve orman ekiplerinin müdahalesiyle diğer bölümlere sıçramadan söndürüldü.</t>
+          <t>Buca belediyesinde 'bankamatik sevgili' İddiaları: SGK müfettiş raporu savcılıkta! Buca belediyesinde 'bankamatik sevgili' İddiaları: SGK müfettiş raporu savcılıkta! Son Mühür Buca Belediyesi’ne yönelik yürütülen rüşvet ve usulsüzlük soruşturmasında 42 kişi tutuklanırken, SGK müfettişlerinin hazırladığı raporla yeni bir boyut kazandı. Gizlilik kararı bulunan dosyaya, işe gelmeden maaş alan 'bankamatikçi' personelin yanı sıra, belediye iştiraki şirketlere 'sevgili' kontenjanından usulsüz alımlar yapıldığı iddiaları girdi. Olayın geçmişte Uşak ve Bornova belediyelerinde yaşanan benzer skandallarla bağı araştırılıyor. SON MÜHÜR/Cumhur Erkek-İzmir Cumhuriyet Başsavcılığı koordinasyonunda Mali Şube ekipleri tarafından başlatılan operasyonda aralarında Buca Belediye Başkanı Görkem Dman, eski başkan Erhan Kılıç, çok sayıda belediye çalışanı ile müteahhitin olduğu 42 kişi tutuklanmıştı. Sahte ruhsat ve rüşvet iddialarıyla başlayan soruşturma, derinleştirilen incelemelerle birlikte kamuoyunda 'bankamatikçi' olarak bilinen haksız kazanç ve usulsüz personel istihdamı alanına kaydı. SGK Müfettişleri Raporu Dosyada Soruşturma dosyasında en dikkat çeken iddia ise istihdam edilen bazı kişilerin profilleri oldu. İddialara göre, Buca Belediyesi’nin iştirak şirketlerine, liyakata aykırı şekilde bazı yetkililerin yakın ilişkide olduğu kişilerin 'sevgili' kontenjanından işe yerleştirildiği ileri sürüldü. Nisan ayında Buca Belediyesi’nde geniş çaplı bir denetim başlatan Sosyal Güvenlik Kurumu (SGK) müfettişleri, bir ay gibi kısa bir sürede incelemelerini tamamlayarak hazırladıkları raporu soruşturma savcısına teslim etti. Soruşturma kapsamında, belediyede fiilen çalışmayan bu kişileri bildikleri halde duruma müdahale etmeyen, kendi aralarında bu konuda yazışmalar yapan ve sahte puantaj cetvellerine imza atarak kamuyu zarara uğratan kamu görevlileri tutuklanarak cezaevine gönderildi. Uşak ve Bornova Örneği Bu yöntem, daha önce Uşak Belediyesi'nde yaşanan ve ardından İzmir’e sıçrayan 'bankamatik sevgili' skandalını akıllara getirdi. Uşak’taki soruşturmanın ucu Bornova Belediyesi’ne kadar uzanmış, süreçte Bornova Belediye Başkanı gözaltına alınarak adli kontrol şartıyla serbest bırakılmıştı. Savcılığın, Buca'daki sistemin de bu geçmiş organizasyonlarla bir bağlantısı olup olmadığını titizlikle araştırdığı öğrenildi. Dosyada 'İtirafçı' Hareketliliği Gizlilik kararı bulunan soruşturma dosyasında, teknik takip verileri ve WhatsApp yazışmalarının yanı sıra yeni itirafçıların ortaya çıktığı belirtiliyor. İlk operasyonda etkin pişmanlıktan yararlanarak rüşvet çarkının şifrelerini veren S.K.'nın ardından, bankamatik ve usulsüz personel sürecine dahil olan bazı isimlerin de adliyede itirafçı olmak için savcılığa başvurduğu kulislere yansıyan bilgiler arasında yer alıyor. Buca belediyesinde 'bankamatik sevgili' İddiaları: SGK müfettiş raporu savcılıkta! SGK Müfettişleri Raporu Dosyada Dosyada 'İtirafçı' Hareketliliği SON MÜHÜR/Cumhur Erkek-İzmir Cumhuriyet Başsavcılığı koordinasyonunda Mali Şube ekipleri tarafından başlatılan operasyonda aralarında Buca Belediye Başkanı Görkem Dman, eski başkan Erhan Kılıç, çok sayıda belediye çalışanı ile müteahhitin olduğu 42 kişi tutuklanmıştı. Soruşturma dosyasında en dikkat çeken iddia ise istihdam edilen bazı kişilerin profilleri oldu. Bu yöntem, daha önce Uşak Belediyesi'nde yaşanan ve ardından İzmir’e sıçrayan 'bankamatik sevgili' skandalını akıllara getirdi. Gizlilik kararı bulunan soruşturma dosyasında, teknik takip verileri ve WhatsApp yazışmalarının yanı sıra yeni itirafçıların ortaya çıktığı belirtiliyor.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -3236,19 +3355,15 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.haberler.com/amp/sinop-ta-fabrika-deposunda-yangin-sonduruldu-19919889-haberi/</t>
+          <t>https://www.sonmuhur.com/buca-belediyesinde-bankamatik-sevgili-iddialari-sgk-mufettis-raporu-savcilikta/amp</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Sinop</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Ayancık</t>
-        </is>
-      </c>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -3256,7 +3371,7 @@
       <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr"/>
@@ -3270,7 +3385,7 @@
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="n">
-        <v>95.33</v>
+        <v>95</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>12</v>
@@ -3279,27 +3394,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 06:20:58</t>
+          <t>2026-06-08 05:25:00</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>nitelikli dolandırıcılık</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kars Polisi Banka Personeli ve Güvenlikçileri Bilgilendirdi: Şüpheli İşlemlerde Jet İhbar Dönemi</t>
+          <t>100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Kars Polisi Banka Personeli ve Güvenlikçileri Bilgilendirdi: Şüpheli İşlemlerde Jet İhbar Dönemi igdirhaber.net</t>
+          <t>100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti Ekonomim</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -3309,32 +3424,32 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Kars Polisi Banka Personeli ve Güvenlikçileri Bilgilendirdi: Şüpheli İşlemlerde Jet İhbar Dönemi igdirhaber.net</t>
+          <t>Patrop Group 15 yıl önce alüminyum üretimi için iki dev fabrika kurdu. 6 kıtada 100 ülkeye ihracat yapan alüminyum devi, yüksek kur, maliyet baskısı ve nakit akışı sorunlarına dayanamayıp, konkordato ilan etti.... 100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti İstanbul 2. Asliye Ticaret Mahkemesi, Patrop Group İnşaat Sanayi ve Ticaret A.Ş. ile şirket ortağı Ziya Güngör tarafından yapılan konkordato sürecinde iflasa karar verdi. Haber Merkezi | 08.06.2026 08:25 Patrop Group 15 yıl önce alüminyum üretimi için iki dev fabrika kurdu. 6 kıtada 100 ülkeye ihracat yapan alüminyum devi, yüksek kur, maliyet baskısı ve nakit akışı sorunlarına dayanamayıp, konkordato ilan etti. Yaklaşık 3 aylık konkordato sürecinin ardından şirketin iflasına karar verildi. Mahkeme kararını verdi Mahkeme tarafından yayımlanan ilan metnine göre, İstanbul Ticaret Sicil Müdürlüğü'ne kayıtlı Patrop Group İnşaat Sanayi ve Ticaret A.Ş. hakkında 21 Mayıs 2026 tarihinde saat 17.15 itibarıyla iflasın açılmasına karar verildi. Mahkemenin aldığı karara göre Patrop Group İnşaat'ın iflas tasfiyesi, İstanbul İflas Müdürlüğü tarafından adi tasfiye usulüyle yapılacak. İcra ve İflas Kanunu'nun ilgili hükümleri kapsamında iflas kararı ilan edilecek ve davacılar tarafından yatırılan iflas avansları da İstanbul İflas Müdürlüğü'ne verilecek. Vergi denetiminde yapay zekâ dönemi başlıyor Ekonomi Benzine zam ya da indirim var mı? İşte 8 Haziran 2026 güncel benzin, motorin ve LPG fiyatları Ekonomi Buca Belediye Başkanı Görkem Duman, görevden uzaklaştırıldı Gündem Banka ATM'lerinden geçen sahte dolar üreten şebeke çökertildi Gündem Patrop Group 15 yıl önce alüminyum üretimi için iki dev fabrika kurdu. 6 kıtada 100 ülkeye ihracat yapan alüminyum devi, yüksek kur, maliyet baskısı ve nakit akışı sorunlarına dayanamayıp, konkordato ilan etti. Yaklaşık 3 aylık konkordato sürecinin ardından şirketin iflasına karar verildi. Mahkeme kararını verdi Mahkeme tarafından yayımlanan ilan metnine göre, İstanbul Ticaret Sicil Müdürlüğü'ne kayıtlı Patrop Group İnşaat Sanayi ve Ticaret A.Ş. hakkında 21 Mayıs 2026 tarihinde saat 17.15 itibarıyla iflasın açılmasına karar verildi. Mahkemenin aldığı karara göre Patrop Group İnşaat'ın iflas tasfiyesi, İstanbul İflas Müdürlüğü tarafından adi tasfiye usulüyle yapılacak. İcra ve İflas Kanunu'nun ilgili hükümleri kapsamında iflas kararı ilan edilecek ve davacılar tarafından yatırılan iflas avansları da İstanbul İflas Müdürlüğü'ne verilecek. Vergi denetiminde yapay zekâ dönemi başlıyor Ekonomi Benzine zam ya da indirim var mı? İşte 8 Haziran 2026 güncel benzin, motorin ve LPG fiyatları Ekonomi Buca Belediye Başkanı Görkem Duman, görevden uzaklaştırıldı Gündem Banka ATM'lerinden geçen sahte dolar üreten şebeke çökertildi Gündem 100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti İstanbul 2. Asliye Ticaret Mahkemesi, Patrop Group İnşaat Sanayi ve Ticaret A.Ş. ile şirket ortağı Ziya Güngör tarafından yapılan konkordato sürecinde iflasa karar verdi. Patrop Group 15 yıl önce alüminyum üretimi için iki dev fabrika kurdu. 6 kıtada 100 ülkeye ihracat yapan alüminyum devi, yüksek kur, maliyet baskısı ve nakit akışı sorunlarına dayanamayıp, konkordato ilan etti. Yaklaşık 3 aylık konkordato sürecinin ardından şirketin iflasına karar verildi. Mahkeme tarafından yayımlanan ilan metnine göre, İstanbul Ticaret Sicil Müdürlüğü'ne kayıtlı Patrop Group İnşaat Sanayi ve Ticaret A.Ş. hakkında 21 Mayıs 2026 tarihinde saat 17.15 itibarıyla iflasın açılmasına karar verildi. Mahkemenin aldığı karara göre Patrop Group İnşaat'ın iflas tasfiyesi, İstanbul İflas Müdürlüğü tarafından adi tasfiye usulüyle yapılacak. İcra ve İflas Kanunu'nun ilgili hükümleri kapsamında iflas kararı ilan edilecek ve davacılar tarafından yatırılan iflas avansları da İstanbul İflas Müdürlüğü'ne verilecek.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Kars Polisi Banka Personeli ve Güvenlikçileri Bilgilendirdi: Şüpheli İşlemlerde Jet İhbar Dönemi Kars Polisi Banka Personeli ve Güvenlikçileri Bilgilendirdi: Şüpheli İşlemlerde Jet İhbar Dönemi igdirhaber.net Kars Polisi Banka Personeli ve Güvenlikçileri Bilgilendirdi: Şüpheli İşlemlerde Jet İhbar Dönemi igdirhaber.net</t>
+          <t>100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti 100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti Ekonomim Patrop Group 15 yıl önce alüminyum üretimi için iki dev fabrika kurdu. 6 kıtada 100 ülkeye ihracat yapan alüminyum devi, yüksek kur, maliyet baskısı ve nakit akışı sorunlarına dayanamayıp, konkordato ilan etti.... 100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti İstanbul 2. Asliye Ticaret Mahkemesi, Patrop Group İnşaat Sanayi ve Ticaret A.Ş. ile şirket ortağı Ziya Güngör tarafından yapılan konkordato sürecinde iflasa karar verdi. Haber Merkezi | 08.06.2026 08:25 Patrop Group 15 yıl önce alüminyum üretimi için iki dev fabrika kurdu. Yaklaşık 3 aylık konkordato sürecinin ardından şirketin iflasına karar verildi. Mahkeme kararını verdi Mahkeme tarafından yayımlanan ilan metnine göre, İstanbul Ticaret Sicil Müdürlüğü'ne kayıtlı Patrop Group İnşaat Sanayi ve Ticaret A.Ş. hakkında 21 Mayıs 2026 tarihinde saat 17.15 itibarıyla iflasın açılmasına karar verildi. Mahkemenin aldığı karara göre Patrop Group İnşaat'ın iflas tasfiyesi, İstanbul İflas Müdürlüğü tarafından adi tasfiye usulüyle yapılacak. İcra ve İflas Kanunu'nun ilgili hükümleri kapsamında iflas kararı ilan edilecek ve davacılar tarafından yatırılan iflas avansları da İstanbul İflas Müdürlüğü'ne verilecek. Vergi denetiminde yapay zekâ dönemi başlıyor Ekonomi Benzine zam ya da indirim var mı? İşte 8 Haziran 2026 güncel benzin, motorin ve LPG fiyatları Ekonomi Buca Belediye Başkanı Görkem Duman, görevden uzaklaştırıldı Gündem Banka ATM'lerinden geçen sahte dolar üreten şebeke çökertildi Gündem Patrop Group 15 yıl önce alüminyum üretimi için iki dev fabrika kurdu. İşte 8 Haziran 2026 güncel benzin, motorin ve LPG fiyatları Ekonomi Buca Belediye Başkanı Görkem Duman, görevden uzaklaştırıldı Gündem Banka ATM'lerinden geçen sahte dolar üreten şebeke çökertildi Gündem 100 ülkeye ihracat yapıyordu: Türk alüminyum şirketi iflas etti İstanbul 2. Mahkeme tarafından yayımlanan ilan metnine göre, İstanbul Ticaret Sicil Müdürlüğü'ne kayıtlı Patrop Group İnşaat Sanayi ve Ticaret A.Ş. hakkında 21 Mayıs 2026 tarihinde saat 17.15 itibarıyla iflasın açılmasına karar verildi.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQaVBVaS1ab0N4cmNHSU92dVVFdEt3WHN2cHljaG9CQ3ZtMXVVTW11LWlBYi1FbUEyalhrZGV2VFhiNF9HS2R4cXpMaDFlMlMxdUlzaTVQYW51WEpUY0VJSWt5aGFpaXJYeFpheFhIcUpyNG54NVZyX2JmTUFsMlpLaG9IM3ZuYWRfOTJBY3hpOHNnZmg0ejQ5ZnlnYWl4bjAxbzllcmJzME9NZHE5UjZ3Sk8xMVQxYnRBTzQ3RE5YN2NNQ2d4clRr?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.ekonomim.com/amp/sirketler/100-ulkeye-ihracat-yapiyordu-turk-aluminyum-sirketi-iflas-etti-haberi-898438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
@@ -3342,25 +3457,49 @@
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş:57:body | Patrop Group İnşaat Sanayi ve Ticaret A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr"/>
-      <c r="V14" s="2" t="inlineStr"/>
-      <c r="W14" s="2" t="inlineStr"/>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş Türkiye</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group</t>
+        </is>
+      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="n">
-        <v>82.86</v>
+        <v>159.9</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>13</v>
@@ -3369,12 +3508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 12:25:00</t>
+          <t>2026-06-08 06:24:00</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>tasfiye</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3384,12 +3523,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Şimşek ‘Büyüyoruz’ Dedi, Son İki Günde 6 Şirket Konkordato İlan Etti</t>
+          <t>Dünya devine büyük şok: 6 kıtaya ihracat yapan Türk sanayi devi iflas etti!</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Şimşek ‘Büyüyoruz’ Dedi, Son İki Günde 6 Şirket Konkordato İlan Etti Habererk.com</t>
+          <t>Dünya devine büyük şok: 6 kıtaya ihracat yapan Türk sanayi devi iflas etti! Bursada Bugün</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -3399,22 +3538,18 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>sanayi</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Son iki gün içinde farklı sektörlerde faaliyet gösteren 6 şirket konkordato başvurusunda bulundu. Yüksek finansman maliyetleri, krediye erişim sorunları ve nakit akışı sıkıntıları, reel sektörün karşı karşıya olduğu başlıca riskler arasında gösteriliyor Son iki gün içinde farklı sektörlerde faaliyet gösteren 6 şirket konkordato başvurusunda bulundu. Yüksek finansman maliyetleri, krediye erişim sorunları ve nakit akışı sıkıntıları, reel sektörün karşı karşıya olduğu başlıca riskler arasında gösteriliyor Son iki gün içinde farklı sektörlerde faaliyet gösteren 6 şirket konkordato başvurusunda bulundu. Yüksek finansman maliyetleri, krediye erişim sorunları ve nakit akışı sıkıntıları, reel sektörün karşı karşıya olduğu başlıca riskler arasında gösteriliyor Beğen,</t>
+          <t>15 yıl önce iki dev fabrikayla üretime başlayan ve 6 kıtada 100 ülkeye ihracat yapan alüminyum devi Patrop Group, yüksek kur ve maliyet baskılarına dayanamayarak iflas etti; mahkeme dev şirketin tasfiyesine karar verdi. 15 yıl önce iki dev fabrikayla üretime başlayan ve 6 kıtada 100 ülkeye ihracat yapan alüminyum devi Patrop Group, yüksek kur ve maliyet baskılarına dayanamayarak iflas etti; mahkeme dev şirketin tasfiyesine karar verdi. 15 yıl önce iki dev fabrikayla üretime başlayan ve 6 kıtada 100 ülkeye ihracat yapan alüminyum devi Patrop Group, yüksek kur ve maliyet baskılarına dayanamayarak iflas etti; mahkeme dev şirketin tasfiyesine karar verdi. Dünya devine büyük şok: 6 kıtaya ihracat yapan Türk sanayi devi iflas etti! Mahkeme Nihai Kararını Açıkladı: Büyük Üretici İçin Tasfiye Süreci Başladı İstanbul İflas Müdürlüğü Devreye Giriyor 15 yıl önce iki dev fabrikayla üretime başlayan ve 6 kıtada 100 ülkeye ihracat yapan alüminyum devi Patrop Group, yüksek kur ve maliyet baskılarına dayanamayarak iflas etti; mahkeme dev şirketin tasfiyesine karar verdi. Yaklaşık 15 yıl önce büyük yatırımlarla sektöre adım atan ve kısa sürede küresel ölçekte bir güce dönüşen alüminyum üreticisi, ekonomik dalgalanmalara daha fazla direnemedi. Üretim üssü olarak kurulan iki dev fabrika vasıtasıyla dünya genelinde yüzü aşkın ülkeye ürün tedariki sağlayan endüstri devi, son dönemde artan maliyet baskıları ve likidite sıkışıklığı nedeniyle zor günler geçiriyordu. Döviz kurundaki ani yükselişlerin yarattığı finansal yükü taşımakta zorlanan şirket, çareyi yargıya başvurarak koruma talep etmekte bulmuştu. Ancak yaklaşık üç ay süren yasal süreç, dev firmanın kurtarılması için yeterli olmadı. Şirketin mali dengesini yeniden sağlama amacıyla başlatılan konkordato sürecinin olumsuz sonuçlanması üzerine yargı kanadından radikal bir hamle geldi. İstanbul Ticaret Sicil Müdürlüğü bünyesinde faaliyet gösteren Patrop Group İnşaat Sanayi ve Ticaret A.Ş. için yasal koruma kalkanı kaldırılarak resmi olarak iflas bayrağı çekildi. İlgili mahkemenin akşam saatlerinde kayda geçen kararıyla birlikte, sanayi devinin ticari faaliyetleri hukuki olarak sona ermiş oldu. Alınan bu kritik kararın ardından şirketin varlıklarının ve borçlarının yönetimi için yeni bir döneme girildi. İcra ve İflas Kanunu hükümleri uyarınca yürütülecek olan tasfiye işlemleri, İstanbul İflas Müdürlüğü tarafından adi tasfiye kurallarına göre gerçekleştirilecek. Yasal prosedürlerin hızlı bir şekilde işletilmesi amacıyla davayı açan taraflarca sağlanan iflas avansları da ilgili müdürlüğün hesaplarına aktarıldı. Sektörde derin bir yankı uyandıran bu gelişme, küresel pazarda geniş bir müşteri ağına sahip olan markanın tasfiye sürecinin resmen kamuoyuna duyurulmasıyla netlik kazandı. Diğer Ekonomi Haberleri için tıklayın Ülke batmış fabrika batsa ne olur Camları kırık otomobilin arka koltuğunda ölü bulundu TOKİ Bursa için düğmeye bastı! Başvurular yakında başlıyor Hamile eşe kan donduran tuzak! İşte katil kocanın savunması Kenan İmirzalıoğlu ve Sinem Kobal'dan arkadaşlarına sürpriz midye ikramı Bursa Rallisi'ni Kerem Kazaz kazandı Bursa'da kan donduran olayın duruşmasında çarpıcı ifadeler!</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Şimşek ‘Büyüyoruz’ Dedi, Son İki Günde 6 Şirket Konkordato İlan Etti Şimşek ‘Büyüyoruz’ Dedi, Son İki Günde 6 Şirket Konkordato İlan Etti Habererk.com Son iki gün içinde farklı sektörlerde faaliyet gösteren 6 şirket konkordato başvurusunda bulundu. Yüksek finansman maliyetleri, krediye erişim sorunları ve nakit akışı sıkıntıları, reel sektörün karşı karşıya olduğu başlıca riskler arasında gösteriliyor Son iki gün içinde farklı sektörlerde faaliyet gösteren 6 şirket konkordato başvurusunda bulundu. Yüksek finansman maliyetleri, krediye erişim sorunları ve nakit akışı sıkıntıları, reel sektörün karşı karşıya olduğu başlıca riskler arasında gösteriliyor Beğen,</t>
+          <t>Dünya devine büyük şok: 6 kıtaya ihracat yapan Türk sanayi devi iflas etti! Dünya devine büyük şok: 6 kıtaya ihracat yapan Türk sanayi devi iflas etti! Bursada Bugün 15 yıl önce iki dev fabrikayla üretime başlayan ve 6 kıtada 100 ülkeye ihracat yapan alüminyum devi Patrop Group, yüksek kur ve maliyet baskılarına dayanamayarak iflas etti; mahkeme dev şirketin tasfiyesine karar verdi. Dünya devine büyük şok: 6 kıtaya ihracat yapan Türk sanayi devi iflas etti! Mahkeme Nihai Kararını Açıkladı: Büyük Üretici İçin Tasfiye Süreci Başladı İstanbul İflas Müdürlüğü Devreye Giriyor 15 yıl önce iki dev fabrikayla üretime başlayan ve 6 kıtada 100 ülkeye ihracat yapan alüminyum devi Patrop Group, yüksek kur ve maliyet baskılarına dayanamayarak iflas etti; mahkeme dev şirketin tasfiyesine karar verdi. Yaklaşık 15 yıl önce büyük yatırımlarla sektöre adım atan ve kısa sürede küresel ölçekte bir güce dönüşen alüminyum üreticisi, ekonomik dalgalanmalara daha fazla direnemedi. Üretim üssü olarak kurulan iki dev fabrika vasıtasıyla dünya genelinde yüzü aşkın ülkeye ürün tedariki sağlayan endüstri devi, son dönemde artan maliyet baskıları ve likidite sıkışıklığı nedeniyle zor günler geçiriyordu. Döviz kurundaki ani yükselişlerin yarattığı finansal yükü taşımakta zorlanan şirket, çareyi yargıya başvurarak koruma talep etmekte bulmuştu. Ancak yaklaşık üç ay süren yasal süreç, dev firmanın kurtarılması için yeterli olmadı. Şirketin mali dengesini yeniden sağlama amacıyla başlatılan konkordato sürecinin olumsuz sonuçlanması üzerine yargı kanadından radikal bir hamle geldi. İstanbul Ticaret Sicil Müdürlüğü bünyesinde faaliyet gösteren Patrop Group İnşaat Sanayi ve Ticaret A.Ş. için yasal koruma kalkanı kaldırılarak resmi olarak iflas bayrağı çekildi. İlgili mahkemenin akşam saatlerinde kayda geçen kararıyla birlikte, sanayi devinin ticari faaliyetleri hukuki olarak sona ermiş oldu. Alınan bu kritik kararın ardından şirketin varlıklarının ve borçlarının yönetimi için yeni bir döneme girildi. İcra ve İflas Kanunu hükümleri uyarınca yürütülecek olan tasfiye işlemleri, İstanbul İflas Müdürlüğü tarafından adi tasfiye kurallarına göre gerçekleştirilecek. Yasal prosedürlerin hızlı bir şekilde işletilmesi amacıyla davayı açan taraflarca sağlanan iflas avansları da ilgili müdürlüğün hesaplarına aktarıldı. Sektörde derin bir yankı uyandıran bu gelişme, küresel pazarda geniş bir müşteri ağına sahip olan markanın tasfiye sürecinin resmen kamuoyuna duyurulmasıyla netlik kazandı. Diğer Ekonomi Haberleri için tıklayın Ülke batmış fabrika batsa ne olur Camları kırık otomobilin arka koltuğunda ölü bulundu TOKİ Bursa için düğmeye bastı! Başvurular yakında başlıyor Hamile eşe kan donduran tuzak! İşte katil kocanın savunması Kenan İmirzalıoğlu ve Sinem Kobal'dan arkadaşlarına sürpriz midye ikramı Bursa Rallisi'ni Kerem Kazaz kazandı Bursa'da kan donduran olayın duruşmasında çarpıcı ifadeler!</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -3424,33 +3559,61 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.habererk.com/haber/simsek-buyuyoruz-dedi-son-iki-gunde-6-sirket-konkordato-ilan-etti_334268/</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>https://www.bursadabugun.com/haber/dunya-devine-buyuk-sok-6-kitaya-ihracat-yapan-turk-sanayi-devi-iflas-etti-1927050.html</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr"/>
-      <c r="V15" s="2" t="inlineStr"/>
-      <c r="W15" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş Bursa Türkiye</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group</t>
+        </is>
+      </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="n">
-        <v>77.93000000000001</v>
+        <v>176.75</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>14</v>
@@ -3459,7 +3622,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 08:23:00</t>
+          <t>2026-06-08 06:25:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3474,12 +3637,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Gıda ve kahve şirketine 3 aylık konkordato mühleti</t>
+          <t>15 yıllık sanayi devi iflas etti! 100 ülkeye hizmet veriyordu</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Gıda ve kahve şirketine 3 aylık konkordato mühleti odakgazetesi.com</t>
+          <t>15 yıllık sanayi devi iflas etti! 100 ülkeye hizmet veriyordu Haber 7</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -3489,58 +3652,82 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>gıda, şirket</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>sanayi</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Gıda ve kahve şirketine 3 aylık konkordato mühleti odakgazetesi.com</t>
+          <t>YAŞAM Ünlü otomobil fabrikası kapatılıyor! Bir dönem sona eriyor YAŞAM Hemen yapın: Ölüm riskinizi azaltıyor! Kimse bilmiyordu YAŞAM Teşkilat'ta üzücü veda! Seyircisi hayal kırıklığına uğradı YAŞAM 2 kez yapanın ehliyeti gidiyor! Bu hareket trafikten men ediyor YAŞAM Yardım etmek istedi saldırıya uğradı! "Besle kargayı oysun gözünü" sözü gerçek oldu Nokta Elektronik Medya A.Ş. UYGULAMALAR 15 yıllık sanayi devi iflas etti! 100 ülkeye hizmet veriyordu Yaklaşık 15 yıl önce alüminyum sektörüne yatırım yaparak iki büyük üretim tesisi kuran ve ürünlerini 100'den fazla ülkeye ulaştıran Patrop Group'tan körü haber geldi. Şirket hakkında yürütülen 3 aylık konkordato sürecinin tamamlanmasının ardından mahkeme, Patrop Group'un iflasına hükmederek tasfiye sürecinin başlatılmasına karar verdi. Alüminyum sektörünün önde gelen şirketlerinden Patrop Group için süreç iflasla sonuçlandı. Uzun yıllardır üretim ve uluslararası ticaret faaliyetleri yürüten şirket, yaklaşık üç ay önce mali darboğazı aşabilmek amacıyla konkordato talebinde bulunmuştu. Ancak mahkemenin verdiği son kararla birlikte şirketin iflası resmen kesinleşti. Ünlü otomobil fabrikası kapatılıyor! Bir dönem sona eriyor Konkordato dosyasını değerlendiren mahkeme, İstanbul Ticaret Sicil Müdürlüğü'ne kayıtlı Patrop Group İnşaat Sanayi ve Ticaret A.Ş. hakkında 21 Mayıs 2026 tarihinde saat 17.15 itibarıyla iflasın açılmasına hükmetti. Karar doğrultusunda şirketin tasfiye işlemlerinin İstanbul İflas Müdürlüğü tarafından adi tasfiye usulü çerçevesinde yürütüleceği bildirildi. Hemen yapın: Ölüm riskinizi azaltıyor! Kimse bilmiyordu Önümüzdeki süreçte iflas kararının, İcra ve İflas Kanunu'nun ilgili hükümleri kapsamında resmi olarak ilan edilmesi bekleniyor. Ayrıca dava sürecinde yatırılan iflas avanslarının da İstanbul İflas Müdürlüğü'ne devredileceği ifade edildi.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Gıda ve kahve şirketine 3 aylık konkordato mühleti Gıda ve kahve şirketine 3 aylık konkordato mühleti odakgazetesi.com Gıda ve kahve şirketine 3 aylık konkordato mühleti odakgazetesi.com</t>
+          <t>15 yıllık sanayi devi iflas etti! 100 ülkeye hizmet veriyordu 15 yıllık sanayi devi iflas etti! 100 ülkeye hizmet veriyordu Haber 7 YAŞAM Ünlü otomobil fabrikası kapatılıyor! Bir dönem sona eriyor YAŞAM Hemen yapın: Ölüm riskinizi azaltıyor! Kimse bilmiyordu YAŞAM Teşkilat'ta üzücü veda! Seyircisi hayal kırıklığına uğradı YAŞAM 2 kez yapanın ehliyeti gidiyor! Bu hareket trafikten men ediyor YAŞAM Yardım etmek istedi saldırıya uğradı! "Besle kargayı oysun gözünü" sözü gerçek oldu Nokta Elektronik Medya A.Ş. UYGULAMALAR 15 yıllık sanayi devi iflas etti! 100 ülkeye hizmet veriyordu Yaklaşık 15 yıl önce alüminyum sektörüne yatırım yaparak iki büyük üretim tesisi kuran ve ürünlerini 100'den fazla ülkeye ulaştıran Patrop Group'tan körü haber geldi. Şirket hakkında yürütülen 3 aylık konkordato sürecinin tamamlanmasının ardından mahkeme, Patrop Group'un iflasına hükmederek tasfiye sürecinin başlatılmasına karar verdi. Alüminyum sektörünün önde gelen şirketlerinden Patrop Group için süreç iflasla sonuçlandı. Uzun yıllardır üretim ve uluslararası ticaret faaliyetleri yürüten şirket, yaklaşık üç ay önce mali darboğazı aşabilmek amacıyla konkordato talebinde bulunmuştu. Ancak mahkemenin verdiği son kararla birlikte şirketin iflası resmen kesinleşti. Ünlü otomobil fabrikası kapatılıyor! Bir dönem sona eriyor Konkordato dosyasını değerlendiren mahkeme, İstanbul Ticaret Sicil Müdürlüğü'ne kayıtlı Patrop Group İnşaat Sanayi ve Ticaret A.Ş. hakkında 21 Mayıs 2026 tarihinde saat 17.15 itibarıyla iflasın açılmasına hükmetti. Karar doğrultusunda şirketin tasfiye işlemlerinin İstanbul İflas Müdürlüğü tarafından adi tasfiye usulü çerçevesinde yürütüleceği bildirildi. Kimse bilmiyordu Önümüzdeki süreçte iflas kararının, İcra ve İflas Kanunu'nun ilgili hükümleri kapsamında resmi olarak ilan edilmesi bekleniyor. Ayrıca dava sürecinde yatırılan iflas avanslarının da İstanbul İflas Müdürlüğü'ne devredileceği ifade edildi.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOLVRFekhSdURPRzl2T0FOSHlRSGFKcU00Y1laQk1Ya1hYVG9NWl90X3l2ZWZEVnp2ZEI0aVE4WEhkSF9KaF9HZlJFenBsZVlVRHJaR3h6M1ZmX1FYamwxWnpaMXpsVTkxUWVURW1RdUxqR0gxbDByWW92U3FNN1RCa2dHcWNyZw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPMHQ4NWR5N3BGc3ZiWjJkWVBxdEpxdWEyU04yd2RBUjNwbmkxdGlNVzZDLVNndS11ZThiTDVBeTE4SmhlcmlWbGpYVzV2SlUtYUxhX0VHTVl4Q1FnMTJGUGZ6QUE2YlpqdTRyV2tQaW5pbUU1dGtFUC1CM2xvdnFNaGMteWRWSkN4SlBwS05CNzFXbFhSelV1RE9ucDhhSkhMRWFERHM3SUVUUW9xSFHSAa4BQVVfeXFMTzB0ODVkeTdwRnN2YloyZFlQcXRKcXVhMlNOMndkQVIzcG5pMXRpTVc2Qy1TZ3UtdWU4Ykw1QXkxOEpoZXJpVmxqWFc1dkpVLWFMYV9FR01ZeENRZzEyRlBmekFBNmJaanU0cldrUGluaW1FNXRrRVAtQjNsb3ZxTWhjLXlkVkpDeEpQcEtOQjcxV2xYUnpVdURPbnA4YUpITEVhRERzN0lFVFFvcUhR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>YAŞAM Ünlü otomobil fabrikası | Ünlü otomobil fabrikası | büyük üretim tesisi</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Nokta Elektronik Medya A.Ş | Patrop Group İnşaat Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Nokta Elektronik Medya A.Ş:73:body | Nokta Elektronik Medya A.Ş:raw_legal | Patrop Group İnşaat Sanayi ve Ticaret A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr"/>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="2" t="inlineStr"/>
+          <t>il yok | ilçe yok</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Nokta Elektronik Medya A.Ş Türkiye | Patrop Group İnşaat Sanayi ve Ticaret A.Ş Türkiye</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Nokta Elektronik ve Bilişim Sistemleri | NOKTA ELEKTRONİK BILGISAYAR TV BAKIM SERVİSİ | Noktalife Elektronik | Nokta Elektronik Ve Bilişim Sistemleri San.Tic.A.Ş | Patrop Group</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Nokta Elektronik ve Bilişim Sistemleri</t>
+        </is>
+      </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>76.19047619047619 | 61.111111111111114 | 69.56521739130434 | 86.95652173913044 | 100.0</t>
+        </is>
+      </c>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="n">
-        <v>50.42</v>
+        <v>185.35</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>15</v>
@@ -3549,7 +3736,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 17:34:27</t>
+          <t>2026-06-08 08:13:19</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -3564,12 +3751,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'ün yarım asırlık tekstil devi iflas etti!</t>
+          <t>Kocaeli’de 3 şirket için konkordato süresi uzatıldı</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'ün yarım asırlık tekstil devi iflas etti! İnegöl Online</t>
+          <t>Kocaeli’de 3 şirket için konkordato süresi uzatıldı Kocaeli Barış Gazetesi</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -3579,18 +3766,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>tekstil</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Yaklaşık 150 kişiye istihdam sağlayan şirket için iflas kararı verildi. Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Yaklaşık 150 kişiye istihdam sağlayan şirket için iflas kararı verildi. Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Yaklaşık 150 kişiye istihdam sağlayan şirket için iflas kararı verildi. Hilal Gül 6 Haziran 2026 13:49 | 2 dk 6 Haziran 2026 13:49 | 2 dk İnegöl'ün yarım asırlık tekstil devi iflas etti! Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Yaklaşık 150 kişiye istihdam sağlayan şirket için iflas kararı verildi. KONKORDATO TALEBİ REDDEDİLDİ Türkiye tekstil sektöründe yaşanan ekonomik sıkıntılar nedeniyle konkordato ve iflas haberlerine bir yenisi daha eklendi. Bursa merkezli Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi hakkında mahkeme tarafından iflas kararı verildi. Bursa Ticaret Sicil Müdürlüğü'ne kayıtlı olarak faaliyet gösteren ve Bursa Yenice Organize Sanayi Bölgesi'nde üretim yapan şirketin konkordato talebi mahkeme tarafından reddedildi. Şirket ile ortakları Mesut Güzeldağ ve Selçuk Güzeldağ tarafından açılan davada kesin mühlet talepleri uygun bulunmadı. İlgili ticaret mahkemesinde görülen davada, şirket ve ortaklarının konkordato başvuruları İcra ve İflas Kanunu'nun 292 ve 308'inci maddeleri kapsamında değerlendirildi. Yapılan incelemeler sonucunda konkordato taleplerinin reddine karar verildi. Kararla birlikte daha önce verilen geçici mühlet kaldırılırken, şirket lehine uygulanan tüm koruyucu tedbirler de sona erdirildi. Ayrıca konkordato komiserleri kurulunun görevine son verildiği öğrenildi. Mahkeme tarafından yapılan değerlendirmelerde Güzeldağ Tekstil'in borca batık durumda olduğu tespit edildi. Bunun üzerine şirketin 3 Haziran 2026 tarihinde saat 13.50 itibarıyla iflasına hükmedildi. Mahkeme, iflas tasfiyesinin adi tasfiye usulüyle yürütülmesine karar verdi. İşlemlerin başlatılması amacıyla dosyanın Bursa İflas Müdürlüğü'ne gönderilmesi kararlaştırıldı. Temelleri 1960'lı yıllarda manifatura ticaretiyle atılan Güzeldağ Tekstil, ilerleyen yıllarda kumaş üretimi, boya, baskı ve apre alanlarında faaliyet göstererek sektörün önemli firmalarından biri haline geldi. Şirket, uzun yıllar boyunca hem iç pazarda hem de uluslararası pazarlarda üretim gerçekleştirdi. 1996 yılında Bursa Yenice Organize Sanayi Bölgesi'nde 14 bin metrekare kapalı alana sahip üretim tesisini hizmete açan firma, son yıllarda yaptığı yatırımlar, Ar-Ge çalışmaları ve üretim kapasitesiyle dikkat çekiyordu. Yaklaşık 150 kişiye istihdam sağlayan şirket, yurt içi ve yurt dışındaki müşterilerine yönelik üretim faaliyetlerini sürdürüyordu. Haber yüklenirken bir hata oluştu.</t>
+          <t>www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>İnegöl'ün yarım asırlık tekstil devi iflas etti! İnegöl'ün yarım asırlık tekstil devi iflas etti! İnegöl Online Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Yaklaşık 150 kişiye istihdam sağlayan şirket için iflas kararı verildi. Hilal Gül 6 Haziran 2026 13:49 | 2 dk 6 Haziran 2026 13:49 | 2 dk İnegöl'ün yarım asırlık tekstil devi iflas etti! KONKORDATO TALEBİ REDDEDİLDİ Türkiye tekstil sektöründe yaşanan ekonomik sıkıntılar nedeniyle konkordato ve iflas haberlerine bir yenisi daha eklendi. Bursa merkezli Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi hakkında mahkeme tarafından iflas kararı verildi. Bursa Ticaret Sicil Müdürlüğü'ne kayıtlı olarak faaliyet gösteren ve Bursa Yenice Organize Sanayi Bölgesi'nde üretim yapan şirketin konkordato talebi mahkeme tarafından reddedildi. Şirket ile ortakları Mesut Güzeldağ ve Selçuk Güzeldağ tarafından açılan davada kesin mühlet talepleri uygun bulunmadı. İlgili ticaret mahkemesinde görülen davada, şirket ve ortaklarının konkordato başvuruları İcra ve İflas Kanunu'nun 292 ve 308'inci maddeleri kapsamında değerlendirildi. Kararla birlikte daha önce verilen geçici mühlet kaldırılırken, şirket lehine uygulanan tüm koruyucu tedbirler de sona erdirildi. Ayrıca konkordato komiserleri kurulunun görevine son verildiği öğrenildi. Mahkeme tarafından yapılan değerlendirmelerde Güzeldağ Tekstil'in borca batık durumda olduğu tespit edildi. Bunun üzerine şirketin 3 Haziran 2026 tarihinde saat 13.50 itibarıyla iflasına hükmedildi. Mahkeme, iflas tasfiyesinin adi tasfiye usulüyle yürütülmesine karar verdi. İşlemlerin başlatılması amacıyla dosyanın Bursa İflas Müdürlüğü'ne gönderilmesi kararlaştırıldı. Temelleri 1960'lı yıllarda manifatura ticaretiyle atılan Güzeldağ Tekstil, ilerleyen yıllarda kumaş üretimi, boya, baskı ve apre alanlarında faaliyet göstererek sektörün önemli firmalarından biri haline geldi. Şirket, uzun yıllar boyunca hem iç pazarda hem de uluslararası pazarlarda üretim gerçekleştirdi. 1996 yılında Bursa Yenice Organize Sanayi Bölgesi'nde 14 bin metrekare kapalı alana sahip üretim tesisini hizmete açan firma, son yıllarda yaptığı yatırımlar, Ar-Ge çalışmaları ve üretim kapasitesiyle dikkat çekiyordu. Yaklaşık 150 kişiye istihdam sağlayan şirket, yurt içi ve yurt dışındaki müşterilerine yönelik üretim faaliyetlerini sürdürüyordu.</t>
+          <t>Kocaeli’de 3 şirket için konkordato süresi uzatıldı Kocaeli’de 3 şirket için konkordato süresi uzatıldı Kocaeli Barış Gazetesi www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Doğrulama başarılı.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3600,65 +3791,37 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.inegolonline.com/haber/inegol-un-yarim-asirlik-tekstil-devi-iflas-etti-355925</t>
+          <t>https://www.kocaelibarisgazetesi.com/gundem/kocaelide-3-sirket-icin-konkordato-suresi-uzatildi-h155766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Bursa | Çanakkale | Karabük</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl | Yenice</t>
-        </is>
-      </c>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi:57:body | Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi:raw_legal</t>
-        </is>
-      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi İnegöl Bursa Türkiye</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Güzel Dağ Tekstil</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>Güzel Dağ Tekstil</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>58.333333333333336</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="n">
-        <v>177.9</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>16</v>
@@ -3667,7 +3830,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:36:22</t>
+          <t>2026-06-07 12:25:00</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3682,12 +3845,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mahkemeden karar çıktı: Bursa’da üretim devi iflas etti</t>
+          <t>Mahkeme kararıyla üretim devinin iflası açıklandı!</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Mahkemeden karar çıktı: Bursa’da üretim devi iflas etti Bursa Hayat Gazetesi</t>
+          <t>Mahkeme kararıyla üretim devinin iflası açıklandı! Manisa Kulis Haber</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -3707,22 +3870,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Mahkemeden karar çıktı: Bursa’da üretim devi iflas etti Bursa Hayat Gazetesi</t>
+          <t>Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Mahkeme, şirketin borca batık durumda olduğuna hükmederek iflasına karar verdi. Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Mahkeme, şirketin borca batık durumda olduğuna hükmederek iflasına karar verdi. Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Mahkeme, şirketin borca batık durumda olduğuna hükmederek iflasına karar verdi. Mahkeme kararıyla üretim devinin iflası açıklandı! Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Mahkeme, şirketin borca batık durumda olduğuna hükmederek iflasına karar verdi. 07.06.2026 - 15:25 Yayınlanma 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Tekstil sektöründe yaşanan ekonomik zorluklar nedeniyle konkordato ve iflas süreçlerine bir yenisi daha eklendi. Bursa'da faaliyet gösteren Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi hakkında mahkeme tarafından iflas kararı verildi. Konkordato Talebi Kabul Edilmedi Bursa Ticaret Sicil Müdürlüğü'ne kayıtlı olarak faaliyet gösteren ve Bursa Yenice Organize Sanayi Bölgesi'nde üretim yapan şirketin konkordato başvurusu ilgili mahkeme tarafından değerlendirildi. Şirket ile ortakları Mesut Güzeldağ ve Selçuk Güzeldağ tarafından yapılan kesin mühlet taleplerinin uygun bulunmadığı bildirildi. Geçici Mühlet ve Tedbirler Kaldırıldı Mahkeme kararıyla birlikte daha önce verilen geçici mühlet kaldırıldı. Şirket lehine uygulanan koruyucu tedbirlerin de sona erdirildiği açıklandı. Ayrıca konkordato komiserleri kurulunun görevine son verildiği öğrenildi. Mahkeme İflasa Hükmetti Yapılan incelemeler sonucunda şirketin borca batık durumda olduğu tespit edildi. Mahkeme, Güzeldağ Tekstil'in 3 Haziran 2026 tarihi itibarıyla iflasına karar verdi. İflas tasfiyesinin adi tasfiye usulüyle yürütülmesine hükmedilirken, dosyanın gerekli işlemler için Bursa İflas Müdürlüğü'ne gönderilmesine karar verildi. Uzun Yıllardır Tekstil Sektöründe Faaliyet Gösteriyordu Temelleri 1960'lı yıllarda manifatura ticaretiyle atılan Güzeldağ Tekstil, ilerleyen yıllarda kumaş üretimi, boya, baskı ve apre alanlarında faaliyet gösterdi. 1996 yılında Bursa Yenice Organize Sanayi Bölgesi'nde üretim tesisini hizmete açan şirket, yurt içi ve yurt dışındaki müşterilerine yönelik üretim gerçekleştiriyordu. Kaynak: Haber Merkezi Bun</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Mahkemeden karar çıktı: Bursa’da üretim devi iflas etti Mahkemeden karar çıktı: Bursa’da üretim devi iflas etti Bursa Hayat Gazetesi Mahkemeden karar çıktı: Bursa’da üretim devi iflas etti Bursa Hayat Gazetesi</t>
+          <t>Mahkeme kararıyla üretim devinin iflası açıklandı! Mahkeme kararıyla üretim devinin iflası açıklandı! Manisa Kulis Haber Bursa merkezli Güzeldağ Tekstil'in konkordato talebi mahkeme tarafından reddedildi. Mahkeme, şirketin borca batık durumda olduğuna hükmederek iflasına karar verdi. Mahkeme kararıyla üretim devinin iflası açıklandı! 07.06.2026 - 15:25 Yayınlanma 1 Dk Okunma Süresi</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQWW1Kam1fbF9jRE5LSEF6WHZWVkVEQk9oMXNfMkRSTkhZQmpTZWdEb2xEM1ptQlhMM3Z1QU40RmYtc0xjbERvSnE5ZEJvSVdJZW01RnFMaVZyM1dKX2g0T3JRZzZNLXUwUVRjcS0zVGpvTml3Q2xtNWpfbzBqRjRBcFl2d003UWJvUkRpdm5uNFo2UXQ3SXZPWkNreVRGQQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.manisakulishaber.com/mahkeme-karariyla-uretim-devinin-iflasi-aciklandi</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3734,25 +3897,49 @@
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi:raw_legal</t>
+        </is>
+      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr"/>
-      <c r="V18" s="2" t="inlineStr"/>
-      <c r="W18" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>Güzeldağ Tekstil Dericilik Sanayi ve Ticaret Limited Şirketi Bursa Türkiye</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Güzeldağ Tekstil</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Güzeldağ Tekstil</t>
+        </is>
+      </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="n">
-        <v>55.26</v>
+        <v>126.25</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>17</v>
@@ -3761,27 +3948,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:14</t>
+          <t>2026-06-08 06:35:00</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Turizm sezonunda dolandırıcılık yöntemlerini tespit etme.</t>
+          <t>Dev alüminyum fabrikası iflas etti</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Turizm sezonunda dolandırıcılık yöntemlerini tespit etme. Vietnam.vn</t>
+          <t>Dev alüminyum fabrikası iflas etti Afyon Haber</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3791,18 +3978,22 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>turizm</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Turizm sezonunda dolandırıcılık yöntemlerini tespit etme. Vietnam.vn</t>
+          <t>Dev alüminyum fabrikası iflas etti Afyon Haber</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Turizm sezonunda dolandırıcılık yöntemlerini tespit etme. Turizm sezonunda dolandırıcılık yöntemlerini tespit etme. Vietnam.vn Turizm sezonunda dolandırıcılık yöntemlerini tespit etme.</t>
+          <t>Dev alüminyum fabrikası iflas etti Dev alüminyum fabrikası iflas etti Afyon Haber Dev alüminyum fabrikası iflas etti Afyon Haber</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3812,19 +4003,23 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5WbXBnVlRlOXI1WTdRSG95d3lld1ZQTEdmUUhqR0Q2Yk1IUnFFUFN0OWRlUVY0dmxFUWlJNURFQldTYk5QV3BYb0ozX0VKY3hRTEVXTi1McklkUnFoOTFzbnVobnI5WEFGYXVRU1pGQUIwZw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBwNTNOeUNvdUtSOU04c0dZd185OGlxUmRfdFVPLXktWWZsOS1IdTU4SGZ3OFFwVVQtN0NJUk9lMVludnlNc1NYSzY2RHcwU2RIcWNzY2RSOGNQMjhoOWY3eF9QZTV2OHdTdktRRDRB?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Dev alüminyum fabrikası</t>
+        </is>
+      </c>
       <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr"/>
@@ -3838,7 +4033,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="n">
-        <v>54.18</v>
+        <v>60.96</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>18</v>
@@ -3847,12 +4042,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:34:11</t>
+          <t>2026-06-08 08:52:00</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3862,12 +4057,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Banka ve ATM'lerde Bilgilendirme Yapıldı.. Kars'ta Dolandırıcılığa Karşı Uyarı!</t>
+          <t>Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Banka ve ATM'lerde Bilgilendirme Yapıldı.. Kars'ta Dolandırıcılığa Karşı Uyarı! PolitiKARS</t>
+          <t>Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI Sakarya Yenihaber</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3887,12 +4082,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Kars Emniyet Müdürlüğü ekipleri, iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı yurttaşları bilgilendirmek amacıyla çalışma gerçekleştirdi. Kars Emniyet Müdürlüğü ekipleri, iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı yurttaşları bilgilendirmek amacıyla çalışma gerçekleştirdi. Kars Emniyet Müdürlüğü ekipleri, iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı yurttaşları bilgilendirmek amacıyla çalışma gerçekleştirdi. Banka ve ATM'lerde Bilgilendirme Yapıldı.. Kars'ta Dolandırıcılığa Karşı Uyarı! Kars Emniyet Müdürlüğü ekipleri, iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı yurttaşları bilgilendirmek amacıyla çalışma gerçekleştirdi. A+ A- Kars Emniyet Müdürlüğü ekipleri, iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı yurttaşları bilgilendirmek amacıyla çalışma gerçekleştirdi. Kent merkezindeki banka şubeleri ve ATM noktalarında yapılan faaliyetlerde, son dönemde karşılaşılan dolandırıcılık yöntemleri hakkında bilgi verildi. Çalışma kapsamında yurttaşlara bilgilendirici broşürler dağıtılırken, şüpheli durumların ilgili birimlere bildirilmesi istendi. BANKA VE ATM NOKTALARINDA BİLGİLENDİRME Kars Emniyet Müdürlüğü Toplum Destekli Polislik Şube Müdürlüğü ekipleri tarafından iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı farkındalık çalışması yapıldı. Kent merkezinde bulunan banka şubeleri ve ATM noktalarını ziyaret eden ekipler, banka personeli, özel güvenlik görevlileri ve yurttaşlarla bir araya geldi. Çalışmalarda son dönemde sıkça karşılaşılan dolandırıcılık yöntemleri hakkında bilgilendirmelerde bulunuldu. YURTTAŞLARA UYARILAR YAPILDI Ekipler tarafından yapılan bilgilendirmelerde, kendisini polis, asker, savcı veya kamu görevlisi olarak tanıtan kişilerin taleplerine itibar edilmemesi gerektiği ifade edildi. Telefon, kısa mesaj ve sosyal medya uygulamaları üzerinden gerçekleştirilen dolandırıcılık girişimlerine karşı dikkatli olunması gerektiği belirtilirken, kişisel bilgiler ile banka hesap bilgilerinin üçüncü kişilerle paylaşılmaması konusunda uyarılar yapıldı. BROŞÜRLER DAĞITILDI PolitiKARS'ın derlediği bilgilere göre; faaliyet kapsamında banka çalışanları ve özel güvenlik görevlilerine de şüpheli durumlarla karşılaşmaları halinde ilgili birimlere bilgi vermelerinin önemi anlatıldı. Yurttaşlara dolandırıcılık yöntemlerine ilişkin bilgilendirici broşürler dağıtılırken, mağduriyet yaşanmaması için dikkat edilmesi gereken hususlar aktarıldı. ÇALIŞMALARIN SÜRECEĞİ BİLDİRİLDİ Kars Emniyet Müdürlüğü tarafından yapılan açıklamada, yurttaşların huzur ve güvenliğinin sağlanmasına yönelik benzer bilgilendirme çalışmalarının devam edeceği belirtildi. Açıklamada ayrıca, şüpheli durumlarla karşılaşılması halinde yurttaşların 112 Acil Çağrı Merkezi'ne veya en yakın kolluk birimine başvurmaları istendi. Etiketle</t>
+          <t>Sakarya’da görülen nitelikli dolandırıcılık davasında 7 yıl hapis ve 1 milyon 200 bin lira adli para cezasına çarptırılan sanık hakkında verilen kararın tebliğ edilememesi üzerine Sakarya Bölge Adliye Mahkemesi ilanen tebligat yoluna gitti. Sakarya’da görülen nitelikli dolandırıcılık davasında 7 yıl hapis ve 1 milyon 200 bin lira adli para cezasına çarptırılan sanık hakkında verilen kararın tebliğ... Sakarya’da görülen nitelikli dolandırıcılık davasında 7 yıl hapis ve 1 milyon 200 bin lira adli para cezasına çarptırılan sanık hakkında verilen kararın tebliğ edilememesi üzerine Sakarya Bölge Adliye Mahkemesi ilanen tebligat yoluna gitti. Sakarya Yenihaber | Huriye Bolazar Sakarya 5. Ağır Ceza Mahkemesi’nde görülen davada, sanık Doğuş Kaytan'ın bilişim sistemlerini kullanarak ve kendisini banka görevlisi gibi tanıtarak dolandırıcılık yaptığı gerekçesiyle yargılandığı belirtildi. 1 MİLYON 200 BİN LİRA ADLİ PARA CEZASI Mahkeme, sanığın "Bilişim Sistemlerinin, Banka veya Kredi Kurumlarının Araç Olarak Kullanılması ile Kişinin Kendisini Kamu Görevlisi veya Banka Çalışanı Olarak Tanıtması Suretiyle Dolandırıcılık" suçunu işlediğine hükmederek 7 yıl hapis ve 1 milyon 200 bin lira adli para cezası verdi. İSTİNAF BAŞVURUSU REDDEDİLDİ Yerel mahkemenin kararının ardından dosya Sakarya Bölge Adliye Mahkemesi 11. Ceza Dairesi'ne taşındı. Yapılan incelemede istinaf başvurusunun esastan reddine karar verildi ve ilk derece mahkemesinin verdiği ceza onandı. KARAR TEBLİĞ EDİLEMEDİ Mahkeme kayıtlarına göre, sanığa gerekçeli kararın tebliği için çeşitli girişimlerde bulunulmasına rağmen sonuç alınamadı. Bunun üzerine 7201 sayılı Tebligat Kanunu kapsamında ilanen tebligat yöntemine başvuruldu. İKİ HAFTALIK TEMYİZ SÜRESİ BAŞLADI Sakarya Bölge Adliye Mahkemesi'nin ilanına göre kararın yayımlanmasından iki hafta sonra tebligat yapılmış sayılacak. Sanık bu tarihten itibaren iki hafta içerisinde temyiz başvurusunda bulunabilecek. Belirlenen süre içerisinde temyiz yoluna başvurulmaması halinde ise karar kesinleşecek. Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI Sakarya’da görülen nitelikli dolandırıcılık davasında 7 yıl hapis ve 1 milyon 200 bin lira adli para cezasına çarptırılan sanık hakkında verilen kararın tebliğ edilememesi üzerine Sakarya Bölge Adliye Mahkemesi ilanen tebligat yoluna gitti. Sakarya Yenihaber | Huriye Bolazar Sakarya 5. Ağır Ceza Mahkemesi’nde görülen davada, sanık Doğuş Kaytan'ın bilişim sistemlerini kullanarak ve kendisini banka görevlisi gibi tanıtarak dolandırıcılık yaptığı gerekçesiyle yargılandığı belirtildi. 1 MİLYON 200 BİN LİRA ADLİ PARA CEZASI Mahkeme, sanığın "Bilişim Sistemlerinin, Banka veya Kredi Kurumlarının Araç Olarak Kullanılması ile Kişinin Kendisini Kamu Görevlisi veya Banka Çalışanı Olarak Tanıtması Suretiyle Dolandırıcılık" suçunu işlediğine hükmederek 7 yıl hapis ve 1 milyon 200 bin lira adli para cezası verdi. İSTİNAF BAŞVURUSU REDDEDİLDİ Yerel mahkemenin kararının ardından dosya Sakarya Bölge Adliye Mahkemesi 11. Ceza Dairesi'ne taşındı. Yapılan incelemede istinaf başvurusunun esastan reddine karar verildi ve ilk derece mahkemesinin verdiği ceza onandı. Mahkeme kayıtlarına göre, sanığa gerekçeli kararın tebliği için çeşitli girişimlerde bulunulmasına rağmen sonuç alınamadı. Bunun üzerine 7201 sayılı Tebligat Kanunu kapsamında ilanen tebligat yöntemine başvuruldu. İKİ HAFTALIK TEMYİZ SÜRESİ BAŞLADI Sakarya Bölge Adliye Mahkemesi'nin ilanına göre kararın yayımlanmasından iki hafta sonra tebligat yapılmış sayılacak. Sanık bu tarihten itibaren iki hafta içerisinde temyiz başvurusunda bulunabilecek. Belirlenen süre içerisinde temyiz yoluna başvurulmaması halinde ise karar kesinleşecek. 08 Haz 2026 - 11:52 - Asayiş Yazdır Yorum yazarak Sakarya Yenihaber Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yorumlardan Sakarya Yenihabe</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Banka ve ATM'lerde Bilgilendirme Yapıldı.. Kars'ta Dolandırıcılığa Karşı Uyarı! Banka ve ATM'lerde Bilgilendirme Yapıldı.. Kars'ta Dolandırıcılığa Karşı Uyarı! PolitiKARS Kars Emniyet Müdürlüğü ekipleri, iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı yurttaşları bilgilendirmek amacıyla çalışma gerçekleştirdi. Banka ve ATM'lerde Bilgilendirme Yapıldı.. Kars'ta Dolandırıcılığa Karşı Uyarı! A+ A- Kars Emniyet Müdürlüğü ekipleri, iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı yurttaşları bilgilendirmek amacıyla çalışma gerçekleştirdi. Kent merkezindeki banka şubeleri ve ATM noktalarında yapılan faaliyetlerde, son dönemde karşılaşılan dolandırıcılık yöntemleri hakkında bilgi verildi. Çalışma kapsamında yurttaşlara bilgilendirici broşürler dağıtılırken, şüpheli durumların ilgili birimlere bildirilmesi istendi. BANKA VE ATM NOKTALARINDA BİLGİLENDİRME Kars Emniyet Müdürlüğü Toplum Destekli Polislik Şube Müdürlüğü ekipleri tarafından iletişim yoluyla gerçekleştirilen dolandırıcılık olaylarına karşı farkındalık çalışması yapıldı. Kent merkezinde bulunan banka şubeleri ve ATM noktalarını ziyaret eden ekipler, banka personeli, özel güvenlik görevlileri ve yurttaşlarla bir araya geldi. Çalışmalarda son dönemde sıkça karşılaşılan dolandırıcılık yöntemleri hakkında bilgilendirmelerde bulunuldu. YURTTAŞLARA UYARILAR YAPILDI Ekipler tarafından yapılan bilgilendirmelerde, kendisini polis, asker, savcı veya kamu görevlisi olarak tanıtan kişilerin taleplerine itibar edilmemesi gerektiği ifade edildi. Telefon, kısa mesaj ve sosyal medya uygulamaları üzerinden gerçekleştirilen dolandırıcılık girişimlerine karşı dikkatli olunması gerektiği belirtilirken, kişisel bilgiler ile banka hesap bilgilerinin üçüncü kişilerle pay</t>
+          <t>Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI Sakarya Yenihaber Sakarya’da görülen nitelikli dolandırıcılık davasında 7 yıl hapis ve 1 milyon 200 bin lira adli para cezasına çarptırılan sanık hakkında verilen kararın tebliğ edilememesi üzerine Sakarya Bölge Adliye Mahkemesi ilanen tebligat yoluna gitti. Sakarya’da görülen nitelikli dolandırıcılık davasında 7 yıl hapis ve 1 milyon 200 bin lira adli para cezasına çarptırılan sanık hakkında verilen kararın tebliğ... Sakarya Yenihaber | Huriye Bolazar Sakarya 5. Ağır Ceza Mahkemesi’nde görülen davada, sanık Doğuş Kaytan'ın bilişim sistemlerini kullanarak ve kendisini banka görevlisi gibi tanıtarak dolandırıcılık yaptığı gerekçesiyle yargılandığı belirtildi. 1 MİLYON 200 BİN LİRA ADLİ PARA CEZASI Mahkeme, sanığın "Bilişim Sistemlerinin, Banka veya Kredi Kurumlarının Araç Olarak Kullanılması ile Kişinin Kendisini Kamu Görevlisi veya Banka Çalışanı Olarak Tanıtması Suretiyle Dolandırıcılık" suçunu işlediğine hükmederek 7 yıl hapis ve 1 milyon 200 bin lira adli para cezası verdi. İSTİNAF BAŞVURUSU REDDEDİLDİ Yerel mahkemenin kararının ardından dosya Sakarya Bölge Adliye Mahkemesi 11. Yapılan incelemede istinaf başvurusunun esastan reddine karar verildi ve ilk derece mahkemesinin verdiği ceza onandı. KARAR TEBLİĞ EDİLEMEDİ Mahkeme kayıtlarına göre, sanığa gerekçeli kararın tebliği için çeşitli girişimlerde bulunulmasına rağmen sonuç alınamadı. Bunun üzerine 7201 sayılı Tebligat Kanunu kapsamında ilanen tebligat yöntemine başvuruldu. İKİ HAFTALIK TEMYİZ SÜRESİ BAŞLADI Sakarya Bölge Adliye Mahkemesi'nin ilanına göre kararın yayımlanmasından iki hafta sonra tebligat yapılmış sayılacak. Sanık bu tarihten itibaren iki hafta içerisinde temyiz başvurusunda bulunabilecek. Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI Sakarya’da görülen nitelikli dolandırıcılık davasında 7 yıl hapis ve 1 milyon 200 bin lira adli para cezasına çarptırılan sanık hakkında verilen kararın tebliğ edilememesi üzerine Sakarya Bölge Adliye Mahkemesi ilanen tebligat yoluna gitti. 08 Haz 2026 - 11:52 - Asayiş Yazdır Yorum yazarak Sakarya Yenihaber Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3902,12 +4097,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.politikars.com/banka-ve-atmlerde-bilgilendirme-yapildi-karsta-dolandiriciliga-karsi-uyari-586569h.htm</t>
+          <t>https://www.sakaryayenihaber.com/haber/28131654/kendisini-bankaci-gibi-tanitti-milyonluk-ceza-aldi</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Kars</t>
+          <t>Sakarya</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -3932,7 +4127,7 @@
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>19</v>
@@ -3941,27 +4136,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 11:14:50</t>
+          <t>2026-06-07 14:50:16</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>vergi incelemesi</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan 'Yeşil ve Geleceğin Şehirleri Projesi' için finansman</t>
+          <t>Ticaret Bakanlığından Kurban Bayramı Öncesi Dijital Dolandırıcılık Uyarısı</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan 'Yeşil ve Geleceğin Şehirleri Projesi' için finansman Ekonomi Gazetesi</t>
+          <t>Ticaret Bakanlığından Kurban Bayramı Öncesi Dijital Dolandırıcılık Uyarısı basvur.co</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3971,22 +4166,18 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>ticaret</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan 'Yeşil ve Geleceğin Şehirleri Projesi' için finansman Ekonomi Gazetesi</t>
+          <t>Ticaret Bakanlığından Kurban Bayramı Öncesi Dijital Dolandırıcılık Uyarısı basvur.co</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan 'Yeşil ve Geleceğin Şehirleri Projesi' için finansman Dünya Bankası'ndan 'Yeşil ve Geleceğin Şehirleri Projesi' için finansman Ekonomi Gazetesi Dünya Bankası'ndan 'Yeşil ve Geleceğin Şehirleri Projesi' için finansman Ekonomi Gazetesi</t>
+          <t>Ticaret Bakanlığından Kurban Bayramı Öncesi Dijital Dolandırıcılık Uyarısı Ticaret Bakanlığından Kurban Bayramı Öncesi Dijital Dolandırıcılık Uyarısı basvur.co Ticaret Bakanlığından Kurban Bayramı Öncesi Dijital Dolandırıcılık Uyarısı basvur.co</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3996,7 +4187,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOTVNxY0ZXbnpXSVVGNHNOTWdLWFNMVDF3eUVwRlJrTDZuUzhSeFRVNUtTbHowNUd3dkdnT09pRENhdk1qQmQ1S2ZiLTFCNDIwYkRiUnIzbmdVeGlTMkZ3cFR6NDU3UGRGX2NEVGNuZk9wb2c0ZlFSVHl4MklQNnh3YVF4aWswMWZobGx1bkZRazg5S1RBZnNEajRXN19TQzl4cjlIMFkydC1keERRdTB3bTVRZ3A1dw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQSHloTlNrSlpXaXIyaEo3OXJJNENhVExsbXlMdU01OWNYWGRqbDNfRmxpcjNXX2RSUFJmYktSMjVxdk1IM1AwckJ5MW9uYjFSLWpvdDk1SDdjSmtTQWZ4U3V0ZDltaW9IdnM4ZklLbkhMbExudjdJcVBnUC1oZHV1MTNkWE9MeWJlakhvcDdFTnhWcFBBcVZFQV94dU1NYjcwam8zSkdTMXJ3R0NRTzRLZDdIdW8?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
@@ -4022,7 +4213,7 @@
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="n">
-        <v>65.14</v>
+        <v>74.84</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>20</v>
@@ -4031,27 +4222,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 04:57:39</t>
+          <t>2026-06-07 14:12:47</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>banka dolandırıcılığı</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3 yıl sonra kullanılmayan banka hesaplarının devre dışı bırakılması önerisi.</t>
+          <t>IATA, birçok havayolu şirketinin iflas riskiyle karşı karşıya olduğu konusunda uyarıda bulundu.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3 yıl sonra kullanılmayan banka hesaplarının devre dışı bırakılması önerisi. Vietnam.vn</t>
+          <t>IATA, birçok havayolu şirketinin iflas riskiyle karşı karşıya olduğu konusunda uyarıda bulundu. Vietnam.vn</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -4061,22 +4252,22 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3 yıl sonra kullanılmayan banka hesaplarının devre dışı bırakılması önerisi. Vietnam.vn</t>
+          <t>IATA, birçok havayolu şirketinin iflas riskiyle karşı karşıya olduğu konusunda uyarıda bulundu. Vietnam.vn</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>3 yıl sonra kullanılmayan banka hesaplarının devre dışı bırakılması önerisi. 3 yıl sonra kullanılmayan banka hesaplarının devre dışı bırakılması önerisi. Vietnam.vn 3 yıl sonra kullanılmayan banka hesaplarının devre dışı bırakılması önerisi.</t>
+          <t>IATA, birçok havayolu şirketinin iflas riskiyle karşı karşıya olduğu konusunda uyarıda bulundu. IATA, birçok havayolu şirketinin iflas riskiyle karşı karşıya olduğu konusunda uyarıda bulundu. Vietnam.vn IATA, birçok havayolu şirketinin iflas riskiyle karşı karşıya olduğu konusunda uyarıda bulundu.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -4086,7 +4277,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOVGdGQVVNMlUxQ1huaFRUZ2JBblNkN2dZWU40NzNJRUdjcDZzckFWemZ4QnlCdVMyNjh1QXdsOHZ5ZzQtMUQ4U0JQWFpwOEJPNUdaWFVhcFRtdGhweWQ1Z1pFNXZJNWd3SkhWMl94Um5zMFNXNWMyZEhsN200dENFcEJtcHdzR3FDZXc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQX2tLMnNSLXJmSm5hY21zYllxQjZOSDRYTGxhN2hTbjNaUDNhZVN0OG5aa1E5S0JLRlBWcEtZYWUyLXdvZ29qY0hDSXZHLWw3bmRGMmJBMm9YajRMR0RwT0J2NlRERmttWWE5MmQzU1EyUDJTUHFFakFUYnhKOXV3VjYyQTcxekkwOVp4UmZhUC1hQQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
@@ -4112,7 +4303,7 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="n">
-        <v>66.62</v>
+        <v>91.06</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>21</v>
@@ -4121,27 +4312,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 08:37:17</t>
+          <t>2026-06-08 09:12:22</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>banka hesaplarına bloke</t>
+          <t>suç örgütü</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>İBB iştiraki İSTTELKOM’a operasyon: Dijital materyallere el konuldu</t>
+          <t>Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>İBB iştiraki İSTTELKOM’a operasyon: Dijital materyallere el konuldu velev.press</t>
+          <t>Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı soL Haber</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -4151,18 +4342,22 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Büyükşehir Belediyesi (İBB) iştiraklerinden İSTTELKOM’a bağlı üç farklı adreste Terörle Mücadele ekipleri arama yaptı. Soruşturma kapsamında 20’den fazla çalışanın banka hesaplarına bloke konulduğu ileri sürüldü. İstanbul Büyükşehir Belediyesi (İBB) iştiraklerinden İSTTELKOM’a bağlı üç farklı adreste Terörle Mücadele ekipleri arama yaptı. Soruşturma kapsamında 20’den fazla çalışanın banka hesaplarına bloke konulduğu ileri sürüldü. İstanbul Büyükşehir Belediyesi (İBB) iştiraklerinden İSTTELKOM’a bağlı üç farklı adreste Terörle Mücadele ekipleri arama yaptı. Soruşturma kapsamında 20’den fazla çalışanın banka hesaplarına bloke konulduğu ileri sürüldü. İstanbul Büyükşehir Belediyesi (İBB) iştirak şirketlerinden İSTTELKOM’a üç farklı adreste Terörle Mücadele (TEM) şube müdürlüğü ekipleri tarafından arama yapıldı. Aramalarda ele geçirilen bir çok dijital materyele el koyuldu.Halk TV muhabiri Gamze Altunay’ın aktardığı bilgilere göre, operasyonun kapsamı ve ekiplerin arama amacıyla mı yoksa başka bir işlem için mi şirkette bulunduğu henüz netlik kazanmadı. Altunay, operasyona dair ulaşılan ilk ayrıntıları paylaştı. 20</t>
+          <t>Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın.Koç Holding Şeref Başkanı Rahmi Koç’un Kürtleri ve kadınları hedef alan ve kamuoyunda büyük tepki çeken "fıkrasının" ardından, holding bünyesindeki Otokoç tesisleri art arda silahlı saldırıların hedefi oldu. Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı | soL haber Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı Koç Holding bünyesindeki kurumlara saldırılarla bağlantılı olduğu değerlendirilen ve kırmızı bültenle aranan organize suç örgütü lideri Rojhat Ertekin'in iadesi için bakanlık harekete geçti, DEM Parti toplumsal barış vurgusu yaparak etkin soruşturma çağrısında bulundu ve "Bu saldırılar kabul edilemez" açıklaması yaptı. Haber Merkezi Yayın Tarihi: 08.06.2026 , 12:12 Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın. Koç Holding Şeref Başkanı Rahmi Koç’un Kürtleri ve kadınları hedef alan ve kamuoyunda büyük tepki çeken "fıkrasının" ardından, holding bünyesindeki Otokoç tesisleri art arda silahlı saldırıların hedefi oldu. Saldırıların ardından olaylarla bağlantılı olduğu iddia edilen suç örgütü lideri Rojhat Ertekin'in Yunanistan'da yakalandığı bildirildi. DEM Parti ise yaşanan şiddet sarmalına karşı bir açıklama yayımlayarak saldırıları kınadı ve şeffaf soruşturma çağrısı yaptı. İstanbul, Antalya ve Diyarbakır Rahmi Koç'un tepki çeken ifadelerinin basına yansımasından kısa bir süre sonra ilk saldırı haberi İstanbul'dan geldi. Dün sabah saatlerinde Maltepe’de bulunan Otokoç Genel Müdürlüğü binasına düzenlenen silahlı saldırıyı, Antalya Kepez’deki Otokoç yetkili servisine yönelik ikinci bir saldırı izledi. Bu iki olayın ardından, üçüncü bir silahlı saldırı bu sabah Diyarbakır'daki Yapı Kredi Bankası'nda gerçekleşti. Kırmızı bültenle aranan 'Ertekin' Atina'da Saldırıların ardından sosyal medyada dolaşıma giren bir videoda adı geçen ve eylemlerle bağlantılı olduğu değerlendirilen "Serdar" kod adlı şahsın, organize suç örgütü lideri Rojhat Ertekin olduğu ortaya çıktı. Sosyal medyada paylaşılan videoda, “Rahmi Koç, Serdar Ertekin ağabeyimin selamı var” ifadeleri kullanıldı. Videoyu paylaşan gazeteci Murat Ağırel, "Serdar Ertekin, diğer adıyla 'Rojhat Ertekin', Ertekinler suç örgütünün lideri olarak biliniyor. Hakkında kırmızı bülten bulunan Ertekin, Yunanistan’da yakalanmıştı" ifadelerini kullandı. Gazeteci İsmail Saymaz 'ın aktardığı detaylara göre Ocak ayında Yunanistan'ın başkenti Atina'da saklandığı villaya Yunan polisi tarafından düzenlenen operasyonla gözaltına alınan Ertekin'in, halihazırda Atina'da tutulduğu belirtti. Saymaz, coğrafi yakınlık ve geçiş kolaylığı nedeniyle son dönemde Türkiye merkezli birçok suç örgütünün Atina'da yoğunlaştığına dikkat çekti. Rojhat Ertekin Doğan Haber Ajansı 'nın (DHA) haberine göre hakkında "suç işlemek amacıyla örgüt kurmak", "kasten öldürme", "uyuşturucu madde ticareti", "nitelikli yağma" ve "silahlı soygun" gibi çok sayıda ağır suçtan tutuklama kararı bulunan Ertekin'in Türkiye'ye iadesi için Adalet Bakanlığı tarafından gerekli diplomatik ve hukuki işlemlerin başlatıldığı kaydedildi. DEM Parti: Bu saldırılar kabul edilemez Halkların Eşitlik ve Demokrasi Partisi (DEM Parti), yaşanan sürece dair yazılı bir açıklama yayımladı. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısında tutumlarının net olduğunu vurgulayan parti yönetimi, saldırıların kabul edilemez olduğunun altını çizdi. DEM Parti'nin açıklamasında şu ifadelere yer verildi: "Otokoç Genel Müdürlüğü'ne yönelik silahlı saldırıları kınıyoruz. Can kaybı yaşanmamış olması en büyük tesellimizdir. Yaşananların tüm yönleriyle aydınlatılması, sorumluların hukuk önünde hesap vermesi ve benzer olayların bir daha yaşanmaması için etkin ve şeffaf bir soruşturmanın ivedilikle yürütülmesi gereklidir. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısındaki tutumumuz nettir, bu tür saldırılar kabul edilemez." soL Haber'i WhatsApp ve Telegram kanallarından takip edin, önemli gelişmeleri kaçırmayın. İLGİLİ HABER Koç'a yönelik üçüncü saldırı: Diyarbakır'da Yapı Kredi Bankası'na ateş edildi Haber Merkezi AKP’den ‘Koç Holding’ açıklaması: ‘Saldırıları lanetliyoruz, ülkemizi karıştırmak isteyenlere izin vermeyeceğiz’ Haber Merkezi soL YZ Beta, soL’un geliştirdiği ve soL arşiviyle çalışan bir yapay zeka robotudur. Kullanımı, soL abonelerine açıktır. Yükleniyor... Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı Koç Holding bünyesindeki kurumlara saldırılarla bağlantılı olduğu değerlendirilen ve kırmızı bültenle aranan organize suç örgütü lideri Rojhat Ertekin'in iadesi için bakanlık harekete geçti, DEM Parti toplumsal barış vurgusu yaparak etkin soruşturma çağrısında bulundu ve "Bu saldırılar kabul edilemez" açıklaması yaptı. Haber Merkezi Yayın Tarihi: 08.06.2026 , 12:12 Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın. Koç Holding Şeref Başkanı Rahmi Koç’un Kürtleri ve kadınları hedef alan ve kamuoyunda büyük tepki çeken "fıkrasının" ardından, holding bünyesindeki Otokoç tesisleri art arda silahlı saldırıların hedefi oldu. Saldırıların ardından olaylarla bağlantılı olduğu iddia edilen suç örgütü lideri Rojhat Ertekin'in Yunanistan'da yakalandığı bildirildi. DEM Parti ise yaşanan şiddet sarmalına karşı bir açıklama yayımlayarak saldırıları kınadı ve şeffaf soruşturma çağrısı yaptı. İstanbul, Antalya ve Diyarbakır Rahmi Koç'un tepki çeken ifadelerinin basına yansımasından kısa bir süre sonra ilk saldırı haberi İstanbul'dan geldi. Dün sabah saatlerinde Maltepe’de bulunan Otokoç Genel Müdürlüğü binasına düzenlenen silahlı saldırıyı, Antalya Kepez’deki Otokoç yetkili servisine yönelik ikinci bir saldırı izledi. Bu iki olayın ardından, üçüncü bir silahlı saldırı bu sabah Diyarbakır'daki Yapı Kredi Bankası'nda gerçekleşti. Kırmızı bültenle aranan 'Ertekin' Atina'da Saldırıların ardından sosyal medyada dolaşıma giren bir videoda adı geçen ve eylemlerle bağlantılı olduğu değerlendirilen "Serdar" kod adlı şahsın, organize suç örgütü lideri Rojhat Ertekin olduğu ortaya çıktı. Sosyal medyada paylaşılan videoda, “Rahmi Koç, Serdar Ertekin ağabeyimin selamı var” ifadeleri kullanıldı. Videoyu paylaşan gazeteci Murat Ağırel, "Serdar Ertekin, diğer adıyla 'Rojhat Ertekin', Ertekinler suç örgütünün lideri olarak biliniyor. Hakkında kırmızı bülten bulunan Ertekin, Yunanistan’da yakalanmıştı" ifadelerini kullandı. Gazeteci İsmail Saymaz 'ın aktardığı detaylara göre Ocak ayında Yunanistan'ın başkenti Atina'da saklandığı villaya Yunan polisi tarafından düzenlenen operasyonla gözaltına alınan Ertekin'in, halihazırda Atina'da tutulduğu belirtti. Saymaz, coğrafi yakınlık ve geçiş kolaylığı nedeniyle son dönemde Türkiye merkezli birçok suç örgütünün Atina'da yoğunlaştığına dikkat çekti. Rojhat Ertekin Doğan Haber Ajansı 'nın (DHA) haberine göre hakkında "suç işlemek amacıyla örgüt kurmak", "kasten öldürme", "uyuşturucu madde ticareti", "nitelikli yağma" ve "silahlı soygun" gibi çok sayıda ağır suçtan tutuklama kararı bulunan Ertekin'in Türkiye'ye iadesi için Adalet Bakanlığı tarafından gerekli diplomatik ve hukuki işlemlerin başlatıldığı kaydedildi. DEM Parti: Bu saldırılar kabul edilemez Halkların Eşitlik ve Demokrasi Partisi (DEM Parti), yaşanan sürece dair yazılı bir açıklama yayımladı. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısında tutumlarının net olduğunu vurgulayan parti yönetimi, saldırıların kabul edilemez olduğunun altını çizdi. DEM Parti'nin açıklamasında şu ifadelere yer verildi: "Otokoç Genel Müdürlüğü'ne yönelik silahlı saldırıları kınıyoruz. Can kaybı yaşanmamış olması en büyük tesellimizdir. Yaşananların tüm yönleriyle aydınlatılması, sorumluların hukuk önünde hesap vermesi ve benzer olayların bir daha yaşanmaması için etkin ve şeffaf bir soruşturmanın ivedilikle yürütülmesi gereklidir. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısındaki tutumumuz nettir, bu tür saldırılar kabul edilemez." soL Haber'i WhatsApp ve Telegram kanallarından takip edin, önemli gelişmeleri kaçırmayın. İLGİLİ HABER Koç'a yönelik üçüncü saldırı: Diyarbakır'da Yapı Kredi Bankası'na ateş edildi Haber Merkezi AKP’den ‘Koç Holding’ açıklaması: ‘Saldırıları lanetliyoruz, ülkemizi karıştırmak isteyenlere izin vermeyeceğiz’ Haber Merkezi soL YZ Beta, soL’un geliştirdiği ve soL arşiviyle çalışan bir yapay zeka robotudur. Kullanımı, soL abonelerine açıktır. Yükleniyor... Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı Koç Holding bünyesindeki kurumlara saldırılarla bağlantılı olduğu değerlendirilen ve kırmızı bültenle aranan organize suç örgütü lideri Rojhat Ertekin'in iadesi için bakanlık harekete geçti, DEM Parti toplumsal barış vurgusu yaparak etkin soruşturma çağrısında bulundu ve "Bu saldırılar kabul edilemez" açıklaması yaptı. Haber Merkezi Yayın Tarihi: 08.06.2026 , 12:12 Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın. Koç Holding Şeref Başkanı Rahmi Koç’un Kürtleri ve kadınları hedef alan ve kamuoyunda büyük tepki çeken "fıkrasının" ardından, holding bünyesindeki Otokoç tesisleri art arda silahlı saldırıların hedefi oldu. Saldırıların ardından olaylarla bağlantılı olduğu iddia edilen suç örgütü lideri Rojhat Ertekin'in Yunanistan'da yakalandığı bildirildi. DEM Parti ise yaşanan şiddet sarmalına karşı bir açıklama yayımlayarak saldırıları kınadı ve şeffaf soruşturma çağrısı yaptı. İstanbul, Antalya ve Diyarbakır Rahmi Koç'un tepki çeken ifadelerinin basına yansımasından kısa bir süre sonra ilk saldırı haberi İstanbul'dan geldi. Dün sabah saatlerinde Maltepe’de bulunan Otokoç Genel Müdürlüğü binasına düzenlenen silahlı saldırıyı, Antalya Kepez’deki Otokoç yetkili servisine yönelik ikinci bir saldırı izledi. Bu iki olayın ardından, üçüncü bir silahlı saldırı bu sabah Diyarbakır'daki Yapı Kredi Bankası'nda gerçekleşti. Kırmızı bültenle aranan 'Ertekin' Atina'da Saldırıların ardından sosyal medyada dolaşıma giren bir videoda adı geçen ve eylemlerle bağlantılı olduğu değerlendirilen "Serdar" kod adlı şahsın, organize suç örgütü lideri Rojhat Ertekin olduğu ortaya çıktı. Sosyal medyada paylaşılan videoda, “Rahmi Koç, Serdar Ertekin ağabeyimin selamı var” ifadeleri kullanıldı. Videoyu paylaşan gazeteci Murat Ağırel, "Serdar Ertekin, diğer adıyla 'Rojhat Ertekin', Ertekinler suç örgütünün lideri olarak biliniyor. Hakkında kırmızı bülten bulunan Ertekin, Yunanistan’da yakalanmıştı" ifadelerini kullandı. Gazeteci İsmail Saymaz 'ın aktardığı detaylara göre Ocak ayında Yunanistan'ın başkenti Atina'da saklandığı villaya Yunan polisi tarafından düzenlenen operasyonla gözaltına alınan Ertekin'in, halihazırda Atina'da tutulduğu belirtti. Saymaz, coğrafi yakınlık ve geçiş kolaylığı nedeniyle son dönemde Türkiye merkezli birçok suç örgütünün Atina'da yoğunlaştığına dikkat çekti. Rojhat Ertekin Doğan Haber Ajansı 'nın (DHA) haberine göre hakkında "suç işlemek amacıyla örgüt kurmak", "kasten öldürme", "uyuşturucu madde ticareti", "nitelikli yağma" ve "silahlı soygun" gibi çok sayıda ağır suçtan tutuklama kararı bulunan Ertekin'in Türkiye'ye iadesi için Adalet Bakanlığı tarafından gerekli diplomatik ve hukuki işlemlerin başlatıldığı kaydedildi. DEM Parti: Bu saldırılar kabul edilemez Halkların Eşitlik ve Demokrasi Partisi (DEM Parti), yaşanan sürece dair yazılı bir açıklama yayımladı. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısında tutumlarının net olduğunu vurgulayan parti yönetimi, saldırıların kabul edilemez olduğunun altını çizdi. DEM Parti'nin açıklamasında şu ifadelere yer verildi: "Otokoç Genel Müdürlüğü'ne yönelik silahlı saldırıları kınıyoruz. Can kaybı yaşanmamış olması en büyük tesellimizdir. Yaşananların tüm yönleriyle aydınlatılması, sorumluların hukuk önünde hesap vermesi ve benzer olayların bir daha yaşanmaması için etkin ve şeffaf bir soruşturmanın ivedilikle yürütülmesi gereklidir. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısındaki tutumumuz nettir, bu tür saldırılar kabul edilemez." soL Haber'i WhatsApp ve Telegram kanallarından takip edin, önemli gelişmeleri kaçırmayın. İLGİLİ HABER Koç'a yönelik üçüncü saldırı: Diyarbakır'da Yapı Kredi Bankası'na ateş edildi Haber Merkezi AKP’den ‘Koç Holding’ açıklaması: ‘Saldırıları lanetliyoruz, ülkemizi karıştırmak isteyenlere izin vermeyeceğiz’ Haber Merkezi soL YZ Beta, soL’un geliştirdiği ve soL arşiviyle çalışan bir yapay zeka robotudur. Kullanımı, soL abonelerine açıktır. Yükleniyor... Haber Merkezi Yayın Tarihi: 08.06.2026 , 12:12 Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın. Koç Holding Şeref Başkanı Rahmi Koç’un Kürtleri ve kadınları hedef alan ve kamuoyunda büyük tepki çeken "fıkrasının" ardından, holding bünyesindeki Otokoç tesisleri art arda silahlı saldırıların hedefi oldu. Saldırıların ardından olaylarla bağlantılı olduğu iddia edilen suç örgütü lideri Rojhat Ertekin'in Yunanistan'da yakalandığı bildirildi. DEM Parti ise yaşanan şiddet sarmalına karşı bir açıklama yayımlayarak saldırıları kınadı ve şeffaf soruşturma çağrısı yaptı. İstanbul, Antalya ve Diyarbakır Rahmi Koç'un tepki çeken ifadelerinin basına yansımasından kısa bir süre sonra ilk saldırı haberi İstanbul'dan geldi. Dün sabah saatlerinde Maltepe’de bulunan Otokoç Genel Müdürlüğü binasına düzenlenen silahlı saldırıyı, Antalya Kepez’deki Otokoç yetkili servisine yönelik ikinci bir saldırı izledi. Bu iki olayın ardından, üçüncü bir silahlı saldırı bu sabah Diyarbakır'daki Yapı Kredi Bankası'nda gerçekleşti. Kırmızı bültenle aranan 'Ertekin' Atina'da Saldırıların ardından sosyal medyada dolaşıma giren bir videoda adı geçen ve eylemlerle bağlantılı olduğu değerlendirilen "Serdar" kod adlı şahsın, organize suç örgütü lideri Rojhat Ertekin olduğu ortaya çıktı. Sosyal medyada paylaşılan videoda, “Rahmi Koç, Serdar Ertekin ağabeyimin selamı var” ifadeleri kullanıldı. Videoyu paylaşan gazeteci Murat Ağırel, "Serdar Ertekin, diğer adıyla 'Rojhat Ertekin', Ertekinler suç örgütünün lideri olarak biliniyor. Hakkında kırmızı bülten bulunan Ertekin, Yunanistan’da yakalanmıştı" ifadelerini kullandı. Gazeteci İsmail Saymaz 'ın aktardığı detaylara göre Ocak ayında Yunanistan'ın başkenti Atina'da saklandığı villaya Yunan polisi tarafından düzenlenen operasyonla gözaltına alınan Ertekin'in, halihazırda Atina'da tutulduğu belirtti. Saymaz, coğrafi yakınlık ve geçiş kolaylığı nedeniyle son dönemde Türkiye merkezli birçok suç örgütünün Atina'da yoğunlaştığına dikkat çekti. Rojhat Ertekin Doğan Haber Ajansı 'nın (DHA) haberine göre hakkında "suç işlemek amacıyla örgüt kurmak", "kasten öldürme", "uyuşturucu madde ticareti", "nitelikli yağma" ve "silahlı soygun" gibi çok sayıda ağır suçtan tutuklama kararı bulunan Ertekin'in Türkiye'ye iadesi için Adalet Bakanlığı tarafından gerekli diplomatik ve hukuki işlemlerin başlatıldığı kaydedildi. DEM Parti: Bu saldırılar kabul edilemez Halkların Eşitlik ve Demokrasi Partisi (DEM Parti), yaşanan sürece dair yazılı bir açıklama yayımladı. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısında tutumlarının net olduğunu vurgulayan parti yönetimi, saldırıların kabul edilemez olduğunun altını çizdi. DEM Parti'nin açıklamasında şu ifadelere yer verildi: "Otokoç Genel Müdürlüğü'ne yönelik silahlı saldırıları kınıyoruz. Can kaybı yaşanmamış olması en büyük tesellimizdir. Yaşananların tüm yönleriyle aydınlatılması, sorumluların hukuk önünde hesap vermesi ve benzer olayların bir daha yaşanmaması için etkin ve şeffaf bir soruşturmanın ivedilikle yürütülmesi gereklidir. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısındaki tutumumuz nettir, bu tür saldırılar kabul edilemez." soL Haber'i WhatsApp ve Telegram kanallarından takip edin, önemli gelişmeleri kaçırmayın. İLGİLİ HABER Koç'a yönelik üçüncü saldırı: Diyarbakır'da Yapı Kredi Bankası'na ateş edildi Haber Merkezi AKP’den ‘Koç Holding’ açıklaması: ‘Saldırıları lanetliyoruz, ülkemizi karıştırmak isteyenlere izin vermeyeceğiz’ Haber Merkezi KİŞİSEL VERİLER HAKKINDA AYDINLATMA METNİ İşbu Kişisel Veriler Hakkında Aydınlatma Metni (“Aydınlatma Metni”) , 6698 sayılı Kişisel Verilerin Korunması Kanunu’nun (“Kanun”) 10. maddesi ile Aydınlatma Yükümlülüğünün Yerine Getirilmesinde Uyulacak Usul ve Esaslar Hakkında Tebliğ (“Tebliğ”) kapsamında veri sorumlusu sıfatıyla Gelenek Basım Yayım ve Ticaret Limited Şirketi (“soL Haber Portalı”) tarafından, soL Haber Portalı ile iletişime geçmiş olmanız kapsamında tarafınızı bilgilendirmek amacıyla hazırlanmıştır. Kişisel Verileriniz, haber.sol.org.tr adresinde mukim soL Haber Portalı tarafından; veri sorumlusu sıfatıyla, Kanun uyarınca, aşağıda sıralanan amaçlar çerçevesinde ve bu amaçlarla bağlantılı, sınırlı ve ölçülü şekilde, tarafımıza ulaştığı şekliyle, otomatik veya otomatik olmayan yöntemler ile kişisel verilerin doğruluğunu ve güncelliğini koruyarak aşağıda açıklanan kapsamda işlenecektir. İşbu Aydınlatma Metni’ni, yürürlükteki mevzuatta yapılabilecek değişiklikler çerçevesinde her zaman; kişisel verilerin işlenmesi ve aktarılması amaçlarında ve toplanma yöntemlerinde gerçekleşecek değişiklikler çerçevesinde ise ilgili kişisel veri sahiplerinin değişikliğe ilişkin rızası doğrultusunda güncelleme hakkımızı saklı tutuyoruz. Yapılan güncellemelerin takibini haber.sol.org.tr linkinden kolaylıkla sağlayabilirsiniz. İşbu Aydınlatma Metni kapsamında işlenen kişisel verileriniz şöyledir: Kimlik: *ad - soyad, İletişim: *cep telefon numarası, *şahsi e-posta adresi. Bu kişisel verilerinizin (1) işlenme amaçlarını, (2) kimlere ve hangi amaçla aktarılabileceğini, (3) toplanmasının yöntemini ve hukuki sebeplerini, (4) haklarınızı ve (5) saklama sürelerini aşağıda bilginize sunarız: (1) Kişisel Verilerinizin İşlenmesi Tarafımız, aşağıdaki amaçlar doğrultusunda, ilgili mevzuattan kaynaklanan kanuni yükümlülüklerimizi yerine getirebilmek için gerekli çalışmaların yapılabilmesini mümkün kılacak, işbu Aydınlatma Metni’nde belirlenen yöntemlerle toplanan kişisel verilerinizi sizlerden talep etmekteyiz. İşbu metin ile belirlenen amaçlar ve kapsam dışında kullanılmamak kaydıyla, veri güvenliğine ilişkin teknik ve idari tedbirleri de almak suretiyle Kanun’un 5. ve 6. maddelerinde belirtilen şartlar dahilinde işlenecektir. Kişisel verileriniz, Kanun’un 5. maddesinin (2) numaralı fıkrasının (b) bendinde belirtilen veri sorumlusunun meşru menfaatleri için veri işlenmesinin zorunlu olması; (c) bendinde belirtilen bir sözleşmenin kurulması veya ifasıyla doğrudan doğruya ilgili olması kaydıyla, sözleşmenin taraflarına ait kişisel verilerin işlenmesinin gerekli olması ve (e) bendinde belirtilen bir hakkın tesisi, kullanılması veya korunması için veri işlemenin zorunlu olması istisnalarına dayanılarak sizden alınmakta ve işlenmektedir. Ayrıca elde edilen kişisel veriler, soL Haber Portalı bünyesinde kullanılan bulut yazılım sistemleri ile yedekleme amacı başta olmak üzere işlenmektedir. *talep, şikayet, bilgi, isteklerin toplanması, *talebiniz doğrultusunda iletişime geçilmesi, *hizmetlerimizin geliştirilmesi, *performans ölçümü, *olumsuzlukların giderilmesi, *verilerin bulut sisteminde yedeklenmesi, *5651 Sayılı İnternet Ortamında Yapılan Yayınların Düzenlenmesi ve Bu Yayınlar Yoluyla İşlenen Suçlarla Mücadele Edilmesi Hakkında Kanun ve sair mevzuatta açıkça öngörüldüğü üzere trafik kayıtlarını tutma yükümlülüğümüzün yerine getirilmesi, *Hizmetlerimizin ihtiyaçlarınız doğrultusunda kişiselleştirilmesi, *Pazarlama analiz çalışmalarının yürütülmesi, *İş süreçlerinin iyileştirilmesine yönelik önlemlerin değerlendirilmesi. . Söz konusu kişisel verileriniz, yasal saklama süresi aşılmamak kaydıyla işleme amacının gerektirdiği süre boyunca saklanacak, bu süre sona erdiğinde usulüne uygun olarak imha edilecektir. (2) Kişisel Verilerinizin Aktarılması Kişisel verilerin üçüncü kişilerle paylaşımı açık rızaları doğrultusunda gerçekleşmekte ve kural olarak açık rızaları olmaksızın üçüncü kişilere aktarılmamaktadır. Tarafımızca, işbu Aydınlatma Metni’nde belirtilen şekilde toplanan ve belirtilen amaçlarla işlenen kişisel verileriniz hizmet sağlayıcı çalışmaların işleyişini sağlayabilmek adına soL Haber Portalı’nın kendi iç işleyişinde ilgili teknik ve idari birimlerle paylaşılabilmektedir. Bu paylaşım, e-posta yoluyla ve diğer her türlü yöntemle kişisel verilerin korunması gözetilerek gerçekleştirilmektedir. Yine açık rızanız doğrultusunda, tarafımızdan, işbu Aydınlatma Metni’nde belirtilen şekilde toplanan ve belirtilen amaçlarla işlenen kişisel verileriniz, Kanun’un 8. ve 9. maddelerinde belirtilen kişisel veri işleme şartları ve amaçları dahilinde aşağıdaki kişilere aktarılabilecektir: *tedarikçilerimize, *iş ortaklarımıza, *ifa yardımcılarına, *yasal yükümlülüklerimizin yerine getirilmesi amacıyla ilgili yetkili kamu kurum ve kuruluşları ile mahkemelere; *hukuki uyuşmazlık durumunda hukuk danışmanlarına ve avukatlara. Üçüncü kişilere veri aktarımı sırasında hak ihlallerini önlemek için gerekli teknik ve idari önlemler alınmaktadır. Aşağıda belirtilen veriler, soL Haber Portalı’nın ilişkide olduğu/olacağı yurt dışındaki kişilere içinde bulunulan ilişkinin gereği olarak aktarılmaktadır. Ayrıca bulut yazılım sisteminde kişisel verilerin işlenmesi ve online destek alınması sebebiyle yapılan işin niteliği gereği yurtdışı aktarımı gerçekleşmektedir. Kimlik: *ad - soyad, İletişim: *cep telefon numarası, *şahsi e-posta adresi. (3) Kişisel Verilerinizin Toplanması Kişisel verileriniz tarafımızdan otomatik olmayan yöntemlerle, yazılı ya da elektronik olarak toplanmaktadır. Tarafımızca çevrimiçi ve çevrimdışı olarak toplanan bilgiler gibi farklı yöntemlerle veya farklı zamanlarda sizden toplanan bilgiler eşleştirilebilir ve Kanun’a ve işbu Aydınlatma Metni’ne istinaden kullanılabilir. Bu kapsamda kişisel verileriniz Kanun’un 5. ve 6. maddelerinde belirtilen kişisel veri işleme şartları ve amaçları çerçevesinde ve işbu Aydınlatma Metni’nde yer alan hukuki sebepler ve amaçlar doğrultusunda işlenebilmesi ve aktarılabilmesi için toplanacaktır. (3) Haklarınız Kanun’un ilgili kişinin haklarını düzenleyen 11. maddesi kapsamındaki taleplerinizi, “Veri Sorumlusuna Başvuru Usul ve Esasları Hakkında Tebliğ” göre; * şahsen veya yazılı başvuru için adresimiz: Caferağa Mah. Nail Bey Sokak No:11/20 Kadıköy İstanbul * elektronik posta adresimiz: habermerkezi@sol.org.tr (Konu kısmına “Kişisel Verilerin Korunması Mevzuatı Kapsamında Bilgi Talebi” yazılacaktır.) adreslerinden soL Haber Portalı’na iletebilirsiniz. Başvurunuzda; adınız, soyadınız, Türkiye Cumhuriyeti vatandaşı iseniz T.C. kimlik numaranız, yabancı iseniz uyruğunuz / pasaport numaranız veya varsa kimlik numaranız, tebligata esas yerleşim yeri veya iş yeri adresiniz, varsa bildirime esas elektronik posta adresiniz / telefon numaranız / faks numaranız, talebiniz ve başvurunuz yazılı ise imzanızın yer alması zorunludur. Bunun yanında veri sahibi olarak talebinize ilişkin bilgi ve belgeleri başvurunuza eklemeniz gerekmektedir. Bilgilerinize. Kapat Okudum ve anladım. Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı İstanbul, Antalya ve Diyarbakır Kırmızı bültenle aranan 'Ertekin' Atina'da DEM Parti: Bu saldırılar kabul edilemez KİŞİSEL VERİLER HAKKINDA AYDINLATMA METNİ Yayın Tarihi: 08.06.2026 , 12:12 Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın. Koç Holding Şeref Başkanı Rahmi Koç’un Kürtleri ve kadınları hedef alan ve kamuoyunda büyük tepki çeken "fıkrasının" ardından, holding bünyesindeki Otokoç tesisleri art arda silahlı saldırıların hedefi oldu. Saldırıların ardından olaylarla bağlantılı olduğu iddia edilen suç örgütü lideri Rojhat Ertekin'in Yunanistan'da yakalandığı bildirildi. DEM Parti ise yaşanan şiddet sarmalına karşı bir açıklama yayımlayarak saldırıları kınadı ve şeffaf soruşturma çağrısı yaptı. Rahmi Koç'un tepki çeken ifadelerinin basına yansımasından kısa bir süre sonra ilk saldırı haberi İstanbul'dan geldi. Dün sabah saatlerinde Maltepe’de bulunan Otokoç Genel Müdürlüğü binasına düzenlenen silahlı saldırıyı, Antalya Kepez’deki Otokoç yetkili servisine yönelik ikinci bir saldırı izledi. Bu iki olayın ardından, üçüncü bir silahlı saldırı bu sabah Diyarbakır'daki Yapı Kredi Bankası'nda gerçekleşti. Saldırıların ardından sosyal medyada dolaşıma giren bir videoda adı geçen ve eylemlerle bağlantılı olduğu değerlendirilen "Serdar" kod adlı şahsın, organize suç örgütü lideri Rojhat Ertekin olduğu ortaya çıktı. Sosyal medyada paylaşılan videoda, “Rahmi Koç, Serdar Ertekin ağabeyimin selamı var” ifadeleri kullanıldı. Videoyu paylaşan gazeteci Murat Ağırel, "Serdar Ertekin, diğer adıyla 'Rojhat Ertekin', Ertekinler suç örgütünün lideri olarak biliniyor. Hakkında kırmızı bülten bulunan Ertekin, Yunanistan’da yakalanmıştı" ifadelerini kullandı. Gazeteci İsmail Saymaz 'ın aktardığı detaylara göre Ocak ayında Yunanistan'ın başkenti Atina'da saklandığı villaya Yunan polisi tarafından düzenlenen operasyonla gözaltına alınan Ertekin'in, halihazırda Atina'da tutulduğu belirtti. Saymaz, coğrafi yakınlık ve geçiş kolaylığı nedeniyle son dönemde Türkiye merkezli birçok suç örgütünün Atina'da yoğunlaştığına dikkat çekti. Doğan Haber Ajansı 'nın (DHA) haberine göre hakkında "suç işlemek amacıyla örgüt kurmak", "kasten öldürme", "uyuşturucu madde ticareti", "nitelikli yağma" ve "silahlı soygun" gibi çok sayıda ağır suçtan tutuklama kararı bulunan Ertekin'in Türkiye'ye iadesi için Adalet Bakanlığı tarafından gerekli diplomatik ve hukuki işlemlerin başlatıldığı kaydedildi. Halkların Eşitlik ve Demokrasi Partisi (DEM Parti), yaşanan sürece dair yazılı bir açıklama yayımladı. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısında tutumlarının net olduğunu vurgulayan parti yönetimi, saldırıların kabul edilemez olduğunun altını çizdi. DEM Parti'nin açıklamasında şu ifadelere yer verildi: "Otokoç Genel Müdürlüğü'ne yönelik silahlı saldırıları kınıyoruz. Can kaybı yaşanmamış olması en büyük tesellimizdir. Yaşananların tüm yönleriyle aydınlatılması, sorumluların hukuk önünde hesap vermesi ve benzer olayların bir daha yaşanmaması için etkin ve şeffaf bir soruşturmanın ivedilikle yürütülmesi gereklidir. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısındaki tutumumuz nettir, bu tür saldırılar kabul edilemez." soL Haber'i WhatsApp ve Telegram kanallarından takip edin, önemli gelişmeleri kaçırmayın. soL YZ Beta, soL’un geliştirdiği ve soL arşiviyle çalışan bir yapay zeka robotudur. Kullanımı, soL abonelerine açıktır. İşbu Kişisel Veriler Hakkında Aydınlatma Metni (“Aydınlatma Metni”) , 6698 sayılı Kişisel Verilerin Korunması Kanunu’nun (“Kanun”) 10. maddesi ile Aydınlatma Yükümlülüğünün Yerine Getirilmesinde Uyulacak Usul ve Esaslar Hakkında Tebliğ (“Tebliğ”) kapsamında veri sorumlusu sıfatıyla Gelenek Basım Yayım ve Ticaret Limited Şirketi (“soL Haber Portalı”) tarafından, soL Haber Portalı ile iletişime geçmiş olmanız kapsamında tarafınızı bilgilendirmek amacıyla hazırlanmıştır. Kişisel Verileriniz, haber.sol.org.tr adresinde mukim soL Haber Portalı tarafından; veri sorumlusu sıfatıyla, Kanun uyarınca, aşağıda sıralanan amaçlar çerçevesinde ve bu amaçlarla bağlantılı, sınırlı ve ölçülü şekilde, tarafımıza ulaştığı şekliyle, otomatik veya otomatik olmayan yöntemler ile kişisel verilerin doğruluğunu ve güncelliğini koruyarak aşağıda açıklanan kapsamda işlenecektir. İşbu Aydınlatma Metni’ni, yürürlükteki mevzuatta yapılabilecek değişiklikler çerçevesinde her zaman; kişisel verilerin işlenmesi ve aktarılması amaçlarında ve toplanma yöntemlerinde gerçekleşecek değişiklikler çerçevesinde ise ilgili kişisel veri sahiplerinin değişikliğe ilişkin rızası doğrultusunda güncelleme hakkımızı saklı tutuyoruz. Yapılan güncellemelerin takibini haber.sol.org.tr linkinden kolaylıkla sağlayabilirsiniz. İşbu Aydınlatma Metni kapsamında işlenen kişisel verileriniz şöyledir: Kimlik: *ad - soyad, İletişim: *cep telefon numarası, *şahsi e-posta adresi. Bu kişisel verilerinizin (1) işlenme amaçlarını, (2) kimlere ve hangi amaçla aktarılabileceğini, (3) toplanmasının yöntemini ve hukuki sebeplerini, (4) haklarınızı ve (5) saklama sürelerini aşağıda bilginize sunarız: (1) Kişisel Verilerinizin İşlenmesi Tarafımız, aşağıdaki amaçlar doğrultusunda, ilgili mevzuattan kaynaklanan kanuni yükümlülüklerimizi yerine getirebilmek için gerekli çalışmaların yapılabilmesini mümkün kılacak, işbu Aydınlatma Metni’nde belirlenen yöntemlerle toplanan kişisel verilerinizi sizlerden talep etmekteyiz. İşbu metin ile belirlenen amaçlar ve kapsam dışında kullanılmamak kaydıyla, veri güvenliğine ilişkin teknik ve idari tedbirleri de almak suretiyle Kanun’un 5. ve 6. maddelerinde belirtilen şartlar dahilinde işlenecektir. Kişisel verileriniz, Kanun’un 5. maddesinin (2) numaralı fıkrasının (b) bendinde belirtilen veri sorumlusunun meşru menfaatleri için veri işlenmesinin zorunlu olması; (c) bendinde belirtilen bir sözleşmenin kurulması veya ifasıyla doğrudan doğruya ilgili olması kaydıyla, sözleşmenin taraflarına ait kişisel verilerin işlenmesinin gerekli olması ve (e) bendinde belirtilen bir hakkın tesisi, kullanılması veya korunması için veri işlemenin zorunlu olması istisnalarına dayanılarak sizden alınmakta ve işlenmektedir. Ayrıca elde edilen kişisel veriler, soL Haber Portalı bünyesinde kullanılan bulut yazılım sistemleri ile yedekleme amacı başta olmak üzere işlenmektedir. *talep, şikayet, bilgi, isteklerin toplanması, *talebiniz doğrultusunda iletişime geçilmesi, *hizmetlerimizin geliştirilmesi, *performans ölçümü, *olumsuzlukların giderilmesi, *verilerin bulut sisteminde yedeklenmesi, *5651 Sayılı İnternet Ortamında Yapılan Yayınların Düzenlenmesi ve Bu Yayınlar Yoluyla İşlenen Suçlarla Mücadele Edilmesi Hakkında Kanun ve sair mevzuatta açıkça öngörüldüğü üzere trafik kayıtlarını tutma yükümlülüğümüzün yerine getirilmesi, *Hizmetlerimizin ihtiyaçlarınız doğrultusunda kişiselleştirilmesi, *Pazarlama analiz çalışmalarının yürütülmesi, *İş süreçlerinin iyileştirilmesine yönelik önlemlerin değerlendirilmesi. . Söz konusu kişisel verileriniz, yasal saklama süresi aşılmamak kaydıyla işleme amacının gerektirdiği süre boyunca saklanacak, bu süre sona erdiğinde usulüne uygun olarak imha edilecektir. (2) Kişisel Verilerinizin Aktarılması Kişisel verilerin üçüncü kişilerle paylaşımı açık rızaları doğrultusunda gerçekleşmekte ve kural olarak açık rızaları olmaksızın üçüncü kişilere aktarılmamaktadır. Tarafımızca, işbu Aydınlatma Metni’nde belirtilen şekilde toplanan ve belirtilen amaçlarla işlenen kişisel verileriniz hizmet sağlayıcı çalışmaların işleyişini sağlayabilmek adına soL Haber Portalı’nın kendi iç işleyişinde ilgili teknik ve idari birimlerle paylaşılabilmektedir. Bu paylaşım, e-posta yoluyla ve diğer her türlü yöntemle kişisel verilerin korunması gözetilerek gerçekleştirilmektedir. Yine açık rızanız doğrultusunda, tarafımızdan, işbu Aydınlatma Metni’nde belirtilen şekilde toplanan ve belirtilen amaçlarla işlenen kişisel verileriniz, Kanun’un 8. ve 9. maddelerinde belirtilen kişisel veri işleme şartları ve amaçları dahilinde aşağıdaki kişilere aktarılabilecektir: *tedarikçilerimize, *iş ortaklarımıza, *ifa yardımcılarına, *yasal yükümlülüklerimizin yerine getirilmesi amacıyla ilgili yetkili kamu kurum ve kuruluşları ile mahkemelere; *hukuki uyuşmazlık durumunda hukuk danışmanlarına ve avukatlara. Üçüncü kişilere veri aktarımı sırasında hak ihlallerini önlemek için gerekli teknik ve idari önlemler alınmaktadır. Aşağıda belirtilen veriler, soL Haber Portalı’nın ilişkide olduğu/olacağı yurt dışındaki kişilere içinde bulunulan ilişkinin gereği olarak aktarılmaktadır. Ayrıca bulut yazılım sisteminde kişisel verilerin işlenmesi ve online destek alınması sebebiyle yapılan işin niteliği gereği yurtdışı aktarımı gerçekleşmektedir. (3) Kişisel Verilerinizin Toplanması Kişisel verileriniz tarafımızdan otomatik olmayan yöntemlerle, yazılı ya da elektronik olarak toplanmaktadır. Tarafımızca çevrimiçi ve çevrimdışı olarak toplanan bilgiler gibi farklı yöntemlerle veya farklı zamanlarda sizden toplanan bilgiler eşleştirilebilir ve Kanun’a ve işbu Aydınlatma Metni’ne istinaden kullanılabilir. Bu kapsamda kişisel verileriniz Kanun’un 5. ve 6. maddelerinde belirtilen kişisel veri işleme şartları ve amaçları çerçevesinde ve işbu Aydınlatma Metni’nde yer alan hukuki sebepler ve amaçlar doğrultusunda işlenebilmesi ve aktarılabilmesi için topl</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>İBB iştiraki İSTTELKOM’a operasyon: Dijital materyallere el konuldu İBB iştiraki İSTTELKOM’a operasyon: Dijital materyallere el konuldu velev.press İstanbul Büyükşehir Belediyesi (İBB) iştiraklerinden İSTTELKOM’a bağlı üç farklı adreste Terörle Mücadele ekipleri arama yaptı. Soruşturma kapsamında 20’den fazla çalışanın banka hesaplarına bloke konulduğu ileri sürüldü. İstanbul Büyükşehir Belediyesi (İBB) iştirak şirketlerinden İSTTELKOM’a üç farklı adreste Terörle Mücadele (TEM) şube müdürlüğü ekipleri tarafından arama yapıldı. Aramalarda ele geçirilen bir çok dijital materyele el koyuldu.Halk TV muhabiri Gamze Altunay’ın aktardığı bilgilere göre, operasyonun kapsamı ve ekiplerin arama amacıyla mı yoksa başka bir işlem için mi şirkette bulunduğu henüz netlik kazanmadı.</t>
+          <t>Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı soL Haber Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın.Koç Holding Şeref Başkanı Rahmi Koç’un Kürtleri ve kadınları hedef alan ve kamuoyunda büyük tepki çeken "fıkrasının" ardından, holding bünyesindeki Otokoç tesisleri art arda silahlı saldırıların hedefi oldu. Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı | soL haber Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı Koç Holding bünyesindeki kurumlara saldırılarla bağlantılı olduğu değerlendirilen ve kırmızı bültenle aranan organize suç örgütü lideri Rojhat Ertekin'in iadesi için bakanlık harekete geçti, DEM Parti toplumsal barış vurgusu yaparak etkin soruşturma çağrısında bulundu ve "Bu saldırılar kabul edilemez" açıklaması yaptı. Haber Merkezi Yayın Tarihi: 08.06.2026 , 12:12 Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın. Koç Holding Şeref Başkanı Rahmi Koç’un Kürtleri ve kadınları hedef alan ve kamuoyunda büyük tepki çeken "fıkrasının" ardından, holding bünyesindeki Otokoç tesisleri art arda silahlı saldırıların hedefi oldu. Saldırıların ardından olaylarla bağlantılı olduğu iddia edilen suç örgütü lideri Rojhat Ertekin'in Yunanistan'da yakalandığı bildirildi. DEM Parti ise yaşanan şiddet sarmalına karşı bir açıklama yayımlayarak saldırıları kınadı ve şeffaf soruşturma çağrısı yaptı. İstanbul, Antalya ve Diyarbakır Rahmi Koç'un tepki çeken ifadelerinin basına yansımasından kısa bir süre sonra ilk saldırı haberi İstanbul'dan geldi. Dün sabah saatlerinde Maltepe’de bulunan Otokoç Genel Müdürlüğü binasına düzenlenen silahlı saldırıyı, Antalya Kepez’deki Otokoç yetkili servisine yönelik ikinci bir saldırı izledi. Bu iki olayın ardından, üçüncü bir silahlı saldırı bu sabah Diyarbakır'daki Yapı Kredi Bankası'nda gerçekleşti. Kırmızı bültenle aranan 'Ertekin' Atina'da Saldırıların ardından sosyal medyada dolaşıma giren bir videoda adı geçen ve eylemlerle bağlantılı olduğu değerlendirilen "Serdar" kod adlı şahsın, organize suç örgütü lideri Rojhat Ertekin olduğu ortaya çıktı. Gazeteci İsmail Saymaz 'ın aktardığı detaylara göre Ocak ayında Yunanistan'ın başkenti Atina'da saklandığı villaya Yunan polisi tarafından düzenlenen operasyonla gözaltına alınan Ertekin'in, halihazırda Atina'da tutulduğu belirtti. Saymaz, coğrafi yakınlık ve geçiş kolaylığı nedeniyle son dönemde Türkiye merkezli birçok suç örgütünün Atina'da yoğunlaştığına dikkat çekti. Rojhat Ertekin Doğan Haber Ajansı 'nın (DHA) haberine göre hakkında "suç işlemek amacıyla örgüt kurmak", "kasten öldürme", "uyuşturucu madde ticareti", "nitelikli yağma" ve "silahlı soygun" gibi çok sayıda ağır suçtan tutuklama kararı bulunan Ertekin'in Türkiye'ye iadesi için Adalet Bakanlığı tarafından gerekli diplomatik ve hukuki işlemlerin başlatıldığı kaydedildi. DEM Parti: Bu saldırılar kabul edilemez Halkların Eşitlik ve Demokrasi Partisi (DEM Parti), yaşanan sürece dair yazılı bir açıklama yayımladı. Toplumsal barışı tehdit eden her türlü şiddet eylemi karşısında tutumlarının net olduğunu vurgulayan parti yönetimi, saldırıların kabul edilemez olduğunun altını çizdi. DEM Parti'nin açıklamasında şu ifadelere yer verildi: "Otokoç Genel Müdürlüğü'ne yönelik silahlı saldırıları kınıyoruz. Can kaybı yaşanmamış olması en büyük tesellimizdir. Yaşananların tüm yönleriyle aydınlatılması, sorumluların hukuk önünde hesap vermesi ve benzer olayların bir daha yaşanmaması için etkin ve şeffaf bir soruşturmanın ivedilikle yürütülmesi gereklidir. İLGİLİ HABER Koç'a yönelik üçüncü saldırı: Diyarbakır'da Yapı Kredi Bankası'na ateş edildi Haber Merkezi AKP’den ‘Koç Holding’ açıklaması: ‘Saldırıları lanetliyoruz, ülkemizi karıştırmak isteyenlere izin vermeyeceğiz’ Haber Merkezi soL YZ Beta, soL’un geliştirdiği ve soL arşiviyle çalışan bir yapay zeka robotudur. Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı Koç Holding bünyesindeki kurumlara saldırılarla bağlantılı olduğu değerlendirilen ve kırmızı bültenle aranan organize suç örgütü lideri Rojhat Ertekin'in iadesi için bakanlık harekete geçti, DEM Parti toplumsal barış vurgusu yaparak etkin soruşturma çağrısında bulundu ve "Bu saldırılar kabul edilemez" açıklaması yaptı. İLGİLİ HABER Koç'a yönelik üçüncü saldırı: Diyarbakır'da Yapı Kredi Bankası'na ateş edildi Haber Merkezi AKP’den ‘Koç Holding’ açıklaması: ‘Saldırıları lanetliyoruz, ülkemizi karıştırmak isteyenlere izin vermeyeceğiz’ Haber Merkezi KİŞİSEL VERİLER HAKKINDA AYDINLATMA METNİ İşbu Kişisel Veriler Hakkında Aydınlatma Metni (“Aydınlatma Metni”) , 6698 sayılı Kişisel Verilerin Korunması Kanunu’nun (“Kanun”) 10. maddesi ile Aydınlatma Yükümlülüğünün Yerine Getirilmesinde Uyulacak Usul ve Esaslar Hakkında Tebliğ (“Tebliğ”) kapsamında veri sorumlusu sıfatıyla Gelenek Basım Yayım ve Ticaret Limited Şirketi (“soL Haber Portalı”) tarafından, soL Haber Portalı ile iletişime geçmiş olmanız kapsamında tarafınızı bilgilendirmek amacıyla hazırlanmıştır. Kişisel Verileriniz, haber.sol.org.tr adresinde mukim soL Haber Portalı tarafından; veri sorumlusu sıfatıyla, Kanun uyarınca, aşağıda sıralanan amaçlar çerçevesinde ve bu amaçlarla bağlantılı, sınırlı ve ölçülü şekilde, tarafımıza ulaştığı şekliyle, otomatik veya otomatik olmayan yöntemler ile kişisel verilerin doğruluğunu ve güncelliğini koruyarak aşağıda açıklanan kapsamda işlenecektir. İşbu Aydınlatma Metni’ni, yürürlükteki mevzuatta yapılabilecek değişiklikler çerçevesinde her zaman; kişisel verilerin işlenmesi ve aktarılması amaçlarında ve toplanma yöntemlerinde gerçekleşecek değişiklikler çerçevesinde ise ilgili kişisel veri sahiplerinin değişikliğe ilişkin rızası doğrultusunda güncelleme hakkımızı saklı tutuyoruz. İşbu Aydınlatma Metni kapsamında işlenen kişisel verileriniz şöyledir: Kimlik: *ad - soyad, İletişim: *cep telefon numarası, *şahsi e-posta adresi. Bu kişisel verilerinizin (1) işlenme amaçlarını, (2) kimlere ve hangi amaçla aktarılabileceğini, (3) toplanmasının yöntemini ve hukuki sebeplerini, (4) haklarınızı ve (5) saklama sürelerini aşağıda bilginize sunarız: (1) Kişisel Verilerinizin İşlenmesi Tarafımız, aşağıdaki amaçlar doğrultusunda, ilgili mevzuattan kaynaklanan kanuni yükümlülüklerimizi yerine getirebilmek için gerekli çalışmaların yapılabilmesini mümkün kılacak, işbu Aydınlatma Metni’nde belirlenen yöntemlerle toplanan kişisel verilerinizi sizlerden talep etmekteyiz. maddesinin (2) numaralı fıkrasının (b) bendinde belirtilen veri sorumlusunun meşru menfaatleri için veri işlenmesinin zorunlu olması; (c) bendinde belirtilen bir sözleşmenin kurulması veya ifasıyla doğrudan doğruya ilgili olması kaydıyla, sözleşmenin taraflarına ait kişisel verilerin işlenmesinin gerekli olması ve (e) bendinde belirtilen bir hakkın tesisi, kullanılması veya korunması için veri işlemenin zorunlu olması istisnalarına dayanılarak sizden alınmakta ve işlenmektedir. *talep, şikayet, bilgi, isteklerin toplanması, *talebiniz doğrultusunda iletişime geçilmesi, *hizmetlerimizin geliştirilmesi, *performans ölçümü, *olumsuzlukların giderilmesi, *verilerin bulut sisteminde yedeklenmesi, *5651 Sayılı İnternet Ortamında Yapılan Yayınların Düzenlenmesi ve Bu Yayınlar Yoluyla İşlenen Suçlarla Mücadele Edilmesi Hakkında Kanun ve sair mevzuatta açıkça öngörüldüğü üzere trafik kayıtlarını tutma yükümlülüğümüzün yerine getirilmesi, *Hizmetlerimizin ihtiyaçlarınız doğrultusunda kişiselleştirilmesi, *Pazarlama analiz çalışmalarının yürütülmesi, *İş süreçlerinin iyileştirilmesine yönelik önlemlerin değerlendirilmesi. Söz konusu kişisel verileriniz, yasal saklama süresi aşılmamak kaydıyla işleme amacının gerektirdiği süre boyunca saklanacak, bu süre sona erdiğinde usulüne uygun olarak imha edilecektir. maddelerinde belirtilen kişisel veri işleme şartları ve amaçları dahilinde aşağıdaki kişilere aktarılabilecektir: *tedarikçilerimize, *iş ortaklarımıza, *ifa yardımcılarına, *yasal yükümlülüklerimizin yerine getirilmesi amacıyla ilgili yetkili kamu kurum ve kuruluşları ile mahkemelere; *hukuki uyuşmazlık durumunda hukuk danışmanlarına ve avukatlara. Üçüncü kişilere veri aktarımı sırasında hak ihlallerini önlemek için gerekli teknik ve idari önlemler alınmaktadır. Aşağıda belirtilen veriler, soL Haber Portalı’nın ilişkide olduğu/olacağı yurt dışındaki kişilere içinde bulunulan ilişkinin gereği olarak aktarılmaktadır. Ayrıca bulut yazılım sisteminde kişisel verilerin işlenmesi ve online destek alınması sebebiyle yapılan işin niteliği gereği yurtdışı aktarımı gerçekleşmektedir. Kimlik: *ad - soyad, İletişim: *cep telefon numarası, *şahsi e-posta adresi. (3) Kişisel Verilerinizin Toplanması Kişisel verileriniz tarafımızdan otomatik olmayan yöntemlerle, yazılı ya da elektronik olarak toplanmaktadır. Tarafımızca çevrimiçi ve çevrimdışı olarak toplanan bilgiler gibi farklı yöntemlerle veya farklı zamanlarda sizden toplanan bilgiler eşleştirilebilir ve Kanun’a ve işbu Aydınlatma Metni’ne istinaden kullanılabilir. maddesi kapsamındaki taleplerinizi, “Veri Sorumlusuna Başvuru Usul ve Esasları Hakkında Tebliğ” göre; * şahsen veya yazılı başvuru için adresimiz: Caferağa Mah. Nail Bey Sokak No:11/20 Kadıköy İstanbul * elektronik posta adresimiz: habermerkezi@sol.org.tr (Konu kısmına “Kişisel Verilerin Korunması Mevzuatı Kapsamında Bilgi Talebi” yazılacaktır.) adreslerinden soL Haber Portalı’na iletebilirsiniz. kimlik numaranız, yabancı iseniz uyruğunuz / pasaport numaranız veya varsa kimlik numaranız, tebligata esas yerleşim yeri veya iş yeri adresiniz, varsa bildirime esas elektronik posta adresiniz / telefon numaranız / faks numaranız, talebiniz ve başvurunuz yazılı ise imzanızın yer alması zorunludur. Bunun yanında veri sahibi olarak talebinize ilişkin bilgi ve belgeleri başvurunuza eklemeniz gerekmektedir. Koç Holding'e silahlı saldırılar: Saldırıların adresi 'Ertekinler' adlı suç örgütü, DEM Parti kınadı İstanbul, Antalya ve Diyarbakır Kırmızı bültenle aranan 'Ertekin' Atina'da DEM Parti: Bu saldırılar kabul edilemez KİŞİSEL VERİLER HAKKINDA AYDINLATMA METNİ Yayın Tarihi: 08.06.2026 , 12:12 Algoritmaya müdahale edin: Tek bir işlemle soL Haber’i Google’da ‘tercih edilen kaynak’ olarak seçin, aramalarınızda soL öne çıksın. Rahmi Koç'un tepki çeken ifadelerinin basına yansımasından kısa bir süre sonra ilk saldırı haberi İstanbul'dan geldi. Saldırıların ardından sosyal medyada dolaşıma giren bir videoda adı geçen ve eylemlerle bağlantılı olduğu değerlendirilen "Serdar" kod adlı şahsın, organize suç örgütü lideri Rojhat Ertekin olduğu ortaya çıktı. Doğan Haber Ajansı 'nın (DHA) haberine göre hakkında "suç işlemek amacıyla örgüt kurmak", "kasten öldürme", "uyuşturucu madde ticareti", "nitelikli yağma" ve "silahlı soygun" gibi çok sayıda ağır suçtan tutuklama kararı bulunan Ertekin'in Türkiye'ye iadesi için Adalet Bakanlığı tarafından gerekli diplomatik ve hukuki işlemlerin başlatıldığı kaydedildi. Halkların Eşitlik ve Demokrasi Partisi (DEM Parti), yaşanan sürece dair yazılı bir açıklama yayımladı. soL YZ Beta, soL’un geliştirdiği ve soL arşiviyle çalışan bir yapay zeka robotudur. İşbu Kişisel Veriler Hakkında Aydınlatma Metni (“Aydınlatma Metni”) , 6698 sayılı Kişisel Verilerin Korunması Kanunu’nun (“Kanun”) 10.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -4172,33 +4367,61 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://velev.press/gundem/ibb-istiraki-isttelkoma-operasyon/</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>https://haber.sol.org.tr/haber/koc-holdinge-silahli-saldirilar-saldirilarin-adresi-ertekinler-adli-suc-orgutu-dem-parti</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul | Antalya</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Kepez | Maltepe</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>bir hakkın tesisi</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding | Gelenek Basım Yayım ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding:292:body+summary+title | Gelenek Basım Yayım ve Ticaret Limited Şirketi:104:body | Gelenek Basım Yayım ve Ticaret Limited Şirketi:raw_legal</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr"/>
+          <t>iyi</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding Kepez Diyarbakır Türkiye | Gelenek Basım Yayım ve Ticaret Limited Şirketi Kepez Diyarbakır Türkiye</t>
+        </is>
+      </c>
       <c r="V23" s="2" t="inlineStr"/>
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>Kepez | Diyarbakır</t>
+        </is>
+      </c>
       <c r="AA23" s="2" t="n">
-        <v>72.62</v>
+        <v>234.5</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>22</v>
@@ -4207,27 +4430,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 18:45:07</t>
+          <t>2026-06-08 06:14:59</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>yolsuzluk</t>
+          <t>gözaltı</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>KPK, banka bildirim hizmetlerindeki yolsuzluk iddialarını soruşturuyor</t>
+          <t>Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KPK, banka bildirim hizmetlerindeki yolsuzluk iddialarını soruşturuyor samsunsporluyuz.com</t>
+          <t>Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı PolitiKARS</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -4247,12 +4470,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>KPK, banka bildirim hizmetlerindeki yolsuzluk iddialarını soruşturuyor 6 Haziran 2026 yazar Begüm Gündoğdu Jakarta (ANTARA) — Endonezya Yolsuzlukla Mücadele Komisyonu (KPK), bir devlet bankası ile bir telekomünikasyon şirketinde SMS ve WhatsApp aracılığıyla verilen bildirim hizmetleriyle ilgili yolsuzluk iddialarını soruşturmaya başladı. “Konu, SMS ve WhatsApp ile iletilen bildirimlerle ilgili,” KPK Sözcüsü Budi Prasetyo Cuma günü açıkladı. Prasetyo, şirketlerdeki projelerle ilgili şüpheli genel soruşturma yetkileri çıkarılması ve henüz şüpheli isimler açıklanmadan soruşturmaların başlatılması yönündeki soruları yanıtlarken bu bilgileri verdi. Daha önce KPK, iki devlet şirketindeki bildirim hizmetlerine ilişkin satın alma işlemlerini incelediğini açıklamıştı. KPK’ye göre bu satın alma işlemlerinin devlete verdiği zararın yaklaşık iki trilyon rupiah (107 milyon ABD doları) olduğu şüphesi bulunuyor. Prasetyo, yürütülen soruşturmanın önceki dosyalarla bağlantılı olmayan ayrı bir konu olduğunu belirtti. Kurum ayrıca bankadaki elektronik veri yakalama (EDC) cihazlarının tedarikinde de olası yolsuzluk iddialarını araştırıyor; bu dava ilk olarak 26 Haziran 2025’te duyurulmuştu. 30 Haziran 2025’te KPK, EDC tedarik projesinin 2,1 trilyon rupiah (113 milyon ABD doları) değerinde olduğunu ve 13 kişi hakkında altı aylık yurt dışına çıkış yasağı getirildiğini bildirdi. Yurt dışına çıkışı yasaklananların baş harfleri</t>
+          <t>İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. HABERLER AJANS HABERLERİ Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. 08 Haziran 2026 Pazartesi 08:13 İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. İstanbul İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğüne bağlı ekipler, piyasaya ATM ve para sayma makinesinden geçen sahte dolar süren bir şebekeyi tespit etti. İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma çerçevesinde şebekeye yönelik çalışma başlatan siber polisi, kentte farklı bankaların ATM'sine sahte 50 dolar banknotları yatırarak sisteme sokulduğunu saptadı. Söz konusu sahte 50 dolarlardan oluşan toplam 102 bin 750 doları ATM'ler aracılığıyla sisteme dahil ettikleri, sonrasında farklı banka ATM'lerinden Türk lirası olarak çekerek vurgun yaptıkları anlaşıldı. ATM'lerde bulunan güvenlik kameralarını incelemeye alan emniyet ekipleri, tanınmamak için şapka, gözlü ve maske kullanarak para yatırdığı belirlenen şüphelileri tek tek tespit etti. Ardından bu sabah operasyon başlatıldı. İstanbul başta olmak üzere Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da çok sayıda adrese eş zamanlı düzenlenen operasyonda 9 şüpheli şahıs yakalanarak gözaltına alındı. Gözaltına alınan şebeke üyeleri, sorgulanmak üzere emniyete götürüldü. Zanlılar ile ilgili gerçekleştirilen operasyon kapsamında yürütülen tahkikat işlemleri devam ediyor. HABERLER AJANS HABERLERİ Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. 08 Haziran 2026 Pazartesi 08:13 İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. İstanbul İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğüne bağlı ekipler, piyasaya ATM ve para sayma makinesinden geçen sahte dolar süren bir şebekeyi tespit etti. İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma çerçevesinde şebekeye yönelik çalışma başlatan siber polisi, kentte farklı bankaların ATM'sine sahte 50 dolar banknotları yatırarak sisteme sokulduğunu saptadı. Söz konusu sahte 50 dolarlardan oluşan toplam 102 bin 750 doları ATM'ler aracılığıyla sisteme dahil ettikleri, sonrasında farklı banka ATM'lerinden Türk lirası olarak çekerek vurgun yaptıkları anlaşıldı. ATM'lerde bulunan güvenlik kameralarını incelemeye alan emniyet ekipleri, tanınmamak için şapka, gözlü ve maske kullanarak para yatırdığı belirlenen şüphelileri tek tek tespit etti. Ardından bu sabah operasyon başlatıldı. İstanbul başta olmak üzere Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da çok sayıda adrese eş zamanlı düzenlenen operasyonda 9 şüpheli şahıs yakalanarak gözaltına alındı. Gözaltına alınan şebeke üyeleri, sorgulanmak üzere emniyete götürüldü. Zanlılar ile ilgili gerçekleştirilen operasyon kapsamında yürütülen tahkikat işlemleri devam ediyor. Ajans Haberleri Haberleri Yaşlı Çift Evlerinde Ölü Bulundu Film Gibi Soygun Kameraya Yansıdı: Kepengi Araçla Yıkıp 16 Bin Dolar Çaldılar Bitlis Balı Uluslararası Yarışmada 4’üncü Kez Zirvede Cizre’de Mangal Dumanı Nehir Üzerinde Sis Görünümü Oluşturdu İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. İstanbul İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğüne bağlı ekipler, piyasaya ATM ve para sayma makinesinden geçen sahte dolar süren bir şebekeyi tespit etti. İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma çerçevesinde şebekeye yönelik çalışma başlatan siber polisi, kentte farklı bankaların ATM'sine sahte 50 dolar banknotları yatırarak sisteme sokulduğunu saptadı. Söz konusu sahte 50 dolarlardan oluşan toplam 102 bin 750 doları ATM'ler aracılığıyla sisteme dahil ettikleri, sonrasında farklı banka ATM'lerinden Türk lirası olarak çekerek vurgun yaptıkları anlaşıldı. ATM'lerde bulunan güvenlik kameralarını incelemeye alan emniyet ekipleri, tanınmamak için şapka, gözlü ve maske kullanarak para yatırdığı belirlenen şüphelileri tek tek tespit etti. Ardından bu sabah operasyon başlatıldı. İstanbul başta olmak üzere Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da çok sayıda adrese eş zamanlı düzenlenen operasyonda 9 şüpheli şahıs yakalanarak gözaltına alındı. Gözaltına alınan şebeke üyeleri, sorgulanmak üzere emniyete götürüldü. Zanlılar ile ilgili gerçekleştirilen operasyon kapsamında yürütülen tahkikat işlemleri devam ediyor. Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. Ajans Haberleri Haberleri İstanbul İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğüne bağlı ekipler, piyasaya ATM ve para sayma makinesinden geçen sahte dolar süren bir şebekeyi tespit etti. İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma çerçevesinde şebekeye yönelik çalışma başlatan siber polisi, kentte farklı bankaların ATM'sine sahte 50 dolar banknotları yatırarak sisteme sokulduğunu saptadı. Söz konusu sahte 50 dolarlardan oluşan toplam 102 bin 750 doları ATM'ler aracılığıyla sisteme dahil ettikleri, sonrasında farklı banka ATM'lerinden Türk lirası olarak çekerek vurgun yaptıkları anlaşıldı. ATM'lerde bulunan güvenlik kameralarını incelemeye alan emniyet ekipleri, tanınmamak için şapka, gözlü ve maske kullanarak para yatırdığı belirlenen şüphelileri tek tek tespit etti. Ardından bu sabah operasyon başlatıldı. İstanbul başta olmak üzere Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da çok sayıda adrese eş zamanlı düzenlenen operasyonda 9 şüpheli şahıs yakalanarak gözaltına alındı. Gözaltına alınan şebeke üyeleri, sorgulanmak üzere emniyete götürüldü. Zanlılar ile ilgili gerçekleştirilen operasyon kapsamında yürütülen tahkikat işlemleri devam ediyor.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>KPK, banka bildirim hizmetlerindeki yolsuzluk iddialarını soruşturuyor KPK, banka bildirim hizmetlerindeki yolsuzluk iddialarını soruşturuyor samsunsporluyuz.com KPK, banka bildirim hizmetlerindeki yolsuzluk iddialarını soruşturuyor 6 Haziran 2026 yazar Begüm Gündoğdu Jakarta (ANTARA) — Endonezya Yolsuzlukla Mücadele Komisyonu (KPK), bir devlet bankası ile bir telekomünikasyon şirketinde SMS ve WhatsApp aracılığıyla verilen bildirim hizmetleriyle ilgili yolsuzluk iddialarını soruşturmaya başladı. “Konu, SMS ve WhatsApp ile iletilen bildirimlerle ilgili,” KPK Sözcüsü Budi Prasetyo Cuma günü açıkladı. Prasetyo, şirketlerdeki projelerle ilgili şüpheli genel soruşturma yetkileri çıkarılması ve henüz şüpheli isimler açıklanmadan soruşturmaların başlatılması yönündeki soruları yanıtlarken bu bilgileri verdi. Daha önce KPK, iki devlet şirketindeki bildirim hizmetlerine ilişkin satın alma işlemlerini incelediğini açıklamıştı. KPK’ye göre bu satın alma işlemlerinin devlete verdiği zararın yaklaşık iki trilyon rupiah (107 milyon ABD doları) olduğu şüphesi bulunuyor. Prasetyo, yürütülen soruşturmanın önceki dosyalarla bağlantılı olmayan ayrı bir konu olduğunu belirtti. Kurum ayrıca bankadaki elektronik veri yakalama (EDC) cihazlarının tedarikinde de olası yolsuzluk iddialarını araştırıyor; bu dava ilk olarak 26 Haziran 2025’te duyurulmuştu. 30 Haziran 2025’te KPK, EDC tedarik projesinin 2,1 trilyon rupiah (113 milyon ABD doları) değerinde olduğunu ve 13 kişi hakkında altı aylık yurt dışına çıkış yasağı getirildiğini bildirdi. Yurt dışına çıkışı yasaklananların baş harfleri</t>
+          <t>Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı PolitiKARS İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. HABERLER AJANS HABERLERİ Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. 08 Haziran 2026 Pazartesi 08:13 İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. İstanbul İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğüne bağlı ekipler, piyasaya ATM ve para sayma makinesinden geçen sahte dolar süren bir şebekeyi tespit etti. İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma çerçevesinde şebekeye yönelik çalışma başlatan siber polisi, kentte farklı bankaların ATM'sine sahte 50 dolar banknotları yatırarak sisteme sokulduğunu saptadı. Söz konusu sahte 50 dolarlardan oluşan toplam 102 bin 750 doları ATM'ler aracılığıyla sisteme dahil ettikleri, sonrasında farklı banka ATM'lerinden Türk lirası olarak çekerek vurgun yaptıkları anlaşıldı. ATM'lerde bulunan güvenlik kameralarını incelemeye alan emniyet ekipleri, tanınmamak için şapka, gözlü ve maske kullanarak para yatırdığı belirlenen şüphelileri tek tek tespit etti. Ardından bu sabah operasyon başlatıldı. İstanbul başta olmak üzere Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da çok sayıda adrese eş zamanlı düzenlenen operasyonda 9 şüpheli şahıs yakalanarak gözaltına alındı. Gözaltına alınan şebeke üyeleri, sorgulanmak üzere emniyete götürüldü. Zanlılar ile ilgili gerçekleştirilen operasyon kapsamında yürütülen tahkikat işlemleri devam ediyor. Ajans Haberleri Haberleri Yaşlı Çift Evlerinde Ölü Bulundu Film Gibi Soygun Kameraya Yansıdı: Kepengi Araçla Yıkıp 16 Bin Dolar Çaldılar Bitlis Balı Uluslararası Yarışmada 4’üncü Kez Zirvede Cizre’de Mangal Dumanı Nehir Üzerinde Sis Görünümü Oluşturdu İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. Banka ATM’lerinden Geçen Sahte Dolar Üreten Şebeke Çökertildi: 9 Gözaltı İstanbul merkezli 6 ilde ATM'lere 102 bin 750 sahte dolar yatıran şebekeye yönelik yapılan operasyonda 9 kişi yakalandı. Ajans Haberleri Haberleri İstanbul İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğüne bağlı ekipler, piyasaya ATM ve para sayma makinesinden geçen sahte dolar süren bir şebekeyi tespit etti.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -4262,11 +4485,19 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.samsunsporluyuz.com/haberler/kpk-banka-bildirim-hizmetlerindeki-yolsuzluk-iddialarini-sorusturuyor/39403/</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>https://www.politikars.com/service/amp/banka-atmlerinden-gecen-sahte-dolar-ureten-sebeke-cokertildi-9-gozalti-586639h.htm</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul | Şırnak</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Cizre</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -4274,7 +4505,7 @@
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr"/>
@@ -4288,7 +4519,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="n">
-        <v>77.76000000000001</v>
+        <v>105.75</v>
       </c>
       <c r="AB24" s="2" t="n">
         <v>23</v>
@@ -4297,12 +4528,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 13:40:54</t>
+          <t>2026-06-08 08:48:31</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>banka soruşturma</t>
+          <t>bankaya soruşturma</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4312,12 +4543,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Kişisel verilerin sızdırılması ve banka hesaplarının ele geçirilmesi riskine karşı uyarı.</t>
+          <t>Diyarbakır'da banka şubesine silahlı saldırı! Gece yarısı ateş açıldı, polis ekipleri saldırganı arıyor</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Kişisel verilerin sızdırılması ve banka hesaplarının ele geçirilmesi riskine karşı uyarı. Vietnam.vn</t>
+          <t>Diyarbakır'da banka şubesine silahlı saldırı! Gece yarısı ateş açıldı, polis ekipleri saldırganı arıyor A Haber</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -4337,26 +4568,34 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Kişisel verilerin sızdırılması ve banka hesaplarının ele geçirilmesi riskine karşı uyarı. Vietnam.vn</t>
+          <t>Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendi. Bankaya 3-4 el ateş açan şüpheli olay yerinden kaçarken, polis ekipleri saldırganın yakalanması için çalışma başlattı. Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendi. Bankaya 3-4 el ateş açan şüpheli olay yerinden kaçarken, polis ekipleri saldırganın yakalanması için çalışma başlattı. Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendi. Bankaya 3-4 el ateş açan şüpheli olay yerinden kaçarken, polis ekipleri saldırganın yakalanması için çalışma başlattı. Giriş Tarihi: 08 Haziran 2026 11:48 Son Güncelleme: 08 Haziran 2026 11:55 ahaber.com.tr Haber Merkezi | DHA Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendi. Bankaya 3-4 el ateş açan şüpheli olay yerinden kaçarken, polis ekipleri saldırganın yakalanması için çalışma başlattı. Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendiği öğrenildi. (Foto: DHA) Kimliği henüz belirlenemeyen kişi, kapalı durumdaki banka şubesine tabancayla 3-4 el ateş etti. Saldırının ardından şüpheli olay yerinden kaçtı. Sabah saatlerinde bankaya gelen görevliler durumu polis ekiplerine bildirdi. İhbar üzerine olay yerine sevk edilen ekipler, banka çevresinde inceleme yaptı. (Foto: DHA) ŞÜPHELİ İÇİN ÇALIŞMA BAŞLATILDI Polis ekipleri, silahlı saldırıyı gerçekleştiren şüphelinin yakalanması için çalışma başlattı. Öte yandan banka şubesinin kapalı kepengine asılan duyuruda, "Şubemiz hizmet verememektedir. Diğer şubelerden destek alabilirsiniz" ifadelerinin yer aldığı görüldü. (Foto: DHA) Olayla ilgili soruşturma sürüyor. Koç Holdinge bağlı Otokoça silahlı saldırı KOÇ HOLDİNG'E BAĞLI OTOKOÇ'A SİLAHLI SALDIRI Rahmi Koçun skandal sözlerine soruşturma! RAHMİ KOÇ'UN SKANDAL SÖZLERİNE SORUŞTURMA! Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendiği öğrenildi. (Foto: DHA) Kimliği henüz belirlenemeyen kişi, kapalı durumdaki banka şubesine tabancayla 3-4 el ateş etti. Saldırının ardından şüpheli olay yerinden kaçtı. Sabah saatlerinde bankaya gelen görevliler durumu polis ekiplerine bildirdi. İhbar üzerine olay yerine sevk edilen ekipler, banka çevresinde inceleme yaptı. (Foto: DHA) ŞÜPHELİ İÇİN ÇALIŞMA BAŞLATILDI Polis ekipleri, silahlı saldırıyı gerçekleştiren şüphelinin yakalanması için çalışma başlattı. Öte yandan banka şubesinin kapalı kepengine asılan duyuruda, "Şubemiz hizmet verememektedir. Diğer şubelerden destek alabilirsiniz" ifadelerinin yer aldığı görüldü. (Foto: DHA) Olayla ilgili soruşturma sürüyor. Koç Holdinge bağlı Otokoça silahlı saldırı KOÇ HOLDİNG'E BAĞLI OTOKOÇ'A SİLAHLI SALDIRI Rahmi Koçun skandal sözlerine soruşturma! RAHMİ KOÇ'UN SKANDAL SÖZLERİNE SORUŞTURMA! Mobil uygulamalarımızı indirin Diyarbakır'da banka şubesine silahlı saldırı! Gece yarısı ateş açıldı, polis ekipleri saldırganı arıyor Kimliği henüz belirlenemeyen kişi, kapalı durumdaki banka şubesine tabancayla 3-4 el ateş etti. Saldırının ardından şüpheli olay yerinden kaçtı. Sabah saatlerinde bankaya gelen görevliler durumu polis ekiplerine bildirdi. İhbar üzerine olay yerine sevk edilen ekipler, banka çevresinde inceleme yaptı. ŞÜPHELİ İÇİN ÇALIŞMA BAŞLATILDI Polis ekipleri, silahlı saldırıyı gerçekleştiren şüphelinin yakalanması için çalışma başlattı. Öte yandan banka şubesinin kapalı kepengine asılan duyuruda, "Şubemiz hizmet verememektedir. Diğer şubelerden destek alabilirsiniz" ifadelerinin yer aldığı görüldü. Olayla ilgili soruşturma sürüyor.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Kişisel verilerin sızdırılması ve banka hesaplarının ele geçirilmesi riskine karşı uyarı. Kişisel verilerin sızdırılması ve banka hesaplarının ele geçirilmesi riskine karşı uyarı. Vietnam.vn Kişisel verilerin sızdırılması ve banka hesaplarının ele geçirilmesi riskine karşı uyarı.</t>
+          <t>Diyarbakır'da banka şubesine silahlı saldırı! Gece yarısı ateş açıldı, polis ekipleri saldırganı arıyor Diyarbakır'da banka şubesine silahlı saldırı! Gece yarısı ateş açıldı, polis ekipleri saldırganı arıyor A Haber Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendi. Bankaya 3-4 el ateş açan şüpheli olay yerinden kaçarken, polis ekipleri saldırganın yakalanması için çalışma başlattı. Giriş Tarihi: 08 Haziran 2026 11:48 Son Güncelleme: 08 Haziran 2026 11:55 ahaber.com.tr Haber Merkezi | DHA Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendi. Diyarbakır'ın Sur ilçesinde gece saatlerinde kapalı olan bir banka şubesine silahlı saldırı düzenlendiği öğrenildi. (Foto: DHA) Kimliği henüz belirlenemeyen kişi, kapalı durumdaki banka şubesine tabancayla 3-4 el ateş etti. Saldırının ardından şüpheli olay yerinden kaçtı. Sabah saatlerinde bankaya gelen görevliler durumu polis ekiplerine bildirdi. (Foto: DHA) ŞÜPHELİ İÇİN ÇALIŞMA BAŞLATILDI Polis ekipleri, silahlı saldırıyı gerçekleştiren şüphelinin yakalanması için çalışma başlattı. Öte yandan banka şubesinin kapalı kepengine asılan duyuruda, "Şubemiz hizmet verememektedir. (Foto: DHA) Olayla ilgili soruşturma sürüyor. Koç Holdinge bağlı Otokoça silahlı saldırı KOÇ HOLDİNG'E BAĞLI OTOKOÇ'A SİLAHLI SALDIRI Rahmi Koçun skandal sözlerine soruşturma! RAHMİ KOÇ'UN SKANDAL SÖZLERİNE SORUŞTURMA! Mobil uygulamalarımızı indirin Diyarbakır'da banka şubesine silahlı saldırı! Gece yarısı ateş açıldı, polis ekipleri saldırganı arıyor Kimliği henüz belirlenemeyen kişi, kapalı durumdaki banka şubesine tabancayla 3-4 el ateş etti. ŞÜPHELİ İÇİN ÇALIŞMA BAŞLATILDI Polis ekipleri, silahlı saldırıyı gerçekleştiren şüphelinin yakalanması için çalışma başlattı. Olayla ilgili soruşturma sürüyor.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdjZwZjBpbUI4R1FrNDBpNlpWc1RIZlVlSzBNNjEyejVDQm5ONlFPbXdLekFSLTJBeGxEOFFpMmNzQ3pQQ1JDb0F6dHVSXzYxM3htMno5VDZXdHNMMllRNTlLdG5wU09hVDRReExOWmdwdzNValZUY0kzZFd3c214RmduSzdYR29XbXJSazB5OEdrdjMtMGFLaE5FRjE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>https://www.ahaber.com.tr/gundem/2026/06/08/diyarbakirda-banka-subesine-silahli-saldiri-gece-yarisi-ates-acildi-polis-ekipleri-saldirgani-ariyor</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -4364,7 +4603,7 @@
       <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr"/>
@@ -4378,7 +4617,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="n">
-        <v>76.5</v>
+        <v>128.25</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>24</v>
@@ -4387,12 +4626,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 19:30:00</t>
+          <t>2026-06-08 08:07:00</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>banka soruşturma</t>
+          <t>bankaya soruşturma</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4402,12 +4641,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24 yıllık banka el değiştirdi! Yeni sahibi belli oldu</t>
+          <t>Koç Grubu'na bir saldırı daha: Banka şubesini kurşunladılar!</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24 yıllık banka el değiştirdi! Yeni sahibi belli oldu Aydın Ses Gazetesi</t>
+          <t>Koç Grubu'na bir saldırı daha: Banka şubesini kurşunladılar! Haber Hürriyeti</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4427,12 +4666,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Tasarruf Mevduatı Sigorta Fonu (TMSF) tarafından satışa çıkarılan BankPozitif’in yeni sahibi belli oldu. Türkiye’de 24 yıldır faaliyet gösteren banka, gerçekleştirilen ihale sürecinin ardından Efor Çay ve Ofçay markalarının sahibi Efor Holding tarafından satın alındı. Tasarruf Mevduatı Sigorta Fonu (TMSF) tarafından satışa çıkarılan BankPozitif’in yeni sahibi belli oldu. Türkiye’de 24 yıldır faaliyet gösteren banka, gerçekleştirilen ihale sürecinin ardından Efor Çay ve Ofçay markalarının sahibi Efor Holding tarafından satın alındı. Tasarruf Mevduatı Sigorta Fonu (TMSF) tarafından satışa çıkarılan BankPozitif’in yeni sahibi belli oldu. Türkiye’de 24 yıldır faaliyet gösteren banka, gerçekleştirilen ihale sürecinin ardından Efor Çay ve Ofçay markalarının sahibi Efor Holding tarafından satın alındı. 24 yıllık banka el değiştirdi! Yeni sahibi belli oldu Tasarruf Mevduatı Sigorta Fonu (TMSF) tarafından satışa çıkarılan BankPozitif’in yeni sahibi belli oldu. Türkiye’de 24 yıldır faaliyet gösteren banka, gerçekleştirilen ihale sürecinin ardından Efor Çay ve Ofçay markalarının sahibi Efor Holding tarafından satın alındı. 06.06.2026 - 22:30 Yayınlanma 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + BankPozitif’in de aralarında bulunduğu bazı şirketlerin yönetimi, yasa dışı bahis soruşturması kapsamında 14 Mart 2025 tarihinde TMSF’ye devredilmişti. Soruşturma çerçevesinde iş insanı Erkan Kork gözaltına alınmış, daha sonra tutuklanarak hakkında dava açılmıştı. TMSF Yönetimine Geçmişti İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma kapsamında Erkan Kork’un sahibi olduğu şirketlere kayyım atanırken, dijital ödeme platformu Payfix ile BankPozitif de TMSF yönetimine geçen şirketler arasında yer almıştı. Soruşturmanın tamamlanmasının ardından Erkan Kork hakkında 26 yıla kadar hapis istemiyle dava açılırken, TMSF tarafından bazı şirket ve taşınmazların satış süreci başlatıldı. İhaleyi Efor Holding Kazandı TMSF'nin satışa çıkardığı şirketler arasında en dikkat çekenlerden biri olan BankPozitif, geçtiğimiz aylarda 1 milyar 100 milyon TL muhammen bedelle yeniden ihaleye çıkarıldı. Yükleniyor... Daha önce duyurulan ihale çeşitli nedenlerle ertelenirken, gerçekleştirilen son ihale sonucunda bankayı Rize merkezli Efor Holding satın aldı. Holding, Efor Çay ve Ofçay markalarıyla Türkiye’nin önemli çay üreticileri arasında bulunuyor. Nazilli Karaçay'da sandıkta 4 aday 2 bin 500 seçmen yeni muhtarını belirleyecek İçeriği Görüntüle Rekabet Kurumu Onayı Verdi Satış işleminin tamamlanabilmesi için gerekli incelemeleri gerçekleştiren Rekabet Kurumu da hisse devrine onay verdi. 7145 sayılı Kanun’un Geçici 2. maddesi kapsamında TMSF kayyım yönetiminde bulunan BankPozitif’in hisselerinin Efor Holding’e devredilmesine izin verilmesiyle birlikte bankanın yeni sahibi resmen Efor Holding oldu. 2002 yılından bu yana Türkiye’de faaliyet gösteren BankPozitif’in yeni dönemde nasıl bir büyüme ve yatırım stratejisi izleyeceği ise merak konusu oldu. Kaynak: HABER MERKEZİ Yükleniyor... Editörün Seçtiği Aydın’da firari hırsız yakayı ele verdi Editörün Seçtiği Nazillili vatandaş insanlık ölmemiş dedirtti Editörün Seçtiği 24 yıllık banka el değiştirdi! Yeni sahibi belli oldu Editör Hakkında Cemre UZUN Bunl</t>
+          <t>Rahmi Koç'un kamuoyunda tartışma yaratan sözlerinin ardından Koç Holding'e ait İstanbul ve Antalya'daki binalara yönelik saldırıların ardından bu kez Diyarbakır'daki Yapı Kredi Bankası şubesi silahlı saldırıya uğradı. Olay sonrası polis ekipleri bölgede inceleme başlattı. Rahmi Koç'un kamuoyunda tartışma yaratan sözlerinin ardından Koç Holding'e ait İstanbul ve Antalya'daki binalara yönelik saldırıların ardından bu kez Diyarbakır... Rahmi Koç'un kamuoyunda tartışma yaratan sözlerinin ardından Koç Holding'e ait İstanbul ve Antalya'daki binalara yönelik saldırıların ardından bu kez Diyarbakır'daki Yapı Kredi Bankası şubesi silahlı saldırıya uğradı. Olay sonrası polis ekipleri bölgede inceleme başlattı. Diyarbakır'ın Sur ilçesinde bulunan Koç Holding bünyesindeki Yapı Kredi Bankası şubesine silahlı saldırı düzenlendi. Sabah saatlerinde ortaya çıkan olayın ardından polis ekipleri banka çevresinde geniş güvenlik önlemi aldı. Rahmi Koç'un "Kürt kadın" fıkrası nedeniyle hakkında soruşturma başlatılmasının ardından İstanbul ve Antalya'daki Koç Holding binalarına yönelik saldırılar gündeme gelirken, bu kez Diyarbakır'daki banka şubesi hedef oldu. Bu haberi kaçırmayın Koç'a ikinci saldırı! İstanbul’un ardından Antalya’da da silahlar patladı... Devamını Oku CAMLARDA KURŞUN İZLERİ BULUNDU Amida Haber'in aktardığına göre saldırı, Sur ilçesindeki Gazi Caddesi üzerinde bulunan Yapı Kredi Bankası şubesinde meydana geldi. Sabah işbaşı yapmak üzere bankaya gelen görevliler, şubenin camlarında kurşun izlerini fark ederek durumu polise bildirdi. İhbar üzerine olay yerine sevk edilen Diyarbakır Emniyet Müdürlüğü ekipleri, banka binası ve çevresinde inceleme yaptı. Çalışmalar nedeniyle Gazi Caddesi bir süre araç trafiğine kapatıldı. Bu haberi kaçırmayın Otokoç Genel Müdürlüğü'ne silahlı saldırı! 2 kişi gözaltına alındı Devamını Oku BANKA GEÇİCİ OLARAK KAPATILDI Silahlı saldırının ardından banka şubesi geçici olarak hizmete kapatıldı. Şube girişine müşterileri bilgilendirmek amacıyla duyuru asıldı. Duyuruda, "Şubemiz hizmet vermemektedir, diğer şubelerden destek alabilirsiniz" ifadelerine yer verildi. Polis ekiplerinin olay yerindeki incelemeleri sürerken, saldırıyı gerçekleştiren kişi ya da kişilerin belirlenmesi için çalışma başlatıldı. Bu haberi kaçırmayın Başsavcılık Rahmi Koç hakkında soruşturma başlattı! Koç özür diledi Devamını Oku Koç Grubu'na bir saldırı daha: Banka şubesini kurşunladılar! CAMLARDA KURŞUN İZLERİ BULUNDU BANKA GEÇİCİ OLARAK KAPATILDI Rahmi Koç'un kamuoyunda tartışma yaratan sözlerinin ardından Koç Holding'e ait İstanbul ve Antalya'daki binalara yönelik saldırıların ardından bu kez Diyarbakır'daki Yapı Kredi Bankası şubesi silahlı saldırıya uğradı. Olay sonrası polis ekipleri bölgede inceleme başlattı. Diyarbakır'ın Sur ilçesinde bulunan Koç Holding bünyesindeki Yapı Kredi Bankası şubesine silahlı saldırı düzenlendi. Sabah saatlerinde ortaya çıkan olayın ardından polis ekipleri banka çevresinde geniş güvenlik önlemi aldı. Rahmi Koç'un "Kürt kadın" fıkrası nedeniyle hakkında soruşturma başlatılmasının ardından İstanbul ve Antalya'daki Koç Holding binalarına yönelik saldırılar gündeme gelirken, bu kez Diyarbakır'daki banka şubesi hedef oldu. Amida Haber'in aktardığına göre saldırı, Sur ilçesindeki Gazi Caddesi üzerinde bulunan Yapı Kredi Bankası şubesinde meydana geldi. Sabah işbaşı yapmak üzere bankaya gelen görevliler, şubenin camlarında kurşun izlerini fark ederek durumu polise bildirdi. İhbar üzerine olay yerine sevk edilen Diyarbakır Emniyet Müdürlüğü ekipleri, banka binası ve çevresinde inceleme yaptı. Çalışmalar nedeniyle Gazi Caddesi bir süre araç trafiğine kapatıldı. Silahlı saldırının ardından banka şubesi geçici olarak hizmete kapatıldı. Şube girişine müşterileri bilgilendirmek amacıyla duyuru asıldı. Duyuruda, "Şubemiz hizmet vermemektedir, diğer şubelerden destek alabilirsiniz" ifadelerine yer verildi. Polis ekiplerinin olay yerindeki incelemeleri sürerken, saldırıyı gerçekleştiren kişi ya da kişilerin belirlenmesi için çalışma başlatıldı. 08 Haz 2026 - 11:07 - Gündem Yazdır Yorum yazarak Haber Hürriyeti Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yorumlardan Haber</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>24 yıllık banka el değiştirdi! Yeni sahibi belli oldu 24 yıllık banka el değiştirdi! Yeni sahibi belli oldu Aydın Ses Gazetesi Tasarruf Mevduatı Sigorta Fonu (TMSF) tarafından satışa çıkarılan BankPozitif’in yeni sahibi belli oldu. Türkiye’de 24 yıldır faaliyet gösteren banka, gerçekleştirilen ihale sürecinin ardından Efor Çay ve Ofçay markalarının sahibi Efor Holding tarafından satın alındı. 24 yıllık banka el değiştirdi! Yeni sahibi belli oldu Tasarruf Mevduatı Sigorta Fonu (TMSF) tarafından satışa çıkarılan BankPozitif’in yeni sahibi belli oldu. 06.06.2026 - 22:30 Yayınlanma 1 Dk Okunma Süresi</t>
+          <t>Koç Grubu'na bir saldırı daha: Banka şubesini kurşunladılar! Koç Grubu'na bir saldırı daha: Banka şubesini kurşunladılar! Haber Hürriyeti Rahmi Koç'un kamuoyunda tartışma yaratan sözlerinin ardından Koç Holding'e ait İstanbul ve Antalya'daki binalara yönelik saldırıların ardından bu kez Diyarbakır'daki Yapı Kredi Bankası şubesi silahlı saldırıya uğradı. Olay sonrası polis ekipleri bölgede inceleme başlattı. Rahmi Koç'un kamuoyunda tartışma yaratan sözlerinin ardından Koç Holding'e ait İstanbul ve Antalya'daki binalara yönelik saldırıların ardından bu kez Diyarbakır... Diyarbakır'ın Sur ilçesinde bulunan Koç Holding bünyesindeki Yapı Kredi Bankası şubesine silahlı saldırı düzenlendi. Sabah saatlerinde ortaya çıkan olayın ardından polis ekipleri banka çevresinde geniş güvenlik önlemi aldı. Rahmi Koç'un "Kürt kadın" fıkrası nedeniyle hakkında soruşturma başlatılmasının ardından İstanbul ve Antalya'daki Koç Holding binalarına yönelik saldırılar gündeme gelirken, bu kez Diyarbakır'daki banka şubesi hedef oldu. Bu haberi kaçırmayın Koç'a ikinci saldırı! İstanbul’un ardından Antalya’da da silahlar patladı... Devamını Oku CAMLARDA KURŞUN İZLERİ BULUNDU Amida Haber'in aktardığına göre saldırı, Sur ilçesindeki Gazi Caddesi üzerinde bulunan Yapı Kredi Bankası şubesinde meydana geldi. Sabah işbaşı yapmak üzere bankaya gelen görevliler, şubenin camlarında kurşun izlerini fark ederek durumu polise bildirdi. İhbar üzerine olay yerine sevk edilen Diyarbakır Emniyet Müdürlüğü ekipleri, banka binası ve çevresinde inceleme yaptı. 2 kişi gözaltına alındı Devamını Oku BANKA GEÇİCİ OLARAK KAPATILDI Silahlı saldırının ardından banka şubesi geçici olarak hizmete kapatıldı. Şube girişine müşterileri bilgilendirmek amacıyla duyuru asıldı. Duyuruda, "Şubemiz hizmet vermemektedir, diğer şubelerden destek alabilirsiniz" ifadelerine yer verildi. Polis ekiplerinin olay yerindeki incelemeleri sürerken, saldırıyı gerçekleştiren kişi ya da kişilerin belirlenmesi için çalışma başlatıldı. Bu haberi kaçırmayın Başsavcılık Rahmi Koç hakkında soruşturma başlattı! Koç özür diledi Devamını Oku Koç Grubu'na bir saldırı daha: Banka şubesini kurşunladılar! CAMLARDA KURŞUN İZLERİ BULUNDU BANKA GEÇİCİ OLARAK KAPATILDI Rahmi Koç'un kamuoyunda tartışma yaratan sözlerinin ardından Koç Holding'e ait İstanbul ve Antalya'daki binalara yönelik saldırıların ardından bu kez Diyarbakır'daki Yapı Kredi Bankası şubesi silahlı saldırıya uğradı. Amida Haber'in aktardığına göre saldırı, Sur ilçesindeki Gazi Caddesi üzerinde bulunan Yapı Kredi Bankası şubesinde meydana geldi. Silahlı saldırının ardından banka şubesi geçici olarak hizmete kapatıldı.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -4442,19 +4681,31 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.sesgazetesi.com.tr/24-yillik-banka-el-degistirdi-yeni-sahibi-belli-oldu</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>https://www.haberhurriyeti.com/haber/28131252/koc-grubuna-bir-saldiri-daha-banka-subesini-kursunladilar</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Antalya | Diyarbakır | İstanbul</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Sur ilçesindeki Gazi Caddesi</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr"/>
@@ -4468,7 +4719,7 @@
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="n">
-        <v>57.5</v>
+        <v>102</v>
       </c>
       <c r="AB26" s="2" t="n">
         <v>25</v>
@@ -4477,12 +4728,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:29:00</t>
+          <t>2026-06-08 05:49:49</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>elektronik para ve ödeme kuruluşu</t>
+          <t>banka soruşturma</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4492,12 +4743,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan Türkiye'ye 191,5 Milyon Euro Finansman</t>
+          <t>İstanbul merkezli 6 ilde banka ATM'lerine sahte dolar yatıran şebeke çökertildi: 9 kişi yakalandı</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan Türkiye'ye 191,5 Milyon Euro Finansman Paranın Yönü</t>
+          <t>İstanbul merkezli 6 ilde banka ATM'lerine sahte dolar yatıran şebeke çökertildi: 9 kişi yakalandı Sabah</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4517,25 +4768,29 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan Türkiye'ye 191,5 Milyon Euro Finansman Paranın Yönü</t>
+          <t>İstanbul merkezli 6 ilde, ATM'lerin ve para sayma makinelerine haksız kazançla elde edilen sahte 50 dolarlık banknotları sisteme yükleyen şebeke çökertildi. Şapka ve maskeyle gizlenerek ATM'lere toplam 102 bin 750 sahte dolar yatıran ve bu parayı TL olarak çekerek vurgun yapan 9 şüpheli, siber... İstanbul merkezli 6 ilde, ATM'lerin ve para sayma makinelerine haksız kazançla elde edilen sahte 50 dolarlık banknotları sisteme yükleyen şebeke çökertildi. Şapka ve maskeyle gizlenerek ATM'lere toplam 102 bin 750 sahte dolar yatıran ve bu parayı TL olarak çekerek vurgun yapan 9 şüpheli, siber... Haberin devamı... İstanbul merkezli 6 ilde banka ATM'lerine sahte dolar yatıran şebeke çökertildi: 9 kişi yakalandı Giriş Tarihi: 8.06.2026 08:49 Son Güncelleme: 8.06.2026 08:50 İstanbul merkezli 6 ilde, ATM'lerin ve para sayma makinelerine haksız kazançla elde edilen sahte 50 dolarlık banknotları sisteme yükleyen şebeke çökertildi. Şapka ve maskeyle gizlenerek ATM'lere toplam 102 bin 750 sahte dolar yatıran ve bu parayı TL olarak çekerek vurgun yapan 9 şüpheli, siber polisinin eş zamanlı operasyonuyla yakalandı. İstanbul İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğüne bağlı ekipler, piyasaya ATM ve para sayma makinesinden geçen sahte dolar süren bir şebekeyi tespit etti. 102 BİN 750 DOLARLIK VURGUN YAPTIKLARI TESPİT EDİLDİ İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma çerçevesinde şebekeye yönelik çalışma başlatan siber polisi, kentte farklı bankaların ATM'sine sahte 50 dolar banknotları yatırarak sisteme sokulduğunu saptadı. Söz konusu sahte 50 dolarlardan oluşan toplam 102 bin 750 doları ATM'ler aracılığıyla sisteme dahil ettikleri, sonrasında farklı banka ATM'lerinden Türk lirası olarak çekerek vurgun yaptıkları anlaşıldı. ATM'lerde bulunan güvenlik kameralarını incelemeye alan emniyet ekipleri, tanınmamak için şapka, gözlü ve maske kullanarak para yatırdığı belirlenen şüphelileri tek tek tespit etti. Ardından bu sabah operasyon başlatıldı. İstanbul başta olmak üzere Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da çok sayıda adrese eş zamanlı düzenlenen operasyonda 9 şüpheli şahıs yakalanarak gözaltına alındı. Gözaltına alınan şebeke üyeleri, sorgulanmak üzere emniyete götürüldü. Zanlılar ile ilgili gerçekleştirilen operasyon kapsamında yürütülen tahkikat işlemleri devam ediyor. Sabah.com.tr Uygulamamızı İndirin</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Dünya Bankası'ndan Türkiye'ye 191,5 Milyon Euro Finansman Dünya Bankası'ndan Türkiye'ye 191,5 Milyon Euro Finansman Paranın Yönü Dünya Bankası'ndan Türkiye'ye 191,5 Milyon Euro Finansman Paranın Yönü</t>
+          <t>İstanbul merkezli 6 ilde banka ATM'lerine sahte dolar yatıran şebeke çökertildi: 9 kişi yakalandı İstanbul merkezli 6 ilde banka ATM'lerine sahte dolar yatıran şebeke çökertildi: 9 kişi yakalandı Sabah İstanbul merkezli 6 ilde, ATM'lerin ve para sayma makinelerine haksız kazançla elde edilen sahte 50 dolarlık banknotları sisteme yükleyen şebeke çökertildi. Şapka ve maskeyle gizlenerek ATM'lere toplam 102 bin 750 sahte dolar yatıran ve bu parayı TL olarak çekerek vurgun yapan 9 şüpheli, siber... İstanbul merkezli 6 ilde banka ATM'lerine sahte dolar yatıran şebeke çökertildi: 9 kişi yakalandı Giriş Tarihi: 8.06.2026 08:49 Son Güncelleme: 8.06.2026 08:50 İstanbul merkezli 6 ilde, ATM'lerin ve para sayma makinelerine haksız kazançla elde edilen sahte 50 dolarlık banknotları sisteme yükleyen şebeke çökertildi. Şapka ve maskeyle gizlenerek ATM'lere toplam 102 bin 750 sahte dolar yatıran ve bu parayı TL olarak çekerek vurgun yapan 9 şüpheli, siber polisinin eş zamanlı operasyonuyla yakalandı. İstanbul İl Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğüne bağlı ekipler, piyasaya ATM ve para sayma makinesinden geçen sahte dolar süren bir şebekeyi tespit etti. 102 BİN 750 DOLARLIK VURGUN YAPTIKLARI TESPİT EDİLDİ İstanbul Cumhuriyet Başsavcılığı tarafından yürütülen soruşturma çerçevesinde şebekeye yönelik çalışma başlatan siber polisi, kentte farklı bankaların ATM'sine sahte 50 dolar banknotları yatırarak sisteme sokulduğunu saptadı. Söz konusu sahte 50 dolarlardan oluşan toplam 102 bin 750 doları ATM'ler aracılığıyla sisteme dahil ettikleri, sonrasında farklı banka ATM'lerinden Türk lirası olarak çekerek vurgun yaptıkları anlaşıldı. ATM'lerde bulunan güvenlik kameralarını incelemeye alan emniyet ekipleri, tanınmamak için şapka, gözlü ve maske kullanarak para yatırdığı belirlenen şüphelileri tek tek tespit etti. Ardından bu sabah operasyon başlatıldı. İstanbul başta olmak üzere Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da çok sayıda adrese eş zamanlı düzenlenen operasyonda 9 şüpheli şahıs yakalanarak gözaltına alındı. Gözaltına alınan şebeke üyeleri, sorgulanmak üzere emniyete götürüldü. Zanlılar ile ilgili gerçekleştirilen operasyon kapsamında yürütülen tahkikat işlemleri devam ediyor.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQzFkZEhZbWZXcFkyUXYwMnZ5NTRUMW1vVl9paFRQNVMybHhTTVNKM292RnhtLTRqcXhlbjkwQjhlMmhRWFFENnRkT3BfeXo3clo5QW9RVlVTbTNvdWxiNFF3Rk9rcENIT0hfeXByRE9NU2xzcXo3Uk5LWFo1RnhZeFlGVldleGdlNXhoTy0tOVRlNmFUNlcwOTdOcGJ2dw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>https://www.sabah.com.tr/yasam/istanbul-merkezli-6-ilde-banka-atmlerine-sahte-dolar-yatiran-sebeke-cokertildi-9-kisi-yakalandi-7598756</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
@@ -4544,7 +4799,7 @@
       <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr"/>
@@ -4558,7 +4813,7 @@
       <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="n">
-        <v>44.7</v>
+        <v>105.25</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>26</v>
@@ -4567,12 +4822,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 18:24:37</t>
+          <t>2026-06-08 07:50:00</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>elektronik para ve ödeme kuruluşları</t>
+          <t>bankaya soruşturma</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4582,12 +4837,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti</t>
+          <t>Rahmi Koç'un fıkrası krize döndü! Bu kez banka hedef alındı: Diyarbakır'da Yapı Kredi binasına silahlı saldırı</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti Haberhergün</t>
+          <t>Rahmi Koç'un fıkrası krize döndü! Bu kez banka hedef alındı: Diyarbakır'da Yapı Kredi binasına silahlı saldırı SuperHaber</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4607,12 +4862,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti. Şirket üzerinden yapılan para aklama iddialarıyla ilgili 24 şüpheli gözaltına alındı. Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti. Şirket üzerinden yapılan para aklama iddialarıyla ilgili 24 şüpheli gözaltına alındı. Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti. Şirket üzerinden yapılan para aklama iddialarıyla ilgili 24 şüpheli gözaltına alındı. Beğen,</t>
+          <t>Rahmi Koç'un gündem olan “Kürt kadın” fıkrası sonrası Koç Grubu şirketlerine yönelik gerilim sürüyor. Otokoç'a düzenlenen silahlı saldırının ardından bu kez Diyarbakır'ın Sur ilçesindeki Yapı Kredi Bankası şubesi kurşunlandı, polis olayla ilgili soruşturma başlattı. Rahmi Koç'un gündem olan “Kürt kadın” fıkrası sonrası Koç Grubu şirketlerine yönelik gerilim sürüyor. Otokoç'a düzenlenen silahlı saldırının ardından bu kez Diyarbakır'ın Sur ilçesindeki Yapı Kredi Bankası şubesi kurşunlandı, polis olayla ilgili soruşturma başlattı. Rahmi Koç'un gündem olan “Kürt kadın” fıkrası sonrası Koç Grubu şirketlerine yönelik gerilim sürüyor. Otokoç'a düzenlenen silahlı saldırının ardından bu kez Diyarbakır'ın Sur ilçesindeki Yapı Kredi Bankası şubesi kurşunlandı, polis olayla ilgili soruşturma başlattı.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti Haberhergün Merkez Bankası, Parolapara'nın faaliyet iznini iptal etti. Şirket üzerinden yapılan para aklama iddialarıyla ilgili 24 şüpheli gözaltına alındı.</t>
+          <t>Rahmi Koç'un fıkrası krize döndü! Bu kez banka hedef alındı: Diyarbakır'da Yapı Kredi binasına silahlı saldırı Rahmi Koç'un fıkrası krize döndü! Bu kez banka hedef alındı: Diyarbakır'da Yapı Kredi binasına silahlı saldırı SuperHaber Rahmi Koç'un gündem olan “Kürt kadın” fıkrası sonrası Koç Grubu şirketlerine yönelik gerilim sürüyor. Otokoç'a düzenlenen silahlı saldırının ardından bu kez Diyarbakır'ın Sur ilçesindeki Yapı Kredi Bankası şubesi kurşunlandı, polis olayla ilgili soruşturma başlattı.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -4622,10 +4877,14 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.haberhergun.com/haber/merkez-bankasi-parolapara-nin-faaliyet-iznini-iptal-etti_74544/</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>https://www.superhaber.com/rahmi-kocun-fikrasi-krize-dondu-bu-kez-banka-hedef-alindi-diyarbakirda-yapi-kredi-binasina-silahli-saldiri-haber-577795</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
@@ -4634,7 +4893,7 @@
       <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr"/>
@@ -4648,7 +4907,7 @@
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="n">
-        <v>48.16</v>
+        <v>109.25</v>
       </c>
       <c r="AB28" s="2" t="n">
         <v>27</v>
@@ -4657,12 +4916,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 01:00:00</t>
+          <t>2026-06-08 05:30:00</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>şüpheli işlem</t>
+          <t>ödeme kuruluşu</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4672,12 +4931,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ATM’de kartını unutanlar yandı! önce kartı aramayın, bankayı arayın</t>
+          <t>60 Ay Vadeli Konut Kredisi Şaşırttı: 2 Milyon TL İçin Bankaların Yeni Oranları Netleşti!</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ATM’de kartını unutanlar yandı! önce kartı aramayın, bankayı arayın YeniSöke Gazetesi</t>
+          <t>60 Ay Vadeli Konut Kredisi Şaşırttı: 2 Milyon TL İçin Bankaların Yeni Oranları Netleşti! Afyon Ana Haber</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4697,12 +4956,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Günlük hayatın koşturmacası içinde ATM’lerde unutulan veya kaybedilen banka ve kredi kartları, büyük maddi kayıpların yanı sıra ciddi hukuki sorumlulukları da beraberinde getiriyor. Günlük hayatın koşturmacası içinde ATM’lerde unutulan veya kaybedilen banka ve kredi kartları, büyük maddi kayıpların yanı sıra ciddi hukuki sorumlulukları da b... Günlük hayatın koşturmacası içinde ATM’lerde unutulan veya kaybedilen banka ve kredi kartları, büyük maddi kayıpların yanı sıra ciddi hukuki sorumlulukları da beraberinde getiriyor. Hukukçular, ATM’de unutulan kartların kötü niyetli üçüncü kişiler tarafından harcamalarda kullanılmasının önündeki en büyük engelleyici adımın "zamanında bildirim" olduğunu vurguluyor. Kartın kaybolduğunun fark edildiği an ile bankaya haber verildiği an arasında geçen her dakika, hukuken kart sahibinin aleyhine işleyebiliyor. "Kartı Kapatmamak Yasal Risk Doğurur" Konunun hukuki boyutuna ve mevzuattaki karşılığına dikkat çeken Avukat Kübra Pekel, ATM’de kart unutmanın çok sık karşılaşılan bir durum olduğunu ancak yasal sonuçlarının vatandaşlar tarafından göz ardı edildiğini belirtti. Pekel, banka kartı veya kredi kartının kaybolduğunun ya da çalındığının fark edilmesinin ardından derhal bankaya bilgi verilmesinin hukuki bir yükümlülük olduğunu hatırlatarak şu uyarılarda bulundu: Sorumluluk Kart Sahibine Geçebilir: Kartın kaybolduğu veya ATM’de unutulduğu resmi olarak bankaya bildirilmezse, kartı ele geçiren kötü niyetli kişilerin yaptığı belirli işlemlerden ve harcamalardan yasal olarak kart sahibi sorumlu tutulabilir. Zaman Kaybetmeden Bloke Şart: Bu tür mağduriyetlerin önüne geçebilmek adına, kartın kaybedildiğinin anlaşıldığı ilk saniyede zaman kaybetmeden müşteri hizmetleri ya da mobil şube üzerinden kartın kullanıma kapatılması gerekiyor. Önce Kartı Aramayın, Önce Bankayı Arayın! Mevzuatın kart sahiplerine "hızlı hareket etme ve basiretli davranma" yükümlülüğü getirdiğini kaydeden Avukat Kübra Pekel, kayıp veya çalıntı durumlarında yapılan bildirimin zamanlamasının olası davalarda en kritik delil olduğunu söyledi. Vatandaşların sıklıkla düştüğü bir hataya değinen Pekel, "Kartın kaybolduğunu fark eden kişiler, önce kartın nerede olabileceğini (evde mi, arabada mı, cüzdanın arkasında mı kaldı diye) saatlerce araştırmak yerine, ilk iş olarak bankayla iletişime geçerek kartı bloke ettirmelidir. Kartı ararken geçen her dakikalık gecikme, olası maddi zararları katlayarak artırır" dedi. Güvenliğiniz İçin Altın Değerinde İki Önlem ATM işlemlerinin ardından kartın hazineden geri alındığından kesin olarak emin olunması gerektiğini ifade eden Pekel, dijital çağda dolandırıcılardan korunmanın en pratik iki yolunu şöyle sıraladı: Mobil Bildirimleri Açık Tutun: Akıllı telefonlardaki mobil bankacılık uygulamalarının anlık bildirim (push notification) özellikleri mutlaka açık tutulmalıdır. Bu sayede karttan bilginiz dışında yapılan en ufak bir harcama veya şüpheli işlem anında ekrana düşer ve erken fark etmenizi sağlar. Hızlı Bildirim Hak Kaybını Engeller : Şüpheli bir işlem ya da kart kaybı anında bankaya yapılan jet hızındaki bildirimler, hem paranızı kurtarır hem de ileride açılması muhtemel ceza ve tazminat davalarında yasal olarak hak kaybı yaşamanızın önüne geçer. ATM’de kartını unutanlar yandı! önce kartı aramayın, bankayı arayın "Kartı Kapatmamak Yasal Risk Doğurur" Önce Kartı Aramayın, Önce Bankayı Arayın! Güvenliğiniz İçin Altın Değerinde İki Önlem Günlük hayatın koşturmacası içinde ATM’lerde unutulan veya kaybedilen banka ve kredi kartları, büyük maddi kayıpların yanı sıra ciddi hukuki sorumlulukları da beraberinde getiriyor. Hukukçular, ATM’de unutulan kartların kötü niyetli üçüncü kişiler tarafından harcamalarda kullanılmasının önündeki en büyük engelleyici adımın "zamanında bildirim" olduğunu vurguluyor. Kartın kaybolduğunun fark edildiği an ile bankaya haber verildiği an arasında geçen her dakika, hukuken kart sahibinin aleyhine işleyebiliyor. Konunun hukuki boyutuna ve mevzuattaki karşılığına dikkat çeken Avukat Kübra Pekel, ATM’de kart unutmanın çok sık karşılaşılan bir durum olduğunu ancak yasal sonuçlarının vatandaşlar tarafından göz ardı edildiğini belirtti. Pekel, banka kartı veya kredi kartının kaybolduğunun ya da çalındığının fark edilmesinin ardından derhal bankaya bilgi verilmesinin hukuki bir yükümlülük olduğunu hatırlatarak şu uyarılarda bulundu: Sorumluluk Kart Sahibine Geçebilir: Kartın kaybolduğu veya ATM’de unutulduğu resmi olarak bankaya bildirilmezse, kartı ele geçiren kötü niyetli kişilerin yaptığı belirli işlemlerden ve harcamalardan yasal olarak kart sahibi sorumlu tutulabilir. Zaman Kaybetmeden Bloke Şart: Bu tür mağduriyetlerin önüne geçebilmek adına, kartın kaybedildiğinin anlaşıldığı ilk saniyede zaman kaybetmeden müşteri hizmetleri ya da mobil şube üzerinden kartın kullanıma kapatılması gerekiyor. Mevzuatın kart sahiplerine "hızlı hareket etme ve basiretli davranma" yükümlülüğü getirdiğini kaydeden Avukat Kübra Pekel, kayıp veya çalıntı durumlarında yapılan bildirimin zamanlamasının olası davalarda en kritik delil olduğunu söyledi. Vatandaşların sıklıkla düştüğü bir hataya değinen Pekel, "Kartın kaybolduğunu fark eden kişiler, önce kartın nerede olabileceğini (evde mi, arabada mı, cüzdanın arkasında mı kaldı diye) saatlerce araştırmak yerine, ilk iş olarak bankayla iletişime geçerek kartı bloke ettirmelidir. Kartı ararken geçen her dakikalık gecikme, olası maddi zararları katlayarak artırır" dedi. ATM işlemlerinin ardından kartın hazineden geri alındığından kesin olarak emin olunması gerektiğini ifade eden Pekel, dijital çağda dolandırıcılardan korunmanın en pratik iki yolunu şöyle sıraladı: Mobil Bildirimleri Açık Tutun: Akıllı telefonlardaki mobil bankacılık uygulamalarının anlık bildirim (push notification) özellikleri mutlaka açık tutulmalıdır. Bu sayede karttan bilginiz dışında yapılan en ufak bir harcama veya şüpheli işlem anında ekrana düşer ve erken fark etmenizi sağlar. Hızlı Bildirim Hak Kaybını Engeller : Şüpheli bir işlem ya da kart kaybı anında bankaya yapılan jet hızındaki bildirimler, hem paranızı kurtarır hem de ileride açılması muhtemel ceza ve tazminat davalarında yasal olarak hak kaybı yaşamanızın önüne geçer. 07 Haz 2026 - 04:00 Aydin / Efeler (Merkez) - Asayiş Yazdır Yorum yazarak YeniSöke Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yoru</t>
+          <t>Gayrimenkul piyasasında yaşanan hareketlilik ve kredi faizlerindeki dinamik değişimler ev sahibi olmak isteyen vatandaşların bütçe hesaplarını doğrudan etkilemeye devam ediyor. Gayrimenkul piyasasında yaşanan hareketlilik ve kredi faizlerindeki dinamik değişimler ev sahibi olmak isteyen vatandaşların bütçe hesaplarını doğrudan etkilemeye devam ediyor. Gayrimenkul piyasasında yaşanan hareketlilik ve kredi faizlerindeki dinamik değişimler ev sahibi olmak isteyen vatandaşların bütçe hesaplarını doğrudan etkilemeye devam ediyor. Gayrimenkul piyasasında yaşanan hareketlilik ve kredi faizlerindeki dinamik değişimler ev sahibi olmak isteyen vatandaşların bütçe hesaplarını doğrudan etkilemeye devam ediyor. Bankacılık sektörünün Haziran 2026 dönemine ait güncel verileri incelendiğinde, 2 milyon TL tutarındaki bir konut kredisi için 60 ay vadeli seçeneklerde bankalar arasındaki makasın hiç olmadığı kadar açıldığı görülüyor. Ev hayali kuran tüketiciler için en uygun maliyet sunan finans kuruluşu ile en yüksek oranlı kurum arasındaki farklar, kredi kullanmadan önce çok sıkı bir piyasa araştırması yapılması gerektiğini bir kez daha gözler önüne seriyor. Finansal piyasalarda yaşanan bu dalgalanma konut edinme maliyetlerini doğrudan yukarı taşırken, aylık ödeme miktarlarını da ciddi oranda şekillendiriyor. Yapılan güncel hesaplamalar neticesinde 2 milyon TL hacmindeki bir gayrimenkul kredisi için vatandaşların cebinden çıkacak aylık taksit tutarlarının 66 bin TL seviyesinden başlayarak 77 bin TL sınırına kadar dayandığı net bir şekilde gözlemleniyor. Toplam geri ödeme planlarında ortaya çıkan ve yarım milyon lirayı aşan bu devasa uçurum, doğru bankayı seçmenin ne kadar kritik bir önem taşıdığını ortaya koyuyor. Kamu Ve Katılım Bankaları Finansman Yarışında Öne Çıkıyor Gayrimenkul sektörünü fonlamak ve vatandaşların konut erişimini kolaylaştırmak adına katılım finans kuruluşları ile kamu bankalarının sunduğu paketler mevcut piyasa şartlarında en makul seçenekler olarak dikkat çekiyor. Listenin ilk basamaklarında yer alan Vakıf Katılım, %2,63 kâr payı oranıyla müşterilerine kapılarını açarken aylık 66.636 TL taksit imkanı tanıyor. Bu finansman modeli tercih edildiğinde 5 yıllık sürecin sonunda toplam geri ödeme tutarı 4.025.174 TL seviyesinde dengelenerek diğer kurumlara karşı büyük bir avantaj sağlıyor. Kamu sermayeli bankacılık devlerinden biri olan Halkbank ise katılım bankalarının hemen ardından güçlü bir alternatif olarak rekabete dahil oluyor. Kurum tarafından uygulanan %2,69 faiz oranıyla birlikte vatandaşların ödemesi gereken aylık taksit miktarı 67.535 TL olarak hesaplanıyor. Vade sonu geldiğinde kamunun bu önemli aktörüne yapılacak toplam geri ödeme miktarı ise 4.093.928 TL seviyesine ulaşarak bütçesini korumak isteyen tüketiciler için listenin üst sıralarındaki yerini sağlamlaştırıyor. Alternatif Katılım Finansman Modellerinde Faiz Dengesi Sektörde rekabetin dozu artarken diğer katılım bankaları da benzer oranlarla sisteme dahil olarak ev sahibi olmak isteyen kitleye farklı çözümler üretiyor. Ziraat Katılım bünyesinde sunulan %2,79 kâr payı oranıyla birlikte aylık taksit yükü 69.046 TL seviyesine çıkarken, bu paketin 60 aylık toplam maliyeti 4.160.964 TL olarak kayıtlara geçiyor. Hemen ardında konumlanan Kuveyt Türk ise %2,80 oran belirleyerek aylık 69.197 TL taksit ödemesi ve toplamda 4.189.579 TL geri ödeme tutarıyla müşterilerine hitap ediyor. Bahsi geçen bu katılım finans kuruluşlarının sunduğu paketler, bütçesini belirli sınırlar içinde tutmak ve aşırı maliyet artışından kaçınmak isteyen yatırımcılar için adeta bir can simidi görevi üstleniyor. Aylık ödemelerin 70 bin TL sınırının altında kalması, uzun vadeli borçlanmalarda aile bütçelerinin sürdürülebilirliği açısından büyük bir önem arz ediyor. Finans dünyasındaki uzmanlar, bu oranların piyasa ortalamasına göre hala değerlendirilebilir sınırlar içinde kaldığını ifade ediyor. Özel Bankacılık Sektöründe Yıllık Maliyet Oranları Tırmanışta Özel sermayeli bankaların konut kredisi politikalarında ise çok daha temkinli ve yüksek oranlı bir yaklaşım benimsediği net bir biçimde gözlemleniyor. Sektörün bilinen büyük aktörlerinden Akbank ve Garanti, %3,00 faiz oranıyla müşterilerine finansman sağlarken bu oran aylık taksitlerin 72.265 TL gibi yüksek bir seviyeye fırlamasına neden oluyor. Bu iki bankadan 2 milyon TL tutarında kredi çeken bir tüketicinin 5 yılın sonunda yapacağı toplam ödeme miktarı ise 4.382.555 TL seviyesine ulaşıyor. Piyasadaki en yüksek maliyetli teklif ise faiz oranını %3,31 olarak belirleyen Denizbank cephesinden geliyor. Bu kurumu tercih eden bir vatandaşın her ay düzenli olarak ödemesi gereken taksit tutarı 77.131 TL gibi oldukça yüksek bir rakama tekabül ediyor. Kredinin vade süresi tamamlandığında ise bankaya ödenecek toplam para miktarı 4.658.008 TL seviyesine kadar tırmanarak tüketicinin omzundaki finansal yükü ciddi oranda artırıyor. Doğru Tercih Yapan Tüketicinin Kazancı Dudak Uçuklatıyor Bankaların sunduğu bu güncel veriler derinlemesine analiz edildiğinde, en uygun fiyata sahip finans kuruluşu ile en yüksek maliyet çıkaran kurum arasındaki uçurumun boyutu daha net anlaşılıyor. İki uç nokta arasında tercih yapacak bir vatandaşın toplam geri ödemede karşılaşacağı fark tam olarak 632.834 TL olarak hesaplanıyor. Bu tutar, günümüz ekonomik koşullarında neredeyse yeni satın alınacak bir konutun tüm tapu harçlarını, ekspertiz ve sigorta giderlerini, hatta ev dekorasyon masraflarını tek başına karşılayabilecek bir hacme sahip bulunuyor. Gayrimenkul uzmanları, konut kredisi kullanmayı planlayan kişilerin sadece aşina oldukları bankalarla yetinmeyip tüm piyasayı taramalarının hayati önem taşıdığını vurguluyor. Aylık ödemelerdeki yaklaşık 11 bin TL değerindeki bu fark, orta ve uzun vadede hane halkının yaşam standardını doğrudan etkileyecek bir boyuta ulaşıyor. Finansal okuryazarlığın ve doğru kaynak yönetiminin öne çıktığı bu dönemde, atılacak bilinçli adımlar tüketicilerin yüz yüz binlerce lirasının cebinde kalmasını sağlıyor. Kaynak: Zeki Ersin Yıldırım 60 Ay Vadeli Konut Kredisi Şaşırttı: 2 Milyon TL İçin Bankaların Yeni Oranları Netleşti! Gayrimenkul piyasasında yaşanan hareketlilik ve kredi faizlerindeki dinamik değişimler ev sahibi olmak isteyen vatandaşların bütçe hesaplarını doğrudan etkilemeye devam ediyor. Kamu Ve Katılım Bankaları Finansman Yarışında Öne Çıkıyor Alternatif Katılım Finansman Modellerinde Faiz Dengesi Özel Bankacılık Sektöründe Yıllık Maliyet Oranları Tırmanışta Doğru Tercih Yapan Tüketicinin Kazancı Dudak Uçuklatıyor Gayrimenkul piyasasında yaşanan hareketlilik ve kredi faizlerindeki dinamik değişimler ev sahibi olmak isteyen vatandaşların bütçe hesaplarını doğrudan etkilemeye devam ediyor. Bankacılık sektörünün Haziran 2026 dönemine ait güncel verileri incelendiğinde, 2 milyon TL tutarındaki bir konut kredisi için 60 ay vadeli seçeneklerde bankalar arasındaki makasın hiç olmadığı kadar açıldığı görülüyor. Ev hayali kuran tüketiciler için en uygun maliyet sunan finans kuruluşu ile en yüksek oranlı kurum arasındaki farklar, kredi kullanmadan önce çok sıkı bir piyasa araştırması yapılması gerektiğini bir kez daha gözler önüne seriyor. Finansal piyasalarda yaşanan bu dalgalanma konut edinme maliyetlerini doğrudan yukarı taşırken, aylık ödeme miktarlarını da ciddi oranda şekillendiriyor. Yapılan güncel hesaplamalar neticesinde 2 milyon TL hacmindeki bir gayrimenkul kredisi için vatandaşların cebinden çıkacak aylık taksit tutarlarının 66 bin TL seviyesinden başlayarak 77 bin TL sınırına kadar dayandığı net bir şekilde gözlemleniyor. Toplam geri ödeme planlarında ortaya çıkan ve yarım milyon lirayı aşan bu devasa uçurum, doğru bankayı seçmenin ne kadar kritik bir önem taşıdığını ortaya koyuyor. Gayrimenkul sektörünü fonlamak ve vatandaşların konut erişimini kolaylaştırmak adına katılım finans kuruluşları ile kamu bankalarının sunduğu paketler mevcut piyasa şartlarında en makul seçenekler olarak dikkat çekiyor. Listenin ilk basamaklarında yer alan Vakıf Katılım, %2,63 kâr payı oranıyla müşterilerine kapılarını açarken aylık 66.636 TL taksit imkanı tanıyor. Bu finansman modeli tercih edildiğinde 5 yıllık sürecin sonunda toplam geri ödeme tutarı 4.025.174 TL seviyesinde dengelenerek diğer kurumlara karşı büyük bir avantaj sağlıyor. Kamu sermayeli bankacılık devlerinden biri olan Halkbank ise katılım bankalarının hemen ardından güçlü bir alternatif olarak rekabete dahil oluyor. Kurum tarafından uygulanan %2,69 faiz oranıyla birlikte vatandaşların ödemesi gereken aylık taksit miktarı 67.535 TL olarak hesaplanıyor. Vade sonu geldiğinde kamunun bu önemli aktörüne yapılacak toplam geri ödeme miktarı ise 4.093.928 TL seviyesine ulaşarak bütçesini korumak isteyen tüketiciler için listenin üst sıralarındaki yerini sağlamlaştırıyor. Sektörde rekabetin dozu artarken diğer katılım bankaları da benzer oranlarla sisteme dahil olarak ev sahibi olmak isteyen kitleye farklı çözümler üretiyor. Ziraat Katılım bünyesinde sunulan %2,79 kâr payı oranıyla birlikte aylık taksit yükü 69.046 TL seviyesine çıkarken, bu paketin 60 aylık toplam maliyeti 4.160.964 TL olarak kayıtlara geçiyor. Hemen ardında konumlanan Kuveyt Türk ise %2,80 oran belirleyerek aylık 69.197 TL taksit ödemesi ve toplamda 4.189.579 TL geri ödeme tutarıyla müşterilerine hitap ediyor. Bahsi geçen bu katılım finans kuruluşlarının sunduğu paketler, bütçesini belirli sınırlar içinde tutmak ve aşırı maliyet artışından kaçınmak isteyen yatırımcılar için adeta bir can simidi görevi üstleniyor. Aylık ödemelerin 70 bin TL sınırının altında kalması, uzun vadeli borçlanmalarda aile bütçelerinin sürdürülebilirliği açısından büyük bir önem arz ediyor. Finans dünyasındaki uzmanlar, bu oranların piyasa ortalamasına göre hala değerlendirilebilir sınırlar içinde kaldığını ifade ediyor. Özel sermayeli bankaların konut kredisi politikalarında ise çok daha temkinli ve yüksek oranlı bir yaklaşım benimsediği net bir biçimde gözlemleniyor. Sektörün bilinen büyük aktörlerinden Akbank ve Garanti, %3,00 faiz oranıyla müşterilerine finansman sağlarken bu oran aylık taksitlerin 72.265 TL gibi yüksek bir seviyeye fırlamasına neden oluyor. Bu iki bankadan 2 milyon TL tutarında kredi çeken bir tüketicinin 5 yılın sonunda yapacağı toplam ödeme miktarı ise 4.382.555 TL seviyesine ulaşıyor. Piyasadaki en yüksek maliyetli teklif ise faiz oranını %3,31 olarak belirleyen Denizbank cephesinden geliyor. Bu kurumu tercih eden bir vatandaşın her ay düzenli olarak ödemesi gereken taksit tutarı 77.131 TL gibi oldukça yüksek bir rakama tekabül ediyor. Kredinin vade süresi tamamlandığında ise bankaya ödenecek toplam para miktarı 4.658.008 TL seviyesine kadar tırmanarak tüketicinin omzundaki finansal yükü ciddi oranda artırıyor. Bankaların sunduğu bu güncel veriler derinlemesine analiz edildiğinde, en uygun fiyata sahip finans kuruluşu ile en yüksek maliyet çıkaran kurum arasındaki uçurumun boyutu daha net anlaşılıyor. İki uç nokta arasında tercih yapacak bir vatandaşın toplam geri ödemede karşılaşacağı fark tam olarak 632.834 TL olarak hesaplanıyor. Bu tutar, günümüz ekonomik koşullarında neredeyse yeni satın alınacak bir konutun tüm tapu harçlarını, ekspertiz ve sigorta giderlerini, hatta ev dekorasyon masraflarını tek başına karşılayabilecek bir hacme sahip bulunuyor. Gayrimenkul uzmanları, konut kredisi kullanmayı planlayan kişilerin sadece aşina oldukları bankalarla yetinmeyip tüm piyasayı taramalarının hayati önem taşıdığını vurguluyor. Aylık ödemelerdeki yaklaşık 11 bin TL değerindeki bu fark, orta ve uzun vadede hane halkının yaşam standardını doğrudan etkileyecek bir boyuta ulaşıyor. Finansal okuryazarlığın ve doğru kaynak yönetiminin öne çıktığı bu dönemde, atılacak bilinçli adımlar tüketicilerin yüz yüz binlerce lirasının cebinde kalmasını sağlıyor. Kaynak: Zeki Ersin Yıldırım</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ATM’de kartını unutanlar yandı! önce kartı aramayın, bankayı arayın ATM’de kartını unutanlar yandı! önce kartı aramayın, bankayı arayın YeniSöke Gazetesi Günlük hayatın koşturmacası içinde ATM’lerde unutulan veya kaybedilen banka ve kredi kartları, büyük maddi kayıpların yanı sıra ciddi hukuki sorumlulukları da beraberinde getiriyor. Günlük hayatın koşturmacası içinde ATM’lerde unutulan veya kaybedilen banka ve kredi kartları, büyük maddi kayıpların yanı sıra ciddi hukuki sorumlulukları da b... Hukukçular, ATM’de unutulan kartların kötü niyetli üçüncü kişiler tarafından harcamalarda kullanılmasının önündeki en büyük engelleyici adımın "zamanında bildirim" olduğunu vurguluyor. Kartın kaybolduğunun fark edildiği an ile bankaya haber verildiği an arasında geçen her dakika, hukuken kart sahibinin aleyhine işleyebiliyor. "Kartı Kapatmamak Yasal Risk Doğurur" Konunun hukuki boyutuna ve mevzuattaki karşılığına dikkat çeken Avukat Kübra Pekel, ATM’de kart unutmanın çok sık karşılaşılan bir durum olduğunu ancak yasal sonuçlarının vatandaşlar tarafından göz ardı edildiğini belirtti. Pekel, banka kartı veya kredi kartının kaybolduğunun ya da çalındığının fark edilmesinin ardından derhal bankaya bilgi verilmesinin hukuki bir yükümlülük olduğunu hatırlatarak şu uyarılarda bulundu: Sorumluluk Kart Sahibine Geçebilir: Kartın kaybolduğu veya ATM’de unutulduğu resmi olarak bankaya bildirilmezse, kartı ele geçiren kötü niyetli kişilerin yaptığı belirli işlemlerden ve harcamalardan yasal olarak kart sahibi sorumlu tutulabilir. Zaman Kaybetmeden Bloke Şart: Bu tür mağduriyetlerin önüne geçebilmek adına, kartın kaybedildiğinin anlaşıldığı ilk saniyede zaman kaybetmeden müşteri hizmetleri ya da mobil şube üzerinden kartın kullanıma kapatılması gerekiyor. Önce Kartı Aramayın, Önce Bankayı Arayın! Mevzuatın kart sahiplerine "hızlı hareket etme ve basiretli davranma" yükümlülüğü getirdiğini kaydeden Avukat Kübra Pekel, kayıp veya çalıntı durumlarında yapılan bildirimin zamanlamasının olası davalarda en kritik delil olduğunu söyledi. Vatandaşların sıklıkla düştüğü bir hataya değinen Pekel, "Kartın kaybolduğunu fark eden kişiler, önce kartın nerede olabileceğini (evde mi, arabada mı, cüzdanın arkasında mı kaldı diye) saatlerce araştırmak yerine, ilk iş olarak bankayla iletişime geçerek kartı bloke ettirmelidir. Kartı ararken geçen her dakikalık gecikme, olası maddi zararları katlayarak artırır" dedi. Bu sayede karttan bilginiz dışında yapılan en ufak bir harcama veya şüpheli işlem anında ekrana düşer ve erken fark etmenizi sağlar. ATM’de kartını unutanlar yandı! önce kartı aramayın, bankayı arayın "Kartı Kapatmamak Yasal Risk Doğurur" Önce Kartı Aramayın, Önce Bankayı Arayın! Konunun hukuki boyutuna ve mevzuattaki karşılığına dikkat çeken Avukat Kübra Pekel, ATM’de kart unutmanın çok sık karşılaşılan bir durum olduğunu ancak yasal sonuçlarının vatandaşlar tarafından göz ardı edildiğini belirtti. 07 Haz 2026 - 04:00 Aydin / Efeler (Merkez) - Asayiş Yazdır Yorum yazarak YeniSöke Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
+          <t>60 Ay Vadeli Konut Kredisi Şaşırttı: 2 Milyon TL İçin Bankaların Yeni Oranları Netleşti! 60 Ay Vadeli Konut Kredisi Şaşırttı: 2 Milyon TL İçin Bankaların Yeni Oranları Netleşti! Afyon Ana Haber Gayrimenkul piyasasında yaşanan hareketlilik ve kredi faizlerindeki dinamik değişimler ev sahibi olmak isteyen vatandaşların bütçe hesaplarını doğrudan etkilemeye devam ediyor. Bankacılık sektörünün Haziran 2026 dönemine ait güncel verileri incelendiğinde, 2 milyon TL tutarındaki bir konut kredisi için 60 ay vadeli seçeneklerde bankalar arasındaki makasın hiç olmadığı kadar açıldığı görülüyor. Ev hayali kuran tüketiciler için en uygun maliyet sunan finans kuruluşu ile en yüksek oranlı kurum arasındaki farklar, kredi kullanmadan önce çok sıkı bir piyasa araştırması yapılması gerektiğini bir kez daha gözler önüne seriyor. Finansal piyasalarda yaşanan bu dalgalanma konut edinme maliyetlerini doğrudan yukarı taşırken, aylık ödeme miktarlarını da ciddi oranda şekillendiriyor. Yapılan güncel hesaplamalar neticesinde 2 milyon TL hacmindeki bir gayrimenkul kredisi için vatandaşların cebinden çıkacak aylık taksit tutarlarının 66 bin TL seviyesinden başlayarak 77 bin TL sınırına kadar dayandığı net bir şekilde gözlemleniyor. Toplam geri ödeme planlarında ortaya çıkan ve yarım milyon lirayı aşan bu devasa uçurum, doğru bankayı seçmenin ne kadar kritik bir önem taşıdığını ortaya koyuyor. Kamu Ve Katılım Bankaları Finansman Yarışında Öne Çıkıyor Gayrimenkul sektörünü fonlamak ve vatandaşların konut erişimini kolaylaştırmak adına katılım finans kuruluşları ile kamu bankalarının sunduğu paketler mevcut piyasa şartlarında en makul seçenekler olarak dikkat çekiyor. Listenin ilk basamaklarında yer alan Vakıf Katılım, %2,63 kâr payı oranıyla müşterilerine kapılarını açarken aylık 66.636 TL taksit imkanı tanıyor. Bu finansman modeli tercih edildiğinde 5 yıllık sürecin sonunda toplam geri ödeme tutarı 4.025.174 TL seviyesinde dengelenerek diğer kurumlara karşı büyük bir avantaj sağlıyor. Kurum tarafından uygulanan %2,69 faiz oranıyla birlikte vatandaşların ödemesi gereken aylık taksit miktarı 67.535 TL olarak hesaplanıyor. Vade sonu geldiğinde kamunun bu önemli aktörüne yapılacak toplam geri ödeme miktarı ise 4.093.928 TL seviyesine ulaşarak bütçesini korumak isteyen tüketiciler için listenin üst sıralarındaki yerini sağlamlaştırıyor. Bahsi geçen bu katılım finans kuruluşlarının sunduğu paketler, bütçesini belirli sınırlar içinde tutmak ve aşırı maliyet artışından kaçınmak isteyen yatırımcılar için adeta bir can simidi görevi üstleniyor. Aylık ödemelerin 70 bin TL sınırının altında kalması, uzun vadeli borçlanmalarda aile bütçelerinin sürdürülebilirliği açısından büyük bir önem arz ediyor. Finans dünyasındaki uzmanlar, bu oranların piyasa ortalamasına göre hala değerlendirilebilir sınırlar içinde kaldığını ifade ediyor. Özel Bankacılık Sektöründe Yıllık Maliyet Oranları Tırmanışta Özel sermayeli bankaların konut kredisi politikalarında ise çok daha temkinli ve yüksek oranlı bir yaklaşım benimsediği net bir biçimde gözlemleniyor. Sektörün bilinen büyük aktörlerinden Akbank ve Garanti, %3,00 faiz oranıyla müşterilerine finansman sağlarken bu oran aylık taksitlerin 72.265 TL gibi yüksek bir seviyeye fırlamasına neden oluyor. Bu iki bankadan 2 milyon TL tutarında kredi çeken bir tüketicinin 5 yılın sonunda yapacağı toplam ödeme miktarı ise 4.382.555 TL seviyesine ulaşıyor. Piyasadaki en yüksek maliyetli teklif ise faiz oranını %3,31 olarak belirleyen Denizbank cephesinden geliyor. Bu kurumu tercih eden bir vatandaşın her ay düzenli olarak ödemesi gereken taksit tutarı 77.131 TL gibi oldukça yüksek bir rakama tekabül ediyor. Doğru Tercih Yapan Tüketicinin Kazancı Dudak Uçuklatıyor Bankaların sunduğu bu güncel veriler derinlemesine analiz edildiğinde, en uygun fiyata sahip finans kuruluşu ile en yüksek maliyet çıkaran kurum arasındaki uçurumun boyutu daha net anlaşılıyor. İki uç nokta arasında tercih yapacak bir vatandaşın toplam geri ödemede karşılaşacağı fark tam olarak 632.834 TL olarak hesaplanıyor. Gayrimenkul uzmanları, konut kredisi kullanmayı planlayan kişilerin sadece aşina oldukları bankalarla yetinmeyip tüm piyasayı taramalarının hayati önem taşıdığını vurguluyor. Aylık ödemelerdeki yaklaşık 11 bin TL değerindeki bu fark, orta ve uzun vadede hane halkının yaşam standardını doğrudan etkileyecek bir boyuta ulaşıyor. Finansal okuryazarlığın ve doğru kaynak yönetiminin öne çıktığı bu dönemde, atılacak bilinçli adımlar tüketicilerin yüz yüz binlerce lirasının cebinde kalmasını sağlıyor. Kaynak: Zeki Ersin Yıldırım 60 Ay Vadeli Konut Kredisi Şaşırttı: 2 Milyon TL İçin Bankaların Yeni Oranları Netleşti! Kamu Ve Katılım Bankaları Finansman Yarışında Öne Çıkıyor Alternatif Katılım Finansman Modellerinde Faiz Dengesi Özel Bankacılık Sektöründe Yıllık Maliyet Oranları Tırmanışta Doğru Tercih Yapan Tüketicinin Kazancı Dudak Uçuklatıyor Gayrimenkul piyasasında yaşanan hareketlilik ve kredi faizlerindeki dinamik değişimler ev sahibi olmak isteyen vatandaşların bütçe hesaplarını doğrudan etkilemeye devam ediyor. Gayrimenkul sektörünü fonlamak ve vatandaşların konut erişimini kolaylaştırmak adına katılım finans kuruluşları ile kamu bankalarının sunduğu paketler mevcut piyasa şartlarında en makul seçenekler olarak dikkat çekiyor. Özel sermayeli bankaların konut kredisi politikalarında ise çok daha temkinli ve yüksek oranlı bir yaklaşım benimsediği net bir biçimde gözlemleniyor. Bankaların sunduğu bu güncel veriler derinlemesine analiz edildiğinde, en uygun fiyata sahip finans kuruluşu ile en yüksek maliyet çıkaran kurum arasındaki uçurumun boyutu daha net anlaşılıyor.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -4712,19 +4971,11 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://yenisokegazetesi.com/haber/28122445/atmde-kartini-unutanlar-yandi-once-karti-aramayin-bankayi-arayin</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>Aydın</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Efeler</t>
-        </is>
-      </c>
+          <t>https://www.afyonanahaber.com.tr/60-ay-vadeli-konut-kredisi-sasirtti-2-milyon-tl-icin-bankalarin-yeni-oranlari-netlesti/amp</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr"/>
@@ -4732,7 +4983,7 @@
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr"/>
@@ -4746,7 +4997,7 @@
       <c r="Y29" s="2" t="inlineStr"/>
       <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="n">
-        <v>103.75</v>
+        <v>91</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>28</v>
@@ -4755,12 +5006,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 14:34:00</t>
+          <t>2026-06-08 08:45:54</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>faaliyet izni iptali</t>
+          <t>elektronik para ve ödeme kuruluşları</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4770,12 +5021,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>HAZİRAN 2026 İHTİYAÇ KREDİSİ FAİZ ORANLARI: BANKA BANKA GÜNCEL LİSTE</t>
+          <t>Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>HAZİRAN 2026 İHTİYAÇ KREDİSİ FAİZ ORANLARI: BANKA BANKA GÜNCEL LİSTE Bugün Kocaeli Gazetesi</t>
+          <t>Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor Medya Ege</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4785,32 +5036,28 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>para transferi</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Haziran 2026 itibarıyla bankalar yeni müşteri kazanımı yarışına hız verdi. Faizsiz nakit avanslardan düşük faizli ihtiyaç kredilerine kadar birçok fırsat sunulurken, 250 bin lira nakit arayan tüketiciler için 24 ay vadeli geri ödeme tutarları netleşti. Haziran 2026 itibarıyla bankalar yeni müşteri kazanımı yarışına hız verdi. Faizsiz nakit avanslardan düşük faizli ihtiyaç kredilerine kadar birçok fırsat sunulurken, 250 bin lira nakit arayan tüketiciler için 24 ay vadeli geri ödeme tutarları netleşti. Haziran 2026 itibarıyla bankalar yeni müşteri kazanımı yarışına hız verdi. Faizsiz nakit avanslardan düşük faizli ihtiyaç kredilerine kadar birçok fırsat sunulurken, 250 bin lira nakit arayan tüketiciler için 24 ay vadeli geri ödeme tutarları netleşti. Nakit ihtiyacı olan vatandaşlar için Haziran ayında bankaların güncellediği kredi kampanyaları büyük fırsatlar barındırıyor; işte yeni müşterilere özel faizsiz nakit destekleri ve 250 bin liralık ihtiyaç kredisinde banka banka aylık taksit rakamları... YENİ MÜŞTERİLERE ÖZEL FAİZSİZ KREDİ VE NAKİT AVANS KAMPANYALARI Bankalar, portföylerine yeni müşteriler katmak amacıyla "sıfır faizli" kredi ve taksitli nakit avans paketlerini duyurdu. İşte öne çıkan faizsiz destek paketleri: DenizBank: 65.000 TL’ye varan %0 faizli kredi, 25.000 TL’ye varan %0 faizli nakit avans ve 10.000 TL’ye varan %0 faizli taksitli kurtaran hesap ile toplam 100.000 TL destek. Garanti BBVA: 50.000 TL’ye varan %0 faizli kredi ve 50.000 TL’ye varan %0 faizli taksitli avans hesap ile toplam 100.000 TL fırsat. Akbank: 45.000 TL’ye varan 12 ay vadeli %0 faizli ihtiyaç kredisi ve 25.000 TL’ye varan %0 faizli taksitli avans ile toplam 70.000 TL destek. İş Bankası: 25.000 TL’ye varan %0 faizli taksitli nakit avans ve 30.000 TL’ye varan %0 faizli ek hesap ile toplam 55.000 TL fırsat. QNB: 25.000 TL’ye varan 3 ay vadeli %0 faizli ihtiyaç kredisi ve 25.000 TL’ye varan %0 faizli taksitli nakit avans ile toplam 50.000 TL destek. Albaraka Türk: Kredi kartlarıyla 40.000 TL’ye varan vade farksız 6 taksit ve 100.000 TL’ye varan %0 kâr paylı ihtiyaç finansmanı ile toplam 140.000 TL kâr paysız fırsat. DÜŞÜK FAİZLİ YENİ MÜŞTERİ FIRSATLARI Faizsiz seçeneklerin yanı sıra, yüksek limitli nakit ihtiyaçları için düşük faizli "hoş geldin" kampanyaları da dikkat çekiyor: TEB: 500.000 TL’ye varan ihtiyaç kredisi (%4,19’dan başlayan faiz) ve 25.000 TL’ye varan %0 faizli taksitli nakit avans. ON Dijital: 400.000 TL’ye varan 12 ay vadeli %3,49 faizli ertelemeli kredi ve aidatsız kredi kartı avantajı. Enpara.com: 125.000 TL’ye varan 36 ay vadeli %3,39 faizli masrafsız ihtiyaç kredisi. GetirFinans: 100.000 TL’ye varan 6 ay vadeli %2,49 faizli ihtiyaç kredisi ve 650.000 TL’ye varan %3,09’dan başlayan tüketici kredisi. Ziraat Dinamik: 100.000 TL’ye varan %2,99 faizli dijital kredi ve 20.000 TL’ye varan %1,99 taksitli avans. Yapı Kredi: 3 aya kadar ertelemeli, üst limiti 750.000 TL olan %4,69 faizli kredi fırsatı. Kuveyt Türk: Kuveyt Türk Mobil’den Pratik BES planına dahil olanlara 2.000 TL hediye imkanı. 250 BİN TL İÇİN 24 AY VADELİ KREDİ HESAPLAMALARI Peki, 250.000 TL nakit ihtiyacı olan bir tüketici için 24 ay vadede geri ödeme detayları nasıl şekilleniyor? İşte bu haftanın rakamlarına göre banka banka faiz oranları, aylık taksit tutarları ve toplam geri ödeme miktarları: Alternatif Bank: Bireysel Dijital Kredi kapsamında %2,99 faiz oranıyla sunulan pakette aylık taksit 16.208 TL, toplam geri ödeme ise 390.231 TL olarak hesaplanıyor. Anadolubank: Sigortalı Dijital İhtiyaç Kredisi faiz oranı %3,19. Aylık taksit tutarı 16.644 TL olurken, toplam geri ödeme 400.716 TL'yi buluyor. ING: Dijital İhtiyaç Kredisi için %3,29 faiz oranı uygulanıyor. Tüketiciler aylık 16.865 TL taksit ödeyerek toplamda 406.010 TL geri ödeme yapıyor. QNB: %3,34 faiz oranına sahip ihtiyaç kredisinde aylık taksit 16.976 TL, toplam ödeme ise 408.670 TL olarak belirlendi. GetirFinans: %3,39 faiz oranı sunulan kredide aylık ödeme 17.087 TL, bankaya ödenecek toplam tutar ise 411.339 TL. Enpara.com: Masrafsız ihtiyaç kredisinde faiz oranı %3,59. Bu kampanyada aylık taksit 17.535 TL, toplam ödeme 420.849 TL seviyesinde. Aktif Bank: %3,59 faiz oranlı ihtiyaç kredisinin aylık taksiti 17.535 TL ve toplam geri ödemesi 422.099 TL. ON Dijital: Ertelemeli seçenek sunan kredisinde %3,79 faiz uyguluyor. Aylık taksit 17.989 TL, toplam ödeme ise 432.993 TL. Vakıf Katılım: Yeni müşterilere özel ihtiyaç finansmanında %3,83 kâr payı oranıyla aylık taksit 18.081 TL, toplam geri ödeme tutarı 435.188 TL olarak yansıyor. Akbank: Bireysel ihtiyaç kredisi kampanyasında faiz oranı %3,99. Tüketici aylık 18.449 TL ödeyerek toplamda 444.019 TL geri ödeme gerçekleştiriyor. İş Bankası: %4,04 faiz oranlı ihtiyaç kredisi için aylık 18.564 TL taksit ve toplamda 446.796 TL ödeme yapılması gerekiyor. TEB / CEPTETEB: %4,19 faiz oranına sahip kredi paketlerinde aylık taksit tutarı 18.914 TL, toplam geri ödeme ise 455.175 TL olarak hesaplanıyor. Ziraat Bankası: Standart ihtiyaç kredisi paketinde faiz %4,29. Bu pakette aylık ödeme 19.148 TL, toplam tutar ise 460.801 TL'ye ulaşıyor. Yapı Kredi: %4,99 faizli kredi seçeneğinde tüketiciler aylık 20.825 TL taksit ödüyor, toplam tutar ise 501.050 TL seviyesinde gerçekleşiyor. Halkbank: %5,06 faiz oranlı pakette ise aylık taksit 20.996 TL ve toplam geri ödeme tutarı 505.157 TL oluyor. HAZİRAN 2026 İHTİYAÇ KREDİSİ FAİZ ORANLARI: BANKA BANKA GÜNCEL LİSTE Haziran 2026 itibarıyla bankalar yeni müşteri kazanımı yarışına hız verdi. Faizsiz nakit avanslardan düşük faizli ihtiyaç kredilerine kadar birçok fırsat sunulurken, 250 bin lira nakit arayan tüketiciler için 24 ay vadeli geri ödeme tutarları netleşti. YENİ MÜŞTERİLERE ÖZEL FAİZSİZ KREDİ VE NAKİT AVANS KAMPANYALARI DÜŞÜK FAİZLİ YENİ MÜŞTERİ FIRSATLARI 250 BİN TL İÇİN 24 AY VADELİ KREDİ HESAPLAMALARI Nakit ihtiyacı olan vatandaşlar için Haziran ayında bankaların güncellediği kredi kampanyaları büyük fırsatlar barındırıyor; işte yeni müşterilere özel faizsiz nakit destekleri ve 250 bin liralık ihtiyaç kredisinde banka banka aylık taksit rakamları... Bankalar, portföylerine yeni müşteriler katmak amacıyla "sıfır faizli" kredi ve taksitli nakit avans paketlerini duyurdu. İşte öne çıkan faizsiz destek paketleri: DenizBank: 65.000 TL’ye varan %0 faizli kredi, 25.000 TL’ye varan %0 faizli nakit avans ve 10.000 TL’ye varan %0 faizli taksitli kurtaran hesap ile toplam 100.000 TL destek. Garanti BBVA: 50.000 TL’ye varan %0 faizli kredi ve 50.000 TL’ye varan %0 faizli taksitli avans hesap ile toplam 100.000 TL fırsat. Akbank: 45.000 TL’ye varan 12 ay vadeli %0 faizli ihtiyaç kredisi ve 25.000 TL’ye varan %0 faizli taksitli avans ile toplam 70.000 TL destek. İş Bankası: 25.000 TL’ye varan %0 faizli taksitli nakit avans ve 30.000 TL’ye varan %0 faizli ek hesap ile toplam 55.000 TL fırsat. QNB: 25.000 TL’ye varan 3 ay vadeli %0 faizli ihtiyaç kredisi ve 25.000 TL’ye varan %0 faizli taksitli nakit avans ile toplam 50.000 TL destek. Albaraka Türk: Kredi kartlarıyla 40.000 TL’ye varan vade farksız 6 taksit ve 100.000 TL’ye varan %0 kâr paylı ihtiyaç finansmanı ile toplam 140.000 TL kâr paysız fırsat. Faizsiz seçeneklerin yanı sıra, yüksek limitli nakit ihtiyaçları için düşük faizli "hoş geldin" kampanyaları da dikkat çekiyor: TEB: 500.000 TL’ye varan ihtiyaç kredisi (%4,19’dan başlayan faiz) ve 25.000 TL’ye varan %0 faizli taksitli nakit avans. ON Dijital: 400.000 TL’ye varan 12 ay vadeli %3,49 faizli ertelemeli kredi ve aidatsız kredi kartı avantajı. Enpara.com: 125.000 TL’ye varan 36 ay vadeli %3,39 faizli masrafsız ihtiyaç kredisi. GetirFinans: 100.000 TL’ye varan 6 ay vadeli %2,49 faizli ihtiyaç kredisi ve 650.000 TL’ye varan %3,09’dan başlayan tüketici kredisi. Ziraat Dinamik: 100.000 TL’ye varan %2,99 faizli dijital kredi ve 20.000 TL’ye varan %1,99 taksitli avans. Yapı Kredi: 3 aya kadar ertelemeli, üst limiti 750.000 TL olan %4,69 faizli kredi fırsatı. Kuveyt Türk: Kuveyt Türk Mobil’den Pratik BES planına dahil olanlara 2.000 TL hediye imkanı. Peki, 250.000 TL nakit ihtiyacı olan bir tüketici için 24 ay vadede geri ödeme detayları nasıl şekilleniyor? İşte bu haftanın rakamlarına göre banka banka faiz oranları, aylık taksit tutarları ve toplam geri ödeme miktarları: Alternatif Bank: Bireysel Dijital Kredi kapsamında %2,99 faiz oranıyla sunulan pakette aylık taksit 16.208 TL, toplam geri ödeme ise 390.231 TL olarak hesaplanıyor. Anadolubank: Sigortalı Dijital İhtiyaç Kredisi faiz oranı %3,19. Aylık taksit tutarı 16.644 TL olurken, toplam geri ödeme 400.716 TL'yi buluyor. ING: Dijital İhtiyaç Kredisi için %3,29 faiz oranı uygulanıyor. Tüketiciler aylık 16.865 TL taksit ödeyerek toplamda 406.010 TL geri ödeme yapıyor. QNB: %3,34 faiz oranına sahip ihtiyaç kredisinde aylık taksit 16.976 TL, toplam ödeme ise 408.670 TL olarak belirlendi. GetirFinans: %3,39 faiz oranı sunulan kredide aylık ödeme 17.087 TL, bankaya ödenecek toplam tutar ise 411.339 TL. Enpara.com: Masrafsız ihtiyaç kredisinde faiz oranı %3,59. Bu kampanyada aylık taksit 17.535 TL, toplam ödeme 420.849 TL seviyesinde. Aktif Bank: %3,59 faiz oranlı ihtiyaç kredisinin aylık taksiti 17.535 TL ve toplam geri ödemesi 422.099 TL. ON Dijital: Ertelemeli seçenek sunan kredisinde %3,79 faiz uyguluyor. Aylık taksit 17.989 TL, toplam ödeme ise 432.993 TL. Vakıf Katılım: Yeni müşterilere özel ihtiyaç finansmanında %3,83 kâr payı oranıyla aylık taksit 18.081 TL, toplam geri ödeme tutarı 435.188 TL olarak yansıyor. Akbank: Bireysel ihtiyaç kredisi kampanyasında faiz oranı %3,99. Tüketici aylık 18.449 TL ödeyerek toplamda 444.019 TL geri ödeme gerçekleştiriyor. İş Bankası: %4,04 faiz oranlı ihtiyaç kredisi için aylık 18.564 TL taksit ve toplamda 446.796 TL ödeme yapılması gerekiyor. TEB / CEPTETEB: %4,19 faiz oranına sahip kredi paketlerinde aylık taksit tutarı 18.914 TL, toplam geri ödeme ise 455.175 TL olarak hesaplanıyor. Ziraat Bankası: Standart ihtiyaç kredisi paketinde faiz %4,29. Bu pakette aylık ödeme 19.148 TL, toplam tutar ise 460.801 TL'ye ulaşıyor. Yapı Kredi: %4,99 faizli kredi seçeneğinde tüketiciler aylık 20.825 TL taksit ödüyor, toplam tutar ise 501.050 TL seviyesinde gerçekleşiyor. Halkbank: %5,06 faiz oranlı pakette ise aylık taksit 20.996 TL ve toplam geri ödeme tutarı 505.157 TL oluyor.</t>
+          <t>Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor Medya Ege</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>HAZİRAN 2026 İHTİYAÇ KREDİSİ FAİZ ORANLARI: BANKA BANKA GÜNCEL LİSTE HAZİRAN 2026 İHTİYAÇ KREDİSİ FAİZ ORANLARI: BANKA BANKA GÜNCEL LİSTE Bugün Kocaeli Gazetesi Haziran 2026 itibarıyla bankalar yeni müşteri kazanımı yarışına hız verdi. Faizsiz nakit avanslardan düşük faizli ihtiyaç kredilerine kadar birçok fırsat sunulurken, 250 bin lira nakit arayan tüketiciler için 24 ay vadeli geri ödeme tutarları netleşti. Nakit ihtiyacı olan vatandaşlar için Haziran ayında bankaların güncellediği kredi kampanyaları büyük fırsatlar barındırıyor; işte yeni müşterilere özel faizsiz nakit destekleri ve 250 bin liralık ihtiyaç kredisinde banka banka aylık taksit rakamları... YENİ MÜŞTERİLERE ÖZEL FAİZSİZ KREDİ VE NAKİT AVANS KAMPANYALARI Bankalar, portföylerine yeni müşteriler katmak amacıyla "sıfır faizli" kredi ve taksitli nakit avans paketlerini duyurdu. İşte öne çıkan faizsiz destek paketleri: DenizBank: 65.000 TL’ye varan %0 faizli kredi, 25.000 TL’ye varan %0 faizli nakit avans ve 10.000 TL’ye varan %0 faizli taksitli kurtaran hesap ile toplam 100.000 TL destek. Garanti BBVA: 50.000 TL’ye varan %0 faizli kredi ve 50.000 TL’ye varan %0 faizli taksitli avans hesap ile toplam 100.000 TL fırsat. Akbank: 45.000 TL’ye varan 12 ay vadeli %0 faizli ihtiyaç kredisi ve 25.000 TL’ye varan %0 faizli taksitli avans ile toplam 70.000 TL destek. İş Bankası: 25.000 TL’ye varan %0 faizli taksitli nakit avans ve 30.000 TL’ye varan %0 faizli ek hesap ile toplam 55.000 TL fırsat. Albaraka Türk: Kredi kartlarıyla 40.000 TL’ye varan vade farksız 6 taksit ve 100.000 TL’ye varan %0 kâr paylı ihtiyaç finansmanı ile toplam 140.000 TL kâr paysız fırsat. DÜŞÜK FAİZLİ YENİ MÜŞTERİ FIRSATLARI Faizsiz seçeneklerin yanı sıra, yüksek limitli nakit ihtiyaçları için düşük faizli "hoş geldin" kampanyaları da dikkat çekiyor: TEB: 500.000 TL’ye varan ihtiyaç kredisi (%4,19’dan başlayan faiz) ve 25.000 TL’ye varan %0 faizli taksitli nakit avans. ON Dijital: 400.000 TL’ye varan 12 ay vadeli %3,49 faizli ertelemeli kredi ve aidatsız kredi kartı avantajı. Enpara.com: 125.000 TL’ye varan 36 ay vadeli %3,39 faizli masrafsız ihtiyaç kredisi. GetirFinans: 100.000 TL’ye varan 6 ay vadeli %2,49 faizli ihtiyaç kredisi ve 650.000 TL’ye varan %3,09’dan başlayan tüketici kredisi. Ziraat Dinamik: 100.000 TL’ye varan %2,99 faizli dijital kredi ve 20.000 TL’ye varan %1,99 taksitli avans. Yapı Kredi: 3 aya kadar ertelemeli, üst limiti 750.000 TL olan %4,69 faizli kredi fırsatı. 250 BİN TL İÇİN 24 AY VADELİ KREDİ HESAPLAMALARI Peki, 250.000 TL nakit ihtiyacı olan bir tüketici için 24 ay vadede geri ödeme detayları nasıl şekilleniyor? İşte bu haftanın rakamlarına göre banka banka faiz oranları, aylık taksit tutarları ve toplam geri ödeme miktarları: Alternatif Bank: Bireysel Dijital Kredi kapsamında %2,99 faiz oranıyla sunulan pakette aylık taksit 16.208 TL, toplam geri ödeme ise 390.231 TL olarak hesaplanıyor. QNB: %3,34 faiz oranına sahip ihtiyaç kredisinde aylık taksit 16.976 TL, toplam ödeme ise 408.670 TL olarak belirlendi. Enpara.com: Masrafsız ihtiyaç kredisinde faiz oranı %3,59. Akbank: Bireysel ihtiyaç kredisi kampanyasında faiz oranı %3,99. TEB / CEPTETEB: %4,19 faiz oranına sahip kredi paketlerinde aylık taksit tutarı 18.914 TL, toplam geri ödeme ise 455.175 TL olarak hesaplanıyor. Bu pakette aylık ödeme 19.148 TL, toplam tutar ise 460.801 TL'ye ulaşıyor. Yapı Kredi: %4,99 faizli kredi seçeneğinde tüketiciler aylık 20.825 TL taksit ödüyor, toplam tutar ise 501.050 TL seviyesinde gerçekleşiyor. HAZİRAN 2026 İHTİYAÇ KREDİSİ FAİZ ORANLARI: BANKA BANKA GÜNCEL LİSTE Haziran 2026 itibarıyla bankalar yeni müşteri kazanımı yarışına hız verdi. YENİ MÜŞTERİLERE ÖZEL FAİZSİZ KREDİ VE NAKİT AVANS KAMPANYALARI DÜŞÜK FAİZLİ YENİ MÜŞTERİ FIRSATLARI 250 BİN TL İÇİN 24 AY VADELİ KREDİ HESAPLAMALARI Nakit ihtiyacı olan vatandaşlar için Haziran ayında bankaların güncellediği kredi kampanyaları büyük fırsatlar barındırıyor; işte yeni müşterilere özel faizsiz nakit destekleri ve 250 bin liralık ihtiyaç kredisinde banka banka aylık taksit rakamları... Bankalar, portföylerine yeni müşteriler katmak amacıyla "sıfır faizli" kredi ve taksitli nakit avans paketlerini duyurdu. Faizsiz seçeneklerin yanı sıra, yüksek limitli nakit ihtiyaçları için düşük faizli "hoş geldin" kampanyaları da dikkat çekiyor: TEB: 500.000 TL’ye varan ihtiyaç kredisi (%4,19’dan başlayan faiz) ve 25.000 TL’ye varan %0 faizli taksitli nakit avans. Peki, 250.000 TL nakit ihtiyacı olan bir tüketici için 24 ay vadede geri ödeme detayları nasıl şekilleniyor?</t>
+          <t>Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor Medya Ege Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor Medya Ege</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://www.bugunkocaeli.com.tr/haziran-2026-ihtiyac-kredisi-faiz-oranlari-banka-banka-guncel-liste/amp</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbnRGTWt3Z0JMZllmZkljbTg1cUg5Tl9ybnE1RUZ0Wnc5M25fWmJ2UXd1blRGYXAtSWc3c3RKXzhoOWNyOVhMbGdJRVQydWhzSjFXQjhqU1J0dG05MzNLN1gzZzVZalRRRndUR2xROE5RdVluWWtPUUpkXy1nakhpSGw0d1hUeXRmUFVkTmV6emZNa1lna2IybW5xZ3RlZU9udEsyVDRjdjVqUXplOVZCVUY2LVBwZ3N3MXFFb1Nnb9IBzwFBVV95cUxPeTlfVVlTR1hnOGFMVkVqemRDQ0dVUWhWaHg3UU9FZHJPbkUxU3lxdFZXZTJWdnRYTVF2TWlJejRncjNGbUpxSWtuQWxQbEVGbzRfNDd3MlZSclgzM2hSWWhGc1RacFoteXo2ZnQ4MmJtN25BYUdxbnNUQ1ZJSUZKOWpFamZ0MGRuY28xSGdyV2xmYzk3TDhvSTRldGM0QkxOc25PVzNwNGs3UHhGc2xOMDJhZEJtRjJVRFNqN291R3E4WVNxZzZBeU5QZ0lFNkk?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
@@ -4836,7 +5083,7 @@
       <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr"/>
       <c r="AA30" s="2" t="n">
-        <v>77.75</v>
+        <v>88.52</v>
       </c>
       <c r="AB30" s="2" t="n">
         <v>29</v>
@@ -4845,27 +5092,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 20:56:23</t>
+          <t>2026-06-08 05:27:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>banka soruşturma</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Orman ürünleri fabrikasında yangın paniği</t>
+          <t>Banka ATM'lerini kullanan sahte para çetesi yakalandı</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Orman ürünleri fabrikasında yangın paniği Yeniçağ Gazetesi</t>
+          <t>Banka ATM'lerini kullanan sahte para çetesi yakalandı Aydınlık</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4875,22 +5122,22 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Orman ürünleri fabrikasında yangın paniği Yeniçağ Gazetesi</t>
+          <t>Banka ATM'lerini kullanan sahte para çetesi yakalandı Aydınlık</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Orman ürünleri fabrikasında yangın paniği Orman ürünleri fabrikasında yangın paniği Yeniçağ Gazetesi Orman ürünleri fabrikasında yangın paniği Yeniçağ Gazetesi</t>
+          <t>Banka ATM'lerini kullanan sahte para çetesi yakalandı Banka ATM'lerini kullanan sahte para çetesi yakalandı Aydınlık Banka ATM'lerini kullanan sahte para çetesi yakalandı Aydınlık</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -4900,7 +5147,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.yenicaggazetesi.com/orman-urunleri-fabrikasinda-yangin-panigi-1037848h.htm</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOVkktTEp1a2YwVUNwTUVrVmJ2OEpRcFg1YklNeFFjcFppQVpkaUdzMnh5dUxxcnJESWNKQmtrQzlvWjBIM0RQZGMzVXppcVpIWmJkXzZ1R0tBY2ROQUtuWl94V3JoeWhBdUVIQm54cDhHSkEyRVpuZWd1bTBJVkg0OW1RazNjYTMzcHF5azN0dmh3aFAtREJqU9IBngFBVV95cUxOQWpJWGhqRF80RE1VaUJTdVRMRTN6YVExQlllVTNpTTBSaWhDdVFyM0REcHg4NTFGdmlPQjgzWEFNc0dvOEZkU2IyRDlYUi1MSzZvTGhwX24tdGMyekM2STVsdElWR0ljWU9RZ2pBcHA0TXRUX3JYSFFtMU9zQ0M1TjliVkprUmh5UmNIUENta1ZPOUI5S2U0Ti1BcUVpQQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
@@ -4926,7 +5173,7 @@
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="n">
-        <v>43.58</v>
+        <v>40.62</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>30</v>
@@ -4935,7 +5182,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 17:35:00</t>
+          <t>2026-06-08 06:35:01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -4950,12 +5197,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır yangın: Yenişehir’de oto tamir atölyesinde hasar oluştu</t>
+          <t>Bafra'da Sanayi Sitesinde Yangın</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır yangın: Yenişehir’de oto tamir atölyesinde hasar oluştu 24 Saat Gazetesi Ankara</t>
+          <t>Bafra'da Sanayi Sitesinde Yangın Son Dakika</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -4965,22 +5212,18 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>atölye</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>atölye</t>
-        </is>
-      </c>
+          <t>sanayi</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır yangın haberinde, Yenişehir ilçesi Elazığ yolundaki oto tamir atölyesinde çıkan yangın itfaiyenin müdahalesiyle söndürüldü. İş yerinde hasar meydana geldi. Diyarbakır yangın haberinde, Yenişehir ilçesi Elazığ yolundaki oto tamir atölyesinde çıkan yangın itfaiyenin müdahalesiyle söndürüldü. İş yerinde hasar meydana geldi. Diyarbakır yangın haberinde, Yenişehir ilçesi Elazığ yolundaki oto tamir atölyesinde çıkan yangın itfaiyenin müdahalesiyle söndürüldü. İş yerinde hasar meydana geldi. Diyarbakır yangın: Yenişehir’de oto tamir atölyesinde hasar oluştu Diyarbakır yangın haberinde, Yenişehir ilçesi Elazığ yolundaki oto tamir atölyesinde çıkan yangın itfaiyenin müdahalesiyle söndürüldü. İş yerinde hasar meydana geldi. Anadolu Ajansı Editör 06.06.2026 - 20:35 Yayınlanma 06.06.2026 - 21:02 Güncelleme Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Diyarbakır’ın merkez Yenişehir ilçesinde bulunan bir oto tamir atölyesinde yangın çıktı. Elazığ yolu üzerindeki iş yerinde başlayan Diyarbakır yangın olayına itfaiye ekipleri müdahale ederken, polis çevrede güvenlik önlemi aldı. Yangın kontrol altına alınarak söndürüldü, atölyede hasar oluştu. Yenişehir’de oto tamir atölyesinde Diyarbakır yangın paniği Yangın, merkez Yenişehir ilçesi Elazığ yolu üzerinde faaliyet gösteren bir oto tamir atölyesinde meydana geldi. Atölyede madeni yağ ve akülerin de bulunduğu öğrenilirken, yangının çıkış nedeni henüz belirlenemedi. Gebze'de 4 kişinin hayatını kaybettiği çöken binanın çevresindeki yapılar yıkılıyor İçeriği Görüntüle İş yerinden yükselen dumanları fark edenlerin ihbarı üzerine bölgeye itfaiye ve polis ekipleri sevk edildi. Madeni yağ ve akü gibi yanıcı ya da risk oluşturabilecek malzemelerin bulunduğu işletmelerde, yangına erken müdahale edilmesi çevredeki diğer iş yerleri açısından da önem taşıyor. Diyarbakır yangın kısa sürede kontrol altına alındı Olay yerine ulaşan polis ekipleri, iş yerinin çevresinde güvenlik önlemi aldı. İtfaiye ekipleri ise atölyedeki yangına müdahale ederek alevlerin büyümesini engelledi. Ekiplerin çalışmasıyla yangın söndürüldü. Yangında can kaybı ya da yaralanmaya ilişkin bilgi paylaşılmazken, oto tamir atölyesinde hasar meydana geldi. İş yerinde oluşan zararın boyutunun yapılacak incelemenin ardından netleşmesi bekleniyor. Yangının çıkış nedeni araştırılıyor Diyarbakır yangın olayının ardından ekiplerin iş yerinde inceleme yapacağı değerlendiriliyor. Yangının çıkış nedeni, teknik inceleme ve olay yerindeki tespitlerin ardından netlik kazanacak. Bölgedeki güvenlik önlemleri, itfaiye ekiplerinin çalışmasının tamamlanmasının ardından kaldırılırken, olayla ilgili inceleme sürüyor. Kaynak: AA Editörün Seçtiği Fenerbahçe başkanlık seçimi bugün yapılıyor: Yeni başkan belli olacak. FB başkanlık seçimi canlı izle Editörün Seçtiği ABD-Almanya maçı ne zaman, saat kaçta, hangi kanalda? ABD-Almanya maçı canlı izle ekranı ve muhtemel 11’ler Editörün Seçtiği 2026 FIFA Dünya Kupası maç programı: Açılış Mexico City’de, final New Jersey’de Editör Hakkında Anadolu Ajansı Bunlar d</t>
+          <t>Bafra Kızılırmak Sanayi Sitesi'nde çıkan yangında traktör ve malzemeler yandı, maddi hasar büyük. Bafra Kızılırmak Sanayi Sitesi'nde çıkan yangında traktör ve malzemeler yandı, maddi hasar büyük. Bafra Kızılırmak Sanayi Sitesi'nde çıkan yangında traktör ve malzemeler yandı, maddi hasar büyük. Bafra'da Sanayi Sitesinde Yangın Son Güncelleme: 08.06.2026 09:35 Bafra Kızılırmak Sanayi Sitesi'nde çıkan yangında traktör ve malzemeler yandı, maddi hasar büyük. Samsun'un Bafra ilçesinde bulunan Kızılırmak Sanayi Sitesi'nde çıkan yangın, korku dolu anlara neden oldu. Yangında iş yerinde bulunan bir traktör ile çok sayıda malzeme kullanılamaz hale gelirken, iş yerinde büyük çapta maddi hasar meydana geldi. Yangın, gece saat 23.00 sıralarında Kızılırmak Sanayi Sitesi'nde meydana geldi. Edinilen bilgilere göre, kapalı durumdaki iş yerinden dumanlar yükseldiğini fark eden devriye görevindeki bekçiler durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ve polis ekibi sevk edildi. Yangına müdahale edebilmek için iş yerinin kepengini kıran itfaiye ekipleri, alevleri kısa sürede kontrol altına alarak çevredeki iş yerlerine sıçramasını önledi. Yangında iş yerinde bulunan bir traktör tamamen yanarak kullanılamaz hale gelirken, içeride bulunan çeşitli malzemeler de alevlere teslim oldu. Olayda can kaybı ya da yaralanma yaşanmazken, iş yerinde büyük çapta maddi hasar oluştu. İş yeri sahibi Recep Bayrak'ın, Artvin'de katıldığı bir cenazeden döndüğü sırada yangın haberini alarak olay yerine geldiği öğrenildi. İtfaiye ekiplerinin soğutma çalışmalarının ardından yangın tamamen söndürülürken, yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. - SAMSUN Kaynak: İHA Samsun'un Bafra ilçesinde bulunan Kızılırmak Sanayi Sitesi'nde çıkan yangın, korku dolu anlara neden oldu. Yangında iş yerinde bulunan bir traktör ile çok sayıda malzeme kullanılamaz hale gelirken, iş yerinde büyük çapta maddi hasar meydana geldi. Yangın, gece saat 23.00 sıralarında Kızılırmak Sanayi Sitesi'nde meydana geldi. Edinilen bilgilere göre, kapalı durumdaki iş yerinden dumanlar yükseldiğini fark eden devriye görevindeki bekçiler durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ve polis ekibi sevk edildi. Yangına müdahale edebilmek için iş yerinin kepengini kıran itfaiye ekipleri, alevleri kısa sürede kontrol altına alarak çevredeki iş yerlerine sıçramasını önledi. Yangında iş yerinde bulunan bir traktör tamamen yanarak kullanılamaz hale gelirken, içeride bulunan çeşitli malzemeler de alevlere teslim oldu. Olayda can kaybı ya da yaralanma yaşanmazken, iş yerinde büyük çapta maddi hasar oluştu. İş yeri sahibi Recep Bayrak'ın, Artvin'de katıldığı bir cenazeden döndüğü sırada yangın haberini alarak olay yerine geldiği öğrenildi. İtfaiye ekiplerinin soğutma çalışmalarının ardından yangın tamamen söndürülürken, yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. - SAMSUN Bafra'da Sanayi Sitesinde Yangın Bafra Kızılırmak Sanayi Sitesi'nde çıkan yangında traktör ve malzemeler yandı, maddi hasar büyük. Samsun'un Bafra ilçesinde bulunan Kızılırmak Sanayi Sitesi'nde çıkan yangın, korku dolu anlara neden oldu. Yangında iş yerinde bulunan bir traktör ile çok sayıda malzeme kullanılamaz hale gelirken, iş yerinde büyük çapta maddi hasar meydana geldi. Yangın, gece saat 23.00 sıralarında Kızılırmak Sanayi Sitesi'nde meydana geldi. Edinilen bilgilere göre, kapalı durumdaki iş yerinden dumanlar yükseldiğini fark eden devriye görevindeki bekçiler durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ve polis ekibi sevk edildi. Yangına müdahale edebilmek için iş yerinin kepengini kıran itfaiye ekipleri, alevleri kısa sürede kontrol altına alarak çevredeki iş yerlerine sıçramasını önledi. Yangında iş yerinde bulunan bir traktör tamamen yanarak kullanılamaz hale gelirken, içeride bulunan çeşitli malzemeler de alevlere teslim oldu. Olayda can kaybı ya da yaralanma yaşanmazken, iş yerinde büyük çapta maddi hasar oluştu. İş yeri sahibi Recep Bayrak'ın, Artvin'de katıldığı bir cenazeden döndüğü sırada yangın haberini alarak olay yerine geldiği öğrenildi. İtfaiye ekiplerinin soğutma çalışmalarının ardından yangın tamamen söndürülürken, yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. - SAMSUN</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır yangın: Yenişehir’de oto tamir atölyesinde hasar oluştu Diyarbakır yangın: Yenişehir’de oto tamir atölyesinde hasar oluştu 24 Saat Gazetesi Ankara Diyarbakır yangın haberinde, Yenişehir ilçesi Elazığ yolundaki oto tamir atölyesinde çıkan yangın itfaiyenin müdahalesiyle söndürüldü. İş yerinde hasar meydana geldi. Diyarbakır yangın: Yenişehir’de oto tamir atölyesinde hasar oluştu Diyarbakır yangın haberinde, Yenişehir ilçesi Elazığ yolundaki oto tamir atölyesinde çıkan yangın itfaiyenin müdahalesiyle söndürüldü.</t>
+          <t>Bafra'da Sanayi Sitesinde Yangın Bafra'da Sanayi Sitesinde Yangın Son Dakika Bafra Kızılırmak Sanayi Sitesi'nde çıkan yangında traktör ve malzemeler yandı, maddi hasar büyük. Bafra'da Sanayi Sitesinde Yangın Son Güncelleme: 08.06.2026 09:35 Bafra Kızılırmak Sanayi Sitesi'nde çıkan yangında traktör ve malzemeler yandı, maddi hasar büyük. Samsun'un Bafra ilçesinde bulunan Kızılırmak Sanayi Sitesi'nde çıkan yangın, korku dolu anlara neden oldu. Yangında iş yerinde bulunan bir traktör ile çok sayıda malzeme kullanılamaz hale gelirken, iş yerinde büyük çapta maddi hasar meydana geldi. Yangın, gece saat 23.00 sıralarında Kızılırmak Sanayi Sitesi'nde meydana geldi. Edinilen bilgilere göre, kapalı durumdaki iş yerinden dumanlar yükseldiğini fark eden devriye görevindeki bekçiler durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine olay yerine çok sayıda itfaiye ve polis ekibi sevk edildi. Yangına müdahale edebilmek için iş yerinin kepengini kıran itfaiye ekipleri, alevleri kısa sürede kontrol altına alarak çevredeki iş yerlerine sıçramasını önledi. Yangında iş yerinde bulunan bir traktör tamamen yanarak kullanılamaz hale gelirken, içeride bulunan çeşitli malzemeler de alevlere teslim oldu. Olayda can kaybı ya da yaralanma yaşanmazken, iş yerinde büyük çapta maddi hasar oluştu. İş yeri sahibi Recep Bayrak'ın, Artvin'de katıldığı bir cenazeden döndüğü sırada yangın haberini alarak olay yerine geldiği öğrenildi. İtfaiye ekiplerinin soğutma çalışmalarının ardından yangın tamamen söndürülürken, yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. - SAMSUN Kaynak: İHA Samsun'un Bafra ilçesinde bulunan Kızılırmak Sanayi Sitesi'nde çıkan yangın, korku dolu anlara neden oldu. - SAMSUN Bafra'da Sanayi Sitesinde Yangın Bafra Kızılırmak Sanayi Sitesi'nde çıkan yangında traktör ve malzemeler yandı, maddi hasar büyük.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -4990,20 +5233,24 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.24saatgazetesi.com/diyarbakir-yangin-yenisehirde-oto-tamir-atolyesinde-hasar-olustu</t>
+          <t>https://www.sondakika.com/amp/haber-bafra-da-sanayi-sitesinde-yangin-19923191/</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Bursa | Diyarbakır | Mersin</t>
+          <t>Artvin | Samsun | Çankırı</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Yenişehir</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr"/>
+          <t>Kızılırmak | Bafra</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Bafra Kızılırmak Sanayi Sitesi | 35 Bafra Kızılırmak Sanayi Sitesi | 00 sıralarında Kızılırmak Sanayi Sitesi</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="inlineStr"/>
@@ -5024,7 +5271,7 @@
       <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr"/>
       <c r="AA32" s="2" t="n">
-        <v>114.5</v>
+        <v>99.75</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>31</v>
@@ -5033,27 +5280,27 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07 05:28:00</t>
+          <t>2026-06-08 07:03:00</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>şüpheli işlem</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Meydana Gelen Plastik Eşya Deposundaki Yangında Maddi Hasar Oluştu</t>
+          <t>Son Dakika: Ziraat Bankası'ndan 1 Milyon liralık SMS Alanlar Paniğe Kapıldı! Sistem mi Hacklendi?</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Meydana Gelen Plastik Eşya Deposundaki Yangında Maddi Hasar Oluştu Mersin Haber</t>
+          <t>Son Dakika: Ziraat Bankası'ndan 1 Milyon liralık SMS Alanlar Paniğe Kapıldı! Sistem mi Hacklendi? Afyon Ana Haber</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -5063,94 +5310,58 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Meydana Gelen Plastik Eşya Deposundaki Yangında Maddi Hasar Oluştu Mersin Haber</t>
+          <t>Ziraat Bankası müşterileri, 7-8 Haziran 2026 gecesi peş peşe gelen "Telegram Ayyıldız Teams" kaynaklı 1.000.000 TL'lik şüpheli harcama SMS'leriyle güne uyandı. Binlerce kişiyi paniğe sevk eden, çağrı merkezlerini kilitleyen siber güvenlik olayının tüm detayları, BKM ve banka kanallarından gelen ilk bilgiler haberimizde. Ziraat Bankası müşterileri, 7-8 Haziran 2026 gecesi peş peşe gelen "Telegram Ayyıldız Teams" kaynaklı 1.000.000 TL'lik şüpheli harcama SMS'leriyle güne uyandı. Binlerce kişiyi paniğe sevk eden, çağrı merkezlerini kilitleyen siber güvenlik olayının tüm detayları, BKM ve banka kanallarından gelen ilk bilgiler haberimizde. Ziraat Bankası müşterileri, 7-8 Haziran 2026 gecesi peş peşe gelen "Telegram Ayyıldız Teams" kaynaklı 1.000.000 TL'lik şüpheli harcama SMS'leriyle güne uyandı. Binlerce kişiyi paniğe sevk eden, çağrı merkezlerini kilitleyen siber güvenlik olayının tüm detayları, BKM ve banka kanallarından gelen ilk bilgiler haberimizde. Türkiye'nin en köklü kamu bankalarından biri olan Ziraat Bankası , 7 Haziran'ı 8 Haziran 2026 Pazartesi gününe bağlayan gece yarısı ve sabah saatlerinde eşi benzeri görülmemiş bir SMS kriziyle çalkalandı. Bankada hesabı veya kartı bulunan binlerce vatandaşa, eş zamanlı olarak "Telegram Ayyıldız Teams" adlı iş yerinden 1.000.000 TL (1 Milyon Türk Lirası) tutarında harcama yapılmaya çalışıldığına ve onay şifresi gerektiğine dair resmi SMS'ler gitti. Hesaplarında ve kartlarında böyle bir limit dahi bulunmayan vatandaşlar yataklarından fırlayarak paniğe kapılırken, bankanın çağrı merkezi kilitlendi. Siber güvenlik uzmanları ve banka kaynakları olayın perde arkasını araştırmaya başladı. "Limitim Yok, Onayım Yok!" Şikayet Siteleri Çöktü Gece saat 03:00 ile sabah 08:30 arasında telefonlarına gelen mesajı gören vatandaşlar, soluğu şikayet platformlarında ve sosyal medyada aldı. Gelen tüm mesajlarda harcama tutarının standart olarak 1.000.000 TL olması ve işlem yeri olarak "Ate te ayyıldız@telegram" veya "Telegram @ayyıldızteams" ibarelerinin yer alması dikkat çekti. Mağdur vatandaşlar yaşadıkları korkuyu şu sözlerle dile getirdi: "Gece saat 03.26’da telefonuma 1 milyon TL'lik alışveriş şifresi geldi. Benim kartlarımda böyle bir limit bile yok. Kartımın internet alışverişine kapalı olduğunu bildiğim halde dehşete düştüm." "Mesajı alır almaz hemen Ziraat Bankası şüpheli ve çalıntı kart işlemleri birimini aradım. Ancak 15 dakika boyunca hatta beklememe rağmen hiçbir muhataba ulaşamadım. Çağrı merkezi resmen çökmüş durumda." Ziraat Bankası Hacklendi mi? İlk Bilgiler Geldi! Binlerce kişiye aynı anda giden şifre mesajları, akıllara "Ziraat Bankası sistemleri siber saldırıya mı uğradı, kişisel veriler sızdırıldı mı?" sorularını getirdi. Bankanın iç kaynaklarından ve siber güvenlik departmanlarından edinilen ilk gayriresmi bilgilere göre durum korkulandan farklı. Hacklenme Söz Konusu Değil: Banka yetkililerinden sızan bilgilere göre Ziraat Bankası sistemlerinin hacklenmesi veya finansal bir veri sızıntısı durumu bulunmuyor. BKM Kaynaklı SMS Filtreleme Sorunu: Gelen SMS'lerin aslında doğrudan Ziraat Bankası altyapısından ziyade, BKM (Bankalararası Kart Merkezi) üzerinden tetiklendiği belirtildi. Herhangi bir finansal kayıp veya hesaptan para çekilmesi (provizyon) durumu tespit edilmedi. Filtreleme Canlıya Alınıyor: Teknik ekiplerin bu sahte SMS ağını engellemek ve SMS kanallarını filtrelemek için acil bir çalışma başlattığı, filtrelerin gün içinde tamamen devreye alınacağı öğrenildi. Çağrı Merkezine Ulaşılamıyor: Müşteriler Çaresiz Kaldı Olayın en çok eleştirilen yönü ise bankanın kriz yönetimi oldu. Gece yarısı hesaplarının boşaltıldığını düşünen binlerce kişi aynı anda Ziraat Bankası Kayıp/Çalıntı ve Şüpheli İşlem Hattı'nı arayınca hatlar tamamen kilitlendi. Vatandaşlar 15 dakikayı bulan bekleme sürelerine rağmen hiçbir müşteri temsilcisine bağlanamadıklarını belirterek, "Olası bir siber saldırıda bankanın muhatap sunamaması güvensizlik yarattı, sorumluluk bankaya aittir" diyerek tepki gösterdi. Bu Durumda Ne Yapmalısınız? İşte Uzmanlardan 5 Hayati Önlem! Siber güvenlik uzmanları, bu tarz kitlesel SMS krizlerinde vatandaşların kendi güvenliklerini sağlamaları adına şu adımları acilen atması gerektiğini vurguluyor: Kartlarınızı Mobil Uygulamadan Geçici Olarak Kapatın: Paniğe kapılmak yerine bankanızın mobil uygulamasına girerek kredi kartı ve banka kartlarınızı "Geçici olarak kullanıma kapat" seçeneğiyle bloke edin. Mobil Uygulamadan Harcamaları Kontrol Edin: Mesaj geldiyse panik yapmadan hesap hareketlerinizi ve bekleyen provizyonları inceleyin. Eğer bilginiz dışında gerçekleşen bir çekim varsa anında "Charge-back" (Ters ibraz) sürecini başlatın. Şifrenizi Kimseyle Pay</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Sultangazi'de Meydana Gelen Plastik Eşya Deposundaki Yangında Maddi Hasar Oluştu Sultangazi'de Meydana Gelen Plastik Eşya Deposundaki Yangında Maddi Hasar Oluştu Mersin Haber Sultangazi'de Meydana Gelen Plastik Eşya Deposundaki Yangında Maddi Hasar Oluştu Mersin Haber</t>
+          <t>Son Dakika: Ziraat Bankası'ndan 1 Milyon liralık SMS Alanlar Paniğe Kapıldı! Sistem mi Hacklendi? Son Dakika: Ziraat Bankası'ndan 1 Milyon liralık SMS Alanlar Paniğe Kapıldı! Sistem mi Hacklendi? Afyon Ana Haber Ziraat Bankası müşterileri, 7-8 Haziran 2026 gecesi peş peşe gelen "Telegram Ayyıldız Teams" kaynaklı 1.000.000 TL'lik şüpheli harcama SMS'leriyle güne uyandı. Binlerce kişiyi paniğe sevk eden, çağrı merkezlerini kilitleyen siber güvenlik olayının tüm detayları, BKM ve banka kanallarından gelen ilk bilgiler haberimizde. Türkiye'nin en köklü kamu bankalarından biri olan Ziraat Bankası , 7 Haziran'ı 8 Haziran 2026 Pazartesi gününe bağlayan gece yarısı ve sabah saatlerinde eşi benzeri görülmemiş bir SMS kriziyle çalkalandı. Bankada hesabı veya kartı bulunan binlerce vatandaşa, eş zamanlı olarak "Telegram Ayyıldız Teams" adlı iş yerinden 1.000.000 TL (1 Milyon Türk Lirası) tutarında harcama yapılmaya çalışıldığına ve onay şifresi gerektiğine dair resmi SMS'ler gitti. Hesaplarında ve kartlarında böyle bir limit dahi bulunmayan vatandaşlar yataklarından fırlayarak paniğe kapılırken, bankanın çağrı merkezi kilitlendi. Siber güvenlik uzmanları ve banka kaynakları olayın perde arkasını araştırmaya başladı. "Limitim Yok, Onayım Yok!" Şikayet Siteleri Çöktü Gece saat 03:00 ile sabah 08:30 arasında telefonlarına gelen mesajı gören vatandaşlar, soluğu şikayet platformlarında ve sosyal medyada aldı. Gelen tüm mesajlarda harcama tutarının standart olarak 1.000.000 TL olması ve işlem yeri olarak "Ate te ayyıldız@telegram" veya "Telegram @ayyıldızteams" ibarelerinin yer alması dikkat çekti. Mağdur vatandaşlar yaşadıkları korkuyu şu sözlerle dile getirdi: "Gece saat 03.26’da telefonuma 1 milyon TL'lik alışveriş şifresi geldi. Kartımın internet alışverişine kapalı olduğunu bildiğim halde dehşete düştüm." "Mesajı alır almaz hemen Ziraat Bankası şüpheli ve çalıntı kart işlemleri birimini aradım. Ancak 15 dakika boyunca hatta beklememe rağmen hiçbir muhataba ulaşamadım. Çağrı merkezi resmen çökmüş durumda." Ziraat Bankası Hacklendi mi? Binlerce kişiye aynı anda giden şifre mesajları, akıllara "Ziraat Bankası sistemleri siber saldırıya mı uğradı, kişisel veriler sızdırıldı mı?" sorularını getirdi. Hacklenme Söz Konusu Değil: Banka yetkililerinden sızan bilgilere göre Ziraat Bankası sistemlerinin hacklenmesi veya finansal bir veri sızıntısı durumu bulunmuyor. BKM Kaynaklı SMS Filtreleme Sorunu: Gelen SMS'lerin aslında doğrudan Ziraat Bankası altyapısından ziyade, BKM (Bankalararası Kart Merkezi) üzerinden tetiklendiği belirtildi. Gece yarısı hesaplarının boşaltıldığını düşünen binlerce kişi aynı anda Ziraat Bankası Kayıp/Çalıntı ve Şüpheli İşlem Hattı'nı arayınca hatlar tamamen kilitlendi. Siber güvenlik uzmanları, bu tarz kitlesel SMS krizlerinde vatandaşların kendi güvenliklerini sağlamaları adına şu adımları acilen atması gerektiğini vurguluyor: Kartlarınızı Mobil Uygulamadan Geçici Olarak Kapatın: Paniğe kapılmak yerine bankanızın mobil uygulamasına girerek kredi kartı ve banka kartlarınızı "Geçici olarak kullanıma kapat" seçeneğiyle bloke edin. Eğer bilginiz dışında gerçekleşen bir çekim varsa anında "Charge-back" (Ters ibraz) sürecini başlatın.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>summary_only</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQekZ1elpabTRpOUpiMDlVeTQ0cFloRk9la28ycTVEWTlzWjY3QU1hMmtuOWZ5RnBsOFhEUFZ4TzRfX2FJSENfMjJtcjg4dDdVVFdudEFxckV6N1FmRXlrbU9EenRKTjdNQmRRUGIzemFSSzk3NVhfR0xuSXlSY3lEdi1DSmt0M3FnQ3NGSnF2LU1MZ0gxbkp6RENKa1FkOXdqbWZJRXIwU08zV194QjVETVdwUTBHbExIalI3ONIBV0FVX3lxTE5sWkVkYTZWTmh0WGhNcnZKUTJpOEh5emhCTkJaSXBkMmw0RXliZnRESkRZMEFOLXNNbWFjNUJndmNQX01MWEFUM1NsMnNpQnppTld0dVpSQQ?oc=5&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Sultangazi</t>
-        </is>
-      </c>
+          <t>https://www.afyonanahaber.com.tr/son-dakika-ziraat-bankasindan-1-milyon-liralik-sms-alanlar-panige-kapildi-sistem-mi-hacklendi/amp</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Meydana Gelen Plastik</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>Meydana Gelen Plastik:292:body+summary+title</t>
-        </is>
-      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>Meydana Gelen Plastik Sultangazi İstanbul Türkiye</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>PLASTPET AMBALAJ - Plastik Polyester Çember Satış | Taylan Plastik</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>PLASTPET AMBALAJ - Plastik Polyester Çember Satış</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t>50.0 | 66.66666666666666</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="inlineStr">
-        <is>
-          <t>Sultangazi Ambalaj | Çuval İmalatı-Big Bag Çuval İmalatı-ikinci El Big Bag Çuval Alım Satımı-İskele Filesi İmalatı | Yön Ambalaj</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" s="2" t="n">
-        <v>214.18</v>
+        <v>82.75</v>
       </c>
       <c r="AB33" s="2" t="n">
         <v>32</v>
@@ -5159,27 +5370,27 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 10:36:00</t>
+          <t>2026-06-08 07:21:00</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>şüpheli işlem</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Kullanılmayan akaryakıt istasyonunda yangın</t>
+          <t>Ayyıldız Teams mesajı vatandaşı yatağından fırlattı! Ziraat Bankası’nda sabaha karşı 1 Milyon TL'lik SMS şoku! Müşteri hizmetlerine ulaşılamıyor... Kim bu Ayyıldız Teams?</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kullanılmayan akaryakıt istasyonunda yangın Tigris Haber</t>
+          <t>Ayyıldız Teams mesajı vatandaşı yatağından fırlattı! Ziraat Bankası’nda sabaha karşı 1 Milyon TL'lik SMS şoku! Müşteri hizmetlerine ulaşılamıyor... Kim bu Ayyıldız Teams? SuperHaber</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5189,22 +5400,22 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>akaryakıt istasyonu, istasyon</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>akaryakıt tesisi</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Batman'da kullanılmayan bir akaryakıt istasyonunda çıkan yangın, çevrede kısa süreli paniğe neden oldu. Batman'da kullanılmayan bir akaryakıt istasyonunda çıkan yangın, çevrede kısa süreli paniğe neden oldu. Batman'da kullanılmayan bir akaryakıt istasyonunda çıkan yangın, çevrede kısa süreli paniğe neden oldu. Kullanılmayan akaryakıt istasyonunda yangın 06 Haziran 2026 Cumartesi 13:36 Batman'da kullanılmayan bir akaryakıt istasyonunda çıkan yangın, çevrede kısa süreli paniğe neden oldu. TİGRİS HABER - Edinilen bilgilere göre, dün gece saatlerinde Gültepe Mahallesi'nde bulunan ve uzun süredir kullanılmayan bir akaryakıt istasyonunda henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine itfaiye, sağlık ve güvenlik ekipleri sevk edildi. Yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Yangında can kaybı ya da yaralanma yaşanmazken, iş yerinde maddi hasar meydana geldi. Yangının çıkış nedeninin belirlenmesi için ekipler tarafından inceleme başlatıldığı öğrenildi. İlk yorum yazan siz olun Bölge Haberleri TİGRİS HABER - Edinilen bilgilere göre, dün gece saatlerinde Gültepe Mahallesi'nde bulunan ve uzun süredir kullanılmayan bir akaryakıt istasyonunda henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine itfaiye, sağlık ve güvenlik ekipleri sevk edildi. Yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Yangında can kaybı ya da yaralanma yaşanmazken, iş yerinde maddi hasar meydana geldi. Yangının çıkış nedeninin belirlenmesi için ekipler tarafından inceleme başlatıldığı öğrenildi. Kullanılmayan akaryakıt istasyonunda yangın</t>
+          <t>Ziraat Bankası müşterileri, bu sabahın ilk ışıklarında cep telefonlarına gelen şok edici mesajlarla güne başladı. Sabaha karşı saat 04:00 civarında binlerce vatandaşa, "TELEGRAM @AYYILDIZTEAMS" iş yerinden 1 milyon TL'lik harcama yapıldığına dair şüpheli onay SMS'leri ulaştı. Şüpheli mesaj dalgasının ardından panikle bankaya vatandaşlar akın etti fakat Ziraat Bankası müşteri hizmetleri tamamen kilitlendi. Ziraat Bankası müşterileri, bu sabahın ilk ışıklarında cep telefonlarına gelen şok edici mesajlarla güne başladı. Sabaha karşı saat 04:00 civarında binlerce vatandaşa, "TELEGRAM @AYYILDIZTEAMS" iş yerinden 1 milyon TL'lik harcama yapıldığına dair şüpheli onay SMS'leri ulaştı. Şüpheli mesaj dalgasının ardından panikle bankaya vatandaşlar akın etti fakat Ziraat Bankası müşteri hizmetleri tamamen kilitlendi. Ziraat Bankası müşterileri, bu sabahın ilk ışıklarında cep telefonlarına gelen şok edici mesajlarla güne başladı. Sabaha karşı saat 04:00 civarında binlerce vatandaşa, "TELEGRAM @AYYILDIZTEAMS" iş yerinden 1 milyon TL'lik harcama yapıldığına dair şüpheli onay SMS'leri ulaştı. Şüpheli mesaj dalgasının ardından panikle bankaya vatandaşlar akın etti fakat Ziraat Bankası müşteri hizmetleri tamamen kilitlendi.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Kullanılmayan akaryakıt istasyonunda yangın Kullanılmayan akaryakıt istasyonunda yangın Tigris Haber Batman'da kullanılmayan bir akaryakıt istasyonunda çıkan yangın, çevrede kısa süreli paniğe neden oldu. Kullanılmayan akaryakıt istasyonunda yangın 06 Haziran 2026 Cumartesi 13:36 Batman'da kullanılmayan bir akaryakıt istasyonunda çıkan yangın, çevrede kısa süreli paniğe neden oldu. TİGRİS HABER - Edinilen bilgilere göre, dün gece saatlerinde Gültepe Mahallesi'nde bulunan ve uzun süredir kullanılmayan bir akaryakıt istasyonunda henüz belirlenemeyen nedenle yangın çıktı. İhbar üzerine olay yerine itfaiye, sağlık ve güvenlik ekipleri sevk edildi. Yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Yangında can kaybı ya da yaralanma yaşanmazken, iş yerinde maddi hasar meydana geldi. Yangının çıkış nedeninin belirlenmesi için ekipler tarafından inceleme başlatıldığı öğrenildi. İlk yorum yazan siz olun Bölge Haberleri TİGRİS HABER - Edinilen bilgilere göre, dün gece saatlerinde Gültepe Mahallesi'nde bulunan ve uzun süredir kullanılmayan bir akaryakıt istasyonunda henüz belirlenemeyen nedenle yangın çıktı. Kullanılmayan akaryakıt istasyonunda yangın</t>
+          <t>Ayyıldız Teams mesajı vatandaşı yatağından fırlattı! Ziraat Bankası’nda sabaha karşı 1 Milyon TL'lik SMS şoku! Müşteri hizmetlerine ulaşılamıyor... Kim bu Ayyıldız Teams? Ayyıldız Teams mesajı vatandaşı yatağından fırlattı! Ziraat Bankası’nda sabaha karşı 1 Milyon TL'lik SMS şoku! Müşteri hizmetlerine ulaşılamıyor... Kim bu Ayyıldız Teams? SuperHaber Ziraat Bankası müşterileri, bu sabahın ilk ışıklarında cep telefonlarına gelen şok edici mesajlarla güne başladı. Sabaha karşı saat 04:00 civarında binlerce vatandaşa, "TELEGRAM @AYYILDIZTEAMS" iş yerinden 1 milyon TL'lik harcama yapıldığına dair şüpheli onay SMS'leri ulaştı. Şüpheli mesaj dalgasının ardından panikle bankaya vatandaşlar akın etti fakat Ziraat Bankası müşteri hizmetleri tamamen kilitlendi.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -5214,27 +5425,19 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.tigrishaber.com/service/amp/kullanilmayan-akaryakit-istasyonunda-yangin-154780h.htm</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Batman</t>
-        </is>
-      </c>
+          <t>https://www.superhaber.com/ayyildiz-teams-ziraat-bankasi-mesaji-herkesi-korkuttu-ayyildiz-tim-telegram-grubu-1-milyon-tl-harcama-yapmaya-calisti-ayyildiz-teams-kim-galeri-577792</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>dün gece saatlerinde Gültepe Mahallesi</t>
-        </is>
-      </c>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr"/>
@@ -5248,7 +5451,7 @@
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="n">
-        <v>90.5</v>
+        <v>156.51</v>
       </c>
       <c r="AB34" s="2" t="n">
         <v>33</v>
@@ -5257,27 +5460,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06 09:16:14</t>
+          <t>2026-06-08 07:44:00</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>soruşturma</t>
+          <t>şüpheli işlem</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de iş insanı Rahmi Koç'un hastane açılışındaki sözlerine ilişkin soruşturma başlatıldı</t>
+          <t>Ziraat Bankası Müşterileri Dikkat! SMS Sistemi Hacklendi mi?</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de iş insanı Rahmi Koç'un hastane açılışındaki sözlerine ilişkin soruşturma başlatıldı Anadolu Ajansı</t>
+          <t>Ziraat Bankası Müşterileri Dikkat! SMS Sistemi Hacklendi mi? Özgün Kocaeli Gazetesi</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -5287,18 +5490,22 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>iş insanı</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de iş insanı Rahmi Koç'un hastane açılışındaki sözlerine ilişkin soruşturma başlatıldı Anadolu Ajansı</t>
+          <t>Ziraat Bankası Müşterileri Dikkat! SMS Sistemi Hacklendi mi? Özgün Kocaeli Gazetesi</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de iş insanı Rahmi Koç'un hastane açılışındaki sözlerine ilişkin soruşturma başlatıldı İzmir'de iş insanı Rahmi Koç'un hastane açılışındaki sözlerine ilişkin soruşturma başlatıldı Anadolu Ajansı İzmir'de iş insanı Rahmi Koç'un hastane açılışındaki sözlerine ilişkin soruşturma başlatıldı Anadolu Ajansı</t>
+          <t>Ziraat Bankası Müşterileri Dikkat! SMS Sistemi Hacklendi mi? Ziraat Bankası Müşterileri Dikkat! SMS Sistemi Hacklendi mi? Özgün Kocaeli Gazetesi Ziraat Bankası Müşterileri Dikkat! SMS Sistemi Hacklendi mi?</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5308,14 +5515,10 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOT0I5b1RXUko2YVZxazg1UFZ1ZjlQNnBWZGZmS2RacUF2VDduRFNQR1JvWkFQLXBIMlMyYU9vNFlmem5SRFZCVk9EaHJiZXNIQTE1a0Y4ODlqY05mY3BIYnRDLV9PZl82N0hGWVo1WEc1ZF9TN0tPX08zNEpGeHZvTlM0LVlUZ3llXzZOa1NFeW40VXc0dnFra1ZZX3JXQ3B5SVdFSDZudEFJQl8zcGk0MTIxUHpVY2IyVXJIb3ZseFhFejI4VWhLcXdn?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNcEFtSWU5azBvd3prbk00Z18yWVBJaHJKYWRqR3JHc0xQZzlRQU1zcWloMmNYaGFpUHFDckRnUzNGbi1UNXZ4cVRjOEsyUWV1YUJpek1IN0tOR2xvV0tjdlFmRXM0VUQxNGFIXy1PSW5yVlVNWGFVRW5TQmJ4QkJpUEZSNWVPU2pyOV9zbEdlY2xoVXhy0gGaAUFVX3lxTFBKV0lhcUlKaFZDRGtFZnA2YWctaWlNbU45cW5ELUh5SmhZNnpiNnhpdEpZdXhyVHp4UnVNZ05fSnJMSkFUeWZKUXRUR09EVkd0NFdud05lLTZwaS1raklPNzFZLVQ3U3pWLXZfajByQjR0ZE5GVUxkNkNwWWlRRGxISEctLUVEeG0yVGxsUlA5TERRZHBvUGUyV1E?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
@@ -5324,7 +5527,7 @@
       <c r="S35" s="2" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr"/>
@@ -5338,14 +5541,308 @@
       <c r="Y35" s="2" t="inlineStr"/>
       <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" s="2" t="n">
-        <v>99.81999999999999</v>
+        <v>57.58</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>34</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 08:01:43</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>şüpheli işlem</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası'nda 1 Milyonluk Sahte İşlem Mesajları Vatandaşı Panikletti!</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası'nda 1 Milyonluk Sahte İşlem Mesajları Vatandaşı Panikletti! haber.com</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Türkiye'nin en büyük kamu bankalarından Ziraat Bankası müşterileri, dün gece yarısından itibaren "Telegram Ayyıldız Teams" adlı iş yerinden 1.000.000 TL tutarında harcama yapılmaya çalışıldığına dair onay şifresi içeren SMS'ler Türkiye'nin en büyük kamu bankalarından Ziraat Bankası müşterileri, dün gece yarısından itibaren "Telegram Ayyıldız Teams" adlı iş yerinden 1.000.000 TL tutarında harcama yapılmaya çalışıldığına dair onay şifresi içeren SMS'ler Türkiye’nin en büyük kamu bankalarından Ziraat Bankası müşterileri, 8 Haziran 2026 Pazartesi günü sabah saatlerine bir siber kriz paniğiyle uyandı. Gece yarısından itibaren binlerce vatandaşın telefonuna, "Telegram Ayyıldız Teams" adlı iş yerinden 1.000.000 TL tutarında harcama yapılmaya çalışıldığına dair onay şifresi içeren SMS’ler ulaştı. 1 Milyon TL'lik SMS'ler Gece saat 03:00 ile sabah 08:30 arasında telefonlarına gelen mesajlarla uyanan vatandaşlar, hesaplarının hacklendiğini düşünerek büyük panik yaşadı. Gelen mesajların tamamında işlem yeri olarak "Ate te ayyıldız@telegram" veya "Telegram @ayyıldızteams" ibarelerinin yer alması ve harcama tutarının standart olarak 1.000.000 TL olması dikkat çekti. Bankadan İlk Açıklama Vatandaşların "Kişisel veriler sızdı mı?" soruları üzerine banka kaynaklarından ve siber güvenlik departmanlarından gelen ilk gayriresmi bilgiler, durumun teknik bir aksaklıktan kaynaklandığını ortaya koydu: Banka sistemlerine yönelik bir saldırı veya finansal veri sızıntısı bulunmuyor. SMS’lerin, doğrudan Ziraat Bankası altyapısından ziyade Bankalararası Kart Merkezi (BKM) üzerinden tetiklendiği belirlendi. Yapılan incelemelerde herhangi bir hesaptan para çekilmesi veya provizyon durumu tespit edilmedi. Teknik ekipler, sahte SMS trafiğini engellemek için acil bir filtreleme çalışması başlattı. Bankaya Tepkiler Büyüyor Olayın ardından binlerce vatandaşın eş zamanlı olarak Ziraat Bankası Kayıp/Çalıntı ve Şüpheli İşlem Hattı’nı araması, çağrı merkezinin tamamen kilitlenmesine neden oldu. Müşteri temsilcilerine ulaşamayan ve bekleme sürelerinin 15 dakikayı bulduğunu belirten kullanıcılar, bankanın kriz anındaki yetersizliğine sert tepki gösterdi. Vatandaşlar, "Olası bir siber saldırıda bankanın muhatap sunamaması güvensizlik yarattı" diyerek sorumluluğun bankaya ait olduğunu vurguladı. Buca Belediye Başkanı Görkem Duman Görevden.. Avrasya Tüneli'nde Kaza: Trafik Kısa Süreliğine.. Buca Belediye Başkanı Görkem Duman Görevden.. Avrasya Tüneli'nde Kaza: Trafik Kısa Süreliğine.. Ana Sayfa Fo</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Ziraat Bankası'nda 1 Milyonluk Sahte İşlem Mesajları Vatandaşı Panikletti! Ziraat Bankası'nda 1 Milyonluk Sahte İşlem Mesajları Vatandaşı Panikletti! haber.com Türkiye'nin en büyük kamu bankalarından Ziraat Bankası müşterileri, dün gece yarısından itibaren "Telegram Ayyıldız Teams" adlı iş yerinden 1.000.000 TL tutarında harcama yapılmaya çalışıldığına dair onay şifresi içeren SMS'ler Türkiye'nin en büyük kamu bankalarından Ziraat Bankası müşterileri, dün gece yarısından itibaren "Telegram Ayyıldız Teams" adlı iş yerinden 1.000.000 TL tutarında harcama yapılmaya çalışıldığına dair onay şifresi içeren SMS'ler Türkiye’nin en büyük kamu bankalarından Ziraat Bankası müşterileri, 8 Haziran 2026 Pazartesi günü sabah saatlerine bir siber kriz paniğiyle uyandı. Gece yarısından itibaren binlerce vatandaşın telefonuna, "Telegram Ayyıldız Teams" adlı iş yerinden 1.000.000 TL tutarında harcama yapılmaya çalışıldığına dair onay şifresi içeren SMS’ler ulaştı. 1 Milyon TL'lik SMS'ler Gece saat 03:00 ile sabah 08:30 arasında telefonlarına gelen mesajlarla uyanan vatandaşlar, hesaplarının hacklendiğini düşünerek büyük panik yaşadı. Gelen mesajların tamamında işlem yeri olarak "Ate te ayyıldız@telegram" veya "Telegram @ayyıldızteams" ibarelerinin yer alması ve harcama tutarının standart olarak 1.000.000 TL olması dikkat çekti. Bankadan İlk Açıklama Vatandaşların "Kişisel veriler sızdı mı?" soruları üzerine banka kaynaklarından ve siber güvenlik departmanlarından gelen ilk gayriresmi bilgiler, durumun teknik bir aksaklıktan kaynaklandığını ortaya koydu: Banka sistemlerine yönelik bir saldırı veya finansal veri sızıntısı bulunmuyor. SMS’lerin, doğrudan Ziraat Bankası altyapısından ziyade Bankalararası Kart Merkezi (BKM) üzerinden tetiklendiği belirlendi. Yapılan incelemelerde herhangi bir hesaptan para çekilmesi veya provizyon durumu tespit edilmedi. Teknik ekipler, sahte SMS trafiğini engellemek için acil bir filtreleme çalışması başlattı. Bankaya Tepkiler Büyüyor Olayın ardından binlerce vatandaşın eş zamanlı olarak Ziraat Bankası Kayıp/Çalıntı ve Şüpheli İşlem Hattı’nı araması, çağrı merkezinin tamamen kilitlenmesine neden oldu. Müşteri temsilcilerine ulaşamayan ve bekleme sürelerinin 15 dakikayı bulduğunu belirten kullanıcılar, bankanın kriz anındaki yetersizliğine sert tepki gösterdi. Vatandaşlar, "Olası bir siber saldırıda bankanın muhatap sunamaması güvensizlik yarattı" diyerek sorumluluğun bankaya ait olduğunu vurguladı. Buca Belediye Başkanı Görkem Duman Görevden.. Avrasya Tüneli'nde Kaza: Trafik Kısa Süreliğine..</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.haber.com/3-sayfa/ziraat-bankasi-nda-1-milyonluk-sahte-islem-mesajlari-vatandasi-panikletti-20737</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="AB36" s="2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 06:43:01</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>gözaltı</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı Yeni Şafak</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul merkezli 6 ilde düzenlenen sahte para operasyonunda 9 şüpheli gözaltına alındı. İstanbul merkezli 6 ilde düzenlenen sahte para operasyonunda 9 şüpheli gözaltına alındı. İstanbul merkezli 6 ilde düzenlenen sahte para operasyonunda 9 şüpheli gözaltına alındı. Dolandırıcılar 102 bin 750 dolar haksız kazanç elde etti. GÜNDEM Filyos Çayı'na düşen CHP İl Başkan Yardımcısı Mustafa Erten’in cansız bedeni bulundu GÜNDEM Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı GÜNDEM Avrasya Tüneli'nde meydana gelen kaza sebebiyle tünel trafiğe kapatıldı GÜNDEM Özgür Özel 'baba ocağı' dediği partisine veda etmeye hazırlanıyor GÜNDEM Yolsuzluk soruşturmasında tutuklanmıştı: CHP'li Buca Belediye Başkanı Görkem Duman görevden uzaklaştırıldı Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı İstanbul merkezli 6 ilde düzenlenen sahte para operasyonunda 9 şüpheli gözaltına alındı. İstanbul Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğü ekipleri, İstanbul Cumhuriyet Başsavcılığı koordinesinde yaptığı çalışmada, 50 dolarlık sahte banknotları banka ATM'leri aracılığıyla sisteme dahil edildiğini ve sonrasında farklı banka ATM'lerinden dövizin Türk lirası olarak çekilerek haksız kazanç sağlandığını belirledi. Bu yöntemle 102 bin 750 dolar haksız kazanç elde ettikleri tespit edilen zanlıların yakalanması için İstanbul, Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da operasyon düzenlendi. Operasyonda yakalanan 9 şüpheli, işlemleri için emniyete götürüldü.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı Yeni Şafak İstanbul merkezli 6 ilde düzenlenen sahte para operasyonunda 9 şüpheli gözaltına alındı. Dolandırıcılar 102 bin 750 dolar haksız kazanç elde etti. GÜNDEM Filyos Çayı'na düşen CHP İl Başkan Yardımcısı Mustafa Erten’in cansız bedeni bulundu GÜNDEM Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı GÜNDEM Avrasya Tüneli'nde meydana gelen kaza sebebiyle tünel trafiğe kapatıldı GÜNDEM Özgür Özel 'baba ocağı' dediği partisine veda etmeye hazırlanıyor GÜNDEM Yolsuzluk soruşturmasında tutuklanmıştı: CHP'li Buca Belediye Başkanı Görkem Duman görevden uzaklaştırıldı Banka ATM’lerine sahte dolar yükleyen şebeke çökertildi: 9 gözaltı İstanbul merkezli 6 ilde düzenlenen sahte para operasyonunda 9 şüpheli gözaltına alındı. İstanbul Emniyet Müdürlüğü Siber Suçlarla Mücadele Şube Müdürlüğü ekipleri, İstanbul Cumhuriyet Başsavcılığı koordinesinde yaptığı çalışmada, 50 dolarlık sahte banknotları banka ATM'leri aracılığıyla sisteme dahil edildiğini ve sonrasında farklı banka ATM'lerinden dövizin Türk lirası olarak çekilerek haksız kazanç sağlandığını belirledi. Bu yöntemle 102 bin 750 dolar haksız kazanç elde ettikleri tespit edilen zanlıların yakalanması için İstanbul, Artvin, Bursa, Edirne, Samsun ve Diyarbakır'da operasyon düzenlendi. Operasyonda yakalanan 9 şüpheli, işlemleri için emniyete götürüldü.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yenisafak.com/amphtml/gundem/banka-atmlerine-sahte-dolar-yukleyen-sebeke-cokertildi-9-gozalti-4830600</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır | İstanbul</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AB37" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07 20:42:00</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>gözaltı</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik gözaltında…</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik gözaltında… Enerji Günlüğü</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>enerji</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Enerji Günlüğü - Temerrüde düşen Kontrolmatik’in kupon (faiz) ödemelerini yapmaması üzerine Şirket’in tahvilleri Borçlanma Araçları Piyasası Gözaltı Pazarı’na alındı. Enerji Günlüğü - Temerrüde düşen Kontrolmatik’in kupon (faiz) ödemelerini yapmaması üzerine Şirket’in tahvilleri Borçlanma Araçları Piyasası Gözaltı Pazarı’na alındı. Enerji Günlüğü - Temerrüde düşen Kontrolmatik’in kupon (faiz) ödemelerini yapmaması üzerine Şirket’in tahvilleri Borçlanma Araçları Piyasası Gözaltı Pazarı’na alındı. HABERLER ELEKTRİK Kontrolmatik tahvilleri gözaltı pazarına düştü Temerrüde düşen Kontrolmatik’in kupon (faiz) ödemelerini yapmaması üzerine Şirket’in tahvilleri Borçlanma Araçları Piyasası Gözaltı Pazarı’na alındı. 07 Haziran 2026 Pazar 23:42 Enerji Günlüğü - Temerrüde düşen ve olağan genel kurul için gerekli çoğunluğu sağlayamayan Kontrolmatik ’le ilgili yeni gelişme… Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ tarafından nitelikli yatırımcılara ihraç edilen TRSKNTR32719 ve TRFKNTR92611 ISIN kodlu borçlanma araçlarının 05/06/2026 tarihli kupon ödemesi yapılmadı. Bunun üzerine Kotasyon Yönergesi'nin 29. maddesinin birinci fıkrasının (e) bendi ve dördüncü fıkrası çerçevesinde söz konusu borçlanma araçlarının Borçlanma Araçları Piyasası Gözaltı Pazarı'na alınmasına karar verildi. Aynı maddenin sekizinci fıkrası kapsamında kağıtların işlem sırası 08/06/2026 tarihinde kapalı kalacak, 09/06/2026 tarihinden itibaren yeniden işleme açılacak. Enerji Günlüğü - Temerrüde düşen ve olağan genel kurul için gerekli çoğunluğu sağlayamayan Kontrolmatik ’le ilgili yeni gelişme… Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ tarafından nitelikli yatırımcılara ihraç edilen TRSKNTR32719 ve TRFKNTR92611 ISIN kodlu borçlanma araçlarının 05/06/2026 tarihli kupon ödemesi yapılmadı. Bunun üzerine Kotasyon Yönergesi'nin 29. maddesinin birinci fıkrasının (e) bendi ve dördüncü fıkrası çerçevesinde söz konusu borçlanma araçlarının Borçlanma Araçları Piyasası Gözaltı Pazarı'na alınmasına karar verildi. Aynı maddenin sekizinci fıkrası kapsamında kağıtların işlem sırası 08/06/2026 tarihinde kapalı kalacak, 09/06/2026 tarihinden itibaren yeniden işleme açılacak. Kontrolmatik tahvilleri gözaltı pazarına düştü Temerrüde düşen Kontrolmatik’in kupon (faiz) ödemelerini yapmaması üzerine Şirket’in tahvilleri Borçlanma Araçları Piyasası Gözaltı Pazarı’na alındı. Enerji Günlüğü - Temerrüde düşen ve olağan genel kurul için gerekli çoğunluğu sağlayamayan Kontrolmatik ’le ilgili yeni gelişme… Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ tarafından nitelikli yatırımcılara ihraç edilen TRSKNTR32719 ve TRFKNTR92611 ISIN kodlu borçlanma araçlarının 05/06/2026 tarihli kupon ödemesi yapılmadı. Bunun üzerine Kotasyon Yönergesi'nin 29. maddesinin birinci fıkrasının (e) bendi ve dördüncü fıkrası çerçevesinde söz konusu borçlanma araçlarının Borçlanma Araçları Piyasası Gözaltı Pazarı'na alınmasına karar verildi. Aynı maddenin sekizinci fıkrası kapsamında kağıtların işlem sırası 08/06/2026 tarihinde kapalı kalacak, 09/06/2026 tarihinden itibaren yeniden işleme açılacak.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik gözaltında… Kontrolmatik gözaltında… Enerji Günlüğü Enerji Günlüğü - Temerrüde düşen Kontrolmatik’in kupon (faiz) ödemelerini yapmaması üzerine Şirket’in tahvilleri Borçlanma Araçları Piyasası Gözaltı Pazarı’na alındı. HABERLER ELEKTRİK Kontrolmatik tahvilleri gözaltı pazarına düştü Temerrüde düşen Kontrolmatik’in kupon (faiz) ödemelerini yapmaması üzerine Şirket’in tahvilleri Borçlanma Araçları Piyasası Gözaltı Pazarı’na alındı. 07 Haziran 2026 Pazar 23:42 Enerji Günlüğü - Temerrüde düşen ve olağan genel kurul için gerekli çoğunluğu sağlayamayan Kontrolmatik ’le ilgili yeni gelişme… Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ tarafından nitelikli yatırımcılara ihraç edilen TRSKNTR32719 ve TRFKNTR92611 ISIN kodlu borçlanma araçlarının 05/06/2026 tarihli kupon ödemesi yapılmadı. Bunun üzerine Kotasyon Yönergesi'nin 29. maddesinin birinci fıkrasının (e) bendi ve dördüncü fıkrası çerçevesinde söz konusu borçlanma araçlarının Borçlanma Araçları Piyasası Gözaltı Pazarı'na alınmasına karar verildi. Aynı maddenin sekizinci fıkrası kapsamında kağıtların işlem sırası 08/06/2026 tarihinde kapalı kalacak, 09/06/2026 tarihinden itibaren yeniden işleme açılacak. Enerji Günlüğü - Temerrüde düşen ve olağan genel kurul için gerekli çoğunluğu sağlayamayan Kontrolmatik ’le ilgili yeni gelişme… Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ tarafından nitelikli yatırımcılara ihraç edilen TRSKNTR32719 ve TRFKNTR92611 ISIN kodlu borçlanma araçlarının 05/06/2026 tarihli kupon ödemesi yapılmadı. Kontrolmatik tahvilleri gözaltı pazarına düştü Temerrüde düşen Kontrolmatik’in kupon (faiz) ödemelerini yapmaması üzerine Şirket’in tahvilleri Borçlanma Araçları Piyasası Gözaltı Pazarı’na alındı.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enerjigunlugu.net/service/amp/kontrolmatik-tahvilleri-gozalti-pazarina-dustu-68422h.htm</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ:60:body | Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ:raw_legal</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik Teknoloji Enerji ve Mühendislik AŞ Türkiye</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik Teknoloji</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolmatik Teknoloji</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="AB38" s="2" t="n">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB35"/>
+  <autoFilter ref="A1:AB38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -5381,6 +5878,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,22 +512,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:26:08</t>
+          <t>2026-06-09 11:11:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MASAK Tek Tek İnceledi, Rakam Dudak Uçuklattı</t>
+          <t>Gaziantep Tekstil Fabrikası Yangını</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MASAK Tek Tek İnceledi, Rakam Dudak Uçuklattı Bodrum Olay Gazetesi</t>
+          <t>Gaziantep Tekstil Fabrikası Yangını | Son Dakika Gelişmeleri HaberGo</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -535,13 +535,13 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Muğla</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Gaziantep Tekstil</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -552,22 +552,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 05:35:00</t>
+          <t>2026-06-09 19:40:34</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını alevler gökyüzünü kapladı!</t>
+          <t>Europol: Kosova Merkezli Suç Ağı Çökertildi, 80 Milyon Euroluk Mal Varlığına El Konuldu</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını alevler gökyüzünü kapladı! Gaziantep Oluşum Gazetesi</t>
+          <t>Europol: Kosova Merkezli Suç Ağı Çökertildi, 80 Milyon Euroluk Mal Varlığına El Konuldu Kosovahaber.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -575,16 +575,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Gaziantep</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Şahinbey</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
@@ -596,7 +588,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 19:02:00</t>
+          <t>2026-06-09 15:07:33</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -606,12 +598,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Bir Mobilya Fabrikasında Çıkan Yangında İtfaiye Eri Şehit Oldu, 1 Kişi Hastaneye Kaldırıldı.</t>
+          <t>Çorlu'da Market Deposunda Yangın</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Bir Mobilya Fabrikasında Çıkan Yangında İtfaiye Eri Şehit Oldu, 1 Kişi Hastaneye Kaldırıldı. Mersin Haber</t>
+          <t>Çorlu'da Market Deposunda Yangın SonDakika</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -621,49 +613,41 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
+          <t>Tekirdağ</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Karatay</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Bir Mobilya</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Burda Mobilya</t>
-        </is>
-      </c>
+          <t>Çorlu</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:58:50</t>
+          <t>2026-06-09 10:20:01</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Devlet Bankası'nın 1 Temmuz 2026'dan itibaren geçerli olacak yeni organizasyon yapısı.</t>
+          <t>Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Devlet Bankası'nın 1 Temmuz 2026'dan itibaren geçerli olacak yeni organizasyon yapısı. Vietnam.vn</t>
+          <t>Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -671,35 +655,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Düzce | Gaziantep | İstanbul | Karaman</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Edremit | Gebze | Tarsus</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Molhan Tekstil</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:42:59</t>
+          <t>2026-06-09 13:32:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak?</t>
+          <t>İran'da 'vatan hainliği' suçlamasıyla 200'den fazla kişinin mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak? Halk TV</t>
+          <t>İran'da 'vatan hainliği' suçlamasıyla 200'den fazla kişinin mal varlığına el konuldu Ensonhaber</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -709,41 +705,33 @@
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Can Holding</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Can Holding A.Ş</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:45:00</t>
+          <t>2026-06-09 13:22:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Konya’da korkutan fabrika yangını: Alevler şehri dumana boğdu! Ekipler seferber oldu</t>
+          <t>İstanbul merkezli 24 ilde büyük operasyon! 350 milyon liralık mal varlığına da el konuldu</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Konya’da korkutan fabrika yangını: Alevler şehri dumana boğdu! Ekipler seferber oldu Konya Yenigün Gazetesi</t>
+          <t>İstanbul merkezli 24 ilde büyük operasyon! 350 milyon liralık mal varlığına da el konuldu Gazete Vatan</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -753,7 +741,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -768,22 +756,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 09:31:46</t>
+          <t>2026-06-09 16:28:12</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu</t>
+          <t>EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu tv42haber.com</t>
+          <t>EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu - beş kişi tutuklandı KoSSev</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -791,16 +779,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Diyarbakır | Isparta | Karaman | Konya | Manisa</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Beyşehir</t>
-        </is>
-      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
@@ -812,22 +792,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:50:00</t>
+          <t>2026-06-09 09:02:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı</t>
+          <t>Yasa dışı bahis baronlarına Bursa’dan operasyon: 47 kişinin tüm mal varlığına el konuldu!</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Mersin Haber</t>
+          <t>Yasa dışı bahis baronlarına Bursa’dan operasyon: 47 kişinin tüm mal varlığına el konuldu! bursatv.com.tr</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -837,14 +817,10 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Konya | Mersin | İstanbul | Malatya</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Silivri | Karatay | Darende</t>
-        </is>
-      </c>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
@@ -856,22 +832,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 20:27:58</t>
+          <t>2026-06-09 18:33:53</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Yangında depo ve garaj kullanılamaz hale geldi</t>
+          <t>72 yaşındaki tatlıcıdan tüyler ürpertici tarikat iddiası: '7 yıldır evime giremiyorum, mal varlığıma el koydular!</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Yangında depo ve garaj kullanılamaz hale geldi Aksaray Yenigün Gazetesi</t>
+          <t>72 yaşındaki tatlıcıdan tüyler ürpertici tarikat iddiası: '7 yıldır evime giremiyorum, mal varlığıma el koydular! Saray Medya</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -892,7 +868,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:44</t>
+          <t>2026-06-09 10:17:02</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -902,12 +878,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Beyşehir Kurucuova’da Garaj ve Depoda Yangın Paniği</t>
+          <t>Konya'da Fabrika Yangını: İtfaiye Eri Mehmet Tekeli Şehit Oldu</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Beyşehir Kurucuova’da Garaj ve Depoda Yangın Paniği bgrt.com.tr</t>
+          <t>Konya'da Fabrika Yangını: İtfaiye Eri Mehmet Tekeli Şehit Oldu SonDakika</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -915,8 +891,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Konya</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Karatay</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
@@ -928,7 +912,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 07:26:00</t>
+          <t>2026-06-10 01:30:45</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -938,12 +922,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını: Ekiplerin müdahalesi sürüyor Olay yerine çok sayıda ekip sevk edildi</t>
+          <t>Bir ağaç işleme şirketinin fabrikasında 17.000 m²'den fazla alanı yok eden yangının sebebi araştırılıyor.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını: Ekiplerin müdahalesi sürüyor Olay yerine çok sayıda ekip sevk edildi Habertürk</t>
+          <t>Bir ağaç işleme şirketinin fabrikasında 17.000 m²'den fazla alanı yok eden yangının sebebi araştırılıyor. Vietnam.vn</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -951,11 +935,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Gaziantep</t>
-        </is>
-      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
@@ -968,7 +948,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 08:23:00</t>
+          <t>2026-06-09 20:48:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -978,12 +958,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor</t>
+          <t>Gaziantep'te 14 saat süren fabrika yangını söndürüldü</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Mersin Haber</t>
+          <t>Gaziantep'te 14 saat süren fabrika yangını söndürüldü Referans Gazetesi</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -993,30 +973,22 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep | Mersin | Şanlıurfa</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Organize Sanayi</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Gaziantep Organize Sanayi Bölgesi</t>
-        </is>
-      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:15:22</t>
+          <t>2026-06-10 01:55:48</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1026,12 +998,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Konya’da yatak fabrikasında yangın! Kompresör patladı: İtfaiye eri yaralandı</t>
+          <t>Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Konya’da yatak fabrikasında yangın! Kompresör patladı: İtfaiye eri yaralandı | YEREL HABERLER GZT</t>
+          <t>Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti. Vietnam.vn</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1039,11 +1011,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Konya</t>
-        </is>
-      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1056,7 +1024,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:00</t>
+          <t>2026-06-09 11:13:48</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1066,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor</t>
+          <t>Fabrika yangını: Ekiplerin müdahalesi sürüyor</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor Mersin Haber</t>
+          <t>Fabrika yangını: Ekiplerin müdahalesi sürüyor urfabaraj.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1079,16 +1047,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Mersin | Gaziantep</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Şahinbey</t>
-        </is>
-      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
@@ -1100,7 +1060,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00:00</t>
+          <t>2026-06-09 18:46:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1110,12 +1070,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fabrika Yangını: İtfaiye Personeli Şehit Oldu</t>
+          <t>Zonguldak'ta fabrikada yangın var!</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fabrika Yangını: İtfaiye Personeli Şehit Oldu Kırşehir Çiğdem</t>
+          <t>Zonguldak'ta fabrikada yangın var! YENİ ADIM GAZETESİ</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1123,7 +1083,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Zonguldak</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1136,22 +1100,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 06:49:00</t>
+          <t>2026-06-09 21:10:00</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep 5. OSB'de Korkutan Yangın: Dev Tekstil Fabrikası Alevlere Teslim Oldu!</t>
+          <t>Şanlıurfa'da MASAK İnceledi, Oyun Bozuldu: 8 Milyar Liralık Para Hacmi Ortaya Çıktı</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep 5. OSB'de Korkutan Yangın: Dev Tekstil Fabrikası Alevlere Teslim Oldu! Olay Medya</t>
+          <t>Şanlıurfa'da MASAK İnceledi, Oyun Bozuldu: 8 Milyar Liralık Para Hacmi Ortaya Çıktı Urfanatik</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1159,7 +1123,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Şanlıurfa</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1172,22 +1140,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 07:06:00</t>
+          <t>2026-06-10 07:30:00</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep’te tekstil fabrikasında dev yangın! Çok sayıda sağlık v ...</t>
+          <t>Bursa'da 12 yıllık süreç sona erdi! Ünlü tatlı firmasının iflas dosyası kapatıldı</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep’te tekstil fabrikasında dev yangın! Çok sayıda sağlık v ... Referans Gazetesi</t>
+          <t>Bursa'da 12 yıllık süreç sona erdi! Ünlü tatlı firmasının iflas dosyası kapatıldı Bursada Bugün</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1197,10 +1165,14 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Nilüfer</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
@@ -1212,22 +1184,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:12:00</t>
+          <t>2026-06-09 11:25:54</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı</t>
+          <t>Türk otomotiv devi Güçlü Zirve iflas etti: Yıllardır sektöre yön veriyordu</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı Konya Bakış</t>
+          <t>Türk otomotiv devi Güçlü Zirve iflas etti: Yıllardır sektöre yön veriyordu Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1237,14 +1209,10 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Karatay</t>
-        </is>
-      </c>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
@@ -1256,22 +1224,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 13:32:00</t>
+          <t>2026-06-09 09:03:28</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Konya’da fabrikada yangın! Siyah dumanlar gökyüzünü kapladı</t>
+          <t>Almanya'nın önde gelen araç kiralama şirketi Nextmove iflas etti</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Konya’da fabrikada yangın! Siyah dumanlar gökyüzünü kapladı yenikonya.com.tr</t>
+          <t>Almanya'nın önde gelen araç kiralama şirketi Nextmove iflas etti Patronlar Dünyası</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1279,11 +1247,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Konya</t>
-        </is>
-      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1296,7 +1260,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 06:13:43</t>
+          <t>2026-06-10 02:51:00</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1306,12 +1270,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da dev şirketin konkordato sürecinde kritik aşama! Alacaklılar toplanıyor...</t>
+          <t>Kocası tarafından aldatılan Dieu (Quynh Chau), şirketinin iflas etme riskiyle de karşı karşıya kalır.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da dev şirketin konkordato sürecinde kritik aşama! Alacaklılar toplanıyor... Bursa Hakimiyet</t>
+          <t>Kocası tarafından aldatılan Dieu (Quynh Chau), şirketinin iflas etme riskiyle de karşı karşıya kalır. Vietnam.vn</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1319,11 +1283,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1336,7 +1296,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 05:55:46</t>
+          <t>2026-06-09 09:31:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1346,12 +1306,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da otomotiv ve yedek parça sektöründe faaliyet gösteren dev şirket iflas etti</t>
+          <t>100 ülkeye ihracat yapan alüminyum devi şirket iflas etti</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da otomotiv ve yedek parça sektöründe faaliyet gösteren dev şirket iflas etti | EKONOMİ HABERLERİ GZT</t>
+          <t>100 ülkeye ihracat yapan alüminyum devi şirket iflas etti emlak 365</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1361,22 +1321,30 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Antalya</t>
+          <t>Ankara</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group İnşaat Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Patrop Group</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 09:29:00</t>
+          <t>2026-06-09 20:04:02</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1386,12 +1354,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>100'den fazla ülkeye ihracat yapıyordu: Türk sanayi devi iflas etti</t>
+          <t>Shtip'te tekstil işçileri, iflas eden Alman-Bulgar şirketlerinden kendilerine ödenmesi gereken maaşları talep ederek protesto gösterisi düzenledi.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>100'den fazla ülkeye ihracat yapıyordu: Türk sanayi devi iflas etti Cumhuriyet</t>
+          <t>Shtip'te tekstil işçileri, iflas eden Alman-Bulgar şirketlerinden kendilerine ödenmesi gereken maaşları talep ederek protesto gösterisi düzenledi. Слободен печат</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1401,26 +1369,18 @@
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>AĞI Patrop Group İnşaat Sanayi ve Ticaret A.Ş</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Patrop Group</t>
-        </is>
-      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 11:23:53</t>
+          <t>2026-06-10 06:33:00</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1430,12 +1390,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bursa'nın 30 yıllık tekstil devi resmen iflas etti! Mahkeme kararı ilan edildi...</t>
+          <t>İzmir'de dev tarım firmasına kötü haber! Mahkeme konkordato talebini reddetti!</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Bursa'nın 30 yıllık tekstil devi resmen iflas etti! Mahkeme kararı ilan edildi... Bursa Hakimiyet</t>
+          <t>İzmir'de dev tarım firmasına kötü haber! Mahkeme konkordato talebini reddetti! Son Mühür</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1445,22 +1405,30 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Tusem Tarım Gıda Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Tusem Tarım</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 07:39:00</t>
+          <t>2026-06-09 10:58:00</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1470,12 +1438,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Denizli tekstil sektöründe konkordato depremi! Dev firmaya mahkemeden kötü haber</t>
+          <t>Matbaa ve Tekstil Sektöründe Tasfiye: Silindir Çeşitleri ve Hurda Bakır Fiyatları</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Denizli tekstil sektöründe konkordato depremi! Dev firmaya mahkemeden kötü haber gazetesehir.com</t>
+          <t>Matbaa ve Tekstil Sektöründe Tasfiye: Silindir Çeşitleri ve Hurda Bakır Fiyatları HaberTS</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1483,32 +1451,24 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Denizli</t>
-        </is>
-      </c>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Çağdaş Dokuma Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>ÇAĞDAŞ DOKUMA SAN. VE TİC.LTD.ŞTİ</t>
-        </is>
-      </c>
+          <t>Matbaa ve Tekstil</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 14:56:00</t>
+          <t>2026-06-09 18:56:00</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1518,12 +1478,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA!! Gaziantep'te DEV firma konkordato ilan etti!</t>
+          <t>Mühür ve Ambalaj Sanayisinde Tasfiye: Saf Kurşun Arzı ve Net Kurşun Hurda Fiyatı</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA!! Gaziantep'te DEV firma konkordato ilan etti! Gaziantep Oluşum Gazetesi</t>
+          <t>Mühür ve Ambalaj Sanayisinde Tasfiye: Saf Kurşun Arzı ve Net Kurşun Hurda Fiyatı yeniistiklal.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1533,22 +1493,34 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>İstanbul | İzmir</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Esenyurt</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Mühür ve Ambalaj</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Gürsa Ambalaj A.Ş.- İSTANBUL ESENYURT</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 09:13:00</t>
+          <t>2026-06-09 14:02:12</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1558,12 +1530,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli'deki üç şirket iflas etmek üzere!</t>
+          <t>Manisa'daki ünlü zeytin firmasının konkordato talebine ret</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Kocaeli'deki üç şirket iflas etmek üzere! Nokta Gazetesi</t>
+          <t>Manisa'daki ünlü zeytin firmasının konkordato talebine ret Tek Referans</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1571,11 +1543,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Kocaeli</t>
-        </is>
-      </c>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1588,22 +1556,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 08:52:00</t>
+          <t>2026-06-09 14:25:13</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI</t>
+          <t>Denizli Tekstilinde Şok Karar! Mahkeme Konkordatoyu Reddetti</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Kendisini bankacı gibi tanıttı MİLYONLUK CEZA ALDI Sakarya Yenihaber</t>
+          <t>Denizli Tekstilinde Şok Karar! Mahkeme Konkordatoyu Reddetti DENİZLİ24HABER</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1611,11 +1579,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Sakarya</t>
-        </is>
-      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1628,7 +1592,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 09:06:00</t>
+          <t>2026-06-09 11:06:00</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1638,12 +1602,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>100’ü aşkın ülkeye ihracat yapan şirket hakkında iflas kararı</t>
+          <t>Kocaeli'de 3 Şirketin Konkordatosu Uzatıldı</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>100’ü aşkın ülkeye ihracat yapan şirket hakkında iflas kararı Gazete Oksijen</t>
+          <t>Kocaeli'de 3 Şirketin Konkordatosu Uzatıldı Kocaeli TV</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1651,8 +1615,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Kocaeli | İstanbul</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Gebze</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
@@ -1664,22 +1636,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:22:00</t>
+          <t>2026-06-09 17:02:00</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Doğalgaz ve enerji devinden iflas başvurusu</t>
+          <t>Bolu Caddesi’nde bankada dolandırıcılık girişimi polis tarafından durduruldu</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Doğalgaz ve enerji devinden iflas başvurusu Yıldırım Gazetesi</t>
+          <t>Bolu Caddesi’nde bankada dolandırıcılık girişimi polis tarafından durduruldu Bolu Olay</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1687,8 +1659,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Merkez</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
@@ -1700,22 +1680,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:18:48</t>
+          <t>2026-06-10 07:44:56</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Yakıt fiyatlarındaki artış nedeniyle birçok düşük maliyetli havayolu şirketi iflas edecek.</t>
+          <t>Yangın güvenliği denetimi ve kabul prosedürleri 1 Temmuz'dan itibaren kaldırılacaktır; sakinlerin ve işletmelerin bunu dikkate alması gerekmektedir.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Yakıt fiyatlarındaki artış nedeniyle birçok düşük maliyetli havayolu şirketi iflas edecek. Vietnam.vn</t>
+          <t>Yangın güvenliği denetimi ve kabul prosedürleri 1 Temmuz'dan itibaren kaldırılacaktır; sakinlerin ve işletmelerin bunu dikkate alması gerekmektedir. Vietnam.vn</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1736,22 +1716,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 01:28:52</t>
+          <t>2026-06-10 07:56:15</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Yazlık ve villa kiralamalarında dolandırıcılık uyarısı</t>
+          <t>Yangın, 17.000 metrekareden fazla bir alana sahip ahşap işleme fabrikasını yok etti.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Yazlık ve villa kiralamalarında dolandırıcılık uyarısı Turizm News</t>
+          <t>Yangın, 17.000 metrekareden fazla bir alana sahip ahşap işleme fabrikasını yok etti. Vietnam.vn</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1772,22 +1752,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:26:57</t>
+          <t>2026-06-10 03:02:37</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Sahte banka mesajları yoluyla dolandırıcılık: İki kişi tutuklandı, en az 50.000 euro zarar, yaklaşık 150 kişi yaralandı</t>
+          <t>15 Haziran'dan sonra SIM kartınızın bloke edilmesi banka hesabınızı ve dijital hizmetlerinizi nasıl etkileyecek?</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sahte banka mesajları yoluyla dolandırıcılık: İki kişi tutuklandı, en az 50.000 euro zarar, yaklaşık 150 kişi yaralandı KoSSev</t>
+          <t>15 Haziran'dan sonra SIM kartınızın bloke edilmesi banka hesabınızı ve dijital hizmetlerinizi nasıl etkileyecek? Vietnam.vn</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1808,22 +1788,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 20:54:14</t>
+          <t>2026-06-09 20:53:46</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Bankalar, yeni ve karmaşık para transferi dolandırıcılık yöntemlerine karşı uyarı yayınladı.</t>
+          <t>Bankacılıkta Büyük Utanç! Bankaların Kar Masasında Bankacı Yokmuş!</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Bankalar, yeni ve karmaşık para transferi dolandırıcılık yöntemlerine karşı uyarı yayınladı. Vietnam.vn</t>
+          <t>Bankacılıkta Büyük Utanç! Bankaların Kar Masasında Bankacı Yokmuş! ParaMedya</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1844,22 +1824,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 20:22:00</t>
+          <t>2026-06-09 13:25:04</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de binanın damındaki depoda çıkan yangın söndürüldü</t>
+          <t>Yine aynı ilimiz! Koç Grubu'na bağlı bankaya bir saldırı daha</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Mersin'de binanın damındaki depoda çıkan yangın söndürüldü Aksu TV Haber</t>
+          <t>Yine aynı ilimiz! Koç Grubu'na bağlı bankaya bir saldırı daha MSN</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1869,14 +1849,10 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Mersin</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Akdeniz</t>
-        </is>
-      </c>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
@@ -1888,22 +1864,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 20:00:00</t>
+          <t>2026-06-09 13:52:02</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Ataşehir'de mobilya imalathanesinde yangın paniği</t>
+          <t>Diyarbakır'da banka ATM'lerine yönelik saldırılar sürüyor Yenişehir'de hedef Yapı Kredi</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Ataşehir'de mobilya imalathanesinde yangın paniği Bursada Bugün</t>
+          <t>Diyarbakır'da banka ATM'lerine yönelik saldırılar sürüyor Yenişehir'de hedef Yapı Kredi Diyarbakir.Net</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1913,12 +1889,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Bursa | İstanbul</t>
+          <t>Diyarbakır | Bursa | Mersin</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Ataşehir</t>
+          <t>Yenişehir</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -1932,22 +1908,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 07:37:59</t>
+          <t>2026-06-09 10:29:00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Ege Üniversitesi Hastanesinde Şafak Operasyonu ! 45 Kişiye Gözaltı!</t>
+          <t>Yapı Kredi Bankası ATM'si kurşunlandı!</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Ege Üniversitesi Hastanesinde Şafak Operasyonu ! 45 Kişiye Gözaltı! Bilim ve Sağlık Haber Ajansı</t>
+          <t>Yapı Kredi Bankası ATM'si kurşunlandı! Bursada Bugün</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1955,8 +1931,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Diyarbakır | Mersin</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Nilüfer | Yenişehir | Sur</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
@@ -1968,7 +1952,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 13:05:23</t>
+          <t>2026-06-10 06:41:00</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1978,12 +1962,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>banka ATM dolandırıcılığı</t>
+          <t>Düzce’de büyük vurgun önlendi! Telefon tuzağı bankada bozuldu</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>banka ATM dolandırıcılığı – Bursa'ya Dair Her Şey – Bursa Haber, Bursa Son Dakika Haber Bursa'ya Dair Her Şey</t>
+          <t>Düzce’de büyük vurgun önlendi! Telefon tuzağı bankada bozuldu Düzce Damla Gazetesi</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1991,7 +1975,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2004,7 +1992,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 11:56:54</t>
+          <t>2026-06-09 10:36:00</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2014,12 +2002,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası kullanıcılarını tedirgin eden SMS iddiası: “Ayyıldız Teams” mesajları gündem oldu</t>
+          <t>Diyarbakır’da Koç Holding'e ait bankaya ikinci saldırı!</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası kullanıcılarını tedirgin eden SMS iddiası: “Ayyıldız Teams” mesajları gündem oldu Muhalif</t>
+          <t>Diyarbakır’da Koç Holding'e ait bankaya ikinci saldırı! Mücadele Gazetesi</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2027,20 +2015,28 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Diyarbakır</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Koç Holding</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 13:08:00</t>
+          <t>2026-06-09 10:26:49</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2050,12 +2046,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Telegram Ayyıldız Teams Olayı Nedir? Banka SMS Mesajı, 1 Milyon TL İşlem Uyarısı Ve Oltalama İddiasında Bilinenler</t>
+          <t>Diyarbakır’da banka şubelerine yönelik saldırı zinciri: Bu kez hedefte ATM var</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Telegram Ayyıldız Teams Olayı Nedir? Banka SMS Mesajı, 1 Milyon TL İşlem Uyarısı Ve Oltalama İddiasında Bilinenler Urfanatik</t>
+          <t>Diyarbakır’da banka şubelerine yönelik saldırı zinciri: Bu kez hedefte ATM var Yeni Birlik Gazetesi</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2065,10 +2061,14 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Şanlıurfa</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
+          <t>Diyarbakır | İzmir | Bursa | Mersin</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Yenişehir</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 14:13:00</t>
+          <t>2026-06-09 11:39:19</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası’ndan "1 Milyon TL'lik Doğrulama Kodu" Açıklaması: Veri Sızıntısı Var mı?</t>
+          <t>Türk bankaları Suriye’de de faaliyet gösterecek: Bakan Bolat açıkladı</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Ziraat Bankası’ndan "1 Milyon TL'lik Doğrulama Kodu" Açıklaması: Veri Sızıntısı Var mı? Mavi Marmara Gazetesi</t>
+          <t>Türk bankaları Suriye’de de faaliyet gösterecek: Bakan Bolat açıkladı Finans 365</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2116,22 +2116,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 08:51:30</t>
+          <t>2026-06-09 12:53:00</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Koç Holding'e Bir Saldırı Daha: Diyarbakır'da Banka Şubesi Kurşunlandı</t>
+          <t>Şanlıurfa’da binlerce kaçak ürüne el konuldu! 22 şüpheliye işlem</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Koç Holding'e Bir Saldırı Daha: Diyarbakır'da Banka Şubesi Kurşunlandı Gerçek Gündem</t>
+          <t>Şanlıurfa’da binlerce kaçak ürüne el konuldu! 22 şüpheliye işlem Ajans Urfa</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2141,30 +2141,26 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Antalya | Diyarbakır</t>
+          <t>Şanlıurfa</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Koç Holding</t>
-        </is>
-      </c>
+          <t>Viranşehir</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>maps sonucu düşük güven nedeniyle elendi</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:04:00</t>
+          <t>2026-06-09 11:42:00</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2174,12 +2170,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır’da Bankaya Silahlı Saldırı Kim Yaptı? Sur Gazi Caddesi’nde Polis İncelemesi Başladı</t>
+          <t>Ziraat Bankası’nın hacklenmesinin ardınan Halkbank güvenlik mesajı gönderdi</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır’da Bankaya Silahlı Saldırı Kim Yaptı? Sur Gazi Caddesi’nde Polis İncelemesi Başladı Urfanatik</t>
+          <t>Ziraat Bankası’nın hacklenmesinin ardınan Halkbank güvenlik mesajı gönderdi kayserihaber.com</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2189,14 +2185,10 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Diyarbakır</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
@@ -2208,7 +2200,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:09:30</t>
+          <t>2026-06-09 13:29:59</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2218,12 +2210,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SGK ödemelerinde banka ücreti iddiaları yalanlandı: DMM'den net açıklama</t>
+          <t>Telegram Ayyıldız Teams Nedir? Ziraat Bankası Müşterilerine Gelen SMS'lerin Nedeni Merak Ediliyor</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>SGK ödemelerinde banka ücreti iddiaları yalanlandı: DMM'den net açıklama Alparslan Diyarı</t>
+          <t>Telegram Ayyıldız Teams Nedir? Ziraat Bankası Müşterilerine Gelen SMS'lerin Nedeni Merak Ediliyor Taşınmaz Haber</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2241,452 +2233,8 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 09:51:47</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Banka / Finansal Kuruluş</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Koç Holdinge Ait Bankaya Silahlı Saldırı!</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Koç Holdinge Ait Bankaya Silahlı Saldırı! Ajans Balıklıgöl</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 08:45:54</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Banka / Finansal Kuruluş</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Morpara ile Ücretsiz Para Transferi: Yurt İçi ve Yurt Dışında Sıfır Komisyon Dönemi Başlıyor Medya Ege</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 12:32:33</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Banka / Finansal Kuruluş</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>TCMB Açık Bankacılık Altyapısında Yeni Özellikleri Kullanıma Sundu</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>TCMB Açık Bankacılık Altyapısında Yeni Özellikleri Kullanıma Sundu Banka Dünyası</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 09:53:40</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Banka / Finansal Kuruluş</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>İBB Davası'nda 46’ıncı gün... Murat Kapki: "Çocuklarımın okul parasını ödeyemiyoruz. Banka hesaplarımın açılarak ailemin hiç değilse biraz rahatlamasını sağlamanızı istiyorum"</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>İBB Davası'nda 46’ıncı gün... Murat Kapki: "Çocuklarımın okul parasını ödeyemiyoruz. Banka hesaplarımın açılarak ailemin hiç değilse biraz rahatlamasını sağlamanızı istiyorum" Anka</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 10:02:50</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Operasyon / Soruşturma / Suç</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Sur’daki Banka Şubesinde Kurşun İzleri Tespit Edildi.. Saldırıyla İlgili Soruşturma Başlatıldı!</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Sur’daki Banka Şubesinde Kurşun İzleri Tespit Edildi.. Saldırıyla İlgili Soruşturma Başlatıldı! PolitiKARS</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Diyarbakır</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 08:46:00</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Operasyon / Soruşturma / Suç</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Banka ATM’lerinden geçen sahte dolar üreten şebeke çökertildi: 9 gözaltı</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Banka ATM’lerinden geçen sahte dolar üreten şebeke çökertildi: 9 gözaltı Kartepe Şehir</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Diyarbakır | İstanbul</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 13:59:01</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Banka / Finansal Kuruluş</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası'ndan veri sızıntısı iddialarına yalanlama... Başka bankanın sanal POS'u üzerinden denendi</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası'ndan veri sızıntısı iddialarına yalanlama... Başka bankanın sanal POS'u üzerinden denendi | Koruma mekanizmaları devrede Takvim</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 09:42:51</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Banka / Finansal Kuruluş</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası'ndan gelen SMS ortalığı karıştırdı: Milyonluk harcama</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası'ndan gelen SMS ortalığı karıştırdı: Milyonluk harcama Odatv</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 16:15:00</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Banka / Finansal Kuruluş</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası Hacklendi Mi? Bankadan Açıklama Geldi</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası Hacklendi Mi? Bankadan Açıklama Geldi Özgün Kocaeli Gazetesi</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 12:55:43</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Banka / Finansal Kuruluş</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası müşterilerini korkutan SMS! 1 milyon TL'lik işlem mesajları paniğe neden oldu</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Ziraat Bankası müşterilerini korkutan SMS! 1 milyon TL'lik işlem mesajları paniğe neden oldu İLKHABER-Gazetesi</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 20:04:23</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Operasyon / Soruşturma / Suç</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Demokratlar Duffy ailesinin şirket fonlu gezisini soruşturma istiyor</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Demokratlar Duffy ailesinin şirket fonlu gezisini soruşturma istiyor Investing.com Türkiye</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08 16:48:13</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Operasyon / Soruşturma / Suç</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Birleşik Krallık'ın rekabet otoritesi, eBay'in Depop'u satın almasına yönelik bir soruşturma başlattı</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Birleşik Krallık'ın rekabet otoritesi, eBay'in Depop'u satın almasına yönelik bir soruşturma başlattı FashionNetwork France</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J56"/>
+  <autoFilter ref="A1:J44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2731,18 +2279,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2754,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB56"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2932,27 +2468,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:26:08</t>
+          <t>2026-06-09 11:11:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MASAK raporu</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MASAK Tek Tek İnceledi, Rakam Dudak Uçuklattı</t>
+          <t>Gaziantep Tekstil Fabrikası Yangını</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>MASAK Tek Tek İnceledi, Rakam Dudak Uçuklattı Bodrum Olay Gazetesi</t>
+          <t>Gaziantep Tekstil Fabrikası Yangını | Son Dakika Gelişmeleri HaberGo</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2962,44 +2498,56 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>fabrika, tekstil</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Muğla’nın da aralarında bulunduğu 15 ilde jandarma ve MASAK iş birliğiyle düzenlenen yasa dışı bahis operasyonunda 3 milyar liralık para Muğla’nın da aralarında bulunduğu 15 ilde jandarma ve MASAK iş birliğiyle düzenlenen yasa dışı bahis operasyonunda 3 milyar liralık para</t>
+          <t>Gaziantep Tekstil Fabrikası Yangını | Son Dakika Gelişmeleri HaberGo</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>MASAK Tek Tek İnceledi, Rakam Dudak Uçuklattı MASAK Tek Tek İnceledi, Rakam Dudak Uçuklattı Bodrum Olay Gazetesi Muğla’nın da aralarında bulunduğu 15 ilde jandarma ve MASAK iş birliğiyle düzenlenen yasa dışı bahis operasyonunda 3 milyar liralık para Muğla’nın da aralarında bulunduğu 15 ilde jandarma ve MASAK iş birliğiyle düzenlenen yasa dışı bahis operasyonunda 3 milyar liralık para</t>
+          <t>Gaziantep Tekstil Fabrikası Yangını Gaziantep Tekstil Fabrikası Yangını | Son Dakika Gelişmeleri HaberGo Gaziantep Tekstil Fabrikası Yangını | Son Dakika Gelişmeleri HaberGo</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://bodrumolay.com/masak-tek-tek-inceledi-rakam-dudak-ucuklatti/</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Muğla</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQOWFycnJ5Z2Y4V25zS2xJMDhScktlMlBldTRqcVhwUXQ3MFYyWXp5dWx6cjBKbTI2OGVwVmNnLW02TDB0ajN6VTZzV3BfLXJ6dHh3QURDZlFJaVpnMWRreUR5SUZpcG1UazVnMWJyNUxxQ053THM4SVZXTnZ2MElZbC1fbkVvMnNTMHc4cXdmT1gtdVhzSmt4dUZmbnBJcFc0c0daLUg5Yw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Gaziantep Tekstil Fabrikası | Yangını Gaziantep Tekstil Fabrikası</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Gaziantep Tekstil</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Gaziantep Tekstil:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr"/>
@@ -3013,7 +2561,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="n">
-        <v>59.73</v>
+        <v>131.18</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -3022,27 +2570,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 05:35:00</t>
+          <t>2026-06-09 19:40:34</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>para aklama</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını alevler gökyüzünü kapladı!</t>
+          <t>Europol: Kosova Merkezli Suç Ağı Çökertildi, 80 Milyon Euroluk Mal Varlığına El Konuldu</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını alevler gökyüzünü kapladı! Gaziantep Oluşum Gazetesi</t>
+          <t>Europol: Kosova Merkezli Suç Ağı Çökertildi, 80 Milyon Euroluk Mal Varlığına El Konuldu Kosovahaber.com</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -3052,22 +2600,18 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>el konuldu, mal varlığı</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep’in Şahinbey ilçesine bağlı Mavikent Mahallesi’nde bulunan bir geri dönüşüm istasyonunda gece saatlerinde büyük çaplı yangın çıktı. Gaziantep’in Şahinbey ilçesine bağlı Mavikent Mahallesi’nde bulunan bir geri dönüşüm istasyonunda gece saatlerinde büyük çaplı yangın çıktı. Gaziantep’in Şahinbey ilçesine bağlı Mavikent Mahallesi’nde bulunan bir geri dönüşüm istasyonunda gece saatlerinde büyük çaplı yangın çıktı. Gökyüzünü kaplayan alevler kentin birçok noktasından görülürken, itfaiye ekipleri yangını kontrol altına almak için seferber oldu. Gaziantep, gece saatlerinde Mavikent Mahallesi'nden gelen yangın haberiyle sarsıldı. Edinilen bilgilere göre, Mavikent Geri Dönüşüm İstasyonu’nda henüz belirlenmeyen bir nedenle yangın çıktı. Tesis içerisindeki plastik, kağıt ve geri dönüştürülebilir atıkların alev almasıyla yangın kısa sürede büyüyerek tüm binayı sardı. ​Alevler Gökyüzünü Kapladı, Kent Alarm Durumuna Geçti ​Geri dönüşüm malzemelerinin hızla tutuşması nedeniyle büyüyen alevler ve yoğun kara duman, kentin birçok farklı noktasından çıplak gözle görüldü. Çevredeki vatandaşların ve tesis görevlilerinin ihbarı üzerine olay yerine Gaziantep Büyükşehir Belediyesi’ne bağlı çok sayıda itfaiye ekibi, sağlık görevlileri ve polis sevk edildi. ​İtfaiyenin Yoğun Müdahalesi Sürüyor ​Olay yerine ulaşan itfaiye ekipleri, yangının çevredeki diğer tesislere ve yerleşim yerlerine sıçramasını önlemek adına dört bir yandan müdahaleye başladı. Tonlarca su ve köpükle yürütülen söndürme çalışmalarına iş makineleri de destek veriyor. Polis ekipleri bölgede geniş güvenlik önlemleri alarak meraklı vatandaşları alandan uzaklaştırırken, sağlık ekipleri de olası bir dumandan etkilenme veya yaralanma durumuna karşı hazır bekletiliyor. ​Yangının çıkış nedeninin belirlenmesi için söndürme çalışmalarının ardından geniş çaplı soruşturma başlatılacağı öğrenildi. Gaziantep'te fabrika yangını alevler gökyüzünü kapladı! Gaziantep’in Şahinbey ilçesine bağlı Mavikent Mahallesi’nde bulunan bir geri dönüşüm istasyonunda gece saatlerinde büyük çaplı yangın çıktı. 09 Haz 2026 - 08:35 - Asayiş Yazdır Muhabir İbrahim Halil Demirtekin Yorum yazarak Gaziantep Oluşum Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yor</t>
+          <t>Europol, şifreli iletişim platforması SKY ECC üzerinden elde edilen mesajların, Kosova merkezli uluslararası bir organize suç şebekesini ortaya çıkardığını açıkladı. Europol’e göre örgüt; büyük ölçekli uyuşturucu kaçakçılığı, sahte kimlik belgelerinin kullanımı, yasa dışı silah bulundurma ve kara para aklama faaliyetleri yürütüyordu. Yaklaşık üç yıl süren soruşturma, 9 Haziran’da Kosova’da düzenlenen eş zamanlı operasyonla sonuçlandı. Operasyonda suç örgütünün kilit konumdaki beş üyesi gözaltına alındı. Yaklaşık 150 güvenlik görevlisinin katıldığı operasyona Europol uzmanları da destek verdi. Soruşturmaya göre suç örgütü, Avrupa’nın çeşitli ülkelerindeki uyuşturucu sevkiyatlarını şifreli iletişim sistemleri üzerinden koordine ediyor, operasyonel merkezini ise Kosova’da bulunduruyordu. Örgütün üst düzey yöneticileri Kosova’dan, uluslararası uyuşturucu sevkiyatlarını yönetiyor, lojistik faaliyetleri koordine ediyor, suç gelirlerinin aklanmasını organize ediyordu. Europol tarafından</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını alevler gökyüzünü kapladı! Gaziantep'te fabrika yangını alevler gökyüzünü kapladı! Gaziantep Oluşum Gazetesi Gaziantep’in Şahinbey ilçesine bağlı Mavikent Mahallesi’nde bulunan bir geri dönüşüm istasyonunda gece saatlerinde büyük çaplı yangın çıktı. Gökyüzünü kaplayan alevler kentin birçok noktasından görülürken, itfaiye ekipleri yangını kontrol altına almak için seferber oldu. Gaziantep, gece saatlerinde Mavikent Mahallesi'nden gelen yangın haberiyle sarsıldı. Edinilen bilgilere göre, Mavikent Geri Dönüşüm İstasyonu’nda henüz belirlenmeyen bir nedenle yangın çıktı. Tesis içerisindeki plastik, kağıt ve geri dönüştürülebilir atıkların alev almasıyla yangın kısa sürede büyüyerek tüm binayı sardı. ​Alevler Gökyüzünü Kapladı, Kent Alarm Durumuna Geçti ​Geri dönüşüm malzemelerinin hızla tutuşması nedeniyle büyüyen alevler ve yoğun kara duman, kentin birçok farklı noktasından çıplak gözle görüldü. Çevredeki vatandaşların ve tesis görevlilerinin ihbarı üzerine olay yerine Gaziantep Büyükşehir Belediyesi’ne bağlı çok sayıda itfaiye ekibi, sağlık görevlileri ve polis sevk edildi. ​İtfaiyenin Yoğun Müdahalesi Sürüyor ​Olay yerine ulaşan itfaiye ekipleri, yangının çevredeki diğer tesislere ve yerleşim yerlerine sıçramasını önlemek adına dört bir yandan müdahaleye başladı. Tonlarca su ve köpükle yürütülen söndürme çalışmalarına iş makineleri de destek veriyor. Polis ekipleri bölgede geniş güvenlik önlemleri alarak meraklı vatandaşları alandan uzaklaştırırken, sağlık ekipleri de olası bir dumandan etkilenme veya yaralanma durumuna karşı hazır bekletiliyor. ​Yangının çıkış nedeninin belirlenmesi için söndürme çalışmalarının ardından geniş çaplı soruşturma başlatılacağı öğrenildi. Gaziantep'te fabrika yangını alevler gökyüzünü kapladı! 09 Haz 2026 - 08:35 - Asayiş Yazdır Muhabir İbrahim Halil Demirtekin Yorum yazarak Gaziantep Oluşum Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
+          <t>Europol: Kosova Merkezli Suç Ağı Çökertildi, 80 Milyon Euroluk Mal Varlığına El Konuldu Europol: Kosova Merkezli Suç Ağı Çökertildi, 80 Milyon Euroluk Mal Varlığına El Konuldu Kosovahaber.com Europol, şifreli iletişim platforması SKY ECC üzerinden elde edilen mesajların, Kosova merkezli uluslararası bir organize suç şebekesini ortaya çıkardığını açıkladı. Europol’e göre örgüt; büyük ölçekli uyuşturucu kaçakçılığı, sahte kimlik belgelerinin kullanımı, yasa dışı silah bulundurma ve kara para aklama faaliyetleri yürütüyordu. Yaklaşık üç yıl süren soruşturma, 9 Haziran’da Kosova’da düzenlenen eş zamanlı operasyonla sonuçlandı. Operasyonda suç örgütünün kilit konumdaki beş üyesi gözaltına alındı. Yaklaşık 150 güvenlik görevlisinin katıldığı operasyona Europol uzmanları da destek verdi. Soruşturmaya göre suç örgütü, Avrupa’nın çeşitli ülkelerindeki uyuşturucu sevkiyatlarını şifreli iletişim sistemleri üzerinden koordine ediyor, operasyonel merkezini ise Kosova’da bulunduruyordu. Örgütün üst düzey yöneticileri Kosova’dan, uluslararası uyuşturucu sevkiyatlarını yönetiyor, lojistik faaliyetleri koordine ediyor, suç gelirlerinin aklanmasını organize ediyordu.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -3077,31 +2621,19 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.gaziantepolusum.com/haber/28136039/gaziantepte-fabrika-yangini-alevler-gokyuzunu-kapladi</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Gaziantep</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Şahinbey</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Şahinbey ilçesine bağlı Mavikent Mahallesi | gece saatlerinde Mavikent Mahallesi</t>
-        </is>
-      </c>
+          <t>https://kosovahaber.com/haber/europol-kosova-merkezli-suc-agi-cokertildi-80-milyon-euroluk-mal-varligina-el-konuldu-102141</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
@@ -3115,7 +2647,7 @@
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="n">
-        <v>128.75</v>
+        <v>95.19</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>2</v>
@@ -3124,7 +2656,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 19:02:00</t>
+          <t>2026-06-09 15:07:33</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3139,12 +2671,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Bir Mobilya Fabrikasında Çıkan Yangında İtfaiye Eri Şehit Oldu, 1 Kişi Hastaneye Kaldırıldı.</t>
+          <t>Çorlu'da Market Deposunda Yangın</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Bir Mobilya Fabrikasında Çıkan Yangında İtfaiye Eri Şehit Oldu, 1 Kişi Hastaneye Kaldırıldı. Mersin Haber</t>
+          <t>Çorlu'da Market Deposunda Yangın SonDakika</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -3154,90 +2686,70 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Bir Mobilya Fabrikasında Çıkan Yangında İtfaiye Eri Şehit Oldu, 1 Kişi Hastaneye Kaldırıldı. Mersin Haber</t>
+          <t>Tekirdağ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, itfaiyenin müdahalesiyle söndürüldü. Tekirdağ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, itfaiyenin müdahalesiyle söndürüldü. Tekirdağ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, itfaiyenin müdahalesiyle söndürüldü. Çorlu'da Market Deposunda Yangın Son Güncelleme: 09.06.2026 18:07 Tekirdağ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, itfaiyenin müdahalesiyle söndürüldü. Mehmetcan ARSLAN/ ÇORLU ( Tekirdağ ), TEKİRDAĞ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, paniğe neden oldu. Yangın, itfaiyenin müdahalesiyle, büyümeden söndürüldü. Yangın Muhittin Mahallesi Serçe Sokak üzerinde 17.00 sularında meydana geldi. Sokak üzerindeki marketin depo kısmında, henüz bilinmeyen nedenle yangın çıktı. Alevler kısa sürede büyüyerek dumanların yükselmesine neden oldu. İhbarla bölgeye itfaiye, sağlık ve polis ekipleri sevk edildi. Market içerisinde bulunan müşteriler ve çalışanlar panikle dışarı çıktı. Polis çevrede güvenlik önlemleri alırken, itfaiye yangına müdahale etti. Ekiplerinin yaklaşık 1 saat süren çalışmasıyla yangın kontrol altına alınarak söndürüldü. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Haber-Kamera: Mehmetcan ARSLAN - ÇORLU (Tekirdağ), Kaynak: DHA Mehmetcan ARSLAN/ ÇORLU ( Tekirdağ ), TEKİRDAĞ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, paniğe neden oldu. Yangın, itfaiyenin müdahalesiyle, büyümeden söndürüldü. Yangın Muhittin Mahallesi Serçe Sokak üzerinde 17.00 sularında meydana geldi. Sokak üzerindeki marketin depo kısmında, henüz bilinmeyen nedenle yangın çıktı. Alevler kısa sürede büyüyerek dumanların yükselmesine neden oldu. İhbarla bölgeye itfaiye, sağlık ve polis ekipleri sevk edildi. Market içerisinde bulunan müşteriler ve çalışanlar panikle dışarı çıktı. Polis çevrede güvenlik önlemleri alırken, itfaiye yangına müdahale etti. Ekiplerinin yaklaşık 1 saat süren çalışmasıyla yangın kontrol altına alınarak söndürüldü. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Haber-Kamera: Mehmetcan ARSLAN - ÇORLU (Tekirdağ), Çorlu'da Market Deposunda Yangın Tekirdağ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, itfaiyenin müdahalesiyle söndürüldü. Mehmetcan ARSLAN/ ÇORLU ( Tekirdağ ), TEKİRDAĞ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, paniğe neden oldu. Yangın, itfaiyenin müdahalesiyle, büyümeden söndürüldü. Yangın Muhittin Mahallesi Serçe Sokak üzerinde 17.00 sularında meydana geldi. Sokak üzerindeki marketin depo kısmında, henüz bilinmeyen nedenle yangın çıktı. Alevler kısa sürede büyüyerek dumanların yükselmesine neden oldu. İhbarla bölgeye itfaiye, sağlık ve polis ekipleri sevk edildi. Market içerisinde bulunan müşteriler ve çalışanlar panikle dışarı çıktı. Polis çevrede güvenlik önlemleri alırken, itfaiye yangına müdahale etti. Ekiplerinin yaklaşık 1 saat süren çalışmasıyla yangın kontrol altına alınarak söndürüldü. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Haber-Kamera: Mehmetcan ARSLAN - ÇORLU (Tekirdağ),</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Bir Mobilya Fabrikasında Çıkan Yangında İtfaiye Eri Şehit Oldu, 1 Kişi Hastaneye Kaldırıldı. Konya Karatay'da Bir Mobilya Fabrikasında Çıkan Yangında İtfaiye Eri Şehit Oldu, 1 Kişi Hastaneye Kaldırıldı. Mersin Haber Konya Karatay'da Bir Mobilya Fabrikasında Çıkan Yangında İtfaiye Eri Şehit Oldu, 1 Kişi Hastaneye Kaldırıldı.</t>
+          <t>Çorlu'da Market Deposunda Yangın Çorlu'da Market Deposunda Yangın SonDakika Tekirdağ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, itfaiyenin müdahalesiyle söndürüldü. Çorlu'da Market Deposunda Yangın Son Güncelleme: 09.06.2026 18:07 Tekirdağ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, itfaiyenin müdahalesiyle söndürüldü. Mehmetcan ARSLAN/ ÇORLU ( Tekirdağ ), TEKİRDAĞ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, paniğe neden oldu. Yangın, itfaiyenin müdahalesiyle, büyümeden söndürüldü. Yangın Muhittin Mahallesi Serçe Sokak üzerinde 17.00 sularında meydana geldi. Sokak üzerindeki marketin depo kısmında, henüz bilinmeyen nedenle yangın çıktı. Alevler kısa sürede büyüyerek dumanların yükselmesine neden oldu. İhbarla bölgeye itfaiye, sağlık ve polis ekipleri sevk edildi. Market içerisinde bulunan müşteriler ve çalışanlar panikle dışarı çıktı. Polis çevrede güvenlik önlemleri alırken, itfaiye yangına müdahale etti. Ekiplerinin yaklaşık 1 saat süren çalışmasıyla yangın kontrol altına alınarak söndürüldü. Yangının çıkış nedenine ilişkin inceleme başlatıldı. Haber-Kamera: Mehmetcan ARSLAN - ÇORLU (Tekirdağ), Kaynak: DHA Mehmetcan ARSLAN/ ÇORLU ( Tekirdağ ), TEKİRDAĞ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, paniğe neden oldu. Haber-Kamera: Mehmetcan ARSLAN - ÇORLU (Tekirdağ), Çorlu'da Market Deposunda Yangın Tekirdağ'ın Çorlu ilçesinde bir marketin deposunda çıkan yangın, itfaiyenin müdahalesiyle söndürüldü. Haber-Kamera: Mehmetcan ARSLAN - ÇORLU (Tekirdağ),</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>summary_only</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOa3VtelRtRVFBMzFWekdkZlU2RWk4Q24teGtnZHhjQUhTZDZLS21LeVRnU2MxdmR5Und6eWhyUTNtV3RfeFhtNjRkNUkyMnlWd25BcVJIZ3FaQU5rX3RVcEt5MUF1NUhrT0dYY3lNWG9JcUxsZWtGMkdhVkdFZWhSZzJKMWliSm53OV9DaXJkVVdjV2F3WlRWTG5Odm5fQjhoYzVtMVRQckFYOVJlU0o0NGszRV9QdEpWR284S3kzWGxwcFdKOG9peUpiWlhBMXFweXBDRnlrUlUtYXhjcVZCR9IBV0FVX3lxTE9rWlJFbzJqMFZ5R0pKcXFZY1hvY2hjS19vS0dRNHpfZVRnMjNJNFo3UjVlenluQmV1a3FOUEI3eHFYY09iX0N0c3d0UVdqX3VmQ2FZUnJzUQ?oc=5&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+          <t>https://www.sondakika.com/amp/haber-corlu-da-market-deposunda-yangin-19929943/</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
+          <t>Tekirdağ</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Karatay</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>Çorlu</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yangın Muhittin Mahallesi</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Bir Mobilya</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>Bir Mobilya:292:body+summary+title</t>
-        </is>
-      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>Bir Mobilya Karatay Konya Türkiye</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Burda Mobilya | Kibrit mobilya | Aras Ofis Mobilya | Konya mila mobilya center konya ofis büro takımları ofis mobilyaları | Rabi Mobilya Satış Mağazası Konya</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>Burda Mobilya</t>
-        </is>
-      </c>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>83.33333333333333 | 80.0 | 77.77777777777777 | 77.77777777777777 | 77.77777777777777</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="n">
-        <v>236.22</v>
+        <v>99.5</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>3</v>
@@ -3246,27 +2758,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 04:58:50</t>
+          <t>2026-06-09 10:20:01</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>kara para</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Devlet Bankası'nın 1 Temmuz 2026'dan itibaren geçerli olacak yeni organizasyon yapısı.</t>
+          <t>Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Devlet Bankası'nın 1 Temmuz 2026'dan itibaren geçerli olacak yeni organizasyon yapısı. Vietnam.vn</t>
+          <t>Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -3276,58 +2788,82 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika, tekstil</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Devlet Bankası'nın 1 Temmuz 2026'dan itibaren geçerli olacak yeni organizasyon yapısı. Vietnam.vn</t>
+          <t>Gaziantep 5.Organize Sanayi Bölgesi'ndeki Molhan Tekstil fabrikasında sabah çıkan yangın, ekiplerin müdahalesiyle kontrol altına alındı; can kaybı yok, soğutma sürüyor. Gaziantep 5.Organize Sanayi Bölgesi'ndeki Molhan Tekstil fabrikasında sabah çıkan yangın, ekiplerin müdahalesiyle kontrol altına alındı; can kaybı yok, soğutma sürüyor. Gaziantep 5.Organize Sanayi Bölgesi'ndeki Molhan Tekstil fabrikasında sabah çıkan yangın, ekiplerin müdahalesiyle kontrol altına alındı; can kaybı yok, soğutma sürüyor. Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı Olay ve müdahale Gaziantep'in 5.Organize Sanayi Bölgesi nde bulunan Molhan Tekstil fabrikasında sabah saat 09.04 civarında bilinmeyen bir nedenle yangın çıktı. Kısa sürede büyüyen alevler için 112 acil çağrı merkezine ihbarda bulunuldu. İhbar üzerine bölgeye çok sayıda itfaiye, sağlık, polis ve AFAD ekibi sevk edildi. Olay yerine ulaşan itfaiye ekipleri, fabrikayı saran yangına müdahale etti; müdahale, 60 personel ve yaklaşık 50 araç ile yürütüldü. Ekiplerin yoğun çalışması sonucu yangın yaklaşık 5 saat süren müdahalenin ardından kontrol altına alındı. Yetkili açıklaması Gaziantep Büyükşehir Belediyesi Başkanvekili Halil Uğur , çalışmalarla ilgili olarak şu bilgileri verdi: "Sabah 09.04’te itfaiye daire başkanlığımıza gelen ihbara istinaden ekiplerimiz harekete geçti. Bize gelen ihbardan 6 dakika sonra organize itfaiye ekiplerimizle birlikte yangına müdahalemiz başladı. Araştırmalarımıza göre yangın fabrikanın depo alanında çıkıyor. Teknik olarak detaylar araştırılıyor. Sevindirici olay da şu ana kadar can kaybının olmamış olmasıdır. İtfaiye daire başkanlığımızın kontrolünde 50’ye yakın itfaiye aracı ve destek araçla müdahale ediyoruz. Bunların yanında GASKİ, Kent estetiği, organize sanayinin tüm araçlarıyla birlikte yangına müdahale ediyoruz. Yangının etrafa sıçramasıyla ilgili durum kontrol altına alındı. Söndürme işlemi yapılıyor. Kısa süre içinde söndürme işlemi tamamlandıktan sonra soğutma çalışmalarına başlayacağız. Yangın kontrolümüz altında. Geçmiş olsun dileklerimi iletiyorum." Güncel durum İtfaiye ekipleri fabrikada yer yer söndürme ve soğutma çalışmalarına devam ediyor. Yetkililer, yangının etrafı sarması riskinin kontrol altına alındığını ve teknik incelemelerle yangının çıkış nedeninin araştırıldığını belirtiyor. Şu ana kadar can kaybı bildirilmedi , soğutma çalışmaları tamamlanana kadar bölgedeki müdahale sürdürülüyor. GAZİANTEP'TE BİR TEKSTİL FABRİKASINDA ÇIKAN VE KISA SÜREDE BÜYÜYEN YANGIN KONTROL ALTINA ALINDI. 1 Karaman'da motosiklet kaldırıma çarpıp karşı şeride savruldu; sürücü yaralanmadı Karaman'da motosiklet kaldırıma çarpıp karşı şeride savruldu; sürücü yaralanmadı 2 Çan'da tamir için bırakılan araç Edremit'te bulundu: 2 şüpheli tutuklandı Çan'da tamir için bırakılan araç Edremit'te bulundu: 2 şüpheli tutuklandı 3 Gebze'de 3 katlı binanın en üst katında çıkan yangın söndürüldü Gebze'de 3 katlı binanın en üst katında çıkan yangın söndürüldü 4 Konya'da Mayıs ayında polis bölgesinde 1.556 trafik kazası: 3 ölü, 1.143 yaralı Konya'da Mayıs ayında polis bölgesinde 1.556 trafik kazası: 3 ölü, 1.143 yaralı 5 Gebze'de 3. kat yangını: Çamaşır makinesi kaynaklı olduğu iddia edildi, itfaiye söndürdü Gebze'de 3. kat yangını: Çamaşır makinesi kaynaklı olduğu iddia edildi, itfaiye söndürdü 6 Tarsus’ta Adana-Mersin Otoyolu Ziyaret Tepe mevkiinde otomobil tıra çarptı: 1 ölü, 4 yaralı Tarsus’ta Adana-Mersin Otoyolu Ziyaret Tepe mevkiinde otomobil tıra çarptı: 1 ölü, 4 yaralı 7 Bulgaristan sınır polisi filosunu güçlendirdi: 10 milyon 487 bin 747,64 avroluk yeni araç ve ekipman Bulgaristan sınır polisi filosunu güçlendirdi: 10 milyon 487 bin 747,64 avroluk yeni araç ve ekipman Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı Gaziantep 5.Organize Sanayi Bölgesi'ndeki Molhan Tekstil fabrikasında sabah çıkan yangın, ekiplerin müdahalesiyle kontrol altına alındı; can kaybı yok, soğutma sürüyor. Gaziantep'in 5.Organize Sanayi Bölgesi nde bulunan Molhan Tekstil fabrikasında sabah saat 09.04 civarında bilinmeyen bir nedenle yangın çıktı. Kısa sürede büyüyen alevler için 112 acil çağrı merkezine ihbarda bulunuldu. İhbar üzerine bölgeye çok sayıda itfaiye, sağlık, polis ve AFAD ekibi sevk edildi. Olay yerine ulaşan itfaiye ekipleri, fabrikayı saran yangına müdahale etti; müdahale, 60 personel ve yaklaşık 50 araç ile yürütüldü. Ekiplerin yoğun çalışması sonucu yangın yaklaşık 5 saat süren müdahalenin ardından kontrol altına alındı. Gaziantep Büyükşehir Belediyesi Başkanvekili Halil Uğur , çalışmalarla ilgili olarak şu bilgileri verdi: "Sabah 09.04’te itfaiye daire başkanlığımıza gelen ihbara istinaden ekiplerimiz harekete geçti. Bize gelen ihbardan 6 dakika sonra organize itfaiye ekiplerimizle birlikte yangına müdahalemiz başladı. Araştırmalarımıza göre yangın fabrikanın depo alanında çıkıyor. Teknik olarak detaylar araştırılıyor. Sevindirici olay da şu ana kadar can kaybının olmamış olmasıdır. İtfaiye daire başkanlığımızın kontrolünde 50’ye yakın itfaiye aracı ve destek araçla müdahale ediyoruz. Bunların yanında GASKİ, Kent estetiği, organize sanayinin tüm araçlarıyla birlikte yangına müdahale ediyoruz. Yangının etrafa sıçramasıyla ilgili durum kontrol altına alındı. Söndürme işlemi yapılıyor. Kısa süre içinde söndürme işlemi tamamlandıktan sonra soğutma çalışmalarına başlayacağız. Yangın kontrolümüz altında. Geçmiş olsun dileklerimi iletiyorum." İtfaiye ekipleri fabrikada yer yer söndürme ve soğutma çalışmalarına devam ediyor. Yetkililer, yangının etrafı sarması riskinin kontrol altına alındığını ve teknik incelemelerle yangının çıkış nedeninin araştırıldığını belirtiyor. Şu ana kadar can kaybı bildirilmedi , soğutma çalışmaları tamamlanana kadar bölgedeki müdahale sürdürülüyor. GAZİANTEP'TE BİR TEKSTİL FABRİKASINDA ÇIKAN VE KISA SÜREDE BÜYÜYEN YANGIN KONTROL ALTINA ALINDI. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. aksiyon.com.tr Gündem'deyim ama spesifik olarak eğitim ve sağlık politikalarındaki güncel gelişmelere odaklanıyorum. Öğrenmeye açık, meraklı ve enerjik bir yapım var. 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Devlet Bankası'nın 1 Temmuz 2026'dan itibaren geçerli olacak yeni organizasyon yapısı. Vietnam Devlet Bankası'nın 1 Temmuz 2026'dan itibaren geçerli olacak yeni organizasyon yapısı. Vietnam.vn Vietnam Devlet Bankası'nın 1 Temmuz 2026'dan itibaren geçerli olacak yeni organizasyon yapısı.</t>
+          <t>Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı Aksiyon.com.TR Gaziantep 5.Organize Sanayi Bölgesi'ndeki Molhan Tekstil fabrikasında sabah çıkan yangın, ekiplerin müdahalesiyle kontrol altına alındı; can kaybı yok, soğutma sürüyor. Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı Olay ve müdahale Gaziantep'in 5.Organize Sanayi Bölgesi nde bulunan Molhan Tekstil fabrikasında sabah saat 09.04 civarında bilinmeyen bir nedenle yangın çıktı. Kısa sürede büyüyen alevler için 112 acil çağrı merkezine ihbarda bulunuldu. İhbar üzerine bölgeye çok sayıda itfaiye, sağlık, polis ve AFAD ekibi sevk edildi. Olay yerine ulaşan itfaiye ekipleri, fabrikayı saran yangına müdahale etti; müdahale, 60 personel ve yaklaşık 50 araç ile yürütüldü. Ekiplerin yoğun çalışması sonucu yangın yaklaşık 5 saat süren müdahalenin ardından kontrol altına alındı. Yetkili açıklaması Gaziantep Büyükşehir Belediyesi Başkanvekili Halil Uğur , çalışmalarla ilgili olarak şu bilgileri verdi: "Sabah 09.04’te itfaiye daire başkanlığımıza gelen ihbara istinaden ekiplerimiz harekete geçti. Bize gelen ihbardan 6 dakika sonra organize itfaiye ekiplerimizle birlikte yangına müdahalemiz başladı. Araştırmalarımıza göre yangın fabrikanın depo alanında çıkıyor. Teknik olarak detaylar araştırılıyor. Sevindirici olay da şu ana kadar can kaybının olmamış olmasıdır. İtfaiye daire başkanlığımızın kontrolünde 50’ye yakın itfaiye aracı ve destek araçla müdahale ediyoruz. Bunların yanında GASKİ, Kent estetiği, organize sanayinin tüm araçlarıyla birlikte yangına müdahale ediyoruz. Yangının etrafa sıçramasıyla ilgili durum kontrol altına alındı. Kısa süre içinde söndürme işlemi tamamlandıktan sonra soğutma çalışmalarına başlayacağız. Yangın kontrolümüz altında. Geçmiş olsun dileklerimi iletiyorum." Güncel durum İtfaiye ekipleri fabrikada yer yer söndürme ve soğutma çalışmalarına devam ediyor. Yetkililer, yangının etrafı sarması riskinin kontrol altına alındığını ve teknik incelemelerle yangının çıkış nedeninin araştırıldığını belirtiyor. GAZİANTEP'TE BİR TEKSTİL FABRİKASINDA ÇIKAN VE KISA SÜREDE BÜYÜYEN YANGIN KONTROL ALTINA ALINDI. 1 Karaman'da motosiklet kaldırıma çarpıp karşı şeride savruldu; sürücü yaralanmadı Karaman'da motosiklet kaldırıma çarpıp karşı şeride savruldu; sürücü yaralanmadı 2 Çan'da tamir için bırakılan araç Edremit'te bulundu: 2 şüpheli tutuklandı Çan'da tamir için bırakılan araç Edremit'te bulundu: 2 şüpheli tutuklandı 3 Gebze'de 3 katlı binanın en üst katında çıkan yangın söndürüldü Gebze'de 3 katlı binanın en üst katında çıkan yangın söndürüldü 4 Konya'da Mayıs ayında polis bölgesinde 1.556 trafik kazası: 3 ölü, 1.143 yaralı Konya'da Mayıs ayında polis bölgesinde 1.556 trafik kazası: 3 ölü, 1.143 yaralı 5 Gebze'de 3. kat yangını: Çamaşır makinesi kaynaklı olduğu iddia edildi, itfaiye söndürdü Gebze'de 3. kat yangını: Çamaşır makinesi kaynaklı olduğu iddia edildi, itfaiye söndürdü 6 Tarsus’ta Adana-Mersin Otoyolu Ziyaret Tepe mevkiinde otomobil tıra çarptı: 1 ölü, 4 yaralı Tarsus’ta Adana-Mersin Otoyolu Ziyaret Tepe mevkiinde otomobil tıra çarptı: 1 ölü, 4 yaralı 7 Bulgaristan sınır polisi filosunu güçlendirdi: 10 milyon 487 bin 747,64 avroluk yeni araç ve ekipman Bulgaristan sınır polisi filosunu güçlendirdi: 10 milyon 487 bin 747,64 avroluk yeni araç ve ekipman Gaziantep'te Molhan Tekstil fabrikasında çıkan yangın kontrol altına alındı Gaziantep 5.Organize Sanayi Bölgesi'ndeki Molhan Tekstil fabrikasında sabah çıkan yangın, ekiplerin müdahalesiyle kontrol altına alındı; can kaybı yok, soğutma sürüyor. Gaziantep'in 5.Organize Sanayi Bölgesi nde bulunan Molhan Tekstil fabrikasında sabah saat 09.04 civarında bilinmeyen bir nedenle yangın çıktı. Gaziantep Büyükşehir Belediyesi Başkanvekili Halil Uğur , çalışmalarla ilgili olarak şu bilgileri verdi: "Sabah 09.04’te itfaiye daire başkanlığımıza gelen ihbara istinaden ekiplerimiz harekete geçti. Geçmiş olsun dileklerimi iletiyorum." İtfaiye ekipleri fabrikada yer yer söndürme ve soğutma çalışmalarına devam ediyor. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? TRT 1, 2 Ocak yayın planını değiştirdi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNWVh0NHctTDZHUzVpWlFtMDdKck1TZWFnSkRYa2N1ZFR4eUJGNzV4OUpLRi1NVDhVcHVXbWxBTlhwVi1YX3pXTnRmVFBKbkRFNFJiM2tWLVpqeXVjbXNKRzhwdDVQdjRleFU5SDNwOWo0a0lWVGpCME9rTzlvNlRFN2E4SFg4WVNjRmxMMDRHRUluUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>https://www.aksiyon.com.tr/gaziantep-te-molhan-tekstil-fabrikasinda-cikan-yangin-kontrol-altina-alindi-290982</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Düzce | Gaziantep | İstanbul | Karaman</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Edremit | Gebze | Tarsus</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Molhan Tekstil</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Molhan Tekstil:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
+          <t>faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Molhan Tekstil Edremit Bursa Türkiye</t>
+        </is>
+      </c>
       <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>Edremit | Bursa</t>
+        </is>
+      </c>
       <c r="AA5" s="2" t="n">
-        <v>80.3</v>
+        <v>183</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>4</v>
@@ -3336,27 +2872,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 02:42:59</t>
+          <t>2026-06-09 13:32:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>kara para</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak?</t>
+          <t>İran'da 'vatan hainliği' suçlamasıyla 200'den fazla kişinin mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak? Halk TV</t>
+          <t>İran'da 'vatan hainliği' suçlamasıyla 200'den fazla kişinin mal varlığına el konuldu Ensonhaber</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -3366,22 +2902,18 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>banka, holding</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş | şirket / firma</t>
-        </is>
-      </c>
+          <t>el konuldu, mal varlığı</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Bahadır Özgür yazdı: Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak? Bahadır Özgür yazdı: Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak? Bahadır Özgür yazdı: Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak?</t>
+          <t>Son zamanlarda İran'da 'vatan hainliği' suçlamasıyla mal varlıklarına el konulan kişi sayısının 200'ü geçtiği belirtildi. Asgar Cihangir'in açıklamalarıyla gündeme gelen bu durum, ülkede büyük yankı uyandırdı. Son zamanlarda İran'da 'vatan hainliği' suçlamasıyla mal varlıklarına el konulan kişi sayısının 200'ü geçtiği belirtildi. Asgar Cihangir'in açıklamalarıyla gündeme gelen bu durum, ülkede büyük yankı uyandırdı. Son zamanlarda İran'da 'vatan hainliği' suçlamasıyla mal varlıklarına el konulan kişi sayısının 200'ü geçtiği belirtildi. Asgar Cihangir'in açıklamalarıyla gündeme gelen bu durum, ülkede büyük yankı uyandırdı. İran'da 'vatan hainliği' suçlamasıyla 200'den fazla kişinin mal varlığına el konuldu Son zamanlarda İran'da 'vatan hainliği' suçlamasıyla mal varlıklarına el konulan kişi sayısının 200'ü geçtiği belirtildi. Asgar Cihangir'in açıklamalarıyla gündeme gelen bu durum, ülkede büyük yankı uyandırdı. İran yaşadığı saldırılarda can ve mal kaybı yaşadı, olayların yol açtığı belirsizlik ve gerginliklerle ekonomisi derin yara aldı. Bu süreçte düşmanla iş birliği yaptığı tespit edilenlere yaptırımlar gündeme geldi. İran Yargı Erki Sözcüsü Asgar Cihangir, şu ana kadar 200'den fazla kişinin mal varlığına "vatan hainliği" suçlamasıyla el konulduğunu açıkladı. İran devlet televizyonunun haberine göre Cihangir, ülkede mal varlığına el konulan kişilere ilişkin açıklamalarda bulundu. Şu ana kadar 200'den fazla kişinin "vatan hainliği" suçlamasıyla mal varlığına el konulduğunu belirten Cihangir, aynı suçlamayla hakkında inceleme yürütülen başka kişilerin mal varlıklarına ilişkin tespit çalışmalarının da sürdüğünü ifade etti. Cihangir, yargı erkinin söz konusu dosyalarla ilgili kesin sonuca ulaşıncaya kadar çalışmalarına devam edeceğini kaydetti.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak? Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak? Halk TV Bahadır Özgür yazdı: Papara bankaya, banka çaycıya gitti: Can Holding ganimetini kimler paylaşacak?</t>
+          <t>İran'da 'vatan hainliği' suçlamasıyla 200'den fazla kişinin mal varlığına el konuldu İran'da 'vatan hainliği' suçlamasıyla 200'den fazla kişinin mal varlığına el konuldu Ensonhaber Son zamanlarda İran'da 'vatan hainliği' suçlamasıyla mal varlıklarına el konulan kişi sayısının 200'ü geçtiği belirtildi. Asgar Cihangir'in açıklamalarıyla gündeme gelen bu durum, ülkede büyük yankı uyandırdı. İran'da 'vatan hainliği' suçlamasıyla 200'den fazla kişinin mal varlığına el konuldu Son zamanlarda İran'da 'vatan hainliği' suçlamasıyla mal varlıklarına el konulan kişi sayısının 200'ü geçtiği belirtildi. İran yaşadığı saldırılarda can ve mal kaybı yaşadı, olayların yol açtığı belirsizlik ve gerginliklerle ekonomisi derin yara aldı. İran Yargı Erki Sözcüsü Asgar Cihangir, şu ana kadar 200'den fazla kişinin mal varlığına "vatan hainliği" suçlamasıyla el konulduğunu açıkladı. İran devlet televizyonunun haberine göre Cihangir, ülkede mal varlığına el konulan kişilere ilişkin açıklamalarda bulundu. Şu ana kadar 200'den fazla kişinin "vatan hainliği" suçlamasıyla mal varlığına el konulduğunu belirten Cihangir, aynı suçlamayla hakkında inceleme yürütülen başka kişilerin mal varlıklarına ilişkin tespit çalışmalarının da sürdüğünü ifade etti.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -3391,7 +2923,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://halktv.com.tr/makale/papara-bankaya-banka-cayciya-gitti-can-holding-ganimetini-kimler-paylasacak-1034908</t>
+          <t>https://www.ensonhaber.com/iranda-vatan-hainligi-suclamasiyla-200den-fazla-kisinin-mal-varligina-el-konuldu-h1540853</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
@@ -3399,49 +2931,25 @@
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>Can Holding</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>Can Holding:292:body+summary+title</t>
-        </is>
-      </c>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>Can Holding Türkiye</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Can Holding A.Ş</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Can Holding A.Ş</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="n">
-        <v>175.49</v>
+        <v>96.75</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>5</v>
@@ -3450,27 +2958,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:45:00</t>
+          <t>2026-06-09 13:22:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Konya’da korkutan fabrika yangını: Alevler şehri dumana boğdu! Ekipler seferber oldu</t>
+          <t>İstanbul merkezli 24 ilde büyük operasyon! 350 milyon liralık mal varlığına da el konuldu</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Konya’da korkutan fabrika yangını: Alevler şehri dumana boğdu! Ekipler seferber oldu Konya Yenigün Gazetesi</t>
+          <t>İstanbul merkezli 24 ilde büyük operasyon! 350 milyon liralık mal varlığına da el konuldu Gazete Vatan</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3480,22 +2988,18 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>el konuldu, mal varlığı</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Konya’da korkutan fabrika yangını: Alevler şehri dumana boğdu! Ekipler seferber oldu Konya Yenigün Gazetesi</t>
+          <t>İstanbul merkezli 24 ilde büyük operasyon! 350 milyon liralık mal varlığına da el konuldu Gazete Vatan</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Konya’da korkutan fabrika yangını: Alevler şehri dumana boğdu! Ekipler seferber oldu Konya’da korkutan fabrika yangını: Alevler şehri dumana boğdu! Ekipler seferber oldu Konya Yenigün Gazetesi Konya’da korkutan fabrika yangını: Alevler şehri dumana boğdu! Ekipler seferber oldu Konya Yenigün Gazetesi</t>
+          <t>İstanbul merkezli 24 ilde büyük operasyon! 350 milyon liralık mal varlığına da el konuldu İstanbul merkezli 24 ilde büyük operasyon! 350 milyon liralık mal varlığına da el konuldu Gazete Vatan İstanbul merkezli 24 ilde büyük operasyon! 350 milyon liralık mal varlığına da el konuldu Gazete Vatan</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -3505,12 +3009,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPMzJFT2c3Yk9RZ2dFdEl4TndRYVlUS1I4U2REa21HelpmQ0VUUGh4dVVWZE5UZ3NwR2diR0dHVk15MXhubkZ4UnpEQ19DTFV0dHVCaGpWazJaMXNkQkM0cmFsOUQ3aDd3VVY2STJPVnJKMDVOcml1a1dqOFZrMTNKaUlWUDE5ZkxuUFZFOGI5NWJudmFBQlNWSWhpTDlEcVViNlFPZGdJMzdmOWNMT0pN0gG0AUFVX3lxTE5QVWxrQk1Gek9xRWE0eWU2RXJWcnBHUXlaMGxKMDJ3SldlVUVnWEREYmxSc1pqdkpGUHlZV3AtU29fSEl3S25uZW1LZ3Z6WWhya1dPTDlmOGhfZklhS1B5ZUcweW1rRzd6YjZRcjl6WnBrRVdIeENxT2tpcFp3WG5QWThRdmpXN3pOTWdSUUw4dVZsVER4YUtaOTJCZ0FCaFFabS1PWW9pS3ZycC0wYlU0NzJadw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQdFczOUpwaFc0YjBfZmFJSUVRUlFtM3J3b0dIZmVtYVVKYjgyZi1hNzFUUE9PQmlSNlFRdXhkTFFoMl9XOUE2YlR3YVA5MlFXVTZfZElSVkNzWXNMX2xfTUNtcFQ5T2dBTGU1dWQxNUZuallKVWZmOWxWU0JMTmdBeVBsMjBrbE0tN003cjg2QWdXQWtLOFExTC0tZGc4QURnTlJxa1VwWkxpNGc1Z3hsdGVpR0VrbnJPX3g5TjdjV2ZfMnItVlIzX2NQWQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
@@ -3535,7 +3039,7 @@
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="n">
-        <v>95.81999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>6</v>
@@ -3544,27 +3048,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 09:31:46</t>
+          <t>2026-06-09 16:28:12</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu</t>
+          <t>EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu tv42haber.com</t>
+          <t>EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu - beş kişi tutuklandı KoSSev</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -3574,56 +3078,40 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>el konuldu, mal varlığı</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu Yayınlama: 08.06.2026 10:20Güncelleme: 08.06.2026 11:42 Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde çıktı. Edinilen bilgiye göre, mahalle sakinlerinden N.G.’ye ait garaj ve depo olarak kullanılan yapıda henüz belirlenemeyen bir nedenle yangın başladı. Alevleri fark eden vatandaşların ihbarı üzerine adrese Kurucuova, Yeşildağ ve Beyşehir’den itfaiye ekiplerinin yanı sıra Isparta’nın Yenişarbademli ilçesinden de ekipler sevk edildi. Ekiplerin müdahalesi sayesinde yangın çevredeki evlere sıçramadan kontrol altına alındı. Yangının söndürülmesinin ardından soğutma çalışmaları gerçekleştirildi. Can kaybı ya da yaralanmanın yaşanmadığı yangında garaj ve depo olarak kullanılan yapıda büyük çapta maddi hasar meydana geldi. İtfaiye ekiplerinin yaptığı ilk incelemede, yangının elektrik kablolarının aşırı ısınmasından kaynaklandığının belirlendiği öğrenildi. Yangınla ilgili tahkikat sürüyor. Haber Merkezi Tv42 Haber, Konya haberleri, Konya Gündem, Konya Haber, Konya Gündemi Asayiş Diyarbakır’da Yapı Kredi Bankası Şubesi’ne silahlı saldırı Yaşlı çift evlerinde ölü bulundu Kontrolden çıkan otomobil refüjdeki bariyerlere çarptı: 1 yaralı Manisa’da 5 ilçede eş zamanlı orman yangını tatbikatı gerçekleştirildi Karaman’da motosikletin çarptığı 3 yaşındaki çocuk yaralandı Diyarbakır’da Yapı Kredi Bankası Şubesi’ne silahlı saldırı Yaşlı çift evlerinde ölü bulundu Kontrolden çıkan otomobil refüjdeki bariyerlere çarptı: 1 yaralı Manisa’da 5 ilçede eş zamanlı orman yangını tatbikatı gerçekleştirildi Karaman’da motosikletin çarptığı 3 yaşındaki çocuk yaralandı Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde çıktı. Edinilen bilgiye göre, mahalle sakinlerinden N.G.’ye ait garaj ve depo olarak kullanılan yapıda henüz belirlenemeyen bir nedenle yangın başladı. Alevleri fark eden vatandaşların ihbarı üzerine adrese Kurucuova, Yeşildağ ve Beyşehir’den itfaiye ekiplerinin yanı sıra Isparta’nın Yenişarbademli ilçesinden de ekipler sevk edildi. Ekiplerin müdahalesi sayesinde yangın çevredeki evlere sıçramadan kontrol altına alındı. Yangının söndürülmesinin ardından soğutma çalışmaları gerçekleştirildi. Can kaybı ya da yaralanmanın yaşanmadığı yangında garaj ve depo olarak kullanılan yapıda büyük çapta maddi hasar meydana geldi. İtfaiye ekiplerinin yaptığı ilk incelemede, yangının elektrik kablolarının aşırı ısınmasından kaynaklandığının belirlendiği öğrenildi. Yangınla ilgili tahkikat sürüyor. Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu © 2026 Tv42 Haber, Konya haberleri, Konya Gündem, Konya Haber, Konya Gündemi. Tüm hakları saklıdır.</t>
+          <t>EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu - beş kişi tutuklandı Haber - Kosova EUROPOL: Yaklaşık 80 milyon euro değerinde mal varlığına el konuldu EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu - beş kişi tutuklandı Haber - Kosova EUROPOL: Yaklaşık 80 milyon euro değerinde mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu tv42haber.com Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu Yayınlama: 08.06.2026 10:20Güncelleme: 08.06.2026 11:42 Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Yangın, ilçeye bağlı Kurucuova Mahallesi’nde çıktı. Edinilen bilgiye göre, mahalle sakinlerinden N.G.’ye ait garaj ve depo olarak kullanılan yapıda henüz belirlenemeyen bir nedenle yangın başladı. Alevleri fark eden vatandaşların ihbarı üzerine adrese Kurucuova, Yeşildağ ve Beyşehir’den itfaiye ekiplerinin yanı sıra Isparta’nın Yenişarbademli ilçesinden de ekipler sevk edildi. Ekiplerin müdahalesi sayesinde yangın çevredeki evlere sıçramadan kontrol altına alındı. Yangının söndürülmesinin ardından soğutma çalışmaları gerçekleştirildi. Can kaybı ya da yaralanmanın yaşanmadığı yangında garaj ve depo olarak kullanılan yapıda büyük çapta maddi hasar meydana geldi. İtfaiye ekiplerinin yaptığı ilk incelemede, yangının elektrik kablolarının aşırı ısınmasından kaynaklandığının belirlendiği öğrenildi. Yangınla ilgili tahkikat sürüyor. Haber Merkezi Tv42 Haber, Konya haberleri, Konya Gündem, Konya Haber, Konya Gündemi Asayiş Diyarbakır’da Yapı Kredi Bankası Şubesi’ne silahlı saldırı Yaşlı çift evlerinde ölü bulundu Kontrolden çıkan otomobil refüjdeki bariyerlere çarptı: 1 yaralı Manisa’da 5 ilçede eş zamanlı orman yangını tatbikatı gerçekleştirildi Karaman’da motosikletin çarptığı 3 yaşındaki çocuk yaralandı Diyarbakır’da Yapı Kredi Bankası Şubesi’ne silahlı saldırı Yaşlı çift evlerinde ölü bulundu Kontrolden çıkan otomobil refüjdeki bariyerlere çarptı: 1 yaralı Manisa’da 5 ilçede eş zamanlı orman yangını tatbikatı gerçekleştirildi Karaman’da motosikletin çarptığı 3 yaşındaki çocuk yaralandı Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu. Konya’da depo olarak kullanılan alanda çıkan yangın korkuttu Konya’nın Beyşehir ilçesinde garaj ve depo olarak kullanılan yerde çıkan yangın kısa süreli paniğe neden oldu © 2026 Tv42 Haber, Konya haberleri, Konya Gündem, Konya Haber, Konya Gündemi.</t>
+          <t>EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu - beş kişi tutuklandı KoSSev EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu - beş kişi tutuklandı Haber - Kosova EUROPOL: Yaklaşık 80 milyon euro değerinde mal varlığına el konuldu EUROPOL: Kosova'da yaklaşık 80 milyon euro değerinde mal varlığına el konuldu - beş kişi tutuklandı Haber - Kosova EUROPOL: Yaklaşık 80 milyon euro değerinde mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOZUVDbmhVc3dVRmZsOFFxSDNSbkNnc2FoNEJhY1Y5RWdRYWFtSFlBLXRtYTQ0YnVBc1ZtTTdFdk9oWk1KYS0xN0RjcTREZnR2WFNrQWJ6SWdEVGI4aHR5ZmhHclVwNnk3b0pNOGtNWDRldHc2WEVpZGgzaUt6cGFma2hUYmltQTV0WVFiTnY4OUVBWEhjb3VmdURTSkdDYU42ZmdCRtIBpAFBVV95cUxOZUVDbmhVc3dVRmZsOFFxSDNSbkNnc2FoNEJhY1Y5RWdRYWFtSFlBLXRtYTQ0YnVBc1ZtTTdFdk9oWk1KYS0xN0RjcTREZnR2WFNrQWJ6SWdEVGI4aHR5ZmhHclVwNnk3b0pNOGtNWDRldHc2WEVpZGgzaUt6cGFma2hUYmltQTV0WVFiTnY4OUVBWEhjb3VmdURTSkdDYU42ZmdCRg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Diyarbakır | Isparta | Karaman | Konya | Manisa</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Beyşehir</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>ilçeye bağlı Kurucuova Mahallesi</t>
-        </is>
-      </c>
+          <t>https://kossev.info/tr/europol-zaplenjena-imovina-od-oko-80-miliona-evra-na-kosovu-uhapseno-pet-osoba/</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr"/>
@@ -3637,7 +3125,7 @@
       <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="n">
-        <v>121.5</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>7</v>
@@ -3646,27 +3134,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:50:00</t>
+          <t>2026-06-09 09:02:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı</t>
+          <t>Yasa dışı bahis baronlarına Bursa’dan operasyon: 47 kişinin tüm mal varlığına el konuldu!</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Mersin Haber</t>
+          <t>Yasa dışı bahis baronlarına Bursa’dan operasyon: 47 kişinin tüm mal varlığına el konuldu! bursatv.com.tr</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -3676,60 +3164,44 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>el konuldu, mal varlığı</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Mersin'den haberiniz olsun! Mersin ve ilçelerinden son dakika ve önemli haberler, gelişmeler olayları sunar. Konya'nın Karatay ilçesinde bir mobilya fabrikasında çıkan yangında 1 itfaiye eri ile 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Yangın, itfaiye Mersin'den haberiniz olsun! Mersin ve ilçelerinden son dakika ve önemli haberler, gelişmeler olayları sunar. Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Haber Merkezi • 08 Haziran 2026 18:50 • Güncellendi: 08 Haziran 2026 18:54 Konya'nın Karatay ilçesinde bir mobilya fabrikasında çıkan yangında 1 itfaiye eri ile 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Yangın, itfaiye ekiplerinin ve TOMA'nın hızlı müdahalesi ile kontrol altına alındı. Konya'nın Karatay ilçesinde bir mobilya fabrikasında çıkan yangında 1 itfaiye eri ile 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Yangın, itfaiye ekiplerinin ve TOMA'nın hızlı müdahalesi ile kontrol altına alındı. Facebook X WhatsApp 08 Haziran 2026 18:50 Yangın, saat 17.30 sıralarında Konya'nın merkez ilçelerinden biri olan Karatay'da, Fevzi Çakmak Mahallesi Sedirler Caddesi üzerinde bulunan bir mobilya fabrikasının deposunda meydana geldi. Edinilen bilgilere göre, fabrikanın depo bölümünde henüz belirlenemeyen bir nedenle alevler yükselmeye başladı. Yangını gören vatandaşların ihbarı üzerine, olay yerine itfaiye ekipleri, Konya İl Emniyet Müdürlüğüne bağlı TOMA, sağlık ve polis ekipleri sevk edildi. İtfaiye ekipleri, çıkan yangına müdahaleye başlarken, polis ekipleri ise cadde üzerindeki trafik akışını kontrollü bir şekilde sağladı. Yangın söndürme çalışmalarına TOMA ekipleri de destek verdi. Yaklaşık 1 saatlik süren müdahalenin ardından yangın kontrol altına alındı. Bu süreçte 1 itfaiye eri ve 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Olay anının dron ile görüntülendiği bilgisi de edinildi. Ekiplerin depoda yangın sonrası soğutma çalışmaları sürerken, yangının çıkış sebebinin belirlenmesi için yapılacak incelemenin ardından detayların netleşeceği öğrenildi. Malatya Darende'de Bacağı Kırılan 76 Yaşındaki Adam Ambulans Helikopterle Sevk Edildi Silivri'de Motosiklet Panayırı, Binin Üzerinde Tutkunun Katılımıyla Gerçekleşti Konya Konyaaltı Kaynak: Mersin Haber + IHA İlgili Haberler Yangın, saat 17.30 sıralarında Konya'nın merkez ilçelerinden biri olan Karatay'da, Fevzi Çakmak Mahallesi Sedirler Caddesi üzerinde bulunan bir mobilya fabrikasının deposunda meydana geldi. Edinilen bilgilere göre, fabrikanın depo bölümünde henüz belirlenemeyen bir nedenle alevler yükselmeye başladı. Yangını gören vatandaşların ihbarı üzerine, olay yerine itfaiye ekipleri, Konya İl Emniyet Müdürlüğüne bağlı TOMA, sağlık ve polis ekipleri sevk edildi. İtfaiye ekipleri, çıkan yangına müdahaleye başlarken, polis ekipleri ise cadde üzerindeki trafik akışını kontrollü bir şekilde sağladı. Yangın söndürme çalışmalarına TOMA ekipleri de destek verdi. Yaklaşık 1 saatlik süren müdahalenin ardından yangın kontrol altına alındı. Bu süreçte 1 itfaiye eri ve 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Olay anının dron ile görüntülendiği bilgisi de edinildi. Ekiplerin depoda yangın sonrası soğutma çalışmaları sürerken, yangının çıkış sebebinin belirlenmesi için yapılacak incelemenin ardından detayların netleşeceği öğrenildi. Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Haber Merkezi • 08 Haziran 2026 18:50 • Güncellendi: 08 Haziran 2026 18:54 Konya'nın Karatay ilçesinde bir mobilya fabrikasında çıkan yangında 1 itfaiye eri ile 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Yangın, itfaiye ekiplerinin ve TOMA'nın hızlı müdahalesi ile kontrol altına alındı. Haber Merkezi • 08 Haziran 2026 18:50 • Güncellendi: 08 Haziran 2026 18:54 Konya'nın Karatay ilçesinde bir mobilya fabrikasında çıkan yangında 1 itfaiye eri ile 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Yangın, itfaiye ekiplerinin ve TOMA'nın hızlı müdahalesi ile kontrol altına alındı. Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Yangın, saat 17.30 sıralarında Konya'nın merkez ilçelerinden biri olan Karatay'da, Fevzi Çakmak Mahallesi Sedirler Caddesi üzerinde bulunan bir mobilya fabrikasının deposunda meydana geldi. Edinilen bilgilere göre, fabrikanın depo bölümünde henüz belirlenemeyen bir nedenle alevler yükselmeye başladı. Yangını gören vatandaşların ihbarı üzerine, olay yerine itfaiye ekipleri, Konya İl Emniyet Müdürlüğüne bağlı TOMA, sağlık ve polis ekipleri sevk edildi. İtfaiye ekipleri, çıkan yangına müdahaleye başlarken, polis ekipleri ise cadde üzerindeki trafik akışını kontrollü bir şekilde sağladı. Yangın söndürme çalışmalarına TOMA ekipleri de destek verdi. Yaklaşık 1 saatlik süren müdahalenin ardından yangın kontrol altına alındı. Bu süreçte 1 itfaiye eri ve 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Olay anının dron ile görüntülendiği bilgisi de edinildi. Ekiplerin depoda yangın sonrası soğutma çalışmaları sürerken, yangının çıkış sebebinin belirlenmesi için yapılacak incelemenin ardından detayların netleşeceği öğrenildi.</t>
+          <t>Yasa dışı bahis baronlarına Bursa’dan operasyon: 47 kişinin tüm mal varlığına el konuldu! bursatv.com.tr</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Mersin Haber Mersin'den haberiniz olsun! Konya'nın Karatay ilçesinde bir mobilya fabrikasında çıkan yangında 1 itfaiye eri ile 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Yangın, itfaiye Mersin'den haberiniz olsun! Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Haber Merkezi • 08 Haziran 2026 18:50 • Güncellendi: 08 Haziran 2026 18:54 Konya'nın Karatay ilçesinde bir mobilya fabrikasında çıkan yangında 1 itfaiye eri ile 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Yangın, itfaiye ekiplerinin ve TOMA'nın hızlı müdahalesi ile kontrol altına alındı. Facebook X WhatsApp 08 Haziran 2026 18:50 Yangın, saat 17.30 sıralarında Konya'nın merkez ilçelerinden biri olan Karatay'da, Fevzi Çakmak Mahallesi Sedirler Caddesi üzerinde bulunan bir mobilya fabrikasının deposunda meydana geldi. Edinilen bilgilere göre, fabrikanın depo bölümünde henüz belirlenemeyen bir nedenle alevler yükselmeye başladı. Yangını gören vatandaşların ihbarı üzerine, olay yerine itfaiye ekipleri, Konya İl Emniyet Müdürlüğüne bağlı TOMA, sağlık ve polis ekipleri sevk edildi. İtfaiye ekipleri, çıkan yangına müdahaleye başlarken, polis ekipleri ise cadde üzerindeki trafik akışını kontrollü bir şekilde sağladı. Yangın söndürme çalışmalarına TOMA ekipleri de destek verdi. Yaklaşık 1 saatlik süren müdahalenin ardından yangın kontrol altına alındı. Bu süreçte 1 itfaiye eri ve 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Ekiplerin depoda yangın sonrası soğutma çalışmaları sürerken, yangının çıkış sebebinin belirlenmesi için yapılacak incelemenin ardından detayların netleşeceği öğrenildi. Malatya Darende'de Bacağı Kırılan 76 Yaşındaki Adam Ambulans Helikopterle Sevk Edildi Silivri'de Motosiklet Panayırı, Binin Üzerinde Tutkunun Katılımıyla Gerçekleşti Konya Konyaaltı Kaynak: Mersin Haber + IHA İlgili Haberler Yangın, saat 17.30 sıralarında Konya'nın merkez ilçelerinden biri olan Karatay'da, Fevzi Çakmak Mahallesi Sedirler Caddesi üzerinde bulunan bir mobilya fabrikasının deposunda meydana geldi. Haber Merkezi • 08 Haziran 2026 18:50 • Güncellendi: 08 Haziran 2026 18:54 Konya'nın Karatay ilçesinde bir mobilya fabrikasında çıkan yangında 1 itfaiye eri ile 1 kişi dumandan etkilenerek hastaneye kaldırıldı. Konya Karatay'da Mobilya Fabrikasında Meydana Gelen Yangında 1 İtfaiye Eri Yaralandı Yangın, saat 17.30 sıralarında Konya'nın merkez ilçelerinden biri olan Karatay'da, Fevzi Çakmak Mahallesi Sedirler Caddesi üzerinde bulunan bir mobilya fabrikasının deposunda meydana geldi.</t>
+          <t>Yasa dışı bahis baronlarına Bursa’dan operasyon: 47 kişinin tüm mal varlığına el konuldu! Yasa dışı bahis baronlarına Bursa’dan operasyon: 47 kişinin tüm mal varlığına el konuldu! bursatv.com.tr Yasa dışı bahis baronlarına Bursa’dan operasyon: 47 kişinin tüm mal varlığına el konuldu!</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.mersinhaber.com/haber-konya-karatayda-mobilya-fabrikasinda-meydana-gelen-yanginda-1-itfaiye-eri-yaralandi/663643</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNLUE1MUNuaGJ1Tzh0SVZlZGlSOG9TRlExZHA1dVlyTGViUU44MlliYkZrY2EyYXlMenFOQk1nYVBCTlhSdVdBVHAxb2wxMVdwMk9Kb2dzdWtDVnVIbVJPc2tRMlljUHd1SVdpZkw1Z2VBeHNVbllabWE4OWlranBYc0k3dlZ6a3JfVkh5QS01S3ZOVTNWN3d5MXIyZzRIZk9pMFpBMVZlZmVGbzV4NnJHd3VKWdIBuAFBVV95cUxNUEZvZVVDU2hmeldyUnFSMExCem1jZjdocnU5LXlldzFmR0RMVW91NTFRSjhvYjh3SU94MzZMZ2kyeVNzaVhFcFh5b3NTaUV3NW5wZjdhbFhjYWdnVEVldWNnMW92ZVA0YVF3TFBPN21JRWN3R3ZwUnpMVHFYSEF1T0V3TWpsYUU1eG9YRzJKM0c1UlQwenZqVFpiQ1VCTkNjQ2RCVjJacWlUTDhiekRva2ZOTXVyZXJx?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Konya | Mersin | İstanbul | Malatya</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Silivri | Karatay | Darende</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Fevzi Çakmak Mahallesi</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Fevzi Çakmak Mahallesi Sedirler Caddesi</t>
-        </is>
-      </c>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr"/>
@@ -3743,7 +3215,7 @@
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="n">
-        <v>159.25</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>8</v>
@@ -3752,27 +3224,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 20:27:58</t>
+          <t>2026-06-09 18:33:53</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Yangında depo ve garaj kullanılamaz hale geldi</t>
+          <t>72 yaşındaki tatlıcıdan tüyler ürpertici tarikat iddiası: '7 yıldır evime giremiyorum, mal varlığıma el koydular!</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Yangında depo ve garaj kullanılamaz hale geldi Aksaray Yenigün Gazetesi</t>
+          <t>72 yaşındaki tatlıcıdan tüyler ürpertici tarikat iddiası: '7 yıldır evime giremiyorum, mal varlığıma el koydular! Saray Medya</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3782,32 +3254,28 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>mal varlığı</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Yangında depo ve garaj kullanılamaz hale geldi Aksaray Yenigün Gazetesi</t>
+          <t>72 yaşındaki Adanalı tatlıcı Hasan Masat, ailesinin bir tarikat etkisi altına girdiğini ve bu nedenle mal varlığına el konulup emekli maaşını dahi alamadığını iddia etti. 72 yaşındaki Adanalı tatlıcı Hasan Masat, ailesinin bir tarikat etkisi altına girdiğini ve bu nedenle mal varlığına el konulup emekli maaşını dahi alamadığını iddia etti. 72 yaşındaki Adanalı tatlıcı Hasan Masat, ailesinin bir tarikat etkisi altına girdiğini ve bu nedenle mal varlığına el konulup emekli maaşını dahi alamadığını iddia etti. 72 yaşındaki tatlıcıdan tüyler ürpertici tarikat iddiası: '7 yıldır evime giremiyorum, mal varlığıma el koydular! ASAYİŞ Yayınlanma : 09 Haziran 2026 21:33 Düzenleme : 09 Haziran 2026 21:33 Paylaş Paylaş Paylaş A A Sesli Dinle 72 yaşındaki Adanalı tatlıcı Hasan Masat, ailesinin bir tarikat etkisi altına girdiğini ve bu nedenle mal varlığına el konulup emekli maaşını dahi alamadığını iddia etti. Adana'da 72 yaşındaki ünlü tatlıcı Hasan Masat, hayatının en zorlu mücadelesini veriyor. Kendisinin uyuşturucu kullandığı ve akıl sağlığının yerinde olmadığı yönünde mahkemeden tedbir kararı çıkartıldığını iddia eden Masat, bu durumun ardında oğlunun, eşinin ve kızının bir tarikatın etkisi altına girmesinin yattığını öne sürüyor. Emekli maaşı, araçları ve sahip olduğu tüm mal varlığı üzerinde tedbir kararı olmasının kendisini mağdur ettiğini belirten Masat, yaşadıklarını 'kabus' olarak tanımlıyor. AİLESİ TARİKAT ETKİSİ ALTINDA İDDİASI Kentte birçok şubesi bulunan ve tatlıcılık sektöründe tanınan Hasan Masat, yaşadığı dramı şöyle anlatıyor: " 7-8 yıldır evime bile giremiyorum. Bir tarikata takıldılar. Ben biat etmeyince üzerime yürüdüler. " Masat, bu tarikatın etkisiyle kendisine karşı haksız kararlar aldırıldığını savunuyor. Niğde'deki bahçesinde 3 yıl geçirdiğini, hatta dükkanının bile 2 buçuk ay kapalı kaldığını söylüyor. 2017 yılından beri ailesinden uzak durduğunu ve yaşadığı zorluklara rağmen tırnaklarıyla kazıyarak geldiği bu noktada, tatlıcılıkla özdeşleşen aracının parçalandığını da ekliyor. MAL VARLIĞINA TEDBİR, EMEKLİ MAAŞINA EL KONULDU Masat, hakkında uyuşturucu kullandığı, akıl sağlığının yerinde olmadığı ve gerçek dışı bir yaşam sürdüğü gerekçeleriyle mal varlıkları üzerinde tedbir kararı çıkarıldığını dile getiriyor. Bu kararların oğlunun avukatları tarafından alındığını ve tüm malına çökmek istediklerini iddia ediyor. Sekiz dokuz dükkanı olduğunu ancak sadece ilk göz ağrısı olan dükkanının kaldığını belirtiyor. İki yıldır emekli maaşını bile alamadığını, araçlarına kadar tedbir konulduğunu vurguluyor. Yaşadığı darp olaylarına ve küfürlere maruz kaldığına dikkat çekerek, kamera kayıtlarının neden incelenmediğini sorguluyor. Kendisinin sigara bile içmediğini, ancak hakkında uyuşturucu kullandığına dair polis raporları hazırlandığını ve mahkemeye sehven düzeltme gönderildiğini ancak bu lekenin üzerine atıldığını söylüyor. Allah'a ve adalete güvendiğini belirten Masat, yaşadığı mağduriyetin bir an önce giderilmesini umuyor. #Tarikatiddiaları #Tatlıcıdramı İHA Yorum Yaz Son Dakika 1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Yangında depo ve garaj kullanılamaz hale geldi Yangında depo ve garaj kullanılamaz hale geldi Aksaray Yenigün Gazetesi Yangında depo ve garaj kullanılamaz hale geldi Aksaray Yenigün Gazetesi</t>
+          <t>72 yaşındaki tatlıcıdan tüyler ürpertici tarikat iddiası: '7 yıldır evime giremiyorum, mal varlığıma el koydular! 72 yaşındaki tatlıcıdan tüyler ürpertici tarikat iddiası: '7 yıldır evime giremiyorum, mal varlığıma el koydular! Saray Medya 72 yaşındaki Adanalı tatlıcı Hasan Masat, ailesinin bir tarikat etkisi altına girdiğini ve bu nedenle mal varlığına el konulup emekli maaşını dahi alamadığını iddia etti. 72 yaşındaki tatlıcıdan tüyler ürpertici tarikat iddiası: '7 yıldır evime giremiyorum, mal varlığıma el koydular! ASAYİŞ Yayınlanma : 09 Haziran 2026 21:33 Düzenleme : 09 Haziran 2026 21:33 P</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://yenigungazete.com/asayis/yanginda-depo-ve-garaj-kullanilamaz-hale-geldi/</t>
+          <t>https://www.saraymedya.com/haber/72-yasindaki-tatlicidan-tuyler-urpertici-tarikat-iddiasi-7-yildir-evime-giremiyorum-mal-varligima-el-koydular_270302/</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
@@ -3833,7 +3301,7 @@
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="n">
-        <v>49.46</v>
+        <v>118.75</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>9</v>
@@ -3842,12 +3310,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 12:53:44</t>
+          <t>2026-06-09 10:17:02</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3857,12 +3325,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Beyşehir Kurucuova’da Garaj ve Depoda Yangın Paniği</t>
+          <t>Konya'da Fabrika Yangını: İtfaiye Eri Mehmet Tekeli Şehit Oldu</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Beyşehir Kurucuova’da Garaj ve Depoda Yangın Paniği bgrt.com.tr</t>
+          <t>Konya'da Fabrika Yangını: İtfaiye Eri Mehmet Tekeli Şehit Oldu SonDakika</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3872,36 +3340,44 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Beyşehir Kurucuova’da Garaj ve Depoda Yangın Paniği bgrt.com.tr</t>
+          <t>Konya Karatay'da bir yatak fabrikasında çıkan yangında, işçileri tahliye eden itfaiye eri Mehmet Tekeli, yoğun duman arasında karbonmonoksit gazından zehirlenerek şehit düştü. 18 yıllık görev süresinde birçok afette yer alan Tekeli, 100 yıllık Konya İtfaiye Teşkilatı'nın ilk şehidi oldu. Törende annesi Maynur Tekeli tabutuna sarılarak gözyaşı döktü. Konya Karatay'da bir yatak fabrikasında çıkan yangında, işçileri tahliye eden itfaiye eri Mehmet Tekeli, yoğun duman arasında karbonmonoksit gazından zehirlenerek şehit düştü. 18 yıllık görev süresinde birçok afette yer alan Tekeli, 100 yıllık Konya İtfaiye Teşkilatı'nın ilk şehidi oldu. Törende annesi Maynur Tekeli tabutuna sarılarak gözyaşı döktü. Konya Karatay'da bir yatak fabrikasında çıkan yangında, işçileri tahliye eden itfaiye eri Mehmet Tekeli, yoğun duman arasında karbonmonoksit gazından zehirlenerek şehit düştü. 18 yıllık görev süresinde birçok afette yer alan Tekeli, 100 yıllık Konya İtfaiye Teşkilatı'nın ilk şehidi oldu. Törende annesi Maynur Tekeli tabutuna sarılarak gözyaşı döktü.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Beyşehir Kurucuova’da Garaj ve Depoda Yangın Paniği Beyşehir Kurucuova’da Garaj ve Depoda Yangın Paniği bgrt.com.tr Beyşehir Kurucuova’da Garaj ve Depoda Yangın Paniği bgrt.com.tr</t>
+          <t>Konya'da Fabrika Yangını: İtfaiye Eri Mehmet Tekeli Şehit Oldu Konya'da Fabrika Yangını: İtfaiye Eri Mehmet Tekeli Şehit Oldu SonDakika Konya Karatay'da bir yatak fabrikasında çıkan yangında, işçileri tahliye eden itfaiye eri Mehmet Tekeli, yoğun duman arasında karbonmonoksit gazından zehirlenerek şehit düştü. 18 yıllık görev süresinde birçok afette yer alan Tekeli, 100 yıllık Konya İtfaiye Teşkilatı'nın ilk şehidi oldu. Törende annesi Maynur Tekeli tabutuna sarılarak gözyaşı döktü.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNclpiUUZhc0ZsQjJ4eklTdmNXNlFSLTNaVF9rUDkxbWd1QzZJQTVXYktfMllydlJUQk9RTEhteFVQaDFUa0dlY0JVZEVCcnhkemo3eHZaUWV6SWE0TmJBd01zRGoxcDFtcUJmVzVib0xjWmhVU1p1UGtkT0VmYi1rVmc0RW9MVWxzcGFwaVBjOENDdw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>https://www.sondakika.com/amp/haber-konya-da-fabrika-yangini-itfaiye-eri-mehmet-tekeli-19928544/</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Konya</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Karatay</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -3909,7 +3385,7 @@
       <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr"/>
@@ -3923,7 +3399,7 @@
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="n">
-        <v>49.88</v>
+        <v>95.55</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>10</v>
@@ -3932,7 +3408,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 07:26:00</t>
+          <t>2026-06-10 01:30:45</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3947,12 +3423,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını: Ekiplerin müdahalesi sürüyor Olay yerine çok sayıda ekip sevk edildi</t>
+          <t>Bir ağaç işleme şirketinin fabrikasında 17.000 m²'den fazla alanı yok eden yangının sebebi araştırılıyor.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını: Ekiplerin müdahalesi sürüyor Olay yerine çok sayıda ekip sevk edildi Habertürk</t>
+          <t>Bir ağaç işleme şirketinin fabrikasında 17.000 m²'den fazla alanı yok eden yangının sebebi araştırılıyor. Vietnam.vn</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3962,22 +3438,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>fabrika, şirket</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>fabrika | şirket / firma</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını: Ekiplerin müdahalesi sürüyor Olay yerine çok sayıda ekip sevk edildi Habertürk</t>
+          <t>Bir ağaç işleme şirketinin fabrikasında 17.000 m²'den fazla alanı yok eden yangının sebebi araştırılıyor. Vietnam.vn</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep'te fabrika yangını: Ekiplerin müdahalesi sürüyor Olay yerine çok sayıda ekip sevk edildi Gaziantep'te fabrika yangını: Ekiplerin müdahalesi sürüyor Olay yerine çok sayıda ekip sevk edildi Habertürk Gaziantep'te fabrika yangını: Ekiplerin müdahalesi sürüyor Olay yerine çok sayıda ekip sevk edildi Habertürk</t>
+          <t>Bir ağaç işleme şirketinin fabrikasında 17.000 m²'den fazla alanı yok eden yangının sebebi araştırılıyor. Bir ağaç işleme şirketinin fabrikasında 17.000 m²'den fazla alanı yok eden yangının sebebi araştırılıyor. Vietnam.vn Bir ağaç işleme şirketinin fabrikasında 17.000 m²'den fazla alanı yok eden yangının sebebi araştırılıyor.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -3987,14 +3463,10 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQTXJ0OWlHZlk2Z3NwT0Vpcm9rWHFoX1E1OU13WHBIODNDTFhBSDlRbGJDUC1aUkJzUDZjQTQ3NWhrazdXaGJZQVlGQnhldlhVeG9wRHNKVmRVeUZXc0Zxbl80MDBSWlV3cmEyMWFPM2RQX0VvSjFzeEMxQ244SFhLRmJlUnV3T2lRYXQzRGNYYkdqQTRlVVBpUE93U1JsaHNwZlA2dUt5a3BveDhuR0htMGpuT2NkekpERi0wa0RNaTFpOEpiYU1iNVY1Tmc3ZVF5Tmg3RkxpSFBXbEFV?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Gaziantep</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbmhoX01DMzRnVDg4Y2x0d2toQTVwMnBWZXBISy1fT3p4dGFtdG1LaWhZenBzaGRQVDJaVHBNamxfMGlKdUY4b2huR2FrcUZ3a3pGNGcyV0RsekF1T2pacUJvOFdiUm4xM3gzb2xzUlhVS1ZkNDQyTVlfNjRvLUQ0b1lpNVZfV0d3dnFUOG0wN2pBVVE4ZWE3ZHMxLWpJS0dLS1BKb25R?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -4003,7 +3475,7 @@
       <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr"/>
@@ -4017,7 +3489,7 @@
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="n">
-        <v>103.08</v>
+        <v>98.66</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>11</v>
@@ -4026,7 +3498,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 08:23:00</t>
+          <t>2026-06-09 20:48:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -4041,12 +3513,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor</t>
+          <t>Gaziantep'te 14 saat süren fabrika yangını söndürüldü</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Mersin Haber</t>
+          <t>Gaziantep'te 14 saat süren fabrika yangını söndürüldü Referans Gazetesi</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -4056,18 +3528,22 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>organize sanayi, sanayi</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Mersin'den haberiniz olsun! Mersin ve ilçelerinden son dakika ve önemli haberler, gelişmeler olayları sunar. Gaziantep'te bir tekstil fabrikasında çıkan yangına müdahale devam ediyor. Olayda ölü veya yaralı bulunmuyor. Mersin'den haberiniz olsun! Mersin ve ilçelerinden son dakika ve önemli haberler, gelişmeler olayları sunar. Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Haber Merkezi • 09 Haziran 2026 11:23 • Güncellendi: 09 Haziran 2026 11:25 Gaziantep'te bir tekstil fabrikasında çıkan yangına müdahale devam ediyor. Olayda ölü veya yaralı bulunmuyor. Gaziantep'te bir tekstil fabrikasında çıkan yangına müdahale devam ediyor. Olayda ölü veya yaralı bulunmuyor. Facebook X WhatsApp 09 Haziran 2026 11:23 Yangın, Gaziantep 5. Organize Sanayi Bölgesi'nde yer alan Molhan Tekstil fabrikasında meydana geldi. Bilinmeyen bir sebepten dolayı başlayan yangın, kısa süre içerisinde hızla yayıldı. Yangın ihbarı üzerine, 112 acil çağrı merkezine başvuruldu ve hemen ardından olay yerine çok sayıda itfaiye, sağlık, polis ve AFAD ekibi gönderildi. İtfaiye ekipleri, fabrikayı saran alevlere müdahaleye başladı. Yangın söndürme çalışmaları sürerken, olayda herhangi bir can kaybı veya yaralanma olmadığı bildirildi. Yangınla mücadele çalışmaları devam ediyor. Şanlıurfa'da 14 Kilometrelik Grup Yolunda Sıcak Asfalt Çalışmaları Sürüyor Kopenhag'da Maersk Şirketinin İsrail'e Silah Parçaları Taşıdığı İddia Edildi Gaziantep Kaynak: Mersin Haber + IHA İlgili Haberler Yangın, Gaziantep 5. Organize Sanayi Bölgesi'nde yer alan Molhan Tekstil fabrikasında meydana geldi. Bilinmeyen bir sebepten dolayı başlayan yangın, kısa süre içerisinde hızla yayıldı. Yangın ihbarı üzerine, 112 acil çağrı merkezine başvuruldu ve hemen ardından olay yerine çok sayıda itfaiye, sağlık, polis ve AFAD ekibi gönderildi. İtfaiye ekipleri, fabrikayı saran alevlere müdahaleye başladı. Yangın söndürme çalışmaları sürerken, olayda herhangi bir can kaybı veya yaralanma olmadığı bildirildi. Yangınla mücadele çalışmaları devam ediyor. Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Haber Merkezi • 09 Haziran 2026 11:23 • Güncellendi: 09 Haziran 2026 11:25 Gaziantep'te bir tekstil fabrikasında çıkan yangına müdahale devam ediyor. Olayda ölü veya yaralı bulunmuyor. Haber Merkezi • 09 Haziran 2026 11:23 • Güncellendi: 09 Haziran 2026 11:25 Gaziantep'te bir tekstil fabrikasında çıkan yangına müdahale devam ediyor. Olayda ölü veya yaralı bulunmuyor. Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Yangın, Gaziantep 5. Organize Sanayi Bölgesi'nde yer alan Molhan Tekstil fabrikasında meydana geldi. Bilinmeyen bir sebepten dolayı başlayan yangın, kısa süre içerisinde hızla yayıldı. Yangın ihbarı üzerine, 112 acil çağrı merkezine başvuruldu ve hemen ardından olay yerine çok sayıda itfaiye, sağlık, polis ve AFAD ekibi gönderildi. İtfaiye ekipleri, fabrikayı saran alevlere müdahaleye başladı. Yangın söndürme çalışmaları sürerken, olayda herhangi bir can kaybı veya yaralanma olmadığı bildirildi. Yangınla mücadele çalışmaları devam ediyor.</t>
+          <t>Gaziantep'te Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren tekstil fabrikasında çıkan yangın 14 saatlik hummalı çalışmalar sonucunda söndürüldü. Gaziantep'te Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren tekstil fabrikasında çıkan yangın 14 saatlik hummalı çalışmalar sonucunda söndürüldü. Gaziantep'te Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren tekstil fabrikasında çıkan yangın 14 saatlik hummalı çalışmalar sonucunda söndürüldü. Gaziantep'te 14 saat süren fabrika yangını söndürüldü Gaziantep'te Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren tekstil fabrikasında çıkan yangın 14 saatlik hummalı çalışmalar sonucunda söndürüldü. Mansur Yalvaç Editör 09.06.2026 - 23:48 Yayınlanma 1 Paylaşım 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 5. OSB'de bulunan bir tekstil fabrikasında henüz bilinmeyen nedenle yangın çıktı. İhbar üzerine olay yerine itfaiye, polis ve sağlık ekipleri sevk edildi. Gaziantep Büyükşehir Belediye Başkan Vekili Halil Uğur, AA muhabirine, saat 09.04'te İtfaiye Daire Başkanlığına yangın ihbarı geldiğini belirterek, ihbardan 6 dakika sonra ekiplerin olay yerine yetiştiğini söyledi. Elyaf pamuk ipliği üreten bir tesiste yangın çıktığını ifade eden Uğur, şu bilgileri verdi: "Yangın içeriği ile ilgili araştırmalar devam ediyor. Önemli olan can kaybının olmaması, bu bizler için sevindirici bir durum. Bu arada Büyükşehir İtfaiye Daire Başkanlığı, OSB İtfaiye Müdürlüğü ekipleri ve diğer belediyelerin desteğiyle 50'ye yakın araç, 100'den fazla personelle yangın kontrol altına alındı. Fabrika çok ciddi hasar aldı. Yangın çıkış sebebiyle ilgili olarak gerek bizim arkadaşlarımız gerek şube müdürlüğümüzle birlikte yapacağımız çalışmalar ortaya net raporlar çıkacak." Yaklaşık 14 saatlik çalışma sonrası yangın söndürülürken soğutma çalışması tamamlandı. Kaynak: AA Editörün Seçtiği Gaziantep FK’nın 2025-2026 sezonu istatistikleri! 3 teknik direktör ve tüm skorlar… Editörün Seçtiği Gaziantep FK’da Draguş-Camara takası bombası Editörün Seçtiği Gaziantep’te Konkordato furyası sürüyor… O firma ile ilgili flaş karar! Editör Hakkında Mansur Yalvaç Lisans eğitimini Atatürk Üniversitesi İletişim Fakültesi Gazetecilik Bölümü'nde tamamladıktan sonra, YL eğitimini GAÜN Sosyal Bilimler Enstitüsü'nde İletişim ve T. D. Ana Bilim Dalı'nda “Medyada Anlam İnşası: Bitcoin Örneği” başlıklı teziyle tamamladı. 2014 yılında başladığı profesyonel kariyerini halen Referansgazetesi.com.tr'de Güncel, Spor, Sağlık ve Ekonomi Editörü olarak sürdürmektedir. Bunlar</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Gaziantep Şehri 5. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Mersin Haber Mersin'den haberiniz olsun! Gaziantep'te bir tekstil fabrikasında çıkan yangına müdahale devam ediyor. Olayda ölü veya yaralı bulunmuyor. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Haber Merkezi • 09 Haziran 2026 11:23 • Güncellendi: 09 Haziran 2026 11:25 Gaziantep'te bir tekstil fabrikasında çıkan yangına müdahale devam ediyor. Facebook X WhatsApp 09 Haziran 2026 11:23 Yangın, Gaziantep 5. Organize Sanayi Bölgesi'nde yer alan Molhan Tekstil fabrikasında meydana geldi. Bilinmeyen bir sebepten dolayı başlayan yangın, kısa süre içerisinde hızla yayıldı. Yangın ihbarı üzerine, 112 acil çağrı merkezine başvuruldu ve hemen ardından olay yerine çok sayıda itfaiye, sağlık, polis ve AFAD ekibi gönderildi. İtfaiye ekipleri, fabrikayı saran alevlere müdahaleye başladı. Yangın söndürme çalışmaları sürerken, olayda herhangi bir can kaybı veya yaralanma olmadığı bildirildi. Yangınla mücadele çalışmaları devam ediyor. Şanlıurfa'da 14 Kilometrelik Grup Yolunda Sıcak Asfalt Çalışmaları Sürüyor Kopenhag'da Maersk Şirketinin İsrail'e Silah Parçaları Taşıdığı İddia Edildi Gaziantep Kaynak: Mersin Haber + IHA İlgili Haberler Yangın, Gaziantep 5. Haber Merkezi • 09 Haziran 2026 11:23 • Güncellendi: 09 Haziran 2026 11:25 Gaziantep'te bir tekstil fabrikasında çıkan yangına müdahale devam ediyor. Organize Sanayi Bölgesi'nde Yangın Söndürme Çalışmaları Sürüyor Yangın, Gaziantep 5.</t>
+          <t>Gaziantep'te 14 saat süren fabrika yangını söndürüldü Gaziantep'te 14 saat süren fabrika yangını söndürüldü Referans Gazetesi Gaziantep'te Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren tekstil fabrikasında çıkan yangın 14 saatlik hummalı çalışmalar sonucunda söndürüldü. Gaziantep'te 14 saat süren fabrika yangını söndürüldü Gaziantep'te Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren tekstil fabrikasında çıkan yangın 14 saatlik hummalı çalışmalar sonucunda söndürüldü. Mansur Yalvaç Editör 09.06.2026 - 23:48 Yayınlanma 1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -4077,61 +3553,41 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.mersinhaber.com/haber-gaziantepte-fabrika-yanginina-mudahale-suruyor/664032</t>
+          <t>https://www.referansgazetesi.com.tr/gaziantepte-14-saat-suren-fabrika-yangini-sonduruldu</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep | Mersin | Şanlıurfa</t>
+          <t>Gaziantep</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>te Organize Sanayi</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Organize Sanayi</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>Organize Sanayi:292:body+summary+title</t>
-        </is>
-      </c>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>Organize Sanayi Gaziantep Türkiye</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Gaziantep Organize Sanayi Bölgesi | Organize Sanayi 1. Kısım | Gaziantep Organize Sanayi/Gaziantep | Organize Sanayi Bölgesi</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>Gaziantep Organize Sanayi Bölgesi</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>100.0 | 100.0 | 100.0 | 100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="n">
-        <v>211.75</v>
+        <v>99.25</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>12</v>
@@ -4140,7 +3596,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:15:22</t>
+          <t>2026-06-10 01:55:48</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4155,12 +3611,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Konya’da yatak fabrikasında yangın! Kompresör patladı: İtfaiye eri yaralandı</t>
+          <t>Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Konya’da yatak fabrikasında yangın! Kompresör patladı: İtfaiye eri yaralandı | YEREL HABERLER GZT</t>
+          <t>Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti. Vietnam.vn</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -4180,38 +3636,38 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Konya’da yatak fabrikasında yangın! Kompresör patladı: İtfaiye eri yaralandı | YEREL HABERLER GZT</t>
+          <t>Ho Chi Minh şehrindeki yetkililer, Binh Co semtindeki bir şirkette çıkan ve yaklaşık 17.000 metrekarelik fabrika alanını yok eden büyük yangın olay yerini kordon altına alarak soruşturma başlattı. Ho Chi Minh şehrindeki yetkililer, Binh Co semtindeki bir şirkette çıkan ve yaklaşık 17.000 metrekarelik fabrika alanını yok eden büyük yangın olay yerini kordon altına alarak soruşturma başlattı. Ho Chi Minh şehrindeki yetkililer, Binh Co semtindeki bir şirkette çıkan ve yaklaşık 17.000 metrekarelik fabrika alanını yok eden büyük yangın olay yerini kordon altına alarak soruşturma başlattı. Vietnam.vn'i takip et G o o g l e News 0 Yangın yeri. Fotoğraf: VTC News . 10 Haziran sabahı, Ho Chi Minh Şehri Polisi'ne bağlı 32. Bölge İtfaiye ve Kurtarma Ekibi (PC07), Ho Chi Minh Şehri, Binh Co Mahallesi, 1. Bölge'de (eski adıyla Tan Uyen, Binh Duong) bulunan GO Co., Ltd. şirketindeki yangının nedenini araştırmak, hasarı değerlendirmek ve incelemek için diğer profesyonel birimlerle koordinasyon içinde çalışmalarına devam etti. Bu şirket ahşap mobilya ve kanepe imalatında uzmanlaşmıştır ve ayrıca bir kağıt laminasyon atölyesine sahiptir. İlk bilgilere göre, 9 Haziran günü saat 22:10 civarında, çalışanlar ve bölge sakinleri şirketin mobilya üretim atölyesinde yangın çıktığını fark etti. Yangın fark edildikten hemen sonra, olay yerindeki itfaiye ekibi ve işçiler taşınabilir yangın söndürücülerle su kullanarak alevleri söndürdüler. Ancak, içerideki büyük miktardaki ahşap ve yanıcı madde nedeniyle yangın hızla yayıldı ve tüm fabrika alanını sardı. Yangının kontrol altına alınamayacak bir boyutta olduğunu anlayan bölge sakinleri durumu yetkililere bildirdi. Bunlar da ilginizi çekebilir Hung Yen, VNeID'yi halka daha da yaklaştırmak amacıyla Dijital Yaz Kampanyasını başlattı. (PLVN) - Hung Yen İl Emniyet Müdürlüğü, İl Gençlik Birliği ve İl Kadın Birliği ile koordinasyon içinde, dijital vatandaşlara rehberlik etmek ve insanlara Hükümet Projesi 06'yı uygulamada eşlik etmek amacıyla "VNeID ile Dijital Yaz Kampanyası"nın lansman törenini düzenledi. Saat 22:21'de yangın fabrikayı tamamen sarmıştı. Fotoğraf: VTC News . İhbarı alan 32. Bölge İtfaiye ve Kurtarma Ekibi, yangını söndürmek ve yayılmasını önlemek için bir plan uygulamak üzere olay yerine çok sayıda özel araç ve onlarca subay ve asker gönderdi. Yetkililer ilk etapta yangının her biri yaklaşık 8.500 m²'lik iki atölyede çıktığını ve toplamda yaklaşık 17.000 m²'lik bir alanı etkilediğini belirledi. Yangında en çok yanıcı madde olarak ahşap ve boya bulunduğu için, yangın hızla yayıldı, kontrol altına alma çabaları önemli zorluklar yarattı ve komşu yapılara sıçrama riski oluşturdu. Gece yarısından sonra bile, İtfaiye ve Kurtarma Polisi, çevredeki alanı kontrol altına almak ve korumak için birden fazla itfaiye ekibini görevde tutmaya devam etti. Olayda can kaybı yaşanmadı ve maddi hasar tespit çalışmaları devam ediyor. Yangının nedeni ise hala araştırılıyor. Bunlar da ilginizi çekebilir 75 yaşındaki bir öğretmen, eşsiz bir sanat eseriyle 2026 Dünya Kupası'nı karşılıyor. (HTV) - Ho Chi Minh şehrinde yaşayan 75 yaşındaki emekli bir öğretmen, yumurta kabuklarından yapılmış üç adet 2026 Dünya Kupası maskotunu tamamladı. Kartal Clutch, geyik Maple ve leopar Zayu'dan oluşan bu eserler, sadece yaratıcılığı sergilemekle kalmıyor, aynı zamanda bu olağanüstü sanatçının yıllar içinde geliştirdiği futbol sevgisini de somutlaştırıyor. Kaynak: https://znews.vn/lua-thieu-rui-17000-m-nha-xuong-tai-tphcm-trong-dem-post1658273.html Vietnam.vn'i takip et G o o g l e News 0 Yorum ( 0 ) Yangın yeri. Fotoğraf: VTC News . 10 Haziran sabahı, Ho Chi Minh Şehri Polisi'ne bağlı 32. Bölge İtfaiye ve Kurtarma Ekibi (PC07), Ho Chi Minh Şehri, Binh Co Mahallesi, 1. Bölge'de (eski adıyla Tan Uyen, Binh Duong) bulunan GO Co., Ltd. şirketindeki yangının nedenini araştırmak, hasarı değerlendirmek ve incelemek için diğer profesyonel birimlerle koordinasyon içinde çalışmalarına devam etti. Yangın yeri. Fotoğraf: VTC News . 10 Haziran sabahı, Ho Chi Minh Şehri Polisi'ne bağlı 32. Bölge İtfaiye ve Kurtarma Ekibi (PC07), Ho Chi Minh Şehri, Binh Co Mahallesi, 1. Bölge'de (eski adıyla Tan Uyen, Binh Duong) bulunan GO Co., Ltd. şirketindeki yangının nedenini araştırmak, hasarı değerlendirmek ve incelemek için diğer profesyonel birimlerle koordinasyon içinde çalışmalarına devam etti. Bu şirket ahşap mobilya ve kanepe imalatında uzmanlaşmıştır ve ayrıca bir kağıt laminasyon atölyesine sahiptir. İlk bilgilere göre, 9 Haziran günü saat 22:10 civarında, çalışanlar ve bölge sakinleri şirketin mobilya üretim atölyesinde yangın çıktığını fark etti. Yangın fark edildikten hemen sonra, olay yerindeki itfaiye ekibi ve işçiler taşınabilir yangın söndürücülerle su kullanarak alevleri söndürdüler. Ancak, içerideki büyük miktardaki ahşap ve yanıcı madde nedeniyle yangın hızla yayıldı ve tüm fabrika alanını sardı. Yangının kontrol altına alınamayacak bir boyutta olduğunu anlayan bölge sakinleri durumu yetkililere bildirdi. Bunlar da ilginizi çekebilir Hung Yen, VNeID'yi halka daha da yaklaştırmak amacıyla Dijital Yaz Kampanyasını başlattı. (PLVN) - Hung Yen İl Emniyet Müdürlüğü, İl Gençlik Birliği ve İl Kadın Birliği ile koordinasyon içinde, dijital vatandaşlara rehberlik etmek ve insanlara Hükümet Projesi 06'yı uygulamada eşlik etmek amacıyla "VNeID ile Dijital Yaz Kampanyası"nın lansman törenini düzenledi. Saat 22:21'de yangın fabrikayı tamamen sarmıştı. Fotoğraf: VTC News . İhbarı alan 32. Bölge İtfaiye ve Kurtarma Ekibi, yangını söndürmek ve yayılmasını önlemek için bir plan uygulamak üzere olay yerine çok sayıda özel araç ve onlarca subay ve asker gönderdi. Yetkililer ilk etapta yangının her biri yaklaşık 8.500 m²'lik iki atölyede çıktığını ve toplamda yaklaşık 17.000 m²'lik bir alanı etkilediğini belirledi. Yangında en çok yanıcı madde olarak ahşap ve boya bulunduğu için, yangın hızla yayıldı, kontrol altına alma çabaları önemli zorluklar yarattı ve komşu yapılara sıçrama riski oluşturdu. Gece yarısından sonra bile, İtfaiye ve Kurtarma Polisi, çevredeki alanı kontrol altına almak ve korumak için birden fazla itfaiye ekibini görevde tutmaya devam etti. Olayda can kaybı yaşanmadı ve maddi hasar tespit çalışmaları devam ediyor. Yangının nedeni ise hala araştırılıyor. Bunlar da ilginizi çekebilir 75 yaşındaki bir öğretmen, eşsiz bir sanat eseriyle 2026 Dünya Kupası'nı karşılıyor. (HTV) - Ho Chi Minh şehrinde yaşayan 75 yaşındaki emekli bir öğretmen, yumurta kabuklarından yapılmış üç adet 2026 Dünya Kupası maskotunu tamamladı. Kartal Clutch, geyik Maple ve leopar Zayu'dan oluşan bu eserler, sadece yaratıcılığı sergilemekle kalmıyor, aynı zamanda bu olağanüstü sanatçının yıllar içinde geliştirdiği futbol sevgisini de somutlaştırıyor. Kaynak: https://znews.vn/lua-thieu-rui-17000-m-nha-xuong-tai-tphcm-trong-dem-post1658273.html Bu şirket ahşap mobilya ve kanepe imalatında uzmanlaşmıştır ve ayrıca bir kağıt laminasyon atölyesine sahiptir. İlk bilgilere göre, 9 Haziran günü saat 22:10 civarında, çalışanlar ve bölge sakinleri şirketin mobilya üretim atölyesinde yangın çıktığını fark etti. Yangın fark edildikten hemen sonra, olay yerindeki itfaiye ekibi ve işçiler taşınabilir yangın söndürücülerle su kullanarak alevleri söndürdüler. Ancak, içerideki büyük miktardaki ahşap ve yanıcı madde nedeniyle yangın hızla yayıldı ve tüm fabrika alanını sardı. Yangının kontrol altına alınamayacak bir boyutta olduğunu anlayan bölge sakinleri durumu yetkililere bildirdi. Saat 22:21'de yangın fabrikayı tamamen sarmıştı. Fotoğraf: VTC News . İhbarı alan 32. Bölge İtfaiye ve Kurtarma Ekibi, yangını söndürmek ve yayılmasını önlemek için bir plan uygulamak üzere olay yerine çok sayıda özel araç ve onlarca subay ve asker gönderdi. Yetkililer ilk etapta yangının her biri yaklaşık 8.500 m²'lik iki atölyede çıktığını ve toplamda yaklaşık 17.000 m²'lik bir alanı etkilediğini belirledi. Yangında en çok yanıcı madde olarak ahşap ve boya bulunduğu için, yangın hızla yayıldı, kontrol altına alma çabaları önemli zorluklar yarattı ve komşu yapılara sıçrama riski oluşturdu. Gece yarısından sonra bile, İtfaiye ve Kurtarma Polisi, çevredeki alanı kontrol altına almak ve korumak için birden fazla itfaiye ekibini görevde tutmaya devam etti. Olayda can kaybı yaşanmadı ve maddi hasar tespit çalışmaları devam ediyor. Yangının nedeni ise hala araştırılıyor. Kaynak: https://znews.vn/lua-thieu-rui-17000-m-nha-xuong-tai-tphcm-trong-dem-post1658273.html Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti. Ho Chi Minh şehrindeki yetkililer, Binh Co semtindeki bir şirkette çıkan ve yaklaşık 17.000 metrekarelik fabrika alanını yok eden büyük yangın olay yerini kordon altına alarak soruşturma başlattı. ZNews • 10/06/2026 Vietnam.vn'i takip et G o o g l e News 0 Yangın yeri. Fotoğraf: VTC News . 10 Haziran sabahı, Ho Chi Minh Şehri Polisi'ne bağlı 32. Bölge İtfaiye ve Kurtarma Ekibi (PC07), Ho Chi Minh Şehri, Binh Co Mahallesi, 1. Bölge'de (eski adıyla Tan Uyen, Binh Duong) bulunan GO Co., Ltd. şirketindeki yangının nedenini araştırmak, hasarı değerlendirmek ve incelemek için diğer profesyonel birimlerle koordinasyon içinde çalışmalarına devam etti. Bu şirket ahşap mobilya ve kanepe imalatında uzmanlaşmıştır ve ayrıca bir kağıt laminasyon atölyesine sahiptir. İlk bilgilere göre, 9 Haziran günü saat 22:10 civarında, çalışanlar ve bölge sakinleri şirketin mobilya üretim atölyesinde yangın çıktığını fark etti. Yangın fark edildikten hemen sonra, olay yerindeki itfaiye ekibi ve işçiler taşınabilir yangın söndürücülerle su kullanarak alevleri söndürdüler. Ancak, içerideki büyük miktardaki ahşap ve yanıcı madde nedeniyle yangın hızla yayıldı ve tüm fabrika alanını sardı. Yangının kontrol altına alınamayacak bir boyutta olduğunu anlayan bölge sakinleri durumu yetkililere bildirdi. Bunlar da ilginizi çekebilir Hung Yen, VNeID'yi halka daha da yaklaştırmak amacıyla Dijital Yaz Kampanyasını başlattı. (PLVN) - Hung Yen İl Emniyet Müdürlüğü, İl Gençlik Birliği ve İl Kadın Birliği ile koordinasyon içinde, dijital vatandaşlara rehberlik etmek ve insanlara Hükümet Projesi 06'yı uygulamada eşlik etmek amacıyla "VNeID ile Dijital Yaz Kampanyası"nın lansman törenini düzenledi. Saat 22:21'de yangın fabrikayı tamamen sarmıştı. Fotoğraf: VTC News . İhbarı alan 32. Bölge İtfaiye ve Kurtarma Ekibi, yangını söndürmek ve yayılmasını önlemek için bir plan uygulamak üzere olay yerine çok sayıda özel araç ve onlarca subay ve asker gönderdi. Yetkililer ilk etapta yangının her biri yaklaşık 8.500 m²'lik iki atölyede çıktığını ve toplamda yaklaşık 17.000 m²'lik bir alanı etkilediğini belirledi. Yangında en çok yanıcı madde olarak ahşap ve boya bulunduğu için, yangın hızla yayıldı, kontrol altına alma çabaları önemli zorluklar yarattı ve komşu yapılara sıçrama riski oluşturdu. Gece yarısından sonra bile, İtfaiye ve Kurtarma Polisi, çevredeki alanı kontrol altına almak ve korumak için birden fazla itfaiye ekibini görevde tutmaya devam etti. Olayda can kaybı yaşanmadı ve maddi hasar tespit çalışmaları devam ediyor. Yangının nedeni ise hala araştırılıyor. Bunlar da ilginizi çekebilir 75 yaşındaki bir öğretmen, eşsiz bir sanat eseriyle 2026 Dünya Kupası'nı karşılıyor. (HTV) - Ho Chi Minh şehrinde yaşayan 75 yaşındaki emekli bir öğretmen, yumurta kabuklarından yapılmış üç adet 2026 Dünya Kupası maskotunu tamamladı. Kartal Clutch, geyik Maple ve leopar Zayu'dan oluşan bu eserler, sadece yaratıcılığı sergilemekle kalmıyor, aynı zamanda bu olağanüstü sanatçının yıllar içinde geliştirdiği futbol sevgisini de somutlaştırıyor. Kaynak: https://znews.vn/lua-thieu-rui-17000-m-nha-xuong-tai-tphcm-trong-dem-post1658273.html Vietnam.vn'i takip et G o o g l e News 0 Yorum ( 0 ) Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti. Hanoi'deki bir restoran, Tayland Başbakanını karşılamak için hazırlanan 11 yemeği açıkladı. Dong Nai'de durian mevsimi Tuz üreticileri, Ngang Geçidi'nin eteğindeki son tuz tarlalarında geçimlerini sağlamak için kavurucu güneşe katlanıyorlar. Da Lat'ın yıl boyu süren serin ikliminin tadını çıkarın. Vietnam Kültürel Miras Sergisi için seçilen 10 fotoğraf [Fotoğraf] Parti Merkez Komitesi Daimi Komitesi, Ulusal Kalkınmanın Yeni Çağında Güvenlik Koruması konulu Ulusal Bilimsel Konferansa katılıyor. Hanoi'li turistler 62 milyon VND'ye 19 günlük Avrupa seyahatlerinin sırrını açıklıyor. Yangın yeri. Fotoğraf: VTC News . 10 Haziran sabahı, Ho Chi Minh Şehri Polisi'ne bağlı 32. Bölge İtfaiye ve Kurtarma Ekibi (PC07), Ho Chi Minh Şehri, Binh Co Mahallesi, 1. Bölge'de (eski adıyla Tan Uyen, Binh Duong) bulunan GO Co., Ltd. şirketindeki yangının nedenini araştırmak, hasarı değerlendirmek ve incelemek için diğer profesyonel birimlerle koordinasyon içinde çalışmalarına devam etti. Bu şirket ahşap mobilya ve kanepe imalatında uzmanlaşmıştır ve ayrıca bir kağıt laminasyon atölyesine sahiptir. İlk bilgilere göre, 9 Haziran günü saat 22:10 civarında, çalışanlar ve bölge sakinleri şirketin mobilya üretim atölyesinde yangın çıktığını fark etti. Yangın fark edildikten hemen sonra, olay yerindeki itfaiye ekibi ve işçiler taşınabilir yangın söndürücülerle su kullanarak alevleri söndürdüler. Ancak, içerideki büyük miktardaki ahşap ve yanıcı madde nedeniyle yangın hızla yayıldı ve tüm fabrika alanını sardı. Yangının kontrol altına alınamayacak bir boyutta olduğunu anlayan bölge sakinleri durumu yetkililere bildirdi. Saat 22:21'de yangın fabrikayı tamamen sarmıştı. Fotoğraf: VTC News . İhbarı alan 32. Bölge İtfaiye ve Kurtarma Ekibi, yangını söndürmek ve yayılmasını önlemek için bir plan uygulamak üzere olay yerine çok sayıda özel araç ve onlarca subay ve asker gönderdi. Yetkililer ilk etapta yangının her biri yaklaşık 8.500 m²'lik iki atölyede çıktığını ve toplamda yaklaşık 17.000 m²'lik bir alanı etkilediğini belirledi. Yangında en çok yanıcı madde olarak ahşap ve boya bulunduğu için, yangın hızla yayıldı, kontrol altına alma çabaları önemli zorluklar yarattı ve komşu yapılara sıçrama riski oluşturdu. Gece yarısından sonra bile, İtfaiye ve Kurtarma Polisi, çevredeki alanı kontrol altına almak ve korumak için birden fazla itfaiye ekibini görevde tutmaya devam etti. Olayda can kaybı yaşanmadı ve maddi hasar tespit çalışmaları devam ediyor. Yangının nedeni ise hala araştırılıyor.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Konya’da yatak fabrikasında yangın! Kompresör patladı: İtfaiye eri yaralandı Konya’da yatak fabrikasında yangın! Kompresör patladı: İtfaiye eri yaralandı | YEREL HABERLER GZT Konya’da yatak fabrikasında yangın! Kompresör patladı: İtfaiye eri yaralandı | YEREL HABERLER GZT</t>
+          <t>Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti. Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti. Vietnam.vn Ho Chi Minh şehrindeki yetkililer, Binh Co semtindeki bir şirkette çıkan ve yaklaşık 17.000 metrekarelik fabrika alanını yok eden büyük yangın olay yerini kordon altına alarak soruşturma başlattı. Vietnam.vn'i takip et G o o g l e News 0 Yangın yeri. 10 Haziran sabahı, Ho Chi Minh Şehri Polisi'ne bağlı 32. Bölge İtfaiye ve Kurtarma Ekibi (PC07), Ho Chi Minh Şehri, Binh Co Mahallesi, 1. Bölge'de (eski adıyla Tan Uyen, Binh Duong) bulunan GO Co., Ltd. şirketindeki yangının nedenini araştırmak, hasarı değerlendirmek ve incelemek için diğer profesyonel birimlerle koordinasyon içinde çalışmalarına devam etti. Bu şirket ahşap mobilya ve kanepe imalatında uzmanlaşmıştır ve ayrıca bir kağıt laminasyon atölyesine sahiptir. İlk bilgilere göre, 9 Haziran günü saat 22:10 civarında, çalışanlar ve bölge sakinleri şirketin mobilya üretim atölyesinde yangın çıktığını fark etti. Yangın fark edildikten hemen sonra, olay yerindeki itfaiye ekibi ve işçiler taşınabilir yangın söndürücülerle su kullanarak alevleri söndürdüler. Ancak, içerideki büyük miktardaki ahşap ve yanıcı madde nedeniyle yangın hızla yayıldı ve tüm fabrika alanını sardı. Yangının kontrol altına alınamayacak bir boyutta olduğunu anlayan bölge sakinleri durumu yetkililere bildirdi. (PLVN) - Hung Yen İl Emniyet Müdürlüğü, İl Gençlik Birliği ve İl Kadın Birliği ile koordinasyon içinde, dijital vatandaşlara rehberlik etmek ve insanlara Hükümet Projesi 06'yı uygulamada eşlik etmek amacıyla "VNeID ile Dijital Yaz Kampanyası"nın lansman törenini düzenledi. Saat 22:21'de yangın fabrikayı tamamen sarmıştı. Bölge İtfaiye ve Kurtarma Ekibi, yangını söndürmek ve yayılmasını önlemek için bir plan uygulamak üzere olay yerine çok sayıda özel araç ve onlarca subay ve asker gönderdi. Yetkililer ilk etapta yangının her biri yaklaşık 8.500 m²'lik iki atölyede çıktığını ve toplamda yaklaşık 17.000 m²'lik bir alanı etkilediğini belirledi. Yangında en çok yanıcı madde olarak ahşap ve boya bulunduğu için, yangın hızla yayıldı, kontrol altına alma çabaları önemli zorluklar yarattı ve komşu yapılara sıçrama riski oluşturdu. Gece yarısından sonra bile, İtfaiye ve Kurtarma Polisi, çevredeki alanı kontrol altına almak ve korumak için birden fazla itfaiye ekibini görevde tutmaya devam etti. Olayda can kaybı yaşanmadı ve maddi hasar tespit çalışmaları devam ediyor. Yangının nedeni ise hala araştırılıyor. (HTV) - Ho Chi Minh şehrinde yaşayan 75 yaşındaki emekli bir öğretmen, yumurta kabuklarından yapılmış üç adet 2026 Dünya Kupası maskotunu tamamladı. Kartal Clutch, geyik Maple ve leopar Zayu'dan oluşan bu eserler, sadece yaratıcılığı sergilemekle kalmıyor, aynı zamanda bu olağanüstü sanatçının yıllar içinde geliştirdiği futbol sevgisini de somutlaştırıyor. Kaynak: https://znews.vn/lua-thieu-rui-17000-m-nha-xuong-tai-tphcm-trong-dem-post1658273.html Vietnam.vn'i takip et G o o g l e News 0 Yorum ( 0 ) Yangın yeri. Kaynak: https://znews.vn/lua-thieu-rui-17000-m-nha-xuong-tai-tphcm-trong-dem-post1658273.html Bu şirket ahşap mobilya ve kanepe imalatında uzmanlaşmıştır ve ayrıca bir kağıt laminasyon atölyesine sahiptir. Kaynak: https://znews.vn/lua-thieu-rui-17000-m-nha-xuong-tai-tphcm-trong-dem-post1658273.html Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti. ZNews • 10/06/2026 Vietnam.vn'i takip et G o o g l e News 0 Yangın yeri. Kaynak: https://znews.vn/lua-thieu-rui-17000-m-nha-xuong-tai-tphcm-trong-dem-post1658273.html Vietnam.vn'i takip et G o o g l e News 0 Yorum ( 0 ) Ho Chi Minh şehrinde bir fabrikada çıkan yangın, gece boyunca 17.000 m²'lik alanı tamamen yok etti. Hanoi'deki bir restoran, Tayland Başbakanını karşılamak için hazırlanan 11 yemeği açıkladı. Vietnam Kültürel Miras Sergisi için seçilen 10 fotoğraf [Fotoğraf] Parti Merkez Komitesi Daimi Komitesi, Ulusal Kalkınmanın Yeni Çağında Güvenlik Koruması konulu Ulusal Bilimsel Konferansa katılıyor. Hanoi'li turistler 62 milyon VND'ye 19 günlük Avrupa seyahatlerinin sırrını açıklıyor.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNNl9ESnhHUnZQTE04SE9tb3UxQkZDcUMyWEd2UUpVaGtocy1weTNvWWdYQVRiUWdwWHhxc0pnVm10c05OR3JpenNOczVYalFmaFA5QkJaZnlGZzR5YzZxNnpYeTh5WXhLWWVoM1ppdERZd3FsQU5lejBDc2d6WUxEOVBJSjgzdFhHMk93U21MTk14bFQ5STRiSWRmOG5mM1pfeTN4YU9ucnBFUHlzTy1QeXptbGRsZE5Cb0gySXFIVmo?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Konya</t>
-        </is>
-      </c>
+          <t>https://www.vietnam.vn/tr/lua-thieu-rui-17-000-m2-nha-xuong-tai-tp-hcm-trong-dem</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Binh Co Mahallesi</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr"/>
@@ -4225,7 +3681,7 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="n">
-        <v>89.22</v>
+        <v>130</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>13</v>
@@ -4234,7 +3690,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:00</t>
+          <t>2026-06-09 11:13:48</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -4249,12 +3705,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor</t>
+          <t>Fabrika yangını: Ekiplerin müdahalesi sürüyor</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor Mersin Haber</t>
+          <t>Fabrika yangını: Ekiplerin müdahalesi sürüyor urfabaraj.com</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -4264,7 +3720,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>fabrika, tekstil</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4274,34 +3730,26 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Mersin'den haberiniz olsun! Mersin ve ilçelerinden son dakika ve önemli haberler, gelişmeler olayları sunar. Gaziantep Şahinbey'de bir tekstil fabrikasında meydana gelen yangında ekiplerin müdahalesi sürüyor. Olay yerine çok sayıda itfaiye ve sağlık ekibi sevk Mersin'den haberiniz olsun! Mersin ve ilçelerinden son dakika ve önemli haberler, gelişmeler olayları sunar. Yangın, Gaziantep’in 5. Organize Sanayi Bölgesi’nde bulunan bir tekstil fabrikasında patlak verdi. Edinilen bilgilere göre, yangın bilinmeyen bir sebepten dolayı başladı. Durumun ciddiyeti üzerine olay yerine çok sayıda itfaiye, sağlık, AFAD ve polis ekibi yönlendirildi. Yangın alanına ulaşan ekipler, fabrika çevresinde güvenlik önlemleri alarak alevlere müdahale etmeye başladı. Ekiplerin yangını kontrol altına alma çabaları devam ederken, çevredeki vatandaşlar da durumu endişeyle izliyor. Ekipler, yangının büyümesini önlemek için gerekli tüm tedbirleri alarak çalışmalara hızla devam ediyor. Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor Haber Merkezi • 09 Haziran 2026 11:06 • Güncellendi: 09 Haziran 2026 11:11 Gaziantep Şahinbey'de bir tekstil fabrikasında meydana gelen yangında ekiplerin müdahalesi sürüyor. Olay yerine çok sayıda itfaiye ve sağlık ekibi sevk edildi. Haber Merkezi • 09 Haziran 2026 11:06 • Güncellendi: 09 Haziran 2026 11:11 Gaziantep Şahinbey'de bir tekstil fabrikasında meydana gelen yangında ekiplerin müdahalesi sürüyor. Olay yerine çok sayıda itfaiye ve sağlık ekibi sevk edildi. Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor</t>
+          <t>Fabrika yangını: Ekiplerin müdahalesi sürüyor urfabaraj.com</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor Mersin Haber Mersin'den haberiniz olsun! Gaziantep Şahinbey'de bir tekstil fabrikasında meydana gelen yangında ekiplerin müdahalesi sürüyor. Olay yerine çok sayıda itfaiye ve sağlık ekibi sevk Mersin'den haberiniz olsun! Organize Sanayi Bölgesi’nde bulunan bir tekstil fabrikasında patlak verdi. Edinilen bilgilere göre, yangın bilinmeyen bir sebepten dolayı başladı. Durumun ciddiyeti üzerine olay yerine çok sayıda itfaiye, sağlık, AFAD ve polis ekibi yönlendirildi. Yangın alanına ulaşan ekipler, fabrika çevresinde güvenlik önlemleri alarak alevlere müdahale etmeye başladı. Ekiplerin yangını kontrol altına alma çabaları devam ederken, çevredeki vatandaşlar da durumu endişeyle izliyor. Ekipler, yangının büyümesini önlemek için gerekli tüm tedbirleri alarak çalışmalara hızla devam ediyor. Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor Haber Merkezi • 09 Haziran 2026 11:06 • Güncellendi: 09 Haziran 2026 11:11 Gaziantep Şahinbey'de bir tekstil fabrikasında meydana gelen yangında ekiplerin müdahalesi sürüyor. Haber Merkezi • 09 Haziran 2026 11:06 • Güncellendi: 09 Haziran 2026 11:11 Gaziantep Şahinbey'de bir tekstil fabrikasında meydana gelen yangında ekiplerin müdahalesi sürüyor. Gaziantep Şahinbey'de Tekstil Fabrikasında Yangın Çıktı, Ekipler Müdahaleye Devam Ediyor</t>
+          <t>Fabrika yangını: Ekiplerin müdahalesi sürüyor Fabrika yangını: Ekiplerin müdahalesi sürüyor urfabaraj.com Fabrika yangını: Ekiplerin müdahalesi sürüyor urfabaraj.com</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.mersinhaber.com/haber-gaziantep-sahinbeyde-tekstil-fabrikasinda-yangin-cikti-ekipler-mudahaleye-devam-ediyor/664014</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Mersin | Gaziantep</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Şahinbey</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOLXFvZ205SmhRQWUzaU0wYXJTZTNKblk3dVFvQl9qWldkZVJPSXUzMGFKT1N2RVhpZXBwaXpqZFd3WWlRWGQ5TFhTRm9pWVU0UUtISG1odjU2dDU2aVpvSlUyUEo1dFVMalVOUlhYUmRLVmg0R240OUNvOFRBekFvRUNn?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -4309,7 +3757,7 @@
       <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr"/>
@@ -4323,7 +3771,7 @@
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="n">
-        <v>128.25</v>
+        <v>45.84</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>14</v>
@@ -4332,7 +3780,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00:00</t>
+          <t>2026-06-09 18:46:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -4347,12 +3795,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fabrika Yangını: İtfaiye Personeli Şehit Oldu</t>
+          <t>Zonguldak'ta fabrikada yangın var!</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Fabrika Yangını: İtfaiye Personeli Şehit Oldu Kırşehir Çiğdem</t>
+          <t>Zonguldak'ta fabrikada yangın var! YENİ ADIM GAZETESİ</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -4372,12 +3820,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Mobilya imalat fabrikasında çıkan yangına müdahale eden itfaiye eri Mehmet Tekeli, kaldırıldığı hastanede hayatını kaybetti. Mobilya imalat fabrikasında çıkan yangına müdahale eden itfaiye eri Mehmet Tekeli, kaldırıldığı hastanede hayatını kaybetti. Mobilya imalat fabrikasında çıkan yangına müdahale eden itfaiye eri Mehmet Tekeli, kaldırıldığı hastanede hayatını kaybetti. Fabrika Yangını: İtfaiye Personeli Şehit Oldu Mobilya imalat fabrikasında çıkan yangına müdahale eden itfaiye eri Mehmet Tekeli, kaldırıldığı hastanede hayatını kaybetti. 09.06.2026 - 02:00 Yayınlanma 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Mobilya imalat fabrikasında çıkan yangına müdahale eden itfaiye eri Mehmet Tekeli, kaldırıldığı hastanede hayatını kaybetti. Kaman’da Feci İş Kazası: Elektrik Akımına Kapılan İşçi Hayatını Kaybetti İçeriği Görüntüle Konya’nın Karatay ilçesi Çelik ve Ahşap Büro Mobilyacıları Sitesi’ndeki mobilya imalat fabrikasında henüz bilinmeyen nedenle yangın çıktı. İhbar üzerine bölgeye itfaiye, sağlık ve polis ekipleri sevk edildi. Yangına müdahale sırasında ağır yaralanan itfaiye personeli Mehmet Tekeli, kaldırıldığı hastanede yaşamını yitirdi. Konya Büyükşehir Belediye Başkanı Uğur İbrahim Altay, sosyal medya hesabından yaptığı paylaşımda Tekeli için, “Kahraman itfaiyecimiz Mehmet Tekeli şehit oldu. Şehidimize Allah’tan rahmet, ailesine ve mesai arkadaşlarına sabır diliyorum. Mekanı cennet olsun.” ifadelerini kullandı. Konya Valisi İbrahim Akın ve Başkan Altay, bölgeye giderek yangına müdahale çalışmalarını inceledi. Yangın, itfaiye ekiplerinin yoğun çalışmaları sonucu kontrol altına alındı. Kaynak: AA Editörün Seçtiği Trafik lambası direğine çarpan tırdaki 2 kişi yaralandı Bunlar</t>
+          <t>Zonguldak'ın Devrek ilçesindeki Kereste Fabrikasında çıkan yangın büyük korku yaşattı. Zonguldak'ın Devrek ilçesindeki Kereste Fabrikasında çıkan yangın büyük korku yaşattı. Zonguldak'ın Devrek ilçesindeki Kereste Fabrikasında çıkan yangın büyük korku yaşattı. Zonguldak'ta fabrikada yangın var! Zonguldak'ın Devrek ilçesindeki Kereste Fabrikasında çıkan yangın büyük korku yaşattı. Sercan Yıldırım Editör 09.06.2026 - 21:46 Yayınlanma 10.06.2026 - 11:12 Güncelleme 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Zonguldak’ın Devrek ilçesinde faaliyet gösteren Başoğlu Kereste Fabrikası’nda çıkan yangın panik yaşattı. Edinilen bilgiye göre bölgenin önemli sanayi kuruluşları arasında yer alan Başoğlu Kereste Fabrikasında akşam saatlerinde yangın çıktı. Haber verilmesi üzerine olay yerine giden Devrek Belediyesi itfaiye ekipleri zamanında yaptıkları profesyonelce müdahale sonrasında yangını tüm fabrikaya sıçramadan kısa sürede söndürerek kontrol altına aldı. Yangının büyümeden söndürülmesi olası bir facianın önüne geçti. FABRİKA SAHİBİ TEŞEKKÜR ETTİ Fabrıka sahibi Nejdet Başoğlu,Devrek Belediyesi İtfaiye personeli Umut Kanbur, Şener Nekmezci ve Fuat Benli'ye Yangının söndürülmesini sırasında gösterdikleri özverili mücadeleden dolayı teşekkür etti. Kaynak: HABER MERKEZİ Editörün Seçtiği Kahramanların zorlu mesaisi kask kameralarında Editörün Seçtiği Korkutan anız yangını: Ormana sıçramadan söndürüldü Editörün Seçtiği Doğal gaz kutusuna yuva yapan arılar tedirgin etti Editör Hakkında Sercan Yıldırım Bunlar</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Fabrika Yangını: İtfaiye Personeli Şehit Oldu Fabrika Yangını: İtfaiye Personeli Şehit Oldu Kırşehir Çiğdem Mobilya imalat fabrikasında çıkan yangına müdahale eden itfaiye eri Mehmet Tekeli, kaldırıldığı hastanede hayatını kaybetti. Fabrika Yangını: İtfaiye Personeli Şehit Oldu Mobilya imalat fabrikasında çıkan yangına müdahale eden itfaiye eri Mehmet Tekeli, kaldırıldığı hastanede hayatını kaybetti. 09.06.2026 - 02:00 Yayınlanma 1 Dk Okunma Süresi P</t>
+          <t>Zonguldak'ta fabrikada yangın var! Zonguldak'ta fabrikada yangın var! YENİ ADIM GAZETESİ Zonguldak'ın Devrek ilçesindeki Kereste Fabrikasında çıkan yangın büyük korku yaşattı. Zonguldak'ta fabrikada yangın var! Sercan Yıldırım Editör 09.06.2026 - 21:46 Yayınlanma 10.06.2026 - 11:12 Güncelleme 1 Dk Okunma Süresi</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -4387,10 +3835,14 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.kirsehircigdem.com/fabrika-yangini-itfaiye-personeli-sehit-oldu</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>https://www.yeniadimgazetesi.com/zonguldakta-fabrikada-yangin-var</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Zonguldak</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
@@ -4399,7 +3851,7 @@
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr"/>
@@ -4413,7 +3865,7 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="n">
-        <v>60.75</v>
+        <v>63.25</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>15</v>
@@ -4422,27 +3874,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 06:49:00</t>
+          <t>2026-06-09 21:10:00</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep 5. OSB'de Korkutan Yangın: Dev Tekstil Fabrikası Alevlere Teslim Oldu!</t>
+          <t>Şanlıurfa'da MASAK İnceledi, Oyun Bozuldu: 8 Milyar Liralık Para Hacmi Ortaya Çıktı</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep 5. OSB'de Korkutan Yangın: Dev Tekstil Fabrikası Alevlere Teslim Oldu! Olay Medya</t>
+          <t>Şanlıurfa'da MASAK İnceledi, Oyun Bozuldu: 8 Milyar Liralık Para Hacmi Ortaya Çıktı Urfanatik</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -4452,48 +3904,44 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>fabrika, osb, tekstil</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep 5. OSB'de Korkutan Yangın: Dev Tekstil Fabrikası Alevlere Teslim Oldu! Olay Medya</t>
+          <t>Şanlıurfa’nın da aralarında bulunduğu 27 ilde, yıllık 8 milyar liralık para trafiğini yöneten yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı dev operasyonda 72 şüpheli yakalandı. Şanlıurfa’nın da aralarında bulunduğu 27 ilde, yıllık 8 milyar liralık para trafiğini yöneten yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı dev operasyonda 72 şüpheli yakalandı. Şanlıurfa’nın da aralarında bulunduğu 27 ilde, yıllık 8 milyar liralık para trafiğini yöneten yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı dev operasyonda 72 şüpheli yakalandı. Şanlıurfa'da MASAK İnceledi, Oyun Bozuldu: 8 Milyar Liralık Para Hacmi Ortaya Çıktı Şanlıurfa’nın da aralarında bulunduğu 27 ilde, yıllık 8 milyar liralık para trafiğini yöneten yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı dev operasyonda 72 şüpheli yakalandı. İbrahim Çakmak Editör 10.06.2026 - 00:10 Yayınlanma 2 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Antalya Serik Cumhuriyet Başsavcılığı koordinesinde yürütülen ve Mali Suçları Araştırma Kurulu (MASAK) raporlarıyla desteklenen yasa dışı bahis soruşturmasında düğmeye basıldı. Şanlıurfa'nın da aralarında bulunduğu 27 ilde gerçekleştirilen eş zamanlı operasyonlarda, yasa dışı bahis oynatan ve milyarlarca liralık para trafiğini yöneten şebekeye ağır darbe vurularak 72 kişi gözaltına alındı. 8 MİLYAR LİRALIK İŞLEM HACMİ ORTAYA ÇIKTI Bir internet sitesi üzerinden 7258 sayılı " Futbol ve Diğer Spor Müsabakalarında Bahis ve Şans Oyunları Düzenlenmesi Hakkındaki Kanuna " muhalefet edildiğinin tespit edilmesi üzerine İl Emniyet Müdürlüğü ekiplerince geniş çaplı bir inceleme başlattı. Soruşturmanın finansal ayağında devreye giren MASAK, yasa dışı bahis paralarının transferlerine aracılık ettiği değerlendirilen 84 farklı banka hesabını mercek altına aldı. Mali müfettişlerin titiz çalışmaları sonucunda, söz konusu banka hesapları üzerinden sağlanan para akışının yıllık işlem hacminin tam 8 milyar lira olduğu ortaya çıkarıldı. ŞANLIURFA DAHİL 27 İLDE EŞ ZAMANLI OPERASYON DÜZENLENDİ Polis ekiplerinin yürüttüğü teknik ve fiziki takip sonucunda, devasa bahis ağını yöneten 84 şüphelinin Türkiye genelindeki adresleri tek tek belirlendi. Ekiplerin titiz çalışmaları neticesinde şüphelilerin illere göre dağılımı da gün yüzüne çıktı. EŞ ZAMANLI BASKINLARLA 72 ŞÜPHELİ GÖZALTINA ALINDI Soruşturma dosyasında yer alan bilgilere göre şüphelilerin İstanbul'dan 23, Antalya'dan 6, Batman ve Hakkari'den 5'er, Şanlıurfa, Diyarbakır ve Osmaniye'den 4'er kişi olduğu tespit edildi. Ayrıca ağın diğer üyelerinin İzmir, Bursa, Adana, Hatay, Van, Mardin, Mersin, Aydın, Ankara, Samsun, Gaziantep, Nevşehir, Burdur, Kocaeli, Niğde, Isparta, Manisa, Edirne, Muğla ve Siirt gibi geniş bir coğrafyaya yayıldığı saptandı. Kimlikleri ve adresleri kesinleşen şüphelileri adalete teslim etmek amacıyla 27 ilde şafak vakti eş zamanlı olarak düğmeye basıldı. Düzenlenen operasyonlarda, şebeke üyesi olduğu değerlendirilen 72 şüpheli emniyet güçleri tarafından kıskıvrak yakalanarak gözaltına alındı. Dosyada adı geçen 4 şüphelinin halihazırda farklı suçlardan cezaevinde bulunduğu belirlenirken, adreslerinde bulunamayan firari konumdaki 8 şüphelinin yakalanmasına yönelik arama çalışmalarının ise kesintisiz devam ettiği bildirildi. Gözaltına alınan şüphelilerin ikametlerinde ve iş yerlerinde yapılan detaylı aramalarda, yasa dışı bahis organizasyonunun altyapısında kullanıldığı ve para transferlerinin yönetildiği değerlendirilen çok sayıda dijital materyale incelenmek üzere el konuldu. Ele geçirilen bilgisayar, cep telefonu ve sabit diskler ekipler tarafından detaylı incelemeye alındı. Şüphelilerin emniyetteki sorgularının ardından adli makamlara sevk edilecekleri öğrenilirken, olayla ilgili çok yönlü soruşturma sürüyor. Kaynak: Antalya Emniyet Müdürlüğü Editörün Seçtiği Şanlıurfa’da Güncel Akaryakıt Fiyatları 2026: Benzin, Motorin ve LPG Ne Kadar? Editörün Seçtiği 10 Haziran Şanlıurfa Cenaze İlanları 2026: Güncel Bugün Vefat Edenlerin Bilgileri Editörün Seçtiği Dolar Kaç TL Oldu, Euro Ne Kadar? ( 10 Haziran Güncel Döviz Kurları) Editör Hakkında İbrahim Çakmak 2015 yılından itibaren Urfanatik Gazetesi ve Urfanatik internet haber sitesi bünyesinde Gece Muhabiri ve Yazı İşler Sorumlusu olarak görev almakta. Bunlar da ilgini</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep 5. OSB'de Korkutan Yangın: Dev Tekstil Fabrikası Alevlere Teslim Oldu! Gaziantep 5. OSB'de Korkutan Yangın: Dev Tekstil Fabrikası Alevlere Teslim Oldu! Olay Medya OSB'de Korkutan Yangın: Dev Tekstil Fabrikası Alevlere Teslim Oldu!</t>
+          <t>Şanlıurfa'da MASAK İnceledi, Oyun Bozuldu: 8 Milyar Liralık Para Hacmi Ortaya Çıktı Şanlıurfa'da MASAK İnceledi, Oyun Bozuldu: 8 Milyar Liralık Para Hacmi Ortaya Çıktı Urfanatik Şanlıurfa’nın da aralarında bulunduğu 27 ilde, yıllık 8 milyar liralık para trafiğini yöneten yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı dev operasyonda 72 şüpheli yakalandı. Şanlıurfa'da MASAK İnceledi, Oyun Bozuldu: 8 Milyar Liralık Para Hacmi Ortaya Çıktı Şanlıurfa’nın da aralarında bulunduğu 27 ilde, yıllık 8 milyar liralık para trafiğini yöneten yasa dışı bahis şebekesine yönelik düzenlenen eş zamanlı dev operasyonda 72 şüpheli yakalandı. İbrahim Çakmak Editör 10.06.2026 - 00:10 Yayınlanma 2 Dk Okunma Süresi Pa</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.olaymedya.com/asayis/17421326/gaziantep-5-osbde-korkutan-yangin-dev-tekstil-fabrikasi-alevlere-teslim-oldu</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>https://www.urfanatik.com/sanliurfada-masak-inceledi-oyun-bozuldu-8-milyar-liralik-para-hacmi-ortaya-cikti</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Şanlıurfa</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Olay Medya OSB</t>
-        </is>
-      </c>
+      <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr"/>
@@ -4507,7 +3955,7 @@
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="n">
-        <v>101.66</v>
+        <v>105.75</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>16</v>
@@ -4516,27 +3964,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 07:06:00</t>
+          <t>2026-06-10 07:30:00</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep’te tekstil fabrikasında dev yangın! Çok sayıda sağlık v ...</t>
+          <t>Bursa'da 12 yıllık süreç sona erdi! Ünlü tatlı firmasının iflas dosyası kapatıldı</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep’te tekstil fabrikasında dev yangın! Çok sayıda sağlık v ... Referans Gazetesi</t>
+          <t>Bursa'da 12 yıllık süreç sona erdi! Ünlü tatlı firmasının iflas dosyası kapatıldı Bursada Bugün</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -4546,22 +3994,22 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>fabrika, sağlık, tekstil</t>
+          <t>firma</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep Organize Sanayi Bölgesi’nde bir tekstil fabrikasında dev bir yangın çıktı. İşte yangına dair tüm detaylar… Gaziantep Organize Sanayi Bölgesi’nde bir tekstil fabrikasında dev bir yangın çıktı. İşte yangına dair tüm detaylar… Gaziantep Organize Sanayi Bölgesi’nde bir tekstil fabrikasında dev bir yangın çıktı. İşte yangına dair tüm detaylar… Gaziantep’te tekstil fabrikasında dev yangın! Çok sayıda sağlık ve itfaiye ekibi sevk edildi Gaziantep Organize Sanayi Bölgesi’nde bir tekstil fabrikasında dev bir yangın çıktı. İşte yangına dair tüm detaylar… Mehmet FENER Editör 09.06.2026 - 10:06 Yayınlanma 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Havaların ısınmasıyla birlikte yangın tehlikesi de kendini göstermeye başladı. Gaziantep’te önceki süreçte de farklı noktalarda yangınlar yaşanmıştı. Gaziantep Organize Sanayi Bölgesi’nde bir tekstil fabrikasında dev bir yangın çıktı. ÇOK SAYIDA İTFAİYE VE SAĞLIK EKİBİ SEVK EDİLDİ Gaziantep5. Organize Sanayi Bölgesi’nde faaliyet gösteren bir tekstil fabrikasında uğun sabah saatlerinde henüz bilinmeyen bir sebeple yangın çıktı. Edinilen ilk bilgilere göre yangını fark eden fabrika çalışanları kısa sürede 112 Acil Çağrı Merkezi’ne ihbarda bulundu. İhbarın ardından olay yerine çok sayıda emniyet, sağlık ve itfaiye ekibi sevk edildi. Kaynak: Mehmet Fener Editörün Seçtiği Gaziantep FK’nın 2025-2026 sezonu istatistikleri! 3 teknik direktör ve tüm skorlar… Editörün Seçtiği Gaziantep FK’da Draguş-Camara takası bombası Editörün Seçtiği Gaziantep’te Konkordato furyası sürüyor… O firma ile ilgili flaş karar! Editör Hakkında Mehmet FENER Adıyaman Gölbaşı doğumlu. Gaziantep Üniversitesi İletişim Fakültesi Gazetecilik Bölümü’nden mezun oldu. 2019 yılında başladığı gazetecilik mesleğinde, muhabir, grafik tasarım, internet sitesi editörlüğü gibi alanlarda çalıştı. Meslek hayatına Referansgazetesi.com.tr’de yazı işleri müdürü ve “Güncel, Spor ve Teknolojiden Sorumlu Haber Editörü' olarak devam etmektedir. Bunlar da il</t>
+          <t>Bursa'da 2014'te iflas kararı verilen Bağdat Hurma Tatlıcılık şirketinin tasfiye süreci tamamlandı ve iflas dosyası mahkeme kararıyla kapatıldı. Karar, Bursa İflas Dairesi tarafından resmi ilanla duyuruldu. Bursa'da 2014'te iflas kararı verilen Bağdat Hurma Tatlıcılık şirketinin tasfiye süreci tamamlandı ve iflas dosyası mahkeme kararıyla kapatıldı. Karar, Bursa İflas Dairesi tarafından resmi ilanla duyuruldu. Bursa'da 2014'te iflas kararı verilen Bağdat Hurma Tatlıcılık şirketinin tasfiye süreci tamamlandı ve iflas dosyası mahkeme kararıyla kapatıldı. Karar, Bursa İflas Dairesi tarafından resmi ilanla duyuruldu. Bursa'da 12 yıllık süreç sona erdi! Ünlü tatlı firmasının iflas dosyası kapatıldı Bursa'daki Şirket İçin İflas Sürecinde Yeni Karar Mahkeme Kararı Sonrası Dosya Kapatıldı Tasfiye İşlemleri Tamamlandı Bursa'da 2014'te iflas kararı verilen Bağdat Hurma Tatlıcılık şirketinin tasfiye süreci tamamlandı ve iflas dosyası mahkeme kararıyla kapatıldı. Karar, Bursa İflas Dairesi tarafından resmi ilanla duyuruldu. Bursa'da yıllar önce iflas kararı verilen bir gıda şirketine ilişkin dikkat çeken yeni bir gelişme yaşandı. Ticaret hayatında faaliyet gösterdiği dönemde tatlı, pastacılık ve unlu mamul üretimi alanında hizmet veren şirket hakkında yürütülen iflas süreci resmen tamamlandı. Mahkeme kararı doğrultusunda iflas dosyasının kapatıldığı ilan edildi. Bursa İflas Dairesi tarafından yayımlanan resmi ilana göre, faaliyetlerini sonlandıran ve tasfiye sürecine alınan Bağdat Hurma Tatlıcılık Gıda Unlu Ürünler Pastacılık Şekerleme İmalatı Sanayi ve Ticaret Limited Şirketi hakkında önemli bir hukuki süreç sonuçlandı. Uzun yıllardır devam eden iflas işlemlerinin ardından şirketle ilgili yürütülen tasfiye çalışmalarının tamamlandığı ve dosyanın kapatılmasına karar verildiği duyuruldu. Böylece şirketin iflasına ilişkin yasal süreçte yeni bir aşamaya geçilmiş oldu. Söz konusu şirket hakkında iflas kararı, Bursa 5. Asliye Ticaret Mahkemesi tarafından 2014 yılında verilmişti. Mahkemenin kararı doğrultusunda başlayan tasfiye işlemleri yıllar boyunca devam ederken, ilgili süreçlerin tamamlanmasının ardından iflasın kapatılması yönünde karar alındı. İcra ve İflas Kanunu kapsamında yürütülen işlemler sonucunda, şirketin iflas dosyasının kapatılmasına hükmedildi. Kararın ardından Bursa İflas Dairesi tarafından kamuoyuna yönelik ilan yayımlandı. İflas hukukunda dosyanın kapatılması, tasfiye sürecine ilişkin gerekli işlemlerin tamamlanması anlamına geliyor. Bursa'da faaliyet göstermiş olan şirket için yürütülen süreçte de ilgili yasal prosedürlerin sonuçlandırıldığı bildirildi. Gıda ve tatlı üretimi alanında faaliyet gösteren şirketin iflasına ilişkin işlemler, mahkeme ve iflas idaresinin koordinasyonunda yürütülürken, alınan son kararla birlikte dosya resmi olarak kapanmış oldu. Bursa İflas Dairesi tarafından yapılan duyuruda, iflasın kapatılmasına ilişkin kararın İcra ve İflas Kanunu'nun ilgili hükümleri doğrultusunda ilan edildiği belirtildi. Böylece yıllar önce başlayan hukuki süreç, resmi kayıtlar açısından tamamlanmış oldu. Diğer Bursa Haberleri - Bölge Haberleri için tıklayın Bir parti için daha mutlak butlan kararı! Kongre iptal edildi Bursa'da konağın altından geçen yol ilgi odağı oldu! Survivor'da final öncesi dengeleri sarsan gelişme! İkinci eleme adayı netleşti Nilüfer'de imar hareketliliği: Yaylacık'taki parsel düzenlemesi askıya çıktı Bursa'nın tek havalimanı için dikkat çeken çağrı! Kapasitenin yüzde 90'ı kullanılmıyor... Tartışma yaratan fotoğrafla ilgili gerçek ortaya çıktı!</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep’te tekstil fabrikasında dev yangın! Çok sayıda sağlık v ... Gaziantep’te tekstil fabrikasında dev yangın! Çok sayıda sağlık v ... Referans Gazetesi Gaziantep Organize Sanayi Bölgesi’nde bir tekstil fabrikasında dev bir yangın çıktı. İşte yangına dair tüm detaylar… Gaziantep Organize Sanayi Bölgesi’nde bir tekstil fabrikasında dev bir yangın çıktı. İşte yangına dair tüm detaylar… Gaziantep’te tekstil fabrikasında dev yangın! Çok sayıda sağlık ve itfaiye ekibi sevk edildi Gaziantep Organize Sanayi Bölgesi’nde bir tekstil fabrikasında dev bir yangın çıktı. İşte yangına dair tüm detaylar… Mehmet FENER Editör 09.06.2026 - 10:06 Yayınlanma 1 Dk Okunma Süresi Payl</t>
+          <t>Bursa'da 12 yıllık süreç sona erdi! Ünlü tatlı firmasının iflas dosyası kapatıldı Bursa'da 12 yıllık süreç sona erdi! Ünlü tatlı firmasının iflas dosyası kapatıldı Bursada Bugün Bursa'da 2014'te iflas kararı verilen Bağdat Hurma Tatlıcılık şirketinin tasfiye süreci tamamlandı ve iflas dosyası mahkeme kararıyla kapatıldı. Karar, Bursa İflas Dairesi tarafından resmi ilanla duyuruldu. Bursa'da 12 yıllık süreç sona erdi! Ünlü tatlı firmasının iflas dosyası kapatıldı Bursa'daki Şirket İçin İflas Sürecinde Yeni Karar Mahkeme Kararı Sonrası Dosya Kapatıldı Tasfiye İşlemleri Tamamlandı Bursa'da 2014'te iflas kararı verilen Bağdat Hurma Tatlıcılık şirketinin tasfiye süreci tamamlandı ve iflas dosyası mahkeme kararıyla kapatıldı. Bursa'da yıllar önce iflas kararı verilen bir gıda şirketine ilişkin dikkat çeken yeni bir gelişme yaşandı. Ticaret hayatında faaliyet gösterdiği dönemde tatlı, pastacılık ve unlu mamul üretimi alanında hizmet veren şirket hakkında yürütülen iflas süreci resmen tamamlandı. Mahkeme kararı doğrultusunda iflas dosyasının kapatıldığı ilan edildi. Bursa İflas Dairesi tarafından yayımlanan resmi ilana göre, faaliyetlerini sonlandıran ve tasfiye sürecine alınan Bağdat Hurma Tatlıcılık Gıda Unlu Ürünler Pastacılık Şekerleme İmalatı Sanayi ve Ticaret Limited Şirketi hakkında önemli bir hukuki süreç sonuçlandı. Uzun yıllardır devam eden iflas işlemlerinin ardından şirketle ilgili yürütülen tasfiye çalışmalarının tamamlandığı ve dosyanın kapatılmasına karar verildiği duyuruldu. Böylece şirketin iflasına ilişkin yasal süreçte yeni bir aşamaya geçilmiş oldu. Söz konusu şirket hakkında iflas kararı, Bursa 5. Asliye Ticaret Mahkemesi tarafından 2014 yılında verilmişti. Mahkemenin kararı doğrultusunda başlayan tasfiye işlemleri yıllar boyunca devam ederken, ilgili süreçlerin tamamlanmasının ardından iflasın kapatılması yönünde karar alındı. İcra ve İflas Kanunu kapsamında yürütülen işlemler sonucunda, şirketin iflas dosyasının kapatılmasına hükmedildi. Kararın ardından Bursa İflas Dairesi tarafından kamuoyuna yönelik ilan yayımlandı. İflas hukukunda dosyanın kapatılması, tasfiye sürecine ilişkin gerekli işlemlerin tamamlanması anlamına geliyor. Bursa'da faaliyet göstermiş olan şirket için yürütülen süreçte de ilgili yasal prosedürlerin sonuçlandırıldığı bildirildi. Gıda ve tatlı üretimi alanında faaliyet gösteren şirketin iflasına ilişkin işlemler, mahkeme ve iflas idaresinin koordinasyonunda yürütülürken, alınan son kararla birlikte dosya resmi olarak kapanmış oldu. Bursa İflas Dairesi tarafından yapılan duyuruda, iflasın kapatılmasına ilişkin kararın İcra ve İflas Kanunu'nun ilgili hükümleri doğrultusunda ilan edildiği belirtildi. Böylece yıllar önce başlayan hukuki süreç, resmi kayıtlar açısından tamamlanmış oldu. Diğer Bursa Haberleri - Bölge Haberleri için tıklayın Bir parti için daha mutlak butlan kararı! Kongre iptal edildi Bursa'da konağın altından geçen yol ilgi odağı oldu! İkinci eleme adayı netleşti Nilüfer'de imar hareketliliği: Yaylacık'taki parsel düzenlemesi askıya çıktı Bursa'nın tek havalimanı için dikkat çeken çağrı! Kapasitenin yüzde 90'ı kullanılmıyor...</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -4571,27 +4019,27 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.referansgazetesi.com.tr/gaziantepte-tekstil-fabrikasinda-dev-yangin-cok-sayida-saglik-ve-itfaiye-ekibi-sevk-edildi</t>
+          <t>https://www.bursadabugun.com/haber/bursa-da-12-yillik-surec-sona-erdi-unlu-tatli-firmasinin-iflas-dosyasi-kapatildi-1927593.html</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Gaziantep Organize Sanayi</t>
-        </is>
-      </c>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Nilüfer</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr"/>
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr"/>
@@ -4605,7 +4053,7 @@
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="n">
-        <v>119.25</v>
+        <v>123.25</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>17</v>
@@ -4614,27 +4062,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:12:00</t>
+          <t>2026-06-09 11:25:54</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı</t>
+          <t>Türk otomotiv devi Güçlü Zirve iflas etti: Yıllardır sektöre yön veriyordu</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı Konya Bakış</t>
+          <t>Türk otomotiv devi Güçlü Zirve iflas etti: Yıllardır sektöre yön veriyordu Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -4644,22 +4092,18 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>otomotiv</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Konya’nın Karatay ilçesinde faaliyet gösteren bir mobilya fabrikasında çıkan yangın, ekipleri alarma geçirdi. Sanayi bölgesinde yükselen yoğun dumanlar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Konya’nın Karatay ilçesinde faaliyet gösteren bir mobilya fabrikasında çıkan yangın, ekipleri alarma geçirdi. Sanayi bölgesinde yükselen yoğun dumanlar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Konya’nın Karatay ilçesinde faaliyet gösteren bir mobilya fabrikasında çıkan yangın, ekipleri alarma geçirdi. Sanayi bölgesinde yükselen yoğun dumanlar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı Konya’nın Karatay ilçesinde faaliyet gösteren bir mobilya fabrikasında çıkan yangın, ekipleri alarma geçirdi. Sanayi bölgesinde yükselen yoğun dumanlar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Yangına müdahale eden ekipler alevleri kontrol altına almak için yoğun çaba harcarken, söndürme çalışmaları sırasında bir itfaiyecinin içeride mahsur kaldığı bilgisi üzerine bölgede hareketli anlar yaşandı. Ekiplerin müdahalesi sonucu içeride kalan itfaiyeci yaralı olarak kurtarılarak sağlık ekiplerine teslim edildi. İlk müdahalesi olay yerinde yapılan itfaiyeci, ambulansla hastaneye kaldırıldı. Yangın sırasında bir kişinin de dumandan etkilendiği öğrenilirken, sağlık ekipleri tarafından gerekli müdahale yapıldı. Fabrikada bulunan bazı çalışanların ise alevlerin büyümesi üzerine içerideki malzemeleri dışarı çıkarmaya çalıştığı belirtildi. İlk belirlemelere göre fabrikanın dış cephesinde bulunan sandviç paneller ve iç kısımdaki yalıtım malzemelerinin tutuşması, alevlerin kısa sürede büyümesine neden oldu. Bu durum söndürme çalışmalarını da zorlaştırdı. Polis ekipleri çevrede güvenlik önlemleri alırken, itfaiye ekiplerinin yangını tamamen kontrol altına almak için çalışmaları bir süre daha devam etti. Olayla ilgili inceleme başlatıldı. HABER MERKEZİ Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı Konya’nın Karatay ilçesinde faaliyet gösteren bir mobilya fabrikasında çıkan yangın, ekipleri alarma geçirdi. Sanayi bölgesinde yükselen yoğun dumanlar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Yangına müdahale eden ekipler alevleri kontrol altına almak için yoğun çaba harcarken, söndürme çalışmaları sırasında bir itfaiyecinin içeride mahsur kaldığı bilgisi üzerine bölgede hareketli anlar yaşandı. Ekiplerin müdahalesi sonucu içeride kalan itfaiyeci yaralı olarak kurtarılarak sağlık ekiplerine teslim edildi. İlk müdahalesi olay yerinde yapılan itfaiyeci, ambulansla hastaneye kaldırıldı. Yangın sırasında bir kişinin de dumandan etkilendiği öğrenilirken, sağlık ekipleri tarafından gerekli müdahale yapıldı. Fabrikada bulunan bazı çalışanların ise alevlerin büyümesi üzerine içerideki malzemeleri dışarı çıkarmaya çalıştığı belirtildi. İlk belirlemelere göre fabrikanın dış cephesinde bulunan sandviç paneller ve iç kısımdaki yalıtım malzemelerinin tutuşması, alevlerin kısa sürede büyümesine neden oldu. Bu durum söndürme çalışmalarını da zorlaştırdı. Polis ekipleri çevrede güvenlik önlemleri alırken, itfaiye ekiplerinin yangını tamamen kontrol altına almak için çalışmaları bir süre daha devam etti. Olayla ilgili inceleme başlatıldı. HABER MERKEZİ HABERE YORUM KAT UYARI: Küfür, hakaret, rencide edici cümleler veya imalar, inançlara saldırı içeren, imla kuralları ile yazılmamış, Türkçe karakter kullanılmayan ve büyük harflerle yazılmış yoruml</t>
+          <t>Antalya’da faaliyet gösteren otomotiv bakım ve yedek parça firması, Güçlü Zirve Ağır Vasıta Yedek Parça Sanayi ve Ticaret Limited Şirketi, yaşadığı mali krizden çıkamayarak iflas etti. Mahkeme, konkordato talebini reddederken şirket için tasfiye süreci başladı.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı Konya Bakış Konya’nın Karatay ilçesinde faaliyet gösteren bir mobilya fabrikasında çıkan yangın, ekipleri alarma geçirdi. Sanayi bölgesinde yükselen yoğun dumanlar üzerine olay yerine çok sayıda itfaiye, sağlık ve polis ekibi sevk edildi. Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı Konya’nın Karatay ilçesinde faaliyet gösteren bir mobilya fabrikasında çıkan yangın, ekipleri alarma geçirdi. Yangına müdahale eden ekipler alevleri kontrol altına almak için yoğun çaba harcarken, söndürme çalışmaları sırasında bir itfaiyecinin içeride mahsur kaldığı bilgisi üzerine bölgede hareketli anlar yaşandı. Ekiplerin müdahalesi sonucu içeride kalan itfaiyeci yaralı olarak kurtarılarak sağlık ekiplerine teslim edildi. İlk müdahalesi olay yerinde yapılan itfaiyeci, ambulansla hastaneye kaldırıldı. Yangın sırasında bir kişinin de dumandan etkilendiği öğrenilirken, sağlık ekipleri tarafından gerekli müdahale yapıldı. Fabrikada bulunan bazı çalışanların ise alevlerin büyümesi üzerine içerideki malzemeleri dışarı çıkarmaya çalıştığı belirtildi. İlk belirlemelere göre fabrikanın dış cephesinde bulunan sandviç paneller ve iç kısımdaki yalıtım malzemelerinin tutuşması, alevlerin kısa sürede büyümesine neden oldu. Bu durum söndürme çalışmalarını da zorlaştırdı. Polis ekipleri çevrede güvenlik önlemleri alırken, itfaiye ekiplerinin yangını tamamen kontrol altına almak için çalışmaları bir süre daha devam etti. Olayla ilgili inceleme başlatıldı. HABER MERKEZİ Konya’daki fabrika yangınında korku dolu anlar: Yaralı itfaiyeci hastaneye kaldırıldı Konya’nın Karatay ilçesinde faaliyet gösteren bir mobilya fabrikasında çıkan yangın, ekipleri alarma geçirdi.</t>
+          <t>Türk otomotiv devi Güçlü Zirve iflas etti: Yıllardır sektöre yön veriyordu Türk otomotiv devi Güçlü Zirve iflas etti: Yıllardır sektöre yön veriyordu Yeniçağ Gazetesi Antalya’da faaliyet gösteren otomotiv bakım ve yedek parça firması, Güçlü Zirve Ağır Vasıta Yedek Parça Sanayi ve Ticaret Limited Şirketi, yaşadığı mali krizden çıkamayarak iflas etti. Mahkeme, konkordato talebini reddederken şirket için tasfiye süreci başladı.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -4669,19 +4113,15 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://konyabakis.com/yerel/konyadaki-fabrika-yangininda-korku-dolu-anlar-yarali-itfaiyeci-hastaneye-kaldirildi-35210h</t>
+          <t>https://www.yenicaggazetesi.com/turk-otomotiv-devi-guclu-zirve-iflas-etti-yillardir-sektore-yon-veriyordu-1038665h.htm</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Karatay</t>
-        </is>
-      </c>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -4689,7 +4129,7 @@
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr"/>
@@ -4703,7 +4143,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="n">
-        <v>125.75</v>
+        <v>88.36</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>18</v>
@@ -4712,27 +4152,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 13:32:00</t>
+          <t>2026-06-09 09:03:28</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Konya’da fabrikada yangın! Siyah dumanlar gökyüzünü kapladı</t>
+          <t>Almanya'nın önde gelen araç kiralama şirketi Nextmove iflas etti</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Konya’da fabrikada yangın! Siyah dumanlar gökyüzünü kapladı yenikonya.com.tr</t>
+          <t>Almanya'nın önde gelen araç kiralama şirketi Nextmove iflas etti Patronlar Dünyası</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -4742,39 +4182,